--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -821,31 +821,50 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="A4" s="8" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>51.875</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>53.95999908447266</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>50.04000091552734</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>50.72000122070312</v>
+      </c>
       <c r="F4" s="10">
         <f>IFERROR((E4/E3)-1,"")</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
+        <v>41.29999923706055</v>
+      </c>
       <c r="H4" s="10">
         <f>IFERROR((G4/G3)-1,"")</f>
         <v/>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>47.31499862670898</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>45.66999816894531</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>45.93000030517578</v>
+      </c>
       <c r="M4" s="23">
         <f>IFERROR((L4/L3)-1,"")</f>
         <v/>
       </c>
-      <c r="N4" s="10">
-        <f>IFERROR((M4/M3)-1,"")</f>
-        <v/>
+      <c r="N4" s="10" t="n">
+        <v>75.73999786376953</v>
       </c>
       <c r="O4" s="23">
         <f>IFERROR((N4/N3)-1,"")</f>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -816,28 +816,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="A4" s="8" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>51.875</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>53.95999908447266</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>50.04000091552734</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>50.72000122070312</v>
+      </c>
       <c r="F4" s="10">
         <f>IFERROR((E4/E3)-1,"")</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
+        <v>41.29999923706055</v>
+      </c>
       <c r="H4" s="10">
         <f>IFERROR((G4/G3)-1,"")</f>
         <v/>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>47.31499862670898</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>45.66999816894531</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>45.93000030517578</v>
+      </c>
       <c r="M4" s="9" t="n"/>
-      <c r="N4" s="10">
-        <f>IFERROR((M4/M3)-1,"")</f>
-        <v/>
+      <c r="N4" s="10" t="n">
+        <v>75.73999786376953</v>
       </c>
       <c r="O4" s="9" t="n"/>
       <c r="P4" s="11">

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -818,31 +818,50 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="A4" s="8" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>51.875</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>53.95999908447266</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>50.04000091552734</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>50.72000122070312</v>
+      </c>
       <c r="F4" s="10">
         <f>IF(OR(B4="",E4=""),"",IF(B4=0,"",(E4-B4)/B4))</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
+        <v>41.29999923706055</v>
+      </c>
       <c r="H4" s="10">
         <f>""</f>
         <v/>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>47.31499862670898</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>45.66999816894531</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>45.93000030517578</v>
+      </c>
       <c r="M4" s="23">
         <f>IF(OR(I4="",L4=""),"",IF(I4=0,"",(L4-I4)/I4))</f>
         <v/>
       </c>
-      <c r="N4" s="10">
-        <f>IFERROR((M4/M3)-1,"")</f>
-        <v/>
+      <c r="N4" s="10" t="n">
+        <v>75.73999786376953</v>
       </c>
       <c r="O4" s="23">
         <f>""</f>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -824,29 +824,51 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="A4" s="8" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>51.875</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>53.95999908447266</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>50.04000091552734</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>50.72000122070312</v>
+      </c>
       <c r="F4" s="10">
         <f>IF(OR(B4="",E4=""),"",IF(B4=0,"",(E4-B4)/B4))</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
+        <v>41.29999923706055</v>
+      </c>
       <c r="H4" s="10">
         <f>""</f>
         <v/>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>47.31499862670898</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>45.66999816894531</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>45.93000030517578</v>
+      </c>
       <c r="M4" s="23">
         <f>IF(OR(I4="",L4=""),"",IF(I4=0,"",(L4-I4)/I4))</f>
         <v/>
       </c>
-      <c r="N4" s="25" t="inlineStr"/>
+      <c r="N4" s="25" t="n">
+        <v>75.73999786376953</v>
+      </c>
       <c r="O4" s="23">
         <f>""</f>
         <v/>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -935,31 +935,50 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="A4" s="8" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>51.875</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>53.95999908447266</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>50.04000091552734</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>50.72000122070312</v>
+      </c>
       <c r="F4" s="10">
         <f>IF(OR(B4="",E4=""),"",IF(B4=0,"",(E4-B4)/B4))</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
+        <v>41.29999923706055</v>
+      </c>
       <c r="H4" s="10">
         <f>""</f>
         <v/>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>47.31499862670898</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>45.66999816894531</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>45.93000030517578</v>
+      </c>
       <c r="M4" s="23">
         <f>IF(OR(I4="",L4=""),"",IF(I4=0,"",(L4-I4)/I4))</f>
         <v/>
       </c>
-      <c r="N4" s="27">
-        <f>IFERROR((M4/M3)-1,"")</f>
-        <v/>
+      <c r="N4" s="27" t="n">
+        <v>75.73999786376953</v>
       </c>
       <c r="O4" s="23">
         <f>""</f>
@@ -36017,7 +36036,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
@@ -36062,7 +36080,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper_Trades" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Paper_Trades" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -1017,31 +1017,50 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="A4" s="8" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>51.875</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>53.95999908447266</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>50.04000091552734</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>50.72000122070312</v>
+      </c>
       <c r="F4" s="10">
         <f>IF(OR(B4="",E4=""),"",IF(B4=0,"",(E4-B4)/B4))</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
+        <v>41.29999923706055</v>
+      </c>
       <c r="H4" s="10">
         <f>""</f>
         <v/>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>47.31499862670898</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>45.66999816894531</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>45.93000030517578</v>
+      </c>
       <c r="M4" s="23">
         <f>IF(OR(I4="",L4=""),"",IF(I4=0,"",(L4-I4)/I4))</f>
         <v/>
       </c>
-      <c r="N4" s="27">
-        <f>IFERROR((M4/M3)-1,"")</f>
-        <v/>
+      <c r="N4" s="27" t="n">
+        <v>75.73999786376953</v>
       </c>
       <c r="O4" s="23">
         <f>""</f>
@@ -1103,7 +1122,9 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="AD4" s="13" t="n"/>
+      <c r="AD4" s="13" t="n">
+        <v>593.719970703125</v>
+      </c>
       <c r="AE4" s="24">
         <f>""</f>
         <v/>
@@ -1124,7 +1145,9 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="AJ4" s="13" t="n"/>
+      <c r="AJ4" s="13" t="n">
+        <v>387.3299865722656</v>
+      </c>
       <c r="AK4" s="24">
         <f>""</f>
         <v/>
@@ -52645,7 +52668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -52774,7 +52797,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
@@ -52819,7 +52841,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
@@ -53004,7 +53025,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
@@ -53012,8 +53032,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A38:B38"/>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Trades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Paper_Trades" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper_Trades" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -184,6 +184,12 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -709,7 +715,7 @@
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>v6 upgrades: QQQ and SMH signal tracking, market trend filter, paper-trade sheet, and equity-curve framework.</t>
+          <t>v6 upgrades: QQQ/SMH signal tracking, trend filter, paper-trade sheet, and equity curve framework.</t>
         </is>
       </c>
     </row>
@@ -761,13 +767,13 @@
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -803,7 +809,7 @@
           <t>Leadership</t>
         </is>
       </c>
-      <c r="AD2" s="25" t="inlineStr">
+      <c r="AD2" s="34" t="inlineStr">
         <is>
           <t>Signal ETFs</t>
         </is>
@@ -955,112 +961,93 @@
           <t>Bear Spread 5D</t>
         </is>
       </c>
-      <c r="AD3" s="26" t="inlineStr">
+      <c r="AD3" s="35" t="inlineStr">
         <is>
           <t>QQQ Close</t>
         </is>
       </c>
-      <c r="AE3" s="26" t="inlineStr">
+      <c r="AE3" s="35" t="inlineStr">
         <is>
           <t>QQQ Daily %</t>
         </is>
       </c>
-      <c r="AF3" s="26" t="inlineStr">
+      <c r="AF3" s="35" t="inlineStr">
         <is>
           <t>QQQ 3D %</t>
         </is>
       </c>
-      <c r="AG3" s="26" t="inlineStr">
+      <c r="AG3" s="35" t="inlineStr">
         <is>
           <t>QQQ 5D %</t>
         </is>
       </c>
-      <c r="AH3" s="26" t="inlineStr">
+      <c r="AH3" s="35" t="inlineStr">
         <is>
           <t>QQQ 20D MA</t>
         </is>
       </c>
-      <c r="AI3" s="26" t="inlineStr">
+      <c r="AI3" s="35" t="inlineStr">
         <is>
           <t>QQQ Trend</t>
         </is>
       </c>
-      <c r="AJ3" s="26" t="inlineStr">
+      <c r="AJ3" s="35" t="inlineStr">
         <is>
           <t>SMH Close</t>
         </is>
       </c>
-      <c r="AK3" s="26" t="inlineStr">
+      <c r="AK3" s="35" t="inlineStr">
         <is>
           <t>SMH Daily %</t>
         </is>
       </c>
-      <c r="AL3" s="26" t="inlineStr">
+      <c r="AL3" s="35" t="inlineStr">
         <is>
           <t>SMH 3D %</t>
         </is>
       </c>
-      <c r="AM3" s="26" t="inlineStr">
+      <c r="AM3" s="35" t="inlineStr">
         <is>
           <t>SMH 5D %</t>
         </is>
       </c>
-      <c r="AN3" s="26" t="inlineStr">
+      <c r="AN3" s="35" t="inlineStr">
         <is>
           <t>SMH 20D MA</t>
         </is>
       </c>
-      <c r="AO3" s="26" t="inlineStr">
+      <c r="AO3" s="35" t="inlineStr">
         <is>
           <t>SMH Trend</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>51.875</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>53.95999908447266</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>50.04000091552734</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>50.72000122070312</v>
-      </c>
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
       <c r="F4" s="10">
         <f>IF(OR(B4="",E4=""),"",IF(B4=0,"",(E4-B4)/B4))</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>41.29999923706055</v>
-      </c>
+      <c r="G4" s="9" t="n"/>
       <c r="H4" s="10">
         <f>""</f>
         <v/>
       </c>
-      <c r="I4" s="9" t="n">
-        <v>47.31499862670898</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>45.66999816894531</v>
-      </c>
-      <c r="L4" s="9" t="n">
-        <v>45.93000030517578</v>
-      </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="9" t="n"/>
       <c r="M4" s="23">
         <f>IF(OR(I4="",L4=""),"",IF(I4=0,"",(L4-I4)/I4))</f>
         <v/>
       </c>
-      <c r="N4" s="27" t="n">
-        <v>75.73999786376953</v>
+      <c r="N4" s="27">
+        <f>IFERROR((M4/M3)-1,"")</f>
+        <v/>
       </c>
       <c r="O4" s="23">
         <f>""</f>
@@ -1122,9 +1109,7 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="AD4" s="13" t="n">
-        <v>593.719970703125</v>
-      </c>
+      <c r="AD4" s="13" t="n"/>
       <c r="AE4" s="24">
         <f>""</f>
         <v/>
@@ -1145,9 +1130,7 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="AJ4" s="13" t="n">
-        <v>387.3299865722656</v>
-      </c>
+      <c r="AJ4" s="13" t="n"/>
       <c r="AK4" s="24">
         <f>""</f>
         <v/>
@@ -52668,7 +52651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -52708,44 +52691,44 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>QQQ Daily %</t>
+          <t>SOXL 1D %</t>
         </is>
       </c>
       <c r="B4" s="10">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AE:AE&lt;&gt;""),Daily_Data!AE:AE),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!F:F&lt;&gt;""),Daily_Data!F:F),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>QQQ 3D %</t>
+          <t>SOXS 1D %</t>
         </is>
       </c>
       <c r="B5" s="10">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AF:AF&lt;&gt;""),Daily_Data!AF:AF),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!H:H&lt;&gt;""),Daily_Data!H:H),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>QQQ 5D %</t>
+          <t>TQQQ 1D %</t>
         </is>
       </c>
       <c r="B6" s="10">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AG:AG&lt;&gt;""),Daily_Data!AG:AG),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!M:M&lt;&gt;""),Daily_Data!M:M),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>QQQ Trend</t>
+          <t>SQQQ 1D %</t>
         </is>
       </c>
       <c r="B7" s="10">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AI:AI&lt;&gt;""),Daily_Data!AI:AI),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!O:O&lt;&gt;""),Daily_Data!O:O),"")</f>
         <v/>
       </c>
     </row>
@@ -52756,285 +52739,307 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>SMH Daily %</t>
+          <t>SOXL 3D %</t>
         </is>
       </c>
       <c r="B9" s="10">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AK:AK&lt;&gt;""),Daily_Data!AK:AK),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!P:P&lt;&gt;""),Daily_Data!P:P),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>SMH 3D %</t>
+          <t>SOXS 3D %</t>
         </is>
       </c>
       <c r="B10" s="10">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AL:AL&lt;&gt;""),Daily_Data!AL:AL),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!R:R&lt;&gt;""),Daily_Data!R:R),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>SMH 5D %</t>
+          <t>TQQQ 3D %</t>
         </is>
       </c>
       <c r="B11" s="10">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AM:AM&lt;&gt;""),Daily_Data!AM:AM),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!T:T&lt;&gt;""),Daily_Data!T:T),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>SMH Trend</t>
+          <t>SQQQ 3D %</t>
         </is>
       </c>
       <c r="B12" s="10">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AO:AO&lt;&gt;""),Daily_Data!AO:AO),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!V:V&lt;&gt;""),Daily_Data!V:V),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>SOXL 1D %</t>
+          <t>SOXL 5D %</t>
         </is>
       </c>
       <c r="B14" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!F:F&lt;&gt;""),Daily_Data!F:F),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!Q:Q&lt;&gt;""),Daily_Data!Q:Q),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>SOXS 1D %</t>
+          <t>SOXS 5D %</t>
         </is>
       </c>
       <c r="B15" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!H:H&lt;&gt;""),Daily_Data!H:H),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!S:S&lt;&gt;""),Daily_Data!S:S),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>TQQQ 1D %</t>
+          <t>TQQQ 5D %</t>
         </is>
       </c>
       <c r="B16" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!M:M&lt;&gt;""),Daily_Data!M:M),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!U:U&lt;&gt;""),Daily_Data!U:U),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>SQQQ 1D %</t>
+          <t>SQQQ 5D %</t>
         </is>
       </c>
       <c r="B17" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!O:O&lt;&gt;""),Daily_Data!O:O),"")</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!W:W&lt;&gt;""),Daily_Data!W:W),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>SOXL 3D %</t>
+          <t>Daily Direction Score</t>
         </is>
       </c>
-      <c r="B19" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!P:P&lt;&gt;""),Daily_Data!P:P),"")</f>
+      <c r="B19" s="31">
+        <f>IF(OR(B6="",B7=""),"",IF(AND(B6&gt;0,B7&lt;0),1,IF(AND(B6&lt;0,B7&gt;0),-1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>SOXS 3D %</t>
+          <t>3D Direction Score</t>
         </is>
       </c>
-      <c r="B20" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!R:R&lt;&gt;""),Daily_Data!R:R),"")</f>
+      <c r="B20" s="31">
+        <f>IF(OR(B11="",B12=""),"",IF(AND(B11&gt;0,B12&lt;0),1,IF(AND(B11&lt;0,B12&gt;0),-1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>TQQQ 3D %</t>
+          <t>5D Direction Score</t>
         </is>
       </c>
-      <c r="B21" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!T:T&lt;&gt;""),Daily_Data!T:T),"")</f>
+      <c r="B21" s="31">
+        <f>IF(OR(B16="",B17=""),"",IF(AND(B16&gt;0,B17&lt;0),1,IF(AND(B16&lt;0,B17&gt;0),-1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>SQQQ 3D %</t>
+          <t>Total Direction Score</t>
         </is>
       </c>
-      <c r="B22" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!V:V&lt;&gt;""),Daily_Data!V:V),"")</f>
+      <c r="B22" s="31">
+        <f>SUM(N(B19),N(B20),N(B21))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="32" t="n"/>
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Market Direction</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>IF(COUNTA(B19:B21)=0,"Need More Data",IF(B22&gt;0,"Bull",IF(B22&lt;0,"Bear","Mixed")))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>SOXL 5D %</t>
+          <t>Bull Leadership Score</t>
         </is>
       </c>
-      <c r="B24" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!Q:Q&lt;&gt;""),Daily_Data!Q:Q),"")</f>
+      <c r="B24" s="33">
+        <f>IF(B23="Need More Data","",IF(OR(B4="",B6=""),0,IF(B4&gt;B6,1,IF(B4&lt;B6,-1,0)))+IF(OR(B9="",B11=""),0,IF(B9&gt;B11,1,IF(B9&lt;B11,-1,0)))+IF(OR(B14="",B16=""),0,IF(B14&gt;B16,1,IF(B14&lt;B16,-1,0))))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
         <is>
-          <t>SOXS 5D %</t>
+          <t>Bear Leadership Score</t>
         </is>
       </c>
-      <c r="B25" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!S:S&lt;&gt;""),Daily_Data!S:S),"")</f>
+      <c r="B25" s="33">
+        <f>IF(B23="Need More Data","",IF(OR(B5="",B7=""),0,IF(B5&gt;B7,1,IF(B5&lt;B7,-1,0)))+IF(OR(B10="",B12=""),0,IF(B10&gt;B12,1,IF(B10&lt;B12,-1,0)))+IF(OR(B15="",B17=""),0,IF(B15&gt;B17,1,IF(B15&lt;B17,-1,0))))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>TQQQ 5D %</t>
+          <t>Sector Leadership</t>
         </is>
       </c>
-      <c r="B26" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!U:U&lt;&gt;""),Daily_Data!U:U),"")</f>
+      <c r="B26" s="32">
+        <f>IF(B23="Need More Data","Need More Data",IF(B23="Bull",IF(B24&gt;0,"Semiconductors Leading",IF(B24&lt;0,"Tech Leading","Mixed")),IF(B23="Bear",IF(B25&gt;0,"Semiconductors Weakest",IF(B25&lt;0,"Tech Weakest","Mixed")),"Mixed")))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>SQQQ 5D %</t>
+          <t>Trade ETF</t>
         </is>
       </c>
-      <c r="B27" s="30">
-        <f>IFERROR(LOOKUP(2,1/(Daily_Data!W:W&lt;&gt;""),Daily_Data!W:W),"")</f>
+      <c r="B27" s="32">
+        <f>IF(B23="Need More Data","WAIT",IF(B23="Bull",IF(B26="Semiconductors Leading","SOXL",IF(B26="Tech Leading","TQQQ","NO TRADE")),IF(B23="Bear",IF(B26="Semiconductors Weakest","SOXS",IF(B26="Tech Weakest","SQQQ","NO TRADE")),"NO TRADE")))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="32" t="n"/>
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B28" s="32">
+        <f>IF(B27="WAIT","Need More Data",IF(B27="NO TRADE","Weak",IF(AND(ABS(B22)&gt;=2,OR(AND(B23="Bull",ABS(B24)&gt;=2),AND(B23="Bear",ABS(B25)&gt;=2))),"Strong",IF(AND(ABS(B22)&gt;=1,OR(AND(B23="Bull",ABS(B24)&gt;=1),AND(B23="Bear",ABS(B25)&gt;=1))),"Moderate","Weak"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
         <is>
-          <t>Market Filter</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="B29" s="32">
-        <f>IF(OR(B7="",B12=""),"Need More Data",IF(AND(B7="Bull",B12="Bull"),"Bull Allowed",IF(AND(B7="Bear",B12="Bear"),"Bear Allowed","Mixed / Wait")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+        <f>IF(B27="WAIT","Need at least 3-5 trading days of history",IF(B27="NO TRADE","Direction or leadership is mixed",IF(B23="Bull",IF(B26="Semiconductors Leading","Bull trend with semiconductors leading","Bull trend with tech leading"),IF(B26="Semiconductors Weakest","Bear trend with semiconductors leading downside","Bear trend with tech leading downside"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>Bull Leadership Score</t>
+          <t>v5 adds 3-day and 5-day momentum plus leadership spreads so the Signal tab can rank the best ETF more intelligently.</t>
         </is>
-      </c>
-      <c r="B30" s="32">
-        <f>IF(B29&lt;&gt;"Bull Allowed","",IF(B14&gt;B16,1,IF(B14&lt;B16,-1,0))+IF(B19&gt;B21,1,IF(B19&lt;B21,-1,0))+IF(B24&gt;B26,1,IF(B24&lt;B26,-1,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>Bear Leadership Score</t>
-        </is>
-      </c>
-      <c r="B31" s="32">
-        <f>IF(B29&lt;&gt;"Bear Allowed","",IF(B15&gt;B17,1,IF(B15&lt;B17,-1,0))+IF(B20&gt;B22,1,IF(B20&lt;B22,-1,0))+IF(B25&gt;B27,1,IF(B25&lt;B27,-1,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>Sector Leadership</t>
-        </is>
-      </c>
-      <c r="B32" s="32">
-        <f>IF(B29="Need More Data","Need More Data",IF(B29="Mixed / Wait","Mixed",IF(B29="Bull Allowed",IF(B30&gt;0,"Semiconductors Leading",IF(B30&lt;0,"Tech Leading","Mixed")),IF(B31&gt;0,"Semiconductors Weakest",IF(B31&lt;0,"Tech Weakest","Mixed")))))</f>
-        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>Trade ETF</t>
+          <t>QQQ Trend</t>
         </is>
       </c>
       <c r="B33" s="32">
-        <f>IF(B29="Need More Data","WAIT",IF(B29="Mixed / Wait","WAIT",IF(B29="Bull Allowed",IF(B32="Semiconductors Leading","SOXL",IF(B32="Tech Leading","TQQQ","WAIT")),IF(B32="Semiconductors Weakest","SOXS",IF(B32="Tech Weakest","SQQQ","WAIT")))))</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AI:AI&lt;&gt;""),Daily_Data!AI:AI),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>SMH Trend</t>
         </is>
       </c>
       <c r="B34" s="32">
-        <f>IF(B33="WAIT","Low",IF(OR(AND(B29="Bull Allowed",ABS(B30)&gt;=2),AND(B29="Bear Allowed",ABS(B31)&gt;=2)),"Strong",IF(OR(AND(B29="Bull Allowed",ABS(B30)&gt;=1),AND(B29="Bear Allowed",ABS(B31)&gt;=1)),"Moderate","Low")))</f>
+        <f>IFERROR(LOOKUP(2,1/(Daily_Data!AO:AO&lt;&gt;""),Daily_Data!AO:AO),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Market Filter</t>
         </is>
       </c>
       <c r="B35" s="32">
-        <f>IF(B33="WAIT",IF(B29="Mixed / Wait","QQQ and SMH trend filters disagree","Need more trend data"),IF(B29="Bull Allowed",IF(B32="Semiconductors Leading","QQQ and SMH bullish; semiconductors leading","QQQ and SMH bullish; tech leading"),IF(B32="Semiconductors Weakest","QQQ and SMH bearish; semiconductors weakest","QQQ and SMH bearish; tech weakest")))</f>
+        <f>IF(OR(B33="",B34=""),"Need More Data",IF(AND(B33="Bull",B34="Bull"),"Bull Allowed",IF(AND(B33="Bear",B34="Bear"),"Bear Allowed","Mixed / Wait")))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
         <is>
+          <t>Trade ETF v6</t>
+        </is>
+      </c>
+      <c r="B36" s="32">
+        <f>IF(B35="Bull Allowed",IF(B30&gt;0,"SOXL",IF(B30&lt;0,"TQQQ","WAIT")),IF(B35="Bear Allowed",IF(B31&gt;0,"SOXS",IF(B31&lt;0,"SQQQ","WAIT")),"WAIT"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Confidence v6</t>
+        </is>
+      </c>
+      <c r="B37" s="32">
+        <f>IF(B36="WAIT","Low",IF(B35="Bull Allowed",IF(ABS(B30)&gt;=2,"Strong",IF(ABS(B30)&gt;=1,"Moderate","Low")),IF(B35="Bear Allowed",IF(ABS(B31)&gt;=2,"Strong",IF(ABS(B31)&gt;=1,"Moderate","Low")),"Low")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>Reason v6</t>
+        </is>
+      </c>
+      <c r="B38" s="32">
+        <f>IF(B36="WAIT",IF(B35="Mixed / Wait","QQQ and SMH trend filters disagree","Need more signal ETF history"),IF(B35="Bull Allowed",IF(B30&gt;0,"QQQ and SMH bullish; semiconductors leading","QQQ and SMH bullish; tech leading"),IF(B31&gt;0,"QQQ and SMH bearish; semiconductors weakest","QQQ and SMH bearish; tech weakest")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
           <t>Paper-Trade Ready</t>
         </is>
       </c>
-      <c r="B36" s="32">
-        <f>IF(B33="WAIT","Observe Only","Ready for paper-trade tracking")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>v6 adds QQQ and SMH as signal ETFs plus a paper-trade tracker and equity curve framework.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B39" s="32">
+        <f>IF(B36="WAIT","Observe Only","Ready for paper-trade tracking")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58665,84 +58670,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Paper Trade Tracker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="35" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>Signal ETF 1</t>
         </is>
       </c>
-      <c r="C2" s="35" t="inlineStr">
+      <c r="C2" s="37" t="inlineStr">
         <is>
           <t>Signal ETF 2</t>
         </is>
       </c>
-      <c r="D2" s="35" t="inlineStr">
+      <c r="D2" s="37" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="35" t="inlineStr">
+      <c r="E2" s="37" t="inlineStr">
         <is>
           <t>Entry Price 1</t>
         </is>
       </c>
-      <c r="F2" s="35" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Entry Price 2</t>
         </is>
       </c>
-      <c r="G2" s="35" t="inlineStr">
+      <c r="G2" s="37" t="inlineStr">
         <is>
           <t>Exit Price 1</t>
         </is>
       </c>
-      <c r="H2" s="35" t="inlineStr">
+      <c r="H2" s="37" t="inlineStr">
         <is>
           <t>Exit Price 2</t>
         </is>
       </c>
-      <c r="I2" s="35" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>Allocation 1 ($)</t>
         </is>
       </c>
-      <c r="J2" s="35" t="inlineStr">
+      <c r="J2" s="37" t="inlineStr">
         <is>
           <t>Allocation 2 ($)</t>
         </is>
       </c>
-      <c r="K2" s="35" t="inlineStr">
+      <c r="K2" s="37" t="inlineStr">
         <is>
           <t>P&amp;L 1 ($)</t>
         </is>
       </c>
-      <c r="L2" s="35" t="inlineStr">
+      <c r="L2" s="37" t="inlineStr">
         <is>
           <t>P&amp;L 2 ($)</t>
         </is>
       </c>
-      <c r="M2" s="35" t="inlineStr">
+      <c r="M2" s="37" t="inlineStr">
         <is>
           <t>Net P&amp;L ($)</t>
         </is>
       </c>
-      <c r="N2" s="35" t="inlineStr">
+      <c r="N2" s="37" t="inlineStr">
         <is>
           <t>Equity Curve ($)</t>
         </is>
       </c>
-      <c r="O2" s="35" t="inlineStr">
+      <c r="O2" s="37" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper_Trades" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Paper_Trades" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -1023,31 +1023,50 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="A4" s="8" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>51.875</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>53.95999908447266</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>50.04000091552734</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>50.72000122070312</v>
+      </c>
       <c r="F4" s="10">
         <f>IF(OR(B4="",E4=""),"",IF(B4=0,"",(E4-B4)/B4))</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
+        <v>41.29999923706055</v>
+      </c>
       <c r="H4" s="10">
         <f>""</f>
         <v/>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>47.31499862670898</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>45.66999816894531</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>45.93000030517578</v>
+      </c>
       <c r="M4" s="23">
         <f>IF(OR(I4="",L4=""),"",IF(I4=0,"",(L4-I4)/I4))</f>
         <v/>
       </c>
-      <c r="N4" s="27">
-        <f>IFERROR((M4/M3)-1,"")</f>
-        <v/>
+      <c r="N4" s="27" t="n">
+        <v>75.73999786376953</v>
       </c>
       <c r="O4" s="23">
         <f>""</f>
@@ -1109,7 +1128,9 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="AD4" s="13" t="n"/>
+      <c r="AD4" s="13" t="n">
+        <v>593.719970703125</v>
+      </c>
       <c r="AE4" s="24">
         <f>""</f>
         <v/>
@@ -1130,7 +1151,9 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="AJ4" s="13" t="n"/>
+      <c r="AJ4" s="13" t="n">
+        <v>387.3299865722656</v>
+      </c>
       <c r="AK4" s="24">
         <f>""</f>
         <v/>
@@ -52651,7 +52674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -53029,14 +53052,6 @@
         <v/>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A31:B31"/>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoreboard" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Daily_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Signal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scoreboard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -83,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -105,11 +105,44 @@
         <color rgb="00B7B7B7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -139,6 +172,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -830,26 +864,48 @@
       <c r="AK3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="A4" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>54.06000137329102</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>55.66249847412109</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>53.0099983215332</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>53.68999862670898</v>
+      </c>
       <c r="F4" s="4">
         <f>IF(OR(E4="",E3=""),"",(E4/E3)-1)</f>
         <v/>
       </c>
-      <c r="G4" s="4" t="n"/>
+      <c r="G4" s="4" t="n">
+        <v>38.86000061035156</v>
+      </c>
       <c r="H4" s="4" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
+      <c r="I4" s="3" t="n">
+        <v>47.3650016784668</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>48.27000045776367</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>47.18000030517578</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>47.45999908447266</v>
+      </c>
       <c r="M4" s="4">
         <f>IF(OR(L4="",L3=""),"",(L4/L3)-1)</f>
         <v/>
       </c>
-      <c r="N4" s="4" t="n"/>
+      <c r="N4" s="4" t="n">
+        <v>73.20999908447266</v>
+      </c>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
@@ -871,7 +927,9 @@
       </c>
       <c r="AB4" s="4" t="n"/>
       <c r="AC4" s="4" t="n"/>
-      <c r="AD4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n">
+        <v>600.3800048828125</v>
+      </c>
       <c r="AE4" s="4">
         <f>IF(OR(AD4="",AD3=""),"",(AD4/AD3)-1)</f>
         <v/>
@@ -883,7 +941,9 @@
         <f>IF(OR(AH4="",AH3=""),"",(AH4/AH3)-1)</f>
         <v/>
       </c>
-      <c r="AJ4" s="4" t="n"/>
+      <c r="AJ4" s="4" t="n">
+        <v>393.9200134277344</v>
+      </c>
       <c r="AK4" s="4" t="n"/>
     </row>
     <row r="5">
@@ -47434,7 +47494,7 @@
           <t>Current Position</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="21" t="n"/>
       <c r="F5" s="11" t="n"/>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="18" t="n"/>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Signal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Scoreboard" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoreboard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="m/d/yy"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -31,25 +33,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
+    <font/>
   </fonts>
   <fills count="8">
     <fill>
@@ -60,32 +54,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAF3F8"/>
+        <fgColor rgb="00EAF3F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,24 +93,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </left>
       <right style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </right>
       <top style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -124,10 +117,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </right>
       <top style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -135,13 +128,13 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </right>
       <top style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00B7B7B7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -149,21 +142,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,20 +168,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -550,7 +541,43 @@
   <dimension ref="A1:AK500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.97265625" customWidth="1" style="19" min="1" max="37"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -741,7 +768,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Enter data here</t>
+        </is>
+      </c>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
@@ -766,7 +797,10 @@
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
-      <c r="Z2" s="3" t="n"/>
+      <c r="Z2" s="3">
+        <f>IFERROR((M4/M3)-1,"")</f>
+        <v/>
+      </c>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n"/>
@@ -837,48 +871,26 @@
       <c r="AK3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>54.06000137329102</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>55.66249847412109</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>53.0099983215332</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>53.68999862670898</v>
-      </c>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="4">
         <f>IF(OR(E4="",E3=""),"",(E4/E3)-1)</f>
         <v/>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>38.86000061035156</v>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
-      <c r="I4" s="3" t="n">
-        <v>47.3650016784668</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>48.27000045776367</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>47.18000030517578</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>47.45999908447266</v>
-      </c>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
       <c r="M4" s="4">
         <f>IF(OR(L4="",L3=""),"",(L4/L3)-1)</f>
         <v/>
       </c>
-      <c r="N4" s="4" t="n">
-        <v>73.20999908447266</v>
-      </c>
+      <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
@@ -900,9 +912,7 @@
       </c>
       <c r="AB4" s="4" t="n"/>
       <c r="AC4" s="4" t="n"/>
-      <c r="AD4" s="3" t="n">
-        <v>600.3800048828125</v>
-      </c>
+      <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="4">
         <f>IF(OR(AD4="",AD3=""),"",(AD4/AD3)-1)</f>
         <v/>
@@ -914,9 +924,7 @@
         <f>IF(OR(AH4="",AH3=""),"",(AH4/AH3)-1)</f>
         <v/>
       </c>
-      <c r="AJ4" s="4" t="n">
-        <v>393.9200134277344</v>
-      </c>
+      <c r="AJ4" s="4" t="n"/>
       <c r="AK4" s="4" t="n"/>
     </row>
     <row r="5">
@@ -47025,12 +47033,13 @@
   <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.9453125" customWidth="1" style="19" min="1" max="1"/>
-    <col width="22.05859375" customWidth="1" style="19" min="2" max="2"/>
-    <col width="18.0234375" customWidth="1" style="19" min="3" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="19">
+    <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>4 ETF Signal Dashboard</t>
@@ -47063,7 +47072,7 @@
       <c r="A5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>QQQ Signal</t>
         </is>
@@ -47123,7 +47132,7 @@
       <c r="A13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>SMH Signal</t>
         </is>
@@ -47183,147 +47192,147 @@
       <c r="A21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>System Output</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Current Position</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Market Direction</t>
         </is>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="11">
         <f>IF(OR(B10="",B18=""),"",IF(AND(B10="Bull",B18="Bull"),"Bull",IF(AND(B10="Bear",B18="Bear"),"Bear","Wait")))</f>
         <v/>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Primary ETF</t>
         </is>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="11">
         <f>B25</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Leadership</t>
         </is>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="11">
         <f>IF(B23="","",IF(B23="Wait","Mixed",IF(B16&gt;B8,"Semiconductors",IF(B16&lt;B8,"Nasdaq","Tied"))))</f>
         <v/>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Secondary ETF</t>
         </is>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="11">
         <f>IF(B26="","(none)",B26)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Trade 1</t>
         </is>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="11">
         <f>IF(B23="Bull",IF(B24="Semiconductors","SOXL","TQQQ"),IF(B23="Bear",IF(B24="Semiconductors","SOXS","SQQQ"),"WAIT"))</f>
         <v/>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>System State</t>
         </is>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="11">
         <f>B23</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Trade 2</t>
         </is>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="11">
         <f>IF(B23="Bull",IF(B24="Semiconductors","TQQQ","SOXL"),IF(B23="Bear",IF(B24="Semiconductors","SQQQ","SOXS"),""))</f>
         <v/>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="11">
         <f>B27</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="11">
         <f>IF(B23="Wait","Low",IF(ABS(B16-B8)&gt;=0.03,"Strong",IF(ABS(B16-B8)&gt;=0.015,"Moderate","Low")))</f>
         <v/>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Signal Date</t>
         </is>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="13">
         <f>B4</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Bull / Strong Bull</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
+      <c r="B31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Bear / Strong Bear</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
+      <c r="B32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Wait / Neutral / Mixed</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n"/>
+      <c r="B33" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -47346,1608 +47355,1616 @@
   <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.97265625" customWidth="1" style="19" min="1" max="1"/>
-    <col width="13.98828125" customWidth="1" style="19" min="2" max="5"/>
-    <col width="9.953125" customWidth="1" style="19" min="6" max="11"/>
-    <col width="11.97265625" customWidth="1" style="19" min="12" max="12"/>
-    <col width="18.0234375" customWidth="1" style="19" min="13" max="13"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Trade Plan / Manual Tracking</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>System Signal</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Trade 1</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Trade 2</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Shares 1</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Shares 2</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>Entry 1</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>Entry 2</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>Exit 1</t>
         </is>
       </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>Exit 2</t>
         </is>
       </c>
-      <c r="L3" s="15" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M3" s="15" t="inlineStr">
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n"/>
-      <c r="E4" s="22" t="n"/>
-      <c r="F4" s="22" t="n"/>
-      <c r="G4" s="22" t="n"/>
-      <c r="H4" s="16" t="n"/>
-      <c r="I4" s="16" t="n"/>
-      <c r="J4" s="16" t="n"/>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="22" t="n"/>
-      <c r="M4" s="22" t="n"/>
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="n"/>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Current Date</t>
         </is>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="11">
         <f>Signal!B4</f>
         <v/>
       </c>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Current Position</t>
         </is>
       </c>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="22" t="n"/>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="22" t="n"/>
-      <c r="M5" s="22" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="18" t="n"/>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="18" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Market Direction</t>
         </is>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="11">
         <f>Signal!B23</f>
         <v/>
       </c>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Primary ETF</t>
         </is>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="11">
         <f>Signal!D23</f>
         <v/>
       </c>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="22" t="n"/>
-      <c r="M6" s="22" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Trade 1</t>
         </is>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="11">
         <f>Signal!B25</f>
         <v/>
       </c>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Secondary ETF</t>
         </is>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="11">
         <f>Signal!D24</f>
         <v/>
       </c>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Trade 2</t>
         </is>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="11">
         <f>Signal!B26</f>
         <v/>
       </c>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>System State</t>
         </is>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="11">
         <f>Signal!D25</f>
         <v/>
       </c>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="22" t="n"/>
-      <c r="M8" s="22" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="11">
         <f>Signal!B27</f>
         <v/>
       </c>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="11">
         <f>Signal!D26</f>
         <v/>
       </c>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="22" t="n"/>
-      <c r="M9" s="22" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="22" t="n"/>
-      <c r="M10" s="22" t="n"/>
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="22" t="n"/>
-      <c r="M11" s="22" t="n"/>
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="22" t="n"/>
-      <c r="M12" s="22" t="n"/>
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="11" t="n"/>
+      <c r="M12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="22" t="n"/>
-      <c r="M13" s="22" t="n"/>
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="22" t="n"/>
-      <c r="M14" s="22" t="n"/>
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="22" t="n"/>
-      <c r="M15" s="22" t="n"/>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="22" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="22" t="n"/>
-      <c r="M16" s="22" t="n"/>
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="22" t="n"/>
-      <c r="M17" s="22" t="n"/>
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="22" t="n"/>
-      <c r="M18" s="22" t="n"/>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="16" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="18" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="22" t="n"/>
-      <c r="M20" s="22" t="n"/>
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="22" t="n"/>
-      <c r="M21" s="22" t="n"/>
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n"/>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="22" t="n"/>
-      <c r="M22" s="22" t="n"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="16" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="22" t="n"/>
-      <c r="M23" s="22" t="n"/>
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="n"/>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="16" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="22" t="n"/>
-      <c r="M24" s="22" t="n"/>
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="n"/>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="16" t="n"/>
-      <c r="I25" s="16" t="n"/>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="22" t="n"/>
-      <c r="M25" s="22" t="n"/>
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="n"/>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="16" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="22" t="n"/>
-      <c r="M26" s="22" t="n"/>
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n"/>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="22" t="n"/>
-      <c r="M27" s="22" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n"/>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="22" t="n"/>
-      <c r="M28" s="22" t="n"/>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="11" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="n"/>
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="22" t="n"/>
-      <c r="E29" s="22" t="n"/>
-      <c r="F29" s="22" t="n"/>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="16" t="n"/>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="22" t="n"/>
-      <c r="M29" s="22" t="n"/>
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="n"/>
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="22" t="n"/>
-      <c r="F30" s="22" t="n"/>
-      <c r="G30" s="22" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="22" t="n"/>
-      <c r="M30" s="22" t="n"/>
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="22" t="n"/>
-      <c r="G31" s="22" t="n"/>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="22" t="n"/>
-      <c r="M31" s="22" t="n"/>
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="22" t="n"/>
-      <c r="G32" s="22" t="n"/>
-      <c r="H32" s="16" t="n"/>
-      <c r="I32" s="16" t="n"/>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="22" t="n"/>
-      <c r="M32" s="22" t="n"/>
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="11" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="n"/>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="22" t="n"/>
-      <c r="H33" s="16" t="n"/>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="22" t="n"/>
-      <c r="M33" s="22" t="n"/>
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="16" t="n"/>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="22" t="n"/>
-      <c r="M34" s="22" t="n"/>
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="18" t="n"/>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="11" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="n"/>
-      <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
-      <c r="F35" s="22" t="n"/>
-      <c r="G35" s="22" t="n"/>
-      <c r="H35" s="16" t="n"/>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="22" t="n"/>
-      <c r="M35" s="22" t="n"/>
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="11" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="n"/>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="22" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="22" t="n"/>
-      <c r="M36" s="22" t="n"/>
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="18" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="11" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="n"/>
-      <c r="B37" s="22" t="n"/>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
-      <c r="G37" s="22" t="n"/>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="22" t="n"/>
-      <c r="M37" s="22" t="n"/>
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="11" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="16" t="n"/>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="22" t="n"/>
-      <c r="M38" s="22" t="n"/>
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="11" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="n"/>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="22" t="n"/>
-      <c r="H39" s="16" t="n"/>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="22" t="n"/>
-      <c r="M39" s="22" t="n"/>
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="11" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="n"/>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="n"/>
-      <c r="G40" s="22" t="n"/>
-      <c r="H40" s="16" t="n"/>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="22" t="n"/>
-      <c r="M40" s="22" t="n"/>
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="18" t="n"/>
+      <c r="K40" s="18" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="11" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="n"/>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
-      <c r="F41" s="22" t="n"/>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="16" t="n"/>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="22" t="n"/>
-      <c r="M41" s="22" t="n"/>
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="18" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="11" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="n"/>
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="22" t="n"/>
-      <c r="F42" s="22" t="n"/>
-      <c r="G42" s="22" t="n"/>
-      <c r="H42" s="16" t="n"/>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="22" t="n"/>
-      <c r="M42" s="22" t="n"/>
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="18" t="n"/>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="18" t="n"/>
+      <c r="K42" s="18" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="11" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="n"/>
-      <c r="B43" s="22" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="22" t="n"/>
-      <c r="F43" s="22" t="n"/>
-      <c r="G43" s="22" t="n"/>
-      <c r="H43" s="16" t="n"/>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="22" t="n"/>
-      <c r="M43" s="22" t="n"/>
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="18" t="n"/>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="18" t="n"/>
+      <c r="K43" s="18" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="11" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="n"/>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="F44" s="22" t="n"/>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="16" t="n"/>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="22" t="n"/>
-      <c r="M44" s="22" t="n"/>
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="18" t="n"/>
+      <c r="I44" s="18" t="n"/>
+      <c r="J44" s="18" t="n"/>
+      <c r="K44" s="18" t="n"/>
+      <c r="L44" s="11" t="n"/>
+      <c r="M44" s="11" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="n"/>
-      <c r="B45" s="22" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="22" t="n"/>
-      <c r="F45" s="22" t="n"/>
-      <c r="G45" s="22" t="n"/>
-      <c r="H45" s="16" t="n"/>
-      <c r="I45" s="16" t="n"/>
-      <c r="J45" s="16" t="n"/>
-      <c r="K45" s="16" t="n"/>
-      <c r="L45" s="22" t="n"/>
-      <c r="M45" s="22" t="n"/>
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="18" t="n"/>
+      <c r="I45" s="18" t="n"/>
+      <c r="J45" s="18" t="n"/>
+      <c r="K45" s="18" t="n"/>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="11" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n"/>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="22" t="n"/>
-      <c r="F46" s="22" t="n"/>
-      <c r="G46" s="22" t="n"/>
-      <c r="H46" s="16" t="n"/>
-      <c r="I46" s="16" t="n"/>
-      <c r="J46" s="16" t="n"/>
-      <c r="K46" s="16" t="n"/>
-      <c r="L46" s="22" t="n"/>
-      <c r="M46" s="22" t="n"/>
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="18" t="n"/>
+      <c r="I46" s="18" t="n"/>
+      <c r="J46" s="18" t="n"/>
+      <c r="K46" s="18" t="n"/>
+      <c r="L46" s="11" t="n"/>
+      <c r="M46" s="11" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="n"/>
-      <c r="B47" s="22" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="22" t="n"/>
-      <c r="F47" s="22" t="n"/>
-      <c r="G47" s="22" t="n"/>
-      <c r="H47" s="16" t="n"/>
-      <c r="I47" s="16" t="n"/>
-      <c r="J47" s="16" t="n"/>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="22" t="n"/>
-      <c r="M47" s="22" t="n"/>
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="18" t="n"/>
+      <c r="K47" s="18" t="n"/>
+      <c r="L47" s="11" t="n"/>
+      <c r="M47" s="11" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="n"/>
-      <c r="B48" s="22" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="22" t="n"/>
-      <c r="E48" s="22" t="n"/>
-      <c r="F48" s="22" t="n"/>
-      <c r="G48" s="22" t="n"/>
-      <c r="H48" s="16" t="n"/>
-      <c r="I48" s="16" t="n"/>
-      <c r="J48" s="16" t="n"/>
-      <c r="K48" s="16" t="n"/>
-      <c r="L48" s="22" t="n"/>
-      <c r="M48" s="22" t="n"/>
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="18" t="n"/>
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="18" t="n"/>
+      <c r="K48" s="18" t="n"/>
+      <c r="L48" s="11" t="n"/>
+      <c r="M48" s="11" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="n"/>
-      <c r="B49" s="22" t="n"/>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="22" t="n"/>
-      <c r="E49" s="22" t="n"/>
-      <c r="F49" s="22" t="n"/>
-      <c r="G49" s="22" t="n"/>
-      <c r="H49" s="16" t="n"/>
-      <c r="I49" s="16" t="n"/>
-      <c r="J49" s="16" t="n"/>
-      <c r="K49" s="16" t="n"/>
-      <c r="L49" s="22" t="n"/>
-      <c r="M49" s="22" t="n"/>
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="18" t="n"/>
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="18" t="n"/>
+      <c r="K49" s="18" t="n"/>
+      <c r="L49" s="11" t="n"/>
+      <c r="M49" s="11" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="n"/>
-      <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="22" t="n"/>
-      <c r="F50" s="22" t="n"/>
-      <c r="G50" s="22" t="n"/>
-      <c r="H50" s="16" t="n"/>
-      <c r="I50" s="16" t="n"/>
-      <c r="J50" s="16" t="n"/>
-      <c r="K50" s="16" t="n"/>
-      <c r="L50" s="22" t="n"/>
-      <c r="M50" s="22" t="n"/>
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="11" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="18" t="n"/>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="18" t="n"/>
+      <c r="K50" s="18" t="n"/>
+      <c r="L50" s="11" t="n"/>
+      <c r="M50" s="11" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="n"/>
-      <c r="B51" s="22" t="n"/>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="22" t="n"/>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="16" t="n"/>
-      <c r="J51" s="16" t="n"/>
-      <c r="K51" s="16" t="n"/>
-      <c r="L51" s="22" t="n"/>
-      <c r="M51" s="22" t="n"/>
+      <c r="A51" s="11" t="n"/>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="11" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="18" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="11" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="n"/>
-      <c r="B52" s="22" t="n"/>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="22" t="n"/>
-      <c r="F52" s="22" t="n"/>
-      <c r="G52" s="22" t="n"/>
-      <c r="H52" s="16" t="n"/>
-      <c r="I52" s="16" t="n"/>
-      <c r="J52" s="16" t="n"/>
-      <c r="K52" s="16" t="n"/>
-      <c r="L52" s="22" t="n"/>
-      <c r="M52" s="22" t="n"/>
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="18" t="n"/>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="18" t="n"/>
+      <c r="K52" s="18" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="11" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="n"/>
-      <c r="B53" s="22" t="n"/>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="22" t="n"/>
-      <c r="E53" s="22" t="n"/>
-      <c r="F53" s="22" t="n"/>
-      <c r="G53" s="22" t="n"/>
-      <c r="H53" s="16" t="n"/>
-      <c r="I53" s="16" t="n"/>
-      <c r="J53" s="16" t="n"/>
-      <c r="K53" s="16" t="n"/>
-      <c r="L53" s="22" t="n"/>
-      <c r="M53" s="22" t="n"/>
+      <c r="A53" s="11" t="n"/>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="18" t="n"/>
+      <c r="I53" s="18" t="n"/>
+      <c r="J53" s="18" t="n"/>
+      <c r="K53" s="18" t="n"/>
+      <c r="L53" s="11" t="n"/>
+      <c r="M53" s="11" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="n"/>
-      <c r="B54" s="22" t="n"/>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="22" t="n"/>
-      <c r="E54" s="22" t="n"/>
-      <c r="F54" s="22" t="n"/>
-      <c r="G54" s="22" t="n"/>
-      <c r="H54" s="16" t="n"/>
-      <c r="I54" s="16" t="n"/>
-      <c r="J54" s="16" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="22" t="n"/>
-      <c r="M54" s="22" t="n"/>
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="18" t="n"/>
+      <c r="I54" s="18" t="n"/>
+      <c r="J54" s="18" t="n"/>
+      <c r="K54" s="18" t="n"/>
+      <c r="L54" s="11" t="n"/>
+      <c r="M54" s="11" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="n"/>
-      <c r="B55" s="22" t="n"/>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="22" t="n"/>
-      <c r="E55" s="22" t="n"/>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="22" t="n"/>
-      <c r="H55" s="16" t="n"/>
-      <c r="I55" s="16" t="n"/>
-      <c r="J55" s="16" t="n"/>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="22" t="n"/>
-      <c r="M55" s="22" t="n"/>
+      <c r="A55" s="11" t="n"/>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="11" t="n"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="18" t="n"/>
+      <c r="I55" s="18" t="n"/>
+      <c r="J55" s="18" t="n"/>
+      <c r="K55" s="18" t="n"/>
+      <c r="L55" s="11" t="n"/>
+      <c r="M55" s="11" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="n"/>
-      <c r="B56" s="22" t="n"/>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="22" t="n"/>
-      <c r="E56" s="22" t="n"/>
-      <c r="F56" s="22" t="n"/>
-      <c r="G56" s="22" t="n"/>
-      <c r="H56" s="16" t="n"/>
-      <c r="I56" s="16" t="n"/>
-      <c r="J56" s="16" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="22" t="n"/>
-      <c r="M56" s="22" t="n"/>
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="11" t="n"/>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="18" t="n"/>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="18" t="n"/>
+      <c r="L56" s="11" t="n"/>
+      <c r="M56" s="11" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="n"/>
-      <c r="B57" s="22" t="n"/>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="22" t="n"/>
-      <c r="E57" s="22" t="n"/>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="22" t="n"/>
-      <c r="H57" s="16" t="n"/>
-      <c r="I57" s="16" t="n"/>
-      <c r="J57" s="16" t="n"/>
-      <c r="K57" s="16" t="n"/>
-      <c r="L57" s="22" t="n"/>
-      <c r="M57" s="22" t="n"/>
+      <c r="A57" s="11" t="n"/>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="11" t="n"/>
+      <c r="G57" s="11" t="n"/>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n"/>
+      <c r="J57" s="18" t="n"/>
+      <c r="K57" s="18" t="n"/>
+      <c r="L57" s="11" t="n"/>
+      <c r="M57" s="11" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="n"/>
-      <c r="B58" s="22" t="n"/>
-      <c r="C58" s="22" t="n"/>
-      <c r="D58" s="22" t="n"/>
-      <c r="E58" s="22" t="n"/>
-      <c r="F58" s="22" t="n"/>
-      <c r="G58" s="22" t="n"/>
-      <c r="H58" s="16" t="n"/>
-      <c r="I58" s="16" t="n"/>
-      <c r="J58" s="16" t="n"/>
-      <c r="K58" s="16" t="n"/>
-      <c r="L58" s="22" t="n"/>
-      <c r="M58" s="22" t="n"/>
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="11" t="n"/>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="18" t="n"/>
+      <c r="I58" s="18" t="n"/>
+      <c r="J58" s="18" t="n"/>
+      <c r="K58" s="18" t="n"/>
+      <c r="L58" s="11" t="n"/>
+      <c r="M58" s="11" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="n"/>
-      <c r="B59" s="22" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="22" t="n"/>
-      <c r="E59" s="22" t="n"/>
-      <c r="F59" s="22" t="n"/>
-      <c r="G59" s="22" t="n"/>
-      <c r="H59" s="16" t="n"/>
-      <c r="I59" s="16" t="n"/>
-      <c r="J59" s="16" t="n"/>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="22" t="n"/>
-      <c r="M59" s="22" t="n"/>
+      <c r="A59" s="11" t="n"/>
+      <c r="B59" s="11" t="n"/>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="11" t="n"/>
+      <c r="G59" s="11" t="n"/>
+      <c r="H59" s="18" t="n"/>
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="18" t="n"/>
+      <c r="L59" s="11" t="n"/>
+      <c r="M59" s="11" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="n"/>
-      <c r="B60" s="22" t="n"/>
-      <c r="C60" s="22" t="n"/>
-      <c r="D60" s="22" t="n"/>
-      <c r="E60" s="22" t="n"/>
-      <c r="F60" s="22" t="n"/>
-      <c r="G60" s="22" t="n"/>
-      <c r="H60" s="16" t="n"/>
-      <c r="I60" s="16" t="n"/>
-      <c r="J60" s="16" t="n"/>
-      <c r="K60" s="16" t="n"/>
-      <c r="L60" s="22" t="n"/>
-      <c r="M60" s="22" t="n"/>
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="11" t="n"/>
+      <c r="G60" s="11" t="n"/>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="n"/>
+      <c r="L60" s="11" t="n"/>
+      <c r="M60" s="11" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="n"/>
-      <c r="B61" s="22" t="n"/>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="22" t="n"/>
-      <c r="E61" s="22" t="n"/>
-      <c r="F61" s="22" t="n"/>
-      <c r="G61" s="22" t="n"/>
-      <c r="H61" s="16" t="n"/>
-      <c r="I61" s="16" t="n"/>
-      <c r="J61" s="16" t="n"/>
-      <c r="K61" s="16" t="n"/>
-      <c r="L61" s="22" t="n"/>
-      <c r="M61" s="22" t="n"/>
+      <c r="A61" s="11" t="n"/>
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="11" t="n"/>
+      <c r="G61" s="11" t="n"/>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="18" t="n"/>
+      <c r="K61" s="18" t="n"/>
+      <c r="L61" s="11" t="n"/>
+      <c r="M61" s="11" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="n"/>
-      <c r="B62" s="22" t="n"/>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="22" t="n"/>
-      <c r="E62" s="22" t="n"/>
-      <c r="F62" s="22" t="n"/>
-      <c r="G62" s="22" t="n"/>
-      <c r="H62" s="16" t="n"/>
-      <c r="I62" s="16" t="n"/>
-      <c r="J62" s="16" t="n"/>
-      <c r="K62" s="16" t="n"/>
-      <c r="L62" s="22" t="n"/>
-      <c r="M62" s="22" t="n"/>
+      <c r="A62" s="11" t="n"/>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="11" t="n"/>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="18" t="n"/>
+      <c r="I62" s="18" t="n"/>
+      <c r="J62" s="18" t="n"/>
+      <c r="K62" s="18" t="n"/>
+      <c r="L62" s="11" t="n"/>
+      <c r="M62" s="11" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="n"/>
-      <c r="B63" s="22" t="n"/>
-      <c r="C63" s="22" t="n"/>
-      <c r="D63" s="22" t="n"/>
-      <c r="E63" s="22" t="n"/>
-      <c r="F63" s="22" t="n"/>
-      <c r="G63" s="22" t="n"/>
-      <c r="H63" s="16" t="n"/>
-      <c r="I63" s="16" t="n"/>
-      <c r="J63" s="16" t="n"/>
-      <c r="K63" s="16" t="n"/>
-      <c r="L63" s="22" t="n"/>
-      <c r="M63" s="22" t="n"/>
+      <c r="A63" s="11" t="n"/>
+      <c r="B63" s="11" t="n"/>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="11" t="n"/>
+      <c r="G63" s="11" t="n"/>
+      <c r="H63" s="18" t="n"/>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="n"/>
+      <c r="L63" s="11" t="n"/>
+      <c r="M63" s="11" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="n"/>
-      <c r="B64" s="22" t="n"/>
-      <c r="C64" s="22" t="n"/>
-      <c r="D64" s="22" t="n"/>
-      <c r="E64" s="22" t="n"/>
-      <c r="F64" s="22" t="n"/>
-      <c r="G64" s="22" t="n"/>
-      <c r="H64" s="16" t="n"/>
-      <c r="I64" s="16" t="n"/>
-      <c r="J64" s="16" t="n"/>
-      <c r="K64" s="16" t="n"/>
-      <c r="L64" s="22" t="n"/>
-      <c r="M64" s="22" t="n"/>
+      <c r="A64" s="11" t="n"/>
+      <c r="B64" s="11" t="n"/>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
+      <c r="F64" s="11" t="n"/>
+      <c r="G64" s="11" t="n"/>
+      <c r="H64" s="18" t="n"/>
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="18" t="n"/>
+      <c r="L64" s="11" t="n"/>
+      <c r="M64" s="11" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="22" t="n"/>
-      <c r="B65" s="22" t="n"/>
-      <c r="C65" s="22" t="n"/>
-      <c r="D65" s="22" t="n"/>
-      <c r="E65" s="22" t="n"/>
-      <c r="F65" s="22" t="n"/>
-      <c r="G65" s="22" t="n"/>
-      <c r="H65" s="16" t="n"/>
-      <c r="I65" s="16" t="n"/>
-      <c r="J65" s="16" t="n"/>
-      <c r="K65" s="16" t="n"/>
-      <c r="L65" s="22" t="n"/>
-      <c r="M65" s="22" t="n"/>
+      <c r="A65" s="11" t="n"/>
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="11" t="n"/>
+      <c r="F65" s="11" t="n"/>
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="18" t="n"/>
+      <c r="I65" s="18" t="n"/>
+      <c r="J65" s="18" t="n"/>
+      <c r="K65" s="18" t="n"/>
+      <c r="L65" s="11" t="n"/>
+      <c r="M65" s="11" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="22" t="n"/>
-      <c r="B66" s="22" t="n"/>
-      <c r="C66" s="22" t="n"/>
-      <c r="D66" s="22" t="n"/>
-      <c r="E66" s="22" t="n"/>
-      <c r="F66" s="22" t="n"/>
-      <c r="G66" s="22" t="n"/>
-      <c r="H66" s="16" t="n"/>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="16" t="n"/>
-      <c r="K66" s="16" t="n"/>
-      <c r="L66" s="22" t="n"/>
-      <c r="M66" s="22" t="n"/>
+      <c r="A66" s="11" t="n"/>
+      <c r="B66" s="11" t="n"/>
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="11" t="n"/>
+      <c r="F66" s="11" t="n"/>
+      <c r="G66" s="11" t="n"/>
+      <c r="H66" s="18" t="n"/>
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="18" t="n"/>
+      <c r="K66" s="18" t="n"/>
+      <c r="L66" s="11" t="n"/>
+      <c r="M66" s="11" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="n"/>
-      <c r="B67" s="22" t="n"/>
-      <c r="C67" s="22" t="n"/>
-      <c r="D67" s="22" t="n"/>
-      <c r="E67" s="22" t="n"/>
-      <c r="F67" s="22" t="n"/>
-      <c r="G67" s="22" t="n"/>
-      <c r="H67" s="16" t="n"/>
-      <c r="I67" s="16" t="n"/>
-      <c r="J67" s="16" t="n"/>
-      <c r="K67" s="16" t="n"/>
-      <c r="L67" s="22" t="n"/>
-      <c r="M67" s="22" t="n"/>
+      <c r="A67" s="11" t="n"/>
+      <c r="B67" s="11" t="n"/>
+      <c r="C67" s="11" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="11" t="n"/>
+      <c r="G67" s="11" t="n"/>
+      <c r="H67" s="18" t="n"/>
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="18" t="n"/>
+      <c r="K67" s="18" t="n"/>
+      <c r="L67" s="11" t="n"/>
+      <c r="M67" s="11" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="n"/>
-      <c r="B68" s="22" t="n"/>
-      <c r="C68" s="22" t="n"/>
-      <c r="D68" s="22" t="n"/>
-      <c r="E68" s="22" t="n"/>
-      <c r="F68" s="22" t="n"/>
-      <c r="G68" s="22" t="n"/>
-      <c r="H68" s="16" t="n"/>
-      <c r="I68" s="16" t="n"/>
-      <c r="J68" s="16" t="n"/>
-      <c r="K68" s="16" t="n"/>
-      <c r="L68" s="22" t="n"/>
-      <c r="M68" s="22" t="n"/>
+      <c r="A68" s="11" t="n"/>
+      <c r="B68" s="11" t="n"/>
+      <c r="C68" s="11" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="11" t="n"/>
+      <c r="G68" s="11" t="n"/>
+      <c r="H68" s="18" t="n"/>
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="18" t="n"/>
+      <c r="K68" s="18" t="n"/>
+      <c r="L68" s="11" t="n"/>
+      <c r="M68" s="11" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="22" t="n"/>
-      <c r="B69" s="22" t="n"/>
-      <c r="C69" s="22" t="n"/>
-      <c r="D69" s="22" t="n"/>
-      <c r="E69" s="22" t="n"/>
-      <c r="F69" s="22" t="n"/>
-      <c r="G69" s="22" t="n"/>
-      <c r="H69" s="16" t="n"/>
-      <c r="I69" s="16" t="n"/>
-      <c r="J69" s="16" t="n"/>
-      <c r="K69" s="16" t="n"/>
-      <c r="L69" s="22" t="n"/>
-      <c r="M69" s="22" t="n"/>
+      <c r="A69" s="11" t="n"/>
+      <c r="B69" s="11" t="n"/>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="11" t="n"/>
+      <c r="F69" s="11" t="n"/>
+      <c r="G69" s="11" t="n"/>
+      <c r="H69" s="18" t="n"/>
+      <c r="I69" s="18" t="n"/>
+      <c r="J69" s="18" t="n"/>
+      <c r="K69" s="18" t="n"/>
+      <c r="L69" s="11" t="n"/>
+      <c r="M69" s="11" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="n"/>
-      <c r="B70" s="22" t="n"/>
-      <c r="C70" s="22" t="n"/>
-      <c r="D70" s="22" t="n"/>
-      <c r="E70" s="22" t="n"/>
-      <c r="F70" s="22" t="n"/>
-      <c r="G70" s="22" t="n"/>
-      <c r="H70" s="16" t="n"/>
-      <c r="I70" s="16" t="n"/>
-      <c r="J70" s="16" t="n"/>
-      <c r="K70" s="16" t="n"/>
-      <c r="L70" s="22" t="n"/>
-      <c r="M70" s="22" t="n"/>
+      <c r="A70" s="11" t="n"/>
+      <c r="B70" s="11" t="n"/>
+      <c r="C70" s="11" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="11" t="n"/>
+      <c r="F70" s="11" t="n"/>
+      <c r="G70" s="11" t="n"/>
+      <c r="H70" s="18" t="n"/>
+      <c r="I70" s="18" t="n"/>
+      <c r="J70" s="18" t="n"/>
+      <c r="K70" s="18" t="n"/>
+      <c r="L70" s="11" t="n"/>
+      <c r="M70" s="11" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="n"/>
-      <c r="B71" s="22" t="n"/>
-      <c r="C71" s="22" t="n"/>
-      <c r="D71" s="22" t="n"/>
-      <c r="E71" s="22" t="n"/>
-      <c r="F71" s="22" t="n"/>
-      <c r="G71" s="22" t="n"/>
-      <c r="H71" s="16" t="n"/>
-      <c r="I71" s="16" t="n"/>
-      <c r="J71" s="16" t="n"/>
-      <c r="K71" s="16" t="n"/>
-      <c r="L71" s="22" t="n"/>
-      <c r="M71" s="22" t="n"/>
+      <c r="A71" s="11" t="n"/>
+      <c r="B71" s="11" t="n"/>
+      <c r="C71" s="11" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="11" t="n"/>
+      <c r="F71" s="11" t="n"/>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="18" t="n"/>
+      <c r="L71" s="11" t="n"/>
+      <c r="M71" s="11" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="22" t="n"/>
-      <c r="B72" s="22" t="n"/>
-      <c r="C72" s="22" t="n"/>
-      <c r="D72" s="22" t="n"/>
-      <c r="E72" s="22" t="n"/>
-      <c r="F72" s="22" t="n"/>
-      <c r="G72" s="22" t="n"/>
-      <c r="H72" s="16" t="n"/>
-      <c r="I72" s="16" t="n"/>
-      <c r="J72" s="16" t="n"/>
-      <c r="K72" s="16" t="n"/>
-      <c r="L72" s="22" t="n"/>
-      <c r="M72" s="22" t="n"/>
+      <c r="A72" s="11" t="n"/>
+      <c r="B72" s="11" t="n"/>
+      <c r="C72" s="11" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="11" t="n"/>
+      <c r="F72" s="11" t="n"/>
+      <c r="G72" s="11" t="n"/>
+      <c r="H72" s="18" t="n"/>
+      <c r="I72" s="18" t="n"/>
+      <c r="J72" s="18" t="n"/>
+      <c r="K72" s="18" t="n"/>
+      <c r="L72" s="11" t="n"/>
+      <c r="M72" s="11" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="22" t="n"/>
-      <c r="B73" s="22" t="n"/>
-      <c r="C73" s="22" t="n"/>
-      <c r="D73" s="22" t="n"/>
-      <c r="E73" s="22" t="n"/>
-      <c r="F73" s="22" t="n"/>
-      <c r="G73" s="22" t="n"/>
-      <c r="H73" s="16" t="n"/>
-      <c r="I73" s="16" t="n"/>
-      <c r="J73" s="16" t="n"/>
-      <c r="K73" s="16" t="n"/>
-      <c r="L73" s="22" t="n"/>
-      <c r="M73" s="22" t="n"/>
+      <c r="A73" s="11" t="n"/>
+      <c r="B73" s="11" t="n"/>
+      <c r="C73" s="11" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="11" t="n"/>
+      <c r="F73" s="11" t="n"/>
+      <c r="G73" s="11" t="n"/>
+      <c r="H73" s="18" t="n"/>
+      <c r="I73" s="18" t="n"/>
+      <c r="J73" s="18" t="n"/>
+      <c r="K73" s="18" t="n"/>
+      <c r="L73" s="11" t="n"/>
+      <c r="M73" s="11" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="22" t="n"/>
-      <c r="B74" s="22" t="n"/>
-      <c r="C74" s="22" t="n"/>
-      <c r="D74" s="22" t="n"/>
-      <c r="E74" s="22" t="n"/>
-      <c r="F74" s="22" t="n"/>
-      <c r="G74" s="22" t="n"/>
-      <c r="H74" s="16" t="n"/>
-      <c r="I74" s="16" t="n"/>
-      <c r="J74" s="16" t="n"/>
-      <c r="K74" s="16" t="n"/>
-      <c r="L74" s="22" t="n"/>
-      <c r="M74" s="22" t="n"/>
+      <c r="A74" s="11" t="n"/>
+      <c r="B74" s="11" t="n"/>
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="11" t="n"/>
+      <c r="F74" s="11" t="n"/>
+      <c r="G74" s="11" t="n"/>
+      <c r="H74" s="18" t="n"/>
+      <c r="I74" s="18" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="18" t="n"/>
+      <c r="L74" s="11" t="n"/>
+      <c r="M74" s="11" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="22" t="n"/>
-      <c r="B75" s="22" t="n"/>
-      <c r="C75" s="22" t="n"/>
-      <c r="D75" s="22" t="n"/>
-      <c r="E75" s="22" t="n"/>
-      <c r="F75" s="22" t="n"/>
-      <c r="G75" s="22" t="n"/>
-      <c r="H75" s="16" t="n"/>
-      <c r="I75" s="16" t="n"/>
-      <c r="J75" s="16" t="n"/>
-      <c r="K75" s="16" t="n"/>
-      <c r="L75" s="22" t="n"/>
-      <c r="M75" s="22" t="n"/>
+      <c r="A75" s="11" t="n"/>
+      <c r="B75" s="11" t="n"/>
+      <c r="C75" s="11" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="11" t="n"/>
+      <c r="G75" s="11" t="n"/>
+      <c r="H75" s="18" t="n"/>
+      <c r="I75" s="18" t="n"/>
+      <c r="J75" s="18" t="n"/>
+      <c r="K75" s="18" t="n"/>
+      <c r="L75" s="11" t="n"/>
+      <c r="M75" s="11" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="22" t="n"/>
-      <c r="B76" s="22" t="n"/>
-      <c r="C76" s="22" t="n"/>
-      <c r="D76" s="22" t="n"/>
-      <c r="E76" s="22" t="n"/>
-      <c r="F76" s="22" t="n"/>
-      <c r="G76" s="22" t="n"/>
-      <c r="H76" s="16" t="n"/>
-      <c r="I76" s="16" t="n"/>
-      <c r="J76" s="16" t="n"/>
-      <c r="K76" s="16" t="n"/>
-      <c r="L76" s="22" t="n"/>
-      <c r="M76" s="22" t="n"/>
+      <c r="A76" s="11" t="n"/>
+      <c r="B76" s="11" t="n"/>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="11" t="n"/>
+      <c r="F76" s="11" t="n"/>
+      <c r="G76" s="11" t="n"/>
+      <c r="H76" s="18" t="n"/>
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="18" t="n"/>
+      <c r="L76" s="11" t="n"/>
+      <c r="M76" s="11" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="22" t="n"/>
-      <c r="B77" s="22" t="n"/>
-      <c r="C77" s="22" t="n"/>
-      <c r="D77" s="22" t="n"/>
-      <c r="E77" s="22" t="n"/>
-      <c r="F77" s="22" t="n"/>
-      <c r="G77" s="22" t="n"/>
-      <c r="H77" s="16" t="n"/>
-      <c r="I77" s="16" t="n"/>
-      <c r="J77" s="16" t="n"/>
-      <c r="K77" s="16" t="n"/>
-      <c r="L77" s="22" t="n"/>
-      <c r="M77" s="22" t="n"/>
+      <c r="A77" s="11" t="n"/>
+      <c r="B77" s="11" t="n"/>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="11" t="n"/>
+      <c r="F77" s="11" t="n"/>
+      <c r="G77" s="11" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+      <c r="J77" s="18" t="n"/>
+      <c r="K77" s="18" t="n"/>
+      <c r="L77" s="11" t="n"/>
+      <c r="M77" s="11" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="22" t="n"/>
-      <c r="B78" s="22" t="n"/>
-      <c r="C78" s="22" t="n"/>
-      <c r="D78" s="22" t="n"/>
-      <c r="E78" s="22" t="n"/>
-      <c r="F78" s="22" t="n"/>
-      <c r="G78" s="22" t="n"/>
-      <c r="H78" s="16" t="n"/>
-      <c r="I78" s="16" t="n"/>
-      <c r="J78" s="16" t="n"/>
-      <c r="K78" s="16" t="n"/>
-      <c r="L78" s="22" t="n"/>
-      <c r="M78" s="22" t="n"/>
+      <c r="A78" s="11" t="n"/>
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="11" t="n"/>
+      <c r="F78" s="11" t="n"/>
+      <c r="G78" s="11" t="n"/>
+      <c r="H78" s="18" t="n"/>
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="18" t="n"/>
+      <c r="L78" s="11" t="n"/>
+      <c r="M78" s="11" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="22" t="n"/>
-      <c r="B79" s="22" t="n"/>
-      <c r="C79" s="22" t="n"/>
-      <c r="D79" s="22" t="n"/>
-      <c r="E79" s="22" t="n"/>
-      <c r="F79" s="22" t="n"/>
-      <c r="G79" s="22" t="n"/>
-      <c r="H79" s="16" t="n"/>
-      <c r="I79" s="16" t="n"/>
-      <c r="J79" s="16" t="n"/>
-      <c r="K79" s="16" t="n"/>
-      <c r="L79" s="22" t="n"/>
-      <c r="M79" s="22" t="n"/>
+      <c r="A79" s="11" t="n"/>
+      <c r="B79" s="11" t="n"/>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="11" t="n"/>
+      <c r="F79" s="11" t="n"/>
+      <c r="G79" s="11" t="n"/>
+      <c r="H79" s="18" t="n"/>
+      <c r="I79" s="18" t="n"/>
+      <c r="J79" s="18" t="n"/>
+      <c r="K79" s="18" t="n"/>
+      <c r="L79" s="11" t="n"/>
+      <c r="M79" s="11" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="22" t="n"/>
-      <c r="B80" s="22" t="n"/>
-      <c r="C80" s="22" t="n"/>
-      <c r="D80" s="22" t="n"/>
-      <c r="E80" s="22" t="n"/>
-      <c r="F80" s="22" t="n"/>
-      <c r="G80" s="22" t="n"/>
-      <c r="H80" s="16" t="n"/>
-      <c r="I80" s="16" t="n"/>
-      <c r="J80" s="16" t="n"/>
-      <c r="K80" s="16" t="n"/>
-      <c r="L80" s="22" t="n"/>
-      <c r="M80" s="22" t="n"/>
+      <c r="A80" s="11" t="n"/>
+      <c r="B80" s="11" t="n"/>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="11" t="n"/>
+      <c r="F80" s="11" t="n"/>
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="18" t="n"/>
+      <c r="K80" s="18" t="n"/>
+      <c r="L80" s="11" t="n"/>
+      <c r="M80" s="11" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="22" t="n"/>
-      <c r="B81" s="22" t="n"/>
-      <c r="C81" s="22" t="n"/>
-      <c r="D81" s="22" t="n"/>
-      <c r="E81" s="22" t="n"/>
-      <c r="F81" s="22" t="n"/>
-      <c r="G81" s="22" t="n"/>
-      <c r="H81" s="16" t="n"/>
-      <c r="I81" s="16" t="n"/>
-      <c r="J81" s="16" t="n"/>
-      <c r="K81" s="16" t="n"/>
-      <c r="L81" s="22" t="n"/>
-      <c r="M81" s="22" t="n"/>
+      <c r="A81" s="11" t="n"/>
+      <c r="B81" s="11" t="n"/>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="11" t="n"/>
+      <c r="E81" s="11" t="n"/>
+      <c r="F81" s="11" t="n"/>
+      <c r="G81" s="11" t="n"/>
+      <c r="H81" s="18" t="n"/>
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="18" t="n"/>
+      <c r="K81" s="18" t="n"/>
+      <c r="L81" s="11" t="n"/>
+      <c r="M81" s="11" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="22" t="n"/>
-      <c r="B82" s="22" t="n"/>
-      <c r="C82" s="22" t="n"/>
-      <c r="D82" s="22" t="n"/>
-      <c r="E82" s="22" t="n"/>
-      <c r="F82" s="22" t="n"/>
-      <c r="G82" s="22" t="n"/>
-      <c r="H82" s="16" t="n"/>
-      <c r="I82" s="16" t="n"/>
-      <c r="J82" s="16" t="n"/>
-      <c r="K82" s="16" t="n"/>
-      <c r="L82" s="22" t="n"/>
-      <c r="M82" s="22" t="n"/>
+      <c r="A82" s="11" t="n"/>
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="n"/>
+      <c r="F82" s="11" t="n"/>
+      <c r="G82" s="11" t="n"/>
+      <c r="H82" s="18" t="n"/>
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="18" t="n"/>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="11" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="22" t="n"/>
-      <c r="B83" s="22" t="n"/>
-      <c r="C83" s="22" t="n"/>
-      <c r="D83" s="22" t="n"/>
-      <c r="E83" s="22" t="n"/>
-      <c r="F83" s="22" t="n"/>
-      <c r="G83" s="22" t="n"/>
-      <c r="H83" s="16" t="n"/>
-      <c r="I83" s="16" t="n"/>
-      <c r="J83" s="16" t="n"/>
-      <c r="K83" s="16" t="n"/>
-      <c r="L83" s="22" t="n"/>
-      <c r="M83" s="22" t="n"/>
+      <c r="A83" s="11" t="n"/>
+      <c r="B83" s="11" t="n"/>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="11" t="n"/>
+      <c r="E83" s="11" t="n"/>
+      <c r="F83" s="11" t="n"/>
+      <c r="G83" s="11" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="n"/>
+      <c r="L83" s="11" t="n"/>
+      <c r="M83" s="11" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="22" t="n"/>
-      <c r="B84" s="22" t="n"/>
-      <c r="C84" s="22" t="n"/>
-      <c r="D84" s="22" t="n"/>
-      <c r="E84" s="22" t="n"/>
-      <c r="F84" s="22" t="n"/>
-      <c r="G84" s="22" t="n"/>
-      <c r="H84" s="16" t="n"/>
-      <c r="I84" s="16" t="n"/>
-      <c r="J84" s="16" t="n"/>
-      <c r="K84" s="16" t="n"/>
-      <c r="L84" s="22" t="n"/>
-      <c r="M84" s="22" t="n"/>
+      <c r="A84" s="11" t="n"/>
+      <c r="B84" s="11" t="n"/>
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="18" t="n"/>
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="18" t="n"/>
+      <c r="L84" s="11" t="n"/>
+      <c r="M84" s="11" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="22" t="n"/>
-      <c r="B85" s="22" t="n"/>
-      <c r="C85" s="22" t="n"/>
-      <c r="D85" s="22" t="n"/>
-      <c r="E85" s="22" t="n"/>
-      <c r="F85" s="22" t="n"/>
-      <c r="G85" s="22" t="n"/>
-      <c r="H85" s="16" t="n"/>
-      <c r="I85" s="16" t="n"/>
-      <c r="J85" s="16" t="n"/>
-      <c r="K85" s="16" t="n"/>
-      <c r="L85" s="22" t="n"/>
-      <c r="M85" s="22" t="n"/>
+      <c r="A85" s="11" t="n"/>
+      <c r="B85" s="11" t="n"/>
+      <c r="C85" s="11" t="n"/>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="11" t="n"/>
+      <c r="F85" s="11" t="n"/>
+      <c r="G85" s="11" t="n"/>
+      <c r="H85" s="18" t="n"/>
+      <c r="I85" s="18" t="n"/>
+      <c r="J85" s="18" t="n"/>
+      <c r="K85" s="18" t="n"/>
+      <c r="L85" s="11" t="n"/>
+      <c r="M85" s="11" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="22" t="n"/>
-      <c r="B86" s="22" t="n"/>
-      <c r="C86" s="22" t="n"/>
-      <c r="D86" s="22" t="n"/>
-      <c r="E86" s="22" t="n"/>
-      <c r="F86" s="22" t="n"/>
-      <c r="G86" s="22" t="n"/>
-      <c r="H86" s="16" t="n"/>
-      <c r="I86" s="16" t="n"/>
-      <c r="J86" s="16" t="n"/>
-      <c r="K86" s="16" t="n"/>
-      <c r="L86" s="22" t="n"/>
-      <c r="M86" s="22" t="n"/>
+      <c r="A86" s="11" t="n"/>
+      <c r="B86" s="11" t="n"/>
+      <c r="C86" s="11" t="n"/>
+      <c r="D86" s="11" t="n"/>
+      <c r="E86" s="11" t="n"/>
+      <c r="F86" s="11" t="n"/>
+      <c r="G86" s="11" t="n"/>
+      <c r="H86" s="18" t="n"/>
+      <c r="I86" s="18" t="n"/>
+      <c r="J86" s="18" t="n"/>
+      <c r="K86" s="18" t="n"/>
+      <c r="L86" s="11" t="n"/>
+      <c r="M86" s="11" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="22" t="n"/>
-      <c r="B87" s="22" t="n"/>
-      <c r="C87" s="22" t="n"/>
-      <c r="D87" s="22" t="n"/>
-      <c r="E87" s="22" t="n"/>
-      <c r="F87" s="22" t="n"/>
-      <c r="G87" s="22" t="n"/>
-      <c r="H87" s="16" t="n"/>
-      <c r="I87" s="16" t="n"/>
-      <c r="J87" s="16" t="n"/>
-      <c r="K87" s="16" t="n"/>
-      <c r="L87" s="22" t="n"/>
-      <c r="M87" s="22" t="n"/>
+      <c r="A87" s="11" t="n"/>
+      <c r="B87" s="11" t="n"/>
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="11" t="n"/>
+      <c r="E87" s="11" t="n"/>
+      <c r="F87" s="11" t="n"/>
+      <c r="G87" s="11" t="n"/>
+      <c r="H87" s="18" t="n"/>
+      <c r="I87" s="18" t="n"/>
+      <c r="J87" s="18" t="n"/>
+      <c r="K87" s="18" t="n"/>
+      <c r="L87" s="11" t="n"/>
+      <c r="M87" s="11" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="22" t="n"/>
-      <c r="B88" s="22" t="n"/>
-      <c r="C88" s="22" t="n"/>
-      <c r="D88" s="22" t="n"/>
-      <c r="E88" s="22" t="n"/>
-      <c r="F88" s="22" t="n"/>
-      <c r="G88" s="22" t="n"/>
-      <c r="H88" s="16" t="n"/>
-      <c r="I88" s="16" t="n"/>
-      <c r="J88" s="16" t="n"/>
-      <c r="K88" s="16" t="n"/>
-      <c r="L88" s="22" t="n"/>
-      <c r="M88" s="22" t="n"/>
+      <c r="A88" s="11" t="n"/>
+      <c r="B88" s="11" t="n"/>
+      <c r="C88" s="11" t="n"/>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="11" t="n"/>
+      <c r="F88" s="11" t="n"/>
+      <c r="G88" s="11" t="n"/>
+      <c r="H88" s="18" t="n"/>
+      <c r="I88" s="18" t="n"/>
+      <c r="J88" s="18" t="n"/>
+      <c r="K88" s="18" t="n"/>
+      <c r="L88" s="11" t="n"/>
+      <c r="M88" s="11" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="22" t="n"/>
-      <c r="B89" s="22" t="n"/>
-      <c r="C89" s="22" t="n"/>
-      <c r="D89" s="22" t="n"/>
-      <c r="E89" s="22" t="n"/>
-      <c r="F89" s="22" t="n"/>
-      <c r="G89" s="22" t="n"/>
-      <c r="H89" s="16" t="n"/>
-      <c r="I89" s="16" t="n"/>
-      <c r="J89" s="16" t="n"/>
-      <c r="K89" s="16" t="n"/>
-      <c r="L89" s="22" t="n"/>
-      <c r="M89" s="22" t="n"/>
+      <c r="A89" s="11" t="n"/>
+      <c r="B89" s="11" t="n"/>
+      <c r="C89" s="11" t="n"/>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="11" t="n"/>
+      <c r="F89" s="11" t="n"/>
+      <c r="G89" s="11" t="n"/>
+      <c r="H89" s="18" t="n"/>
+      <c r="I89" s="18" t="n"/>
+      <c r="J89" s="18" t="n"/>
+      <c r="K89" s="18" t="n"/>
+      <c r="L89" s="11" t="n"/>
+      <c r="M89" s="11" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="n"/>
-      <c r="B90" s="22" t="n"/>
-      <c r="C90" s="22" t="n"/>
-      <c r="D90" s="22" t="n"/>
-      <c r="E90" s="22" t="n"/>
-      <c r="F90" s="22" t="n"/>
-      <c r="G90" s="22" t="n"/>
-      <c r="H90" s="16" t="n"/>
-      <c r="I90" s="16" t="n"/>
-      <c r="J90" s="16" t="n"/>
-      <c r="K90" s="16" t="n"/>
-      <c r="L90" s="22" t="n"/>
-      <c r="M90" s="22" t="n"/>
+      <c r="A90" s="11" t="n"/>
+      <c r="B90" s="11" t="n"/>
+      <c r="C90" s="11" t="n"/>
+      <c r="D90" s="11" t="n"/>
+      <c r="E90" s="11" t="n"/>
+      <c r="F90" s="11" t="n"/>
+      <c r="G90" s="11" t="n"/>
+      <c r="H90" s="18" t="n"/>
+      <c r="I90" s="18" t="n"/>
+      <c r="J90" s="18" t="n"/>
+      <c r="K90" s="18" t="n"/>
+      <c r="L90" s="11" t="n"/>
+      <c r="M90" s="11" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="22" t="n"/>
-      <c r="B91" s="22" t="n"/>
-      <c r="C91" s="22" t="n"/>
-      <c r="D91" s="22" t="n"/>
-      <c r="E91" s="22" t="n"/>
-      <c r="F91" s="22" t="n"/>
-      <c r="G91" s="22" t="n"/>
-      <c r="H91" s="16" t="n"/>
-      <c r="I91" s="16" t="n"/>
-      <c r="J91" s="16" t="n"/>
-      <c r="K91" s="16" t="n"/>
-      <c r="L91" s="22" t="n"/>
-      <c r="M91" s="22" t="n"/>
+      <c r="A91" s="11" t="n"/>
+      <c r="B91" s="11" t="n"/>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="11" t="n"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="18" t="n"/>
+      <c r="I91" s="18" t="n"/>
+      <c r="J91" s="18" t="n"/>
+      <c r="K91" s="18" t="n"/>
+      <c r="L91" s="11" t="n"/>
+      <c r="M91" s="11" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="22" t="n"/>
-      <c r="B92" s="22" t="n"/>
-      <c r="C92" s="22" t="n"/>
-      <c r="D92" s="22" t="n"/>
-      <c r="E92" s="22" t="n"/>
-      <c r="F92" s="22" t="n"/>
-      <c r="G92" s="22" t="n"/>
-      <c r="H92" s="16" t="n"/>
-      <c r="I92" s="16" t="n"/>
-      <c r="J92" s="16" t="n"/>
-      <c r="K92" s="16" t="n"/>
-      <c r="L92" s="22" t="n"/>
-      <c r="M92" s="22" t="n"/>
+      <c r="A92" s="11" t="n"/>
+      <c r="B92" s="11" t="n"/>
+      <c r="C92" s="11" t="n"/>
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="11" t="n"/>
+      <c r="F92" s="11" t="n"/>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="18" t="n"/>
+      <c r="I92" s="18" t="n"/>
+      <c r="J92" s="18" t="n"/>
+      <c r="K92" s="18" t="n"/>
+      <c r="L92" s="11" t="n"/>
+      <c r="M92" s="11" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="22" t="n"/>
-      <c r="B93" s="22" t="n"/>
-      <c r="C93" s="22" t="n"/>
-      <c r="D93" s="22" t="n"/>
-      <c r="E93" s="22" t="n"/>
-      <c r="F93" s="22" t="n"/>
-      <c r="G93" s="22" t="n"/>
-      <c r="H93" s="16" t="n"/>
-      <c r="I93" s="16" t="n"/>
-      <c r="J93" s="16" t="n"/>
-      <c r="K93" s="16" t="n"/>
-      <c r="L93" s="22" t="n"/>
-      <c r="M93" s="22" t="n"/>
+      <c r="A93" s="11" t="n"/>
+      <c r="B93" s="11" t="n"/>
+      <c r="C93" s="11" t="n"/>
+      <c r="D93" s="11" t="n"/>
+      <c r="E93" s="11" t="n"/>
+      <c r="F93" s="11" t="n"/>
+      <c r="G93" s="11" t="n"/>
+      <c r="H93" s="18" t="n"/>
+      <c r="I93" s="18" t="n"/>
+      <c r="J93" s="18" t="n"/>
+      <c r="K93" s="18" t="n"/>
+      <c r="L93" s="11" t="n"/>
+      <c r="M93" s="11" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="22" t="n"/>
-      <c r="B94" s="22" t="n"/>
-      <c r="C94" s="22" t="n"/>
-      <c r="D94" s="22" t="n"/>
-      <c r="E94" s="22" t="n"/>
-      <c r="F94" s="22" t="n"/>
-      <c r="G94" s="22" t="n"/>
-      <c r="H94" s="16" t="n"/>
-      <c r="I94" s="16" t="n"/>
-      <c r="J94" s="16" t="n"/>
-      <c r="K94" s="16" t="n"/>
-      <c r="L94" s="22" t="n"/>
-      <c r="M94" s="22" t="n"/>
+      <c r="A94" s="11" t="n"/>
+      <c r="B94" s="11" t="n"/>
+      <c r="C94" s="11" t="n"/>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="11" t="n"/>
+      <c r="F94" s="11" t="n"/>
+      <c r="G94" s="11" t="n"/>
+      <c r="H94" s="18" t="n"/>
+      <c r="I94" s="18" t="n"/>
+      <c r="J94" s="18" t="n"/>
+      <c r="K94" s="18" t="n"/>
+      <c r="L94" s="11" t="n"/>
+      <c r="M94" s="11" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="22" t="n"/>
-      <c r="B95" s="22" t="n"/>
-      <c r="C95" s="22" t="n"/>
-      <c r="D95" s="22" t="n"/>
-      <c r="E95" s="22" t="n"/>
-      <c r="F95" s="22" t="n"/>
-      <c r="G95" s="22" t="n"/>
-      <c r="H95" s="16" t="n"/>
-      <c r="I95" s="16" t="n"/>
-      <c r="J95" s="16" t="n"/>
-      <c r="K95" s="16" t="n"/>
-      <c r="L95" s="22" t="n"/>
-      <c r="M95" s="22" t="n"/>
+      <c r="A95" s="11" t="n"/>
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="11" t="n"/>
+      <c r="E95" s="11" t="n"/>
+      <c r="F95" s="11" t="n"/>
+      <c r="G95" s="11" t="n"/>
+      <c r="H95" s="18" t="n"/>
+      <c r="I95" s="18" t="n"/>
+      <c r="J95" s="18" t="n"/>
+      <c r="K95" s="18" t="n"/>
+      <c r="L95" s="11" t="n"/>
+      <c r="M95" s="11" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="22" t="n"/>
-      <c r="B96" s="22" t="n"/>
-      <c r="C96" s="22" t="n"/>
-      <c r="D96" s="22" t="n"/>
-      <c r="E96" s="22" t="n"/>
-      <c r="F96" s="22" t="n"/>
-      <c r="G96" s="22" t="n"/>
-      <c r="H96" s="16" t="n"/>
-      <c r="I96" s="16" t="n"/>
-      <c r="J96" s="16" t="n"/>
-      <c r="K96" s="16" t="n"/>
-      <c r="L96" s="22" t="n"/>
-      <c r="M96" s="22" t="n"/>
+      <c r="A96" s="11" t="n"/>
+      <c r="B96" s="11" t="n"/>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="11" t="n"/>
+      <c r="E96" s="11" t="n"/>
+      <c r="F96" s="11" t="n"/>
+      <c r="G96" s="11" t="n"/>
+      <c r="H96" s="18" t="n"/>
+      <c r="I96" s="18" t="n"/>
+      <c r="J96" s="18" t="n"/>
+      <c r="K96" s="18" t="n"/>
+      <c r="L96" s="11" t="n"/>
+      <c r="M96" s="11" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="22" t="n"/>
-      <c r="B97" s="22" t="n"/>
-      <c r="C97" s="22" t="n"/>
-      <c r="D97" s="22" t="n"/>
-      <c r="E97" s="22" t="n"/>
-      <c r="F97" s="22" t="n"/>
-      <c r="G97" s="22" t="n"/>
-      <c r="H97" s="16" t="n"/>
-      <c r="I97" s="16" t="n"/>
-      <c r="J97" s="16" t="n"/>
-      <c r="K97" s="16" t="n"/>
-      <c r="L97" s="22" t="n"/>
-      <c r="M97" s="22" t="n"/>
+      <c r="A97" s="11" t="n"/>
+      <c r="B97" s="11" t="n"/>
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="11" t="n"/>
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+      <c r="J97" s="18" t="n"/>
+      <c r="K97" s="18" t="n"/>
+      <c r="L97" s="11" t="n"/>
+      <c r="M97" s="11" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="22" t="n"/>
-      <c r="B98" s="22" t="n"/>
-      <c r="C98" s="22" t="n"/>
-      <c r="D98" s="22" t="n"/>
-      <c r="E98" s="22" t="n"/>
-      <c r="F98" s="22" t="n"/>
-      <c r="G98" s="22" t="n"/>
-      <c r="H98" s="16" t="n"/>
-      <c r="I98" s="16" t="n"/>
-      <c r="J98" s="16" t="n"/>
-      <c r="K98" s="16" t="n"/>
-      <c r="L98" s="22" t="n"/>
-      <c r="M98" s="22" t="n"/>
+      <c r="A98" s="11" t="n"/>
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="11" t="n"/>
+      <c r="D98" s="11" t="n"/>
+      <c r="E98" s="11" t="n"/>
+      <c r="F98" s="11" t="n"/>
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+      <c r="J98" s="18" t="n"/>
+      <c r="K98" s="18" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="11" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="22" t="n"/>
-      <c r="B99" s="22" t="n"/>
-      <c r="C99" s="22" t="n"/>
-      <c r="D99" s="22" t="n"/>
-      <c r="E99" s="22" t="n"/>
-      <c r="F99" s="22" t="n"/>
-      <c r="G99" s="22" t="n"/>
-      <c r="H99" s="16" t="n"/>
-      <c r="I99" s="16" t="n"/>
-      <c r="J99" s="16" t="n"/>
-      <c r="K99" s="16" t="n"/>
-      <c r="L99" s="22" t="n"/>
-      <c r="M99" s="22" t="n"/>
+      <c r="A99" s="11" t="n"/>
+      <c r="B99" s="11" t="n"/>
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="11" t="n"/>
+      <c r="E99" s="11" t="n"/>
+      <c r="F99" s="11" t="n"/>
+      <c r="G99" s="11" t="n"/>
+      <c r="H99" s="18" t="n"/>
+      <c r="I99" s="18" t="n"/>
+      <c r="J99" s="18" t="n"/>
+      <c r="K99" s="18" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="11" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="22" t="n"/>
-      <c r="B100" s="22" t="n"/>
-      <c r="C100" s="22" t="n"/>
-      <c r="D100" s="22" t="n"/>
-      <c r="E100" s="22" t="n"/>
-      <c r="F100" s="22" t="n"/>
-      <c r="G100" s="22" t="n"/>
-      <c r="H100" s="16" t="n"/>
-      <c r="I100" s="16" t="n"/>
-      <c r="J100" s="16" t="n"/>
-      <c r="K100" s="16" t="n"/>
-      <c r="L100" s="22" t="n"/>
-      <c r="M100" s="22" t="n"/>
+      <c r="A100" s="11" t="n"/>
+      <c r="B100" s="11" t="n"/>
+      <c r="C100" s="11" t="n"/>
+      <c r="D100" s="11" t="n"/>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="11" t="n"/>
+      <c r="G100" s="11" t="n"/>
+      <c r="H100" s="18" t="n"/>
+      <c r="I100" s="18" t="n"/>
+      <c r="J100" s="18" t="n"/>
+      <c r="K100" s="18" t="n"/>
+      <c r="L100" s="11" t="n"/>
+      <c r="M100" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -48967,10 +48984,20 @@
   <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.98828125" customWidth="1" style="19" min="1" max="11"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="19">
+    <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Paper Trade Scoreboard</t>
@@ -48978,2195 +49005,2195 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Trade ID</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Date In</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Date Out</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>P&amp;L $</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>Days Held</t>
         </is>
       </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="22" t="n"/>
-      <c r="H4" s="16">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="18">
         <f>IF(OR(E4="",F4="",G4=""),"", (F4-E4)*G4)</f>
         <v/>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="20">
         <f>IF(OR(E4="",F4=""),"", (F4/E4)-1)</f>
         <v/>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="11">
         <f>IF(OR(C4="",D4=""),"", D4-C4)</f>
         <v/>
       </c>
-      <c r="K4" s="22" t="n"/>
+      <c r="K4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="16">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="18">
         <f>IF(OR(E5="",F5="",G5=""),"", (F5-E5)*G5)</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="20">
         <f>IF(OR(E5="",F5=""),"", (F5/E5)-1)</f>
         <v/>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="11">
         <f>IF(OR(C5="",D5=""),"", D5-C5)</f>
         <v/>
       </c>
-      <c r="K5" s="22" t="n"/>
+      <c r="K5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="16">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="18">
         <f>IF(OR(E6="",F6="",G6=""),"", (F6-E6)*G6)</f>
         <v/>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="20">
         <f>IF(OR(E6="",F6=""),"", (F6/E6)-1)</f>
         <v/>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="11">
         <f>IF(OR(C6="",D6=""),"", D6-C6)</f>
         <v/>
       </c>
-      <c r="K6" s="22" t="n"/>
+      <c r="K6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n"/>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="16">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="18">
         <f>IF(OR(E7="",F7="",G7=""),"", (F7-E7)*G7)</f>
         <v/>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="20">
         <f>IF(OR(E7="",F7=""),"", (F7/E7)-1)</f>
         <v/>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="11">
         <f>IF(OR(C7="",D7=""),"", D7-C7)</f>
         <v/>
       </c>
-      <c r="K7" s="22" t="n"/>
+      <c r="K7" s="11" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="16">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="18">
         <f>IF(OR(E8="",F8="",G8=""),"", (F8-E8)*G8)</f>
         <v/>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="20">
         <f>IF(OR(E8="",F8=""),"", (F8/E8)-1)</f>
         <v/>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="11">
         <f>IF(OR(C8="",D8=""),"", D8-C8)</f>
         <v/>
       </c>
-      <c r="K8" s="22" t="n"/>
+      <c r="K8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="16">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="18">
         <f>IF(OR(E9="",F9="",G9=""),"", (F9-E9)*G9)</f>
         <v/>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="20">
         <f>IF(OR(E9="",F9=""),"", (F9/E9)-1)</f>
         <v/>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="11">
         <f>IF(OR(C9="",D9=""),"", D9-C9)</f>
         <v/>
       </c>
-      <c r="K9" s="22" t="n"/>
+      <c r="K9" s="11" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="16">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="18">
         <f>IF(OR(E10="",F10="",G10=""),"", (F10-E10)*G10)</f>
         <v/>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="20">
         <f>IF(OR(E10="",F10=""),"", (F10/E10)-1)</f>
         <v/>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="11">
         <f>IF(OR(C10="",D10=""),"", D10-C10)</f>
         <v/>
       </c>
-      <c r="K10" s="22" t="n"/>
+      <c r="K10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="16">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="18">
         <f>IF(OR(E11="",F11="",G11=""),"", (F11-E11)*G11)</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="20">
         <f>IF(OR(E11="",F11=""),"", (F11/E11)-1)</f>
         <v/>
       </c>
-      <c r="J11" s="22">
+      <c r="J11" s="11">
         <f>IF(OR(C11="",D11=""),"", D11-C11)</f>
         <v/>
       </c>
-      <c r="K11" s="22" t="n"/>
+      <c r="K11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="16">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="18">
         <f>IF(OR(E12="",F12="",G12=""),"", (F12-E12)*G12)</f>
         <v/>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="20">
         <f>IF(OR(E12="",F12=""),"", (F12/E12)-1)</f>
         <v/>
       </c>
-      <c r="J12" s="22">
+      <c r="J12" s="11">
         <f>IF(OR(C12="",D12=""),"", D12-C12)</f>
         <v/>
       </c>
-      <c r="K12" s="22" t="n"/>
+      <c r="K12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="16">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="18">
         <f>IF(OR(E13="",F13="",G13=""),"", (F13-E13)*G13)</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="20">
         <f>IF(OR(E13="",F13=""),"", (F13/E13)-1)</f>
         <v/>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="11">
         <f>IF(OR(C13="",D13=""),"", D13-C13)</f>
         <v/>
       </c>
-      <c r="K13" s="22" t="n"/>
+      <c r="K13" s="11" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="16">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="18">
         <f>IF(OR(E14="",F14="",G14=""),"", (F14-E14)*G14)</f>
         <v/>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="20">
         <f>IF(OR(E14="",F14=""),"", (F14/E14)-1)</f>
         <v/>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="11">
         <f>IF(OR(C14="",D14=""),"", D14-C14)</f>
         <v/>
       </c>
-      <c r="K14" s="22" t="n"/>
+      <c r="K14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="16">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="18">
         <f>IF(OR(E15="",F15="",G15=""),"", (F15-E15)*G15)</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="20">
         <f>IF(OR(E15="",F15=""),"", (F15/E15)-1)</f>
         <v/>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="11">
         <f>IF(OR(C15="",D15=""),"", D15-C15)</f>
         <v/>
       </c>
-      <c r="K15" s="22" t="n"/>
+      <c r="K15" s="11" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="22" t="n"/>
-      <c r="H16" s="16">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="18">
         <f>IF(OR(E16="",F16="",G16=""),"", (F16-E16)*G16)</f>
         <v/>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="20">
         <f>IF(OR(E16="",F16=""),"", (F16/E16)-1)</f>
         <v/>
       </c>
-      <c r="J16" s="22">
+      <c r="J16" s="11">
         <f>IF(OR(C16="",D16=""),"", D16-C16)</f>
         <v/>
       </c>
-      <c r="K16" s="22" t="n"/>
+      <c r="K16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="16">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="18">
         <f>IF(OR(E17="",F17="",G17=""),"", (F17-E17)*G17)</f>
         <v/>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="20">
         <f>IF(OR(E17="",F17=""),"", (F17/E17)-1)</f>
         <v/>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="11">
         <f>IF(OR(C17="",D17=""),"", D17-C17)</f>
         <v/>
       </c>
-      <c r="K17" s="22" t="n"/>
+      <c r="K17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="16">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="18">
         <f>IF(OR(E18="",F18="",G18=""),"", (F18-E18)*G18)</f>
         <v/>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="20">
         <f>IF(OR(E18="",F18=""),"", (F18/E18)-1)</f>
         <v/>
       </c>
-      <c r="J18" s="22">
+      <c r="J18" s="11">
         <f>IF(OR(C18="",D18=""),"", D18-C18)</f>
         <v/>
       </c>
-      <c r="K18" s="22" t="n"/>
+      <c r="K18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="16">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="18">
         <f>IF(OR(E19="",F19="",G19=""),"", (F19-E19)*G19)</f>
         <v/>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="20">
         <f>IF(OR(E19="",F19=""),"", (F19/E19)-1)</f>
         <v/>
       </c>
-      <c r="J19" s="22">
+      <c r="J19" s="11">
         <f>IF(OR(C19="",D19=""),"", D19-C19)</f>
         <v/>
       </c>
-      <c r="K19" s="22" t="n"/>
+      <c r="K19" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="16">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="18">
         <f>IF(OR(E20="",F20="",G20=""),"", (F20-E20)*G20)</f>
         <v/>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="20">
         <f>IF(OR(E20="",F20=""),"", (F20/E20)-1)</f>
         <v/>
       </c>
-      <c r="J20" s="22">
+      <c r="J20" s="11">
         <f>IF(OR(C20="",D20=""),"", D20-C20)</f>
         <v/>
       </c>
-      <c r="K20" s="22" t="n"/>
+      <c r="K20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="16">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="18">
         <f>IF(OR(E21="",F21="",G21=""),"", (F21-E21)*G21)</f>
         <v/>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="20">
         <f>IF(OR(E21="",F21=""),"", (F21/E21)-1)</f>
         <v/>
       </c>
-      <c r="J21" s="22">
+      <c r="J21" s="11">
         <f>IF(OR(C21="",D21=""),"", D21-C21)</f>
         <v/>
       </c>
-      <c r="K21" s="22" t="n"/>
+      <c r="K21" s="11" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n"/>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="16">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="18">
         <f>IF(OR(E22="",F22="",G22=""),"", (F22-E22)*G22)</f>
         <v/>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="20">
         <f>IF(OR(E22="",F22=""),"", (F22/E22)-1)</f>
         <v/>
       </c>
-      <c r="J22" s="22">
+      <c r="J22" s="11">
         <f>IF(OR(C22="",D22=""),"", D22-C22)</f>
         <v/>
       </c>
-      <c r="K22" s="22" t="n"/>
+      <c r="K22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="16">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="18">
         <f>IF(OR(E23="",F23="",G23=""),"", (F23-E23)*G23)</f>
         <v/>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="20">
         <f>IF(OR(E23="",F23=""),"", (F23/E23)-1)</f>
         <v/>
       </c>
-      <c r="J23" s="22">
+      <c r="J23" s="11">
         <f>IF(OR(C23="",D23=""),"", D23-C23)</f>
         <v/>
       </c>
-      <c r="K23" s="22" t="n"/>
+      <c r="K23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="n"/>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="16">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="18">
         <f>IF(OR(E24="",F24="",G24=""),"", (F24-E24)*G24)</f>
         <v/>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="20">
         <f>IF(OR(E24="",F24=""),"", (F24/E24)-1)</f>
         <v/>
       </c>
-      <c r="J24" s="22">
+      <c r="J24" s="11">
         <f>IF(OR(C24="",D24=""),"", D24-C24)</f>
         <v/>
       </c>
-      <c r="K24" s="22" t="n"/>
+      <c r="K24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="n"/>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="16">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="18">
         <f>IF(OR(E25="",F25="",G25=""),"", (F25-E25)*G25)</f>
         <v/>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="20">
         <f>IF(OR(E25="",F25=""),"", (F25/E25)-1)</f>
         <v/>
       </c>
-      <c r="J25" s="22">
+      <c r="J25" s="11">
         <f>IF(OR(C25="",D25=""),"", D25-C25)</f>
         <v/>
       </c>
-      <c r="K25" s="22" t="n"/>
+      <c r="K25" s="11" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="n"/>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="16">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="18">
         <f>IF(OR(E26="",F26="",G26=""),"", (F26-E26)*G26)</f>
         <v/>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="20">
         <f>IF(OR(E26="",F26=""),"", (F26/E26)-1)</f>
         <v/>
       </c>
-      <c r="J26" s="22">
+      <c r="J26" s="11">
         <f>IF(OR(C26="",D26=""),"", D26-C26)</f>
         <v/>
       </c>
-      <c r="K26" s="22" t="n"/>
+      <c r="K26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n"/>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="16">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="18">
         <f>IF(OR(E27="",F27="",G27=""),"", (F27-E27)*G27)</f>
         <v/>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="20">
         <f>IF(OR(E27="",F27=""),"", (F27/E27)-1)</f>
         <v/>
       </c>
-      <c r="J27" s="22">
+      <c r="J27" s="11">
         <f>IF(OR(C27="",D27=""),"", D27-C27)</f>
         <v/>
       </c>
-      <c r="K27" s="22" t="n"/>
+      <c r="K27" s="11" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n"/>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="16">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="18">
         <f>IF(OR(E28="",F28="",G28=""),"", (F28-E28)*G28)</f>
         <v/>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="20">
         <f>IF(OR(E28="",F28=""),"", (F28/E28)-1)</f>
         <v/>
       </c>
-      <c r="J28" s="22">
+      <c r="J28" s="11">
         <f>IF(OR(C28="",D28=""),"", D28-C28)</f>
         <v/>
       </c>
-      <c r="K28" s="22" t="n"/>
+      <c r="K28" s="11" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="n"/>
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="22" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="16">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="18">
         <f>IF(OR(E29="",F29="",G29=""),"", (F29-E29)*G29)</f>
         <v/>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="20">
         <f>IF(OR(E29="",F29=""),"", (F29/E29)-1)</f>
         <v/>
       </c>
-      <c r="J29" s="22">
+      <c r="J29" s="11">
         <f>IF(OR(C29="",D29=""),"", D29-C29)</f>
         <v/>
       </c>
-      <c r="K29" s="22" t="n"/>
+      <c r="K29" s="11" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="n"/>
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="22" t="n"/>
-      <c r="H30" s="16">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="18">
         <f>IF(OR(E30="",F30="",G30=""),"", (F30-E30)*G30)</f>
         <v/>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="20">
         <f>IF(OR(E30="",F30=""),"", (F30/E30)-1)</f>
         <v/>
       </c>
-      <c r="J30" s="22">
+      <c r="J30" s="11">
         <f>IF(OR(C30="",D30=""),"", D30-C30)</f>
         <v/>
       </c>
-      <c r="K30" s="22" t="n"/>
+      <c r="K30" s="11" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="22" t="n"/>
-      <c r="H31" s="16">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="18">
         <f>IF(OR(E31="",F31="",G31=""),"", (F31-E31)*G31)</f>
         <v/>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="20">
         <f>IF(OR(E31="",F31=""),"", (F31/E31)-1)</f>
         <v/>
       </c>
-      <c r="J31" s="22">
+      <c r="J31" s="11">
         <f>IF(OR(C31="",D31=""),"", D31-C31)</f>
         <v/>
       </c>
-      <c r="K31" s="22" t="n"/>
+      <c r="K31" s="11" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="22" t="n"/>
-      <c r="H32" s="16">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="18">
         <f>IF(OR(E32="",F32="",G32=""),"", (F32-E32)*G32)</f>
         <v/>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="20">
         <f>IF(OR(E32="",F32=""),"", (F32/E32)-1)</f>
         <v/>
       </c>
-      <c r="J32" s="22">
+      <c r="J32" s="11">
         <f>IF(OR(C32="",D32=""),"", D32-C32)</f>
         <v/>
       </c>
-      <c r="K32" s="22" t="n"/>
+      <c r="K32" s="11" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="n"/>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
-      <c r="G33" s="22" t="n"/>
-      <c r="H33" s="16">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="18">
         <f>IF(OR(E33="",F33="",G33=""),"", (F33-E33)*G33)</f>
         <v/>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="20">
         <f>IF(OR(E33="",F33=""),"", (F33/E33)-1)</f>
         <v/>
       </c>
-      <c r="J33" s="22">
+      <c r="J33" s="11">
         <f>IF(OR(C33="",D33=""),"", D33-C33)</f>
         <v/>
       </c>
-      <c r="K33" s="22" t="n"/>
+      <c r="K33" s="11" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="16">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="18">
         <f>IF(OR(E34="",F34="",G34=""),"", (F34-E34)*G34)</f>
         <v/>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="20">
         <f>IF(OR(E34="",F34=""),"", (F34/E34)-1)</f>
         <v/>
       </c>
-      <c r="J34" s="22">
+      <c r="J34" s="11">
         <f>IF(OR(C34="",D34=""),"", D34-C34)</f>
         <v/>
       </c>
-      <c r="K34" s="22" t="n"/>
+      <c r="K34" s="11" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="n"/>
-      <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="22" t="n"/>
-      <c r="H35" s="16">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="18">
         <f>IF(OR(E35="",F35="",G35=""),"", (F35-E35)*G35)</f>
         <v/>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="20">
         <f>IF(OR(E35="",F35=""),"", (F35/E35)-1)</f>
         <v/>
       </c>
-      <c r="J35" s="22">
+      <c r="J35" s="11">
         <f>IF(OR(C35="",D35=""),"", D35-C35)</f>
         <v/>
       </c>
-      <c r="K35" s="22" t="n"/>
+      <c r="K35" s="11" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="n"/>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="22" t="n"/>
-      <c r="H36" s="16">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="18">
         <f>IF(OR(E36="",F36="",G36=""),"", (F36-E36)*G36)</f>
         <v/>
       </c>
-      <c r="I36" s="17">
+      <c r="I36" s="20">
         <f>IF(OR(E36="",F36=""),"", (F36/E36)-1)</f>
         <v/>
       </c>
-      <c r="J36" s="22">
+      <c r="J36" s="11">
         <f>IF(OR(C36="",D36=""),"", D36-C36)</f>
         <v/>
       </c>
-      <c r="K36" s="22" t="n"/>
+      <c r="K36" s="11" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="n"/>
-      <c r="B37" s="22" t="n"/>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="22" t="n"/>
-      <c r="H37" s="16">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="18">
         <f>IF(OR(E37="",F37="",G37=""),"", (F37-E37)*G37)</f>
         <v/>
       </c>
-      <c r="I37" s="17">
+      <c r="I37" s="20">
         <f>IF(OR(E37="",F37=""),"", (F37/E37)-1)</f>
         <v/>
       </c>
-      <c r="J37" s="22">
+      <c r="J37" s="11">
         <f>IF(OR(C37="",D37=""),"", D37-C37)</f>
         <v/>
       </c>
-      <c r="K37" s="22" t="n"/>
+      <c r="K37" s="11" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="16">
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="18">
         <f>IF(OR(E38="",F38="",G38=""),"", (F38-E38)*G38)</f>
         <v/>
       </c>
-      <c r="I38" s="17">
+      <c r="I38" s="20">
         <f>IF(OR(E38="",F38=""),"", (F38/E38)-1)</f>
         <v/>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="11">
         <f>IF(OR(C38="",D38=""),"", D38-C38)</f>
         <v/>
       </c>
-      <c r="K38" s="22" t="n"/>
+      <c r="K38" s="11" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="n"/>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="22" t="n"/>
-      <c r="H39" s="16">
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="18">
         <f>IF(OR(E39="",F39="",G39=""),"", (F39-E39)*G39)</f>
         <v/>
       </c>
-      <c r="I39" s="17">
+      <c r="I39" s="20">
         <f>IF(OR(E39="",F39=""),"", (F39/E39)-1)</f>
         <v/>
       </c>
-      <c r="J39" s="22">
+      <c r="J39" s="11">
         <f>IF(OR(C39="",D39=""),"", D39-C39)</f>
         <v/>
       </c>
-      <c r="K39" s="22" t="n"/>
+      <c r="K39" s="11" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="n"/>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="22" t="n"/>
-      <c r="H40" s="16">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="18">
         <f>IF(OR(E40="",F40="",G40=""),"", (F40-E40)*G40)</f>
         <v/>
       </c>
-      <c r="I40" s="17">
+      <c r="I40" s="20">
         <f>IF(OR(E40="",F40=""),"", (F40/E40)-1)</f>
         <v/>
       </c>
-      <c r="J40" s="22">
+      <c r="J40" s="11">
         <f>IF(OR(C40="",D40=""),"", D40-C40)</f>
         <v/>
       </c>
-      <c r="K40" s="22" t="n"/>
+      <c r="K40" s="11" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="n"/>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="16">
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="18">
         <f>IF(OR(E41="",F41="",G41=""),"", (F41-E41)*G41)</f>
         <v/>
       </c>
-      <c r="I41" s="17">
+      <c r="I41" s="20">
         <f>IF(OR(E41="",F41=""),"", (F41/E41)-1)</f>
         <v/>
       </c>
-      <c r="J41" s="22">
+      <c r="J41" s="11">
         <f>IF(OR(C41="",D41=""),"", D41-C41)</f>
         <v/>
       </c>
-      <c r="K41" s="22" t="n"/>
+      <c r="K41" s="11" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="n"/>
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-      <c r="G42" s="22" t="n"/>
-      <c r="H42" s="16">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="18">
         <f>IF(OR(E42="",F42="",G42=""),"", (F42-E42)*G42)</f>
         <v/>
       </c>
-      <c r="I42" s="17">
+      <c r="I42" s="20">
         <f>IF(OR(E42="",F42=""),"", (F42/E42)-1)</f>
         <v/>
       </c>
-      <c r="J42" s="22">
+      <c r="J42" s="11">
         <f>IF(OR(C42="",D42=""),"", D42-C42)</f>
         <v/>
       </c>
-      <c r="K42" s="22" t="n"/>
+      <c r="K42" s="11" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="n"/>
-      <c r="B43" s="22" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-      <c r="G43" s="22" t="n"/>
-      <c r="H43" s="16">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="18">
         <f>IF(OR(E43="",F43="",G43=""),"", (F43-E43)*G43)</f>
         <v/>
       </c>
-      <c r="I43" s="17">
+      <c r="I43" s="20">
         <f>IF(OR(E43="",F43=""),"", (F43/E43)-1)</f>
         <v/>
       </c>
-      <c r="J43" s="22">
+      <c r="J43" s="11">
         <f>IF(OR(C43="",D43=""),"", D43-C43)</f>
         <v/>
       </c>
-      <c r="K43" s="22" t="n"/>
+      <c r="K43" s="11" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="n"/>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="16">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="18">
         <f>IF(OR(E44="",F44="",G44=""),"", (F44-E44)*G44)</f>
         <v/>
       </c>
-      <c r="I44" s="17">
+      <c r="I44" s="20">
         <f>IF(OR(E44="",F44=""),"", (F44/E44)-1)</f>
         <v/>
       </c>
-      <c r="J44" s="22">
+      <c r="J44" s="11">
         <f>IF(OR(C44="",D44=""),"", D44-C44)</f>
         <v/>
       </c>
-      <c r="K44" s="22" t="n"/>
+      <c r="K44" s="11" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="n"/>
-      <c r="B45" s="22" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="22" t="n"/>
-      <c r="H45" s="16">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="18">
         <f>IF(OR(E45="",F45="",G45=""),"", (F45-E45)*G45)</f>
         <v/>
       </c>
-      <c r="I45" s="17">
+      <c r="I45" s="20">
         <f>IF(OR(E45="",F45=""),"", (F45/E45)-1)</f>
         <v/>
       </c>
-      <c r="J45" s="22">
+      <c r="J45" s="11">
         <f>IF(OR(C45="",D45=""),"", D45-C45)</f>
         <v/>
       </c>
-      <c r="K45" s="22" t="n"/>
+      <c r="K45" s="11" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n"/>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="22" t="n"/>
-      <c r="H46" s="16">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="18">
         <f>IF(OR(E46="",F46="",G46=""),"", (F46-E46)*G46)</f>
         <v/>
       </c>
-      <c r="I46" s="17">
+      <c r="I46" s="20">
         <f>IF(OR(E46="",F46=""),"", (F46/E46)-1)</f>
         <v/>
       </c>
-      <c r="J46" s="22">
+      <c r="J46" s="11">
         <f>IF(OR(C46="",D46=""),"", D46-C46)</f>
         <v/>
       </c>
-      <c r="K46" s="22" t="n"/>
+      <c r="K46" s="11" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="n"/>
-      <c r="B47" s="22" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="22" t="n"/>
-      <c r="H47" s="16">
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="18">
         <f>IF(OR(E47="",F47="",G47=""),"", (F47-E47)*G47)</f>
         <v/>
       </c>
-      <c r="I47" s="17">
+      <c r="I47" s="20">
         <f>IF(OR(E47="",F47=""),"", (F47/E47)-1)</f>
         <v/>
       </c>
-      <c r="J47" s="22">
+      <c r="J47" s="11">
         <f>IF(OR(C47="",D47=""),"", D47-C47)</f>
         <v/>
       </c>
-      <c r="K47" s="22" t="n"/>
+      <c r="K47" s="11" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="n"/>
-      <c r="B48" s="22" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="22" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="22" t="n"/>
-      <c r="H48" s="16">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="18">
         <f>IF(OR(E48="",F48="",G48=""),"", (F48-E48)*G48)</f>
         <v/>
       </c>
-      <c r="I48" s="17">
+      <c r="I48" s="20">
         <f>IF(OR(E48="",F48=""),"", (F48/E48)-1)</f>
         <v/>
       </c>
-      <c r="J48" s="22">
+      <c r="J48" s="11">
         <f>IF(OR(C48="",D48=""),"", D48-C48)</f>
         <v/>
       </c>
-      <c r="K48" s="22" t="n"/>
+      <c r="K48" s="11" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="n"/>
-      <c r="B49" s="22" t="n"/>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="22" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="22" t="n"/>
-      <c r="H49" s="16">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="18">
         <f>IF(OR(E49="",F49="",G49=""),"", (F49-E49)*G49)</f>
         <v/>
       </c>
-      <c r="I49" s="17">
+      <c r="I49" s="20">
         <f>IF(OR(E49="",F49=""),"", (F49/E49)-1)</f>
         <v/>
       </c>
-      <c r="J49" s="22">
+      <c r="J49" s="11">
         <f>IF(OR(C49="",D49=""),"", D49-C49)</f>
         <v/>
       </c>
-      <c r="K49" s="22" t="n"/>
+      <c r="K49" s="11" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="n"/>
-      <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="22" t="n"/>
-      <c r="H50" s="16">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="18">
         <f>IF(OR(E50="",F50="",G50=""),"", (F50-E50)*G50)</f>
         <v/>
       </c>
-      <c r="I50" s="17">
+      <c r="I50" s="20">
         <f>IF(OR(E50="",F50=""),"", (F50/E50)-1)</f>
         <v/>
       </c>
-      <c r="J50" s="22">
+      <c r="J50" s="11">
         <f>IF(OR(C50="",D50=""),"", D50-C50)</f>
         <v/>
       </c>
-      <c r="K50" s="22" t="n"/>
+      <c r="K50" s="11" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="n"/>
-      <c r="B51" s="22" t="n"/>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-      <c r="G51" s="22" t="n"/>
-      <c r="H51" s="16">
+      <c r="A51" s="11" t="n"/>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="18">
         <f>IF(OR(E51="",F51="",G51=""),"", (F51-E51)*G51)</f>
         <v/>
       </c>
-      <c r="I51" s="17">
+      <c r="I51" s="20">
         <f>IF(OR(E51="",F51=""),"", (F51/E51)-1)</f>
         <v/>
       </c>
-      <c r="J51" s="22">
+      <c r="J51" s="11">
         <f>IF(OR(C51="",D51=""),"", D51-C51)</f>
         <v/>
       </c>
-      <c r="K51" s="22" t="n"/>
+      <c r="K51" s="11" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="n"/>
-      <c r="B52" s="22" t="n"/>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
-      <c r="G52" s="22" t="n"/>
-      <c r="H52" s="16">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="18">
         <f>IF(OR(E52="",F52="",G52=""),"", (F52-E52)*G52)</f>
         <v/>
       </c>
-      <c r="I52" s="17">
+      <c r="I52" s="20">
         <f>IF(OR(E52="",F52=""),"", (F52/E52)-1)</f>
         <v/>
       </c>
-      <c r="J52" s="22">
+      <c r="J52" s="11">
         <f>IF(OR(C52="",D52=""),"", D52-C52)</f>
         <v/>
       </c>
-      <c r="K52" s="22" t="n"/>
+      <c r="K52" s="11" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="n"/>
-      <c r="B53" s="22" t="n"/>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="22" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
-      <c r="G53" s="22" t="n"/>
-      <c r="H53" s="16">
+      <c r="A53" s="11" t="n"/>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="18">
         <f>IF(OR(E53="",F53="",G53=""),"", (F53-E53)*G53)</f>
         <v/>
       </c>
-      <c r="I53" s="17">
+      <c r="I53" s="20">
         <f>IF(OR(E53="",F53=""),"", (F53/E53)-1)</f>
         <v/>
       </c>
-      <c r="J53" s="22">
+      <c r="J53" s="11">
         <f>IF(OR(C53="",D53=""),"", D53-C53)</f>
         <v/>
       </c>
-      <c r="K53" s="22" t="n"/>
+      <c r="K53" s="11" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="n"/>
-      <c r="B54" s="22" t="n"/>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="22" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="22" t="n"/>
-      <c r="H54" s="16">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="18">
         <f>IF(OR(E54="",F54="",G54=""),"", (F54-E54)*G54)</f>
         <v/>
       </c>
-      <c r="I54" s="17">
+      <c r="I54" s="20">
         <f>IF(OR(E54="",F54=""),"", (F54/E54)-1)</f>
         <v/>
       </c>
-      <c r="J54" s="22">
+      <c r="J54" s="11">
         <f>IF(OR(C54="",D54=""),"", D54-C54)</f>
         <v/>
       </c>
-      <c r="K54" s="22" t="n"/>
+      <c r="K54" s="11" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="n"/>
-      <c r="B55" s="22" t="n"/>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="22" t="n"/>
-      <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="22" t="n"/>
-      <c r="H55" s="16">
+      <c r="A55" s="11" t="n"/>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="18">
         <f>IF(OR(E55="",F55="",G55=""),"", (F55-E55)*G55)</f>
         <v/>
       </c>
-      <c r="I55" s="17">
+      <c r="I55" s="20">
         <f>IF(OR(E55="",F55=""),"", (F55/E55)-1)</f>
         <v/>
       </c>
-      <c r="J55" s="22">
+      <c r="J55" s="11">
         <f>IF(OR(C55="",D55=""),"", D55-C55)</f>
         <v/>
       </c>
-      <c r="K55" s="22" t="n"/>
+      <c r="K55" s="11" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="n"/>
-      <c r="B56" s="22" t="n"/>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="22" t="n"/>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="22" t="n"/>
-      <c r="H56" s="16">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="18">
         <f>IF(OR(E56="",F56="",G56=""),"", (F56-E56)*G56)</f>
         <v/>
       </c>
-      <c r="I56" s="17">
+      <c r="I56" s="20">
         <f>IF(OR(E56="",F56=""),"", (F56/E56)-1)</f>
         <v/>
       </c>
-      <c r="J56" s="22">
+      <c r="J56" s="11">
         <f>IF(OR(C56="",D56=""),"", D56-C56)</f>
         <v/>
       </c>
-      <c r="K56" s="22" t="n"/>
+      <c r="K56" s="11" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="n"/>
-      <c r="B57" s="22" t="n"/>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="22" t="n"/>
-      <c r="E57" s="16" t="n"/>
-      <c r="F57" s="16" t="n"/>
-      <c r="G57" s="22" t="n"/>
-      <c r="H57" s="16">
+      <c r="A57" s="11" t="n"/>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="11" t="n"/>
+      <c r="H57" s="18">
         <f>IF(OR(E57="",F57="",G57=""),"", (F57-E57)*G57)</f>
         <v/>
       </c>
-      <c r="I57" s="17">
+      <c r="I57" s="20">
         <f>IF(OR(E57="",F57=""),"", (F57/E57)-1)</f>
         <v/>
       </c>
-      <c r="J57" s="22">
+      <c r="J57" s="11">
         <f>IF(OR(C57="",D57=""),"", D57-C57)</f>
         <v/>
       </c>
-      <c r="K57" s="22" t="n"/>
+      <c r="K57" s="11" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="n"/>
-      <c r="B58" s="22" t="n"/>
-      <c r="C58" s="22" t="n"/>
-      <c r="D58" s="22" t="n"/>
-      <c r="E58" s="16" t="n"/>
-      <c r="F58" s="16" t="n"/>
-      <c r="G58" s="22" t="n"/>
-      <c r="H58" s="16">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="18">
         <f>IF(OR(E58="",F58="",G58=""),"", (F58-E58)*G58)</f>
         <v/>
       </c>
-      <c r="I58" s="17">
+      <c r="I58" s="20">
         <f>IF(OR(E58="",F58=""),"", (F58/E58)-1)</f>
         <v/>
       </c>
-      <c r="J58" s="22">
+      <c r="J58" s="11">
         <f>IF(OR(C58="",D58=""),"", D58-C58)</f>
         <v/>
       </c>
-      <c r="K58" s="22" t="n"/>
+      <c r="K58" s="11" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="n"/>
-      <c r="B59" s="22" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="22" t="n"/>
-      <c r="E59" s="16" t="n"/>
-      <c r="F59" s="16" t="n"/>
-      <c r="G59" s="22" t="n"/>
-      <c r="H59" s="16">
+      <c r="A59" s="11" t="n"/>
+      <c r="B59" s="11" t="n"/>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="11" t="n"/>
+      <c r="H59" s="18">
         <f>IF(OR(E59="",F59="",G59=""),"", (F59-E59)*G59)</f>
         <v/>
       </c>
-      <c r="I59" s="17">
+      <c r="I59" s="20">
         <f>IF(OR(E59="",F59=""),"", (F59/E59)-1)</f>
         <v/>
       </c>
-      <c r="J59" s="22">
+      <c r="J59" s="11">
         <f>IF(OR(C59="",D59=""),"", D59-C59)</f>
         <v/>
       </c>
-      <c r="K59" s="22" t="n"/>
+      <c r="K59" s="11" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="n"/>
-      <c r="B60" s="22" t="n"/>
-      <c r="C60" s="22" t="n"/>
-      <c r="D60" s="22" t="n"/>
-      <c r="E60" s="16" t="n"/>
-      <c r="F60" s="16" t="n"/>
-      <c r="G60" s="22" t="n"/>
-      <c r="H60" s="16">
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="11" t="n"/>
+      <c r="H60" s="18">
         <f>IF(OR(E60="",F60="",G60=""),"", (F60-E60)*G60)</f>
         <v/>
       </c>
-      <c r="I60" s="17">
+      <c r="I60" s="20">
         <f>IF(OR(E60="",F60=""),"", (F60/E60)-1)</f>
         <v/>
       </c>
-      <c r="J60" s="22">
+      <c r="J60" s="11">
         <f>IF(OR(C60="",D60=""),"", D60-C60)</f>
         <v/>
       </c>
-      <c r="K60" s="22" t="n"/>
+      <c r="K60" s="11" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="n"/>
-      <c r="B61" s="22" t="n"/>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="22" t="n"/>
-      <c r="E61" s="16" t="n"/>
-      <c r="F61" s="16" t="n"/>
-      <c r="G61" s="22" t="n"/>
-      <c r="H61" s="16">
+      <c r="A61" s="11" t="n"/>
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="11" t="n"/>
+      <c r="H61" s="18">
         <f>IF(OR(E61="",F61="",G61=""),"", (F61-E61)*G61)</f>
         <v/>
       </c>
-      <c r="I61" s="17">
+      <c r="I61" s="20">
         <f>IF(OR(E61="",F61=""),"", (F61/E61)-1)</f>
         <v/>
       </c>
-      <c r="J61" s="22">
+      <c r="J61" s="11">
         <f>IF(OR(C61="",D61=""),"", D61-C61)</f>
         <v/>
       </c>
-      <c r="K61" s="22" t="n"/>
+      <c r="K61" s="11" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="n"/>
-      <c r="B62" s="22" t="n"/>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="22" t="n"/>
-      <c r="E62" s="16" t="n"/>
-      <c r="F62" s="16" t="n"/>
-      <c r="G62" s="22" t="n"/>
-      <c r="H62" s="16">
+      <c r="A62" s="11" t="n"/>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="18">
         <f>IF(OR(E62="",F62="",G62=""),"", (F62-E62)*G62)</f>
         <v/>
       </c>
-      <c r="I62" s="17">
+      <c r="I62" s="20">
         <f>IF(OR(E62="",F62=""),"", (F62/E62)-1)</f>
         <v/>
       </c>
-      <c r="J62" s="22">
+      <c r="J62" s="11">
         <f>IF(OR(C62="",D62=""),"", D62-C62)</f>
         <v/>
       </c>
-      <c r="K62" s="22" t="n"/>
+      <c r="K62" s="11" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="n"/>
-      <c r="B63" s="22" t="n"/>
-      <c r="C63" s="22" t="n"/>
-      <c r="D63" s="22" t="n"/>
-      <c r="E63" s="16" t="n"/>
-      <c r="F63" s="16" t="n"/>
-      <c r="G63" s="22" t="n"/>
-      <c r="H63" s="16">
+      <c r="A63" s="11" t="n"/>
+      <c r="B63" s="11" t="n"/>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="11" t="n"/>
+      <c r="H63" s="18">
         <f>IF(OR(E63="",F63="",G63=""),"", (F63-E63)*G63)</f>
         <v/>
       </c>
-      <c r="I63" s="17">
+      <c r="I63" s="20">
         <f>IF(OR(E63="",F63=""),"", (F63/E63)-1)</f>
         <v/>
       </c>
-      <c r="J63" s="22">
+      <c r="J63" s="11">
         <f>IF(OR(C63="",D63=""),"", D63-C63)</f>
         <v/>
       </c>
-      <c r="K63" s="22" t="n"/>
+      <c r="K63" s="11" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="n"/>
-      <c r="B64" s="22" t="n"/>
-      <c r="C64" s="22" t="n"/>
-      <c r="D64" s="22" t="n"/>
-      <c r="E64" s="16" t="n"/>
-      <c r="F64" s="16" t="n"/>
-      <c r="G64" s="22" t="n"/>
-      <c r="H64" s="16">
+      <c r="A64" s="11" t="n"/>
+      <c r="B64" s="11" t="n"/>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="11" t="n"/>
+      <c r="H64" s="18">
         <f>IF(OR(E64="",F64="",G64=""),"", (F64-E64)*G64)</f>
         <v/>
       </c>
-      <c r="I64" s="17">
+      <c r="I64" s="20">
         <f>IF(OR(E64="",F64=""),"", (F64/E64)-1)</f>
         <v/>
       </c>
-      <c r="J64" s="22">
+      <c r="J64" s="11">
         <f>IF(OR(C64="",D64=""),"", D64-C64)</f>
         <v/>
       </c>
-      <c r="K64" s="22" t="n"/>
+      <c r="K64" s="11" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="22" t="n"/>
-      <c r="B65" s="22" t="n"/>
-      <c r="C65" s="22" t="n"/>
-      <c r="D65" s="22" t="n"/>
-      <c r="E65" s="16" t="n"/>
-      <c r="F65" s="16" t="n"/>
-      <c r="G65" s="22" t="n"/>
-      <c r="H65" s="16">
+      <c r="A65" s="11" t="n"/>
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="18">
         <f>IF(OR(E65="",F65="",G65=""),"", (F65-E65)*G65)</f>
         <v/>
       </c>
-      <c r="I65" s="17">
+      <c r="I65" s="20">
         <f>IF(OR(E65="",F65=""),"", (F65/E65)-1)</f>
         <v/>
       </c>
-      <c r="J65" s="22">
+      <c r="J65" s="11">
         <f>IF(OR(C65="",D65=""),"", D65-C65)</f>
         <v/>
       </c>
-      <c r="K65" s="22" t="n"/>
+      <c r="K65" s="11" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="22" t="n"/>
-      <c r="B66" s="22" t="n"/>
-      <c r="C66" s="22" t="n"/>
-      <c r="D66" s="22" t="n"/>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="n"/>
-      <c r="G66" s="22" t="n"/>
-      <c r="H66" s="16">
+      <c r="A66" s="11" t="n"/>
+      <c r="B66" s="11" t="n"/>
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="11" t="n"/>
+      <c r="H66" s="18">
         <f>IF(OR(E66="",F66="",G66=""),"", (F66-E66)*G66)</f>
         <v/>
       </c>
-      <c r="I66" s="17">
+      <c r="I66" s="20">
         <f>IF(OR(E66="",F66=""),"", (F66/E66)-1)</f>
         <v/>
       </c>
-      <c r="J66" s="22">
+      <c r="J66" s="11">
         <f>IF(OR(C66="",D66=""),"", D66-C66)</f>
         <v/>
       </c>
-      <c r="K66" s="22" t="n"/>
+      <c r="K66" s="11" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="n"/>
-      <c r="B67" s="22" t="n"/>
-      <c r="C67" s="22" t="n"/>
-      <c r="D67" s="22" t="n"/>
-      <c r="E67" s="16" t="n"/>
-      <c r="F67" s="16" t="n"/>
-      <c r="G67" s="22" t="n"/>
-      <c r="H67" s="16">
+      <c r="A67" s="11" t="n"/>
+      <c r="B67" s="11" t="n"/>
+      <c r="C67" s="11" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+      <c r="G67" s="11" t="n"/>
+      <c r="H67" s="18">
         <f>IF(OR(E67="",F67="",G67=""),"", (F67-E67)*G67)</f>
         <v/>
       </c>
-      <c r="I67" s="17">
+      <c r="I67" s="20">
         <f>IF(OR(E67="",F67=""),"", (F67/E67)-1)</f>
         <v/>
       </c>
-      <c r="J67" s="22">
+      <c r="J67" s="11">
         <f>IF(OR(C67="",D67=""),"", D67-C67)</f>
         <v/>
       </c>
-      <c r="K67" s="22" t="n"/>
+      <c r="K67" s="11" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="n"/>
-      <c r="B68" s="22" t="n"/>
-      <c r="C68" s="22" t="n"/>
-      <c r="D68" s="22" t="n"/>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="n"/>
-      <c r="G68" s="22" t="n"/>
-      <c r="H68" s="16">
+      <c r="A68" s="11" t="n"/>
+      <c r="B68" s="11" t="n"/>
+      <c r="C68" s="11" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="11" t="n"/>
+      <c r="H68" s="18">
         <f>IF(OR(E68="",F68="",G68=""),"", (F68-E68)*G68)</f>
         <v/>
       </c>
-      <c r="I68" s="17">
+      <c r="I68" s="20">
         <f>IF(OR(E68="",F68=""),"", (F68/E68)-1)</f>
         <v/>
       </c>
-      <c r="J68" s="22">
+      <c r="J68" s="11">
         <f>IF(OR(C68="",D68=""),"", D68-C68)</f>
         <v/>
       </c>
-      <c r="K68" s="22" t="n"/>
+      <c r="K68" s="11" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="22" t="n"/>
-      <c r="B69" s="22" t="n"/>
-      <c r="C69" s="22" t="n"/>
-      <c r="D69" s="22" t="n"/>
-      <c r="E69" s="16" t="n"/>
-      <c r="F69" s="16" t="n"/>
-      <c r="G69" s="22" t="n"/>
-      <c r="H69" s="16">
+      <c r="A69" s="11" t="n"/>
+      <c r="B69" s="11" t="n"/>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+      <c r="G69" s="11" t="n"/>
+      <c r="H69" s="18">
         <f>IF(OR(E69="",F69="",G69=""),"", (F69-E69)*G69)</f>
         <v/>
       </c>
-      <c r="I69" s="17">
+      <c r="I69" s="20">
         <f>IF(OR(E69="",F69=""),"", (F69/E69)-1)</f>
         <v/>
       </c>
-      <c r="J69" s="22">
+      <c r="J69" s="11">
         <f>IF(OR(C69="",D69=""),"", D69-C69)</f>
         <v/>
       </c>
-      <c r="K69" s="22" t="n"/>
+      <c r="K69" s="11" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="n"/>
-      <c r="B70" s="22" t="n"/>
-      <c r="C70" s="22" t="n"/>
-      <c r="D70" s="22" t="n"/>
-      <c r="E70" s="16" t="n"/>
-      <c r="F70" s="16" t="n"/>
-      <c r="G70" s="22" t="n"/>
-      <c r="H70" s="16">
+      <c r="A70" s="11" t="n"/>
+      <c r="B70" s="11" t="n"/>
+      <c r="C70" s="11" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="18" t="n"/>
+      <c r="F70" s="18" t="n"/>
+      <c r="G70" s="11" t="n"/>
+      <c r="H70" s="18">
         <f>IF(OR(E70="",F70="",G70=""),"", (F70-E70)*G70)</f>
         <v/>
       </c>
-      <c r="I70" s="17">
+      <c r="I70" s="20">
         <f>IF(OR(E70="",F70=""),"", (F70/E70)-1)</f>
         <v/>
       </c>
-      <c r="J70" s="22">
+      <c r="J70" s="11">
         <f>IF(OR(C70="",D70=""),"", D70-C70)</f>
         <v/>
       </c>
-      <c r="K70" s="22" t="n"/>
+      <c r="K70" s="11" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="n"/>
-      <c r="B71" s="22" t="n"/>
-      <c r="C71" s="22" t="n"/>
-      <c r="D71" s="22" t="n"/>
-      <c r="E71" s="16" t="n"/>
-      <c r="F71" s="16" t="n"/>
-      <c r="G71" s="22" t="n"/>
-      <c r="H71" s="16">
+      <c r="A71" s="11" t="n"/>
+      <c r="B71" s="11" t="n"/>
+      <c r="C71" s="11" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="18">
         <f>IF(OR(E71="",F71="",G71=""),"", (F71-E71)*G71)</f>
         <v/>
       </c>
-      <c r="I71" s="17">
+      <c r="I71" s="20">
         <f>IF(OR(E71="",F71=""),"", (F71/E71)-1)</f>
         <v/>
       </c>
-      <c r="J71" s="22">
+      <c r="J71" s="11">
         <f>IF(OR(C71="",D71=""),"", D71-C71)</f>
         <v/>
       </c>
-      <c r="K71" s="22" t="n"/>
+      <c r="K71" s="11" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="22" t="n"/>
-      <c r="B72" s="22" t="n"/>
-      <c r="C72" s="22" t="n"/>
-      <c r="D72" s="22" t="n"/>
-      <c r="E72" s="16" t="n"/>
-      <c r="F72" s="16" t="n"/>
-      <c r="G72" s="22" t="n"/>
-      <c r="H72" s="16">
+      <c r="A72" s="11" t="n"/>
+      <c r="B72" s="11" t="n"/>
+      <c r="C72" s="11" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="18" t="n"/>
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="11" t="n"/>
+      <c r="H72" s="18">
         <f>IF(OR(E72="",F72="",G72=""),"", (F72-E72)*G72)</f>
         <v/>
       </c>
-      <c r="I72" s="17">
+      <c r="I72" s="20">
         <f>IF(OR(E72="",F72=""),"", (F72/E72)-1)</f>
         <v/>
       </c>
-      <c r="J72" s="22">
+      <c r="J72" s="11">
         <f>IF(OR(C72="",D72=""),"", D72-C72)</f>
         <v/>
       </c>
-      <c r="K72" s="22" t="n"/>
+      <c r="K72" s="11" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="22" t="n"/>
-      <c r="B73" s="22" t="n"/>
-      <c r="C73" s="22" t="n"/>
-      <c r="D73" s="22" t="n"/>
-      <c r="E73" s="16" t="n"/>
-      <c r="F73" s="16" t="n"/>
-      <c r="G73" s="22" t="n"/>
-      <c r="H73" s="16">
+      <c r="A73" s="11" t="n"/>
+      <c r="B73" s="11" t="n"/>
+      <c r="C73" s="11" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="18" t="n"/>
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="11" t="n"/>
+      <c r="H73" s="18">
         <f>IF(OR(E73="",F73="",G73=""),"", (F73-E73)*G73)</f>
         <v/>
       </c>
-      <c r="I73" s="17">
+      <c r="I73" s="20">
         <f>IF(OR(E73="",F73=""),"", (F73/E73)-1)</f>
         <v/>
       </c>
-      <c r="J73" s="22">
+      <c r="J73" s="11">
         <f>IF(OR(C73="",D73=""),"", D73-C73)</f>
         <v/>
       </c>
-      <c r="K73" s="22" t="n"/>
+      <c r="K73" s="11" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="22" t="n"/>
-      <c r="B74" s="22" t="n"/>
-      <c r="C74" s="22" t="n"/>
-      <c r="D74" s="22" t="n"/>
-      <c r="E74" s="16" t="n"/>
-      <c r="F74" s="16" t="n"/>
-      <c r="G74" s="22" t="n"/>
-      <c r="H74" s="16">
+      <c r="A74" s="11" t="n"/>
+      <c r="B74" s="11" t="n"/>
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="11" t="n"/>
+      <c r="H74" s="18">
         <f>IF(OR(E74="",F74="",G74=""),"", (F74-E74)*G74)</f>
         <v/>
       </c>
-      <c r="I74" s="17">
+      <c r="I74" s="20">
         <f>IF(OR(E74="",F74=""),"", (F74/E74)-1)</f>
         <v/>
       </c>
-      <c r="J74" s="22">
+      <c r="J74" s="11">
         <f>IF(OR(C74="",D74=""),"", D74-C74)</f>
         <v/>
       </c>
-      <c r="K74" s="22" t="n"/>
+      <c r="K74" s="11" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="22" t="n"/>
-      <c r="B75" s="22" t="n"/>
-      <c r="C75" s="22" t="n"/>
-      <c r="D75" s="22" t="n"/>
-      <c r="E75" s="16" t="n"/>
-      <c r="F75" s="16" t="n"/>
-      <c r="G75" s="22" t="n"/>
-      <c r="H75" s="16">
+      <c r="A75" s="11" t="n"/>
+      <c r="B75" s="11" t="n"/>
+      <c r="C75" s="11" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="18" t="n"/>
+      <c r="G75" s="11" t="n"/>
+      <c r="H75" s="18">
         <f>IF(OR(E75="",F75="",G75=""),"", (F75-E75)*G75)</f>
         <v/>
       </c>
-      <c r="I75" s="17">
+      <c r="I75" s="20">
         <f>IF(OR(E75="",F75=""),"", (F75/E75)-1)</f>
         <v/>
       </c>
-      <c r="J75" s="22">
+      <c r="J75" s="11">
         <f>IF(OR(C75="",D75=""),"", D75-C75)</f>
         <v/>
       </c>
-      <c r="K75" s="22" t="n"/>
+      <c r="K75" s="11" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="22" t="n"/>
-      <c r="B76" s="22" t="n"/>
-      <c r="C76" s="22" t="n"/>
-      <c r="D76" s="22" t="n"/>
-      <c r="E76" s="16" t="n"/>
-      <c r="F76" s="16" t="n"/>
-      <c r="G76" s="22" t="n"/>
-      <c r="H76" s="16">
+      <c r="A76" s="11" t="n"/>
+      <c r="B76" s="11" t="n"/>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+      <c r="G76" s="11" t="n"/>
+      <c r="H76" s="18">
         <f>IF(OR(E76="",F76="",G76=""),"", (F76-E76)*G76)</f>
         <v/>
       </c>
-      <c r="I76" s="17">
+      <c r="I76" s="20">
         <f>IF(OR(E76="",F76=""),"", (F76/E76)-1)</f>
         <v/>
       </c>
-      <c r="J76" s="22">
+      <c r="J76" s="11">
         <f>IF(OR(C76="",D76=""),"", D76-C76)</f>
         <v/>
       </c>
-      <c r="K76" s="22" t="n"/>
+      <c r="K76" s="11" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="22" t="n"/>
-      <c r="B77" s="22" t="n"/>
-      <c r="C77" s="22" t="n"/>
-      <c r="D77" s="22" t="n"/>
-      <c r="E77" s="16" t="n"/>
-      <c r="F77" s="16" t="n"/>
-      <c r="G77" s="22" t="n"/>
-      <c r="H77" s="16">
+      <c r="A77" s="11" t="n"/>
+      <c r="B77" s="11" t="n"/>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="11" t="n"/>
+      <c r="H77" s="18">
         <f>IF(OR(E77="",F77="",G77=""),"", (F77-E77)*G77)</f>
         <v/>
       </c>
-      <c r="I77" s="17">
+      <c r="I77" s="20">
         <f>IF(OR(E77="",F77=""),"", (F77/E77)-1)</f>
         <v/>
       </c>
-      <c r="J77" s="22">
+      <c r="J77" s="11">
         <f>IF(OR(C77="",D77=""),"", D77-C77)</f>
         <v/>
       </c>
-      <c r="K77" s="22" t="n"/>
+      <c r="K77" s="11" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="22" t="n"/>
-      <c r="B78" s="22" t="n"/>
-      <c r="C78" s="22" t="n"/>
-      <c r="D78" s="22" t="n"/>
-      <c r="E78" s="16" t="n"/>
-      <c r="F78" s="16" t="n"/>
-      <c r="G78" s="22" t="n"/>
-      <c r="H78" s="16">
+      <c r="A78" s="11" t="n"/>
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="18" t="n"/>
+      <c r="F78" s="18" t="n"/>
+      <c r="G78" s="11" t="n"/>
+      <c r="H78" s="18">
         <f>IF(OR(E78="",F78="",G78=""),"", (F78-E78)*G78)</f>
         <v/>
       </c>
-      <c r="I78" s="17">
+      <c r="I78" s="20">
         <f>IF(OR(E78="",F78=""),"", (F78/E78)-1)</f>
         <v/>
       </c>
-      <c r="J78" s="22">
+      <c r="J78" s="11">
         <f>IF(OR(C78="",D78=""),"", D78-C78)</f>
         <v/>
       </c>
-      <c r="K78" s="22" t="n"/>
+      <c r="K78" s="11" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="22" t="n"/>
-      <c r="B79" s="22" t="n"/>
-      <c r="C79" s="22" t="n"/>
-      <c r="D79" s="22" t="n"/>
-      <c r="E79" s="16" t="n"/>
-      <c r="F79" s="16" t="n"/>
-      <c r="G79" s="22" t="n"/>
-      <c r="H79" s="16">
+      <c r="A79" s="11" t="n"/>
+      <c r="B79" s="11" t="n"/>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="18" t="n"/>
+      <c r="G79" s="11" t="n"/>
+      <c r="H79" s="18">
         <f>IF(OR(E79="",F79="",G79=""),"", (F79-E79)*G79)</f>
         <v/>
       </c>
-      <c r="I79" s="17">
+      <c r="I79" s="20">
         <f>IF(OR(E79="",F79=""),"", (F79/E79)-1)</f>
         <v/>
       </c>
-      <c r="J79" s="22">
+      <c r="J79" s="11">
         <f>IF(OR(C79="",D79=""),"", D79-C79)</f>
         <v/>
       </c>
-      <c r="K79" s="22" t="n"/>
+      <c r="K79" s="11" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="22" t="n"/>
-      <c r="B80" s="22" t="n"/>
-      <c r="C80" s="22" t="n"/>
-      <c r="D80" s="22" t="n"/>
-      <c r="E80" s="16" t="n"/>
-      <c r="F80" s="16" t="n"/>
-      <c r="G80" s="22" t="n"/>
-      <c r="H80" s="16">
+      <c r="A80" s="11" t="n"/>
+      <c r="B80" s="11" t="n"/>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="18">
         <f>IF(OR(E80="",F80="",G80=""),"", (F80-E80)*G80)</f>
         <v/>
       </c>
-      <c r="I80" s="17">
+      <c r="I80" s="20">
         <f>IF(OR(E80="",F80=""),"", (F80/E80)-1)</f>
         <v/>
       </c>
-      <c r="J80" s="22">
+      <c r="J80" s="11">
         <f>IF(OR(C80="",D80=""),"", D80-C80)</f>
         <v/>
       </c>
-      <c r="K80" s="22" t="n"/>
+      <c r="K80" s="11" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="22" t="n"/>
-      <c r="B81" s="22" t="n"/>
-      <c r="C81" s="22" t="n"/>
-      <c r="D81" s="22" t="n"/>
-      <c r="E81" s="16" t="n"/>
-      <c r="F81" s="16" t="n"/>
-      <c r="G81" s="22" t="n"/>
-      <c r="H81" s="16">
+      <c r="A81" s="11" t="n"/>
+      <c r="B81" s="11" t="n"/>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="11" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+      <c r="G81" s="11" t="n"/>
+      <c r="H81" s="18">
         <f>IF(OR(E81="",F81="",G81=""),"", (F81-E81)*G81)</f>
         <v/>
       </c>
-      <c r="I81" s="17">
+      <c r="I81" s="20">
         <f>IF(OR(E81="",F81=""),"", (F81/E81)-1)</f>
         <v/>
       </c>
-      <c r="J81" s="22">
+      <c r="J81" s="11">
         <f>IF(OR(C81="",D81=""),"", D81-C81)</f>
         <v/>
       </c>
-      <c r="K81" s="22" t="n"/>
+      <c r="K81" s="11" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="22" t="n"/>
-      <c r="B82" s="22" t="n"/>
-      <c r="C82" s="22" t="n"/>
-      <c r="D82" s="22" t="n"/>
-      <c r="E82" s="16" t="n"/>
-      <c r="F82" s="16" t="n"/>
-      <c r="G82" s="22" t="n"/>
-      <c r="H82" s="16">
+      <c r="A82" s="11" t="n"/>
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="18" t="n"/>
+      <c r="F82" s="18" t="n"/>
+      <c r="G82" s="11" t="n"/>
+      <c r="H82" s="18">
         <f>IF(OR(E82="",F82="",G82=""),"", (F82-E82)*G82)</f>
         <v/>
       </c>
-      <c r="I82" s="17">
+      <c r="I82" s="20">
         <f>IF(OR(E82="",F82=""),"", (F82/E82)-1)</f>
         <v/>
       </c>
-      <c r="J82" s="22">
+      <c r="J82" s="11">
         <f>IF(OR(C82="",D82=""),"", D82-C82)</f>
         <v/>
       </c>
-      <c r="K82" s="22" t="n"/>
+      <c r="K82" s="11" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="22" t="n"/>
-      <c r="B83" s="22" t="n"/>
-      <c r="C83" s="22" t="n"/>
-      <c r="D83" s="22" t="n"/>
-      <c r="E83" s="16" t="n"/>
-      <c r="F83" s="16" t="n"/>
-      <c r="G83" s="22" t="n"/>
-      <c r="H83" s="16">
+      <c r="A83" s="11" t="n"/>
+      <c r="B83" s="11" t="n"/>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="11" t="n"/>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="11" t="n"/>
+      <c r="H83" s="18">
         <f>IF(OR(E83="",F83="",G83=""),"", (F83-E83)*G83)</f>
         <v/>
       </c>
-      <c r="I83" s="17">
+      <c r="I83" s="20">
         <f>IF(OR(E83="",F83=""),"", (F83/E83)-1)</f>
         <v/>
       </c>
-      <c r="J83" s="22">
+      <c r="J83" s="11">
         <f>IF(OR(C83="",D83=""),"", D83-C83)</f>
         <v/>
       </c>
-      <c r="K83" s="22" t="n"/>
+      <c r="K83" s="11" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="22" t="n"/>
-      <c r="B84" s="22" t="n"/>
-      <c r="C84" s="22" t="n"/>
-      <c r="D84" s="22" t="n"/>
-      <c r="E84" s="16" t="n"/>
-      <c r="F84" s="16" t="n"/>
-      <c r="G84" s="22" t="n"/>
-      <c r="H84" s="16">
+      <c r="A84" s="11" t="n"/>
+      <c r="B84" s="11" t="n"/>
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="18">
         <f>IF(OR(E84="",F84="",G84=""),"", (F84-E84)*G84)</f>
         <v/>
       </c>
-      <c r="I84" s="17">
+      <c r="I84" s="20">
         <f>IF(OR(E84="",F84=""),"", (F84/E84)-1)</f>
         <v/>
       </c>
-      <c r="J84" s="22">
+      <c r="J84" s="11">
         <f>IF(OR(C84="",D84=""),"", D84-C84)</f>
         <v/>
       </c>
-      <c r="K84" s="22" t="n"/>
+      <c r="K84" s="11" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="22" t="n"/>
-      <c r="B85" s="22" t="n"/>
-      <c r="C85" s="22" t="n"/>
-      <c r="D85" s="22" t="n"/>
-      <c r="E85" s="16" t="n"/>
-      <c r="F85" s="16" t="n"/>
-      <c r="G85" s="22" t="n"/>
-      <c r="H85" s="16">
+      <c r="A85" s="11" t="n"/>
+      <c r="B85" s="11" t="n"/>
+      <c r="C85" s="11" t="n"/>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="18" t="n"/>
+      <c r="F85" s="18" t="n"/>
+      <c r="G85" s="11" t="n"/>
+      <c r="H85" s="18">
         <f>IF(OR(E85="",F85="",G85=""),"", (F85-E85)*G85)</f>
         <v/>
       </c>
-      <c r="I85" s="17">
+      <c r="I85" s="20">
         <f>IF(OR(E85="",F85=""),"", (F85/E85)-1)</f>
         <v/>
       </c>
-      <c r="J85" s="22">
+      <c r="J85" s="11">
         <f>IF(OR(C85="",D85=""),"", D85-C85)</f>
         <v/>
       </c>
-      <c r="K85" s="22" t="n"/>
+      <c r="K85" s="11" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="22" t="n"/>
-      <c r="B86" s="22" t="n"/>
-      <c r="C86" s="22" t="n"/>
-      <c r="D86" s="22" t="n"/>
-      <c r="E86" s="16" t="n"/>
-      <c r="F86" s="16" t="n"/>
-      <c r="G86" s="22" t="n"/>
-      <c r="H86" s="16">
+      <c r="A86" s="11" t="n"/>
+      <c r="B86" s="11" t="n"/>
+      <c r="C86" s="11" t="n"/>
+      <c r="D86" s="11" t="n"/>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="18" t="n"/>
+      <c r="G86" s="11" t="n"/>
+      <c r="H86" s="18">
         <f>IF(OR(E86="",F86="",G86=""),"", (F86-E86)*G86)</f>
         <v/>
       </c>
-      <c r="I86" s="17">
+      <c r="I86" s="20">
         <f>IF(OR(E86="",F86=""),"", (F86/E86)-1)</f>
         <v/>
       </c>
-      <c r="J86" s="22">
+      <c r="J86" s="11">
         <f>IF(OR(C86="",D86=""),"", D86-C86)</f>
         <v/>
       </c>
-      <c r="K86" s="22" t="n"/>
+      <c r="K86" s="11" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="22" t="n"/>
-      <c r="B87" s="22" t="n"/>
-      <c r="C87" s="22" t="n"/>
-      <c r="D87" s="22" t="n"/>
-      <c r="E87" s="16" t="n"/>
-      <c r="F87" s="16" t="n"/>
-      <c r="G87" s="22" t="n"/>
-      <c r="H87" s="16">
+      <c r="A87" s="11" t="n"/>
+      <c r="B87" s="11" t="n"/>
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="11" t="n"/>
+      <c r="E87" s="18" t="n"/>
+      <c r="F87" s="18" t="n"/>
+      <c r="G87" s="11" t="n"/>
+      <c r="H87" s="18">
         <f>IF(OR(E87="",F87="",G87=""),"", (F87-E87)*G87)</f>
         <v/>
       </c>
-      <c r="I87" s="17">
+      <c r="I87" s="20">
         <f>IF(OR(E87="",F87=""),"", (F87/E87)-1)</f>
         <v/>
       </c>
-      <c r="J87" s="22">
+      <c r="J87" s="11">
         <f>IF(OR(C87="",D87=""),"", D87-C87)</f>
         <v/>
       </c>
-      <c r="K87" s="22" t="n"/>
+      <c r="K87" s="11" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="22" t="n"/>
-      <c r="B88" s="22" t="n"/>
-      <c r="C88" s="22" t="n"/>
-      <c r="D88" s="22" t="n"/>
-      <c r="E88" s="16" t="n"/>
-      <c r="F88" s="16" t="n"/>
-      <c r="G88" s="22" t="n"/>
-      <c r="H88" s="16">
+      <c r="A88" s="11" t="n"/>
+      <c r="B88" s="11" t="n"/>
+      <c r="C88" s="11" t="n"/>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="18" t="n"/>
+      <c r="F88" s="18" t="n"/>
+      <c r="G88" s="11" t="n"/>
+      <c r="H88" s="18">
         <f>IF(OR(E88="",F88="",G88=""),"", (F88-E88)*G88)</f>
         <v/>
       </c>
-      <c r="I88" s="17">
+      <c r="I88" s="20">
         <f>IF(OR(E88="",F88=""),"", (F88/E88)-1)</f>
         <v/>
       </c>
-      <c r="J88" s="22">
+      <c r="J88" s="11">
         <f>IF(OR(C88="",D88=""),"", D88-C88)</f>
         <v/>
       </c>
-      <c r="K88" s="22" t="n"/>
+      <c r="K88" s="11" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="22" t="n"/>
-      <c r="B89" s="22" t="n"/>
-      <c r="C89" s="22" t="n"/>
-      <c r="D89" s="22" t="n"/>
-      <c r="E89" s="16" t="n"/>
-      <c r="F89" s="16" t="n"/>
-      <c r="G89" s="22" t="n"/>
-      <c r="H89" s="16">
+      <c r="A89" s="11" t="n"/>
+      <c r="B89" s="11" t="n"/>
+      <c r="C89" s="11" t="n"/>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+      <c r="G89" s="11" t="n"/>
+      <c r="H89" s="18">
         <f>IF(OR(E89="",F89="",G89=""),"", (F89-E89)*G89)</f>
         <v/>
       </c>
-      <c r="I89" s="17">
+      <c r="I89" s="20">
         <f>IF(OR(E89="",F89=""),"", (F89/E89)-1)</f>
         <v/>
       </c>
-      <c r="J89" s="22">
+      <c r="J89" s="11">
         <f>IF(OR(C89="",D89=""),"", D89-C89)</f>
         <v/>
       </c>
-      <c r="K89" s="22" t="n"/>
+      <c r="K89" s="11" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="n"/>
-      <c r="B90" s="22" t="n"/>
-      <c r="C90" s="22" t="n"/>
-      <c r="D90" s="22" t="n"/>
-      <c r="E90" s="16" t="n"/>
-      <c r="F90" s="16" t="n"/>
-      <c r="G90" s="22" t="n"/>
-      <c r="H90" s="16">
+      <c r="A90" s="11" t="n"/>
+      <c r="B90" s="11" t="n"/>
+      <c r="C90" s="11" t="n"/>
+      <c r="D90" s="11" t="n"/>
+      <c r="E90" s="18" t="n"/>
+      <c r="F90" s="18" t="n"/>
+      <c r="G90" s="11" t="n"/>
+      <c r="H90" s="18">
         <f>IF(OR(E90="",F90="",G90=""),"", (F90-E90)*G90)</f>
         <v/>
       </c>
-      <c r="I90" s="17">
+      <c r="I90" s="20">
         <f>IF(OR(E90="",F90=""),"", (F90/E90)-1)</f>
         <v/>
       </c>
-      <c r="J90" s="22">
+      <c r="J90" s="11">
         <f>IF(OR(C90="",D90=""),"", D90-C90)</f>
         <v/>
       </c>
-      <c r="K90" s="22" t="n"/>
+      <c r="K90" s="11" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="22" t="n"/>
-      <c r="B91" s="22" t="n"/>
-      <c r="C91" s="22" t="n"/>
-      <c r="D91" s="22" t="n"/>
-      <c r="E91" s="16" t="n"/>
-      <c r="F91" s="16" t="n"/>
-      <c r="G91" s="22" t="n"/>
-      <c r="H91" s="16">
+      <c r="A91" s="11" t="n"/>
+      <c r="B91" s="11" t="n"/>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="18" t="n"/>
+      <c r="F91" s="18" t="n"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="18">
         <f>IF(OR(E91="",F91="",G91=""),"", (F91-E91)*G91)</f>
         <v/>
       </c>
-      <c r="I91" s="17">
+      <c r="I91" s="20">
         <f>IF(OR(E91="",F91=""),"", (F91/E91)-1)</f>
         <v/>
       </c>
-      <c r="J91" s="22">
+      <c r="J91" s="11">
         <f>IF(OR(C91="",D91=""),"", D91-C91)</f>
         <v/>
       </c>
-      <c r="K91" s="22" t="n"/>
+      <c r="K91" s="11" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="22" t="n"/>
-      <c r="B92" s="22" t="n"/>
-      <c r="C92" s="22" t="n"/>
-      <c r="D92" s="22" t="n"/>
-      <c r="E92" s="16" t="n"/>
-      <c r="F92" s="16" t="n"/>
-      <c r="G92" s="22" t="n"/>
-      <c r="H92" s="16">
+      <c r="A92" s="11" t="n"/>
+      <c r="B92" s="11" t="n"/>
+      <c r="C92" s="11" t="n"/>
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="18" t="n"/>
+      <c r="F92" s="18" t="n"/>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="18">
         <f>IF(OR(E92="",F92="",G92=""),"", (F92-E92)*G92)</f>
         <v/>
       </c>
-      <c r="I92" s="17">
+      <c r="I92" s="20">
         <f>IF(OR(E92="",F92=""),"", (F92/E92)-1)</f>
         <v/>
       </c>
-      <c r="J92" s="22">
+      <c r="J92" s="11">
         <f>IF(OR(C92="",D92=""),"", D92-C92)</f>
         <v/>
       </c>
-      <c r="K92" s="22" t="n"/>
+      <c r="K92" s="11" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="22" t="n"/>
-      <c r="B93" s="22" t="n"/>
-      <c r="C93" s="22" t="n"/>
-      <c r="D93" s="22" t="n"/>
-      <c r="E93" s="16" t="n"/>
-      <c r="F93" s="16" t="n"/>
-      <c r="G93" s="22" t="n"/>
-      <c r="H93" s="16">
+      <c r="A93" s="11" t="n"/>
+      <c r="B93" s="11" t="n"/>
+      <c r="C93" s="11" t="n"/>
+      <c r="D93" s="11" t="n"/>
+      <c r="E93" s="18" t="n"/>
+      <c r="F93" s="18" t="n"/>
+      <c r="G93" s="11" t="n"/>
+      <c r="H93" s="18">
         <f>IF(OR(E93="",F93="",G93=""),"", (F93-E93)*G93)</f>
         <v/>
       </c>
-      <c r="I93" s="17">
+      <c r="I93" s="20">
         <f>IF(OR(E93="",F93=""),"", (F93/E93)-1)</f>
         <v/>
       </c>
-      <c r="J93" s="22">
+      <c r="J93" s="11">
         <f>IF(OR(C93="",D93=""),"", D93-C93)</f>
         <v/>
       </c>
-      <c r="K93" s="22" t="n"/>
+      <c r="K93" s="11" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="22" t="n"/>
-      <c r="B94" s="22" t="n"/>
-      <c r="C94" s="22" t="n"/>
-      <c r="D94" s="22" t="n"/>
-      <c r="E94" s="16" t="n"/>
-      <c r="F94" s="16" t="n"/>
-      <c r="G94" s="22" t="n"/>
-      <c r="H94" s="16">
+      <c r="A94" s="11" t="n"/>
+      <c r="B94" s="11" t="n"/>
+      <c r="C94" s="11" t="n"/>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
+      <c r="G94" s="11" t="n"/>
+      <c r="H94" s="18">
         <f>IF(OR(E94="",F94="",G94=""),"", (F94-E94)*G94)</f>
         <v/>
       </c>
-      <c r="I94" s="17">
+      <c r="I94" s="20">
         <f>IF(OR(E94="",F94=""),"", (F94/E94)-1)</f>
         <v/>
       </c>
-      <c r="J94" s="22">
+      <c r="J94" s="11">
         <f>IF(OR(C94="",D94=""),"", D94-C94)</f>
         <v/>
       </c>
-      <c r="K94" s="22" t="n"/>
+      <c r="K94" s="11" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="22" t="n"/>
-      <c r="B95" s="22" t="n"/>
-      <c r="C95" s="22" t="n"/>
-      <c r="D95" s="22" t="n"/>
-      <c r="E95" s="16" t="n"/>
-      <c r="F95" s="16" t="n"/>
-      <c r="G95" s="22" t="n"/>
-      <c r="H95" s="16">
+      <c r="A95" s="11" t="n"/>
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="11" t="n"/>
+      <c r="E95" s="18" t="n"/>
+      <c r="F95" s="18" t="n"/>
+      <c r="G95" s="11" t="n"/>
+      <c r="H95" s="18">
         <f>IF(OR(E95="",F95="",G95=""),"", (F95-E95)*G95)</f>
         <v/>
       </c>
-      <c r="I95" s="17">
+      <c r="I95" s="20">
         <f>IF(OR(E95="",F95=""),"", (F95/E95)-1)</f>
         <v/>
       </c>
-      <c r="J95" s="22">
+      <c r="J95" s="11">
         <f>IF(OR(C95="",D95=""),"", D95-C95)</f>
         <v/>
       </c>
-      <c r="K95" s="22" t="n"/>
+      <c r="K95" s="11" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="22" t="n"/>
-      <c r="B96" s="22" t="n"/>
-      <c r="C96" s="22" t="n"/>
-      <c r="D96" s="22" t="n"/>
-      <c r="E96" s="16" t="n"/>
-      <c r="F96" s="16" t="n"/>
-      <c r="G96" s="22" t="n"/>
-      <c r="H96" s="16">
+      <c r="A96" s="11" t="n"/>
+      <c r="B96" s="11" t="n"/>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="11" t="n"/>
+      <c r="E96" s="18" t="n"/>
+      <c r="F96" s="18" t="n"/>
+      <c r="G96" s="11" t="n"/>
+      <c r="H96" s="18">
         <f>IF(OR(E96="",F96="",G96=""),"", (F96-E96)*G96)</f>
         <v/>
       </c>
-      <c r="I96" s="17">
+      <c r="I96" s="20">
         <f>IF(OR(E96="",F96=""),"", (F96/E96)-1)</f>
         <v/>
       </c>
-      <c r="J96" s="22">
+      <c r="J96" s="11">
         <f>IF(OR(C96="",D96=""),"", D96-C96)</f>
         <v/>
       </c>
-      <c r="K96" s="22" t="n"/>
+      <c r="K96" s="11" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="22" t="n"/>
-      <c r="B97" s="22" t="n"/>
-      <c r="C97" s="22" t="n"/>
-      <c r="D97" s="22" t="n"/>
-      <c r="E97" s="16" t="n"/>
-      <c r="F97" s="16" t="n"/>
-      <c r="G97" s="22" t="n"/>
-      <c r="H97" s="16">
+      <c r="A97" s="11" t="n"/>
+      <c r="B97" s="11" t="n"/>
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="18">
         <f>IF(OR(E97="",F97="",G97=""),"", (F97-E97)*G97)</f>
         <v/>
       </c>
-      <c r="I97" s="17">
+      <c r="I97" s="20">
         <f>IF(OR(E97="",F97=""),"", (F97/E97)-1)</f>
         <v/>
       </c>
-      <c r="J97" s="22">
+      <c r="J97" s="11">
         <f>IF(OR(C97="",D97=""),"", D97-C97)</f>
         <v/>
       </c>
-      <c r="K97" s="22" t="n"/>
+      <c r="K97" s="11" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="22" t="n"/>
-      <c r="B98" s="22" t="n"/>
-      <c r="C98" s="22" t="n"/>
-      <c r="D98" s="22" t="n"/>
-      <c r="E98" s="16" t="n"/>
-      <c r="F98" s="16" t="n"/>
-      <c r="G98" s="22" t="n"/>
-      <c r="H98" s="16">
+      <c r="A98" s="11" t="n"/>
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="11" t="n"/>
+      <c r="D98" s="11" t="n"/>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="18">
         <f>IF(OR(E98="",F98="",G98=""),"", (F98-E98)*G98)</f>
         <v/>
       </c>
-      <c r="I98" s="17">
+      <c r="I98" s="20">
         <f>IF(OR(E98="",F98=""),"", (F98/E98)-1)</f>
         <v/>
       </c>
-      <c r="J98" s="22">
+      <c r="J98" s="11">
         <f>IF(OR(C98="",D98=""),"", D98-C98)</f>
         <v/>
       </c>
-      <c r="K98" s="22" t="n"/>
+      <c r="K98" s="11" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="22" t="n"/>
-      <c r="B99" s="22" t="n"/>
-      <c r="C99" s="22" t="n"/>
-      <c r="D99" s="22" t="n"/>
-      <c r="E99" s="16" t="n"/>
-      <c r="F99" s="16" t="n"/>
-      <c r="G99" s="22" t="n"/>
-      <c r="H99" s="16">
+      <c r="A99" s="11" t="n"/>
+      <c r="B99" s="11" t="n"/>
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="11" t="n"/>
+      <c r="E99" s="18" t="n"/>
+      <c r="F99" s="18" t="n"/>
+      <c r="G99" s="11" t="n"/>
+      <c r="H99" s="18">
         <f>IF(OR(E99="",F99="",G99=""),"", (F99-E99)*G99)</f>
         <v/>
       </c>
-      <c r="I99" s="17">
+      <c r="I99" s="20">
         <f>IF(OR(E99="",F99=""),"", (F99/E99)-1)</f>
         <v/>
       </c>
-      <c r="J99" s="22">
+      <c r="J99" s="11">
         <f>IF(OR(C99="",D99=""),"", D99-C99)</f>
         <v/>
       </c>
-      <c r="K99" s="22" t="n"/>
+      <c r="K99" s="11" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="22" t="n"/>
-      <c r="B100" s="22" t="n"/>
-      <c r="C100" s="22" t="n"/>
-      <c r="D100" s="22" t="n"/>
-      <c r="E100" s="16" t="n"/>
-      <c r="F100" s="16" t="n"/>
-      <c r="G100" s="22" t="n"/>
-      <c r="H100" s="16">
+      <c r="A100" s="11" t="n"/>
+      <c r="B100" s="11" t="n"/>
+      <c r="C100" s="11" t="n"/>
+      <c r="D100" s="11" t="n"/>
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="18" t="n"/>
+      <c r="G100" s="11" t="n"/>
+      <c r="H100" s="18">
         <f>IF(OR(E100="",F100="",G100=""),"", (F100-E100)*G100)</f>
         <v/>
       </c>
-      <c r="I100" s="17">
+      <c r="I100" s="20">
         <f>IF(OR(E100="",F100=""),"", (F100/E100)-1)</f>
         <v/>
       </c>
-      <c r="J100" s="22">
+      <c r="J100" s="11">
         <f>IF(OR(C100="",D100=""),"", D100-C100)</f>
         <v/>
       </c>
-      <c r="K100" s="22" t="n"/>
+      <c r="K100" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -51182,79 +51209,79 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.04296875" customWidth="1" style="19" min="1" max="1"/>
-    <col width="16.0078125" customWidth="1" style="19" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Summary Stats</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Total Trades</t>
         </is>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="11">
         <f>COUNTIF(Scoreboard!A4:A100,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Winning Trades</t>
         </is>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="11">
         <f>COUNTIF(Scoreboard!H4:H100,"&gt;0")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Losing Trades</t>
         </is>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="11">
         <f>COUNTIF(Scoreboard!H4:H100,"&lt;0")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="20">
         <f>IF(B3=0,"",B4/B3)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Total P&amp;L</t>
         </is>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="18">
         <f>SUM(Scoreboard!H4:H100)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Average Return</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="20">
         <f>IF(B3=0,"",AVERAGEIF(Scoreboard!I4:I100,"&lt;&gt;"))</f>
         <v/>
       </c>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoreboard" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Daily_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Signal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scoreboard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK500"/>
+  <dimension ref="A1:AK501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47019,6 +47019,67 @@
         <v/>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>54.06000137329102</v>
+      </c>
+      <c r="C501" t="n">
+        <v>55.66249847412109</v>
+      </c>
+      <c r="D501" t="n">
+        <v>53.0099983215332</v>
+      </c>
+      <c r="E501" t="n">
+        <v>53.68999862670898</v>
+      </c>
+      <c r="I501" t="n">
+        <v>38.61000061035156</v>
+      </c>
+      <c r="J501" t="n">
+        <v>39.52000045776367</v>
+      </c>
+      <c r="K501" t="n">
+        <v>37.39500045776367</v>
+      </c>
+      <c r="L501" t="n">
+        <v>38.86000061035156</v>
+      </c>
+      <c r="P501" t="n">
+        <v>47.3650016784668</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>48.27000045776367</v>
+      </c>
+      <c r="R501" t="n">
+        <v>47.18000030517578</v>
+      </c>
+      <c r="S501" t="n">
+        <v>47.45999908447266</v>
+      </c>
+      <c r="W501" t="n">
+        <v>73.33499908447266</v>
+      </c>
+      <c r="X501" t="n">
+        <v>73.68000030517578</v>
+      </c>
+      <c r="Y501" t="n">
+        <v>71.86000061035156</v>
+      </c>
+      <c r="Z501" t="n">
+        <v>73.20999908447266</v>
+      </c>
+      <c r="AD501" t="n">
+        <v>600.3800048828125</v>
+      </c>
+      <c r="AH501" t="n">
+        <v>393.9200134277344</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24964,7 +24964,7 @@
         <v>-0.1445</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.2391</v>
+        <v>-0.239</v>
       </c>
       <c r="AV4" t="n">
         <v>-1.183</v>
@@ -25026,7 +25026,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-1.1475</v>
+        <v>-1.1476</v>
       </c>
       <c r="G6" t="n">
         <v>0.5558999999999999</v>
@@ -25047,7 +25047,7 @@
         <v>5.4681</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.0493</v>
+        <v>3.0492</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.4399</v>
@@ -25056,7 +25056,7 @@
         <v>2.34</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1.799</v>
+        <v>-1.7991</v>
       </c>
       <c r="AP6" t="n">
         <v>-0.9287</v>
@@ -25120,7 +25120,7 @@
         <v>0.6575</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.417</v>
+        <v>2.4171</v>
       </c>
       <c r="AP7" t="n">
         <v>1.7091</v>
@@ -25227,7 +25227,7 @@
         <v>-5.0404</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6684</v>
+        <v>3.6685</v>
       </c>
       <c r="O9" t="n">
         <v>1.3534</v>
@@ -25245,7 +25245,7 @@
         <v>5.0527</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4.2995</v>
+        <v>-4.2994</v>
       </c>
       <c r="AC9" t="n">
         <v>-2.4742</v>
@@ -25403,7 +25403,7 @@
         <v>-0.339</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.727</v>
+        <v>-0.7271</v>
       </c>
       <c r="AQ11" t="n">
         <v>2.3316</v>
@@ -25574,13 +25574,13 @@
         <v>3.431</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7844</v>
+        <v>1.7843</v>
       </c>
       <c r="N14" t="n">
         <v>9.269500000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>12.3519</v>
+        <v>12.3518</v>
       </c>
       <c r="T14" t="n">
         <v>1.396</v>
@@ -25644,7 +25644,7 @@
         <v>-7.5155</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.5609</v>
+        <v>-5.5608</v>
       </c>
       <c r="N15" t="n">
         <v>2.2306</v>
@@ -25653,7 +25653,7 @@
         <v>2.1321</v>
       </c>
       <c r="T15" t="n">
-        <v>8.6538</v>
+        <v>8.6539</v>
       </c>
       <c r="U15" t="n">
         <v>0.6175</v>
@@ -25835,7 +25835,7 @@
         <v>-7.5959</v>
       </c>
       <c r="AX17" t="n">
-        <v>-5.3667</v>
+        <v>-5.3666</v>
       </c>
     </row>
     <row r="18">
@@ -25936,10 +25936,10 @@
         <v>-0.1035</v>
       </c>
       <c r="U19" t="n">
-        <v>10.1978</v>
+        <v>10.1979</v>
       </c>
       <c r="V19" t="n">
-        <v>26.5734</v>
+        <v>26.5735</v>
       </c>
       <c r="AA19" t="n">
         <v>-2.3474</v>
@@ -26143,10 +26143,10 @@
         <v>-28.3397</v>
       </c>
       <c r="T22" t="n">
-        <v>23.6621</v>
+        <v>23.662</v>
       </c>
       <c r="U22" t="n">
-        <v>57.1824</v>
+        <v>57.1823</v>
       </c>
       <c r="V22" t="n">
         <v>58.1105</v>
@@ -26289,7 +26289,7 @@
         <v>27.737</v>
       </c>
       <c r="V24" t="n">
-        <v>62.3619</v>
+        <v>62.3618</v>
       </c>
       <c r="AA24" t="n">
         <v>5.581</v>
@@ -26392,7 +26392,7 @@
         <v>18.5716</v>
       </c>
       <c r="AW25" t="n">
-        <v>16.488</v>
+        <v>16.4879</v>
       </c>
       <c r="AX25" t="n">
         <v>-3.0927</v>
@@ -26411,13 +26411,13 @@
         <v>5.2459</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.6004</v>
+        <v>-15.6003</v>
       </c>
       <c r="M26" t="n">
-        <v>-12.298</v>
+        <v>-12.2981</v>
       </c>
       <c r="N26" t="n">
-        <v>11.8546</v>
+        <v>11.8545</v>
       </c>
       <c r="O26" t="n">
         <v>-8.2704</v>
@@ -26484,7 +26484,7 @@
         <v>17.1821</v>
       </c>
       <c r="M27" t="n">
-        <v>5.2882</v>
+        <v>5.2883</v>
       </c>
       <c r="N27" t="n">
         <v>24.8843</v>
@@ -26532,7 +26532,7 @@
         <v>2.1648</v>
       </c>
       <c r="AW27" t="n">
-        <v>11.236</v>
+        <v>11.2359</v>
       </c>
       <c r="AX27" t="n">
         <v>9.2812</v>
@@ -26788,7 +26788,7 @@
         <v>8.9986</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.1253</v>
+        <v>1.1254</v>
       </c>
       <c r="AH31" t="n">
         <v>-0.9365</v>
@@ -26815,7 +26815,7 @@
         <v>-3.9504</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.2217</v>
+        <v>-1.2218</v>
       </c>
     </row>
     <row r="32">
@@ -26834,13 +26834,13 @@
         <v>-14.8583</v>
       </c>
       <c r="M32" t="n">
-        <v>-7.3073</v>
+        <v>-7.3074</v>
       </c>
       <c r="N32" t="n">
         <v>-15.9269</v>
       </c>
       <c r="O32" t="n">
-        <v>-13.8328</v>
+        <v>-13.8329</v>
       </c>
       <c r="T32" t="n">
         <v>5.2511</v>
@@ -27019,10 +27019,10 @@
         <v>-0.7489</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.7466</v>
+        <v>3.7465</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.9148</v>
+        <v>3.9147</v>
       </c>
       <c r="AX34" t="n">
         <v>-0.5973000000000001</v>
@@ -27047,10 +27047,10 @@
         <v>8.512</v>
       </c>
       <c r="N35" t="n">
-        <v>24.558</v>
+        <v>24.5581</v>
       </c>
       <c r="O35" t="n">
-        <v>15.1247</v>
+        <v>15.1248</v>
       </c>
       <c r="T35" t="n">
         <v>-17.4026</v>
@@ -27095,7 +27095,7 @@
         <v>11.8492</v>
       </c>
       <c r="AX35" t="n">
-        <v>9.343400000000001</v>
+        <v>9.343500000000001</v>
       </c>
     </row>
     <row r="36">
@@ -27178,7 +27178,7 @@
         <v>-0.4052</v>
       </c>
       <c r="G37" t="n">
-        <v>19.4363</v>
+        <v>19.4364</v>
       </c>
       <c r="H37" t="n">
         <v>41.1022</v>
@@ -27208,7 +27208,7 @@
         <v>-11.3814</v>
       </c>
       <c r="AC37" t="n">
-        <v>-23.6202</v>
+        <v>-23.6201</v>
       </c>
       <c r="AH37" t="n">
         <v>-0.6227</v>
@@ -27254,7 +27254,7 @@
         <v>29.1939</v>
       </c>
       <c r="M38" t="n">
-        <v>1.951</v>
+        <v>1.9509</v>
       </c>
       <c r="N38" t="n">
         <v>5.2359</v>
@@ -27415,7 +27415,7 @@
         <v>-3.3805</v>
       </c>
       <c r="AB40" t="n">
-        <v>-5.3014</v>
+        <v>-5.3013</v>
       </c>
       <c r="AC40" t="n">
         <v>-8.282400000000001</v>
@@ -27467,7 +27467,7 @@
         <v>4.6856</v>
       </c>
       <c r="N41" t="n">
-        <v>8.310499999999999</v>
+        <v>8.310600000000001</v>
       </c>
       <c r="O41" t="n">
         <v>10.3416</v>
@@ -27585,7 +27585,7 @@
         <v>2.5729</v>
       </c>
       <c r="AX42" t="n">
-        <v>2.2171</v>
+        <v>2.217</v>
       </c>
     </row>
     <row r="43">
@@ -27649,7 +27649,7 @@
         <v>1.2365</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.9546</v>
+        <v>-0.9545</v>
       </c>
       <c r="AW43" t="n">
         <v>1.7321</v>
@@ -27722,7 +27722,7 @@
         <v>1.7508</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.0053</v>
+        <v>0.0052</v>
       </c>
       <c r="AX44" t="n">
         <v>3.3725</v>
@@ -27762,7 +27762,7 @@
         <v>-12.9288</v>
       </c>
       <c r="AA45" t="n">
-        <v>-2.973</v>
+        <v>-2.9729</v>
       </c>
       <c r="AB45" t="n">
         <v>-1.4413</v>
@@ -27789,7 +27789,7 @@
         <v>1.3723</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.8945</v>
+        <v>0.8946</v>
       </c>
       <c r="AW45" t="n">
         <v>1.6811</v>
@@ -27814,7 +27814,7 @@
         <v>6.1701</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.2369</v>
+        <v>-0.2368</v>
       </c>
       <c r="N46" t="n">
         <v>3.9302</v>
@@ -27829,7 +27829,7 @@
         <v>-10.8635</v>
       </c>
       <c r="V46" t="n">
-        <v>-6.0482</v>
+        <v>-6.0481</v>
       </c>
       <c r="AA46" t="n">
         <v>0.2785</v>
@@ -27875,16 +27875,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>21.4033</v>
+        <v>21.4032</v>
       </c>
       <c r="G47" t="n">
         <v>28.991</v>
       </c>
       <c r="H47" t="n">
-        <v>31.2644</v>
+        <v>31.2643</v>
       </c>
       <c r="M47" t="n">
-        <v>12.1079</v>
+        <v>12.1078</v>
       </c>
       <c r="N47" t="n">
         <v>15.1742</v>
@@ -27905,7 +27905,7 @@
         <v>-12.0833</v>
       </c>
       <c r="AB47" t="n">
-        <v>-14.4595</v>
+        <v>-14.4594</v>
       </c>
       <c r="AC47" t="n">
         <v>-13.1091</v>
@@ -27945,7 +27945,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8.5814</v>
+        <v>8.5815</v>
       </c>
       <c r="G48" t="n">
         <v>36.164</v>
@@ -27969,13 +27969,13 @@
         <v>-30.3636</v>
       </c>
       <c r="V48" t="n">
-        <v>-35.9888</v>
+        <v>-35.9889</v>
       </c>
       <c r="AA48" t="n">
         <v>-4.5814</v>
       </c>
       <c r="AB48" t="n">
-        <v>-15.8774</v>
+        <v>-15.8775</v>
       </c>
       <c r="AC48" t="n">
         <v>-19.2783</v>
@@ -28103,7 +28103,7 @@
         <v>19.4045</v>
       </c>
       <c r="T50" t="n">
-        <v>1.8519</v>
+        <v>1.8518</v>
       </c>
       <c r="U50" t="n">
         <v>-7.8947</v>
@@ -28133,7 +28133,7 @@
         <v>0.1099</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.2448</v>
+        <v>2.2447</v>
       </c>
       <c r="AQ50" t="n">
         <v>6.3405</v>
@@ -28176,13 +28176,13 @@
         <v>0.4329</v>
       </c>
       <c r="U51" t="n">
-        <v>0.9573</v>
+        <v>0.9574</v>
       </c>
       <c r="V51" t="n">
         <v>-27.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>-1.1416</v>
+        <v>-1.1417</v>
       </c>
       <c r="AB51" t="n">
         <v>-3.2285</v>
@@ -28200,7 +28200,7 @@
         <v>10.3044</v>
       </c>
       <c r="AO51" t="n">
-        <v>0.4352</v>
+        <v>0.4353</v>
       </c>
       <c r="AP51" t="n">
         <v>1.1482</v>
@@ -28243,7 +28243,7 @@
         <v>8.3649</v>
       </c>
       <c r="T52" t="n">
-        <v>1.8966</v>
+        <v>1.8965</v>
       </c>
       <c r="U52" t="n">
         <v>4.2328</v>
@@ -28380,13 +28380,13 @@
         <v>-4.9125</v>
       </c>
       <c r="O54" t="n">
-        <v>-3.4395</v>
+        <v>-3.4394</v>
       </c>
       <c r="T54" t="n">
         <v>5.5556</v>
       </c>
       <c r="U54" t="n">
-        <v>8.1035</v>
+        <v>8.103400000000001</v>
       </c>
       <c r="V54" t="n">
         <v>10.582</v>
@@ -28395,7 +28395,7 @@
         <v>4.1119</v>
       </c>
       <c r="AB54" t="n">
-        <v>5.047</v>
+        <v>5.0471</v>
       </c>
       <c r="AC54" t="n">
         <v>3.4541</v>
@@ -28450,7 +28450,7 @@
         <v>-4.6762</v>
       </c>
       <c r="O55" t="n">
-        <v>-3.2445</v>
+        <v>-3.2446</v>
       </c>
       <c r="T55" t="n">
         <v>2.7911</v>
@@ -28483,7 +28483,7 @@
         <v>0.1871</v>
       </c>
       <c r="AP55" t="n">
-        <v>-1.5345</v>
+        <v>-1.5344</v>
       </c>
       <c r="AQ55" t="n">
         <v>-1.0111</v>
@@ -28514,7 +28514,7 @@
         <v>-14.4644</v>
       </c>
       <c r="M56" t="n">
-        <v>-2.8847</v>
+        <v>-2.8848</v>
       </c>
       <c r="N56" t="n">
         <v>-6.4466</v>
@@ -28538,7 +28538,7 @@
         <v>6.6554</v>
       </c>
       <c r="AC56" t="n">
-        <v>7.6134</v>
+        <v>7.6133</v>
       </c>
       <c r="AH56" t="n">
         <v>-1.3994</v>
@@ -28669,7 +28669,7 @@
         <v>-4.2669</v>
       </c>
       <c r="V58" t="n">
-        <v>3.872</v>
+        <v>3.8721</v>
       </c>
       <c r="AA58" t="n">
         <v>1.3675</v>
@@ -28727,7 +28727,7 @@
         <v>0.4855</v>
       </c>
       <c r="N59" t="n">
-        <v>6.1067</v>
+        <v>6.1068</v>
       </c>
       <c r="O59" t="n">
         <v>3.5767</v>
@@ -28879,7 +28879,7 @@
         <v>0.2431</v>
       </c>
       <c r="V61" t="n">
-        <v>-8.3025</v>
+        <v>-8.3024</v>
       </c>
       <c r="AA61" t="n">
         <v>-2.3177</v>
@@ -28912,7 +28912,7 @@
         <v>1.5078</v>
       </c>
       <c r="AW61" t="n">
-        <v>-0.1009</v>
+        <v>-0.1008</v>
       </c>
       <c r="AX61" t="n">
         <v>2.7004</v>
@@ -28943,7 +28943,7 @@
         <v>3.2986</v>
       </c>
       <c r="T62" t="n">
-        <v>-8.245699999999999</v>
+        <v>-8.245799999999999</v>
       </c>
       <c r="U62" t="n">
         <v>-7.0434</v>
@@ -29016,7 +29016,7 @@
         <v>-4.2291</v>
       </c>
       <c r="U63" t="n">
-        <v>-16.1265</v>
+        <v>-16.1266</v>
       </c>
       <c r="V63" t="n">
         <v>-11.9125</v>
@@ -29138,7 +29138,7 @@
         <v>1.967</v>
       </c>
       <c r="G65" t="n">
-        <v>4.8087</v>
+        <v>4.8088</v>
       </c>
       <c r="H65" t="n">
         <v>18.6147</v>
@@ -29232,7 +29232,7 @@
         <v>-18.9167</v>
       </c>
       <c r="AA66" t="n">
-        <v>-0.3579</v>
+        <v>-0.358</v>
       </c>
       <c r="AB66" t="n">
         <v>-0.9342</v>
@@ -29259,7 +29259,7 @@
         <v>1.4315</v>
       </c>
       <c r="AV66" t="n">
-        <v>2.3557</v>
+        <v>2.3558</v>
       </c>
       <c r="AW66" t="n">
         <v>2.6107</v>
@@ -29302,7 +29302,7 @@
         <v>-17.1806</v>
       </c>
       <c r="AA67" t="n">
-        <v>-2.0656</v>
+        <v>-2.0655</v>
       </c>
       <c r="AB67" t="n">
         <v>-5.1327</v>
@@ -29360,7 +29360,7 @@
         <v>1.334</v>
       </c>
       <c r="O68" t="n">
-        <v>1.8005</v>
+        <v>1.8004</v>
       </c>
       <c r="T68" t="n">
         <v>1.0638</v>
@@ -29439,7 +29439,7 @@
         <v>-5.7827</v>
       </c>
       <c r="V69" t="n">
-        <v>-14.0128</v>
+        <v>-14.0127</v>
       </c>
       <c r="AA69" t="n">
         <v>-0.6346000000000001</v>
@@ -29488,10 +29488,10 @@
         <v>-7.6072</v>
       </c>
       <c r="G70" t="n">
-        <v>-8.4513</v>
+        <v>-8.4514</v>
       </c>
       <c r="H70" t="n">
-        <v>4.4839</v>
+        <v>4.4838</v>
       </c>
       <c r="M70" t="n">
         <v>-3.7786</v>
@@ -29503,7 +29503,7 @@
         <v>-1.8596</v>
       </c>
       <c r="T70" t="n">
-        <v>7.6191</v>
+        <v>7.619</v>
       </c>
       <c r="U70" t="n">
         <v>8.1915</v>
@@ -29518,7 +29518,7 @@
         <v>4.3558</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.8345</v>
+        <v>1.8344</v>
       </c>
       <c r="AH70" t="n">
         <v>-2.3409</v>
@@ -29719,7 +29719,7 @@
         <v>-8.062900000000001</v>
       </c>
       <c r="V73" t="n">
-        <v>-1.579</v>
+        <v>-1.5789</v>
       </c>
       <c r="AA73" t="n">
         <v>0.1335</v>
@@ -29862,7 +29862,7 @@
         <v>-7.8663</v>
       </c>
       <c r="AA75" t="n">
-        <v>-3.11</v>
+        <v>-3.1099</v>
       </c>
       <c r="AB75" t="n">
         <v>-1.5576</v>
@@ -29908,7 +29908,7 @@
         <v>11.3332</v>
       </c>
       <c r="G76" t="n">
-        <v>11.1786</v>
+        <v>11.1787</v>
       </c>
       <c r="H76" t="n">
         <v>9.7064</v>
@@ -30032,7 +30032,7 @@
         <v>0.8975</v>
       </c>
       <c r="AW77" t="n">
-        <v>5.3752</v>
+        <v>5.3751</v>
       </c>
       <c r="AX77" t="n">
         <v>5.1276</v>
@@ -30054,7 +30054,7 @@
         <v>16.9813</v>
       </c>
       <c r="M78" t="n">
-        <v>2.7395</v>
+        <v>2.7396</v>
       </c>
       <c r="N78" t="n">
         <v>8.240600000000001</v>
@@ -30142,7 +30142,7 @@
         <v>-16.9038</v>
       </c>
       <c r="AA79" t="n">
-        <v>-0.9931</v>
+        <v>-0.993</v>
       </c>
       <c r="AB79" t="n">
         <v>-4.3783</v>
@@ -30191,7 +30191,7 @@
         <v>2.1562</v>
       </c>
       <c r="H80" t="n">
-        <v>16.7256</v>
+        <v>16.7255</v>
       </c>
       <c r="M80" t="n">
         <v>1.9405</v>
@@ -30617,7 +30617,7 @@
         <v>2.0715</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.0708</v>
+        <v>-0.0707</v>
       </c>
       <c r="O86" t="n">
         <v>4.7719</v>
@@ -30626,7 +30626,7 @@
         <v>-1.0753</v>
       </c>
       <c r="U86" t="n">
-        <v>-1.2081</v>
+        <v>-1.208</v>
       </c>
       <c r="V86" t="n">
         <v>-8</v>
@@ -30690,7 +30690,7 @@
         <v>1.7366</v>
       </c>
       <c r="O87" t="n">
-        <v>2.2546</v>
+        <v>2.2545</v>
       </c>
       <c r="T87" t="n">
         <v>-2.9891</v>
@@ -30754,7 +30754,7 @@
         <v>3.2539</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.7587</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="N88" t="n">
         <v>0.831</v>
@@ -30982,13 +30982,13 @@
         <v>-1.9022</v>
       </c>
       <c r="AA91" t="n">
-        <v>-0.3137</v>
+        <v>-0.3136</v>
       </c>
       <c r="AB91" t="n">
         <v>-1.5488</v>
       </c>
       <c r="AC91" t="n">
-        <v>-0.3137</v>
+        <v>-0.3136</v>
       </c>
       <c r="AH91" t="n">
         <v>-0.5227000000000001</v>
@@ -31049,7 +31049,7 @@
         <v>-3.1165</v>
       </c>
       <c r="V92" t="n">
-        <v>0.14</v>
+        <v>0.1401</v>
       </c>
       <c r="AA92" t="n">
         <v>-2.3597</v>
@@ -31079,7 +31079,7 @@
         <v>1.1432</v>
       </c>
       <c r="AV92" t="n">
-        <v>0.3828</v>
+        <v>0.3827</v>
       </c>
       <c r="AW92" t="n">
         <v>1.1073</v>
@@ -31265,7 +31265,7 @@
         <v>1.5744</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.4834</v>
+        <v>0.4833</v>
       </c>
       <c r="AC95" t="n">
         <v>-2.1955</v>
@@ -31329,10 +31329,10 @@
         <v>5.5866</v>
       </c>
       <c r="V96" t="n">
-        <v>4.7091</v>
+        <v>4.7092</v>
       </c>
       <c r="AA96" t="n">
-        <v>-1.2828</v>
+        <v>-1.2827</v>
       </c>
       <c r="AB96" t="n">
         <v>-1.23</v>
@@ -31362,10 +31362,10 @@
         <v>-0.6077</v>
       </c>
       <c r="AW96" t="n">
-        <v>-1.8927</v>
+        <v>-1.8928</v>
       </c>
       <c r="AX96" t="n">
-        <v>-1.4373</v>
+        <v>-1.4374</v>
       </c>
     </row>
     <row r="97">
@@ -31527,7 +31527,7 @@
         <v>0.9784</v>
       </c>
       <c r="N99" t="n">
-        <v>2.2199</v>
+        <v>2.22</v>
       </c>
       <c r="O99" t="n">
         <v>1.953</v>
@@ -31603,13 +31603,13 @@
         <v>3.0911</v>
       </c>
       <c r="T100" t="n">
-        <v>-0.4149</v>
+        <v>-0.415</v>
       </c>
       <c r="U100" t="n">
-        <v>-5.6356</v>
+        <v>-5.6357</v>
       </c>
       <c r="V100" t="n">
-        <v>-3.0955</v>
+        <v>-3.0956</v>
       </c>
       <c r="AA100" t="n">
         <v>0.4978</v>
@@ -31673,13 +31673,13 @@
         <v>2.1061</v>
       </c>
       <c r="T101" t="n">
-        <v>-1.9445</v>
+        <v>-1.9444</v>
       </c>
       <c r="U101" t="n">
         <v>-7.7124</v>
       </c>
       <c r="V101" t="n">
-        <v>-6.6137</v>
+        <v>-6.6138</v>
       </c>
       <c r="AA101" t="n">
         <v>-0.3852</v>
@@ -31877,10 +31877,10 @@
         <v>5.4752</v>
       </c>
       <c r="N104" t="n">
-        <v>-2.4863</v>
+        <v>-2.4864</v>
       </c>
       <c r="O104" t="n">
-        <v>-2.5949</v>
+        <v>-2.595</v>
       </c>
       <c r="T104" t="n">
         <v>-3.995</v>
@@ -31944,7 +31944,7 @@
         <v>-9.286</v>
       </c>
       <c r="M105" t="n">
-        <v>-2.081</v>
+        <v>-2.0809</v>
       </c>
       <c r="N105" t="n">
         <v>-2.9135</v>
@@ -32230,7 +32230,7 @@
         <v>2.8253</v>
       </c>
       <c r="O109" t="n">
-        <v>4.4477</v>
+        <v>4.4478</v>
       </c>
       <c r="T109" t="n">
         <v>0.4021</v>
@@ -32443,7 +32443,7 @@
         <v>5.4156</v>
       </c>
       <c r="T112" t="n">
-        <v>-0.3086</v>
+        <v>-0.3087</v>
       </c>
       <c r="U112" t="n">
         <v>-13.7517</v>
@@ -32513,7 +32513,7 @@
         <v>1.1936</v>
       </c>
       <c r="T113" t="n">
-        <v>6.966</v>
+        <v>6.9659</v>
       </c>
       <c r="U113" t="n">
         <v>2.068</v>
@@ -32723,7 +32723,7 @@
         <v>-7.5374</v>
       </c>
       <c r="T116" t="n">
-        <v>2.092</v>
+        <v>2.0921</v>
       </c>
       <c r="U116" t="n">
         <v>5.9334</v>
@@ -32784,7 +32784,7 @@
         <v>-13.8341</v>
       </c>
       <c r="M117" t="n">
-        <v>-1.391</v>
+        <v>-1.3909</v>
       </c>
       <c r="N117" t="n">
         <v>-7.1398</v>
@@ -32793,7 +32793,7 @@
         <v>-8.572900000000001</v>
       </c>
       <c r="T117" t="n">
-        <v>1.6394</v>
+        <v>1.6393</v>
       </c>
       <c r="U117" t="n">
         <v>8.613099999999999</v>
@@ -32863,7 +32863,7 @@
         <v>-3.0881</v>
       </c>
       <c r="T118" t="n">
-        <v>-8.467700000000001</v>
+        <v>-8.4678</v>
       </c>
       <c r="U118" t="n">
         <v>-5.0209</v>
@@ -32936,7 +32936,7 @@
         <v>0.7342</v>
       </c>
       <c r="U119" t="n">
-        <v>-6.2841</v>
+        <v>-6.2842</v>
       </c>
       <c r="V119" t="n">
         <v>0.146</v>
@@ -33003,7 +33003,7 @@
         <v>1.4439</v>
       </c>
       <c r="T120" t="n">
-        <v>-2.3324</v>
+        <v>-2.3323</v>
       </c>
       <c r="U120" t="n">
         <v>-9.946199999999999</v>
@@ -33289,7 +33289,7 @@
         <v>10.5263</v>
       </c>
       <c r="V124" t="n">
-        <v>7.1428</v>
+        <v>7.1429</v>
       </c>
       <c r="AA124" t="n">
         <v>2.507</v>
@@ -33353,7 +33353,7 @@
         <v>-1.6771</v>
       </c>
       <c r="T125" t="n">
-        <v>1.6327</v>
+        <v>1.6326</v>
       </c>
       <c r="U125" t="n">
         <v>13.6986</v>
@@ -33365,7 +33365,7 @@
         <v>-2.2283</v>
       </c>
       <c r="AB125" t="n">
-        <v>3.9283</v>
+        <v>3.9284</v>
       </c>
       <c r="AC125" t="n">
         <v>1.6384</v>
@@ -33636,7 +33636,7 @@
         <v>-0.292</v>
       </c>
       <c r="U129" t="n">
-        <v>-5.4016</v>
+        <v>-5.4017</v>
       </c>
       <c r="V129" t="n">
         <v>-7.0748</v>
@@ -33815,7 +33815,7 @@
         <v>2.5477</v>
       </c>
       <c r="AX131" t="n">
-        <v>4.5133</v>
+        <v>4.5132</v>
       </c>
     </row>
     <row r="132">
@@ -33925,7 +33925,7 @@
         <v>-2.5362</v>
       </c>
       <c r="AB133" t="n">
-        <v>-5.3373</v>
+        <v>-5.3372</v>
       </c>
       <c r="AC133" t="n">
         <v>-6.1628</v>
@@ -34254,7 +34254,7 @@
         <v>14.7667</v>
       </c>
       <c r="M138" t="n">
-        <v>1.6897</v>
+        <v>1.6896</v>
       </c>
       <c r="N138" t="n">
         <v>6.4985</v>
@@ -34823,7 +34823,7 @@
         <v>6.0869</v>
       </c>
       <c r="T146" t="n">
-        <v>-6.1225</v>
+        <v>-6.1224</v>
       </c>
       <c r="U146" t="n">
         <v>-13.371</v>
@@ -34887,7 +34887,7 @@
         <v>-1.3567</v>
       </c>
       <c r="N147" t="n">
-        <v>1.2573</v>
+        <v>1.2572</v>
       </c>
       <c r="O147" t="n">
         <v>3.4074</v>
@@ -35319,7 +35319,7 @@
         <v>2.934</v>
       </c>
       <c r="V153" t="n">
-        <v>-1.4051</v>
+        <v>-1.4052</v>
       </c>
       <c r="AA153" t="n">
         <v>-6.3007</v>
@@ -35377,7 +35377,7 @@
         <v>-2.0343</v>
       </c>
       <c r="N154" t="n">
-        <v>-6.7497</v>
+        <v>-6.7496</v>
       </c>
       <c r="O154" t="n">
         <v>-3.9692</v>
@@ -35587,7 +35587,7 @@
         <v>1.901</v>
       </c>
       <c r="N157" t="n">
-        <v>2.8281</v>
+        <v>2.828</v>
       </c>
       <c r="O157" t="n">
         <v>7.1289</v>
@@ -35794,7 +35794,7 @@
         <v>-3.977</v>
       </c>
       <c r="M160" t="n">
-        <v>-2.9415</v>
+        <v>-2.9414</v>
       </c>
       <c r="N160" t="n">
         <v>0.5866</v>
@@ -35937,7 +35937,7 @@
         <v>3.1151</v>
       </c>
       <c r="N162" t="n">
-        <v>2.5888</v>
+        <v>2.5889</v>
       </c>
       <c r="O162" t="n">
         <v>6.3179</v>
@@ -36013,7 +36013,7 @@
         <v>7.9155</v>
       </c>
       <c r="T163" t="n">
-        <v>-8.6021</v>
+        <v>-8.6022</v>
       </c>
       <c r="U163" t="n">
         <v>-19.0476</v>
@@ -36080,7 +36080,7 @@
         <v>11.0707</v>
       </c>
       <c r="O164" t="n">
-        <v>10.5038</v>
+        <v>10.5039</v>
       </c>
       <c r="T164" t="n">
         <v>-0.2941</v>
@@ -36789,7 +36789,7 @@
         <v>1.6807</v>
       </c>
       <c r="V174" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.548</v>
       </c>
       <c r="AA174" t="n">
         <v>0.8159999999999999</v>
@@ -36859,7 +36859,7 @@
         <v>-5.4348</v>
       </c>
       <c r="V175" t="n">
-        <v>5.136</v>
+        <v>5.1359</v>
       </c>
       <c r="AA175" t="n">
         <v>0.2943</v>
@@ -37407,7 +37407,7 @@
         <v>7.5822</v>
       </c>
       <c r="N183" t="n">
-        <v>2.109</v>
+        <v>2.1089</v>
       </c>
       <c r="O183" t="n">
         <v>0.1078</v>
@@ -37964,7 +37964,7 @@
         <v>12.7</v>
       </c>
       <c r="M191" t="n">
-        <v>1.1529</v>
+        <v>1.153</v>
       </c>
       <c r="N191" t="n">
         <v>1.5371</v>
@@ -38116,7 +38116,7 @@
         <v>0</v>
       </c>
       <c r="U193" t="n">
-        <v>-6.0897</v>
+        <v>-6.0898</v>
       </c>
       <c r="V193" t="n">
         <v>-9.0062</v>
@@ -38253,7 +38253,7 @@
         <v>1.0809</v>
       </c>
       <c r="T195" t="n">
-        <v>1.7731</v>
+        <v>1.773</v>
       </c>
       <c r="U195" t="n">
         <v>-2.0478</v>
@@ -38323,7 +38323,7 @@
         <v>-5.9305</v>
       </c>
       <c r="T196" t="n">
-        <v>14.6341</v>
+        <v>14.6342</v>
       </c>
       <c r="U196" t="n">
         <v>12.2867</v>
@@ -38609,7 +38609,7 @@
         <v>4.1916</v>
       </c>
       <c r="V200" t="n">
-        <v>21.2543</v>
+        <v>21.2544</v>
       </c>
       <c r="AA200" t="n">
         <v>-4.2853</v>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24998,7 +24998,7 @@
         <v>-3.3763</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.761200000000001</v>
+        <v>8.7613</v>
       </c>
       <c r="AH5" t="n">
         <v>2.9409</v>
@@ -25010,7 +25010,7 @@
         <v>1.1281</v>
       </c>
       <c r="AP5" t="n">
-        <v>-3.0236</v>
+        <v>-3.0237</v>
       </c>
       <c r="AV5" t="n">
         <v>2.0612</v>
@@ -25026,7 +25026,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-1.1476</v>
+        <v>-1.1475</v>
       </c>
       <c r="G6" t="n">
         <v>0.5558999999999999</v>
@@ -25047,7 +25047,7 @@
         <v>5.4681</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.0492</v>
+        <v>3.0493</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.4399</v>
@@ -25056,7 +25056,7 @@
         <v>2.34</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1.7991</v>
+        <v>-1.799</v>
       </c>
       <c r="AP6" t="n">
         <v>-0.9287</v>
@@ -25084,7 +25084,7 @@
         <v>-5.1724</v>
       </c>
       <c r="M7" t="n">
-        <v>7.0946</v>
+        <v>7.0947</v>
       </c>
       <c r="N7" t="n">
         <v>4.7031</v>
@@ -25099,7 +25099,7 @@
         <v>-13.4445</v>
       </c>
       <c r="V7" t="n">
-        <v>2.092</v>
+        <v>2.0921</v>
       </c>
       <c r="AA7" t="n">
         <v>-7.1067</v>
@@ -25175,7 +25175,7 @@
         <v>-1.933</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.921</v>
+        <v>-3.9211</v>
       </c>
       <c r="AC8" t="n">
         <v>-6.1246</v>
@@ -25315,10 +25315,10 @@
         <v>-3.8055</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.8984</v>
+        <v>-0.8985</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.9074</v>
+        <v>-2.9075</v>
       </c>
       <c r="AH10" t="n">
         <v>0.8828</v>
@@ -25403,7 +25403,7 @@
         <v>-0.339</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.7271</v>
+        <v>-0.727</v>
       </c>
       <c r="AQ11" t="n">
         <v>2.3316</v>
@@ -25458,7 +25458,7 @@
         <v>-3.8055</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.8984</v>
+        <v>-0.8985</v>
       </c>
       <c r="AH12" t="n">
         <v>-1.0042</v>
@@ -25574,13 +25574,13 @@
         <v>3.431</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7843</v>
+        <v>1.7844</v>
       </c>
       <c r="N14" t="n">
         <v>9.269500000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>12.3518</v>
+        <v>12.3519</v>
       </c>
       <c r="T14" t="n">
         <v>1.396</v>
@@ -25644,16 +25644,16 @@
         <v>-7.5155</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.5608</v>
+        <v>-5.5609</v>
       </c>
       <c r="N15" t="n">
         <v>2.2306</v>
       </c>
       <c r="O15" t="n">
-        <v>2.1321</v>
+        <v>2.132</v>
       </c>
       <c r="T15" t="n">
-        <v>8.6539</v>
+        <v>8.6538</v>
       </c>
       <c r="U15" t="n">
         <v>0.6175</v>
@@ -25939,7 +25939,7 @@
         <v>10.1979</v>
       </c>
       <c r="V19" t="n">
-        <v>26.5735</v>
+        <v>26.5734</v>
       </c>
       <c r="AA19" t="n">
         <v>-2.3474</v>
@@ -25948,7 +25948,7 @@
         <v>5.554</v>
       </c>
       <c r="AC19" t="n">
-        <v>13.324</v>
+        <v>13.3241</v>
       </c>
       <c r="AH19" t="n">
         <v>0.4823</v>
@@ -26030,7 +26030,7 @@
         <v>-3.5674</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.7298</v>
+        <v>0.7299</v>
       </c>
       <c r="AP20" t="n">
         <v>1.5375</v>
@@ -26289,7 +26289,7 @@
         <v>27.737</v>
       </c>
       <c r="V24" t="n">
-        <v>62.3618</v>
+        <v>62.3619</v>
       </c>
       <c r="AA24" t="n">
         <v>5.581</v>
@@ -26392,7 +26392,7 @@
         <v>18.5716</v>
       </c>
       <c r="AW25" t="n">
-        <v>16.4879</v>
+        <v>16.488</v>
       </c>
       <c r="AX25" t="n">
         <v>-3.0927</v>
@@ -26411,7 +26411,7 @@
         <v>5.2459</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.6003</v>
+        <v>-15.6004</v>
       </c>
       <c r="M26" t="n">
         <v>-12.2981</v>
@@ -26557,7 +26557,7 @@
         <v>2.0996</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.7214</v>
+        <v>-5.7213</v>
       </c>
       <c r="O28" t="n">
         <v>20.2424</v>
@@ -26730,7 +26730,7 @@
         <v>-7.8167</v>
       </c>
       <c r="AO30" t="n">
-        <v>-3.0153</v>
+        <v>-3.0154</v>
       </c>
       <c r="AP30" t="n">
         <v>-2.2491</v>
@@ -26788,7 +26788,7 @@
         <v>8.9986</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.1254</v>
+        <v>1.1253</v>
       </c>
       <c r="AH31" t="n">
         <v>-0.9365</v>
@@ -26815,7 +26815,7 @@
         <v>-3.9504</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.2218</v>
+        <v>-1.2217</v>
       </c>
     </row>
     <row r="32">
@@ -26834,13 +26834,13 @@
         <v>-14.8583</v>
       </c>
       <c r="M32" t="n">
-        <v>-7.3074</v>
+        <v>-7.3073</v>
       </c>
       <c r="N32" t="n">
         <v>-15.9269</v>
       </c>
       <c r="O32" t="n">
-        <v>-13.8329</v>
+        <v>-13.8328</v>
       </c>
       <c r="T32" t="n">
         <v>5.2511</v>
@@ -27019,10 +27019,10 @@
         <v>-0.7489</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.7465</v>
+        <v>3.7466</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.9147</v>
+        <v>3.9148</v>
       </c>
       <c r="AX34" t="n">
         <v>-0.5973000000000001</v>
@@ -27047,7 +27047,7 @@
         <v>8.512</v>
       </c>
       <c r="N35" t="n">
-        <v>24.5581</v>
+        <v>24.558</v>
       </c>
       <c r="O35" t="n">
         <v>15.1248</v>
@@ -27129,13 +27129,13 @@
         <v>-28.785</v>
       </c>
       <c r="V36" t="n">
-        <v>-29.2999</v>
+        <v>-29.2998</v>
       </c>
       <c r="AA36" t="n">
         <v>-3.2702</v>
       </c>
       <c r="AB36" t="n">
-        <v>-17.3197</v>
+        <v>-17.3198</v>
       </c>
       <c r="AC36" t="n">
         <v>-18.0901</v>
@@ -27178,7 +27178,7 @@
         <v>-0.4052</v>
       </c>
       <c r="G37" t="n">
-        <v>19.4364</v>
+        <v>19.4363</v>
       </c>
       <c r="H37" t="n">
         <v>41.1022</v>
@@ -27254,7 +27254,7 @@
         <v>29.1939</v>
       </c>
       <c r="M38" t="n">
-        <v>1.9509</v>
+        <v>1.951</v>
       </c>
       <c r="N38" t="n">
         <v>5.2359</v>
@@ -27366,7 +27366,7 @@
         <v>0.6158</v>
       </c>
       <c r="AQ39" t="n">
-        <v>4.6001</v>
+        <v>4.6</v>
       </c>
       <c r="AV39" t="n">
         <v>0.7287</v>
@@ -27412,10 +27412,10 @@
         <v>-0.6813</v>
       </c>
       <c r="AA40" t="n">
-        <v>-3.3805</v>
+        <v>-3.3806</v>
       </c>
       <c r="AB40" t="n">
-        <v>-5.3013</v>
+        <v>-5.3014</v>
       </c>
       <c r="AC40" t="n">
         <v>-8.282400000000001</v>
@@ -27467,7 +27467,7 @@
         <v>4.6856</v>
       </c>
       <c r="N41" t="n">
-        <v>8.310600000000001</v>
+        <v>8.310499999999999</v>
       </c>
       <c r="O41" t="n">
         <v>10.3416</v>
@@ -27488,7 +27488,7 @@
         <v>-7.9472</v>
       </c>
       <c r="AC41" t="n">
-        <v>-9.6051</v>
+        <v>-9.605</v>
       </c>
       <c r="AH41" t="n">
         <v>3.17</v>
@@ -27585,7 +27585,7 @@
         <v>2.5729</v>
       </c>
       <c r="AX42" t="n">
-        <v>2.217</v>
+        <v>2.2171</v>
       </c>
     </row>
     <row r="43">
@@ -27616,7 +27616,7 @@
         <v>3.2796</v>
       </c>
       <c r="U43" t="n">
-        <v>-5.2771</v>
+        <v>-5.277</v>
       </c>
       <c r="V43" t="n">
         <v>-7.0911</v>
@@ -27649,7 +27649,7 @@
         <v>1.2365</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.9545</v>
+        <v>-0.9546</v>
       </c>
       <c r="AW43" t="n">
         <v>1.7321</v>
@@ -27683,7 +27683,7 @@
         <v>4.5918</v>
       </c>
       <c r="T44" t="n">
-        <v>-5.1253</v>
+        <v>-5.1254</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -27747,7 +27747,7 @@
         <v>2.9791</v>
       </c>
       <c r="N45" t="n">
-        <v>1.2157</v>
+        <v>1.2158</v>
       </c>
       <c r="O45" t="n">
         <v>4.1219</v>
@@ -27762,7 +27762,7 @@
         <v>-12.9288</v>
       </c>
       <c r="AA45" t="n">
-        <v>-2.9729</v>
+        <v>-2.973</v>
       </c>
       <c r="AB45" t="n">
         <v>-1.4413</v>
@@ -27829,7 +27829,7 @@
         <v>-10.8635</v>
       </c>
       <c r="V46" t="n">
-        <v>-6.0481</v>
+        <v>-6.0482</v>
       </c>
       <c r="AA46" t="n">
         <v>0.2785</v>
@@ -27875,13 +27875,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>21.4032</v>
+        <v>21.4033</v>
       </c>
       <c r="G47" t="n">
         <v>28.991</v>
       </c>
       <c r="H47" t="n">
-        <v>31.2643</v>
+        <v>31.2644</v>
       </c>
       <c r="M47" t="n">
         <v>12.1078</v>
@@ -27890,7 +27890,7 @@
         <v>15.1742</v>
       </c>
       <c r="O47" t="n">
-        <v>13.202</v>
+        <v>13.2021</v>
       </c>
       <c r="T47" t="n">
         <v>-21.625</v>
@@ -27905,7 +27905,7 @@
         <v>-12.0833</v>
       </c>
       <c r="AB47" t="n">
-        <v>-14.4594</v>
+        <v>-14.4595</v>
       </c>
       <c r="AC47" t="n">
         <v>-13.1091</v>
@@ -27945,7 +27945,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8.5815</v>
+        <v>8.5814</v>
       </c>
       <c r="G48" t="n">
         <v>36.164</v>
@@ -27975,7 +27975,7 @@
         <v>-4.5814</v>
       </c>
       <c r="AB48" t="n">
-        <v>-15.8775</v>
+        <v>-15.8774</v>
       </c>
       <c r="AC48" t="n">
         <v>-19.2783</v>
@@ -27993,7 +27993,7 @@
         <v>1.5241</v>
       </c>
       <c r="AP48" t="n">
-        <v>5.591</v>
+        <v>5.5909</v>
       </c>
       <c r="AQ48" t="n">
         <v>7.1</v>
@@ -28024,7 +28024,7 @@
         <v>41.8675</v>
       </c>
       <c r="M49" t="n">
-        <v>1.7645</v>
+        <v>1.7646</v>
       </c>
       <c r="N49" t="n">
         <v>19.3149</v>
@@ -28103,7 +28103,7 @@
         <v>19.4045</v>
       </c>
       <c r="T50" t="n">
-        <v>1.8518</v>
+        <v>1.8519</v>
       </c>
       <c r="U50" t="n">
         <v>-7.8947</v>
@@ -28133,7 +28133,7 @@
         <v>0.1099</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.2447</v>
+        <v>2.2448</v>
       </c>
       <c r="AQ50" t="n">
         <v>6.3405</v>
@@ -28167,7 +28167,7 @@
         <v>1.2326</v>
       </c>
       <c r="N51" t="n">
-        <v>3.341</v>
+        <v>3.3411</v>
       </c>
       <c r="O51" t="n">
         <v>21.1633</v>
@@ -28182,7 +28182,7 @@
         <v>-27.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>-1.1417</v>
+        <v>-1.1416</v>
       </c>
       <c r="AB51" t="n">
         <v>-3.2285</v>
@@ -28200,7 +28200,7 @@
         <v>10.3044</v>
       </c>
       <c r="AO51" t="n">
-        <v>0.4353</v>
+        <v>0.4352</v>
       </c>
       <c r="AP51" t="n">
         <v>1.1482</v>
@@ -28352,7 +28352,7 @@
         <v>-0.1463</v>
       </c>
       <c r="AW53" t="n">
-        <v>-0.8763</v>
+        <v>-0.8762</v>
       </c>
       <c r="AX53" t="n">
         <v>-1.0385</v>
@@ -28380,7 +28380,7 @@
         <v>-4.9125</v>
       </c>
       <c r="O54" t="n">
-        <v>-3.4394</v>
+        <v>-3.4395</v>
       </c>
       <c r="T54" t="n">
         <v>5.5556</v>
@@ -28450,7 +28450,7 @@
         <v>-4.6762</v>
       </c>
       <c r="O55" t="n">
-        <v>-3.2446</v>
+        <v>-3.2445</v>
       </c>
       <c r="T55" t="n">
         <v>2.7911</v>
@@ -28483,7 +28483,7 @@
         <v>0.1871</v>
       </c>
       <c r="AP55" t="n">
-        <v>-1.5344</v>
+        <v>-1.5345</v>
       </c>
       <c r="AQ55" t="n">
         <v>-1.0111</v>
@@ -28657,7 +28657,7 @@
         <v>-1.2828</v>
       </c>
       <c r="N58" t="n">
-        <v>2.548</v>
+        <v>2.5479</v>
       </c>
       <c r="O58" t="n">
         <v>-1.2131</v>
@@ -28669,7 +28669,7 @@
         <v>-4.2669</v>
       </c>
       <c r="V58" t="n">
-        <v>3.8721</v>
+        <v>3.872</v>
       </c>
       <c r="AA58" t="n">
         <v>1.3675</v>
@@ -28836,7 +28836,7 @@
         <v>-0.4048</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.9942</v>
+        <v>0.9941</v>
       </c>
       <c r="AV60" t="n">
         <v>-1.9848</v>
@@ -28879,7 +28879,7 @@
         <v>0.2431</v>
       </c>
       <c r="V61" t="n">
-        <v>-8.3024</v>
+        <v>-8.3025</v>
       </c>
       <c r="AA61" t="n">
         <v>-2.3177</v>
@@ -28912,7 +28912,7 @@
         <v>1.5078</v>
       </c>
       <c r="AW61" t="n">
-        <v>-0.1008</v>
+        <v>-0.1009</v>
       </c>
       <c r="AX61" t="n">
         <v>2.7004</v>
@@ -29028,7 +29028,7 @@
         <v>-5.2676</v>
       </c>
       <c r="AC63" t="n">
-        <v>-5.2277</v>
+        <v>-5.2276</v>
       </c>
       <c r="AH63" t="n">
         <v>1.1898</v>
@@ -29138,7 +29138,7 @@
         <v>1.967</v>
       </c>
       <c r="G65" t="n">
-        <v>4.8088</v>
+        <v>4.8087</v>
       </c>
       <c r="H65" t="n">
         <v>18.6147</v>
@@ -29232,7 +29232,7 @@
         <v>-18.9167</v>
       </c>
       <c r="AA66" t="n">
-        <v>-0.358</v>
+        <v>-0.3579</v>
       </c>
       <c r="AB66" t="n">
         <v>-0.9342</v>
@@ -29302,7 +29302,7 @@
         <v>-17.1806</v>
       </c>
       <c r="AA67" t="n">
-        <v>-2.0655</v>
+        <v>-2.0656</v>
       </c>
       <c r="AB67" t="n">
         <v>-5.1327</v>
@@ -29360,7 +29360,7 @@
         <v>1.334</v>
       </c>
       <c r="O68" t="n">
-        <v>1.8004</v>
+        <v>1.8005</v>
       </c>
       <c r="T68" t="n">
         <v>1.0638</v>
@@ -29463,7 +29463,7 @@
         <v>0.2348</v>
       </c>
       <c r="AP69" t="n">
-        <v>0.5578</v>
+        <v>0.5577</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.6902</v>
@@ -29488,10 +29488,10 @@
         <v>-7.6072</v>
       </c>
       <c r="G70" t="n">
-        <v>-8.4514</v>
+        <v>-8.4513</v>
       </c>
       <c r="H70" t="n">
-        <v>4.4838</v>
+        <v>4.4839</v>
       </c>
       <c r="M70" t="n">
         <v>-3.7786</v>
@@ -29503,7 +29503,7 @@
         <v>-1.8596</v>
       </c>
       <c r="T70" t="n">
-        <v>7.619</v>
+        <v>7.6191</v>
       </c>
       <c r="U70" t="n">
         <v>8.1915</v>
@@ -29518,7 +29518,7 @@
         <v>4.3558</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.8344</v>
+        <v>1.8345</v>
       </c>
       <c r="AH70" t="n">
         <v>-2.3409</v>
@@ -29533,7 +29533,7 @@
         <v>-1.2555</v>
       </c>
       <c r="AP70" t="n">
-        <v>-1.3572</v>
+        <v>-1.3571</v>
       </c>
       <c r="AQ70" t="n">
         <v>-0.5586</v>
@@ -29582,7 +29582,7 @@
         <v>-7.9761</v>
       </c>
       <c r="AA71" t="n">
-        <v>-4.1301</v>
+        <v>-4.13</v>
       </c>
       <c r="AB71" t="n">
         <v>-1.0879</v>
@@ -29719,13 +29719,13 @@
         <v>-8.062900000000001</v>
       </c>
       <c r="V73" t="n">
-        <v>-1.5789</v>
+        <v>-1.579</v>
       </c>
       <c r="AA73" t="n">
         <v>0.1335</v>
       </c>
       <c r="AB73" t="n">
-        <v>-1.1424</v>
+        <v>-1.1423</v>
       </c>
       <c r="AC73" t="n">
         <v>1.9946</v>
@@ -29868,7 +29868,7 @@
         <v>-1.5576</v>
       </c>
       <c r="AC75" t="n">
-        <v>-2.812</v>
+        <v>-2.8119</v>
       </c>
       <c r="AH75" t="n">
         <v>0.634</v>
@@ -29908,7 +29908,7 @@
         <v>11.3332</v>
       </c>
       <c r="G76" t="n">
-        <v>11.1787</v>
+        <v>11.1786</v>
       </c>
       <c r="H76" t="n">
         <v>9.7064</v>
@@ -29929,7 +29929,7 @@
         <v>-11.1266</v>
       </c>
       <c r="V76" t="n">
-        <v>-9.9712</v>
+        <v>-9.9711</v>
       </c>
       <c r="AA76" t="n">
         <v>-4.566</v>
@@ -30032,7 +30032,7 @@
         <v>0.8975</v>
       </c>
       <c r="AW77" t="n">
-        <v>5.3751</v>
+        <v>5.3752</v>
       </c>
       <c r="AX77" t="n">
         <v>5.1276</v>
@@ -30054,7 +30054,7 @@
         <v>16.9813</v>
       </c>
       <c r="M78" t="n">
-        <v>2.7396</v>
+        <v>2.7395</v>
       </c>
       <c r="N78" t="n">
         <v>8.240600000000001</v>
@@ -30142,7 +30142,7 @@
         <v>-16.9038</v>
       </c>
       <c r="AA79" t="n">
-        <v>-0.993</v>
+        <v>-0.9931</v>
       </c>
       <c r="AB79" t="n">
         <v>-4.3783</v>
@@ -30191,7 +30191,7 @@
         <v>2.1562</v>
       </c>
       <c r="H80" t="n">
-        <v>16.7255</v>
+        <v>16.7256</v>
       </c>
       <c r="M80" t="n">
         <v>1.9405</v>
@@ -30358,7 +30358,7 @@
         <v>-1.4042</v>
       </c>
       <c r="AC82" t="n">
-        <v>-5.0242</v>
+        <v>-5.0241</v>
       </c>
       <c r="AH82" t="n">
         <v>1.9613</v>
@@ -30617,7 +30617,7 @@
         <v>2.0715</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.0707</v>
+        <v>-0.0708</v>
       </c>
       <c r="O86" t="n">
         <v>4.7719</v>
@@ -30626,7 +30626,7 @@
         <v>-1.0753</v>
       </c>
       <c r="U86" t="n">
-        <v>-1.208</v>
+        <v>-1.2081</v>
       </c>
       <c r="V86" t="n">
         <v>-8</v>
@@ -30690,7 +30690,7 @@
         <v>1.7366</v>
       </c>
       <c r="O87" t="n">
-        <v>2.2545</v>
+        <v>2.2546</v>
       </c>
       <c r="T87" t="n">
         <v>-2.9891</v>
@@ -30754,7 +30754,7 @@
         <v>3.2539</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.7587</v>
       </c>
       <c r="N88" t="n">
         <v>0.831</v>
@@ -30790,7 +30790,7 @@
         <v>1.3645</v>
       </c>
       <c r="AO88" t="n">
-        <v>-0.225</v>
+        <v>-0.2251</v>
       </c>
       <c r="AP88" t="n">
         <v>0.3367</v>
@@ -30836,7 +30836,7 @@
         <v>2.7855</v>
       </c>
       <c r="U89" t="n">
-        <v>0.2717</v>
+        <v>0.2718</v>
       </c>
       <c r="V89" t="n">
         <v>-6.2262</v>
@@ -30915,7 +30915,7 @@
         <v>-0.2607</v>
       </c>
       <c r="AB90" t="n">
-        <v>-0.4164</v>
+        <v>-0.4165</v>
       </c>
       <c r="AC90" t="n">
         <v>-2.0481</v>
@@ -31079,7 +31079,7 @@
         <v>1.1432</v>
       </c>
       <c r="AV92" t="n">
-        <v>0.3827</v>
+        <v>0.3828</v>
       </c>
       <c r="AW92" t="n">
         <v>1.1073</v>
@@ -31122,7 +31122,7 @@
         <v>-0.2786</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.4296</v>
+        <v>0.4297</v>
       </c>
       <c r="AB93" t="n">
         <v>-2.2478</v>
@@ -31265,7 +31265,7 @@
         <v>1.5744</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.4833</v>
+        <v>0.4834</v>
       </c>
       <c r="AC95" t="n">
         <v>-2.1955</v>
@@ -31329,7 +31329,7 @@
         <v>5.5866</v>
       </c>
       <c r="V96" t="n">
-        <v>4.7092</v>
+        <v>4.7091</v>
       </c>
       <c r="AA96" t="n">
         <v>-1.2827</v>
@@ -31362,10 +31362,10 @@
         <v>-0.6077</v>
       </c>
       <c r="AW96" t="n">
-        <v>-1.8928</v>
+        <v>-1.8927</v>
       </c>
       <c r="AX96" t="n">
-        <v>-1.4374</v>
+        <v>-1.4373</v>
       </c>
     </row>
     <row r="97">
@@ -31408,7 +31408,7 @@
         <v>-0.38</v>
       </c>
       <c r="AC97" t="n">
-        <v>-1.4501</v>
+        <v>-1.45</v>
       </c>
       <c r="AH97" t="n">
         <v>0.4152</v>
@@ -31527,7 +31527,7 @@
         <v>0.9784</v>
       </c>
       <c r="N99" t="n">
-        <v>2.22</v>
+        <v>2.2199</v>
       </c>
       <c r="O99" t="n">
         <v>1.953</v>
@@ -31603,10 +31603,10 @@
         <v>3.0911</v>
       </c>
       <c r="T100" t="n">
-        <v>-0.415</v>
+        <v>-0.4149</v>
       </c>
       <c r="U100" t="n">
-        <v>-5.6357</v>
+        <v>-5.6356</v>
       </c>
       <c r="V100" t="n">
         <v>-3.0956</v>
@@ -31673,7 +31673,7 @@
         <v>2.1061</v>
       </c>
       <c r="T101" t="n">
-        <v>-1.9444</v>
+        <v>-1.9445</v>
       </c>
       <c r="U101" t="n">
         <v>-7.7124</v>
@@ -31877,10 +31877,10 @@
         <v>5.4752</v>
       </c>
       <c r="N104" t="n">
-        <v>-2.4864</v>
+        <v>-2.4863</v>
       </c>
       <c r="O104" t="n">
-        <v>-2.595</v>
+        <v>-2.5949</v>
       </c>
       <c r="T104" t="n">
         <v>-3.995</v>
@@ -31944,7 +31944,7 @@
         <v>-9.286</v>
       </c>
       <c r="M105" t="n">
-        <v>-2.0809</v>
+        <v>-2.081</v>
       </c>
       <c r="N105" t="n">
         <v>-2.9135</v>
@@ -32126,7 +32126,7 @@
         <v>0.9112</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.7487</v>
+        <v>0.7486</v>
       </c>
       <c r="AV107" t="n">
         <v>1.6503</v>
@@ -32230,7 +32230,7 @@
         <v>2.8253</v>
       </c>
       <c r="O109" t="n">
-        <v>4.4478</v>
+        <v>4.4477</v>
       </c>
       <c r="T109" t="n">
         <v>0.4021</v>
@@ -32242,7 +32242,7 @@
         <v>-2.6008</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.0297</v>
+        <v>1.0298</v>
       </c>
       <c r="AB109" t="n">
         <v>-2.5924</v>
@@ -32443,7 +32443,7 @@
         <v>5.4156</v>
       </c>
       <c r="T112" t="n">
-        <v>-0.3087</v>
+        <v>-0.3086</v>
       </c>
       <c r="U112" t="n">
         <v>-13.7517</v>
@@ -32470,10 +32470,10 @@
         <v>3.7098</v>
       </c>
       <c r="AO112" t="n">
-        <v>-0.0776</v>
+        <v>-0.0775</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.2289</v>
+        <v>1.229</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.8709</v>
@@ -32519,7 +32519,7 @@
         <v>2.068</v>
       </c>
       <c r="V113" t="n">
-        <v>-7.3726</v>
+        <v>-7.3727</v>
       </c>
       <c r="AA113" t="n">
         <v>1.5285</v>
@@ -32680,7 +32680,7 @@
         <v>-3.0756</v>
       </c>
       <c r="AO115" t="n">
-        <v>-1.3568</v>
+        <v>-1.3567</v>
       </c>
       <c r="AP115" t="n">
         <v>-1.8297</v>
@@ -32784,7 +32784,7 @@
         <v>-13.8341</v>
       </c>
       <c r="M117" t="n">
-        <v>-1.3909</v>
+        <v>-1.391</v>
       </c>
       <c r="N117" t="n">
         <v>-7.1398</v>
@@ -32863,7 +32863,7 @@
         <v>-3.0881</v>
       </c>
       <c r="T118" t="n">
-        <v>-8.4678</v>
+        <v>-8.467700000000001</v>
       </c>
       <c r="U118" t="n">
         <v>-5.0209</v>
@@ -32942,7 +32942,7 @@
         <v>0.146</v>
       </c>
       <c r="AA119" t="n">
-        <v>0.9577</v>
+        <v>0.9578</v>
       </c>
       <c r="AB119" t="n">
         <v>-2.2368</v>
@@ -32963,10 +32963,10 @@
         <v>-0.2885</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.7811</v>
+        <v>0.781</v>
       </c>
       <c r="AQ119" t="n">
-        <v>-1.1765</v>
+        <v>-1.1766</v>
       </c>
       <c r="AV119" t="n">
         <v>-0.2328</v>
@@ -33003,7 +33003,7 @@
         <v>1.4439</v>
       </c>
       <c r="T120" t="n">
-        <v>-2.3323</v>
+        <v>-2.3324</v>
       </c>
       <c r="U120" t="n">
         <v>-9.946199999999999</v>
@@ -33033,7 +33033,7 @@
         <v>0.4015</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.6563</v>
+        <v>1.6564</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.5849</v>
@@ -33085,7 +33085,7 @@
         <v>-0.3955</v>
       </c>
       <c r="AB121" t="n">
-        <v>-0.676</v>
+        <v>-0.6761</v>
       </c>
       <c r="AC121" t="n">
         <v>-3.8189</v>
@@ -33149,7 +33149,7 @@
         <v>-4.2274</v>
       </c>
       <c r="V122" t="n">
-        <v>-11.6935</v>
+        <v>-11.6936</v>
       </c>
       <c r="AA122" t="n">
         <v>-1.8151</v>
@@ -33295,7 +33295,7 @@
         <v>2.507</v>
       </c>
       <c r="AB124" t="n">
-        <v>4.3675</v>
+        <v>4.3676</v>
       </c>
       <c r="AC124" t="n">
         <v>2.6786</v>
@@ -33380,7 +33380,7 @@
         <v>-3.4777</v>
       </c>
       <c r="AO125" t="n">
-        <v>0.7867</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="AP125" t="n">
         <v>-1.2147</v>
@@ -33426,7 +33426,7 @@
         <v>-3.3467</v>
       </c>
       <c r="U126" t="n">
-        <v>1.1204</v>
+        <v>1.1205</v>
       </c>
       <c r="V126" t="n">
         <v>8.571400000000001</v>
@@ -33523,7 +33523,7 @@
         <v>0.1443</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.8458</v>
+        <v>1.8457</v>
       </c>
       <c r="AQ127" t="n">
         <v>-0.1768</v>
@@ -33563,7 +33563,7 @@
         <v>4.2189</v>
       </c>
       <c r="T128" t="n">
-        <v>-2.1429</v>
+        <v>-2.1428</v>
       </c>
       <c r="U128" t="n">
         <v>-8.299899999999999</v>
@@ -33642,7 +33642,7 @@
         <v>-7.0748</v>
       </c>
       <c r="AA129" t="n">
-        <v>-0.8139</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="AB129" t="n">
         <v>-2.4585</v>
@@ -33800,7 +33800,7 @@
         <v>4.8541</v>
       </c>
       <c r="AO131" t="n">
-        <v>0.5821</v>
+        <v>0.582</v>
       </c>
       <c r="AP131" t="n">
         <v>0.9</v>
@@ -33815,7 +33815,7 @@
         <v>2.5477</v>
       </c>
       <c r="AX131" t="n">
-        <v>4.5132</v>
+        <v>4.5133</v>
       </c>
     </row>
     <row r="132">
@@ -33983,7 +33983,7 @@
         <v>5.3999</v>
       </c>
       <c r="T134" t="n">
-        <v>-1.9481</v>
+        <v>-1.948</v>
       </c>
       <c r="U134" t="n">
         <v>-4.8819</v>
@@ -33998,7 +33998,7 @@
         <v>-3.401</v>
       </c>
       <c r="AC134" t="n">
-        <v>-5.0997</v>
+        <v>-5.0996</v>
       </c>
       <c r="AH134" t="n">
         <v>0.013</v>
@@ -34065,7 +34065,7 @@
         <v>0.6794</v>
       </c>
       <c r="AB135" t="n">
-        <v>-1.57</v>
+        <v>-1.5701</v>
       </c>
       <c r="AC135" t="n">
         <v>-4.3988</v>
@@ -34205,7 +34205,7 @@
         <v>-1.9546</v>
       </c>
       <c r="AB137" t="n">
-        <v>-3.953</v>
+        <v>-3.9531</v>
       </c>
       <c r="AC137" t="n">
         <v>-6.099</v>
@@ -34254,7 +34254,7 @@
         <v>14.7667</v>
       </c>
       <c r="M138" t="n">
-        <v>1.6896</v>
+        <v>1.6897</v>
       </c>
       <c r="N138" t="n">
         <v>6.4985</v>
@@ -34433,7 +34433,7 @@
         <v>-0.3511</v>
       </c>
       <c r="AP140" t="n">
-        <v>-0.427</v>
+        <v>-0.4269</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.151</v>
@@ -34625,7 +34625,7 @@
         <v>-1.3505</v>
       </c>
       <c r="AB143" t="n">
-        <v>-1.2234</v>
+        <v>-1.2235</v>
       </c>
       <c r="AC143" t="n">
         <v>1.9145</v>
@@ -34835,7 +34835,7 @@
         <v>-1.1326</v>
       </c>
       <c r="AB146" t="n">
-        <v>-3.2595</v>
+        <v>-3.2594</v>
       </c>
       <c r="AC146" t="n">
         <v>-5.7179</v>
@@ -34887,7 +34887,7 @@
         <v>-1.3567</v>
       </c>
       <c r="N147" t="n">
-        <v>1.2572</v>
+        <v>1.2573</v>
       </c>
       <c r="O147" t="n">
         <v>3.4074</v>
@@ -35377,7 +35377,7 @@
         <v>-2.0343</v>
       </c>
       <c r="N154" t="n">
-        <v>-6.7496</v>
+        <v>-6.7497</v>
       </c>
       <c r="O154" t="n">
         <v>-3.9692</v>
@@ -35483,7 +35483,7 @@
         <v>0.7057</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.1578</v>
+        <v>2.1577</v>
       </c>
       <c r="AQ155" t="n">
         <v>-1.5079</v>
@@ -35587,7 +35587,7 @@
         <v>1.901</v>
       </c>
       <c r="N157" t="n">
-        <v>2.828</v>
+        <v>2.8281</v>
       </c>
       <c r="O157" t="n">
         <v>7.1289</v>
@@ -35760,7 +35760,7 @@
         <v>3.5382</v>
       </c>
       <c r="AO159" t="n">
-        <v>-0.0262</v>
+        <v>-0.0261</v>
       </c>
       <c r="AP159" t="n">
         <v>1.8984</v>
@@ -35794,7 +35794,7 @@
         <v>-3.977</v>
       </c>
       <c r="M160" t="n">
-        <v>-2.9414</v>
+        <v>-2.9415</v>
       </c>
       <c r="N160" t="n">
         <v>0.5866</v>
@@ -35937,7 +35937,7 @@
         <v>3.1151</v>
       </c>
       <c r="N162" t="n">
-        <v>2.5889</v>
+        <v>2.5888</v>
       </c>
       <c r="O162" t="n">
         <v>6.3179</v>
@@ -36080,7 +36080,7 @@
         <v>11.0707</v>
       </c>
       <c r="O164" t="n">
-        <v>10.5039</v>
+        <v>10.5038</v>
       </c>
       <c r="T164" t="n">
         <v>-0.2941</v>
@@ -36308,7 +36308,7 @@
         <v>1.8576</v>
       </c>
       <c r="AC167" t="n">
-        <v>-5.7306</v>
+        <v>-5.7307</v>
       </c>
       <c r="AH167" t="n">
         <v>-0.1952</v>
@@ -36518,7 +36518,7 @@
         <v>2.6596</v>
       </c>
       <c r="AC170" t="n">
-        <v>5.8778</v>
+        <v>5.8777</v>
       </c>
       <c r="AH170" t="n">
         <v>1.9106</v>
@@ -36655,10 +36655,10 @@
         <v>1.0504</v>
       </c>
       <c r="AB172" t="n">
-        <v>4.6411</v>
+        <v>4.641</v>
       </c>
       <c r="AC172" t="n">
-        <v>9.650399999999999</v>
+        <v>9.650499999999999</v>
       </c>
       <c r="AH172" t="n">
         <v>-0.8459</v>
@@ -36816,7 +36816,7 @@
         <v>1.6185</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.3747</v>
+        <v>0.3746</v>
       </c>
       <c r="AV174" t="n">
         <v>-2.2682</v>
@@ -37072,7 +37072,7 @@
         <v>19.7059</v>
       </c>
       <c r="AA178" t="n">
-        <v>2.699</v>
+        <v>2.6989</v>
       </c>
       <c r="AB178" t="n">
         <v>8.8775</v>
@@ -37288,7 +37288,7 @@
         <v>9.0566</v>
       </c>
       <c r="AC181" t="n">
-        <v>11.7679</v>
+        <v>11.768</v>
       </c>
       <c r="AH181" t="n">
         <v>-4.2246</v>
@@ -37407,7 +37407,7 @@
         <v>7.5822</v>
       </c>
       <c r="N183" t="n">
-        <v>2.1089</v>
+        <v>2.109</v>
       </c>
       <c r="O183" t="n">
         <v>0.1078</v>
@@ -37443,7 +37443,7 @@
         <v>2.5573</v>
       </c>
       <c r="AP183" t="n">
-        <v>0.8819</v>
+        <v>0.8818</v>
       </c>
       <c r="AQ183" t="n">
         <v>0.2485</v>
@@ -37516,7 +37516,7 @@
         <v>3.9647</v>
       </c>
       <c r="AQ184" t="n">
-        <v>2.1097</v>
+        <v>2.1096</v>
       </c>
       <c r="AV184" t="n">
         <v>0.3113</v>
@@ -37964,7 +37964,7 @@
         <v>12.7</v>
       </c>
       <c r="M191" t="n">
-        <v>1.153</v>
+        <v>1.1529</v>
       </c>
       <c r="N191" t="n">
         <v>1.5371</v>
@@ -38006,7 +38006,7 @@
         <v>0.5595</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.0061</v>
+        <v>1.006</v>
       </c>
       <c r="AV191" t="n">
         <v>1.0187</v>
@@ -38070,7 +38070,7 @@
         <v>4.4169</v>
       </c>
       <c r="AO192" t="n">
-        <v>-0.1919</v>
+        <v>-0.1918</v>
       </c>
       <c r="AP192" t="n">
         <v>0.1219</v>
@@ -38216,7 +38216,7 @@
         <v>0.3405</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.656</v>
+        <v>0.6559</v>
       </c>
       <c r="AV194" t="n">
         <v>1.3294</v>
@@ -38548,7 +38548,7 @@
         <v>6.5816</v>
       </c>
       <c r="AC199" t="n">
-        <v>13.9866</v>
+        <v>13.9867</v>
       </c>
       <c r="AH199" t="n">
         <v>-3.6086</v>
@@ -38618,7 +38618,7 @@
         <v>0.461</v>
       </c>
       <c r="AC200" t="n">
-        <v>8.0366</v>
+        <v>8.0367</v>
       </c>
       <c r="AH200" t="n">
         <v>2.3612</v>
@@ -38688,7 +38688,7 @@
         <v>-2.8804</v>
       </c>
       <c r="AC201" t="n">
-        <v>-1.9574</v>
+        <v>-1.9575</v>
       </c>
       <c r="AH201" t="n">
         <v>2.586</v>
@@ -38700,7 +38700,7 @@
         <v>0.5958</v>
       </c>
       <c r="AO201" t="n">
-        <v>1.3036</v>
+        <v>1.3035</v>
       </c>
       <c r="AP201" t="n">
         <v>0.8663999999999999</v>
@@ -38770,7 +38770,7 @@
         <v>2.244</v>
       </c>
       <c r="AO202" t="n">
-        <v>0.4793</v>
+        <v>0.4794</v>
       </c>
       <c r="AP202" t="n">
         <v>3.2641</v>
@@ -38843,7 +38843,7 @@
         <v>0.4683</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.2659</v>
+        <v>2.2658</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.8245</v>
@@ -39108,7 +39108,7 @@
         <v>2.3919</v>
       </c>
       <c r="AC207" t="n">
-        <v>0.1465</v>
+        <v>0.1466</v>
       </c>
       <c r="AH207" t="n">
         <v>-0.2471</v>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24964,7 +24964,7 @@
         <v>-0.1445</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.239</v>
+        <v>-0.2391</v>
       </c>
       <c r="AV4" t="n">
         <v>-1.183</v>
@@ -24998,7 +24998,7 @@
         <v>-3.3763</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.7613</v>
+        <v>8.761200000000001</v>
       </c>
       <c r="AH5" t="n">
         <v>2.9409</v>
@@ -25010,7 +25010,7 @@
         <v>1.1281</v>
       </c>
       <c r="AP5" t="n">
-        <v>-3.0237</v>
+        <v>-3.0236</v>
       </c>
       <c r="AV5" t="n">
         <v>2.0612</v>
@@ -25047,7 +25047,7 @@
         <v>5.4681</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.0493</v>
+        <v>3.0492</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.4399</v>
@@ -25084,7 +25084,7 @@
         <v>-5.1724</v>
       </c>
       <c r="M7" t="n">
-        <v>7.0947</v>
+        <v>7.0946</v>
       </c>
       <c r="N7" t="n">
         <v>4.7031</v>
@@ -25120,7 +25120,7 @@
         <v>0.6575</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.4171</v>
+        <v>2.417</v>
       </c>
       <c r="AP7" t="n">
         <v>1.7091</v>
@@ -25242,7 +25242,7 @@
         <v>-15.0763</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.0527</v>
+        <v>5.0528</v>
       </c>
       <c r="AB9" t="n">
         <v>-4.2994</v>
@@ -25315,10 +25315,10 @@
         <v>-3.8055</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.8985</v>
+        <v>-0.8984</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.9075</v>
+        <v>-2.9074</v>
       </c>
       <c r="AH10" t="n">
         <v>0.8828</v>
@@ -25355,7 +25355,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-2.208</v>
+        <v>-2.2081</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1366</v>
@@ -25458,7 +25458,7 @@
         <v>-3.8055</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.8985</v>
+        <v>-0.8984</v>
       </c>
       <c r="AH12" t="n">
         <v>-1.0042</v>
@@ -25644,7 +25644,7 @@
         <v>-7.5155</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.5609</v>
+        <v>-5.5608</v>
       </c>
       <c r="N15" t="n">
         <v>2.2306</v>
@@ -25720,13 +25720,13 @@
         <v>-5.5137</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4347</v>
+        <v>1.4348</v>
       </c>
       <c r="T16" t="n">
         <v>5.712</v>
       </c>
       <c r="U16" t="n">
-        <v>16.4636</v>
+        <v>16.4635</v>
       </c>
       <c r="V16" t="n">
         <v>10.0767</v>
@@ -26030,7 +26030,7 @@
         <v>-3.5674</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.7299</v>
+        <v>0.7298</v>
       </c>
       <c r="AP20" t="n">
         <v>1.5375</v>
@@ -26392,7 +26392,7 @@
         <v>18.5716</v>
       </c>
       <c r="AW25" t="n">
-        <v>16.488</v>
+        <v>16.4879</v>
       </c>
       <c r="AX25" t="n">
         <v>-3.0927</v>
@@ -26411,10 +26411,10 @@
         <v>5.2459</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.6004</v>
+        <v>-15.6003</v>
       </c>
       <c r="M26" t="n">
-        <v>-12.2981</v>
+        <v>-12.298</v>
       </c>
       <c r="N26" t="n">
         <v>11.8545</v>
@@ -26423,7 +26423,7 @@
         <v>-8.2704</v>
       </c>
       <c r="T26" t="n">
-        <v>22.9469</v>
+        <v>22.9468</v>
       </c>
       <c r="U26" t="n">
         <v>-39.9055</v>
@@ -26484,7 +26484,7 @@
         <v>17.1821</v>
       </c>
       <c r="M27" t="n">
-        <v>5.2883</v>
+        <v>5.2882</v>
       </c>
       <c r="N27" t="n">
         <v>24.8843</v>
@@ -26557,7 +26557,7 @@
         <v>2.0996</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.7213</v>
+        <v>-5.7214</v>
       </c>
       <c r="O28" t="n">
         <v>20.2424</v>
@@ -26730,7 +26730,7 @@
         <v>-7.8167</v>
       </c>
       <c r="AO30" t="n">
-        <v>-3.0154</v>
+        <v>-3.0153</v>
       </c>
       <c r="AP30" t="n">
         <v>-2.2491</v>
@@ -26815,7 +26815,7 @@
         <v>-3.9504</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.2217</v>
+        <v>-1.2218</v>
       </c>
     </row>
     <row r="32">
@@ -26834,7 +26834,7 @@
         <v>-14.8583</v>
       </c>
       <c r="M32" t="n">
-        <v>-7.3073</v>
+        <v>-7.3074</v>
       </c>
       <c r="N32" t="n">
         <v>-15.9269</v>
@@ -27019,10 +27019,10 @@
         <v>-0.7489</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.7466</v>
+        <v>3.7465</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.9148</v>
+        <v>3.9147</v>
       </c>
       <c r="AX34" t="n">
         <v>-0.5973000000000001</v>
@@ -27178,7 +27178,7 @@
         <v>-0.4052</v>
       </c>
       <c r="G37" t="n">
-        <v>19.4363</v>
+        <v>19.4364</v>
       </c>
       <c r="H37" t="n">
         <v>41.1022</v>
@@ -27366,7 +27366,7 @@
         <v>0.6158</v>
       </c>
       <c r="AQ39" t="n">
-        <v>4.6</v>
+        <v>4.6001</v>
       </c>
       <c r="AV39" t="n">
         <v>0.7287</v>
@@ -27585,7 +27585,7 @@
         <v>2.5729</v>
       </c>
       <c r="AX42" t="n">
-        <v>2.2171</v>
+        <v>2.217</v>
       </c>
     </row>
     <row r="43">
@@ -27613,7 +27613,7 @@
         <v>3.4081</v>
       </c>
       <c r="T43" t="n">
-        <v>3.2796</v>
+        <v>3.2797</v>
       </c>
       <c r="U43" t="n">
         <v>-5.277</v>
@@ -27649,7 +27649,7 @@
         <v>1.2365</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.9546</v>
+        <v>-0.9545</v>
       </c>
       <c r="AW43" t="n">
         <v>1.7321</v>
@@ -27747,7 +27747,7 @@
         <v>2.9791</v>
       </c>
       <c r="N45" t="n">
-        <v>1.2158</v>
+        <v>1.2157</v>
       </c>
       <c r="O45" t="n">
         <v>4.1219</v>
@@ -27814,7 +27814,7 @@
         <v>6.1701</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.2368</v>
+        <v>-0.2369</v>
       </c>
       <c r="N46" t="n">
         <v>3.9302</v>
@@ -27829,7 +27829,7 @@
         <v>-10.8635</v>
       </c>
       <c r="V46" t="n">
-        <v>-6.0482</v>
+        <v>-6.0481</v>
       </c>
       <c r="AA46" t="n">
         <v>0.2785</v>
@@ -27875,22 +27875,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>21.4033</v>
+        <v>21.4032</v>
       </c>
       <c r="G47" t="n">
         <v>28.991</v>
       </c>
       <c r="H47" t="n">
-        <v>31.2644</v>
+        <v>31.2643</v>
       </c>
       <c r="M47" t="n">
-        <v>12.1078</v>
+        <v>12.1079</v>
       </c>
       <c r="N47" t="n">
         <v>15.1742</v>
       </c>
       <c r="O47" t="n">
-        <v>13.2021</v>
+        <v>13.202</v>
       </c>
       <c r="T47" t="n">
         <v>-21.625</v>
@@ -27945,7 +27945,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8.5814</v>
+        <v>8.5815</v>
       </c>
       <c r="G48" t="n">
         <v>36.164</v>
@@ -27993,7 +27993,7 @@
         <v>1.5241</v>
       </c>
       <c r="AP48" t="n">
-        <v>5.5909</v>
+        <v>5.591</v>
       </c>
       <c r="AQ48" t="n">
         <v>7.1</v>
@@ -28024,7 +28024,7 @@
         <v>41.8675</v>
       </c>
       <c r="M49" t="n">
-        <v>1.7646</v>
+        <v>1.7645</v>
       </c>
       <c r="N49" t="n">
         <v>19.3149</v>
@@ -28103,7 +28103,7 @@
         <v>19.4045</v>
       </c>
       <c r="T50" t="n">
-        <v>1.8519</v>
+        <v>1.8518</v>
       </c>
       <c r="U50" t="n">
         <v>-7.8947</v>
@@ -28167,7 +28167,7 @@
         <v>1.2326</v>
       </c>
       <c r="N51" t="n">
-        <v>3.3411</v>
+        <v>3.341</v>
       </c>
       <c r="O51" t="n">
         <v>21.1633</v>
@@ -28243,7 +28243,7 @@
         <v>8.3649</v>
       </c>
       <c r="T52" t="n">
-        <v>1.8965</v>
+        <v>1.8966</v>
       </c>
       <c r="U52" t="n">
         <v>4.2328</v>
@@ -28352,7 +28352,7 @@
         <v>-0.1463</v>
       </c>
       <c r="AW53" t="n">
-        <v>-0.8762</v>
+        <v>-0.8763</v>
       </c>
       <c r="AX53" t="n">
         <v>-1.0385</v>
@@ -28383,7 +28383,7 @@
         <v>-3.4395</v>
       </c>
       <c r="T54" t="n">
-        <v>5.5556</v>
+        <v>5.5555</v>
       </c>
       <c r="U54" t="n">
         <v>8.103400000000001</v>
@@ -28660,16 +28660,16 @@
         <v>2.5479</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.2131</v>
+        <v>-1.2132</v>
       </c>
       <c r="T58" t="n">
-        <v>1.6474</v>
+        <v>1.6475</v>
       </c>
       <c r="U58" t="n">
         <v>-4.2669</v>
       </c>
       <c r="V58" t="n">
-        <v>3.872</v>
+        <v>3.8721</v>
       </c>
       <c r="AA58" t="n">
         <v>1.3675</v>
@@ -28727,7 +28727,7 @@
         <v>0.4855</v>
       </c>
       <c r="N59" t="n">
-        <v>6.1068</v>
+        <v>6.1067</v>
       </c>
       <c r="O59" t="n">
         <v>3.5767</v>
@@ -28836,7 +28836,7 @@
         <v>-0.4048</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.9941</v>
+        <v>0.9942</v>
       </c>
       <c r="AV60" t="n">
         <v>-1.9848</v>
@@ -28879,7 +28879,7 @@
         <v>0.2431</v>
       </c>
       <c r="V61" t="n">
-        <v>-8.3025</v>
+        <v>-8.3024</v>
       </c>
       <c r="AA61" t="n">
         <v>-2.3177</v>
@@ -28912,7 +28912,7 @@
         <v>1.5078</v>
       </c>
       <c r="AW61" t="n">
-        <v>-0.1009</v>
+        <v>-0.1008</v>
       </c>
       <c r="AX61" t="n">
         <v>2.7004</v>
@@ -29016,7 +29016,7 @@
         <v>-4.2291</v>
       </c>
       <c r="U63" t="n">
-        <v>-16.1266</v>
+        <v>-16.1265</v>
       </c>
       <c r="V63" t="n">
         <v>-11.9125</v>
@@ -29138,7 +29138,7 @@
         <v>1.967</v>
       </c>
       <c r="G65" t="n">
-        <v>4.8087</v>
+        <v>4.8088</v>
       </c>
       <c r="H65" t="n">
         <v>18.6147</v>
@@ -29463,7 +29463,7 @@
         <v>0.2348</v>
       </c>
       <c r="AP69" t="n">
-        <v>0.5577</v>
+        <v>0.5578</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.6902</v>
@@ -29488,10 +29488,10 @@
         <v>-7.6072</v>
       </c>
       <c r="G70" t="n">
-        <v>-8.4513</v>
+        <v>-8.4514</v>
       </c>
       <c r="H70" t="n">
-        <v>4.4839</v>
+        <v>4.4838</v>
       </c>
       <c r="M70" t="n">
         <v>-3.7786</v>
@@ -29533,7 +29533,7 @@
         <v>-1.2555</v>
       </c>
       <c r="AP70" t="n">
-        <v>-1.3571</v>
+        <v>-1.3572</v>
       </c>
       <c r="AQ70" t="n">
         <v>-0.5586</v>
@@ -29908,7 +29908,7 @@
         <v>11.3332</v>
       </c>
       <c r="G76" t="n">
-        <v>11.1786</v>
+        <v>11.1787</v>
       </c>
       <c r="H76" t="n">
         <v>9.7064</v>
@@ -29929,7 +29929,7 @@
         <v>-11.1266</v>
       </c>
       <c r="V76" t="n">
-        <v>-9.9711</v>
+        <v>-9.9712</v>
       </c>
       <c r="AA76" t="n">
         <v>-4.566</v>
@@ -30032,7 +30032,7 @@
         <v>0.8975</v>
       </c>
       <c r="AW77" t="n">
-        <v>5.3752</v>
+        <v>5.3751</v>
       </c>
       <c r="AX77" t="n">
         <v>5.1276</v>
@@ -30191,7 +30191,7 @@
         <v>2.1562</v>
       </c>
       <c r="H80" t="n">
-        <v>16.7256</v>
+        <v>16.7255</v>
       </c>
       <c r="M80" t="n">
         <v>1.9405</v>
@@ -30790,7 +30790,7 @@
         <v>1.3645</v>
       </c>
       <c r="AO88" t="n">
-        <v>-0.2251</v>
+        <v>-0.225</v>
       </c>
       <c r="AP88" t="n">
         <v>0.3367</v>
@@ -30836,7 +30836,7 @@
         <v>2.7855</v>
       </c>
       <c r="U89" t="n">
-        <v>0.2718</v>
+        <v>0.2717</v>
       </c>
       <c r="V89" t="n">
         <v>-6.2262</v>
@@ -31049,7 +31049,7 @@
         <v>-3.1165</v>
       </c>
       <c r="V92" t="n">
-        <v>0.1401</v>
+        <v>0.14</v>
       </c>
       <c r="AA92" t="n">
         <v>-2.3597</v>
@@ -31079,7 +31079,7 @@
         <v>1.1432</v>
       </c>
       <c r="AV92" t="n">
-        <v>0.3828</v>
+        <v>0.3827</v>
       </c>
       <c r="AW92" t="n">
         <v>1.1073</v>
@@ -31362,10 +31362,10 @@
         <v>-0.6077</v>
       </c>
       <c r="AW96" t="n">
-        <v>-1.8927</v>
+        <v>-1.8928</v>
       </c>
       <c r="AX96" t="n">
-        <v>-1.4373</v>
+        <v>-1.4374</v>
       </c>
     </row>
     <row r="97">
@@ -31609,7 +31609,7 @@
         <v>-5.6356</v>
       </c>
       <c r="V100" t="n">
-        <v>-3.0956</v>
+        <v>-3.0955</v>
       </c>
       <c r="AA100" t="n">
         <v>0.4978</v>
@@ -31679,7 +31679,7 @@
         <v>-7.7124</v>
       </c>
       <c r="V101" t="n">
-        <v>-6.6138</v>
+        <v>-6.6137</v>
       </c>
       <c r="AA101" t="n">
         <v>-0.3852</v>
@@ -32126,7 +32126,7 @@
         <v>0.9112</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.7486</v>
+        <v>0.7487</v>
       </c>
       <c r="AV107" t="n">
         <v>1.6503</v>
@@ -32470,10 +32470,10 @@
         <v>3.7098</v>
       </c>
       <c r="AO112" t="n">
-        <v>-0.0775</v>
+        <v>-0.0776</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.229</v>
+        <v>1.2289</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.8709</v>
@@ -32513,13 +32513,13 @@
         <v>1.1936</v>
       </c>
       <c r="T113" t="n">
-        <v>6.9659</v>
+        <v>6.966</v>
       </c>
       <c r="U113" t="n">
         <v>2.068</v>
       </c>
       <c r="V113" t="n">
-        <v>-7.3727</v>
+        <v>-7.3726</v>
       </c>
       <c r="AA113" t="n">
         <v>1.5285</v>
@@ -32680,7 +32680,7 @@
         <v>-3.0756</v>
       </c>
       <c r="AO115" t="n">
-        <v>-1.3567</v>
+        <v>-1.3568</v>
       </c>
       <c r="AP115" t="n">
         <v>-1.8297</v>
@@ -32723,7 +32723,7 @@
         <v>-7.5374</v>
       </c>
       <c r="T116" t="n">
-        <v>2.0921</v>
+        <v>2.092</v>
       </c>
       <c r="U116" t="n">
         <v>5.9334</v>
@@ -32793,7 +32793,7 @@
         <v>-8.572900000000001</v>
       </c>
       <c r="T117" t="n">
-        <v>1.6393</v>
+        <v>1.6394</v>
       </c>
       <c r="U117" t="n">
         <v>8.613099999999999</v>
@@ -32936,7 +32936,7 @@
         <v>0.7342</v>
       </c>
       <c r="U119" t="n">
-        <v>-6.2842</v>
+        <v>-6.2841</v>
       </c>
       <c r="V119" t="n">
         <v>0.146</v>
@@ -32963,10 +32963,10 @@
         <v>-0.2885</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.781</v>
+        <v>0.7811</v>
       </c>
       <c r="AQ119" t="n">
-        <v>-1.1766</v>
+        <v>-1.1765</v>
       </c>
       <c r="AV119" t="n">
         <v>-0.2328</v>
@@ -33033,7 +33033,7 @@
         <v>0.4015</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.6564</v>
+        <v>1.6563</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.5849</v>
@@ -33149,7 +33149,7 @@
         <v>-4.2274</v>
       </c>
       <c r="V122" t="n">
-        <v>-11.6936</v>
+        <v>-11.6935</v>
       </c>
       <c r="AA122" t="n">
         <v>-1.8151</v>
@@ -33289,7 +33289,7 @@
         <v>10.5263</v>
       </c>
       <c r="V124" t="n">
-        <v>7.1429</v>
+        <v>7.1428</v>
       </c>
       <c r="AA124" t="n">
         <v>2.507</v>
@@ -33353,7 +33353,7 @@
         <v>-1.6771</v>
       </c>
       <c r="T125" t="n">
-        <v>1.6326</v>
+        <v>1.6327</v>
       </c>
       <c r="U125" t="n">
         <v>13.6986</v>
@@ -33380,7 +33380,7 @@
         <v>-3.4777</v>
       </c>
       <c r="AO125" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.7867</v>
       </c>
       <c r="AP125" t="n">
         <v>-1.2147</v>
@@ -33426,7 +33426,7 @@
         <v>-3.3467</v>
       </c>
       <c r="U126" t="n">
-        <v>1.1205</v>
+        <v>1.1204</v>
       </c>
       <c r="V126" t="n">
         <v>8.571400000000001</v>
@@ -33523,7 +33523,7 @@
         <v>0.1443</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.8457</v>
+        <v>1.8458</v>
       </c>
       <c r="AQ127" t="n">
         <v>-0.1768</v>
@@ -33563,7 +33563,7 @@
         <v>4.2189</v>
       </c>
       <c r="T128" t="n">
-        <v>-2.1428</v>
+        <v>-2.1429</v>
       </c>
       <c r="U128" t="n">
         <v>-8.299899999999999</v>
@@ -33636,7 +33636,7 @@
         <v>-0.292</v>
       </c>
       <c r="U129" t="n">
-        <v>-5.4017</v>
+        <v>-5.4016</v>
       </c>
       <c r="V129" t="n">
         <v>-7.0748</v>
@@ -33800,7 +33800,7 @@
         <v>4.8541</v>
       </c>
       <c r="AO131" t="n">
-        <v>0.582</v>
+        <v>0.5821</v>
       </c>
       <c r="AP131" t="n">
         <v>0.9</v>
@@ -33815,7 +33815,7 @@
         <v>2.5477</v>
       </c>
       <c r="AX131" t="n">
-        <v>4.5133</v>
+        <v>4.5132</v>
       </c>
     </row>
     <row r="132">
@@ -33983,7 +33983,7 @@
         <v>5.3999</v>
       </c>
       <c r="T134" t="n">
-        <v>-1.948</v>
+        <v>-1.9481</v>
       </c>
       <c r="U134" t="n">
         <v>-4.8819</v>
@@ -34433,7 +34433,7 @@
         <v>-0.3511</v>
       </c>
       <c r="AP140" t="n">
-        <v>-0.4269</v>
+        <v>-0.427</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.151</v>
@@ -34823,7 +34823,7 @@
         <v>6.0869</v>
       </c>
       <c r="T146" t="n">
-        <v>-6.1224</v>
+        <v>-6.1225</v>
       </c>
       <c r="U146" t="n">
         <v>-13.371</v>
@@ -35319,7 +35319,7 @@
         <v>2.934</v>
       </c>
       <c r="V153" t="n">
-        <v>-1.4052</v>
+        <v>-1.4051</v>
       </c>
       <c r="AA153" t="n">
         <v>-6.3007</v>
@@ -35483,7 +35483,7 @@
         <v>0.7057</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.1577</v>
+        <v>2.1578</v>
       </c>
       <c r="AQ155" t="n">
         <v>-1.5079</v>
@@ -35760,7 +35760,7 @@
         <v>3.5382</v>
       </c>
       <c r="AO159" t="n">
-        <v>-0.0261</v>
+        <v>-0.0262</v>
       </c>
       <c r="AP159" t="n">
         <v>1.8984</v>
@@ -36013,7 +36013,7 @@
         <v>7.9155</v>
       </c>
       <c r="T163" t="n">
-        <v>-8.6022</v>
+        <v>-8.6021</v>
       </c>
       <c r="U163" t="n">
         <v>-19.0476</v>
@@ -36789,7 +36789,7 @@
         <v>1.6807</v>
       </c>
       <c r="V174" t="n">
-        <v>-0.548</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="AA174" t="n">
         <v>0.8159999999999999</v>
@@ -36816,7 +36816,7 @@
         <v>1.6185</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.3746</v>
+        <v>0.3747</v>
       </c>
       <c r="AV174" t="n">
         <v>-2.2682</v>
@@ -36859,7 +36859,7 @@
         <v>-5.4348</v>
       </c>
       <c r="V175" t="n">
-        <v>5.1359</v>
+        <v>5.136</v>
       </c>
       <c r="AA175" t="n">
         <v>0.2943</v>
@@ -37443,7 +37443,7 @@
         <v>2.5573</v>
       </c>
       <c r="AP183" t="n">
-        <v>0.8818</v>
+        <v>0.8819</v>
       </c>
       <c r="AQ183" t="n">
         <v>0.2485</v>
@@ -37516,7 +37516,7 @@
         <v>3.9647</v>
       </c>
       <c r="AQ184" t="n">
-        <v>2.1096</v>
+        <v>2.1097</v>
       </c>
       <c r="AV184" t="n">
         <v>0.3113</v>
@@ -38006,7 +38006,7 @@
         <v>0.5595</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.006</v>
+        <v>1.0061</v>
       </c>
       <c r="AV191" t="n">
         <v>1.0187</v>
@@ -38070,7 +38070,7 @@
         <v>4.4169</v>
       </c>
       <c r="AO192" t="n">
-        <v>-0.1918</v>
+        <v>-0.1919</v>
       </c>
       <c r="AP192" t="n">
         <v>0.1219</v>
@@ -38116,7 +38116,7 @@
         <v>0</v>
       </c>
       <c r="U193" t="n">
-        <v>-6.0898</v>
+        <v>-6.0897</v>
       </c>
       <c r="V193" t="n">
         <v>-9.0062</v>
@@ -38216,7 +38216,7 @@
         <v>0.3405</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.6559</v>
+        <v>0.656</v>
       </c>
       <c r="AV194" t="n">
         <v>1.3294</v>
@@ -38253,7 +38253,7 @@
         <v>1.0809</v>
       </c>
       <c r="T195" t="n">
-        <v>1.773</v>
+        <v>1.7731</v>
       </c>
       <c r="U195" t="n">
         <v>-2.0478</v>
@@ -38323,7 +38323,7 @@
         <v>-5.9305</v>
       </c>
       <c r="T196" t="n">
-        <v>14.6342</v>
+        <v>14.6341</v>
       </c>
       <c r="U196" t="n">
         <v>12.2867</v>
@@ -38609,7 +38609,7 @@
         <v>4.1916</v>
       </c>
       <c r="V200" t="n">
-        <v>21.2544</v>
+        <v>21.2543</v>
       </c>
       <c r="AA200" t="n">
         <v>-4.2853</v>
@@ -38700,7 +38700,7 @@
         <v>0.5958</v>
       </c>
       <c r="AO201" t="n">
-        <v>1.3035</v>
+        <v>1.3036</v>
       </c>
       <c r="AP201" t="n">
         <v>0.8663999999999999</v>
@@ -38770,7 +38770,7 @@
         <v>2.244</v>
       </c>
       <c r="AO202" t="n">
-        <v>0.4794</v>
+        <v>0.4793</v>
       </c>
       <c r="AP202" t="n">
         <v>3.2641</v>
@@ -38843,7 +38843,7 @@
         <v>0.4683</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.2658</v>
+        <v>2.2659</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.8245</v>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>04/08/26</t>
+          <t>2026-04-11</t>
         </is>
       </c>
     </row>
@@ -24606,60 +24606,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX276"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" style="20" min="1" max="1"/>
-    <col width="12" customWidth="1" style="20" min="2" max="2"/>
-    <col width="12" customWidth="1" style="20" min="3" max="3"/>
-    <col width="12" customWidth="1" style="20" min="4" max="4"/>
-    <col width="12" customWidth="1" style="20" min="5" max="5"/>
-    <col width="12" customWidth="1" style="20" min="6" max="6"/>
-    <col width="12" customWidth="1" style="20" min="7" max="7"/>
-    <col width="12" customWidth="1" style="20" min="8" max="8"/>
-    <col width="12" customWidth="1" style="20" min="9" max="9"/>
-    <col width="12" customWidth="1" style="20" min="10" max="10"/>
-    <col width="12" customWidth="1" style="20" min="11" max="11"/>
-    <col width="12" customWidth="1" style="20" min="12" max="12"/>
-    <col width="12" customWidth="1" style="20" min="13" max="13"/>
-    <col width="12" customWidth="1" style="20" min="14" max="14"/>
-    <col width="12" customWidth="1" style="20" min="15" max="15"/>
-    <col width="12" customWidth="1" style="20" min="16" max="16"/>
-    <col width="12" customWidth="1" style="20" min="17" max="17"/>
-    <col width="12" customWidth="1" style="20" min="18" max="18"/>
-    <col width="12" customWidth="1" style="20" min="19" max="19"/>
-    <col width="12" customWidth="1" style="20" min="20" max="20"/>
-    <col width="12" customWidth="1" style="20" min="21" max="21"/>
-    <col width="12" customWidth="1" style="20" min="22" max="22"/>
-    <col width="12" customWidth="1" style="20" min="23" max="23"/>
-    <col width="12" customWidth="1" style="20" min="24" max="24"/>
-    <col width="12" customWidth="1" style="20" min="25" max="25"/>
-    <col width="12" customWidth="1" style="20" min="26" max="26"/>
-    <col width="12" customWidth="1" style="20" min="27" max="27"/>
-    <col width="12" customWidth="1" style="20" min="28" max="28"/>
-    <col width="12" customWidth="1" style="20" min="29" max="29"/>
-    <col width="12" customWidth="1" style="20" min="30" max="30"/>
-    <col width="12" customWidth="1" style="20" min="31" max="31"/>
-    <col width="12" customWidth="1" style="20" min="32" max="32"/>
-    <col width="12" customWidth="1" style="20" min="33" max="33"/>
-    <col width="12" customWidth="1" style="20" min="34" max="34"/>
-    <col width="12" customWidth="1" style="20" min="35" max="35"/>
-    <col width="12" customWidth="1" style="20" min="36" max="36"/>
-    <col width="12" customWidth="1" style="20" min="37" max="37"/>
-    <col width="12" customWidth="1" style="20" min="38" max="38"/>
-    <col width="12" customWidth="1" style="20" min="39" max="39"/>
-    <col width="12" customWidth="1" style="20" min="40" max="40"/>
-    <col width="12" customWidth="1" style="20" min="41" max="41"/>
-    <col width="12" customWidth="1" style="20" min="42" max="42"/>
-    <col width="12" customWidth="1" style="20" min="43" max="43"/>
-    <col width="12" customWidth="1" style="20" min="44" max="44"/>
-    <col width="12" customWidth="1" style="20" min="45" max="45"/>
-    <col width="12" customWidth="1" style="20" min="46" max="46"/>
-    <col width="12" customWidth="1" style="20" min="47" max="47"/>
-    <col width="12" customWidth="1" style="20" min="48" max="48"/>
-    <col width="12" customWidth="1" style="20" min="49" max="49"/>
-    <col width="12" customWidth="1" style="20" min="50" max="50"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24749,2093 +24697,1866 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>SMH_Open</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>SMH_High</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>SMH_Low</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>SMH_Close</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>QQQ_Open</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>QQQ_High</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>QQQ_Low</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>QQQ_Close</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>SOXX_Open</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>SOXX_High</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>SOXX_Low</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>SOXX_Close</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
           <t>SOXL_%Chg</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SOXL_3D</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>SOXL_5D</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>TQQQ_%Chg</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>TQQQ_3D</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>TQQQ_5D</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>SOXS_%Chg</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>SOXS_3D</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SOXS_5D</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>SQQQ_%Chg</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SQQQ_3D</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>SQQQ_5D</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>SMH_%Chg</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>SMH_3D</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>SMH_5D</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>QQQ_%Chg</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>QQQ_3D</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>QQQ_5D</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>SOXX_%Chg</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>SOXX_3D</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>SOXX_5D</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-03-12</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.0705</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="H2" t="n">
+        <v>46.6728</v>
+      </c>
+      <c r="I2" t="n">
+        <v>46.7527</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39.2107</v>
+      </c>
+      <c r="K2" t="n">
+        <v>41.9902</v>
+      </c>
+      <c r="L2" t="n">
+        <v>39.0519</v>
+      </c>
+      <c r="M2" t="n">
+        <v>41.4443</v>
+      </c>
+      <c r="N2" t="n">
+        <v>71.8163</v>
+      </c>
+      <c r="O2" t="n">
+        <v>73.7804</v>
+      </c>
+      <c r="P2" t="n">
+        <v>71.33029999999999</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>73.7308</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2026-03-13</t>
         </is>
+      </c>
+      <c r="B3" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="C3" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="F3" t="n">
+        <v>47.2718</v>
+      </c>
+      <c r="G3" t="n">
+        <v>48.1704</v>
+      </c>
+      <c r="H3" t="n">
+        <v>45.5946</v>
+      </c>
+      <c r="I3" t="n">
+        <v>45.8542</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.0148</v>
+      </c>
+      <c r="K3" t="n">
+        <v>41.6726</v>
+      </c>
+      <c r="L3" t="n">
+        <v>38.3967</v>
+      </c>
+      <c r="M3" t="n">
+        <v>40.9975</v>
+      </c>
+      <c r="N3" t="n">
+        <v>72.8777</v>
+      </c>
+      <c r="O3" t="n">
+        <v>75.5361</v>
+      </c>
+      <c r="P3" t="n">
+        <v>71.4592</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>75.1294</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-1.9218</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-1.0781</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.8969</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2026-03-16</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="C4" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="D4" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="E4" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="F4" t="n">
+        <v>47.2918</v>
+      </c>
+      <c r="G4" t="n">
+        <v>48.1903</v>
+      </c>
+      <c r="H4" t="n">
+        <v>47.1021</v>
+      </c>
+      <c r="I4" t="n">
+        <v>47.3817</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.3272</v>
+      </c>
+      <c r="K4" t="n">
+        <v>39.2306</v>
+      </c>
+      <c r="L4" t="n">
+        <v>37.1261</v>
+      </c>
+      <c r="M4" t="n">
+        <v>38.5754</v>
+      </c>
+      <c r="N4" t="n">
+        <v>72.76860000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>73.086</v>
+      </c>
+      <c r="P4" t="n">
+        <v>71.2807</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>72.6198</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5.8557</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.3312</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-5.9079</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-3.3404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2026-03-17</t>
         </is>
+      </c>
+      <c r="B5" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="F5" t="n">
+        <v>48.0406</v>
+      </c>
+      <c r="G5" t="n">
+        <v>48.6795</v>
+      </c>
+      <c r="H5" t="n">
+        <v>47.7311</v>
+      </c>
+      <c r="I5" t="n">
+        <v>48.0805</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37.6522</v>
+      </c>
+      <c r="K5" t="n">
+        <v>38.9725</v>
+      </c>
+      <c r="L5" t="n">
+        <v>37.4835</v>
+      </c>
+      <c r="M5" t="n">
+        <v>37.7912</v>
+      </c>
+      <c r="N5" t="n">
+        <v>71.6279</v>
+      </c>
+      <c r="O5" t="n">
+        <v>72.0941</v>
+      </c>
+      <c r="P5" t="n">
+        <v>70.63590000000001</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>71.5684</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3468</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9.288</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.4748</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-2.0329</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-8.814500000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1.4478</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-2.9328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2026-03-18</t>
         </is>
+      </c>
+      <c r="B6" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="C6" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E6" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="F6" t="n">
+        <v>47.6412</v>
+      </c>
+      <c r="G6" t="n">
+        <v>48.0306</v>
+      </c>
+      <c r="H6" t="n">
+        <v>45.974</v>
+      </c>
+      <c r="I6" t="n">
+        <v>46.0239</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.7515</v>
+      </c>
+      <c r="K6" t="n">
+        <v>38.4563</v>
+      </c>
+      <c r="L6" t="n">
+        <v>36.739</v>
+      </c>
+      <c r="M6" t="n">
+        <v>38.4166</v>
+      </c>
+      <c r="N6" t="n">
+        <v>72.233</v>
+      </c>
+      <c r="O6" t="n">
+        <v>74.7029</v>
+      </c>
+      <c r="P6" t="n">
+        <v>71.6675</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>74.6037</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1.6924</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6.5063</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-4.2774</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.6549</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-6.2953</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.2411</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.6997</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-03-19</t>
         </is>
+      </c>
+      <c r="B7" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="C7" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="D7" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="F7" t="n">
+        <v>44.7959</v>
+      </c>
+      <c r="G7" t="n">
+        <v>46.2435</v>
+      </c>
+      <c r="H7" t="n">
+        <v>44.2269</v>
+      </c>
+      <c r="I7" t="n">
+        <v>45.6146</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.6924</v>
+      </c>
+      <c r="K7" t="n">
+        <v>42.4171</v>
+      </c>
+      <c r="L7" t="n">
+        <v>36.9574</v>
+      </c>
+      <c r="M7" t="n">
+        <v>37.8309</v>
+      </c>
+      <c r="N7" t="n">
+        <v>76.657</v>
+      </c>
+      <c r="O7" t="n">
+        <v>77.55970000000001</v>
+      </c>
+      <c r="P7" t="n">
+        <v>74.27630000000001</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>75.298</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.5365</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.1606</v>
+      </c>
+      <c r="T7" t="n">
+        <v>9.0891</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.8893</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-3.7295</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-2.4343</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.5246</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-8.7187</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.9307</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.1256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2026-03-20</t>
         </is>
+      </c>
+      <c r="B8" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="C8" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="D8" t="n">
+        <v>49</v>
+      </c>
+      <c r="E8" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="F8" t="n">
+        <v>45.1054</v>
+      </c>
+      <c r="G8" t="n">
+        <v>45.1354</v>
+      </c>
+      <c r="H8" t="n">
+        <v>42.2302</v>
+      </c>
+      <c r="I8" t="n">
+        <v>43.0089</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38.0394</v>
+      </c>
+      <c r="K8" t="n">
+        <v>41.9505</v>
+      </c>
+      <c r="L8" t="n">
+        <v>37.4934</v>
+      </c>
+      <c r="M8" t="n">
+        <v>40.3622</v>
+      </c>
+      <c r="N8" t="n">
+        <v>76.1511</v>
+      </c>
+      <c r="O8" t="n">
+        <v>80.93219999999999</v>
+      </c>
+      <c r="P8" t="n">
+        <v>76.1412</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>79.6031</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-6.7639</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-6.9336</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8280999999999999</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-5.7124</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-10.5481</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-6.2051</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6.6911</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.8032</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.5496</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.7174</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11.2266</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.9547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-03-23</t>
         </is>
+      </c>
+      <c r="B9" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="C9" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="D9" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="E9" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="F9" t="n">
+        <v>45.0355</v>
+      </c>
+      <c r="G9" t="n">
+        <v>46.0738</v>
+      </c>
+      <c r="H9" t="n">
+        <v>44.0572</v>
+      </c>
+      <c r="I9" t="n">
+        <v>44.4964</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37.7316</v>
+      </c>
+      <c r="K9" t="n">
+        <v>39.4986</v>
+      </c>
+      <c r="L9" t="n">
+        <v>35.9547</v>
+      </c>
+      <c r="M9" t="n">
+        <v>38.903</v>
+      </c>
+      <c r="N9" t="n">
+        <v>75.8734</v>
+      </c>
+      <c r="O9" t="n">
+        <v>77.6985</v>
+      </c>
+      <c r="P9" t="n">
+        <v>73.9589</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>76.8554</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.6957</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.8327</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.2293</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.4586</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-3.3189</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-6.0895</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-3.6153</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2661</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.8492</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-3.4517</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.0182</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.8326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-03-24</t>
         </is>
+      </c>
+      <c r="B10" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="C10" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="E10" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.7676</v>
+      </c>
+      <c r="G10" t="n">
+        <v>44.4765</v>
+      </c>
+      <c r="H10" t="n">
+        <v>43.1187</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.548</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>37.46</v>
+      </c>
+      <c r="N10" t="n">
+        <v>78.15479999999999</v>
+      </c>
+      <c r="O10" t="n">
+        <v>79.2559</v>
+      </c>
+      <c r="P10" t="n">
+        <v>76.9248</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>78.502</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.6394</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-2.1314</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-4.5306</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-9.4269</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-3.7092</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.9804</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.8764</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.1425</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.2551</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.6881</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2026-03-25</t>
         </is>
+      </c>
+      <c r="B11" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="C11" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="E11" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="H11" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="I11" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="K11" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="M11" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>75.51000000000001</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.7846</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11.537</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.5905</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.9335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.2112</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-3.5501</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-3.8441</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-10.7581</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-6.2384</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-1.9643</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-3.3203</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.1584</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-03-26</t>
         </is>
+      </c>
+      <c r="B12" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="C12" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="D12" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="E12" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="G12" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="H12" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="J12" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="K12" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="L12" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="N12" t="n">
+        <v>79.02</v>
+      </c>
+      <c r="O12" t="n">
+        <v>82.62</v>
+      </c>
+      <c r="P12" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-14.148</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-7.656</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-10.7201</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-7.1187</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-7.3408</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-9.612299999999999</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.3254</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.853</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8.8528</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.1985</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.3444</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.5647</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-03-27</t>
         </is>
+      </c>
+      <c r="B13" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="C13" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="D13" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="E13" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="G13" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="I13" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="J13" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="K13" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="O13" t="n">
+        <v>87.86</v>
+      </c>
+      <c r="P13" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-4.8193</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-15.1929</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-8.858000000000001</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-5.9423</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-10.9488</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-9.832599999999999</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.6625</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.0561</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.7831</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.9636</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11.3602</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.819800000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-03-30</t>
         </is>
+      </c>
+      <c r="B14" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="C14" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="D14" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="E14" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="F14" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="H14" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="I14" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="J14" t="n">
+        <v>42</v>
+      </c>
+      <c r="K14" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="L14" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="M14" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="N14" t="n">
+        <v>85.27</v>
+      </c>
+      <c r="O14" t="n">
+        <v>90.72</v>
+      </c>
+      <c r="P14" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-12.8513</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-28.7868</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-23.4018</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2.295</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-14.6429</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-14.847</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13.0858</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>35.3137</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>25.286</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.2878</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>16.1902</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>16.3484</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2026-03-31</t>
         </is>
+      </c>
+      <c r="B15" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="C15" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="D15" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="E15" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="F15" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="G15" t="n">
+        <v>42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="I15" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="J15" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="K15" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="L15" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="M15" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="N15" t="n">
+        <v>86.62</v>
+      </c>
+      <c r="O15" t="n">
+        <v>86.66</v>
+      </c>
+      <c r="P15" t="n">
+        <v>79.73999999999999</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="R15" t="n">
+        <v>17.9468</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-2.1646</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-12.8275</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10.0026</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.0914</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-4.2895</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-18.2191</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-3.2054</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.4068</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-9.986599999999999</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-2.4364</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.5324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-04-01</t>
         </is>
+      </c>
+      <c r="B16" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="C16" t="n">
+        <v>54.09</v>
+      </c>
+      <c r="D16" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="E16" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="G16" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="H16" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="I16" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="J16" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="K16" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="L16" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="M16" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="N16" t="n">
+        <v>78.62</v>
+      </c>
+      <c r="O16" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="P16" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9.079499999999999</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12.1219</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-8.380100000000001</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.7188</v>
+      </c>
+      <c r="V16" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-2.6132</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-9.031599999999999</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-15.8701</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-3.7769</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-11.4047</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.6367</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2026-04-02</t>
         </is>
+      </c>
+      <c r="B17" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="C17" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="D17" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="F17" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="H17" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="I17" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="J17" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="K17" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="M17" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="N17" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>76.93000000000001</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9376</v>
+      </c>
+      <c r="S17" t="n">
+        <v>29.8621</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7.719</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="V17" t="n">
+        <v>14.3574</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5.0934</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.9101</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-26.2823</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-12.7489</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.2066</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-13.5652</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-04-06</t>
         </is>
+      </c>
+      <c r="B18" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="C18" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="E18" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="I18" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="K18" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="N18" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="O18" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="P18" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.9052</v>
+      </c>
+      <c r="S18" t="n">
+        <v>14.402</v>
+      </c>
+      <c r="T18" t="n">
+        <v>17.5928</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.7771</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.8061</v>
+      </c>
+      <c r="W18" t="n">
+        <v>13.7184</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-3.8408</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-13.3216</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-19.8376</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-1.7725</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-5.6777</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-04-07</t>
         </is>
+      </c>
+      <c r="B19" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="C19" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="E19" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="G19" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="H19" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="I19" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="K19" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="M19" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="N19" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="O19" t="n">
+        <v>79.88</v>
+      </c>
+      <c r="P19" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>75.91</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.1746</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8.209</v>
+      </c>
+      <c r="T19" t="n">
+        <v>39.2171</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.1282</v>
+      </c>
+      <c r="W19" t="n">
+        <v>16.5215</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-3.2417</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-7.8047</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-31.4116</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.9884</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-04-08</t>
         </is>
+      </c>
+      <c r="B20" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="C20" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="D20" t="n">
+        <v>63.56</v>
+      </c>
+      <c r="E20" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="G20" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="H20" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>48</v>
+      </c>
+      <c r="J20" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="M20" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="N20" t="n">
+        <v>68.20999999999999</v>
+      </c>
+      <c r="O20" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="P20" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>19.3634</v>
+      </c>
+      <c r="S20" t="n">
+        <v>27.9621</v>
+      </c>
+      <c r="T20" t="n">
+        <v>40.8892</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8.7203</v>
+      </c>
+      <c r="V20" t="n">
+        <v>10.7778</v>
+      </c>
+      <c r="W20" t="n">
+        <v>15.1631</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-19.3539</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-24.9652</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-32.3633</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-8.839399999999999</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-10.4671</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2026-04-09</t>
         </is>
+      </c>
+      <c r="B21" t="n">
+        <v>68.12</v>
+      </c>
+      <c r="C21" t="n">
+        <v>72.28</v>
+      </c>
+      <c r="D21" t="n">
+        <v>68.12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="F21" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="G21" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="H21" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="I21" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="K21" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="L21" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="M21" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>69.31999999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>67.72</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6.637</v>
+      </c>
+      <c r="S21" t="n">
+        <v>31.3264</v>
+      </c>
+      <c r="T21" t="n">
+        <v>37.7344</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>11.0204</v>
+      </c>
+      <c r="W21" t="n">
+        <v>13.2547</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-6.5282</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-27.0622</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-30.5019</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-1.9364</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-10.6164</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2025-05-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2025-05-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2025-06-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2025-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2025-10-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
           <t>2026-04-10</t>
         </is>
+      </c>
+      <c r="B22" t="n">
+        <v>74.295</v>
+      </c>
+      <c r="C22" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>74.295</v>
+      </c>
+      <c r="E22" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="F22" t="n">
+        <v>49.3775</v>
+      </c>
+      <c r="G22" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="H22" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="I22" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="K22" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="L22" t="n">
+        <v>23.005</v>
+      </c>
+      <c r="M22" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="N22" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="O22" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="P22" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>67.62</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6.1267</v>
+      </c>
+      <c r="S22" t="n">
+        <v>35.084</v>
+      </c>
+      <c r="T22" t="n">
+        <v>44.8152</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="V22" t="n">
+        <v>11.3703</v>
+      </c>
+      <c r="W22" t="n">
+        <v>13.478</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-5.9921</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-29.1355</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-34.0662</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.3537</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-10.9208</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-12.5113</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24759,1804 +24759,1713 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.53</v>
+        <v>54.06</v>
       </c>
       <c r="C2" t="n">
-        <v>53.88</v>
+        <v>55.68</v>
       </c>
       <c r="D2" t="n">
-        <v>49.53</v>
+        <v>53.01</v>
       </c>
       <c r="E2" t="n">
-        <v>50.28</v>
+        <v>53.69</v>
       </c>
       <c r="F2" t="n">
-        <v>48.0705</v>
+        <v>47.2918</v>
       </c>
       <c r="G2" t="n">
-        <v>48.41</v>
+        <v>48.1903</v>
       </c>
       <c r="H2" t="n">
-        <v>46.6728</v>
+        <v>47.1021</v>
       </c>
       <c r="I2" t="n">
-        <v>46.7527</v>
+        <v>47.3817</v>
       </c>
       <c r="J2" t="n">
-        <v>39.2107</v>
+        <v>38.3272</v>
       </c>
       <c r="K2" t="n">
-        <v>41.9902</v>
+        <v>39.2306</v>
       </c>
       <c r="L2" t="n">
-        <v>39.0519</v>
+        <v>37.1261</v>
       </c>
       <c r="M2" t="n">
-        <v>41.4443</v>
+        <v>38.5754</v>
       </c>
       <c r="N2" t="n">
-        <v>71.8163</v>
+        <v>72.76860000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>73.7804</v>
+        <v>73.086</v>
       </c>
       <c r="P2" t="n">
-        <v>71.33029999999999</v>
+        <v>71.2807</v>
       </c>
       <c r="Q2" t="n">
-        <v>73.7308</v>
+        <v>72.6198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51.88</v>
+        <v>55.1</v>
       </c>
       <c r="C3" t="n">
-        <v>53.96</v>
+        <v>55.4</v>
       </c>
       <c r="D3" t="n">
-        <v>50.04</v>
+        <v>53.3</v>
       </c>
       <c r="E3" t="n">
-        <v>50.72</v>
+        <v>54.95</v>
       </c>
       <c r="F3" t="n">
-        <v>47.2718</v>
+        <v>48.0406</v>
       </c>
       <c r="G3" t="n">
-        <v>48.1704</v>
+        <v>48.6795</v>
       </c>
       <c r="H3" t="n">
-        <v>45.5946</v>
+        <v>47.7311</v>
       </c>
       <c r="I3" t="n">
-        <v>45.8542</v>
+        <v>48.0805</v>
       </c>
       <c r="J3" t="n">
-        <v>40.0148</v>
+        <v>37.6522</v>
       </c>
       <c r="K3" t="n">
-        <v>41.6726</v>
+        <v>38.9725</v>
       </c>
       <c r="L3" t="n">
-        <v>38.3967</v>
+        <v>37.4835</v>
       </c>
       <c r="M3" t="n">
-        <v>40.9975</v>
+        <v>37.7912</v>
       </c>
       <c r="N3" t="n">
-        <v>72.8777</v>
+        <v>71.6279</v>
       </c>
       <c r="O3" t="n">
-        <v>75.5361</v>
+        <v>72.0941</v>
       </c>
       <c r="P3" t="n">
-        <v>71.4592</v>
+        <v>70.63590000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>75.1294</v>
+        <v>71.5684</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8751</v>
+        <v>2.3468</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.9218</v>
+        <v>1.4748</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0781</v>
+        <v>-2.0329</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8969</v>
+        <v>-1.4478</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.06</v>
+        <v>55.03</v>
       </c>
       <c r="C4" t="n">
-        <v>55.68</v>
+        <v>56.48</v>
       </c>
       <c r="D4" t="n">
-        <v>53.01</v>
+        <v>54</v>
       </c>
       <c r="E4" t="n">
-        <v>53.69</v>
+        <v>54.02</v>
       </c>
       <c r="F4" t="n">
-        <v>47.2918</v>
+        <v>47.6412</v>
       </c>
       <c r="G4" t="n">
-        <v>48.1903</v>
+        <v>48.0306</v>
       </c>
       <c r="H4" t="n">
-        <v>47.1021</v>
+        <v>45.974</v>
       </c>
       <c r="I4" t="n">
-        <v>47.3817</v>
+        <v>46.0239</v>
       </c>
       <c r="J4" t="n">
-        <v>38.3272</v>
+        <v>37.7515</v>
       </c>
       <c r="K4" t="n">
-        <v>39.2306</v>
+        <v>38.4563</v>
       </c>
       <c r="L4" t="n">
-        <v>37.1261</v>
+        <v>36.739</v>
       </c>
       <c r="M4" t="n">
-        <v>38.5754</v>
+        <v>38.4166</v>
       </c>
       <c r="N4" t="n">
-        <v>72.76860000000001</v>
+        <v>72.233</v>
       </c>
       <c r="O4" t="n">
-        <v>73.086</v>
+        <v>74.7029</v>
       </c>
       <c r="P4" t="n">
-        <v>71.2807</v>
+        <v>71.6675</v>
       </c>
       <c r="Q4" t="n">
-        <v>72.6198</v>
+        <v>74.6037</v>
       </c>
       <c r="R4" t="n">
-        <v>5.8557</v>
+        <v>-1.6924</v>
       </c>
       <c r="U4" t="n">
-        <v>3.3312</v>
+        <v>-4.2774</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.9079</v>
+        <v>1.6549</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3.3404</v>
+        <v>4.2411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.1</v>
+        <v>49.53</v>
       </c>
       <c r="C5" t="n">
-        <v>55.4</v>
+        <v>56.11</v>
       </c>
       <c r="D5" t="n">
-        <v>53.3</v>
+        <v>48.5</v>
       </c>
       <c r="E5" t="n">
-        <v>54.95</v>
+        <v>54.85</v>
       </c>
       <c r="F5" t="n">
-        <v>48.0406</v>
+        <v>44.7959</v>
       </c>
       <c r="G5" t="n">
-        <v>48.6795</v>
+        <v>46.2435</v>
       </c>
       <c r="H5" t="n">
-        <v>47.7311</v>
+        <v>44.2269</v>
       </c>
       <c r="I5" t="n">
-        <v>48.0805</v>
+        <v>45.6146</v>
       </c>
       <c r="J5" t="n">
-        <v>37.6522</v>
+        <v>41.6924</v>
       </c>
       <c r="K5" t="n">
-        <v>38.9725</v>
+        <v>42.4171</v>
       </c>
       <c r="L5" t="n">
-        <v>37.4835</v>
+        <v>36.9574</v>
       </c>
       <c r="M5" t="n">
-        <v>37.7912</v>
+        <v>37.8309</v>
       </c>
       <c r="N5" t="n">
-        <v>71.6279</v>
+        <v>76.657</v>
       </c>
       <c r="O5" t="n">
-        <v>72.0941</v>
+        <v>77.55970000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>70.63590000000001</v>
+        <v>74.27630000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>71.5684</v>
+        <v>75.298</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3468</v>
+        <v>1.5365</v>
       </c>
       <c r="S5" t="n">
-        <v>9.288</v>
+        <v>2.1606</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4748</v>
+        <v>-0.8893</v>
       </c>
       <c r="V5" t="n">
-        <v>2.84</v>
+        <v>-3.7295</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0329</v>
+        <v>-1.5246</v>
       </c>
       <c r="Y5" t="n">
-        <v>-8.814500000000001</v>
+        <v>-1.93</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.4478</v>
+        <v>0.9307</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.9328</v>
+        <v>3.688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55.03</v>
+        <v>54.69</v>
       </c>
       <c r="C6" t="n">
-        <v>56.48</v>
+        <v>55.36</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E6" t="n">
-        <v>54.02</v>
+        <v>51.14</v>
       </c>
       <c r="F6" t="n">
-        <v>47.6412</v>
+        <v>45.1054</v>
       </c>
       <c r="G6" t="n">
-        <v>48.0306</v>
+        <v>45.1354</v>
       </c>
       <c r="H6" t="n">
-        <v>45.974</v>
+        <v>42.2302</v>
       </c>
       <c r="I6" t="n">
-        <v>46.0239</v>
+        <v>43.0089</v>
       </c>
       <c r="J6" t="n">
-        <v>37.7515</v>
+        <v>38.0394</v>
       </c>
       <c r="K6" t="n">
-        <v>38.4563</v>
+        <v>41.9505</v>
       </c>
       <c r="L6" t="n">
-        <v>36.739</v>
+        <v>37.4934</v>
       </c>
       <c r="M6" t="n">
-        <v>38.4166</v>
+        <v>40.3622</v>
       </c>
       <c r="N6" t="n">
-        <v>72.233</v>
+        <v>76.1511</v>
       </c>
       <c r="O6" t="n">
-        <v>74.7029</v>
+        <v>80.93219999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>71.6675</v>
+        <v>76.1412</v>
       </c>
       <c r="Q6" t="n">
-        <v>74.6037</v>
+        <v>79.6031</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.6924</v>
+        <v>-6.7639</v>
       </c>
       <c r="S6" t="n">
-        <v>6.5063</v>
+        <v>-6.9336</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.2774</v>
+        <v>-5.7124</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3701</v>
+        <v>-10.5481</v>
       </c>
       <c r="X6" t="n">
-        <v>1.6549</v>
+        <v>6.6911</v>
       </c>
       <c r="Y6" t="n">
-        <v>-6.2953</v>
+        <v>6.8032</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.2411</v>
+        <v>5.7174</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.6997</v>
+        <v>11.2266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49.53</v>
+        <v>54.63</v>
       </c>
       <c r="C7" t="n">
-        <v>56.11</v>
+        <v>56.81</v>
       </c>
       <c r="D7" t="n">
-        <v>48.5</v>
+        <v>52.28</v>
       </c>
       <c r="E7" t="n">
-        <v>54.85</v>
+        <v>53.03</v>
       </c>
       <c r="F7" t="n">
-        <v>44.7959</v>
+        <v>45.0355</v>
       </c>
       <c r="G7" t="n">
-        <v>46.2435</v>
+        <v>46.0738</v>
       </c>
       <c r="H7" t="n">
-        <v>44.2269</v>
+        <v>44.0572</v>
       </c>
       <c r="I7" t="n">
-        <v>45.6146</v>
+        <v>44.4964</v>
       </c>
       <c r="J7" t="n">
-        <v>41.6924</v>
+        <v>37.7316</v>
       </c>
       <c r="K7" t="n">
-        <v>42.4171</v>
+        <v>39.4986</v>
       </c>
       <c r="L7" t="n">
-        <v>36.9574</v>
+        <v>35.9547</v>
       </c>
       <c r="M7" t="n">
-        <v>37.8309</v>
+        <v>38.903</v>
       </c>
       <c r="N7" t="n">
-        <v>76.657</v>
+        <v>75.8734</v>
       </c>
       <c r="O7" t="n">
-        <v>77.55970000000001</v>
+        <v>77.6985</v>
       </c>
       <c r="P7" t="n">
-        <v>74.27630000000001</v>
+        <v>73.9589</v>
       </c>
       <c r="Q7" t="n">
-        <v>75.298</v>
+        <v>76.8554</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5365</v>
+        <v>3.6957</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1606</v>
+        <v>-1.8327</v>
       </c>
       <c r="T7" t="n">
-        <v>9.0891</v>
+        <v>-1.2293</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8893</v>
+        <v>3.4586</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.7295</v>
+        <v>-3.3189</v>
       </c>
       <c r="W7" t="n">
-        <v>-2.4343</v>
+        <v>-6.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5246</v>
+        <v>-3.6153</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.93</v>
+        <v>1.2661</v>
       </c>
       <c r="Z7" t="n">
-        <v>-8.7187</v>
+        <v>0.8492</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9307</v>
+        <v>-3.4517</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.688</v>
+        <v>3.0182</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1256</v>
+        <v>5.8326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54.69</v>
+        <v>51.54</v>
       </c>
       <c r="C8" t="n">
-        <v>55.36</v>
+        <v>56.09</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>51.54</v>
       </c>
       <c r="E8" t="n">
-        <v>51.14</v>
+        <v>54.96</v>
       </c>
       <c r="F8" t="n">
-        <v>45.1054</v>
+        <v>43.7676</v>
       </c>
       <c r="G8" t="n">
-        <v>45.1354</v>
+        <v>44.4765</v>
       </c>
       <c r="H8" t="n">
-        <v>42.2302</v>
+        <v>43.1187</v>
       </c>
       <c r="I8" t="n">
-        <v>43.0089</v>
+        <v>43.548</v>
       </c>
       <c r="J8" t="n">
-        <v>38.0394</v>
+        <v>40.08</v>
       </c>
       <c r="K8" t="n">
-        <v>41.9505</v>
+        <v>40.08</v>
       </c>
       <c r="L8" t="n">
-        <v>37.4934</v>
+        <v>36.7</v>
       </c>
       <c r="M8" t="n">
-        <v>40.3622</v>
+        <v>37.46</v>
       </c>
       <c r="N8" t="n">
-        <v>76.1511</v>
+        <v>78.15479999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>80.93219999999999</v>
+        <v>79.2559</v>
       </c>
       <c r="P8" t="n">
-        <v>76.1412</v>
+        <v>76.9248</v>
       </c>
       <c r="Q8" t="n">
-        <v>79.6031</v>
+        <v>78.502</v>
       </c>
       <c r="R8" t="n">
-        <v>-6.7639</v>
+        <v>3.6394</v>
       </c>
       <c r="S8" t="n">
-        <v>-6.9336</v>
+        <v>0.2005</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.0182</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.7124</v>
+        <v>-2.1314</v>
       </c>
       <c r="V8" t="n">
-        <v>-10.5481</v>
+        <v>-4.5306</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.2051</v>
+        <v>-9.4269</v>
       </c>
       <c r="X8" t="n">
-        <v>6.6911</v>
+        <v>-3.7092</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.8032</v>
+        <v>-0.9804</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.5496</v>
+        <v>-0.8764</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.7174</v>
+        <v>2.1425</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.2266</v>
+        <v>4.2551</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.9547</v>
+        <v>9.6881</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.63</v>
+        <v>56.64</v>
       </c>
       <c r="C9" t="n">
-        <v>56.81</v>
+        <v>58.25</v>
       </c>
       <c r="D9" t="n">
-        <v>52.28</v>
+        <v>55.59</v>
       </c>
       <c r="E9" t="n">
-        <v>53.03</v>
+        <v>57.04</v>
       </c>
       <c r="F9" t="n">
-        <v>45.0355</v>
+        <v>44.7</v>
       </c>
       <c r="G9" t="n">
-        <v>46.0738</v>
+        <v>45.22</v>
       </c>
       <c r="H9" t="n">
-        <v>44.0572</v>
+        <v>43.95</v>
       </c>
       <c r="I9" t="n">
-        <v>44.4964</v>
+        <v>44.39</v>
       </c>
       <c r="J9" t="n">
-        <v>37.7316</v>
+        <v>36.32</v>
       </c>
       <c r="K9" t="n">
-        <v>39.4986</v>
+        <v>37.06</v>
       </c>
       <c r="L9" t="n">
-        <v>35.9547</v>
+        <v>35.23</v>
       </c>
       <c r="M9" t="n">
-        <v>38.903</v>
+        <v>36.02</v>
       </c>
       <c r="N9" t="n">
-        <v>75.8734</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>77.6985</v>
+        <v>77.8</v>
       </c>
       <c r="P9" t="n">
-        <v>73.9589</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>76.8554</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>3.6957</v>
+        <v>3.7846</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8327</v>
+        <v>11.537</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2293</v>
+        <v>5.5905</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4586</v>
+        <v>1.9335</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.3189</v>
+        <v>3.2112</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.0895</v>
+        <v>-3.5501</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.6153</v>
+        <v>-3.8441</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2661</v>
+        <v>-10.7581</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8492</v>
+        <v>-6.2384</v>
       </c>
       <c r="AA9" t="n">
-        <v>-3.4517</v>
+        <v>-1.9643</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.0182</v>
+        <v>-3.3203</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.8326</v>
+        <v>3.1584</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.54</v>
+        <v>54.19</v>
       </c>
       <c r="C10" t="n">
-        <v>56.09</v>
+        <v>54.44</v>
       </c>
       <c r="D10" t="n">
-        <v>51.54</v>
+        <v>48.87</v>
       </c>
       <c r="E10" t="n">
-        <v>54.96</v>
+        <v>48.97</v>
       </c>
       <c r="F10" t="n">
-        <v>43.7676</v>
+        <v>43.23</v>
       </c>
       <c r="G10" t="n">
-        <v>44.4765</v>
+        <v>43.68</v>
       </c>
       <c r="H10" t="n">
-        <v>43.1187</v>
+        <v>41.15</v>
       </c>
       <c r="I10" t="n">
-        <v>43.548</v>
+        <v>41.23</v>
       </c>
       <c r="J10" t="n">
-        <v>40.08</v>
+        <v>37.84</v>
       </c>
       <c r="K10" t="n">
-        <v>40.08</v>
+        <v>41.26</v>
       </c>
       <c r="L10" t="n">
-        <v>36.7</v>
+        <v>37.7</v>
       </c>
       <c r="M10" t="n">
-        <v>37.46</v>
+        <v>41.18</v>
       </c>
       <c r="N10" t="n">
-        <v>78.15479999999999</v>
+        <v>79.02</v>
       </c>
       <c r="O10" t="n">
-        <v>79.2559</v>
+        <v>82.62</v>
       </c>
       <c r="P10" t="n">
-        <v>76.9248</v>
+        <v>78.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>78.502</v>
+        <v>82.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3.6394</v>
+        <v>-14.148</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2005</v>
+        <v>-7.656</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0182</v>
+        <v>-10.7201</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.1314</v>
+        <v>-7.1187</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.5306</v>
+        <v>-7.3408</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.4269</v>
+        <v>-9.612299999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.7092</v>
+        <v>14.3254</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.9804</v>
+        <v>5.853</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.8764</v>
+        <v>8.8528</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1425</v>
+        <v>7.1985</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.2551</v>
+        <v>7.3444</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6881</v>
+        <v>9.5647</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>56.64</v>
+        <v>48.04</v>
       </c>
       <c r="C11" t="n">
-        <v>58.25</v>
+        <v>49.38</v>
       </c>
       <c r="D11" t="n">
-        <v>55.59</v>
+        <v>45.96</v>
       </c>
       <c r="E11" t="n">
-        <v>57.04</v>
+        <v>46.61</v>
       </c>
       <c r="F11" t="n">
-        <v>44.7</v>
+        <v>40.56</v>
       </c>
       <c r="G11" t="n">
-        <v>45.22</v>
+        <v>40.59</v>
       </c>
       <c r="H11" t="n">
-        <v>43.95</v>
+        <v>38.56</v>
       </c>
       <c r="I11" t="n">
-        <v>44.39</v>
+        <v>38.78</v>
       </c>
       <c r="J11" t="n">
-        <v>36.32</v>
+        <v>41.94</v>
       </c>
       <c r="K11" t="n">
-        <v>37.06</v>
+        <v>43.71</v>
       </c>
       <c r="L11" t="n">
-        <v>35.23</v>
+        <v>40.8</v>
       </c>
       <c r="M11" t="n">
-        <v>36.02</v>
+        <v>43.1</v>
       </c>
       <c r="N11" t="n">
-        <v>76.43000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="O11" t="n">
-        <v>77.8</v>
+        <v>87.86</v>
       </c>
       <c r="P11" t="n">
-        <v>75.51000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>76.95999999999999</v>
+        <v>87.42</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7846</v>
+        <v>-4.8193</v>
       </c>
       <c r="S11" t="n">
-        <v>11.537</v>
+        <v>-15.1929</v>
       </c>
       <c r="T11" t="n">
-        <v>5.5905</v>
+        <v>-8.858000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9335</v>
+        <v>-5.9423</v>
       </c>
       <c r="V11" t="n">
-        <v>3.2112</v>
+        <v>-10.9488</v>
       </c>
       <c r="W11" t="n">
-        <v>-3.5501</v>
+        <v>-9.832599999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8441</v>
+        <v>4.6625</v>
       </c>
       <c r="Y11" t="n">
-        <v>-10.7581</v>
+        <v>15.0561</v>
       </c>
       <c r="Z11" t="n">
-        <v>-6.2384</v>
+        <v>6.7831</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.9643</v>
+        <v>5.9636</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.3203</v>
+        <v>11.3602</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1584</v>
+        <v>9.819800000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54.19</v>
+        <v>47.86</v>
       </c>
       <c r="C12" t="n">
-        <v>54.44</v>
+        <v>48.29</v>
       </c>
       <c r="D12" t="n">
-        <v>48.87</v>
+        <v>39.52</v>
       </c>
       <c r="E12" t="n">
-        <v>48.97</v>
+        <v>40.62</v>
       </c>
       <c r="F12" t="n">
-        <v>43.23</v>
+        <v>39.75</v>
       </c>
       <c r="G12" t="n">
-        <v>43.68</v>
+        <v>39.91</v>
       </c>
       <c r="H12" t="n">
-        <v>41.15</v>
+        <v>37.32</v>
       </c>
       <c r="I12" t="n">
-        <v>41.23</v>
+        <v>37.89</v>
       </c>
       <c r="J12" t="n">
-        <v>37.84</v>
+        <v>42</v>
       </c>
       <c r="K12" t="n">
-        <v>41.26</v>
+        <v>49.76</v>
       </c>
       <c r="L12" t="n">
-        <v>37.7</v>
+        <v>41.57</v>
       </c>
       <c r="M12" t="n">
-        <v>41.18</v>
+        <v>48.74</v>
       </c>
       <c r="N12" t="n">
-        <v>79.02</v>
+        <v>85.27</v>
       </c>
       <c r="O12" t="n">
-        <v>82.62</v>
+        <v>90.72</v>
       </c>
       <c r="P12" t="n">
-        <v>78.25</v>
+        <v>84.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>82.5</v>
+        <v>89.42</v>
       </c>
       <c r="R12" t="n">
-        <v>-14.148</v>
+        <v>-12.8513</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.656</v>
+        <v>-28.7868</v>
       </c>
       <c r="T12" t="n">
-        <v>-10.7201</v>
+        <v>-23.4018</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.1187</v>
+        <v>-2.295</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.3408</v>
+        <v>-14.6429</v>
       </c>
       <c r="W12" t="n">
-        <v>-9.612299999999999</v>
+        <v>-14.847</v>
       </c>
       <c r="X12" t="n">
-        <v>14.3254</v>
+        <v>13.0858</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.853</v>
+        <v>35.3137</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.8528</v>
+        <v>25.286</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.1985</v>
+        <v>2.2878</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.3444</v>
+        <v>16.1902</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.5647</v>
+        <v>16.3484</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48.04</v>
+        <v>42.88</v>
       </c>
       <c r="C13" t="n">
-        <v>49.38</v>
+        <v>48.18</v>
       </c>
       <c r="D13" t="n">
-        <v>45.96</v>
+        <v>42.61</v>
       </c>
       <c r="E13" t="n">
-        <v>46.61</v>
+        <v>47.91</v>
       </c>
       <c r="F13" t="n">
-        <v>40.56</v>
+        <v>39.09</v>
       </c>
       <c r="G13" t="n">
-        <v>40.59</v>
+        <v>42</v>
       </c>
       <c r="H13" t="n">
-        <v>38.56</v>
+        <v>39.07</v>
       </c>
       <c r="I13" t="n">
-        <v>38.78</v>
+        <v>41.68</v>
       </c>
       <c r="J13" t="n">
-        <v>41.94</v>
+        <v>45.87</v>
       </c>
       <c r="K13" t="n">
-        <v>43.71</v>
+        <v>46.38</v>
       </c>
       <c r="L13" t="n">
-        <v>40.8</v>
+        <v>39.61</v>
       </c>
       <c r="M13" t="n">
-        <v>43.1</v>
+        <v>39.86</v>
       </c>
       <c r="N13" t="n">
-        <v>83.87</v>
+        <v>86.62</v>
       </c>
       <c r="O13" t="n">
-        <v>87.86</v>
+        <v>86.66</v>
       </c>
       <c r="P13" t="n">
-        <v>83.78</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>87.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>-4.8193</v>
+        <v>17.9468</v>
       </c>
       <c r="S13" t="n">
-        <v>-15.1929</v>
+        <v>-2.1646</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.858000000000001</v>
+        <v>-12.8275</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.9423</v>
+        <v>10.0026</v>
       </c>
       <c r="V13" t="n">
-        <v>-10.9488</v>
+        <v>1.0914</v>
       </c>
       <c r="W13" t="n">
-        <v>-9.832599999999999</v>
+        <v>-4.2895</v>
       </c>
       <c r="X13" t="n">
-        <v>4.6625</v>
+        <v>-18.2191</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.0561</v>
+        <v>-3.2054</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.7831</v>
+        <v>6.4068</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.9636</v>
+        <v>-9.986599999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.3602</v>
+        <v>-2.4364</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.819800000000001</v>
+        <v>2.5324</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47.86</v>
+        <v>50.04</v>
       </c>
       <c r="C14" t="n">
-        <v>48.29</v>
+        <v>54.09</v>
       </c>
       <c r="D14" t="n">
-        <v>39.52</v>
+        <v>49.62</v>
       </c>
       <c r="E14" t="n">
-        <v>40.62</v>
+        <v>52.26</v>
       </c>
       <c r="F14" t="n">
-        <v>39.75</v>
+        <v>42.63</v>
       </c>
       <c r="G14" t="n">
-        <v>39.91</v>
+        <v>43.98</v>
       </c>
       <c r="H14" t="n">
-        <v>37.32</v>
+        <v>42.41</v>
       </c>
       <c r="I14" t="n">
-        <v>37.89</v>
+        <v>43.23</v>
       </c>
       <c r="J14" t="n">
-        <v>42</v>
+        <v>38.07</v>
       </c>
       <c r="K14" t="n">
-        <v>49.76</v>
+        <v>38.49</v>
       </c>
       <c r="L14" t="n">
-        <v>41.57</v>
+        <v>34.78</v>
       </c>
       <c r="M14" t="n">
-        <v>48.74</v>
+        <v>36.26</v>
       </c>
       <c r="N14" t="n">
-        <v>85.27</v>
+        <v>78.62</v>
       </c>
       <c r="O14" t="n">
-        <v>90.72</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>84.89</v>
+        <v>76.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>89.42</v>
+        <v>77.45</v>
       </c>
       <c r="R14" t="n">
-        <v>-12.8513</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-28.7868</v>
+        <v>12.1219</v>
       </c>
       <c r="T14" t="n">
-        <v>-23.4018</v>
+        <v>-8.380100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.295</v>
+        <v>3.7188</v>
       </c>
       <c r="V14" t="n">
-        <v>-14.6429</v>
+        <v>11.475</v>
       </c>
       <c r="W14" t="n">
-        <v>-14.847</v>
+        <v>-2.6132</v>
       </c>
       <c r="X14" t="n">
-        <v>13.0858</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>35.3137</v>
+        <v>-15.8701</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.286</v>
+        <v>0.6663</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2878</v>
+        <v>-3.7769</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.1902</v>
+        <v>-11.4047</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.3484</v>
+        <v>0.6367</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42.88</v>
+        <v>46.06</v>
       </c>
       <c r="C15" t="n">
-        <v>48.18</v>
+        <v>53.07</v>
       </c>
       <c r="D15" t="n">
-        <v>42.61</v>
+        <v>46.05</v>
       </c>
       <c r="E15" t="n">
-        <v>47.91</v>
+        <v>52.75</v>
       </c>
       <c r="F15" t="n">
-        <v>39.09</v>
+        <v>40.88</v>
       </c>
       <c r="G15" t="n">
-        <v>42</v>
+        <v>43.55</v>
       </c>
       <c r="H15" t="n">
-        <v>39.07</v>
+        <v>40.44</v>
       </c>
       <c r="I15" t="n">
-        <v>41.68</v>
+        <v>43.33</v>
       </c>
       <c r="J15" t="n">
-        <v>45.87</v>
+        <v>40.57</v>
       </c>
       <c r="K15" t="n">
-        <v>46.38</v>
+        <v>40.59</v>
       </c>
       <c r="L15" t="n">
-        <v>39.61</v>
+        <v>35.73</v>
       </c>
       <c r="M15" t="n">
-        <v>39.86</v>
+        <v>35.93</v>
       </c>
       <c r="N15" t="n">
-        <v>86.62</v>
+        <v>81.7</v>
       </c>
       <c r="O15" t="n">
-        <v>86.66</v>
+        <v>82.5</v>
       </c>
       <c r="P15" t="n">
-        <v>79.73999999999999</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>80.48999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>17.9468</v>
+        <v>0.9376</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1646</v>
+        <v>29.8621</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.8275</v>
+        <v>7.719</v>
       </c>
       <c r="U15" t="n">
-        <v>10.0026</v>
+        <v>0.2313</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0914</v>
+        <v>14.3574</v>
       </c>
       <c r="W15" t="n">
-        <v>-4.2895</v>
+        <v>5.0934</v>
       </c>
       <c r="X15" t="n">
-        <v>-18.2191</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y15" t="n">
-        <v>-3.2054</v>
+        <v>-26.2823</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.4068</v>
+        <v>-12.7489</v>
       </c>
       <c r="AA15" t="n">
-        <v>-9.986599999999999</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.4364</v>
+        <v>-13.5652</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5324</v>
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50.04</v>
+        <v>53.75</v>
       </c>
       <c r="C16" t="n">
-        <v>54.09</v>
+        <v>55.6</v>
       </c>
       <c r="D16" t="n">
-        <v>49.62</v>
+        <v>52.88</v>
       </c>
       <c r="E16" t="n">
-        <v>52.26</v>
+        <v>54.81</v>
       </c>
       <c r="F16" t="n">
-        <v>42.63</v>
+        <v>43.6</v>
       </c>
       <c r="G16" t="n">
-        <v>43.98</v>
+        <v>44.59</v>
       </c>
       <c r="H16" t="n">
-        <v>42.41</v>
+        <v>43.27</v>
       </c>
       <c r="I16" t="n">
-        <v>43.23</v>
+        <v>44.1</v>
       </c>
       <c r="J16" t="n">
-        <v>38.07</v>
+        <v>35.18</v>
       </c>
       <c r="K16" t="n">
-        <v>38.49</v>
+        <v>35.87</v>
       </c>
       <c r="L16" t="n">
-        <v>34.78</v>
+        <v>34.01</v>
       </c>
       <c r="M16" t="n">
-        <v>36.26</v>
+        <v>34.55</v>
       </c>
       <c r="N16" t="n">
-        <v>78.62</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>79.06999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="P16" t="n">
-        <v>76.03</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>77.45</v>
+        <v>75.92</v>
       </c>
       <c r="R16" t="n">
-        <v>9.079499999999999</v>
+        <v>3.9052</v>
       </c>
       <c r="S16" t="n">
-        <v>12.1219</v>
+        <v>14.402</v>
       </c>
       <c r="T16" t="n">
-        <v>-8.380100000000001</v>
+        <v>17.5928</v>
       </c>
       <c r="U16" t="n">
-        <v>3.7188</v>
+        <v>1.7771</v>
       </c>
       <c r="V16" t="n">
-        <v>11.475</v>
+        <v>5.8061</v>
       </c>
       <c r="W16" t="n">
-        <v>-2.6132</v>
+        <v>13.7184</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.031599999999999</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y16" t="n">
-        <v>-15.8701</v>
+        <v>-13.3216</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.6663</v>
+        <v>-19.8376</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.7769</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB16" t="n">
-        <v>-11.4047</v>
+        <v>-5.6777</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.6367</v>
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46.06</v>
+        <v>54.32</v>
       </c>
       <c r="C17" t="n">
-        <v>53.07</v>
+        <v>56.6</v>
       </c>
       <c r="D17" t="n">
-        <v>46.05</v>
+        <v>52.13</v>
       </c>
       <c r="E17" t="n">
-        <v>52.75</v>
+        <v>56.55</v>
       </c>
       <c r="F17" t="n">
-        <v>40.88</v>
+        <v>43.45</v>
       </c>
       <c r="G17" t="n">
-        <v>43.55</v>
+        <v>44.21</v>
       </c>
       <c r="H17" t="n">
-        <v>40.44</v>
+        <v>41.84</v>
       </c>
       <c r="I17" t="n">
-        <v>43.33</v>
+        <v>44.15</v>
       </c>
       <c r="J17" t="n">
-        <v>40.57</v>
+        <v>34.82</v>
       </c>
       <c r="K17" t="n">
-        <v>40.59</v>
+        <v>36.26</v>
       </c>
       <c r="L17" t="n">
-        <v>35.73</v>
+        <v>33.43</v>
       </c>
       <c r="M17" t="n">
-        <v>35.93</v>
+        <v>33.43</v>
       </c>
       <c r="N17" t="n">
-        <v>81.7</v>
+        <v>77.08</v>
       </c>
       <c r="O17" t="n">
-        <v>82.5</v>
+        <v>79.88</v>
       </c>
       <c r="P17" t="n">
-        <v>76.93000000000001</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>77.29000000000001</v>
+        <v>75.91</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9376</v>
+        <v>3.1746</v>
       </c>
       <c r="S17" t="n">
-        <v>29.8621</v>
+        <v>8.209</v>
       </c>
       <c r="T17" t="n">
-        <v>7.719</v>
+        <v>39.2171</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2313</v>
+        <v>0.1134</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3574</v>
+        <v>2.1282</v>
       </c>
       <c r="W17" t="n">
-        <v>5.0934</v>
+        <v>16.5215</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9101</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y17" t="n">
-        <v>-26.2823</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z17" t="n">
-        <v>-12.7489</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.2066</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB17" t="n">
-        <v>-13.5652</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.3152</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.75</v>
+        <v>66.33</v>
       </c>
       <c r="C18" t="n">
-        <v>55.6</v>
+        <v>67.98</v>
       </c>
       <c r="D18" t="n">
-        <v>52.88</v>
+        <v>63.56</v>
       </c>
       <c r="E18" t="n">
-        <v>54.81</v>
+        <v>67.5</v>
       </c>
       <c r="F18" t="n">
-        <v>43.6</v>
+        <v>48.64</v>
       </c>
       <c r="G18" t="n">
-        <v>44.59</v>
+        <v>48.92</v>
       </c>
       <c r="H18" t="n">
-        <v>43.27</v>
+        <v>47.15</v>
       </c>
       <c r="I18" t="n">
-        <v>44.1</v>
+        <v>48</v>
       </c>
       <c r="J18" t="n">
-        <v>35.18</v>
+        <v>27.7</v>
       </c>
       <c r="K18" t="n">
-        <v>35.87</v>
+        <v>29.31</v>
       </c>
       <c r="L18" t="n">
-        <v>34.01</v>
+        <v>26.75</v>
       </c>
       <c r="M18" t="n">
-        <v>34.55</v>
+        <v>26.96</v>
       </c>
       <c r="N18" t="n">
-        <v>76.84999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>77.45</v>
+        <v>70.73</v>
       </c>
       <c r="P18" t="n">
-        <v>75.09999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>75.92</v>
+        <v>69.2</v>
       </c>
       <c r="R18" t="n">
-        <v>3.9052</v>
+        <v>19.3634</v>
       </c>
       <c r="S18" t="n">
-        <v>14.402</v>
+        <v>27.9621</v>
       </c>
       <c r="T18" t="n">
-        <v>17.5928</v>
+        <v>40.8892</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7771</v>
+        <v>8.7203</v>
       </c>
       <c r="V18" t="n">
-        <v>5.8061</v>
+        <v>10.7778</v>
       </c>
       <c r="W18" t="n">
-        <v>13.7184</v>
+        <v>15.1631</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.8408</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y18" t="n">
-        <v>-13.3216</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z18" t="n">
-        <v>-19.8376</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1.7725</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>-5.6777</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC18" t="n">
-        <v>-13.1549</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54.32</v>
+        <v>68.12</v>
       </c>
       <c r="C19" t="n">
-        <v>56.6</v>
+        <v>72.28</v>
       </c>
       <c r="D19" t="n">
-        <v>52.13</v>
+        <v>68.12</v>
       </c>
       <c r="E19" t="n">
-        <v>56.55</v>
+        <v>71.98</v>
       </c>
       <c r="F19" t="n">
-        <v>43.45</v>
+        <v>48.02</v>
       </c>
       <c r="G19" t="n">
-        <v>44.21</v>
+        <v>49.09</v>
       </c>
       <c r="H19" t="n">
-        <v>41.84</v>
+        <v>47.31</v>
       </c>
       <c r="I19" t="n">
-        <v>44.15</v>
+        <v>48.96</v>
       </c>
       <c r="J19" t="n">
-        <v>34.82</v>
+        <v>26.76</v>
       </c>
       <c r="K19" t="n">
-        <v>36.26</v>
+        <v>26.76</v>
       </c>
       <c r="L19" t="n">
-        <v>33.43</v>
+        <v>25.09</v>
       </c>
       <c r="M19" t="n">
-        <v>33.43</v>
+        <v>25.2</v>
       </c>
       <c r="N19" t="n">
-        <v>77.08</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>79.88</v>
+        <v>70.3</v>
       </c>
       <c r="P19" t="n">
-        <v>75.79000000000001</v>
+        <v>67.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>75.91</v>
+        <v>67.86</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1746</v>
+        <v>6.637</v>
       </c>
       <c r="S19" t="n">
-        <v>8.209</v>
+        <v>31.3264</v>
       </c>
       <c r="T19" t="n">
-        <v>39.2171</v>
+        <v>37.7344</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1134</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1282</v>
+        <v>11.0204</v>
       </c>
       <c r="W19" t="n">
-        <v>16.5215</v>
+        <v>13.2547</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.2417</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y19" t="n">
-        <v>-7.8047</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z19" t="n">
-        <v>-31.4116</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.0132</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.9884</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC19" t="n">
-        <v>-15.1085</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>66.33</v>
+        <v>74.3</v>
       </c>
       <c r="C20" t="n">
-        <v>67.98</v>
+        <v>78.3</v>
       </c>
       <c r="D20" t="n">
-        <v>63.56</v>
+        <v>74.3</v>
       </c>
       <c r="E20" t="n">
-        <v>67.5</v>
+        <v>76.39</v>
       </c>
       <c r="F20" t="n">
-        <v>48.64</v>
+        <v>49.36</v>
       </c>
       <c r="G20" t="n">
-        <v>48.92</v>
+        <v>49.81</v>
       </c>
       <c r="H20" t="n">
-        <v>47.15</v>
+        <v>48.82</v>
       </c>
       <c r="I20" t="n">
-        <v>48</v>
+        <v>49.17</v>
       </c>
       <c r="J20" t="n">
-        <v>27.7</v>
+        <v>24.38</v>
       </c>
       <c r="K20" t="n">
-        <v>29.31</v>
+        <v>24.42</v>
       </c>
       <c r="L20" t="n">
-        <v>26.75</v>
+        <v>23.01</v>
       </c>
       <c r="M20" t="n">
-        <v>26.96</v>
+        <v>23.69</v>
       </c>
       <c r="N20" t="n">
-        <v>68.20999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O20" t="n">
-        <v>70.73</v>
+        <v>68.13</v>
       </c>
       <c r="P20" t="n">
-        <v>67.75</v>
+        <v>66.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>69.2</v>
+        <v>67.62</v>
       </c>
       <c r="R20" t="n">
-        <v>19.3634</v>
+        <v>6.1267</v>
       </c>
       <c r="S20" t="n">
-        <v>27.9621</v>
+        <v>35.084</v>
       </c>
       <c r="T20" t="n">
-        <v>40.8892</v>
+        <v>44.8152</v>
       </c>
       <c r="U20" t="n">
-        <v>8.7203</v>
+        <v>0.4289</v>
       </c>
       <c r="V20" t="n">
-        <v>10.7778</v>
+        <v>11.3703</v>
       </c>
       <c r="W20" t="n">
-        <v>15.1631</v>
+        <v>13.478</v>
       </c>
       <c r="X20" t="n">
-        <v>-19.3539</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y20" t="n">
-        <v>-24.9652</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z20" t="n">
-        <v>-32.3633</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA20" t="n">
-        <v>-8.839399999999999</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB20" t="n">
-        <v>-10.4671</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC20" t="n">
-        <v>-14.0266</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>68.12</v>
+        <v>75.59</v>
       </c>
       <c r="C21" t="n">
-        <v>72.28</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>68.12</v>
+        <v>75.25</v>
       </c>
       <c r="E21" t="n">
-        <v>71.98</v>
+        <v>80.56</v>
       </c>
       <c r="F21" t="n">
-        <v>48.02</v>
+        <v>48.78</v>
       </c>
       <c r="G21" t="n">
-        <v>49.09</v>
+        <v>50.74</v>
       </c>
       <c r="H21" t="n">
-        <v>47.31</v>
+        <v>48.465</v>
       </c>
       <c r="I21" t="n">
-        <v>48.96</v>
+        <v>50.66</v>
       </c>
       <c r="J21" t="n">
-        <v>26.76</v>
+        <v>23.92</v>
       </c>
       <c r="K21" t="n">
-        <v>26.76</v>
+        <v>24.025</v>
       </c>
       <c r="L21" t="n">
-        <v>25.09</v>
+        <v>22.3201</v>
       </c>
       <c r="M21" t="n">
-        <v>25.2</v>
+        <v>22.42</v>
       </c>
       <c r="N21" t="n">
-        <v>69.31999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="O21" t="n">
-        <v>70.3</v>
+        <v>68.63</v>
       </c>
       <c r="P21" t="n">
-        <v>67.72</v>
+        <v>65.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>67.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>6.637</v>
+        <v>5.4588</v>
       </c>
       <c r="S21" t="n">
-        <v>31.3264</v>
+        <v>19.3481</v>
       </c>
       <c r="T21" t="n">
-        <v>37.7344</v>
+        <v>46.9805</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>3.0303</v>
       </c>
       <c r="V21" t="n">
-        <v>11.0204</v>
+        <v>5.5417</v>
       </c>
       <c r="W21" t="n">
-        <v>13.2547</v>
+        <v>14.8753</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.5282</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y21" t="n">
-        <v>-27.0622</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z21" t="n">
-        <v>-30.5019</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.9364</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB21" t="n">
-        <v>-10.6164</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC21" t="n">
-        <v>-12.3822</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>74.295</v>
-      </c>
-      <c r="C22" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>74.295</v>
-      </c>
-      <c r="E22" t="n">
-        <v>76.39</v>
-      </c>
-      <c r="F22" t="n">
-        <v>49.3775</v>
-      </c>
-      <c r="G22" t="n">
-        <v>49.81</v>
-      </c>
-      <c r="H22" t="n">
-        <v>48.82</v>
-      </c>
-      <c r="I22" t="n">
-        <v>49.17</v>
-      </c>
-      <c r="J22" t="n">
-        <v>24.38</v>
-      </c>
-      <c r="K22" t="n">
-        <v>24.42</v>
-      </c>
-      <c r="L22" t="n">
-        <v>23.005</v>
-      </c>
-      <c r="M22" t="n">
-        <v>23.69</v>
-      </c>
-      <c r="N22" t="n">
-        <v>67.37</v>
-      </c>
-      <c r="O22" t="n">
-        <v>68.13</v>
-      </c>
-      <c r="P22" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6.1267</v>
-      </c>
-      <c r="S22" t="n">
-        <v>35.084</v>
-      </c>
-      <c r="T22" t="n">
-        <v>44.8152</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.4289</v>
-      </c>
-      <c r="V22" t="n">
-        <v>11.3703</v>
-      </c>
-      <c r="W22" t="n">
-        <v>13.478</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-5.9921</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>-29.1355</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-34.0662</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>-0.3537</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-10.9208</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26402,7 +26402,7 @@
         <v>50.74</v>
       </c>
       <c r="H21" t="n">
-        <v>48.465</v>
+        <v>48.46</v>
       </c>
       <c r="I21" t="n">
         <v>50.66</v>
@@ -26411,10 +26411,10 @@
         <v>23.92</v>
       </c>
       <c r="K21" t="n">
-        <v>24.025</v>
+        <v>24.03</v>
       </c>
       <c r="L21" t="n">
-        <v>22.3201</v>
+        <v>22.32</v>
       </c>
       <c r="M21" t="n">
         <v>22.42</v>
@@ -26466,6 +26466,97 @@
       </c>
       <c r="AC21" t="n">
         <v>-13.6328</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>83.27</v>
+      </c>
+      <c r="C22" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>85.31</v>
+      </c>
+      <c r="F22" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>53.43</v>
+      </c>
+      <c r="H22" t="n">
+        <v>51.395</v>
+      </c>
+      <c r="I22" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="J22" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="L22" t="n">
+        <v>21</v>
+      </c>
+      <c r="M22" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>64.67</v>
+      </c>
+      <c r="O22" t="n">
+        <v>64.67</v>
+      </c>
+      <c r="P22" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5.8962</v>
+      </c>
+      <c r="S22" t="n">
+        <v>18.519</v>
+      </c>
+      <c r="T22" t="n">
+        <v>50.8576</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5.4283</v>
+      </c>
+      <c r="V22" t="n">
+        <v>9.0891</v>
+      </c>
+      <c r="W22" t="n">
+        <v>20.974</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-6.1106</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-16.4683</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-37.0326</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-5.4141</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-8.606</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-18.298</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.06</v>
+        <v>55.1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.68</v>
+        <v>55.4</v>
       </c>
       <c r="D2" t="n">
-        <v>53.01</v>
+        <v>53.3</v>
       </c>
       <c r="E2" t="n">
-        <v>53.69</v>
+        <v>54.95</v>
       </c>
       <c r="F2" t="n">
-        <v>47.2918</v>
+        <v>48.0406</v>
       </c>
       <c r="G2" t="n">
-        <v>48.1903</v>
+        <v>48.6795</v>
       </c>
       <c r="H2" t="n">
-        <v>47.1021</v>
+        <v>47.7311</v>
       </c>
       <c r="I2" t="n">
-        <v>47.3817</v>
+        <v>48.0805</v>
       </c>
       <c r="J2" t="n">
-        <v>38.3272</v>
+        <v>37.6522</v>
       </c>
       <c r="K2" t="n">
-        <v>39.2306</v>
+        <v>38.9725</v>
       </c>
       <c r="L2" t="n">
-        <v>37.1261</v>
+        <v>37.4835</v>
       </c>
       <c r="M2" t="n">
-        <v>38.5754</v>
+        <v>37.7912</v>
       </c>
       <c r="N2" t="n">
-        <v>72.76860000000001</v>
+        <v>71.6279</v>
       </c>
       <c r="O2" t="n">
-        <v>73.086</v>
+        <v>72.0941</v>
       </c>
       <c r="P2" t="n">
-        <v>71.2807</v>
+        <v>70.63590000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>72.6198</v>
+        <v>71.5684</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.1</v>
+        <v>55.03</v>
       </c>
       <c r="C3" t="n">
-        <v>55.4</v>
+        <v>56.48</v>
       </c>
       <c r="D3" t="n">
-        <v>53.3</v>
+        <v>54</v>
       </c>
       <c r="E3" t="n">
-        <v>54.95</v>
+        <v>54.02</v>
       </c>
       <c r="F3" t="n">
-        <v>48.0406</v>
+        <v>47.6412</v>
       </c>
       <c r="G3" t="n">
-        <v>48.6795</v>
+        <v>48.0306</v>
       </c>
       <c r="H3" t="n">
-        <v>47.7311</v>
+        <v>45.974</v>
       </c>
       <c r="I3" t="n">
-        <v>48.0805</v>
+        <v>46.0239</v>
       </c>
       <c r="J3" t="n">
-        <v>37.6522</v>
+        <v>37.7515</v>
       </c>
       <c r="K3" t="n">
-        <v>38.9725</v>
+        <v>38.4563</v>
       </c>
       <c r="L3" t="n">
-        <v>37.4835</v>
+        <v>36.739</v>
       </c>
       <c r="M3" t="n">
-        <v>37.7912</v>
+        <v>38.4166</v>
       </c>
       <c r="N3" t="n">
-        <v>71.6279</v>
+        <v>72.233</v>
       </c>
       <c r="O3" t="n">
-        <v>72.0941</v>
+        <v>74.7029</v>
       </c>
       <c r="P3" t="n">
-        <v>70.63590000000001</v>
+        <v>71.6675</v>
       </c>
       <c r="Q3" t="n">
-        <v>71.5684</v>
+        <v>74.6037</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3468</v>
+        <v>-1.6924</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4748</v>
+        <v>-4.2774</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0329</v>
+        <v>1.6549</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.4478</v>
+        <v>4.2411</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.03</v>
+        <v>49.53</v>
       </c>
       <c r="C4" t="n">
-        <v>56.48</v>
+        <v>56.11</v>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>48.5</v>
       </c>
       <c r="E4" t="n">
-        <v>54.02</v>
+        <v>54.85</v>
       </c>
       <c r="F4" t="n">
-        <v>47.6412</v>
+        <v>44.7959</v>
       </c>
       <c r="G4" t="n">
-        <v>48.0306</v>
+        <v>46.2435</v>
       </c>
       <c r="H4" t="n">
-        <v>45.974</v>
+        <v>44.2269</v>
       </c>
       <c r="I4" t="n">
-        <v>46.0239</v>
+        <v>45.6146</v>
       </c>
       <c r="J4" t="n">
-        <v>37.7515</v>
+        <v>41.6924</v>
       </c>
       <c r="K4" t="n">
-        <v>38.4563</v>
+        <v>42.4171</v>
       </c>
       <c r="L4" t="n">
-        <v>36.739</v>
+        <v>36.9574</v>
       </c>
       <c r="M4" t="n">
-        <v>38.4166</v>
+        <v>37.8309</v>
       </c>
       <c r="N4" t="n">
-        <v>72.233</v>
+        <v>76.657</v>
       </c>
       <c r="O4" t="n">
-        <v>74.7029</v>
+        <v>77.55970000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>71.6675</v>
+        <v>74.27630000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>74.6037</v>
+        <v>75.298</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.6924</v>
+        <v>1.5365</v>
       </c>
       <c r="U4" t="n">
-        <v>-4.2774</v>
+        <v>-0.8893</v>
       </c>
       <c r="X4" t="n">
-        <v>1.6549</v>
+        <v>-1.5246</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.2411</v>
+        <v>0.9307</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.53</v>
+        <v>54.69</v>
       </c>
       <c r="C5" t="n">
-        <v>56.11</v>
+        <v>55.36</v>
       </c>
       <c r="D5" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
-        <v>54.85</v>
+        <v>51.14</v>
       </c>
       <c r="F5" t="n">
-        <v>44.7959</v>
+        <v>45.1054</v>
       </c>
       <c r="G5" t="n">
-        <v>46.2435</v>
+        <v>45.1354</v>
       </c>
       <c r="H5" t="n">
-        <v>44.2269</v>
+        <v>42.2302</v>
       </c>
       <c r="I5" t="n">
-        <v>45.6146</v>
+        <v>43.0089</v>
       </c>
       <c r="J5" t="n">
-        <v>41.6924</v>
+        <v>38.0394</v>
       </c>
       <c r="K5" t="n">
-        <v>42.4171</v>
+        <v>41.9505</v>
       </c>
       <c r="L5" t="n">
-        <v>36.9574</v>
+        <v>37.4934</v>
       </c>
       <c r="M5" t="n">
-        <v>37.8309</v>
+        <v>40.3622</v>
       </c>
       <c r="N5" t="n">
-        <v>76.657</v>
+        <v>76.1511</v>
       </c>
       <c r="O5" t="n">
-        <v>77.55970000000001</v>
+        <v>80.93219999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>74.27630000000001</v>
+        <v>76.1412</v>
       </c>
       <c r="Q5" t="n">
-        <v>75.298</v>
+        <v>79.6031</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5365</v>
+        <v>-6.7639</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1606</v>
+        <v>-6.9336</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8893</v>
+        <v>-5.7124</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.7295</v>
+        <v>-10.5481</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5246</v>
+        <v>6.6911</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.93</v>
+        <v>6.8032</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.9307</v>
+        <v>5.7174</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.688</v>
+        <v>11.2266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.69</v>
+        <v>54.63</v>
       </c>
       <c r="C6" t="n">
-        <v>55.36</v>
+        <v>56.81</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>52.28</v>
       </c>
       <c r="E6" t="n">
-        <v>51.14</v>
+        <v>53.03</v>
       </c>
       <c r="F6" t="n">
-        <v>45.1054</v>
+        <v>45.0355</v>
       </c>
       <c r="G6" t="n">
-        <v>45.1354</v>
+        <v>46.0738</v>
       </c>
       <c r="H6" t="n">
-        <v>42.2302</v>
+        <v>44.0572</v>
       </c>
       <c r="I6" t="n">
-        <v>43.0089</v>
+        <v>44.4964</v>
       </c>
       <c r="J6" t="n">
-        <v>38.0394</v>
+        <v>37.7316</v>
       </c>
       <c r="K6" t="n">
-        <v>41.9505</v>
+        <v>39.4986</v>
       </c>
       <c r="L6" t="n">
-        <v>37.4934</v>
+        <v>35.9547</v>
       </c>
       <c r="M6" t="n">
-        <v>40.3622</v>
+        <v>38.903</v>
       </c>
       <c r="N6" t="n">
-        <v>76.1511</v>
+        <v>75.8734</v>
       </c>
       <c r="O6" t="n">
-        <v>80.93219999999999</v>
+        <v>77.6985</v>
       </c>
       <c r="P6" t="n">
-        <v>76.1412</v>
+        <v>73.9589</v>
       </c>
       <c r="Q6" t="n">
-        <v>79.6031</v>
+        <v>76.8554</v>
       </c>
       <c r="R6" t="n">
-        <v>-6.7639</v>
+        <v>3.6957</v>
       </c>
       <c r="S6" t="n">
-        <v>-6.9336</v>
+        <v>-1.8327</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.7124</v>
+        <v>3.4586</v>
       </c>
       <c r="V6" t="n">
-        <v>-10.5481</v>
+        <v>-3.3189</v>
       </c>
       <c r="X6" t="n">
-        <v>6.6911</v>
+        <v>-3.6153</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.8032</v>
+        <v>1.2661</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.7174</v>
+        <v>-3.4517</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.2266</v>
+        <v>3.0182</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54.63</v>
+        <v>51.54</v>
       </c>
       <c r="C7" t="n">
-        <v>56.81</v>
+        <v>56.09</v>
       </c>
       <c r="D7" t="n">
-        <v>52.28</v>
+        <v>51.54</v>
       </c>
       <c r="E7" t="n">
-        <v>53.03</v>
+        <v>54.96</v>
       </c>
       <c r="F7" t="n">
-        <v>45.0355</v>
+        <v>43.7676</v>
       </c>
       <c r="G7" t="n">
-        <v>46.0738</v>
+        <v>44.4765</v>
       </c>
       <c r="H7" t="n">
-        <v>44.0572</v>
+        <v>43.1187</v>
       </c>
       <c r="I7" t="n">
-        <v>44.4964</v>
+        <v>43.548</v>
       </c>
       <c r="J7" t="n">
-        <v>37.7316</v>
+        <v>40.08</v>
       </c>
       <c r="K7" t="n">
-        <v>39.4986</v>
+        <v>40.08</v>
       </c>
       <c r="L7" t="n">
-        <v>35.9547</v>
+        <v>36.7</v>
       </c>
       <c r="M7" t="n">
-        <v>38.903</v>
+        <v>37.46</v>
       </c>
       <c r="N7" t="n">
-        <v>75.8734</v>
+        <v>78.15479999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>77.6985</v>
+        <v>79.2559</v>
       </c>
       <c r="P7" t="n">
-        <v>73.9589</v>
+        <v>76.9248</v>
       </c>
       <c r="Q7" t="n">
-        <v>76.8554</v>
+        <v>78.502</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6957</v>
+        <v>3.6394</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8327</v>
+        <v>0.2005</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2293</v>
+        <v>0.0182</v>
       </c>
       <c r="U7" t="n">
-        <v>3.4586</v>
+        <v>-2.1314</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.3189</v>
+        <v>-4.5306</v>
       </c>
       <c r="W7" t="n">
-        <v>-6.0895</v>
+        <v>-9.4269</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.6153</v>
+        <v>-3.7092</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2661</v>
+        <v>-0.9804</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.8492</v>
+        <v>-0.8764</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.4517</v>
+        <v>2.1425</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.0182</v>
+        <v>4.2551</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8326</v>
+        <v>9.6881</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.54</v>
+        <v>56.64</v>
       </c>
       <c r="C8" t="n">
-        <v>56.09</v>
+        <v>58.25</v>
       </c>
       <c r="D8" t="n">
-        <v>51.54</v>
+        <v>55.59</v>
       </c>
       <c r="E8" t="n">
-        <v>54.96</v>
+        <v>57.04</v>
       </c>
       <c r="F8" t="n">
-        <v>43.7676</v>
+        <v>44.7</v>
       </c>
       <c r="G8" t="n">
-        <v>44.4765</v>
+        <v>45.22</v>
       </c>
       <c r="H8" t="n">
-        <v>43.1187</v>
+        <v>43.95</v>
       </c>
       <c r="I8" t="n">
-        <v>43.548</v>
+        <v>44.39</v>
       </c>
       <c r="J8" t="n">
-        <v>40.08</v>
+        <v>36.32</v>
       </c>
       <c r="K8" t="n">
-        <v>40.08</v>
+        <v>37.06</v>
       </c>
       <c r="L8" t="n">
-        <v>36.7</v>
+        <v>35.23</v>
       </c>
       <c r="M8" t="n">
-        <v>37.46</v>
+        <v>36.02</v>
       </c>
       <c r="N8" t="n">
-        <v>78.15479999999999</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>79.2559</v>
+        <v>77.8</v>
       </c>
       <c r="P8" t="n">
-        <v>76.9248</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>78.502</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>3.6394</v>
+        <v>3.7846</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2005</v>
+        <v>11.537</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0182</v>
+        <v>5.5905</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.1314</v>
+        <v>1.9335</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.5306</v>
+        <v>3.2112</v>
       </c>
       <c r="W8" t="n">
-        <v>-9.4269</v>
+        <v>-3.5501</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.7092</v>
+        <v>-3.8441</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.9804</v>
+        <v>-10.7581</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.8764</v>
+        <v>-6.2384</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1425</v>
+        <v>-1.9643</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.2551</v>
+        <v>-3.3203</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.6881</v>
+        <v>3.1584</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56.64</v>
+        <v>54.19</v>
       </c>
       <c r="C9" t="n">
-        <v>58.25</v>
+        <v>54.44</v>
       </c>
       <c r="D9" t="n">
-        <v>55.59</v>
+        <v>48.87</v>
       </c>
       <c r="E9" t="n">
-        <v>57.04</v>
+        <v>48.97</v>
       </c>
       <c r="F9" t="n">
-        <v>44.7</v>
+        <v>43.23</v>
       </c>
       <c r="G9" t="n">
-        <v>45.22</v>
+        <v>43.68</v>
       </c>
       <c r="H9" t="n">
-        <v>43.95</v>
+        <v>41.15</v>
       </c>
       <c r="I9" t="n">
-        <v>44.39</v>
+        <v>41.23</v>
       </c>
       <c r="J9" t="n">
-        <v>36.32</v>
+        <v>37.84</v>
       </c>
       <c r="K9" t="n">
-        <v>37.06</v>
+        <v>41.26</v>
       </c>
       <c r="L9" t="n">
-        <v>35.23</v>
+        <v>37.7</v>
       </c>
       <c r="M9" t="n">
-        <v>36.02</v>
+        <v>41.18</v>
       </c>
       <c r="N9" t="n">
-        <v>76.43000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="O9" t="n">
-        <v>77.8</v>
+        <v>82.62</v>
       </c>
       <c r="P9" t="n">
-        <v>75.51000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>76.95999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7846</v>
+        <v>-14.148</v>
       </c>
       <c r="S9" t="n">
-        <v>11.537</v>
+        <v>-7.656</v>
       </c>
       <c r="T9" t="n">
-        <v>5.5905</v>
+        <v>-10.7201</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9335</v>
+        <v>-7.1187</v>
       </c>
       <c r="V9" t="n">
-        <v>3.2112</v>
+        <v>-7.3408</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.5501</v>
+        <v>-9.612299999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.8441</v>
+        <v>14.3254</v>
       </c>
       <c r="Y9" t="n">
-        <v>-10.7581</v>
+        <v>5.853</v>
       </c>
       <c r="Z9" t="n">
-        <v>-6.2384</v>
+        <v>8.8528</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.9643</v>
+        <v>7.1985</v>
       </c>
       <c r="AB9" t="n">
-        <v>-3.3203</v>
+        <v>7.3444</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1584</v>
+        <v>9.5647</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.19</v>
+        <v>48.04</v>
       </c>
       <c r="C10" t="n">
-        <v>54.44</v>
+        <v>49.38</v>
       </c>
       <c r="D10" t="n">
-        <v>48.87</v>
+        <v>45.96</v>
       </c>
       <c r="E10" t="n">
-        <v>48.97</v>
+        <v>46.61</v>
       </c>
       <c r="F10" t="n">
-        <v>43.23</v>
+        <v>40.56</v>
       </c>
       <c r="G10" t="n">
-        <v>43.68</v>
+        <v>40.59</v>
       </c>
       <c r="H10" t="n">
-        <v>41.15</v>
+        <v>38.56</v>
       </c>
       <c r="I10" t="n">
-        <v>41.23</v>
+        <v>38.78</v>
       </c>
       <c r="J10" t="n">
-        <v>37.84</v>
+        <v>41.94</v>
       </c>
       <c r="K10" t="n">
-        <v>41.26</v>
+        <v>43.71</v>
       </c>
       <c r="L10" t="n">
-        <v>37.7</v>
+        <v>40.8</v>
       </c>
       <c r="M10" t="n">
-        <v>41.18</v>
+        <v>43.1</v>
       </c>
       <c r="N10" t="n">
-        <v>79.02</v>
+        <v>83.87</v>
       </c>
       <c r="O10" t="n">
-        <v>82.62</v>
+        <v>87.86</v>
       </c>
       <c r="P10" t="n">
-        <v>78.25</v>
+        <v>83.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>82.5</v>
+        <v>87.42</v>
       </c>
       <c r="R10" t="n">
-        <v>-14.148</v>
+        <v>-4.8193</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.656</v>
+        <v>-15.1929</v>
       </c>
       <c r="T10" t="n">
-        <v>-10.7201</v>
+        <v>-8.858000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.1187</v>
+        <v>-5.9423</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.3408</v>
+        <v>-10.9488</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.612299999999999</v>
+        <v>-9.832599999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>14.3254</v>
+        <v>4.6625</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.853</v>
+        <v>15.0561</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.8528</v>
+        <v>6.7831</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.1985</v>
+        <v>5.9636</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.3444</v>
+        <v>11.3602</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.5647</v>
+        <v>9.819800000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48.04</v>
+        <v>47.86</v>
       </c>
       <c r="C11" t="n">
-        <v>49.38</v>
+        <v>48.29</v>
       </c>
       <c r="D11" t="n">
-        <v>45.96</v>
+        <v>39.52</v>
       </c>
       <c r="E11" t="n">
-        <v>46.61</v>
+        <v>40.62</v>
       </c>
       <c r="F11" t="n">
-        <v>40.56</v>
+        <v>39.75</v>
       </c>
       <c r="G11" t="n">
-        <v>40.59</v>
+        <v>39.91</v>
       </c>
       <c r="H11" t="n">
-        <v>38.56</v>
+        <v>37.32</v>
       </c>
       <c r="I11" t="n">
-        <v>38.78</v>
+        <v>37.89</v>
       </c>
       <c r="J11" t="n">
-        <v>41.94</v>
+        <v>42</v>
       </c>
       <c r="K11" t="n">
-        <v>43.71</v>
+        <v>49.76</v>
       </c>
       <c r="L11" t="n">
-        <v>40.8</v>
+        <v>41.57</v>
       </c>
       <c r="M11" t="n">
-        <v>43.1</v>
+        <v>48.74</v>
       </c>
       <c r="N11" t="n">
-        <v>83.87</v>
+        <v>85.27</v>
       </c>
       <c r="O11" t="n">
-        <v>87.86</v>
+        <v>90.72</v>
       </c>
       <c r="P11" t="n">
-        <v>83.78</v>
+        <v>84.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>87.42</v>
+        <v>89.42</v>
       </c>
       <c r="R11" t="n">
-        <v>-4.8193</v>
+        <v>-12.8513</v>
       </c>
       <c r="S11" t="n">
-        <v>-15.1929</v>
+        <v>-28.7868</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.858000000000001</v>
+        <v>-23.4018</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.9423</v>
+        <v>-2.295</v>
       </c>
       <c r="V11" t="n">
-        <v>-10.9488</v>
+        <v>-14.6429</v>
       </c>
       <c r="W11" t="n">
-        <v>-9.832599999999999</v>
+        <v>-14.847</v>
       </c>
       <c r="X11" t="n">
-        <v>4.6625</v>
+        <v>13.0858</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.0561</v>
+        <v>35.3137</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.7831</v>
+        <v>25.286</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.9636</v>
+        <v>2.2878</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.3602</v>
+        <v>16.1902</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.819800000000001</v>
+        <v>16.3484</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47.86</v>
+        <v>42.88</v>
       </c>
       <c r="C12" t="n">
-        <v>48.29</v>
+        <v>48.18</v>
       </c>
       <c r="D12" t="n">
-        <v>39.52</v>
+        <v>42.61</v>
       </c>
       <c r="E12" t="n">
-        <v>40.62</v>
+        <v>47.91</v>
       </c>
       <c r="F12" t="n">
-        <v>39.75</v>
+        <v>39.09</v>
       </c>
       <c r="G12" t="n">
-        <v>39.91</v>
+        <v>42</v>
       </c>
       <c r="H12" t="n">
-        <v>37.32</v>
+        <v>39.07</v>
       </c>
       <c r="I12" t="n">
-        <v>37.89</v>
+        <v>41.68</v>
       </c>
       <c r="J12" t="n">
-        <v>42</v>
+        <v>45.87</v>
       </c>
       <c r="K12" t="n">
-        <v>49.76</v>
+        <v>46.38</v>
       </c>
       <c r="L12" t="n">
-        <v>41.57</v>
+        <v>39.61</v>
       </c>
       <c r="M12" t="n">
-        <v>48.74</v>
+        <v>39.86</v>
       </c>
       <c r="N12" t="n">
-        <v>85.27</v>
+        <v>86.62</v>
       </c>
       <c r="O12" t="n">
-        <v>90.72</v>
+        <v>86.66</v>
       </c>
       <c r="P12" t="n">
-        <v>84.89</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>89.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>-12.8513</v>
+        <v>17.9468</v>
       </c>
       <c r="S12" t="n">
-        <v>-28.7868</v>
+        <v>-2.1646</v>
       </c>
       <c r="T12" t="n">
-        <v>-23.4018</v>
+        <v>-12.8275</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.295</v>
+        <v>10.0026</v>
       </c>
       <c r="V12" t="n">
-        <v>-14.6429</v>
+        <v>1.0914</v>
       </c>
       <c r="W12" t="n">
-        <v>-14.847</v>
+        <v>-4.2895</v>
       </c>
       <c r="X12" t="n">
-        <v>13.0858</v>
+        <v>-18.2191</v>
       </c>
       <c r="Y12" t="n">
-        <v>35.3137</v>
+        <v>-3.2054</v>
       </c>
       <c r="Z12" t="n">
-        <v>25.286</v>
+        <v>6.4068</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2878</v>
+        <v>-9.986599999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.1902</v>
+        <v>-2.4364</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.3484</v>
+        <v>2.5324</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.88</v>
+        <v>50.04</v>
       </c>
       <c r="C13" t="n">
-        <v>48.18</v>
+        <v>54.09</v>
       </c>
       <c r="D13" t="n">
-        <v>42.61</v>
+        <v>49.62</v>
       </c>
       <c r="E13" t="n">
-        <v>47.91</v>
+        <v>52.26</v>
       </c>
       <c r="F13" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="G13" t="n">
-        <v>42</v>
+        <v>43.98</v>
       </c>
       <c r="H13" t="n">
-        <v>39.07</v>
+        <v>42.41</v>
       </c>
       <c r="I13" t="n">
-        <v>41.68</v>
+        <v>43.23</v>
       </c>
       <c r="J13" t="n">
-        <v>45.87</v>
+        <v>38.07</v>
       </c>
       <c r="K13" t="n">
-        <v>46.38</v>
+        <v>38.49</v>
       </c>
       <c r="L13" t="n">
-        <v>39.61</v>
+        <v>34.78</v>
       </c>
       <c r="M13" t="n">
-        <v>39.86</v>
+        <v>36.26</v>
       </c>
       <c r="N13" t="n">
-        <v>86.62</v>
+        <v>78.62</v>
       </c>
       <c r="O13" t="n">
-        <v>86.66</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>79.73999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="Q13" t="n">
-        <v>80.48999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="R13" t="n">
-        <v>17.9468</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1646</v>
+        <v>12.1219</v>
       </c>
       <c r="T13" t="n">
-        <v>-12.8275</v>
+        <v>-8.380100000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>10.0026</v>
+        <v>3.7188</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0914</v>
+        <v>11.475</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.2895</v>
+        <v>-2.6132</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.2191</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>-3.2054</v>
+        <v>-15.8701</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.4068</v>
+        <v>0.6663</v>
       </c>
       <c r="AA13" t="n">
-        <v>-9.986599999999999</v>
+        <v>-3.7769</v>
       </c>
       <c r="AB13" t="n">
-        <v>-2.4364</v>
+        <v>-11.4047</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5324</v>
+        <v>0.6367</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C14" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D14" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E14" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F14" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G14" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H14" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I14" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J14" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K14" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L14" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M14" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N14" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O14" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P14" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>9.079499999999999</v>
+        <v>0.9376</v>
       </c>
       <c r="S14" t="n">
-        <v>12.1219</v>
+        <v>29.8621</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.380100000000001</v>
+        <v>7.719</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7188</v>
+        <v>0.2313</v>
       </c>
       <c r="V14" t="n">
-        <v>11.475</v>
+        <v>14.3574</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.6132</v>
+        <v>5.0934</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.031599999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y14" t="n">
-        <v>-15.8701</v>
+        <v>-26.2823</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6663</v>
+        <v>-12.7489</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.7769</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB14" t="n">
-        <v>-11.4047</v>
+        <v>-13.5652</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.6367</v>
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C15" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D15" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E15" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F15" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G15" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H15" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I15" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J15" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K15" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L15" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M15" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N15" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P15" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="S15" t="n">
-        <v>29.8621</v>
+        <v>14.402</v>
       </c>
       <c r="T15" t="n">
-        <v>7.719</v>
+        <v>17.5928</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="V15" t="n">
-        <v>14.3574</v>
+        <v>5.8061</v>
       </c>
       <c r="W15" t="n">
-        <v>5.0934</v>
+        <v>13.7184</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y15" t="n">
-        <v>-26.2823</v>
+        <v>-13.3216</v>
       </c>
       <c r="Z15" t="n">
-        <v>-12.7489</v>
+        <v>-19.8376</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB15" t="n">
-        <v>-13.5652</v>
+        <v>-5.6777</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3152</v>
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C16" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D16" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E16" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F16" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G16" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H16" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I16" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J16" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K16" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L16" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M16" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N16" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O16" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P16" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R16" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="S16" t="n">
-        <v>14.402</v>
+        <v>8.209</v>
       </c>
       <c r="T16" t="n">
-        <v>17.5928</v>
+        <v>39.2171</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="V16" t="n">
-        <v>5.8061</v>
+        <v>2.1282</v>
       </c>
       <c r="W16" t="n">
-        <v>13.7184</v>
+        <v>16.5215</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y16" t="n">
-        <v>-13.3216</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z16" t="n">
-        <v>-19.8376</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB16" t="n">
-        <v>-5.6777</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC16" t="n">
-        <v>-13.1549</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C17" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D17" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E17" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F17" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G17" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H17" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I17" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J17" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K17" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L17" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M17" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N17" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P17" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S17" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="T17" t="n">
-        <v>39.2171</v>
+        <v>40.8892</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="W17" t="n">
-        <v>16.5215</v>
+        <v>15.1631</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y17" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z17" t="n">
-        <v>-31.4116</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC17" t="n">
-        <v>-15.1085</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C18" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D18" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E18" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F18" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G18" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H18" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I18" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J18" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K18" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L18" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M18" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N18" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P18" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R18" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S18" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="T18" t="n">
-        <v>40.8892</v>
+        <v>37.7344</v>
       </c>
       <c r="U18" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="W18" t="n">
-        <v>15.1631</v>
+        <v>13.2547</v>
       </c>
       <c r="X18" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y18" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z18" t="n">
-        <v>-32.3633</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA18" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB18" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC18" t="n">
-        <v>-14.0266</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C19" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D19" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E19" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F19" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G19" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H19" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I19" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J19" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K19" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L19" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M19" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N19" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O19" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P19" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R19" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S19" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T19" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V19" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W19" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X19" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y19" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z19" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB19" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC19" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C20" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E20" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F20" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G20" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H20" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I20" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J20" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K20" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L20" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M20" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N20" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O20" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P20" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S20" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T20" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V20" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W20" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X20" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y20" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z20" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB20" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC20" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C21" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F21" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G21" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H21" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I21" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J21" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K21" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L21" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M21" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N21" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O21" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R21" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S21" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T21" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U21" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W21" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X21" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y21" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z21" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA21" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB21" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC21" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C22" t="n">
-        <v>85.56999999999999</v>
+        <v>85.97499999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>51.4</v>
+        <v>53.565</v>
       </c>
       <c r="G22" t="n">
-        <v>53.43</v>
+        <v>55.7382</v>
       </c>
       <c r="H22" t="n">
-        <v>51.395</v>
+        <v>53.33</v>
       </c>
       <c r="I22" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J22" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K22" t="n">
-        <v>22.34</v>
+        <v>22.425</v>
       </c>
       <c r="L22" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M22" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N22" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O22" t="n">
-        <v>64.67</v>
+        <v>62.15</v>
       </c>
       <c r="P22" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R22" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S22" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T22" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U22" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V22" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W22" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y22" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z22" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA22" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB22" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC22" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.1</v>
+        <v>55.03</v>
       </c>
       <c r="C2" t="n">
-        <v>55.4</v>
+        <v>56.48</v>
       </c>
       <c r="D2" t="n">
-        <v>53.3</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>54.95</v>
+        <v>54.02</v>
       </c>
       <c r="F2" t="n">
-        <v>48.0406</v>
+        <v>47.6412</v>
       </c>
       <c r="G2" t="n">
-        <v>48.6795</v>
+        <v>48.0306</v>
       </c>
       <c r="H2" t="n">
-        <v>47.7311</v>
+        <v>45.974</v>
       </c>
       <c r="I2" t="n">
-        <v>48.0805</v>
+        <v>46.0239</v>
       </c>
       <c r="J2" t="n">
-        <v>37.6522</v>
+        <v>37.7515</v>
       </c>
       <c r="K2" t="n">
-        <v>38.9725</v>
+        <v>38.4563</v>
       </c>
       <c r="L2" t="n">
-        <v>37.4835</v>
+        <v>36.739</v>
       </c>
       <c r="M2" t="n">
-        <v>37.7912</v>
+        <v>38.4166</v>
       </c>
       <c r="N2" t="n">
-        <v>71.6279</v>
+        <v>72.233</v>
       </c>
       <c r="O2" t="n">
-        <v>72.0941</v>
+        <v>74.7029</v>
       </c>
       <c r="P2" t="n">
-        <v>70.63590000000001</v>
+        <v>71.6675</v>
       </c>
       <c r="Q2" t="n">
-        <v>71.5684</v>
+        <v>74.6037</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.03</v>
+        <v>49.53</v>
       </c>
       <c r="C3" t="n">
-        <v>56.48</v>
+        <v>56.11</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>48.5</v>
       </c>
       <c r="E3" t="n">
-        <v>54.02</v>
+        <v>54.85</v>
       </c>
       <c r="F3" t="n">
-        <v>47.6412</v>
+        <v>44.7959</v>
       </c>
       <c r="G3" t="n">
-        <v>48.0306</v>
+        <v>46.2435</v>
       </c>
       <c r="H3" t="n">
-        <v>45.974</v>
+        <v>44.2269</v>
       </c>
       <c r="I3" t="n">
-        <v>46.0239</v>
+        <v>45.6146</v>
       </c>
       <c r="J3" t="n">
-        <v>37.7515</v>
+        <v>41.6924</v>
       </c>
       <c r="K3" t="n">
-        <v>38.4563</v>
+        <v>42.4171</v>
       </c>
       <c r="L3" t="n">
-        <v>36.739</v>
+        <v>36.9574</v>
       </c>
       <c r="M3" t="n">
-        <v>38.4166</v>
+        <v>37.8309</v>
       </c>
       <c r="N3" t="n">
-        <v>72.233</v>
+        <v>76.657</v>
       </c>
       <c r="O3" t="n">
-        <v>74.7029</v>
+        <v>77.55970000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>71.6675</v>
+        <v>74.27630000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>74.6037</v>
+        <v>75.298</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.6924</v>
+        <v>1.5365</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.2774</v>
+        <v>-0.8893</v>
       </c>
       <c r="X3" t="n">
-        <v>1.6549</v>
+        <v>-1.5246</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.2411</v>
+        <v>0.9307</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.53</v>
+        <v>54.69</v>
       </c>
       <c r="C4" t="n">
-        <v>56.11</v>
+        <v>55.36</v>
       </c>
       <c r="D4" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
-        <v>54.85</v>
+        <v>51.14</v>
       </c>
       <c r="F4" t="n">
-        <v>44.7959</v>
+        <v>45.1054</v>
       </c>
       <c r="G4" t="n">
-        <v>46.2435</v>
+        <v>45.1354</v>
       </c>
       <c r="H4" t="n">
-        <v>44.2269</v>
+        <v>42.2302</v>
       </c>
       <c r="I4" t="n">
-        <v>45.6146</v>
+        <v>43.0089</v>
       </c>
       <c r="J4" t="n">
-        <v>41.6924</v>
+        <v>38.0394</v>
       </c>
       <c r="K4" t="n">
-        <v>42.4171</v>
+        <v>41.9505</v>
       </c>
       <c r="L4" t="n">
-        <v>36.9574</v>
+        <v>37.4934</v>
       </c>
       <c r="M4" t="n">
-        <v>37.8309</v>
+        <v>40.3622</v>
       </c>
       <c r="N4" t="n">
-        <v>76.657</v>
+        <v>76.1511</v>
       </c>
       <c r="O4" t="n">
-        <v>77.55970000000001</v>
+        <v>80.93219999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>74.27630000000001</v>
+        <v>76.1412</v>
       </c>
       <c r="Q4" t="n">
-        <v>75.298</v>
+        <v>79.6031</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5365</v>
+        <v>-6.7639</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8893</v>
+        <v>-5.7124</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5246</v>
+        <v>6.6911</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9307</v>
+        <v>5.7174</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.69</v>
+        <v>54.63</v>
       </c>
       <c r="C5" t="n">
-        <v>55.36</v>
+        <v>56.81</v>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>52.28</v>
       </c>
       <c r="E5" t="n">
-        <v>51.14</v>
+        <v>53.03</v>
       </c>
       <c r="F5" t="n">
-        <v>45.1054</v>
+        <v>45.0355</v>
       </c>
       <c r="G5" t="n">
-        <v>45.1354</v>
+        <v>46.0738</v>
       </c>
       <c r="H5" t="n">
-        <v>42.2302</v>
+        <v>44.0572</v>
       </c>
       <c r="I5" t="n">
-        <v>43.0089</v>
+        <v>44.4964</v>
       </c>
       <c r="J5" t="n">
-        <v>38.0394</v>
+        <v>37.7316</v>
       </c>
       <c r="K5" t="n">
-        <v>41.9505</v>
+        <v>39.4986</v>
       </c>
       <c r="L5" t="n">
-        <v>37.4934</v>
+        <v>35.9547</v>
       </c>
       <c r="M5" t="n">
-        <v>40.3622</v>
+        <v>38.903</v>
       </c>
       <c r="N5" t="n">
-        <v>76.1511</v>
+        <v>75.8734</v>
       </c>
       <c r="O5" t="n">
-        <v>80.93219999999999</v>
+        <v>77.6985</v>
       </c>
       <c r="P5" t="n">
-        <v>76.1412</v>
+        <v>73.9589</v>
       </c>
       <c r="Q5" t="n">
-        <v>79.6031</v>
+        <v>76.8554</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.7639</v>
+        <v>3.6957</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.9336</v>
+        <v>-1.8327</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.7124</v>
+        <v>3.4586</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.5481</v>
+        <v>-3.3189</v>
       </c>
       <c r="X5" t="n">
-        <v>6.6911</v>
+        <v>-3.6153</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.8032</v>
+        <v>1.2661</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.7174</v>
+        <v>-3.4517</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.2266</v>
+        <v>3.0182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.63</v>
+        <v>51.54</v>
       </c>
       <c r="C6" t="n">
-        <v>56.81</v>
+        <v>56.09</v>
       </c>
       <c r="D6" t="n">
-        <v>52.28</v>
+        <v>51.54</v>
       </c>
       <c r="E6" t="n">
-        <v>53.03</v>
+        <v>54.96</v>
       </c>
       <c r="F6" t="n">
-        <v>45.0355</v>
+        <v>43.7676</v>
       </c>
       <c r="G6" t="n">
-        <v>46.0738</v>
+        <v>44.4765</v>
       </c>
       <c r="H6" t="n">
-        <v>44.0572</v>
+        <v>43.1187</v>
       </c>
       <c r="I6" t="n">
-        <v>44.4964</v>
+        <v>43.548</v>
       </c>
       <c r="J6" t="n">
-        <v>37.7316</v>
+        <v>40.08</v>
       </c>
       <c r="K6" t="n">
-        <v>39.4986</v>
+        <v>40.08</v>
       </c>
       <c r="L6" t="n">
-        <v>35.9547</v>
+        <v>36.7</v>
       </c>
       <c r="M6" t="n">
-        <v>38.903</v>
+        <v>37.46</v>
       </c>
       <c r="N6" t="n">
-        <v>75.8734</v>
+        <v>78.15479999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>77.6985</v>
+        <v>79.2559</v>
       </c>
       <c r="P6" t="n">
-        <v>73.9589</v>
+        <v>76.9248</v>
       </c>
       <c r="Q6" t="n">
-        <v>76.8554</v>
+        <v>78.502</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6957</v>
+        <v>3.6394</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8327</v>
+        <v>0.2005</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4586</v>
+        <v>-2.1314</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.3189</v>
+        <v>-4.5306</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.6153</v>
+        <v>-3.7092</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2661</v>
+        <v>-0.9804</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.4517</v>
+        <v>2.1425</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.0182</v>
+        <v>4.2551</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51.54</v>
+        <v>56.64</v>
       </c>
       <c r="C7" t="n">
-        <v>56.09</v>
+        <v>58.25</v>
       </c>
       <c r="D7" t="n">
-        <v>51.54</v>
+        <v>55.59</v>
       </c>
       <c r="E7" t="n">
-        <v>54.96</v>
+        <v>57.04</v>
       </c>
       <c r="F7" t="n">
-        <v>43.7676</v>
+        <v>44.7</v>
       </c>
       <c r="G7" t="n">
-        <v>44.4765</v>
+        <v>45.22</v>
       </c>
       <c r="H7" t="n">
-        <v>43.1187</v>
+        <v>43.95</v>
       </c>
       <c r="I7" t="n">
-        <v>43.548</v>
+        <v>44.39</v>
       </c>
       <c r="J7" t="n">
-        <v>40.08</v>
+        <v>36.32</v>
       </c>
       <c r="K7" t="n">
-        <v>40.08</v>
+        <v>37.06</v>
       </c>
       <c r="L7" t="n">
-        <v>36.7</v>
+        <v>35.23</v>
       </c>
       <c r="M7" t="n">
-        <v>37.46</v>
+        <v>36.02</v>
       </c>
       <c r="N7" t="n">
-        <v>78.15479999999999</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>79.2559</v>
+        <v>77.8</v>
       </c>
       <c r="P7" t="n">
-        <v>76.9248</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>78.502</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6394</v>
+        <v>3.7846</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2005</v>
+        <v>11.537</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0182</v>
+        <v>5.5905</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.1314</v>
+        <v>1.9335</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.5306</v>
+        <v>3.2112</v>
       </c>
       <c r="W7" t="n">
-        <v>-9.4269</v>
+        <v>-3.5501</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.7092</v>
+        <v>-3.8441</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.9804</v>
+        <v>-10.7581</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.8764</v>
+        <v>-6.2384</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1425</v>
+        <v>-1.9643</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.2551</v>
+        <v>-3.3203</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6881</v>
+        <v>3.1584</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56.64</v>
+        <v>54.19</v>
       </c>
       <c r="C8" t="n">
-        <v>58.25</v>
+        <v>54.44</v>
       </c>
       <c r="D8" t="n">
-        <v>55.59</v>
+        <v>48.87</v>
       </c>
       <c r="E8" t="n">
-        <v>57.04</v>
+        <v>48.97</v>
       </c>
       <c r="F8" t="n">
-        <v>44.7</v>
+        <v>43.23</v>
       </c>
       <c r="G8" t="n">
-        <v>45.22</v>
+        <v>43.68</v>
       </c>
       <c r="H8" t="n">
-        <v>43.95</v>
+        <v>41.15</v>
       </c>
       <c r="I8" t="n">
-        <v>44.39</v>
+        <v>41.23</v>
       </c>
       <c r="J8" t="n">
-        <v>36.32</v>
+        <v>37.84</v>
       </c>
       <c r="K8" t="n">
-        <v>37.06</v>
+        <v>41.26</v>
       </c>
       <c r="L8" t="n">
-        <v>35.23</v>
+        <v>37.7</v>
       </c>
       <c r="M8" t="n">
-        <v>36.02</v>
+        <v>41.18</v>
       </c>
       <c r="N8" t="n">
-        <v>76.43000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="O8" t="n">
-        <v>77.8</v>
+        <v>82.62</v>
       </c>
       <c r="P8" t="n">
-        <v>75.51000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>76.95999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="R8" t="n">
-        <v>3.7846</v>
+        <v>-14.148</v>
       </c>
       <c r="S8" t="n">
-        <v>11.537</v>
+        <v>-7.656</v>
       </c>
       <c r="T8" t="n">
-        <v>5.5905</v>
+        <v>-10.7201</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9335</v>
+        <v>-7.1187</v>
       </c>
       <c r="V8" t="n">
-        <v>3.2112</v>
+        <v>-7.3408</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.5501</v>
+        <v>-9.612299999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.8441</v>
+        <v>14.3254</v>
       </c>
       <c r="Y8" t="n">
-        <v>-10.7581</v>
+        <v>5.853</v>
       </c>
       <c r="Z8" t="n">
-        <v>-6.2384</v>
+        <v>8.8528</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.9643</v>
+        <v>7.1985</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.3203</v>
+        <v>7.3444</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.1584</v>
+        <v>9.5647</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.19</v>
+        <v>48.04</v>
       </c>
       <c r="C9" t="n">
-        <v>54.44</v>
+        <v>49.38</v>
       </c>
       <c r="D9" t="n">
-        <v>48.87</v>
+        <v>45.96</v>
       </c>
       <c r="E9" t="n">
-        <v>48.97</v>
+        <v>46.61</v>
       </c>
       <c r="F9" t="n">
-        <v>43.23</v>
+        <v>40.56</v>
       </c>
       <c r="G9" t="n">
-        <v>43.68</v>
+        <v>40.59</v>
       </c>
       <c r="H9" t="n">
-        <v>41.15</v>
+        <v>38.56</v>
       </c>
       <c r="I9" t="n">
-        <v>41.23</v>
+        <v>38.78</v>
       </c>
       <c r="J9" t="n">
-        <v>37.84</v>
+        <v>41.94</v>
       </c>
       <c r="K9" t="n">
-        <v>41.26</v>
+        <v>43.71</v>
       </c>
       <c r="L9" t="n">
-        <v>37.7</v>
+        <v>40.8</v>
       </c>
       <c r="M9" t="n">
-        <v>41.18</v>
+        <v>43.1</v>
       </c>
       <c r="N9" t="n">
-        <v>79.02</v>
+        <v>83.87</v>
       </c>
       <c r="O9" t="n">
-        <v>82.62</v>
+        <v>87.86</v>
       </c>
       <c r="P9" t="n">
-        <v>78.25</v>
+        <v>83.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>82.5</v>
+        <v>87.42</v>
       </c>
       <c r="R9" t="n">
-        <v>-14.148</v>
+        <v>-4.8193</v>
       </c>
       <c r="S9" t="n">
-        <v>-7.656</v>
+        <v>-15.1929</v>
       </c>
       <c r="T9" t="n">
-        <v>-10.7201</v>
+        <v>-8.858000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.1187</v>
+        <v>-5.9423</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.3408</v>
+        <v>-10.9488</v>
       </c>
       <c r="W9" t="n">
-        <v>-9.612299999999999</v>
+        <v>-9.832599999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>14.3254</v>
+        <v>4.6625</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.853</v>
+        <v>15.0561</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.8528</v>
+        <v>6.7831</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.1985</v>
+        <v>5.9636</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.3444</v>
+        <v>11.3602</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.5647</v>
+        <v>9.819800000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.04</v>
+        <v>47.86</v>
       </c>
       <c r="C10" t="n">
-        <v>49.38</v>
+        <v>48.29</v>
       </c>
       <c r="D10" t="n">
-        <v>45.96</v>
+        <v>39.52</v>
       </c>
       <c r="E10" t="n">
-        <v>46.61</v>
+        <v>40.62</v>
       </c>
       <c r="F10" t="n">
-        <v>40.56</v>
+        <v>39.75</v>
       </c>
       <c r="G10" t="n">
-        <v>40.59</v>
+        <v>39.91</v>
       </c>
       <c r="H10" t="n">
-        <v>38.56</v>
+        <v>37.32</v>
       </c>
       <c r="I10" t="n">
-        <v>38.78</v>
+        <v>37.89</v>
       </c>
       <c r="J10" t="n">
-        <v>41.94</v>
+        <v>42</v>
       </c>
       <c r="K10" t="n">
-        <v>43.71</v>
+        <v>49.76</v>
       </c>
       <c r="L10" t="n">
-        <v>40.8</v>
+        <v>41.57</v>
       </c>
       <c r="M10" t="n">
-        <v>43.1</v>
+        <v>48.74</v>
       </c>
       <c r="N10" t="n">
-        <v>83.87</v>
+        <v>85.27</v>
       </c>
       <c r="O10" t="n">
-        <v>87.86</v>
+        <v>90.72</v>
       </c>
       <c r="P10" t="n">
-        <v>83.78</v>
+        <v>84.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>87.42</v>
+        <v>89.42</v>
       </c>
       <c r="R10" t="n">
-        <v>-4.8193</v>
+        <v>-12.8513</v>
       </c>
       <c r="S10" t="n">
-        <v>-15.1929</v>
+        <v>-28.7868</v>
       </c>
       <c r="T10" t="n">
-        <v>-8.858000000000001</v>
+        <v>-23.4018</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.9423</v>
+        <v>-2.295</v>
       </c>
       <c r="V10" t="n">
-        <v>-10.9488</v>
+        <v>-14.6429</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.832599999999999</v>
+        <v>-14.847</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6625</v>
+        <v>13.0858</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.0561</v>
+        <v>35.3137</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.7831</v>
+        <v>25.286</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.9636</v>
+        <v>2.2878</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.3602</v>
+        <v>16.1902</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.819800000000001</v>
+        <v>16.3484</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47.86</v>
+        <v>42.88</v>
       </c>
       <c r="C11" t="n">
-        <v>48.29</v>
+        <v>48.18</v>
       </c>
       <c r="D11" t="n">
-        <v>39.52</v>
+        <v>42.61</v>
       </c>
       <c r="E11" t="n">
-        <v>40.62</v>
+        <v>47.91</v>
       </c>
       <c r="F11" t="n">
-        <v>39.75</v>
+        <v>39.09</v>
       </c>
       <c r="G11" t="n">
-        <v>39.91</v>
+        <v>42</v>
       </c>
       <c r="H11" t="n">
-        <v>37.32</v>
+        <v>39.07</v>
       </c>
       <c r="I11" t="n">
-        <v>37.89</v>
+        <v>41.68</v>
       </c>
       <c r="J11" t="n">
-        <v>42</v>
+        <v>45.87</v>
       </c>
       <c r="K11" t="n">
-        <v>49.76</v>
+        <v>46.38</v>
       </c>
       <c r="L11" t="n">
-        <v>41.57</v>
+        <v>39.61</v>
       </c>
       <c r="M11" t="n">
-        <v>48.74</v>
+        <v>39.86</v>
       </c>
       <c r="N11" t="n">
-        <v>85.27</v>
+        <v>86.62</v>
       </c>
       <c r="O11" t="n">
-        <v>90.72</v>
+        <v>86.66</v>
       </c>
       <c r="P11" t="n">
-        <v>84.89</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>89.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>-12.8513</v>
+        <v>17.9468</v>
       </c>
       <c r="S11" t="n">
-        <v>-28.7868</v>
+        <v>-2.1646</v>
       </c>
       <c r="T11" t="n">
-        <v>-23.4018</v>
+        <v>-12.8275</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.295</v>
+        <v>10.0026</v>
       </c>
       <c r="V11" t="n">
-        <v>-14.6429</v>
+        <v>1.0914</v>
       </c>
       <c r="W11" t="n">
-        <v>-14.847</v>
+        <v>-4.2895</v>
       </c>
       <c r="X11" t="n">
-        <v>13.0858</v>
+        <v>-18.2191</v>
       </c>
       <c r="Y11" t="n">
-        <v>35.3137</v>
+        <v>-3.2054</v>
       </c>
       <c r="Z11" t="n">
-        <v>25.286</v>
+        <v>6.4068</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2878</v>
+        <v>-9.986599999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>16.1902</v>
+        <v>-2.4364</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.3484</v>
+        <v>2.5324</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42.88</v>
+        <v>50.04</v>
       </c>
       <c r="C12" t="n">
-        <v>48.18</v>
+        <v>54.09</v>
       </c>
       <c r="D12" t="n">
-        <v>42.61</v>
+        <v>49.62</v>
       </c>
       <c r="E12" t="n">
-        <v>47.91</v>
+        <v>52.26</v>
       </c>
       <c r="F12" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="G12" t="n">
-        <v>42</v>
+        <v>43.98</v>
       </c>
       <c r="H12" t="n">
-        <v>39.07</v>
+        <v>42.41</v>
       </c>
       <c r="I12" t="n">
-        <v>41.68</v>
+        <v>43.23</v>
       </c>
       <c r="J12" t="n">
-        <v>45.87</v>
+        <v>38.07</v>
       </c>
       <c r="K12" t="n">
-        <v>46.38</v>
+        <v>38.49</v>
       </c>
       <c r="L12" t="n">
-        <v>39.61</v>
+        <v>34.78</v>
       </c>
       <c r="M12" t="n">
-        <v>39.86</v>
+        <v>36.26</v>
       </c>
       <c r="N12" t="n">
-        <v>86.62</v>
+        <v>78.62</v>
       </c>
       <c r="O12" t="n">
-        <v>86.66</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>79.73999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="Q12" t="n">
-        <v>80.48999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="R12" t="n">
-        <v>17.9468</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1646</v>
+        <v>12.1219</v>
       </c>
       <c r="T12" t="n">
-        <v>-12.8275</v>
+        <v>-8.380100000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>10.0026</v>
+        <v>3.7188</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0914</v>
+        <v>11.475</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.2895</v>
+        <v>-2.6132</v>
       </c>
       <c r="X12" t="n">
-        <v>-18.2191</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>-3.2054</v>
+        <v>-15.8701</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.4068</v>
+        <v>0.6663</v>
       </c>
       <c r="AA12" t="n">
-        <v>-9.986599999999999</v>
+        <v>-3.7769</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.4364</v>
+        <v>-11.4047</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5324</v>
+        <v>0.6367</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C13" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D13" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E13" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F13" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G13" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H13" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I13" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J13" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K13" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L13" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M13" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N13" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O13" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P13" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>9.079499999999999</v>
+        <v>0.9376</v>
       </c>
       <c r="S13" t="n">
-        <v>12.1219</v>
+        <v>29.8621</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.380100000000001</v>
+        <v>7.719</v>
       </c>
       <c r="U13" t="n">
-        <v>3.7188</v>
+        <v>0.2313</v>
       </c>
       <c r="V13" t="n">
-        <v>11.475</v>
+        <v>14.3574</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.6132</v>
+        <v>5.0934</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.031599999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y13" t="n">
-        <v>-15.8701</v>
+        <v>-26.2823</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.6663</v>
+        <v>-12.7489</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3.7769</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB13" t="n">
-        <v>-11.4047</v>
+        <v>-13.5652</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.6367</v>
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C14" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D14" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E14" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F14" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G14" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H14" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I14" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J14" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K14" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L14" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M14" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N14" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P14" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="S14" t="n">
-        <v>29.8621</v>
+        <v>14.402</v>
       </c>
       <c r="T14" t="n">
-        <v>7.719</v>
+        <v>17.5928</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="V14" t="n">
-        <v>14.3574</v>
+        <v>5.8061</v>
       </c>
       <c r="W14" t="n">
-        <v>5.0934</v>
+        <v>13.7184</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y14" t="n">
-        <v>-26.2823</v>
+        <v>-13.3216</v>
       </c>
       <c r="Z14" t="n">
-        <v>-12.7489</v>
+        <v>-19.8376</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB14" t="n">
-        <v>-13.5652</v>
+        <v>-5.6777</v>
       </c>
       <c r="AC14" t="n">
-        <v>-6.3152</v>
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C15" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D15" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E15" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F15" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G15" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H15" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I15" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J15" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K15" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L15" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M15" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N15" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O15" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P15" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R15" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="S15" t="n">
-        <v>14.402</v>
+        <v>8.209</v>
       </c>
       <c r="T15" t="n">
-        <v>17.5928</v>
+        <v>39.2171</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8061</v>
+        <v>2.1282</v>
       </c>
       <c r="W15" t="n">
-        <v>13.7184</v>
+        <v>16.5215</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y15" t="n">
-        <v>-13.3216</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z15" t="n">
-        <v>-19.8376</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB15" t="n">
-        <v>-5.6777</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC15" t="n">
-        <v>-13.1549</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C16" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D16" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E16" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F16" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G16" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H16" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I16" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J16" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K16" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L16" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M16" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N16" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P16" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S16" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="T16" t="n">
-        <v>39.2171</v>
+        <v>40.8892</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="W16" t="n">
-        <v>16.5215</v>
+        <v>15.1631</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y16" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z16" t="n">
-        <v>-31.4116</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC16" t="n">
-        <v>-15.1085</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C17" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D17" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E17" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F17" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G17" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H17" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I17" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J17" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K17" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L17" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M17" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N17" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P17" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R17" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S17" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="T17" t="n">
-        <v>40.8892</v>
+        <v>37.7344</v>
       </c>
       <c r="U17" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="W17" t="n">
-        <v>15.1631</v>
+        <v>13.2547</v>
       </c>
       <c r="X17" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y17" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z17" t="n">
-        <v>-32.3633</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA17" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB17" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC17" t="n">
-        <v>-14.0266</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C18" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D18" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E18" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F18" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G18" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H18" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I18" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J18" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K18" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L18" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M18" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N18" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O18" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P18" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R18" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S18" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T18" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V18" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W18" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X18" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y18" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z18" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB18" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC18" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C19" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E19" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F19" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G19" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H19" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I19" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J19" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K19" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L19" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M19" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N19" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O19" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P19" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S19" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T19" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V19" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W19" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X19" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y19" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z19" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB19" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC19" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C20" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F20" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G20" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H20" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I20" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J20" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K20" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L20" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M20" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N20" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O20" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R20" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S20" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T20" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U20" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W20" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X20" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y20" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z20" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB20" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC20" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C21" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D21" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G21" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H21" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I21" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J21" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K21" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L21" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M21" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N21" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O21" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P21" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R21" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S21" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T21" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U21" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V21" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W21" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y21" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z21" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA21" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB21" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC21" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>85.97499999999999</v>
+        <v>89.39</v>
       </c>
       <c r="D22" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E22" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F22" t="n">
-        <v>53.565</v>
+        <v>56.14</v>
       </c>
       <c r="G22" t="n">
-        <v>55.7382</v>
+        <v>56.92</v>
       </c>
       <c r="H22" t="n">
-        <v>53.33</v>
+        <v>55.095</v>
       </c>
       <c r="I22" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J22" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K22" t="n">
-        <v>22.425</v>
+        <v>21.5599</v>
       </c>
       <c r="L22" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M22" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N22" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O22" t="n">
-        <v>62.15</v>
+        <v>60.0582</v>
       </c>
       <c r="P22" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S22" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U22" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V22" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W22" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y22" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z22" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA22" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB22" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC22" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.03</v>
+        <v>49.53</v>
       </c>
       <c r="C2" t="n">
-        <v>56.48</v>
+        <v>56.11</v>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>48.5</v>
       </c>
       <c r="E2" t="n">
-        <v>54.02</v>
+        <v>54.85</v>
       </c>
       <c r="F2" t="n">
-        <v>47.6412</v>
+        <v>44.7959</v>
       </c>
       <c r="G2" t="n">
-        <v>48.0306</v>
+        <v>46.2435</v>
       </c>
       <c r="H2" t="n">
-        <v>45.974</v>
+        <v>44.2269</v>
       </c>
       <c r="I2" t="n">
-        <v>46.0239</v>
+        <v>45.6146</v>
       </c>
       <c r="J2" t="n">
-        <v>37.7515</v>
+        <v>41.6924</v>
       </c>
       <c r="K2" t="n">
-        <v>38.4563</v>
+        <v>42.4171</v>
       </c>
       <c r="L2" t="n">
-        <v>36.739</v>
+        <v>36.9574</v>
       </c>
       <c r="M2" t="n">
-        <v>38.4166</v>
+        <v>37.8309</v>
       </c>
       <c r="N2" t="n">
-        <v>72.233</v>
+        <v>76.657</v>
       </c>
       <c r="O2" t="n">
-        <v>74.7029</v>
+        <v>77.55970000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>71.6675</v>
+        <v>74.27630000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>74.6037</v>
+        <v>75.298</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49.53</v>
+        <v>54.69</v>
       </c>
       <c r="C3" t="n">
-        <v>56.11</v>
+        <v>55.36</v>
       </c>
       <c r="D3" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>54.85</v>
+        <v>51.14</v>
       </c>
       <c r="F3" t="n">
-        <v>44.7959</v>
+        <v>45.1054</v>
       </c>
       <c r="G3" t="n">
-        <v>46.2435</v>
+        <v>45.1354</v>
       </c>
       <c r="H3" t="n">
-        <v>44.2269</v>
+        <v>42.2302</v>
       </c>
       <c r="I3" t="n">
-        <v>45.6146</v>
+        <v>43.0089</v>
       </c>
       <c r="J3" t="n">
-        <v>41.6924</v>
+        <v>38.0394</v>
       </c>
       <c r="K3" t="n">
-        <v>42.4171</v>
+        <v>41.9505</v>
       </c>
       <c r="L3" t="n">
-        <v>36.9574</v>
+        <v>37.4934</v>
       </c>
       <c r="M3" t="n">
-        <v>37.8309</v>
+        <v>40.3622</v>
       </c>
       <c r="N3" t="n">
-        <v>76.657</v>
+        <v>76.1511</v>
       </c>
       <c r="O3" t="n">
-        <v>77.55970000000001</v>
+        <v>80.93219999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>74.27630000000001</v>
+        <v>76.1412</v>
       </c>
       <c r="Q3" t="n">
-        <v>75.298</v>
+        <v>79.6031</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5365</v>
+        <v>-6.7639</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8893</v>
+        <v>-5.7124</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5246</v>
+        <v>6.6911</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9307</v>
+        <v>5.7174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.69</v>
+        <v>54.63</v>
       </c>
       <c r="C4" t="n">
-        <v>55.36</v>
+        <v>56.81</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>52.28</v>
       </c>
       <c r="E4" t="n">
-        <v>51.14</v>
+        <v>53.03</v>
       </c>
       <c r="F4" t="n">
-        <v>45.1054</v>
+        <v>45.0355</v>
       </c>
       <c r="G4" t="n">
-        <v>45.1354</v>
+        <v>46.0738</v>
       </c>
       <c r="H4" t="n">
-        <v>42.2302</v>
+        <v>44.0572</v>
       </c>
       <c r="I4" t="n">
-        <v>43.0089</v>
+        <v>44.4964</v>
       </c>
       <c r="J4" t="n">
-        <v>38.0394</v>
+        <v>37.7316</v>
       </c>
       <c r="K4" t="n">
-        <v>41.9505</v>
+        <v>39.4986</v>
       </c>
       <c r="L4" t="n">
-        <v>37.4934</v>
+        <v>35.9547</v>
       </c>
       <c r="M4" t="n">
-        <v>40.3622</v>
+        <v>38.903</v>
       </c>
       <c r="N4" t="n">
-        <v>76.1511</v>
+        <v>75.8734</v>
       </c>
       <c r="O4" t="n">
-        <v>80.93219999999999</v>
+        <v>77.6985</v>
       </c>
       <c r="P4" t="n">
-        <v>76.1412</v>
+        <v>73.9589</v>
       </c>
       <c r="Q4" t="n">
-        <v>79.6031</v>
+        <v>76.8554</v>
       </c>
       <c r="R4" t="n">
-        <v>-6.7639</v>
+        <v>3.6957</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.7124</v>
+        <v>3.4586</v>
       </c>
       <c r="X4" t="n">
-        <v>6.6911</v>
+        <v>-3.6153</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.7174</v>
+        <v>-3.4517</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.63</v>
+        <v>51.54</v>
       </c>
       <c r="C5" t="n">
-        <v>56.81</v>
+        <v>56.09</v>
       </c>
       <c r="D5" t="n">
-        <v>52.28</v>
+        <v>51.54</v>
       </c>
       <c r="E5" t="n">
-        <v>53.03</v>
+        <v>54.96</v>
       </c>
       <c r="F5" t="n">
-        <v>45.0355</v>
+        <v>43.7676</v>
       </c>
       <c r="G5" t="n">
-        <v>46.0738</v>
+        <v>44.4765</v>
       </c>
       <c r="H5" t="n">
-        <v>44.0572</v>
+        <v>43.1187</v>
       </c>
       <c r="I5" t="n">
-        <v>44.4964</v>
+        <v>43.548</v>
       </c>
       <c r="J5" t="n">
-        <v>37.7316</v>
+        <v>40.08</v>
       </c>
       <c r="K5" t="n">
-        <v>39.4986</v>
+        <v>40.08</v>
       </c>
       <c r="L5" t="n">
-        <v>35.9547</v>
+        <v>36.7</v>
       </c>
       <c r="M5" t="n">
-        <v>38.903</v>
+        <v>37.46</v>
       </c>
       <c r="N5" t="n">
-        <v>75.8734</v>
+        <v>78.15479999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>77.6985</v>
+        <v>79.2559</v>
       </c>
       <c r="P5" t="n">
-        <v>73.9589</v>
+        <v>76.9248</v>
       </c>
       <c r="Q5" t="n">
-        <v>76.8554</v>
+        <v>78.502</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6957</v>
+        <v>3.6394</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8327</v>
+        <v>0.2005</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4586</v>
+        <v>-2.1314</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.3189</v>
+        <v>-4.5306</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.6153</v>
+        <v>-3.7092</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2661</v>
+        <v>-0.9804</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.4517</v>
+        <v>2.1425</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.0182</v>
+        <v>4.2551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.54</v>
+        <v>56.64</v>
       </c>
       <c r="C6" t="n">
-        <v>56.09</v>
+        <v>58.25</v>
       </c>
       <c r="D6" t="n">
-        <v>51.54</v>
+        <v>55.59</v>
       </c>
       <c r="E6" t="n">
-        <v>54.96</v>
+        <v>57.04</v>
       </c>
       <c r="F6" t="n">
-        <v>43.7676</v>
+        <v>44.7</v>
       </c>
       <c r="G6" t="n">
-        <v>44.4765</v>
+        <v>45.22</v>
       </c>
       <c r="H6" t="n">
-        <v>43.1187</v>
+        <v>43.95</v>
       </c>
       <c r="I6" t="n">
-        <v>43.548</v>
+        <v>44.39</v>
       </c>
       <c r="J6" t="n">
-        <v>40.08</v>
+        <v>36.32</v>
       </c>
       <c r="K6" t="n">
-        <v>40.08</v>
+        <v>37.06</v>
       </c>
       <c r="L6" t="n">
-        <v>36.7</v>
+        <v>35.23</v>
       </c>
       <c r="M6" t="n">
-        <v>37.46</v>
+        <v>36.02</v>
       </c>
       <c r="N6" t="n">
-        <v>78.15479999999999</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>79.2559</v>
+        <v>77.8</v>
       </c>
       <c r="P6" t="n">
-        <v>76.9248</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>78.502</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6394</v>
+        <v>3.7846</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2005</v>
+        <v>11.537</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.1314</v>
+        <v>1.9335</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.5306</v>
+        <v>3.2112</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.7092</v>
+        <v>-3.8441</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.9804</v>
+        <v>-10.7581</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1425</v>
+        <v>-1.9643</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.2551</v>
+        <v>-3.3203</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56.64</v>
+        <v>54.19</v>
       </c>
       <c r="C7" t="n">
-        <v>58.25</v>
+        <v>54.44</v>
       </c>
       <c r="D7" t="n">
-        <v>55.59</v>
+        <v>48.87</v>
       </c>
       <c r="E7" t="n">
-        <v>57.04</v>
+        <v>48.97</v>
       </c>
       <c r="F7" t="n">
-        <v>44.7</v>
+        <v>43.23</v>
       </c>
       <c r="G7" t="n">
-        <v>45.22</v>
+        <v>43.68</v>
       </c>
       <c r="H7" t="n">
-        <v>43.95</v>
+        <v>41.15</v>
       </c>
       <c r="I7" t="n">
-        <v>44.39</v>
+        <v>41.23</v>
       </c>
       <c r="J7" t="n">
-        <v>36.32</v>
+        <v>37.84</v>
       </c>
       <c r="K7" t="n">
-        <v>37.06</v>
+        <v>41.26</v>
       </c>
       <c r="L7" t="n">
-        <v>35.23</v>
+        <v>37.7</v>
       </c>
       <c r="M7" t="n">
-        <v>36.02</v>
+        <v>41.18</v>
       </c>
       <c r="N7" t="n">
-        <v>76.43000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="O7" t="n">
-        <v>77.8</v>
+        <v>82.62</v>
       </c>
       <c r="P7" t="n">
-        <v>75.51000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>76.95999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7846</v>
+        <v>-14.148</v>
       </c>
       <c r="S7" t="n">
-        <v>11.537</v>
+        <v>-7.656</v>
       </c>
       <c r="T7" t="n">
-        <v>5.5905</v>
+        <v>-10.7201</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9335</v>
+        <v>-7.1187</v>
       </c>
       <c r="V7" t="n">
-        <v>3.2112</v>
+        <v>-7.3408</v>
       </c>
       <c r="W7" t="n">
-        <v>-3.5501</v>
+        <v>-9.612299999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.8441</v>
+        <v>14.3254</v>
       </c>
       <c r="Y7" t="n">
-        <v>-10.7581</v>
+        <v>5.853</v>
       </c>
       <c r="Z7" t="n">
-        <v>-6.2384</v>
+        <v>8.8528</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.9643</v>
+        <v>7.1985</v>
       </c>
       <c r="AB7" t="n">
-        <v>-3.3203</v>
+        <v>7.3444</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1584</v>
+        <v>9.5647</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54.19</v>
+        <v>48.04</v>
       </c>
       <c r="C8" t="n">
-        <v>54.44</v>
+        <v>49.38</v>
       </c>
       <c r="D8" t="n">
-        <v>48.87</v>
+        <v>45.96</v>
       </c>
       <c r="E8" t="n">
-        <v>48.97</v>
+        <v>46.61</v>
       </c>
       <c r="F8" t="n">
-        <v>43.23</v>
+        <v>40.56</v>
       </c>
       <c r="G8" t="n">
-        <v>43.68</v>
+        <v>40.59</v>
       </c>
       <c r="H8" t="n">
-        <v>41.15</v>
+        <v>38.56</v>
       </c>
       <c r="I8" t="n">
-        <v>41.23</v>
+        <v>38.78</v>
       </c>
       <c r="J8" t="n">
-        <v>37.84</v>
+        <v>41.94</v>
       </c>
       <c r="K8" t="n">
-        <v>41.26</v>
+        <v>43.71</v>
       </c>
       <c r="L8" t="n">
-        <v>37.7</v>
+        <v>40.8</v>
       </c>
       <c r="M8" t="n">
-        <v>41.18</v>
+        <v>43.1</v>
       </c>
       <c r="N8" t="n">
-        <v>79.02</v>
+        <v>83.87</v>
       </c>
       <c r="O8" t="n">
-        <v>82.62</v>
+        <v>87.86</v>
       </c>
       <c r="P8" t="n">
-        <v>78.25</v>
+        <v>83.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>82.5</v>
+        <v>87.42</v>
       </c>
       <c r="R8" t="n">
-        <v>-14.148</v>
+        <v>-4.8193</v>
       </c>
       <c r="S8" t="n">
-        <v>-7.656</v>
+        <v>-15.1929</v>
       </c>
       <c r="T8" t="n">
-        <v>-10.7201</v>
+        <v>-8.858000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-7.1187</v>
+        <v>-5.9423</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.3408</v>
+        <v>-10.9488</v>
       </c>
       <c r="W8" t="n">
-        <v>-9.612299999999999</v>
+        <v>-9.832599999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>14.3254</v>
+        <v>4.6625</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.853</v>
+        <v>15.0561</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.8528</v>
+        <v>6.7831</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.1985</v>
+        <v>5.9636</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.3444</v>
+        <v>11.3602</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.5647</v>
+        <v>9.819800000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48.04</v>
+        <v>47.86</v>
       </c>
       <c r="C9" t="n">
-        <v>49.38</v>
+        <v>48.29</v>
       </c>
       <c r="D9" t="n">
-        <v>45.96</v>
+        <v>39.52</v>
       </c>
       <c r="E9" t="n">
-        <v>46.61</v>
+        <v>40.62</v>
       </c>
       <c r="F9" t="n">
-        <v>40.56</v>
+        <v>39.75</v>
       </c>
       <c r="G9" t="n">
-        <v>40.59</v>
+        <v>39.91</v>
       </c>
       <c r="H9" t="n">
-        <v>38.56</v>
+        <v>37.32</v>
       </c>
       <c r="I9" t="n">
-        <v>38.78</v>
+        <v>37.89</v>
       </c>
       <c r="J9" t="n">
-        <v>41.94</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>43.71</v>
+        <v>49.76</v>
       </c>
       <c r="L9" t="n">
-        <v>40.8</v>
+        <v>41.57</v>
       </c>
       <c r="M9" t="n">
-        <v>43.1</v>
+        <v>48.74</v>
       </c>
       <c r="N9" t="n">
-        <v>83.87</v>
+        <v>85.27</v>
       </c>
       <c r="O9" t="n">
-        <v>87.86</v>
+        <v>90.72</v>
       </c>
       <c r="P9" t="n">
-        <v>83.78</v>
+        <v>84.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>87.42</v>
+        <v>89.42</v>
       </c>
       <c r="R9" t="n">
-        <v>-4.8193</v>
+        <v>-12.8513</v>
       </c>
       <c r="S9" t="n">
-        <v>-15.1929</v>
+        <v>-28.7868</v>
       </c>
       <c r="T9" t="n">
-        <v>-8.858000000000001</v>
+        <v>-23.4018</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.9423</v>
+        <v>-2.295</v>
       </c>
       <c r="V9" t="n">
-        <v>-10.9488</v>
+        <v>-14.6429</v>
       </c>
       <c r="W9" t="n">
-        <v>-9.832599999999999</v>
+        <v>-14.847</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6625</v>
+        <v>13.0858</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.0561</v>
+        <v>35.3137</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.7831</v>
+        <v>25.286</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.9636</v>
+        <v>2.2878</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.3602</v>
+        <v>16.1902</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.819800000000001</v>
+        <v>16.3484</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47.86</v>
+        <v>42.88</v>
       </c>
       <c r="C10" t="n">
-        <v>48.29</v>
+        <v>48.18</v>
       </c>
       <c r="D10" t="n">
-        <v>39.52</v>
+        <v>42.61</v>
       </c>
       <c r="E10" t="n">
-        <v>40.62</v>
+        <v>47.91</v>
       </c>
       <c r="F10" t="n">
-        <v>39.75</v>
+        <v>39.09</v>
       </c>
       <c r="G10" t="n">
-        <v>39.91</v>
+        <v>42</v>
       </c>
       <c r="H10" t="n">
-        <v>37.32</v>
+        <v>39.07</v>
       </c>
       <c r="I10" t="n">
-        <v>37.89</v>
+        <v>41.68</v>
       </c>
       <c r="J10" t="n">
-        <v>42</v>
+        <v>45.87</v>
       </c>
       <c r="K10" t="n">
-        <v>49.76</v>
+        <v>46.38</v>
       </c>
       <c r="L10" t="n">
-        <v>41.57</v>
+        <v>39.61</v>
       </c>
       <c r="M10" t="n">
-        <v>48.74</v>
+        <v>39.86</v>
       </c>
       <c r="N10" t="n">
-        <v>85.27</v>
+        <v>86.62</v>
       </c>
       <c r="O10" t="n">
-        <v>90.72</v>
+        <v>86.66</v>
       </c>
       <c r="P10" t="n">
-        <v>84.89</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>89.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>-12.8513</v>
+        <v>17.9468</v>
       </c>
       <c r="S10" t="n">
-        <v>-28.7868</v>
+        <v>-2.1646</v>
       </c>
       <c r="T10" t="n">
-        <v>-23.4018</v>
+        <v>-12.8275</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.295</v>
+        <v>10.0026</v>
       </c>
       <c r="V10" t="n">
-        <v>-14.6429</v>
+        <v>1.0914</v>
       </c>
       <c r="W10" t="n">
-        <v>-14.847</v>
+        <v>-4.2895</v>
       </c>
       <c r="X10" t="n">
-        <v>13.0858</v>
+        <v>-18.2191</v>
       </c>
       <c r="Y10" t="n">
-        <v>35.3137</v>
+        <v>-3.2054</v>
       </c>
       <c r="Z10" t="n">
-        <v>25.286</v>
+        <v>6.4068</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2878</v>
+        <v>-9.986599999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.1902</v>
+        <v>-2.4364</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.3484</v>
+        <v>2.5324</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42.88</v>
+        <v>50.04</v>
       </c>
       <c r="C11" t="n">
-        <v>48.18</v>
+        <v>54.09</v>
       </c>
       <c r="D11" t="n">
-        <v>42.61</v>
+        <v>49.62</v>
       </c>
       <c r="E11" t="n">
-        <v>47.91</v>
+        <v>52.26</v>
       </c>
       <c r="F11" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>43.98</v>
       </c>
       <c r="H11" t="n">
-        <v>39.07</v>
+        <v>42.41</v>
       </c>
       <c r="I11" t="n">
-        <v>41.68</v>
+        <v>43.23</v>
       </c>
       <c r="J11" t="n">
-        <v>45.87</v>
+        <v>38.07</v>
       </c>
       <c r="K11" t="n">
-        <v>46.38</v>
+        <v>38.49</v>
       </c>
       <c r="L11" t="n">
-        <v>39.61</v>
+        <v>34.78</v>
       </c>
       <c r="M11" t="n">
-        <v>39.86</v>
+        <v>36.26</v>
       </c>
       <c r="N11" t="n">
-        <v>86.62</v>
+        <v>78.62</v>
       </c>
       <c r="O11" t="n">
-        <v>86.66</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>79.73999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>80.48999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="R11" t="n">
-        <v>17.9468</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1646</v>
+        <v>12.1219</v>
       </c>
       <c r="T11" t="n">
-        <v>-12.8275</v>
+        <v>-8.380100000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>10.0026</v>
+        <v>3.7188</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0914</v>
+        <v>11.475</v>
       </c>
       <c r="W11" t="n">
-        <v>-4.2895</v>
+        <v>-2.6132</v>
       </c>
       <c r="X11" t="n">
-        <v>-18.2191</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>-3.2054</v>
+        <v>-15.8701</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.4068</v>
+        <v>0.6663</v>
       </c>
       <c r="AA11" t="n">
-        <v>-9.986599999999999</v>
+        <v>-3.7769</v>
       </c>
       <c r="AB11" t="n">
-        <v>-2.4364</v>
+        <v>-11.4047</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5324</v>
+        <v>0.6367</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C12" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D12" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E12" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F12" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G12" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H12" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I12" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J12" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K12" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L12" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M12" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N12" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O12" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P12" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>9.079499999999999</v>
+        <v>0.9376</v>
       </c>
       <c r="S12" t="n">
-        <v>12.1219</v>
+        <v>29.8621</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.380100000000001</v>
+        <v>7.719</v>
       </c>
       <c r="U12" t="n">
-        <v>3.7188</v>
+        <v>0.2313</v>
       </c>
       <c r="V12" t="n">
-        <v>11.475</v>
+        <v>14.3574</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.6132</v>
+        <v>5.0934</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.031599999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y12" t="n">
-        <v>-15.8701</v>
+        <v>-26.2823</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.6663</v>
+        <v>-12.7489</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3.7769</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB12" t="n">
-        <v>-11.4047</v>
+        <v>-13.5652</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.6367</v>
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C13" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D13" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E13" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F13" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G13" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H13" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I13" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J13" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K13" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L13" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M13" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N13" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P13" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="S13" t="n">
-        <v>29.8621</v>
+        <v>14.402</v>
       </c>
       <c r="T13" t="n">
-        <v>7.719</v>
+        <v>17.5928</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="V13" t="n">
-        <v>14.3574</v>
+        <v>5.8061</v>
       </c>
       <c r="W13" t="n">
-        <v>5.0934</v>
+        <v>13.7184</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y13" t="n">
-        <v>-26.2823</v>
+        <v>-13.3216</v>
       </c>
       <c r="Z13" t="n">
-        <v>-12.7489</v>
+        <v>-19.8376</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB13" t="n">
-        <v>-13.5652</v>
+        <v>-5.6777</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.3152</v>
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C14" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D14" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E14" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F14" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G14" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H14" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I14" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J14" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K14" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L14" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M14" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N14" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O14" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P14" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="S14" t="n">
-        <v>14.402</v>
+        <v>8.209</v>
       </c>
       <c r="T14" t="n">
-        <v>17.5928</v>
+        <v>39.2171</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8061</v>
+        <v>2.1282</v>
       </c>
       <c r="W14" t="n">
-        <v>13.7184</v>
+        <v>16.5215</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y14" t="n">
-        <v>-13.3216</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z14" t="n">
-        <v>-19.8376</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB14" t="n">
-        <v>-5.6777</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC14" t="n">
-        <v>-13.1549</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C15" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D15" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E15" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F15" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G15" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H15" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I15" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J15" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K15" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L15" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M15" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N15" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P15" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S15" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="T15" t="n">
-        <v>39.2171</v>
+        <v>40.8892</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="W15" t="n">
-        <v>16.5215</v>
+        <v>15.1631</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y15" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z15" t="n">
-        <v>-31.4116</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC15" t="n">
-        <v>-15.1085</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C16" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D16" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E16" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F16" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G16" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H16" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I16" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J16" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K16" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L16" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M16" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N16" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P16" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R16" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S16" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="T16" t="n">
-        <v>40.8892</v>
+        <v>37.7344</v>
       </c>
       <c r="U16" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="W16" t="n">
-        <v>15.1631</v>
+        <v>13.2547</v>
       </c>
       <c r="X16" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y16" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z16" t="n">
-        <v>-32.3633</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA16" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB16" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC16" t="n">
-        <v>-14.0266</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C17" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D17" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E17" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F17" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G17" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H17" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I17" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J17" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K17" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L17" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M17" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N17" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O17" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P17" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R17" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S17" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T17" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V17" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W17" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y17" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z17" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB17" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC17" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C18" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E18" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F18" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G18" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H18" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I18" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J18" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K18" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L18" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M18" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N18" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O18" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P18" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S18" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T18" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V18" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W18" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y18" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z18" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB18" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC18" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C19" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F19" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G19" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H19" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I19" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J19" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K19" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L19" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M19" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N19" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O19" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R19" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S19" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T19" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U19" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W19" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X19" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y19" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z19" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA19" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB19" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC19" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C20" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D20" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G20" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H20" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I20" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J20" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K20" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L20" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M20" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N20" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O20" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P20" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R20" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S20" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T20" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U20" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V20" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W20" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X20" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y20" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z20" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA20" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB20" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC20" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D21" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E21" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F21" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G21" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H21" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I21" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J21" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K21" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L21" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M21" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N21" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O21" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P21" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S21" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U21" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V21" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W21" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y21" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z21" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA21" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB21" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC21" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.01000000000001</v>
+        <v>93.19499999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>89.39</v>
+        <v>94.745</v>
       </c>
       <c r="D22" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E22" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>56.14</v>
+        <v>57.78</v>
       </c>
       <c r="G22" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H22" t="n">
-        <v>55.095</v>
+        <v>57.3699</v>
       </c>
       <c r="I22" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J22" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K22" t="n">
-        <v>21.5599</v>
+        <v>19.8</v>
       </c>
       <c r="L22" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M22" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N22" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O22" t="n">
-        <v>60.0582</v>
+        <v>57.6696</v>
       </c>
       <c r="P22" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S22" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T22" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V22" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y22" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z22" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA22" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB22" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC22" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24759,1804 +24759,1713 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.53</v>
+        <v>54.63</v>
       </c>
       <c r="C2" t="n">
-        <v>56.11</v>
+        <v>56.81</v>
       </c>
       <c r="D2" t="n">
-        <v>48.5</v>
+        <v>52.28</v>
       </c>
       <c r="E2" t="n">
-        <v>54.85</v>
+        <v>53.03</v>
       </c>
       <c r="F2" t="n">
-        <v>44.7959</v>
+        <v>45.0355</v>
       </c>
       <c r="G2" t="n">
-        <v>46.2435</v>
+        <v>46.0738</v>
       </c>
       <c r="H2" t="n">
-        <v>44.2269</v>
+        <v>44.0572</v>
       </c>
       <c r="I2" t="n">
-        <v>45.6146</v>
+        <v>44.4964</v>
       </c>
       <c r="J2" t="n">
-        <v>41.6924</v>
+        <v>37.7316</v>
       </c>
       <c r="K2" t="n">
-        <v>42.4171</v>
+        <v>39.4986</v>
       </c>
       <c r="L2" t="n">
-        <v>36.9574</v>
+        <v>35.9547</v>
       </c>
       <c r="M2" t="n">
-        <v>37.8309</v>
+        <v>38.903</v>
       </c>
       <c r="N2" t="n">
-        <v>76.657</v>
+        <v>75.8734</v>
       </c>
       <c r="O2" t="n">
-        <v>77.55970000000001</v>
+        <v>77.6985</v>
       </c>
       <c r="P2" t="n">
-        <v>74.27630000000001</v>
+        <v>73.9589</v>
       </c>
       <c r="Q2" t="n">
-        <v>75.298</v>
+        <v>76.8554</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.69</v>
+        <v>51.54</v>
       </c>
       <c r="C3" t="n">
-        <v>55.36</v>
+        <v>56.09</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>51.54</v>
       </c>
       <c r="E3" t="n">
-        <v>51.14</v>
+        <v>54.96</v>
       </c>
       <c r="F3" t="n">
-        <v>45.1054</v>
+        <v>43.7676</v>
       </c>
       <c r="G3" t="n">
-        <v>45.1354</v>
+        <v>44.4765</v>
       </c>
       <c r="H3" t="n">
-        <v>42.2302</v>
+        <v>43.1187</v>
       </c>
       <c r="I3" t="n">
-        <v>43.0089</v>
+        <v>43.548</v>
       </c>
       <c r="J3" t="n">
-        <v>38.0394</v>
+        <v>40.08</v>
       </c>
       <c r="K3" t="n">
-        <v>41.9505</v>
+        <v>40.08</v>
       </c>
       <c r="L3" t="n">
-        <v>37.4934</v>
+        <v>36.7</v>
       </c>
       <c r="M3" t="n">
-        <v>40.3622</v>
+        <v>37.46</v>
       </c>
       <c r="N3" t="n">
-        <v>76.1511</v>
+        <v>78.15479999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>80.93219999999999</v>
+        <v>79.2559</v>
       </c>
       <c r="P3" t="n">
-        <v>76.1412</v>
+        <v>76.9248</v>
       </c>
       <c r="Q3" t="n">
-        <v>79.6031</v>
+        <v>78.502</v>
       </c>
       <c r="R3" t="n">
-        <v>-6.7639</v>
+        <v>3.6394</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.7124</v>
+        <v>-2.1314</v>
       </c>
       <c r="X3" t="n">
-        <v>6.6911</v>
+        <v>-3.7092</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.7174</v>
+        <v>2.1425</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.63</v>
+        <v>56.64</v>
       </c>
       <c r="C4" t="n">
-        <v>56.81</v>
+        <v>58.25</v>
       </c>
       <c r="D4" t="n">
-        <v>52.28</v>
+        <v>55.59</v>
       </c>
       <c r="E4" t="n">
-        <v>53.03</v>
+        <v>57.04</v>
       </c>
       <c r="F4" t="n">
-        <v>45.0355</v>
+        <v>44.7</v>
       </c>
       <c r="G4" t="n">
-        <v>46.0738</v>
+        <v>45.22</v>
       </c>
       <c r="H4" t="n">
-        <v>44.0572</v>
+        <v>43.95</v>
       </c>
       <c r="I4" t="n">
-        <v>44.4964</v>
+        <v>44.39</v>
       </c>
       <c r="J4" t="n">
-        <v>37.7316</v>
+        <v>36.32</v>
       </c>
       <c r="K4" t="n">
-        <v>39.4986</v>
+        <v>37.06</v>
       </c>
       <c r="L4" t="n">
-        <v>35.9547</v>
+        <v>35.23</v>
       </c>
       <c r="M4" t="n">
-        <v>38.903</v>
+        <v>36.02</v>
       </c>
       <c r="N4" t="n">
-        <v>75.8734</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>77.6985</v>
+        <v>77.8</v>
       </c>
       <c r="P4" t="n">
-        <v>73.9589</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>76.8554</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6957</v>
+        <v>3.7846</v>
       </c>
       <c r="U4" t="n">
-        <v>3.4586</v>
+        <v>1.9335</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.6153</v>
+        <v>-3.8441</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3.4517</v>
+        <v>-1.9643</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.54</v>
+        <v>54.19</v>
       </c>
       <c r="C5" t="n">
-        <v>56.09</v>
+        <v>54.44</v>
       </c>
       <c r="D5" t="n">
-        <v>51.54</v>
+        <v>48.87</v>
       </c>
       <c r="E5" t="n">
-        <v>54.96</v>
+        <v>48.97</v>
       </c>
       <c r="F5" t="n">
-        <v>43.7676</v>
+        <v>43.23</v>
       </c>
       <c r="G5" t="n">
-        <v>44.4765</v>
+        <v>43.68</v>
       </c>
       <c r="H5" t="n">
-        <v>43.1187</v>
+        <v>41.15</v>
       </c>
       <c r="I5" t="n">
-        <v>43.548</v>
+        <v>41.23</v>
       </c>
       <c r="J5" t="n">
-        <v>40.08</v>
+        <v>37.84</v>
       </c>
       <c r="K5" t="n">
-        <v>40.08</v>
+        <v>41.26</v>
       </c>
       <c r="L5" t="n">
-        <v>36.7</v>
+        <v>37.7</v>
       </c>
       <c r="M5" t="n">
-        <v>37.46</v>
+        <v>41.18</v>
       </c>
       <c r="N5" t="n">
-        <v>78.15479999999999</v>
+        <v>79.02</v>
       </c>
       <c r="O5" t="n">
-        <v>79.2559</v>
+        <v>82.62</v>
       </c>
       <c r="P5" t="n">
-        <v>76.9248</v>
+        <v>78.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>78.502</v>
+        <v>82.5</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6394</v>
+        <v>-14.148</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2005</v>
+        <v>-7.656</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.1314</v>
+        <v>-7.1187</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.5306</v>
+        <v>-7.3408</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.7092</v>
+        <v>14.3254</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.9804</v>
+        <v>5.853</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1425</v>
+        <v>7.1985</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.2551</v>
+        <v>7.3444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56.64</v>
+        <v>48.04</v>
       </c>
       <c r="C6" t="n">
-        <v>58.25</v>
+        <v>49.38</v>
       </c>
       <c r="D6" t="n">
-        <v>55.59</v>
+        <v>45.96</v>
       </c>
       <c r="E6" t="n">
-        <v>57.04</v>
+        <v>46.61</v>
       </c>
       <c r="F6" t="n">
-        <v>44.7</v>
+        <v>40.56</v>
       </c>
       <c r="G6" t="n">
-        <v>45.22</v>
+        <v>40.59</v>
       </c>
       <c r="H6" t="n">
-        <v>43.95</v>
+        <v>38.56</v>
       </c>
       <c r="I6" t="n">
-        <v>44.39</v>
+        <v>38.78</v>
       </c>
       <c r="J6" t="n">
-        <v>36.32</v>
+        <v>41.94</v>
       </c>
       <c r="K6" t="n">
-        <v>37.06</v>
+        <v>43.71</v>
       </c>
       <c r="L6" t="n">
-        <v>35.23</v>
+        <v>40.8</v>
       </c>
       <c r="M6" t="n">
-        <v>36.02</v>
+        <v>43.1</v>
       </c>
       <c r="N6" t="n">
-        <v>76.43000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="O6" t="n">
-        <v>77.8</v>
+        <v>87.86</v>
       </c>
       <c r="P6" t="n">
-        <v>75.51000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>76.95999999999999</v>
+        <v>87.42</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7846</v>
+        <v>-4.8193</v>
       </c>
       <c r="S6" t="n">
-        <v>11.537</v>
+        <v>-15.1929</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9335</v>
+        <v>-5.9423</v>
       </c>
       <c r="V6" t="n">
-        <v>3.2112</v>
+        <v>-10.9488</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.8441</v>
+        <v>4.6625</v>
       </c>
       <c r="Y6" t="n">
-        <v>-10.7581</v>
+        <v>15.0561</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.9643</v>
+        <v>5.9636</v>
       </c>
       <c r="AB6" t="n">
-        <v>-3.3203</v>
+        <v>11.3602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54.19</v>
+        <v>47.86</v>
       </c>
       <c r="C7" t="n">
-        <v>54.44</v>
+        <v>48.29</v>
       </c>
       <c r="D7" t="n">
-        <v>48.87</v>
+        <v>39.52</v>
       </c>
       <c r="E7" t="n">
-        <v>48.97</v>
+        <v>40.62</v>
       </c>
       <c r="F7" t="n">
-        <v>43.23</v>
+        <v>39.75</v>
       </c>
       <c r="G7" t="n">
-        <v>43.68</v>
+        <v>39.91</v>
       </c>
       <c r="H7" t="n">
-        <v>41.15</v>
+        <v>37.32</v>
       </c>
       <c r="I7" t="n">
-        <v>41.23</v>
+        <v>37.89</v>
       </c>
       <c r="J7" t="n">
-        <v>37.84</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
-        <v>41.26</v>
+        <v>49.76</v>
       </c>
       <c r="L7" t="n">
-        <v>37.7</v>
+        <v>41.57</v>
       </c>
       <c r="M7" t="n">
-        <v>41.18</v>
+        <v>48.74</v>
       </c>
       <c r="N7" t="n">
-        <v>79.02</v>
+        <v>85.27</v>
       </c>
       <c r="O7" t="n">
-        <v>82.62</v>
+        <v>90.72</v>
       </c>
       <c r="P7" t="n">
-        <v>78.25</v>
+        <v>84.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>82.5</v>
+        <v>89.42</v>
       </c>
       <c r="R7" t="n">
-        <v>-14.148</v>
+        <v>-12.8513</v>
       </c>
       <c r="S7" t="n">
-        <v>-7.656</v>
+        <v>-28.7868</v>
       </c>
       <c r="T7" t="n">
-        <v>-10.7201</v>
+        <v>-23.4018</v>
       </c>
       <c r="U7" t="n">
-        <v>-7.1187</v>
+        <v>-2.295</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.3408</v>
+        <v>-14.6429</v>
       </c>
       <c r="W7" t="n">
-        <v>-9.612299999999999</v>
+        <v>-14.847</v>
       </c>
       <c r="X7" t="n">
-        <v>14.3254</v>
+        <v>13.0858</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.853</v>
+        <v>35.3137</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.8528</v>
+        <v>25.286</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.1985</v>
+        <v>2.2878</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.3444</v>
+        <v>16.1902</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.5647</v>
+        <v>16.3484</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48.04</v>
+        <v>42.88</v>
       </c>
       <c r="C8" t="n">
-        <v>49.38</v>
+        <v>48.18</v>
       </c>
       <c r="D8" t="n">
-        <v>45.96</v>
+        <v>42.61</v>
       </c>
       <c r="E8" t="n">
-        <v>46.61</v>
+        <v>47.91</v>
       </c>
       <c r="F8" t="n">
-        <v>40.56</v>
+        <v>39.09</v>
       </c>
       <c r="G8" t="n">
-        <v>40.59</v>
+        <v>42</v>
       </c>
       <c r="H8" t="n">
-        <v>38.56</v>
+        <v>39.07</v>
       </c>
       <c r="I8" t="n">
-        <v>38.78</v>
+        <v>41.68</v>
       </c>
       <c r="J8" t="n">
-        <v>41.94</v>
+        <v>45.87</v>
       </c>
       <c r="K8" t="n">
-        <v>43.71</v>
+        <v>46.38</v>
       </c>
       <c r="L8" t="n">
-        <v>40.8</v>
+        <v>39.61</v>
       </c>
       <c r="M8" t="n">
-        <v>43.1</v>
+        <v>39.86</v>
       </c>
       <c r="N8" t="n">
-        <v>83.87</v>
+        <v>86.62</v>
       </c>
       <c r="O8" t="n">
-        <v>87.86</v>
+        <v>86.66</v>
       </c>
       <c r="P8" t="n">
-        <v>83.78</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>87.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>-4.8193</v>
+        <v>17.9468</v>
       </c>
       <c r="S8" t="n">
-        <v>-15.1929</v>
+        <v>-2.1646</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.858000000000001</v>
+        <v>-12.8275</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.9423</v>
+        <v>10.0026</v>
       </c>
       <c r="V8" t="n">
-        <v>-10.9488</v>
+        <v>1.0914</v>
       </c>
       <c r="W8" t="n">
-        <v>-9.832599999999999</v>
+        <v>-4.2895</v>
       </c>
       <c r="X8" t="n">
-        <v>4.6625</v>
+        <v>-18.2191</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.0561</v>
+        <v>-3.2054</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.7831</v>
+        <v>6.4068</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.9636</v>
+        <v>-9.986599999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.3602</v>
+        <v>-2.4364</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.819800000000001</v>
+        <v>2.5324</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47.86</v>
+        <v>50.04</v>
       </c>
       <c r="C9" t="n">
-        <v>48.29</v>
+        <v>54.09</v>
       </c>
       <c r="D9" t="n">
-        <v>39.52</v>
+        <v>49.62</v>
       </c>
       <c r="E9" t="n">
-        <v>40.62</v>
+        <v>52.26</v>
       </c>
       <c r="F9" t="n">
-        <v>39.75</v>
+        <v>42.63</v>
       </c>
       <c r="G9" t="n">
-        <v>39.91</v>
+        <v>43.98</v>
       </c>
       <c r="H9" t="n">
-        <v>37.32</v>
+        <v>42.41</v>
       </c>
       <c r="I9" t="n">
-        <v>37.89</v>
+        <v>43.23</v>
       </c>
       <c r="J9" t="n">
-        <v>42</v>
+        <v>38.07</v>
       </c>
       <c r="K9" t="n">
-        <v>49.76</v>
+        <v>38.49</v>
       </c>
       <c r="L9" t="n">
-        <v>41.57</v>
+        <v>34.78</v>
       </c>
       <c r="M9" t="n">
-        <v>48.74</v>
+        <v>36.26</v>
       </c>
       <c r="N9" t="n">
-        <v>85.27</v>
+        <v>78.62</v>
       </c>
       <c r="O9" t="n">
-        <v>90.72</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>84.89</v>
+        <v>76.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>89.42</v>
+        <v>77.45</v>
       </c>
       <c r="R9" t="n">
-        <v>-12.8513</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-28.7868</v>
+        <v>12.1219</v>
       </c>
       <c r="T9" t="n">
-        <v>-23.4018</v>
+        <v>-8.380100000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.295</v>
+        <v>3.7188</v>
       </c>
       <c r="V9" t="n">
-        <v>-14.6429</v>
+        <v>11.475</v>
       </c>
       <c r="W9" t="n">
-        <v>-14.847</v>
+        <v>-2.6132</v>
       </c>
       <c r="X9" t="n">
-        <v>13.0858</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>35.3137</v>
+        <v>-15.8701</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.286</v>
+        <v>0.6663</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2878</v>
+        <v>-3.7769</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.1902</v>
+        <v>-11.4047</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.3484</v>
+        <v>0.6367</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.88</v>
+        <v>46.06</v>
       </c>
       <c r="C10" t="n">
-        <v>48.18</v>
+        <v>53.07</v>
       </c>
       <c r="D10" t="n">
-        <v>42.61</v>
+        <v>46.05</v>
       </c>
       <c r="E10" t="n">
-        <v>47.91</v>
+        <v>52.75</v>
       </c>
       <c r="F10" t="n">
-        <v>39.09</v>
+        <v>40.88</v>
       </c>
       <c r="G10" t="n">
-        <v>42</v>
+        <v>43.55</v>
       </c>
       <c r="H10" t="n">
-        <v>39.07</v>
+        <v>40.44</v>
       </c>
       <c r="I10" t="n">
-        <v>41.68</v>
+        <v>43.33</v>
       </c>
       <c r="J10" t="n">
-        <v>45.87</v>
+        <v>40.57</v>
       </c>
       <c r="K10" t="n">
-        <v>46.38</v>
+        <v>40.59</v>
       </c>
       <c r="L10" t="n">
-        <v>39.61</v>
+        <v>35.73</v>
       </c>
       <c r="M10" t="n">
-        <v>39.86</v>
+        <v>35.93</v>
       </c>
       <c r="N10" t="n">
-        <v>86.62</v>
+        <v>81.7</v>
       </c>
       <c r="O10" t="n">
-        <v>86.66</v>
+        <v>82.5</v>
       </c>
       <c r="P10" t="n">
-        <v>79.73999999999999</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>80.48999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>17.9468</v>
+        <v>0.9376</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1646</v>
+        <v>29.8621</v>
       </c>
       <c r="T10" t="n">
-        <v>-12.8275</v>
+        <v>7.719</v>
       </c>
       <c r="U10" t="n">
-        <v>10.0026</v>
+        <v>0.2313</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0914</v>
+        <v>14.3574</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.2895</v>
+        <v>5.0934</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.2191</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.2054</v>
+        <v>-26.2823</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.4068</v>
+        <v>-12.7489</v>
       </c>
       <c r="AA10" t="n">
-        <v>-9.986599999999999</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.4364</v>
+        <v>-13.5652</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.5324</v>
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50.04</v>
+        <v>53.75</v>
       </c>
       <c r="C11" t="n">
-        <v>54.09</v>
+        <v>55.6</v>
       </c>
       <c r="D11" t="n">
-        <v>49.62</v>
+        <v>52.88</v>
       </c>
       <c r="E11" t="n">
-        <v>52.26</v>
+        <v>54.81</v>
       </c>
       <c r="F11" t="n">
-        <v>42.63</v>
+        <v>43.6</v>
       </c>
       <c r="G11" t="n">
-        <v>43.98</v>
+        <v>44.59</v>
       </c>
       <c r="H11" t="n">
-        <v>42.41</v>
+        <v>43.27</v>
       </c>
       <c r="I11" t="n">
-        <v>43.23</v>
+        <v>44.1</v>
       </c>
       <c r="J11" t="n">
-        <v>38.07</v>
+        <v>35.18</v>
       </c>
       <c r="K11" t="n">
-        <v>38.49</v>
+        <v>35.87</v>
       </c>
       <c r="L11" t="n">
-        <v>34.78</v>
+        <v>34.01</v>
       </c>
       <c r="M11" t="n">
-        <v>36.26</v>
+        <v>34.55</v>
       </c>
       <c r="N11" t="n">
-        <v>78.62</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>79.06999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="P11" t="n">
-        <v>76.03</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>77.45</v>
+        <v>75.92</v>
       </c>
       <c r="R11" t="n">
-        <v>9.079499999999999</v>
+        <v>3.9052</v>
       </c>
       <c r="S11" t="n">
-        <v>12.1219</v>
+        <v>14.402</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.380100000000001</v>
+        <v>17.5928</v>
       </c>
       <c r="U11" t="n">
-        <v>3.7188</v>
+        <v>1.7771</v>
       </c>
       <c r="V11" t="n">
-        <v>11.475</v>
+        <v>5.8061</v>
       </c>
       <c r="W11" t="n">
-        <v>-2.6132</v>
+        <v>13.7184</v>
       </c>
       <c r="X11" t="n">
-        <v>-9.031599999999999</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y11" t="n">
-        <v>-15.8701</v>
+        <v>-13.3216</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.6663</v>
+        <v>-19.8376</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.7769</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB11" t="n">
-        <v>-11.4047</v>
+        <v>-5.6777</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.6367</v>
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46.06</v>
+        <v>54.32</v>
       </c>
       <c r="C12" t="n">
-        <v>53.07</v>
+        <v>56.6</v>
       </c>
       <c r="D12" t="n">
-        <v>46.05</v>
+        <v>52.13</v>
       </c>
       <c r="E12" t="n">
-        <v>52.75</v>
+        <v>56.55</v>
       </c>
       <c r="F12" t="n">
-        <v>40.88</v>
+        <v>43.45</v>
       </c>
       <c r="G12" t="n">
-        <v>43.55</v>
+        <v>44.21</v>
       </c>
       <c r="H12" t="n">
-        <v>40.44</v>
+        <v>41.84</v>
       </c>
       <c r="I12" t="n">
-        <v>43.33</v>
+        <v>44.15</v>
       </c>
       <c r="J12" t="n">
-        <v>40.57</v>
+        <v>34.82</v>
       </c>
       <c r="K12" t="n">
-        <v>40.59</v>
+        <v>36.26</v>
       </c>
       <c r="L12" t="n">
-        <v>35.73</v>
+        <v>33.43</v>
       </c>
       <c r="M12" t="n">
-        <v>35.93</v>
+        <v>33.43</v>
       </c>
       <c r="N12" t="n">
-        <v>81.7</v>
+        <v>77.08</v>
       </c>
       <c r="O12" t="n">
-        <v>82.5</v>
+        <v>79.88</v>
       </c>
       <c r="P12" t="n">
-        <v>76.93000000000001</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>77.29000000000001</v>
+        <v>75.91</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9376</v>
+        <v>3.1746</v>
       </c>
       <c r="S12" t="n">
-        <v>29.8621</v>
+        <v>8.209</v>
       </c>
       <c r="T12" t="n">
-        <v>7.719</v>
+        <v>39.2171</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2313</v>
+        <v>0.1134</v>
       </c>
       <c r="V12" t="n">
-        <v>14.3574</v>
+        <v>2.1282</v>
       </c>
       <c r="W12" t="n">
-        <v>5.0934</v>
+        <v>16.5215</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9101</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y12" t="n">
-        <v>-26.2823</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z12" t="n">
-        <v>-12.7489</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.2066</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB12" t="n">
-        <v>-13.5652</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC12" t="n">
-        <v>-6.3152</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53.75</v>
+        <v>66.33</v>
       </c>
       <c r="C13" t="n">
-        <v>55.6</v>
+        <v>67.98</v>
       </c>
       <c r="D13" t="n">
-        <v>52.88</v>
+        <v>63.56</v>
       </c>
       <c r="E13" t="n">
-        <v>54.81</v>
+        <v>67.5</v>
       </c>
       <c r="F13" t="n">
-        <v>43.6</v>
+        <v>48.64</v>
       </c>
       <c r="G13" t="n">
-        <v>44.59</v>
+        <v>48.92</v>
       </c>
       <c r="H13" t="n">
-        <v>43.27</v>
+        <v>47.15</v>
       </c>
       <c r="I13" t="n">
-        <v>44.1</v>
+        <v>48</v>
       </c>
       <c r="J13" t="n">
-        <v>35.18</v>
+        <v>27.7</v>
       </c>
       <c r="K13" t="n">
-        <v>35.87</v>
+        <v>29.31</v>
       </c>
       <c r="L13" t="n">
-        <v>34.01</v>
+        <v>26.75</v>
       </c>
       <c r="M13" t="n">
-        <v>34.55</v>
+        <v>26.96</v>
       </c>
       <c r="N13" t="n">
-        <v>76.84999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>77.45</v>
+        <v>70.73</v>
       </c>
       <c r="P13" t="n">
-        <v>75.09999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>75.92</v>
+        <v>69.2</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9052</v>
+        <v>19.3634</v>
       </c>
       <c r="S13" t="n">
-        <v>14.402</v>
+        <v>27.9621</v>
       </c>
       <c r="T13" t="n">
-        <v>17.5928</v>
+        <v>40.8892</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7771</v>
+        <v>8.7203</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8061</v>
+        <v>10.7778</v>
       </c>
       <c r="W13" t="n">
-        <v>13.7184</v>
+        <v>15.1631</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.8408</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y13" t="n">
-        <v>-13.3216</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z13" t="n">
-        <v>-19.8376</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.7725</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>-5.6777</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC13" t="n">
-        <v>-13.1549</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54.32</v>
+        <v>68.12</v>
       </c>
       <c r="C14" t="n">
-        <v>56.6</v>
+        <v>72.28</v>
       </c>
       <c r="D14" t="n">
-        <v>52.13</v>
+        <v>68.12</v>
       </c>
       <c r="E14" t="n">
-        <v>56.55</v>
+        <v>71.98</v>
       </c>
       <c r="F14" t="n">
-        <v>43.45</v>
+        <v>48.02</v>
       </c>
       <c r="G14" t="n">
-        <v>44.21</v>
+        <v>49.09</v>
       </c>
       <c r="H14" t="n">
-        <v>41.84</v>
+        <v>47.31</v>
       </c>
       <c r="I14" t="n">
-        <v>44.15</v>
+        <v>48.96</v>
       </c>
       <c r="J14" t="n">
-        <v>34.82</v>
+        <v>26.76</v>
       </c>
       <c r="K14" t="n">
-        <v>36.26</v>
+        <v>26.76</v>
       </c>
       <c r="L14" t="n">
-        <v>33.43</v>
+        <v>25.09</v>
       </c>
       <c r="M14" t="n">
-        <v>33.43</v>
+        <v>25.2</v>
       </c>
       <c r="N14" t="n">
-        <v>77.08</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>79.88</v>
+        <v>70.3</v>
       </c>
       <c r="P14" t="n">
-        <v>75.79000000000001</v>
+        <v>67.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>75.91</v>
+        <v>67.86</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1746</v>
+        <v>6.637</v>
       </c>
       <c r="S14" t="n">
-        <v>8.209</v>
+        <v>31.3264</v>
       </c>
       <c r="T14" t="n">
-        <v>39.2171</v>
+        <v>37.7344</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1134</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1282</v>
+        <v>11.0204</v>
       </c>
       <c r="W14" t="n">
-        <v>16.5215</v>
+        <v>13.2547</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.2417</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y14" t="n">
-        <v>-7.8047</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z14" t="n">
-        <v>-31.4116</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.0132</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.9884</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC14" t="n">
-        <v>-15.1085</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66.33</v>
+        <v>74.3</v>
       </c>
       <c r="C15" t="n">
-        <v>67.98</v>
+        <v>78.3</v>
       </c>
       <c r="D15" t="n">
-        <v>63.56</v>
+        <v>74.3</v>
       </c>
       <c r="E15" t="n">
-        <v>67.5</v>
+        <v>76.39</v>
       </c>
       <c r="F15" t="n">
-        <v>48.64</v>
+        <v>49.36</v>
       </c>
       <c r="G15" t="n">
-        <v>48.92</v>
+        <v>49.81</v>
       </c>
       <c r="H15" t="n">
-        <v>47.15</v>
+        <v>48.82</v>
       </c>
       <c r="I15" t="n">
-        <v>48</v>
+        <v>49.17</v>
       </c>
       <c r="J15" t="n">
-        <v>27.7</v>
+        <v>24.38</v>
       </c>
       <c r="K15" t="n">
-        <v>29.31</v>
+        <v>24.42</v>
       </c>
       <c r="L15" t="n">
-        <v>26.75</v>
+        <v>23.01</v>
       </c>
       <c r="M15" t="n">
-        <v>26.96</v>
+        <v>23.69</v>
       </c>
       <c r="N15" t="n">
-        <v>68.20999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O15" t="n">
-        <v>70.73</v>
+        <v>68.13</v>
       </c>
       <c r="P15" t="n">
-        <v>67.75</v>
+        <v>66.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>69.2</v>
+        <v>67.62</v>
       </c>
       <c r="R15" t="n">
-        <v>19.3634</v>
+        <v>6.1267</v>
       </c>
       <c r="S15" t="n">
-        <v>27.9621</v>
+        <v>35.084</v>
       </c>
       <c r="T15" t="n">
-        <v>40.8892</v>
+        <v>44.8152</v>
       </c>
       <c r="U15" t="n">
-        <v>8.7203</v>
+        <v>0.4289</v>
       </c>
       <c r="V15" t="n">
-        <v>10.7778</v>
+        <v>11.3703</v>
       </c>
       <c r="W15" t="n">
-        <v>15.1631</v>
+        <v>13.478</v>
       </c>
       <c r="X15" t="n">
-        <v>-19.3539</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y15" t="n">
-        <v>-24.9652</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z15" t="n">
-        <v>-32.3633</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA15" t="n">
-        <v>-8.839399999999999</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB15" t="n">
-        <v>-10.4671</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC15" t="n">
-        <v>-14.0266</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>68.12</v>
+        <v>75.59</v>
       </c>
       <c r="C16" t="n">
-        <v>72.28</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>68.12</v>
+        <v>75.25</v>
       </c>
       <c r="E16" t="n">
-        <v>71.98</v>
+        <v>80.56</v>
       </c>
       <c r="F16" t="n">
-        <v>48.02</v>
+        <v>48.78</v>
       </c>
       <c r="G16" t="n">
-        <v>49.09</v>
+        <v>50.74</v>
       </c>
       <c r="H16" t="n">
-        <v>47.31</v>
+        <v>48.46</v>
       </c>
       <c r="I16" t="n">
-        <v>48.96</v>
+        <v>50.66</v>
       </c>
       <c r="J16" t="n">
-        <v>26.76</v>
+        <v>23.92</v>
       </c>
       <c r="K16" t="n">
-        <v>26.76</v>
+        <v>24.03</v>
       </c>
       <c r="L16" t="n">
-        <v>25.09</v>
+        <v>22.32</v>
       </c>
       <c r="M16" t="n">
-        <v>25.2</v>
+        <v>22.42</v>
       </c>
       <c r="N16" t="n">
-        <v>69.31999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="O16" t="n">
-        <v>70.3</v>
+        <v>68.63</v>
       </c>
       <c r="P16" t="n">
-        <v>67.72</v>
+        <v>65.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>67.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>6.637</v>
+        <v>5.4588</v>
       </c>
       <c r="S16" t="n">
-        <v>31.3264</v>
+        <v>19.3481</v>
       </c>
       <c r="T16" t="n">
-        <v>37.7344</v>
+        <v>46.9805</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>3.0303</v>
       </c>
       <c r="V16" t="n">
-        <v>11.0204</v>
+        <v>5.5417</v>
       </c>
       <c r="W16" t="n">
-        <v>13.2547</v>
+        <v>14.8753</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.5282</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y16" t="n">
-        <v>-27.0622</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z16" t="n">
-        <v>-30.5019</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.9364</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB16" t="n">
-        <v>-10.6164</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC16" t="n">
-        <v>-12.3822</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74.3</v>
+        <v>83.27</v>
       </c>
       <c r="C17" t="n">
-        <v>78.3</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>74.3</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>76.39</v>
+        <v>85.31</v>
       </c>
       <c r="F17" t="n">
-        <v>49.36</v>
+        <v>51.39</v>
       </c>
       <c r="G17" t="n">
-        <v>49.81</v>
+        <v>53.43</v>
       </c>
       <c r="H17" t="n">
-        <v>48.82</v>
+        <v>51.38</v>
       </c>
       <c r="I17" t="n">
-        <v>49.17</v>
+        <v>53.41</v>
       </c>
       <c r="J17" t="n">
-        <v>24.38</v>
+        <v>21.6</v>
       </c>
       <c r="K17" t="n">
-        <v>24.42</v>
+        <v>22.34</v>
       </c>
       <c r="L17" t="n">
-        <v>23.01</v>
+        <v>21</v>
       </c>
       <c r="M17" t="n">
-        <v>23.69</v>
+        <v>21.05</v>
       </c>
       <c r="N17" t="n">
-        <v>67.38</v>
+        <v>64.67</v>
       </c>
       <c r="O17" t="n">
-        <v>68.13</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>66.75</v>
+        <v>62.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>67.62</v>
+        <v>62.02</v>
       </c>
       <c r="R17" t="n">
-        <v>6.1267</v>
+        <v>5.8962</v>
       </c>
       <c r="S17" t="n">
-        <v>35.084</v>
+        <v>18.519</v>
       </c>
       <c r="T17" t="n">
-        <v>44.8152</v>
+        <v>50.8576</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4289</v>
+        <v>5.4283</v>
       </c>
       <c r="V17" t="n">
-        <v>11.3703</v>
+        <v>9.0891</v>
       </c>
       <c r="W17" t="n">
-        <v>13.478</v>
+        <v>20.974</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.9921</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y17" t="n">
-        <v>-29.1355</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z17" t="n">
-        <v>-34.0662</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.3537</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB17" t="n">
-        <v>-10.9208</v>
+        <v>-8.606</v>
       </c>
       <c r="AC17" t="n">
-        <v>-12.5113</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>75.59</v>
+        <v>84.66</v>
       </c>
       <c r="C18" t="n">
-        <v>80.73999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D18" t="n">
-        <v>75.25</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>80.56</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>48.78</v>
+        <v>53.57</v>
       </c>
       <c r="G18" t="n">
-        <v>50.74</v>
+        <v>55.74</v>
       </c>
       <c r="H18" t="n">
-        <v>48.46</v>
+        <v>53.33</v>
       </c>
       <c r="I18" t="n">
-        <v>50.66</v>
+        <v>55.65</v>
       </c>
       <c r="J18" t="n">
-        <v>23.92</v>
+        <v>21.23</v>
       </c>
       <c r="K18" t="n">
-        <v>24.03</v>
+        <v>22.43</v>
       </c>
       <c r="L18" t="n">
-        <v>22.32</v>
+        <v>20.9</v>
       </c>
       <c r="M18" t="n">
-        <v>22.42</v>
+        <v>20.94</v>
       </c>
       <c r="N18" t="n">
-        <v>68.2</v>
+        <v>61.88</v>
       </c>
       <c r="O18" t="n">
-        <v>68.63</v>
+        <v>62.15</v>
       </c>
       <c r="P18" t="n">
-        <v>65.5</v>
+        <v>59.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>65.56999999999999</v>
+        <v>59.44</v>
       </c>
       <c r="R18" t="n">
-        <v>5.4588</v>
+        <v>0.7619</v>
       </c>
       <c r="S18" t="n">
-        <v>19.3481</v>
+        <v>12.5278</v>
       </c>
       <c r="T18" t="n">
-        <v>46.9805</v>
+        <v>27.3481</v>
       </c>
       <c r="U18" t="n">
-        <v>3.0303</v>
+        <v>4.194</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5417</v>
+        <v>13.1788</v>
       </c>
       <c r="W18" t="n">
-        <v>14.8753</v>
+        <v>15.9375</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.3609</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y18" t="n">
-        <v>-16.8398</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z18" t="n">
-        <v>-35.1085</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA18" t="n">
-        <v>-3.0316</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB18" t="n">
-        <v>-5.2457</v>
+        <v>-12.097</v>
       </c>
       <c r="AC18" t="n">
-        <v>-13.6328</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>83.27</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>85.56999999999999</v>
+        <v>89.39</v>
       </c>
       <c r="D19" t="n">
-        <v>80.70999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="E19" t="n">
-        <v>85.31</v>
+        <v>88.37</v>
       </c>
       <c r="F19" t="n">
-        <v>51.39</v>
+        <v>56.13</v>
       </c>
       <c r="G19" t="n">
-        <v>53.43</v>
+        <v>56.92</v>
       </c>
       <c r="H19" t="n">
-        <v>51.38</v>
+        <v>55.1</v>
       </c>
       <c r="I19" t="n">
-        <v>53.41</v>
+        <v>56.43</v>
       </c>
       <c r="J19" t="n">
-        <v>21.6</v>
+        <v>21.13</v>
       </c>
       <c r="K19" t="n">
-        <v>22.34</v>
+        <v>21.56</v>
       </c>
       <c r="L19" t="n">
-        <v>21</v>
+        <v>20.07</v>
       </c>
       <c r="M19" t="n">
-        <v>21.05</v>
+        <v>20.28</v>
       </c>
       <c r="N19" t="n">
-        <v>64.67</v>
+        <v>58.95</v>
       </c>
       <c r="O19" t="n">
-        <v>64.68000000000001</v>
+        <v>60.06</v>
       </c>
       <c r="P19" t="n">
-        <v>62.02</v>
+        <v>58.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>62.02</v>
+        <v>58.61</v>
       </c>
       <c r="R19" t="n">
-        <v>5.8962</v>
+        <v>2.8036</v>
       </c>
       <c r="S19" t="n">
-        <v>18.519</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>50.8576</v>
+        <v>22.7702</v>
       </c>
       <c r="U19" t="n">
-        <v>5.4283</v>
+        <v>1.4016</v>
       </c>
       <c r="V19" t="n">
-        <v>9.0891</v>
+        <v>11.3897</v>
       </c>
       <c r="W19" t="n">
-        <v>20.974</v>
+        <v>15.2574</v>
       </c>
       <c r="X19" t="n">
-        <v>-6.1106</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y19" t="n">
-        <v>-16.4683</v>
+        <v>-9.545</v>
       </c>
       <c r="Z19" t="n">
-        <v>-37.0326</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA19" t="n">
-        <v>-5.4141</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB19" t="n">
-        <v>-8.606</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC19" t="n">
-        <v>-18.298</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84.66</v>
+        <v>93.2</v>
       </c>
       <c r="C20" t="n">
-        <v>85.98</v>
+        <v>94.75</v>
       </c>
       <c r="D20" t="n">
-        <v>79.76000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="E20" t="n">
-        <v>85.95999999999999</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>53.57</v>
+        <v>57.78</v>
       </c>
       <c r="G20" t="n">
-        <v>55.74</v>
+        <v>58.94</v>
       </c>
       <c r="H20" t="n">
-        <v>53.33</v>
+        <v>57.37</v>
       </c>
       <c r="I20" t="n">
-        <v>55.65</v>
+        <v>58.59</v>
       </c>
       <c r="J20" t="n">
-        <v>21.23</v>
+        <v>19.23</v>
       </c>
       <c r="K20" t="n">
-        <v>22.43</v>
+        <v>19.8</v>
       </c>
       <c r="L20" t="n">
-        <v>20.9</v>
+        <v>18.86</v>
       </c>
       <c r="M20" t="n">
-        <v>20.94</v>
+        <v>18.87</v>
       </c>
       <c r="N20" t="n">
-        <v>61.88</v>
+        <v>57.25</v>
       </c>
       <c r="O20" t="n">
-        <v>62.15</v>
+        <v>57.67</v>
       </c>
       <c r="P20" t="n">
-        <v>59.35</v>
+        <v>56.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>59.44</v>
+        <v>56.39</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7619</v>
+        <v>7.1404</v>
       </c>
       <c r="S20" t="n">
-        <v>12.5278</v>
+        <v>10.9835</v>
       </c>
       <c r="T20" t="n">
-        <v>27.3481</v>
+        <v>23.9429</v>
       </c>
       <c r="U20" t="n">
-        <v>4.194</v>
+        <v>3.8278</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1788</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>15.9375</v>
+        <v>19.158</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5226</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y20" t="n">
-        <v>-11.6083</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z20" t="n">
-        <v>-22.3294</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA20" t="n">
-        <v>-4.1599</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB20" t="n">
-        <v>-12.097</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC20" t="n">
-        <v>-14.104</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>85.01000000000001</v>
+        <v>95.97</v>
       </c>
       <c r="C21" t="n">
-        <v>89.39</v>
+        <v>96.92</v>
       </c>
       <c r="D21" t="n">
-        <v>83.31</v>
+        <v>92.03</v>
       </c>
       <c r="E21" t="n">
-        <v>88.37</v>
+        <v>95.94</v>
       </c>
       <c r="F21" t="n">
-        <v>56.13</v>
+        <v>58.4</v>
       </c>
       <c r="G21" t="n">
-        <v>56.92</v>
+        <v>58.58</v>
       </c>
       <c r="H21" t="n">
-        <v>55.1</v>
+        <v>56.91</v>
       </c>
       <c r="I21" t="n">
-        <v>56.43</v>
+        <v>58.08</v>
       </c>
       <c r="J21" t="n">
-        <v>21.13</v>
+        <v>18.635</v>
       </c>
       <c r="K21" t="n">
-        <v>21.56</v>
+        <v>19.41</v>
       </c>
       <c r="L21" t="n">
-        <v>20.07</v>
+        <v>18.44</v>
       </c>
       <c r="M21" t="n">
-        <v>20.28</v>
+        <v>18.63</v>
       </c>
       <c r="N21" t="n">
-        <v>58.95</v>
+        <v>56.59</v>
       </c>
       <c r="O21" t="n">
-        <v>60.06</v>
+        <v>58.035</v>
       </c>
       <c r="P21" t="n">
-        <v>58.11</v>
+        <v>56.4134</v>
       </c>
       <c r="Q21" t="n">
-        <v>58.61</v>
+        <v>56.91</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8036</v>
+        <v>1.3308</v>
       </c>
       <c r="S21" t="n">
-        <v>9.694599999999999</v>
+        <v>11.6101</v>
       </c>
       <c r="T21" t="n">
-        <v>22.7702</v>
+        <v>19.0914</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4016</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>11.3897</v>
+        <v>4.3666</v>
       </c>
       <c r="W21" t="n">
-        <v>15.2574</v>
+        <v>14.6467</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.1519</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y21" t="n">
-        <v>-9.545</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z21" t="n">
-        <v>-19.5238</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.3964</v>
+        <v>0.9221</v>
       </c>
       <c r="AB21" t="n">
-        <v>-10.6146</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC21" t="n">
-        <v>-13.631</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>93.19499999999999</v>
-      </c>
-      <c r="C22" t="n">
-        <v>94.745</v>
-      </c>
-      <c r="D22" t="n">
-        <v>90.66</v>
-      </c>
-      <c r="E22" t="n">
-        <v>94.68000000000001</v>
-      </c>
-      <c r="F22" t="n">
-        <v>57.78</v>
-      </c>
-      <c r="G22" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="H22" t="n">
-        <v>57.3699</v>
-      </c>
-      <c r="I22" t="n">
-        <v>58.59</v>
-      </c>
-      <c r="J22" t="n">
-        <v>19.23</v>
-      </c>
-      <c r="K22" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L22" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="M22" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="N22" t="n">
-        <v>57.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>57.6696</v>
-      </c>
-      <c r="P22" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>56.39</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7.1404</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10.9835</v>
-      </c>
-      <c r="T22" t="n">
-        <v>23.9429</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.8278</v>
-      </c>
-      <c r="V22" t="n">
-        <v>9.698600000000001</v>
-      </c>
-      <c r="W22" t="n">
-        <v>19.158</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-6.9527</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>-10.3563</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-20.3461</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>-3.7877</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-9.0777</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26387,7 +26387,7 @@
         <v>95.97</v>
       </c>
       <c r="C21" t="n">
-        <v>96.92</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D21" t="n">
         <v>92.03</v>
@@ -26408,7 +26408,7 @@
         <v>58.08</v>
       </c>
       <c r="J21" t="n">
-        <v>18.635</v>
+        <v>18.64</v>
       </c>
       <c r="K21" t="n">
         <v>19.41</v>
@@ -26423,10 +26423,10 @@
         <v>56.59</v>
       </c>
       <c r="O21" t="n">
-        <v>58.035</v>
+        <v>58.04</v>
       </c>
       <c r="P21" t="n">
-        <v>56.4134</v>
+        <v>56.41</v>
       </c>
       <c r="Q21" t="n">
         <v>56.91</v>
@@ -26466,6 +26466,97 @@
       </c>
       <c r="AC21" t="n">
         <v>-13.2073</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="C22" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="D22" t="n">
+        <v>95.31999999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>98.09</v>
+      </c>
+      <c r="F22" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="H22" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="I22" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>18.755</v>
+      </c>
+      <c r="L22" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="M22" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="O22" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="P22" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.241</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10.9992</v>
+      </c>
+      <c r="T22" t="n">
+        <v>14.9807</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-1.1708</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.7189</v>
+      </c>
+      <c r="W22" t="n">
+        <v>7.4705</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-2.3081</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-10.2564</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-13.5392</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.1949</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-1.7403</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-7.1429</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.63</v>
+        <v>51.54</v>
       </c>
       <c r="C2" t="n">
-        <v>56.81</v>
+        <v>56.09</v>
       </c>
       <c r="D2" t="n">
-        <v>52.28</v>
+        <v>51.54</v>
       </c>
       <c r="E2" t="n">
-        <v>53.03</v>
+        <v>54.96</v>
       </c>
       <c r="F2" t="n">
-        <v>45.0355</v>
+        <v>43.7676</v>
       </c>
       <c r="G2" t="n">
-        <v>46.0738</v>
+        <v>44.4765</v>
       </c>
       <c r="H2" t="n">
-        <v>44.0572</v>
+        <v>43.1187</v>
       </c>
       <c r="I2" t="n">
-        <v>44.4964</v>
+        <v>43.548</v>
       </c>
       <c r="J2" t="n">
-        <v>37.7316</v>
+        <v>40.08</v>
       </c>
       <c r="K2" t="n">
-        <v>39.4986</v>
+        <v>40.08</v>
       </c>
       <c r="L2" t="n">
-        <v>35.9547</v>
+        <v>36.7</v>
       </c>
       <c r="M2" t="n">
-        <v>38.903</v>
+        <v>37.46</v>
       </c>
       <c r="N2" t="n">
-        <v>75.8734</v>
+        <v>78.15479999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>77.6985</v>
+        <v>79.2559</v>
       </c>
       <c r="P2" t="n">
-        <v>73.9589</v>
+        <v>76.9248</v>
       </c>
       <c r="Q2" t="n">
-        <v>76.8554</v>
+        <v>78.502</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51.54</v>
+        <v>56.64</v>
       </c>
       <c r="C3" t="n">
-        <v>56.09</v>
+        <v>58.25</v>
       </c>
       <c r="D3" t="n">
-        <v>51.54</v>
+        <v>55.59</v>
       </c>
       <c r="E3" t="n">
-        <v>54.96</v>
+        <v>57.04</v>
       </c>
       <c r="F3" t="n">
-        <v>43.7676</v>
+        <v>44.7</v>
       </c>
       <c r="G3" t="n">
-        <v>44.4765</v>
+        <v>45.22</v>
       </c>
       <c r="H3" t="n">
-        <v>43.1187</v>
+        <v>43.95</v>
       </c>
       <c r="I3" t="n">
-        <v>43.548</v>
+        <v>44.39</v>
       </c>
       <c r="J3" t="n">
-        <v>40.08</v>
+        <v>36.32</v>
       </c>
       <c r="K3" t="n">
-        <v>40.08</v>
+        <v>37.06</v>
       </c>
       <c r="L3" t="n">
-        <v>36.7</v>
+        <v>35.23</v>
       </c>
       <c r="M3" t="n">
-        <v>37.46</v>
+        <v>36.02</v>
       </c>
       <c r="N3" t="n">
-        <v>78.15479999999999</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>79.2559</v>
+        <v>77.8</v>
       </c>
       <c r="P3" t="n">
-        <v>76.9248</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>78.502</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6394</v>
+        <v>3.7846</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.1314</v>
+        <v>1.9335</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.7092</v>
+        <v>-3.8441</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1425</v>
+        <v>-1.9643</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.64</v>
+        <v>54.19</v>
       </c>
       <c r="C4" t="n">
-        <v>58.25</v>
+        <v>54.44</v>
       </c>
       <c r="D4" t="n">
-        <v>55.59</v>
+        <v>48.87</v>
       </c>
       <c r="E4" t="n">
-        <v>57.04</v>
+        <v>48.97</v>
       </c>
       <c r="F4" t="n">
-        <v>44.7</v>
+        <v>43.23</v>
       </c>
       <c r="G4" t="n">
-        <v>45.22</v>
+        <v>43.68</v>
       </c>
       <c r="H4" t="n">
-        <v>43.95</v>
+        <v>41.15</v>
       </c>
       <c r="I4" t="n">
-        <v>44.39</v>
+        <v>41.23</v>
       </c>
       <c r="J4" t="n">
-        <v>36.32</v>
+        <v>37.84</v>
       </c>
       <c r="K4" t="n">
-        <v>37.06</v>
+        <v>41.26</v>
       </c>
       <c r="L4" t="n">
-        <v>35.23</v>
+        <v>37.7</v>
       </c>
       <c r="M4" t="n">
-        <v>36.02</v>
+        <v>41.18</v>
       </c>
       <c r="N4" t="n">
-        <v>76.43000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="O4" t="n">
-        <v>77.8</v>
+        <v>82.62</v>
       </c>
       <c r="P4" t="n">
-        <v>75.51000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>76.95999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7846</v>
+        <v>-14.148</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9335</v>
+        <v>-7.1187</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.8441</v>
+        <v>14.3254</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.9643</v>
+        <v>7.1985</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.19</v>
+        <v>48.04</v>
       </c>
       <c r="C5" t="n">
-        <v>54.44</v>
+        <v>49.38</v>
       </c>
       <c r="D5" t="n">
-        <v>48.87</v>
+        <v>45.96</v>
       </c>
       <c r="E5" t="n">
-        <v>48.97</v>
+        <v>46.61</v>
       </c>
       <c r="F5" t="n">
-        <v>43.23</v>
+        <v>40.56</v>
       </c>
       <c r="G5" t="n">
-        <v>43.68</v>
+        <v>40.59</v>
       </c>
       <c r="H5" t="n">
-        <v>41.15</v>
+        <v>38.56</v>
       </c>
       <c r="I5" t="n">
-        <v>41.23</v>
+        <v>38.78</v>
       </c>
       <c r="J5" t="n">
-        <v>37.84</v>
+        <v>41.94</v>
       </c>
       <c r="K5" t="n">
-        <v>41.26</v>
+        <v>43.71</v>
       </c>
       <c r="L5" t="n">
-        <v>37.7</v>
+        <v>40.8</v>
       </c>
       <c r="M5" t="n">
-        <v>41.18</v>
+        <v>43.1</v>
       </c>
       <c r="N5" t="n">
-        <v>79.02</v>
+        <v>83.87</v>
       </c>
       <c r="O5" t="n">
-        <v>82.62</v>
+        <v>87.86</v>
       </c>
       <c r="P5" t="n">
-        <v>78.25</v>
+        <v>83.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>82.5</v>
+        <v>87.42</v>
       </c>
       <c r="R5" t="n">
-        <v>-14.148</v>
+        <v>-4.8193</v>
       </c>
       <c r="S5" t="n">
-        <v>-7.656</v>
+        <v>-15.1929</v>
       </c>
       <c r="U5" t="n">
-        <v>-7.1187</v>
+        <v>-5.9423</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.3408</v>
+        <v>-10.9488</v>
       </c>
       <c r="X5" t="n">
-        <v>14.3254</v>
+        <v>4.6625</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.853</v>
+        <v>15.0561</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.1985</v>
+        <v>5.9636</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.3444</v>
+        <v>11.3602</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.04</v>
+        <v>47.86</v>
       </c>
       <c r="C6" t="n">
-        <v>49.38</v>
+        <v>48.29</v>
       </c>
       <c r="D6" t="n">
-        <v>45.96</v>
+        <v>39.52</v>
       </c>
       <c r="E6" t="n">
-        <v>46.61</v>
+        <v>40.62</v>
       </c>
       <c r="F6" t="n">
-        <v>40.56</v>
+        <v>39.75</v>
       </c>
       <c r="G6" t="n">
-        <v>40.59</v>
+        <v>39.91</v>
       </c>
       <c r="H6" t="n">
-        <v>38.56</v>
+        <v>37.32</v>
       </c>
       <c r="I6" t="n">
-        <v>38.78</v>
+        <v>37.89</v>
       </c>
       <c r="J6" t="n">
-        <v>41.94</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
-        <v>43.71</v>
+        <v>49.76</v>
       </c>
       <c r="L6" t="n">
-        <v>40.8</v>
+        <v>41.57</v>
       </c>
       <c r="M6" t="n">
-        <v>43.1</v>
+        <v>48.74</v>
       </c>
       <c r="N6" t="n">
-        <v>83.87</v>
+        <v>85.27</v>
       </c>
       <c r="O6" t="n">
-        <v>87.86</v>
+        <v>90.72</v>
       </c>
       <c r="P6" t="n">
-        <v>83.78</v>
+        <v>84.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>87.42</v>
+        <v>89.42</v>
       </c>
       <c r="R6" t="n">
-        <v>-4.8193</v>
+        <v>-12.8513</v>
       </c>
       <c r="S6" t="n">
-        <v>-15.1929</v>
+        <v>-28.7868</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.9423</v>
+        <v>-2.295</v>
       </c>
       <c r="V6" t="n">
-        <v>-10.9488</v>
+        <v>-14.6429</v>
       </c>
       <c r="X6" t="n">
-        <v>4.6625</v>
+        <v>13.0858</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.0561</v>
+        <v>35.3137</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.9636</v>
+        <v>2.2878</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.3602</v>
+        <v>16.1902</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.86</v>
+        <v>42.88</v>
       </c>
       <c r="C7" t="n">
-        <v>48.29</v>
+        <v>48.18</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52</v>
+        <v>42.61</v>
       </c>
       <c r="E7" t="n">
-        <v>40.62</v>
+        <v>47.91</v>
       </c>
       <c r="F7" t="n">
-        <v>39.75</v>
+        <v>39.09</v>
       </c>
       <c r="G7" t="n">
-        <v>39.91</v>
+        <v>42</v>
       </c>
       <c r="H7" t="n">
-        <v>37.32</v>
+        <v>39.07</v>
       </c>
       <c r="I7" t="n">
-        <v>37.89</v>
+        <v>41.68</v>
       </c>
       <c r="J7" t="n">
-        <v>42</v>
+        <v>45.87</v>
       </c>
       <c r="K7" t="n">
-        <v>49.76</v>
+        <v>46.38</v>
       </c>
       <c r="L7" t="n">
-        <v>41.57</v>
+        <v>39.61</v>
       </c>
       <c r="M7" t="n">
-        <v>48.74</v>
+        <v>39.86</v>
       </c>
       <c r="N7" t="n">
-        <v>85.27</v>
+        <v>86.62</v>
       </c>
       <c r="O7" t="n">
-        <v>90.72</v>
+        <v>86.66</v>
       </c>
       <c r="P7" t="n">
-        <v>84.89</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>89.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>-12.8513</v>
+        <v>17.9468</v>
       </c>
       <c r="S7" t="n">
-        <v>-28.7868</v>
+        <v>-2.1646</v>
       </c>
       <c r="T7" t="n">
-        <v>-23.4018</v>
+        <v>-12.8275</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.295</v>
+        <v>10.0026</v>
       </c>
       <c r="V7" t="n">
-        <v>-14.6429</v>
+        <v>1.0914</v>
       </c>
       <c r="W7" t="n">
-        <v>-14.847</v>
+        <v>-4.2895</v>
       </c>
       <c r="X7" t="n">
-        <v>13.0858</v>
+        <v>-18.2191</v>
       </c>
       <c r="Y7" t="n">
-        <v>35.3137</v>
+        <v>-3.2054</v>
       </c>
       <c r="Z7" t="n">
-        <v>25.286</v>
+        <v>6.4068</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2878</v>
+        <v>-9.986599999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.1902</v>
+        <v>-2.4364</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.3484</v>
+        <v>2.5324</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>42.88</v>
+        <v>50.04</v>
       </c>
       <c r="C8" t="n">
-        <v>48.18</v>
+        <v>54.09</v>
       </c>
       <c r="D8" t="n">
-        <v>42.61</v>
+        <v>49.62</v>
       </c>
       <c r="E8" t="n">
-        <v>47.91</v>
+        <v>52.26</v>
       </c>
       <c r="F8" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="G8" t="n">
-        <v>42</v>
+        <v>43.98</v>
       </c>
       <c r="H8" t="n">
-        <v>39.07</v>
+        <v>42.41</v>
       </c>
       <c r="I8" t="n">
-        <v>41.68</v>
+        <v>43.23</v>
       </c>
       <c r="J8" t="n">
-        <v>45.87</v>
+        <v>38.07</v>
       </c>
       <c r="K8" t="n">
-        <v>46.38</v>
+        <v>38.49</v>
       </c>
       <c r="L8" t="n">
-        <v>39.61</v>
+        <v>34.78</v>
       </c>
       <c r="M8" t="n">
-        <v>39.86</v>
+        <v>36.26</v>
       </c>
       <c r="N8" t="n">
-        <v>86.62</v>
+        <v>78.62</v>
       </c>
       <c r="O8" t="n">
-        <v>86.66</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>79.73999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>80.48999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="R8" t="n">
-        <v>17.9468</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1646</v>
+        <v>12.1219</v>
       </c>
       <c r="T8" t="n">
-        <v>-12.8275</v>
+        <v>-8.380100000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>10.0026</v>
+        <v>3.7188</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0914</v>
+        <v>11.475</v>
       </c>
       <c r="W8" t="n">
-        <v>-4.2895</v>
+        <v>-2.6132</v>
       </c>
       <c r="X8" t="n">
-        <v>-18.2191</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.2054</v>
+        <v>-15.8701</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.4068</v>
+        <v>0.6663</v>
       </c>
       <c r="AA8" t="n">
-        <v>-9.986599999999999</v>
+        <v>-3.7769</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.4364</v>
+        <v>-11.4047</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5324</v>
+        <v>0.6367</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C9" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D9" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E9" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F9" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G9" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H9" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I9" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J9" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K9" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L9" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M9" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N9" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O9" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P9" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>9.079499999999999</v>
+        <v>0.9376</v>
       </c>
       <c r="S9" t="n">
-        <v>12.1219</v>
+        <v>29.8621</v>
       </c>
       <c r="T9" t="n">
-        <v>-8.380100000000001</v>
+        <v>7.719</v>
       </c>
       <c r="U9" t="n">
-        <v>3.7188</v>
+        <v>0.2313</v>
       </c>
       <c r="V9" t="n">
-        <v>11.475</v>
+        <v>14.3574</v>
       </c>
       <c r="W9" t="n">
-        <v>-2.6132</v>
+        <v>5.0934</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.031599999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y9" t="n">
-        <v>-15.8701</v>
+        <v>-26.2823</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6663</v>
+        <v>-12.7489</v>
       </c>
       <c r="AA9" t="n">
-        <v>-3.7769</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB9" t="n">
-        <v>-11.4047</v>
+        <v>-13.5652</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.6367</v>
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C10" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D10" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E10" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F10" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G10" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H10" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I10" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J10" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K10" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L10" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M10" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N10" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P10" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="S10" t="n">
-        <v>29.8621</v>
+        <v>14.402</v>
       </c>
       <c r="T10" t="n">
-        <v>7.719</v>
+        <v>17.5928</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="V10" t="n">
-        <v>14.3574</v>
+        <v>5.8061</v>
       </c>
       <c r="W10" t="n">
-        <v>5.0934</v>
+        <v>13.7184</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y10" t="n">
-        <v>-26.2823</v>
+        <v>-13.3216</v>
       </c>
       <c r="Z10" t="n">
-        <v>-12.7489</v>
+        <v>-19.8376</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB10" t="n">
-        <v>-13.5652</v>
+        <v>-5.6777</v>
       </c>
       <c r="AC10" t="n">
-        <v>-6.3152</v>
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C11" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D11" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E11" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F11" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G11" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H11" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I11" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J11" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K11" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L11" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M11" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N11" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O11" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P11" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R11" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="S11" t="n">
-        <v>14.402</v>
+        <v>8.209</v>
       </c>
       <c r="T11" t="n">
-        <v>17.5928</v>
+        <v>39.2171</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8061</v>
+        <v>2.1282</v>
       </c>
       <c r="W11" t="n">
-        <v>13.7184</v>
+        <v>16.5215</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y11" t="n">
-        <v>-13.3216</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z11" t="n">
-        <v>-19.8376</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB11" t="n">
-        <v>-5.6777</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC11" t="n">
-        <v>-13.1549</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C12" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D12" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E12" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F12" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G12" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H12" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I12" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J12" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K12" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L12" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M12" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N12" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P12" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S12" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="T12" t="n">
-        <v>39.2171</v>
+        <v>40.8892</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="W12" t="n">
-        <v>16.5215</v>
+        <v>15.1631</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y12" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z12" t="n">
-        <v>-31.4116</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC12" t="n">
-        <v>-15.1085</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C13" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D13" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E13" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F13" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G13" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H13" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I13" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J13" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K13" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L13" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M13" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N13" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P13" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R13" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S13" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="T13" t="n">
-        <v>40.8892</v>
+        <v>37.7344</v>
       </c>
       <c r="U13" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="W13" t="n">
-        <v>15.1631</v>
+        <v>13.2547</v>
       </c>
       <c r="X13" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y13" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z13" t="n">
-        <v>-32.3633</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA13" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB13" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC13" t="n">
-        <v>-14.0266</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C14" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D14" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E14" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F14" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G14" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H14" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I14" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J14" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K14" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L14" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M14" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N14" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O14" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P14" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R14" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S14" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T14" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V14" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W14" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y14" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z14" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB14" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC14" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C15" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E15" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F15" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G15" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H15" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I15" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J15" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K15" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L15" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M15" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N15" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O15" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P15" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S15" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T15" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V15" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W15" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X15" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y15" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z15" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB15" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC15" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C16" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F16" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G16" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H16" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I16" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J16" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K16" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L16" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M16" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N16" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O16" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R16" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S16" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T16" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U16" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W16" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y16" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z16" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB16" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC16" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C17" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D17" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G17" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H17" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I17" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J17" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K17" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L17" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M17" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N17" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O17" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P17" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R17" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S17" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T17" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U17" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V17" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W17" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y17" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z17" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA17" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB17" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC17" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D18" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E18" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F18" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G18" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H18" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I18" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J18" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K18" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L18" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M18" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N18" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O18" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P18" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S18" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U18" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V18" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W18" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y18" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z18" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA18" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB18" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC18" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C19" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D19" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E19" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G19" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H19" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I19" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J19" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K19" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L19" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M19" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N19" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O19" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P19" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S19" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T19" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V19" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y19" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z19" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB19" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC19" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C20" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E20" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F20" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G20" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H20" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I20" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J20" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K20" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L20" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M20" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N20" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O20" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P20" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R20" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S20" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T20" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U20" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W20" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X20" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y20" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z20" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB20" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC20" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C21" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D21" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F21" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G21" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H21" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I21" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J21" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K21" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L21" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M21" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N21" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O21" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P21" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S21" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T21" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V21" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W21" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y21" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z21" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC21" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C22" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D22" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F22" t="n">
-        <v>58.38</v>
+        <v>58.92</v>
       </c>
       <c r="G22" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H22" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I22" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J22" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K22" t="n">
-        <v>18.755</v>
+        <v>17.945</v>
       </c>
       <c r="L22" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M22" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N22" t="n">
-        <v>56.61</v>
+        <v>56.01</v>
       </c>
       <c r="O22" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P22" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R22" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S22" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T22" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V22" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W22" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y22" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z22" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB22" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC22" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.54</v>
+        <v>56.64</v>
       </c>
       <c r="C2" t="n">
-        <v>56.09</v>
+        <v>58.25</v>
       </c>
       <c r="D2" t="n">
-        <v>51.54</v>
+        <v>55.59</v>
       </c>
       <c r="E2" t="n">
-        <v>54.96</v>
+        <v>57.04</v>
       </c>
       <c r="F2" t="n">
-        <v>43.7676</v>
+        <v>44.7</v>
       </c>
       <c r="G2" t="n">
-        <v>44.4765</v>
+        <v>45.22</v>
       </c>
       <c r="H2" t="n">
-        <v>43.1187</v>
+        <v>43.95</v>
       </c>
       <c r="I2" t="n">
-        <v>43.548</v>
+        <v>44.39</v>
       </c>
       <c r="J2" t="n">
-        <v>40.08</v>
+        <v>36.32</v>
       </c>
       <c r="K2" t="n">
-        <v>40.08</v>
+        <v>37.06</v>
       </c>
       <c r="L2" t="n">
-        <v>36.7</v>
+        <v>35.23</v>
       </c>
       <c r="M2" t="n">
-        <v>37.46</v>
+        <v>36.02</v>
       </c>
       <c r="N2" t="n">
-        <v>78.15479999999999</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>79.2559</v>
+        <v>77.8</v>
       </c>
       <c r="P2" t="n">
-        <v>76.9248</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>78.502</v>
+        <v>76.95999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.64</v>
+        <v>54.19</v>
       </c>
       <c r="C3" t="n">
-        <v>58.25</v>
+        <v>54.44</v>
       </c>
       <c r="D3" t="n">
-        <v>55.59</v>
+        <v>48.87</v>
       </c>
       <c r="E3" t="n">
-        <v>57.04</v>
+        <v>48.97</v>
       </c>
       <c r="F3" t="n">
-        <v>44.7</v>
+        <v>43.23</v>
       </c>
       <c r="G3" t="n">
-        <v>45.22</v>
+        <v>43.68</v>
       </c>
       <c r="H3" t="n">
-        <v>43.95</v>
+        <v>41.15</v>
       </c>
       <c r="I3" t="n">
-        <v>44.39</v>
+        <v>41.23</v>
       </c>
       <c r="J3" t="n">
-        <v>36.32</v>
+        <v>37.84</v>
       </c>
       <c r="K3" t="n">
-        <v>37.06</v>
+        <v>41.26</v>
       </c>
       <c r="L3" t="n">
-        <v>35.23</v>
+        <v>37.7</v>
       </c>
       <c r="M3" t="n">
-        <v>36.02</v>
+        <v>41.18</v>
       </c>
       <c r="N3" t="n">
-        <v>76.43000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="O3" t="n">
-        <v>77.8</v>
+        <v>82.62</v>
       </c>
       <c r="P3" t="n">
-        <v>75.51000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>76.95999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="R3" t="n">
-        <v>3.7846</v>
+        <v>-14.148</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9335</v>
+        <v>-7.1187</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.8441</v>
+        <v>14.3254</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.9643</v>
+        <v>7.1985</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.19</v>
+        <v>48.04</v>
       </c>
       <c r="C4" t="n">
-        <v>54.44</v>
+        <v>49.38</v>
       </c>
       <c r="D4" t="n">
-        <v>48.87</v>
+        <v>45.96</v>
       </c>
       <c r="E4" t="n">
-        <v>48.97</v>
+        <v>46.61</v>
       </c>
       <c r="F4" t="n">
-        <v>43.23</v>
+        <v>40.56</v>
       </c>
       <c r="G4" t="n">
-        <v>43.68</v>
+        <v>40.59</v>
       </c>
       <c r="H4" t="n">
-        <v>41.15</v>
+        <v>38.56</v>
       </c>
       <c r="I4" t="n">
-        <v>41.23</v>
+        <v>38.78</v>
       </c>
       <c r="J4" t="n">
-        <v>37.84</v>
+        <v>41.94</v>
       </c>
       <c r="K4" t="n">
-        <v>41.26</v>
+        <v>43.71</v>
       </c>
       <c r="L4" t="n">
-        <v>37.7</v>
+        <v>40.8</v>
       </c>
       <c r="M4" t="n">
-        <v>41.18</v>
+        <v>43.1</v>
       </c>
       <c r="N4" t="n">
-        <v>79.02</v>
+        <v>83.87</v>
       </c>
       <c r="O4" t="n">
-        <v>82.62</v>
+        <v>87.86</v>
       </c>
       <c r="P4" t="n">
-        <v>78.25</v>
+        <v>83.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>82.5</v>
+        <v>87.42</v>
       </c>
       <c r="R4" t="n">
-        <v>-14.148</v>
+        <v>-4.8193</v>
       </c>
       <c r="U4" t="n">
-        <v>-7.1187</v>
+        <v>-5.9423</v>
       </c>
       <c r="X4" t="n">
-        <v>14.3254</v>
+        <v>4.6625</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.1985</v>
+        <v>5.9636</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.04</v>
+        <v>47.86</v>
       </c>
       <c r="C5" t="n">
-        <v>49.38</v>
+        <v>48.29</v>
       </c>
       <c r="D5" t="n">
-        <v>45.96</v>
+        <v>39.52</v>
       </c>
       <c r="E5" t="n">
-        <v>46.61</v>
+        <v>40.62</v>
       </c>
       <c r="F5" t="n">
-        <v>40.56</v>
+        <v>39.75</v>
       </c>
       <c r="G5" t="n">
-        <v>40.59</v>
+        <v>39.91</v>
       </c>
       <c r="H5" t="n">
-        <v>38.56</v>
+        <v>37.32</v>
       </c>
       <c r="I5" t="n">
-        <v>38.78</v>
+        <v>37.89</v>
       </c>
       <c r="J5" t="n">
-        <v>41.94</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>43.71</v>
+        <v>49.76</v>
       </c>
       <c r="L5" t="n">
-        <v>40.8</v>
+        <v>41.57</v>
       </c>
       <c r="M5" t="n">
-        <v>43.1</v>
+        <v>48.74</v>
       </c>
       <c r="N5" t="n">
-        <v>83.87</v>
+        <v>85.27</v>
       </c>
       <c r="O5" t="n">
-        <v>87.86</v>
+        <v>90.72</v>
       </c>
       <c r="P5" t="n">
-        <v>83.78</v>
+        <v>84.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>87.42</v>
+        <v>89.42</v>
       </c>
       <c r="R5" t="n">
-        <v>-4.8193</v>
+        <v>-12.8513</v>
       </c>
       <c r="S5" t="n">
-        <v>-15.1929</v>
+        <v>-28.7868</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.9423</v>
+        <v>-2.295</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.9488</v>
+        <v>-14.6429</v>
       </c>
       <c r="X5" t="n">
-        <v>4.6625</v>
+        <v>13.0858</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.0561</v>
+        <v>35.3137</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.9636</v>
+        <v>2.2878</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.3602</v>
+        <v>16.1902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47.86</v>
+        <v>42.88</v>
       </c>
       <c r="C6" t="n">
-        <v>48.29</v>
+        <v>48.18</v>
       </c>
       <c r="D6" t="n">
-        <v>39.52</v>
+        <v>42.61</v>
       </c>
       <c r="E6" t="n">
-        <v>40.62</v>
+        <v>47.91</v>
       </c>
       <c r="F6" t="n">
-        <v>39.75</v>
+        <v>39.09</v>
       </c>
       <c r="G6" t="n">
-        <v>39.91</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>37.32</v>
+        <v>39.07</v>
       </c>
       <c r="I6" t="n">
-        <v>37.89</v>
+        <v>41.68</v>
       </c>
       <c r="J6" t="n">
-        <v>42</v>
+        <v>45.87</v>
       </c>
       <c r="K6" t="n">
-        <v>49.76</v>
+        <v>46.38</v>
       </c>
       <c r="L6" t="n">
-        <v>41.57</v>
+        <v>39.61</v>
       </c>
       <c r="M6" t="n">
-        <v>48.74</v>
+        <v>39.86</v>
       </c>
       <c r="N6" t="n">
-        <v>85.27</v>
+        <v>86.62</v>
       </c>
       <c r="O6" t="n">
-        <v>90.72</v>
+        <v>86.66</v>
       </c>
       <c r="P6" t="n">
-        <v>84.89</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>89.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>-12.8513</v>
+        <v>17.9468</v>
       </c>
       <c r="S6" t="n">
-        <v>-28.7868</v>
+        <v>-2.1646</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.295</v>
+        <v>10.0026</v>
       </c>
       <c r="V6" t="n">
-        <v>-14.6429</v>
+        <v>1.0914</v>
       </c>
       <c r="X6" t="n">
-        <v>13.0858</v>
+        <v>-18.2191</v>
       </c>
       <c r="Y6" t="n">
-        <v>35.3137</v>
+        <v>-3.2054</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2878</v>
+        <v>-9.986599999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.1902</v>
+        <v>-2.4364</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42.88</v>
+        <v>50.04</v>
       </c>
       <c r="C7" t="n">
-        <v>48.18</v>
+        <v>54.09</v>
       </c>
       <c r="D7" t="n">
-        <v>42.61</v>
+        <v>49.62</v>
       </c>
       <c r="E7" t="n">
-        <v>47.91</v>
+        <v>52.26</v>
       </c>
       <c r="F7" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>43.98</v>
       </c>
       <c r="H7" t="n">
-        <v>39.07</v>
+        <v>42.41</v>
       </c>
       <c r="I7" t="n">
-        <v>41.68</v>
+        <v>43.23</v>
       </c>
       <c r="J7" t="n">
-        <v>45.87</v>
+        <v>38.07</v>
       </c>
       <c r="K7" t="n">
-        <v>46.38</v>
+        <v>38.49</v>
       </c>
       <c r="L7" t="n">
-        <v>39.61</v>
+        <v>34.78</v>
       </c>
       <c r="M7" t="n">
-        <v>39.86</v>
+        <v>36.26</v>
       </c>
       <c r="N7" t="n">
-        <v>86.62</v>
+        <v>78.62</v>
       </c>
       <c r="O7" t="n">
-        <v>86.66</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>79.73999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>80.48999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="R7" t="n">
-        <v>17.9468</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1646</v>
+        <v>12.1219</v>
       </c>
       <c r="T7" t="n">
-        <v>-12.8275</v>
+        <v>-8.380100000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>10.0026</v>
+        <v>3.7188</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0914</v>
+        <v>11.475</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.2895</v>
+        <v>-2.6132</v>
       </c>
       <c r="X7" t="n">
-        <v>-18.2191</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>-3.2054</v>
+        <v>-15.8701</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4068</v>
+        <v>0.6663</v>
       </c>
       <c r="AA7" t="n">
-        <v>-9.986599999999999</v>
+        <v>-3.7769</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.4364</v>
+        <v>-11.4047</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5324</v>
+        <v>0.6367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C8" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D8" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E8" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F8" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G8" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H8" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I8" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J8" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K8" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L8" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M8" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N8" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O8" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P8" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>9.079499999999999</v>
+        <v>0.9376</v>
       </c>
       <c r="S8" t="n">
-        <v>12.1219</v>
+        <v>29.8621</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.380100000000001</v>
+        <v>7.719</v>
       </c>
       <c r="U8" t="n">
-        <v>3.7188</v>
+        <v>0.2313</v>
       </c>
       <c r="V8" t="n">
-        <v>11.475</v>
+        <v>14.3574</v>
       </c>
       <c r="W8" t="n">
-        <v>-2.6132</v>
+        <v>5.0934</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.031599999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y8" t="n">
-        <v>-15.8701</v>
+        <v>-26.2823</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6663</v>
+        <v>-12.7489</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3.7769</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB8" t="n">
-        <v>-11.4047</v>
+        <v>-13.5652</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.6367</v>
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C9" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D9" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E9" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F9" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G9" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H9" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I9" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J9" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K9" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L9" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M9" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N9" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P9" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="S9" t="n">
-        <v>29.8621</v>
+        <v>14.402</v>
       </c>
       <c r="T9" t="n">
-        <v>7.719</v>
+        <v>17.5928</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="V9" t="n">
-        <v>14.3574</v>
+        <v>5.8061</v>
       </c>
       <c r="W9" t="n">
-        <v>5.0934</v>
+        <v>13.7184</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y9" t="n">
-        <v>-26.2823</v>
+        <v>-13.3216</v>
       </c>
       <c r="Z9" t="n">
-        <v>-12.7489</v>
+        <v>-19.8376</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB9" t="n">
-        <v>-13.5652</v>
+        <v>-5.6777</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.3152</v>
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C10" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D10" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E10" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F10" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G10" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H10" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I10" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J10" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K10" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L10" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M10" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N10" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O10" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P10" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R10" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="S10" t="n">
-        <v>14.402</v>
+        <v>8.209</v>
       </c>
       <c r="T10" t="n">
-        <v>17.5928</v>
+        <v>39.2171</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="V10" t="n">
-        <v>5.8061</v>
+        <v>2.1282</v>
       </c>
       <c r="W10" t="n">
-        <v>13.7184</v>
+        <v>16.5215</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y10" t="n">
-        <v>-13.3216</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z10" t="n">
-        <v>-19.8376</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB10" t="n">
-        <v>-5.6777</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC10" t="n">
-        <v>-13.1549</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C11" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D11" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E11" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F11" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G11" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H11" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I11" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J11" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K11" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L11" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M11" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N11" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P11" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S11" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="T11" t="n">
-        <v>39.2171</v>
+        <v>40.8892</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="W11" t="n">
-        <v>16.5215</v>
+        <v>15.1631</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y11" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z11" t="n">
-        <v>-31.4116</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC11" t="n">
-        <v>-15.1085</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C12" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D12" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E12" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F12" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G12" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H12" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I12" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J12" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K12" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L12" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M12" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N12" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P12" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R12" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S12" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="T12" t="n">
-        <v>40.8892</v>
+        <v>37.7344</v>
       </c>
       <c r="U12" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="W12" t="n">
-        <v>15.1631</v>
+        <v>13.2547</v>
       </c>
       <c r="X12" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y12" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z12" t="n">
-        <v>-32.3633</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA12" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB12" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC12" t="n">
-        <v>-14.0266</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C13" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D13" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E13" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F13" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G13" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H13" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I13" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J13" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K13" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L13" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M13" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N13" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O13" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P13" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R13" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S13" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T13" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V13" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W13" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y13" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z13" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB13" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC13" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C14" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E14" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F14" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G14" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H14" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I14" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J14" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K14" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L14" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M14" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N14" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O14" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P14" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S14" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T14" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V14" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W14" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y14" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z14" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB14" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC14" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C15" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F15" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G15" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H15" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I15" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J15" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K15" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L15" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M15" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N15" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O15" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R15" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S15" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T15" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U15" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W15" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X15" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y15" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z15" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA15" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB15" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC15" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C16" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D16" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G16" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H16" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I16" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J16" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K16" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L16" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M16" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N16" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O16" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P16" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R16" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S16" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T16" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U16" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V16" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W16" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y16" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z16" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA16" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB16" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC16" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D17" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E17" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F17" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G17" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H17" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I17" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J17" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K17" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L17" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M17" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N17" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O17" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P17" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S17" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U17" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V17" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W17" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y17" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z17" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA17" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB17" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC17" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C18" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D18" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E18" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G18" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H18" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I18" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J18" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K18" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L18" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M18" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N18" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O18" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P18" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S18" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T18" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V18" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y18" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z18" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB18" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC18" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C19" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E19" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F19" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G19" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H19" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I19" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J19" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K19" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L19" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M19" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N19" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O19" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P19" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q19" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R19" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S19" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T19" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U19" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W19" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X19" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y19" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z19" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA19" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB19" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC19" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C20" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D20" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F20" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G20" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H20" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I20" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J20" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K20" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L20" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M20" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N20" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O20" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P20" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S20" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T20" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V20" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W20" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y20" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z20" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC20" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C21" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D21" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F21" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G21" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H21" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I21" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J21" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K21" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L21" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M21" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N21" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O21" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P21" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R21" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S21" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T21" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W21" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y21" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z21" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB21" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C22" t="n">
-        <v>106.09</v>
+        <v>116.7699</v>
       </c>
       <c r="D22" t="n">
-        <v>99.59999999999999</v>
+        <v>107.466</v>
       </c>
       <c r="E22" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F22" t="n">
-        <v>58.92</v>
+        <v>59.74</v>
       </c>
       <c r="G22" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H22" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I22" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J22" t="n">
-        <v>17.37</v>
+        <v>16.345</v>
       </c>
       <c r="K22" t="n">
-        <v>17.945</v>
+        <v>16.52</v>
       </c>
       <c r="L22" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M22" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N22" t="n">
-        <v>56.01</v>
+        <v>55.25</v>
       </c>
       <c r="O22" t="n">
-        <v>56.49</v>
+        <v>57.135</v>
       </c>
       <c r="P22" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R22" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S22" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T22" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U22" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V22" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W22" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y22" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z22" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA22" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB22" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC22" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.64</v>
+        <v>54.19</v>
       </c>
       <c r="C2" t="n">
-        <v>58.25</v>
+        <v>54.44</v>
       </c>
       <c r="D2" t="n">
-        <v>55.59</v>
+        <v>48.87</v>
       </c>
       <c r="E2" t="n">
-        <v>57.04</v>
+        <v>48.97</v>
       </c>
       <c r="F2" t="n">
-        <v>44.7</v>
+        <v>43.23</v>
       </c>
       <c r="G2" t="n">
-        <v>45.22</v>
+        <v>43.68</v>
       </c>
       <c r="H2" t="n">
-        <v>43.95</v>
+        <v>41.15</v>
       </c>
       <c r="I2" t="n">
-        <v>44.39</v>
+        <v>41.23</v>
       </c>
       <c r="J2" t="n">
-        <v>36.32</v>
+        <v>37.84</v>
       </c>
       <c r="K2" t="n">
-        <v>37.06</v>
+        <v>41.26</v>
       </c>
       <c r="L2" t="n">
-        <v>35.23</v>
+        <v>37.7</v>
       </c>
       <c r="M2" t="n">
-        <v>36.02</v>
+        <v>41.18</v>
       </c>
       <c r="N2" t="n">
-        <v>76.43000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="O2" t="n">
-        <v>77.8</v>
+        <v>82.62</v>
       </c>
       <c r="P2" t="n">
-        <v>75.51000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>76.95999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.19</v>
+        <v>48.04</v>
       </c>
       <c r="C3" t="n">
-        <v>54.44</v>
+        <v>49.38</v>
       </c>
       <c r="D3" t="n">
-        <v>48.87</v>
+        <v>45.96</v>
       </c>
       <c r="E3" t="n">
-        <v>48.97</v>
+        <v>46.61</v>
       </c>
       <c r="F3" t="n">
-        <v>43.23</v>
+        <v>40.56</v>
       </c>
       <c r="G3" t="n">
-        <v>43.68</v>
+        <v>40.59</v>
       </c>
       <c r="H3" t="n">
-        <v>41.15</v>
+        <v>38.56</v>
       </c>
       <c r="I3" t="n">
-        <v>41.23</v>
+        <v>38.78</v>
       </c>
       <c r="J3" t="n">
-        <v>37.84</v>
+        <v>41.94</v>
       </c>
       <c r="K3" t="n">
-        <v>41.26</v>
+        <v>43.71</v>
       </c>
       <c r="L3" t="n">
-        <v>37.7</v>
+        <v>40.8</v>
       </c>
       <c r="M3" t="n">
-        <v>41.18</v>
+        <v>43.1</v>
       </c>
       <c r="N3" t="n">
-        <v>79.02</v>
+        <v>83.87</v>
       </c>
       <c r="O3" t="n">
-        <v>82.62</v>
+        <v>87.86</v>
       </c>
       <c r="P3" t="n">
-        <v>78.25</v>
+        <v>83.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>82.5</v>
+        <v>87.42</v>
       </c>
       <c r="R3" t="n">
-        <v>-14.148</v>
+        <v>-4.8193</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.1187</v>
+        <v>-5.9423</v>
       </c>
       <c r="X3" t="n">
-        <v>14.3254</v>
+        <v>4.6625</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.1985</v>
+        <v>5.9636</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.04</v>
+        <v>47.86</v>
       </c>
       <c r="C4" t="n">
-        <v>49.38</v>
+        <v>48.29</v>
       </c>
       <c r="D4" t="n">
-        <v>45.96</v>
+        <v>39.52</v>
       </c>
       <c r="E4" t="n">
-        <v>46.61</v>
+        <v>40.62</v>
       </c>
       <c r="F4" t="n">
-        <v>40.56</v>
+        <v>39.75</v>
       </c>
       <c r="G4" t="n">
-        <v>40.59</v>
+        <v>39.91</v>
       </c>
       <c r="H4" t="n">
-        <v>38.56</v>
+        <v>37.32</v>
       </c>
       <c r="I4" t="n">
-        <v>38.78</v>
+        <v>37.89</v>
       </c>
       <c r="J4" t="n">
-        <v>41.94</v>
+        <v>42</v>
       </c>
       <c r="K4" t="n">
-        <v>43.71</v>
+        <v>49.76</v>
       </c>
       <c r="L4" t="n">
-        <v>40.8</v>
+        <v>41.57</v>
       </c>
       <c r="M4" t="n">
-        <v>43.1</v>
+        <v>48.74</v>
       </c>
       <c r="N4" t="n">
-        <v>83.87</v>
+        <v>85.27</v>
       </c>
       <c r="O4" t="n">
-        <v>87.86</v>
+        <v>90.72</v>
       </c>
       <c r="P4" t="n">
-        <v>83.78</v>
+        <v>84.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>87.42</v>
+        <v>89.42</v>
       </c>
       <c r="R4" t="n">
-        <v>-4.8193</v>
+        <v>-12.8513</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.9423</v>
+        <v>-2.295</v>
       </c>
       <c r="X4" t="n">
-        <v>4.6625</v>
+        <v>13.0858</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.9636</v>
+        <v>2.2878</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.86</v>
+        <v>42.88</v>
       </c>
       <c r="C5" t="n">
-        <v>48.29</v>
+        <v>48.18</v>
       </c>
       <c r="D5" t="n">
-        <v>39.52</v>
+        <v>42.61</v>
       </c>
       <c r="E5" t="n">
-        <v>40.62</v>
+        <v>47.91</v>
       </c>
       <c r="F5" t="n">
-        <v>39.75</v>
+        <v>39.09</v>
       </c>
       <c r="G5" t="n">
-        <v>39.91</v>
+        <v>42</v>
       </c>
       <c r="H5" t="n">
-        <v>37.32</v>
+        <v>39.07</v>
       </c>
       <c r="I5" t="n">
-        <v>37.89</v>
+        <v>41.68</v>
       </c>
       <c r="J5" t="n">
-        <v>42</v>
+        <v>45.87</v>
       </c>
       <c r="K5" t="n">
-        <v>49.76</v>
+        <v>46.38</v>
       </c>
       <c r="L5" t="n">
-        <v>41.57</v>
+        <v>39.61</v>
       </c>
       <c r="M5" t="n">
-        <v>48.74</v>
+        <v>39.86</v>
       </c>
       <c r="N5" t="n">
-        <v>85.27</v>
+        <v>86.62</v>
       </c>
       <c r="O5" t="n">
-        <v>90.72</v>
+        <v>86.66</v>
       </c>
       <c r="P5" t="n">
-        <v>84.89</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>89.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>-12.8513</v>
+        <v>17.9468</v>
       </c>
       <c r="S5" t="n">
-        <v>-28.7868</v>
+        <v>-2.1646</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.295</v>
+        <v>10.0026</v>
       </c>
       <c r="V5" t="n">
-        <v>-14.6429</v>
+        <v>1.0914</v>
       </c>
       <c r="X5" t="n">
-        <v>13.0858</v>
+        <v>-18.2191</v>
       </c>
       <c r="Y5" t="n">
-        <v>35.3137</v>
+        <v>-3.2054</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2878</v>
+        <v>-9.986599999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.1902</v>
+        <v>-2.4364</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.88</v>
+        <v>50.04</v>
       </c>
       <c r="C6" t="n">
-        <v>48.18</v>
+        <v>54.09</v>
       </c>
       <c r="D6" t="n">
-        <v>42.61</v>
+        <v>49.62</v>
       </c>
       <c r="E6" t="n">
-        <v>47.91</v>
+        <v>52.26</v>
       </c>
       <c r="F6" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>43.98</v>
       </c>
       <c r="H6" t="n">
-        <v>39.07</v>
+        <v>42.41</v>
       </c>
       <c r="I6" t="n">
-        <v>41.68</v>
+        <v>43.23</v>
       </c>
       <c r="J6" t="n">
-        <v>45.87</v>
+        <v>38.07</v>
       </c>
       <c r="K6" t="n">
-        <v>46.38</v>
+        <v>38.49</v>
       </c>
       <c r="L6" t="n">
-        <v>39.61</v>
+        <v>34.78</v>
       </c>
       <c r="M6" t="n">
-        <v>39.86</v>
+        <v>36.26</v>
       </c>
       <c r="N6" t="n">
-        <v>86.62</v>
+        <v>78.62</v>
       </c>
       <c r="O6" t="n">
-        <v>86.66</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>79.73999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>80.48999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="R6" t="n">
-        <v>17.9468</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.1646</v>
+        <v>12.1219</v>
       </c>
       <c r="U6" t="n">
-        <v>10.0026</v>
+        <v>3.7188</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0914</v>
+        <v>11.475</v>
       </c>
       <c r="X6" t="n">
-        <v>-18.2191</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>-3.2054</v>
+        <v>-15.8701</v>
       </c>
       <c r="AA6" t="n">
-        <v>-9.986599999999999</v>
+        <v>-3.7769</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.4364</v>
+        <v>-11.4047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C7" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D7" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E7" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F7" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G7" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H7" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I7" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J7" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K7" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L7" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M7" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N7" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O7" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P7" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>9.079499999999999</v>
+        <v>0.9376</v>
       </c>
       <c r="S7" t="n">
-        <v>12.1219</v>
+        <v>29.8621</v>
       </c>
       <c r="T7" t="n">
-        <v>-8.380100000000001</v>
+        <v>7.719</v>
       </c>
       <c r="U7" t="n">
-        <v>3.7188</v>
+        <v>0.2313</v>
       </c>
       <c r="V7" t="n">
-        <v>11.475</v>
+        <v>14.3574</v>
       </c>
       <c r="W7" t="n">
-        <v>-2.6132</v>
+        <v>5.0934</v>
       </c>
       <c r="X7" t="n">
-        <v>-9.031599999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y7" t="n">
-        <v>-15.8701</v>
+        <v>-26.2823</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6663</v>
+        <v>-12.7489</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.7769</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB7" t="n">
-        <v>-11.4047</v>
+        <v>-13.5652</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.6367</v>
+        <v>-6.3152</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C8" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D8" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E8" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F8" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G8" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I8" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J8" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K8" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L8" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M8" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N8" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P8" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="S8" t="n">
-        <v>29.8621</v>
+        <v>14.402</v>
       </c>
       <c r="T8" t="n">
-        <v>7.719</v>
+        <v>17.5928</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="V8" t="n">
-        <v>14.3574</v>
+        <v>5.8061</v>
       </c>
       <c r="W8" t="n">
-        <v>5.0934</v>
+        <v>13.7184</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y8" t="n">
-        <v>-26.2823</v>
+        <v>-13.3216</v>
       </c>
       <c r="Z8" t="n">
-        <v>-12.7489</v>
+        <v>-19.8376</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB8" t="n">
-        <v>-13.5652</v>
+        <v>-5.6777</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.3152</v>
+        <v>-13.1549</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C9" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D9" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E9" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F9" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G9" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H9" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I9" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J9" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K9" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L9" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M9" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N9" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O9" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P9" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R9" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="S9" t="n">
-        <v>14.402</v>
+        <v>8.209</v>
       </c>
       <c r="T9" t="n">
-        <v>17.5928</v>
+        <v>39.2171</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="V9" t="n">
-        <v>5.8061</v>
+        <v>2.1282</v>
       </c>
       <c r="W9" t="n">
-        <v>13.7184</v>
+        <v>16.5215</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y9" t="n">
-        <v>-13.3216</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z9" t="n">
-        <v>-19.8376</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB9" t="n">
-        <v>-5.6777</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC9" t="n">
-        <v>-13.1549</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C10" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D10" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E10" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F10" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G10" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H10" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I10" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J10" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K10" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L10" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M10" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N10" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P10" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S10" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="T10" t="n">
-        <v>39.2171</v>
+        <v>40.8892</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="W10" t="n">
-        <v>16.5215</v>
+        <v>15.1631</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y10" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z10" t="n">
-        <v>-31.4116</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC10" t="n">
-        <v>-15.1085</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C11" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D11" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E11" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F11" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G11" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H11" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I11" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J11" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K11" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L11" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M11" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N11" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P11" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R11" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S11" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="T11" t="n">
-        <v>40.8892</v>
+        <v>37.7344</v>
       </c>
       <c r="U11" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="W11" t="n">
-        <v>15.1631</v>
+        <v>13.2547</v>
       </c>
       <c r="X11" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y11" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z11" t="n">
-        <v>-32.3633</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA11" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB11" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC11" t="n">
-        <v>-14.0266</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C12" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D12" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E12" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F12" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G12" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H12" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I12" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J12" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K12" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L12" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M12" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N12" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O12" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P12" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R12" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T12" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V12" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W12" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y12" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z12" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB12" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC12" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C13" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E13" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F13" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G13" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H13" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I13" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J13" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K13" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L13" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M13" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N13" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O13" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P13" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S13" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T13" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V13" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W13" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y13" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z13" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB13" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC13" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C14" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F14" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G14" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H14" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I14" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J14" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K14" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L14" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M14" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N14" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O14" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R14" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S14" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T14" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W14" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y14" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z14" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB14" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC14" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C15" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D15" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G15" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H15" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I15" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J15" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K15" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M15" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N15" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O15" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P15" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R15" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S15" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T15" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U15" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V15" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W15" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y15" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z15" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA15" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB15" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC15" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D16" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E16" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F16" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G16" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H16" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I16" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J16" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K16" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L16" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M16" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N16" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O16" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P16" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q16" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S16" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U16" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V16" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W16" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y16" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z16" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA16" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB16" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC16" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C17" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D17" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E17" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G17" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H17" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I17" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J17" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K17" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L17" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M17" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N17" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O17" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P17" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S17" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T17" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V17" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y17" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z17" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB17" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC17" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C18" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E18" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F18" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G18" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H18" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I18" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J18" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K18" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L18" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M18" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N18" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O18" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P18" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R18" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S18" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T18" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U18" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W18" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X18" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y18" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z18" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA18" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB18" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC18" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C19" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D19" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F19" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G19" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H19" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I19" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J19" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K19" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L19" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M19" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N19" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O19" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P19" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S19" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T19" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V19" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W19" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y19" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z19" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB19" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC19" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C20" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D20" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F20" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G20" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H20" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I20" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J20" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K20" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L20" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M20" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N20" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O20" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P20" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R20" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S20" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T20" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V20" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y20" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z20" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB20" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC20" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C21" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D21" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E21" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F21" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G21" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H21" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I21" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J21" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K21" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L21" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M21" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N21" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O21" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P21" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R21" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S21" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T21" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U21" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V21" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W21" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X21" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y21" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z21" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA21" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB21" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C22" t="n">
-        <v>116.7699</v>
+        <v>130.1175</v>
       </c>
       <c r="D22" t="n">
-        <v>107.466</v>
+        <v>120.25</v>
       </c>
       <c r="E22" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F22" t="n">
-        <v>59.74</v>
+        <v>61.08</v>
       </c>
       <c r="G22" t="n">
-        <v>60.73</v>
+        <v>62.73</v>
       </c>
       <c r="H22" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I22" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J22" t="n">
-        <v>16.345</v>
+        <v>13.985</v>
       </c>
       <c r="K22" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L22" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M22" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N22" t="n">
-        <v>55.25</v>
+        <v>53.925</v>
       </c>
       <c r="O22" t="n">
-        <v>57.135</v>
+        <v>54.425</v>
       </c>
       <c r="P22" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R22" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S22" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T22" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W22" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y22" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z22" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB22" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24759,1804 +24759,1713 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.19</v>
+        <v>47.86</v>
       </c>
       <c r="C2" t="n">
-        <v>54.44</v>
+        <v>48.29</v>
       </c>
       <c r="D2" t="n">
-        <v>48.87</v>
+        <v>39.52</v>
       </c>
       <c r="E2" t="n">
-        <v>48.97</v>
+        <v>40.62</v>
       </c>
       <c r="F2" t="n">
-        <v>43.23</v>
+        <v>39.75</v>
       </c>
       <c r="G2" t="n">
-        <v>43.68</v>
+        <v>39.91</v>
       </c>
       <c r="H2" t="n">
-        <v>41.15</v>
+        <v>37.32</v>
       </c>
       <c r="I2" t="n">
-        <v>41.23</v>
+        <v>37.89</v>
       </c>
       <c r="J2" t="n">
-        <v>37.84</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>41.26</v>
+        <v>49.76</v>
       </c>
       <c r="L2" t="n">
-        <v>37.7</v>
+        <v>41.57</v>
       </c>
       <c r="M2" t="n">
-        <v>41.18</v>
+        <v>48.74</v>
       </c>
       <c r="N2" t="n">
-        <v>79.02</v>
+        <v>85.27</v>
       </c>
       <c r="O2" t="n">
-        <v>82.62</v>
+        <v>90.72</v>
       </c>
       <c r="P2" t="n">
-        <v>78.25</v>
+        <v>84.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>82.5</v>
+        <v>89.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48.04</v>
+        <v>42.88</v>
       </c>
       <c r="C3" t="n">
-        <v>49.38</v>
+        <v>48.18</v>
       </c>
       <c r="D3" t="n">
-        <v>45.96</v>
+        <v>42.61</v>
       </c>
       <c r="E3" t="n">
-        <v>46.61</v>
+        <v>47.91</v>
       </c>
       <c r="F3" t="n">
-        <v>40.56</v>
+        <v>39.09</v>
       </c>
       <c r="G3" t="n">
-        <v>40.59</v>
+        <v>42</v>
       </c>
       <c r="H3" t="n">
-        <v>38.56</v>
+        <v>39.07</v>
       </c>
       <c r="I3" t="n">
-        <v>38.78</v>
+        <v>41.68</v>
       </c>
       <c r="J3" t="n">
-        <v>41.94</v>
+        <v>45.87</v>
       </c>
       <c r="K3" t="n">
-        <v>43.71</v>
+        <v>46.38</v>
       </c>
       <c r="L3" t="n">
-        <v>40.8</v>
+        <v>39.61</v>
       </c>
       <c r="M3" t="n">
-        <v>43.1</v>
+        <v>39.86</v>
       </c>
       <c r="N3" t="n">
-        <v>83.87</v>
+        <v>86.62</v>
       </c>
       <c r="O3" t="n">
-        <v>87.86</v>
+        <v>86.66</v>
       </c>
       <c r="P3" t="n">
-        <v>83.78</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>87.42</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.8193</v>
+        <v>17.9468</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.9423</v>
+        <v>10.0026</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6625</v>
+        <v>-18.2191</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.9636</v>
+        <v>-9.986599999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.86</v>
+        <v>50.04</v>
       </c>
       <c r="C4" t="n">
-        <v>48.29</v>
+        <v>54.09</v>
       </c>
       <c r="D4" t="n">
-        <v>39.52</v>
+        <v>49.62</v>
       </c>
       <c r="E4" t="n">
-        <v>40.62</v>
+        <v>52.26</v>
       </c>
       <c r="F4" t="n">
-        <v>39.75</v>
+        <v>42.63</v>
       </c>
       <c r="G4" t="n">
-        <v>39.91</v>
+        <v>43.98</v>
       </c>
       <c r="H4" t="n">
-        <v>37.32</v>
+        <v>42.41</v>
       </c>
       <c r="I4" t="n">
-        <v>37.89</v>
+        <v>43.23</v>
       </c>
       <c r="J4" t="n">
-        <v>42</v>
+        <v>38.07</v>
       </c>
       <c r="K4" t="n">
-        <v>49.76</v>
+        <v>38.49</v>
       </c>
       <c r="L4" t="n">
-        <v>41.57</v>
+        <v>34.78</v>
       </c>
       <c r="M4" t="n">
-        <v>48.74</v>
+        <v>36.26</v>
       </c>
       <c r="N4" t="n">
-        <v>85.27</v>
+        <v>78.62</v>
       </c>
       <c r="O4" t="n">
-        <v>90.72</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>84.89</v>
+        <v>76.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>89.42</v>
+        <v>77.45</v>
       </c>
       <c r="R4" t="n">
-        <v>-12.8513</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.295</v>
+        <v>3.7188</v>
       </c>
       <c r="X4" t="n">
-        <v>13.0858</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2878</v>
+        <v>-3.7769</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.88</v>
+        <v>46.06</v>
       </c>
       <c r="C5" t="n">
-        <v>48.18</v>
+        <v>53.07</v>
       </c>
       <c r="D5" t="n">
-        <v>42.61</v>
+        <v>46.05</v>
       </c>
       <c r="E5" t="n">
-        <v>47.91</v>
+        <v>52.75</v>
       </c>
       <c r="F5" t="n">
-        <v>39.09</v>
+        <v>40.88</v>
       </c>
       <c r="G5" t="n">
-        <v>42</v>
+        <v>43.55</v>
       </c>
       <c r="H5" t="n">
-        <v>39.07</v>
+        <v>40.44</v>
       </c>
       <c r="I5" t="n">
-        <v>41.68</v>
+        <v>43.33</v>
       </c>
       <c r="J5" t="n">
-        <v>45.87</v>
+        <v>40.57</v>
       </c>
       <c r="K5" t="n">
-        <v>46.38</v>
+        <v>40.59</v>
       </c>
       <c r="L5" t="n">
-        <v>39.61</v>
+        <v>35.73</v>
       </c>
       <c r="M5" t="n">
-        <v>39.86</v>
+        <v>35.93</v>
       </c>
       <c r="N5" t="n">
-        <v>86.62</v>
+        <v>81.7</v>
       </c>
       <c r="O5" t="n">
-        <v>86.66</v>
+        <v>82.5</v>
       </c>
       <c r="P5" t="n">
-        <v>79.73999999999999</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>80.48999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>17.9468</v>
+        <v>0.9376</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.1646</v>
+        <v>29.8621</v>
       </c>
       <c r="U5" t="n">
-        <v>10.0026</v>
+        <v>0.2313</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0914</v>
+        <v>14.3574</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.2191</v>
+        <v>-0.9101</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3.2054</v>
+        <v>-26.2823</v>
       </c>
       <c r="AA5" t="n">
-        <v>-9.986599999999999</v>
+        <v>-0.2066</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.4364</v>
+        <v>-13.5652</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.04</v>
+        <v>53.75</v>
       </c>
       <c r="C6" t="n">
-        <v>54.09</v>
+        <v>55.6</v>
       </c>
       <c r="D6" t="n">
-        <v>49.62</v>
+        <v>52.88</v>
       </c>
       <c r="E6" t="n">
-        <v>52.26</v>
+        <v>54.81</v>
       </c>
       <c r="F6" t="n">
-        <v>42.63</v>
+        <v>43.6</v>
       </c>
       <c r="G6" t="n">
-        <v>43.98</v>
+        <v>44.59</v>
       </c>
       <c r="H6" t="n">
-        <v>42.41</v>
+        <v>43.27</v>
       </c>
       <c r="I6" t="n">
-        <v>43.23</v>
+        <v>44.1</v>
       </c>
       <c r="J6" t="n">
-        <v>38.07</v>
+        <v>35.18</v>
       </c>
       <c r="K6" t="n">
-        <v>38.49</v>
+        <v>35.87</v>
       </c>
       <c r="L6" t="n">
-        <v>34.78</v>
+        <v>34.01</v>
       </c>
       <c r="M6" t="n">
-        <v>36.26</v>
+        <v>34.55</v>
       </c>
       <c r="N6" t="n">
-        <v>78.62</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>79.06999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="P6" t="n">
-        <v>76.03</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>77.45</v>
+        <v>75.92</v>
       </c>
       <c r="R6" t="n">
-        <v>9.079499999999999</v>
+        <v>3.9052</v>
       </c>
       <c r="S6" t="n">
-        <v>12.1219</v>
+        <v>14.402</v>
       </c>
       <c r="U6" t="n">
-        <v>3.7188</v>
+        <v>1.7771</v>
       </c>
       <c r="V6" t="n">
-        <v>11.475</v>
+        <v>5.8061</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.031599999999999</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y6" t="n">
-        <v>-15.8701</v>
+        <v>-13.3216</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.7769</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB6" t="n">
-        <v>-11.4047</v>
+        <v>-5.6777</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46.06</v>
+        <v>54.32</v>
       </c>
       <c r="C7" t="n">
-        <v>53.07</v>
+        <v>56.6</v>
       </c>
       <c r="D7" t="n">
-        <v>46.05</v>
+        <v>52.13</v>
       </c>
       <c r="E7" t="n">
-        <v>52.75</v>
+        <v>56.55</v>
       </c>
       <c r="F7" t="n">
-        <v>40.88</v>
+        <v>43.45</v>
       </c>
       <c r="G7" t="n">
-        <v>43.55</v>
+        <v>44.21</v>
       </c>
       <c r="H7" t="n">
-        <v>40.44</v>
+        <v>41.84</v>
       </c>
       <c r="I7" t="n">
-        <v>43.33</v>
+        <v>44.15</v>
       </c>
       <c r="J7" t="n">
-        <v>40.57</v>
+        <v>34.82</v>
       </c>
       <c r="K7" t="n">
-        <v>40.59</v>
+        <v>36.26</v>
       </c>
       <c r="L7" t="n">
-        <v>35.73</v>
+        <v>33.43</v>
       </c>
       <c r="M7" t="n">
-        <v>35.93</v>
+        <v>33.43</v>
       </c>
       <c r="N7" t="n">
-        <v>81.7</v>
+        <v>77.08</v>
       </c>
       <c r="O7" t="n">
-        <v>82.5</v>
+        <v>79.88</v>
       </c>
       <c r="P7" t="n">
-        <v>76.93000000000001</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>77.29000000000001</v>
+        <v>75.91</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9376</v>
+        <v>3.1746</v>
       </c>
       <c r="S7" t="n">
-        <v>29.8621</v>
+        <v>8.209</v>
       </c>
       <c r="T7" t="n">
-        <v>7.719</v>
+        <v>39.2171</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2313</v>
+        <v>0.1134</v>
       </c>
       <c r="V7" t="n">
-        <v>14.3574</v>
+        <v>2.1282</v>
       </c>
       <c r="W7" t="n">
-        <v>5.0934</v>
+        <v>16.5215</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9101</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y7" t="n">
-        <v>-26.2823</v>
+        <v>-7.8047</v>
       </c>
       <c r="Z7" t="n">
-        <v>-12.7489</v>
+        <v>-31.4116</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.2066</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB7" t="n">
-        <v>-13.5652</v>
+        <v>-1.9884</v>
       </c>
       <c r="AC7" t="n">
-        <v>-6.3152</v>
+        <v>-15.1085</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53.75</v>
+        <v>66.33</v>
       </c>
       <c r="C8" t="n">
-        <v>55.6</v>
+        <v>67.98</v>
       </c>
       <c r="D8" t="n">
-        <v>52.88</v>
+        <v>63.56</v>
       </c>
       <c r="E8" t="n">
-        <v>54.81</v>
+        <v>67.5</v>
       </c>
       <c r="F8" t="n">
-        <v>43.6</v>
+        <v>48.64</v>
       </c>
       <c r="G8" t="n">
-        <v>44.59</v>
+        <v>48.92</v>
       </c>
       <c r="H8" t="n">
-        <v>43.27</v>
+        <v>47.15</v>
       </c>
       <c r="I8" t="n">
-        <v>44.1</v>
+        <v>48</v>
       </c>
       <c r="J8" t="n">
-        <v>35.18</v>
+        <v>27.7</v>
       </c>
       <c r="K8" t="n">
-        <v>35.87</v>
+        <v>29.31</v>
       </c>
       <c r="L8" t="n">
-        <v>34.01</v>
+        <v>26.75</v>
       </c>
       <c r="M8" t="n">
-        <v>34.55</v>
+        <v>26.96</v>
       </c>
       <c r="N8" t="n">
-        <v>76.84999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>77.45</v>
+        <v>70.73</v>
       </c>
       <c r="P8" t="n">
-        <v>75.09999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>75.92</v>
+        <v>69.2</v>
       </c>
       <c r="R8" t="n">
-        <v>3.9052</v>
+        <v>19.3634</v>
       </c>
       <c r="S8" t="n">
-        <v>14.402</v>
+        <v>27.9621</v>
       </c>
       <c r="T8" t="n">
-        <v>17.5928</v>
+        <v>40.8892</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7771</v>
+        <v>8.7203</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8061</v>
+        <v>10.7778</v>
       </c>
       <c r="W8" t="n">
-        <v>13.7184</v>
+        <v>15.1631</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.8408</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y8" t="n">
-        <v>-13.3216</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z8" t="n">
-        <v>-19.8376</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.7725</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.6777</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC8" t="n">
-        <v>-13.1549</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.32</v>
+        <v>68.12</v>
       </c>
       <c r="C9" t="n">
-        <v>56.6</v>
+        <v>72.28</v>
       </c>
       <c r="D9" t="n">
-        <v>52.13</v>
+        <v>68.12</v>
       </c>
       <c r="E9" t="n">
-        <v>56.55</v>
+        <v>71.98</v>
       </c>
       <c r="F9" t="n">
-        <v>43.45</v>
+        <v>48.02</v>
       </c>
       <c r="G9" t="n">
-        <v>44.21</v>
+        <v>49.09</v>
       </c>
       <c r="H9" t="n">
-        <v>41.84</v>
+        <v>47.31</v>
       </c>
       <c r="I9" t="n">
-        <v>44.15</v>
+        <v>48.96</v>
       </c>
       <c r="J9" t="n">
-        <v>34.82</v>
+        <v>26.76</v>
       </c>
       <c r="K9" t="n">
-        <v>36.26</v>
+        <v>26.76</v>
       </c>
       <c r="L9" t="n">
-        <v>33.43</v>
+        <v>25.09</v>
       </c>
       <c r="M9" t="n">
-        <v>33.43</v>
+        <v>25.2</v>
       </c>
       <c r="N9" t="n">
-        <v>77.08</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>79.88</v>
+        <v>70.3</v>
       </c>
       <c r="P9" t="n">
-        <v>75.79000000000001</v>
+        <v>67.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>75.91</v>
+        <v>67.86</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1746</v>
+        <v>6.637</v>
       </c>
       <c r="S9" t="n">
-        <v>8.209</v>
+        <v>31.3264</v>
       </c>
       <c r="T9" t="n">
-        <v>39.2171</v>
+        <v>37.7344</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1134</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1282</v>
+        <v>11.0204</v>
       </c>
       <c r="W9" t="n">
-        <v>16.5215</v>
+        <v>13.2547</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.2417</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y9" t="n">
-        <v>-7.8047</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z9" t="n">
-        <v>-31.4116</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.0132</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.9884</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC9" t="n">
-        <v>-15.1085</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66.33</v>
+        <v>74.3</v>
       </c>
       <c r="C10" t="n">
-        <v>67.98</v>
+        <v>78.3</v>
       </c>
       <c r="D10" t="n">
-        <v>63.56</v>
+        <v>74.3</v>
       </c>
       <c r="E10" t="n">
-        <v>67.5</v>
+        <v>76.39</v>
       </c>
       <c r="F10" t="n">
-        <v>48.64</v>
+        <v>49.36</v>
       </c>
       <c r="G10" t="n">
-        <v>48.92</v>
+        <v>49.81</v>
       </c>
       <c r="H10" t="n">
-        <v>47.15</v>
+        <v>48.82</v>
       </c>
       <c r="I10" t="n">
-        <v>48</v>
+        <v>49.17</v>
       </c>
       <c r="J10" t="n">
-        <v>27.7</v>
+        <v>24.38</v>
       </c>
       <c r="K10" t="n">
-        <v>29.31</v>
+        <v>24.42</v>
       </c>
       <c r="L10" t="n">
-        <v>26.75</v>
+        <v>23.01</v>
       </c>
       <c r="M10" t="n">
-        <v>26.96</v>
+        <v>23.69</v>
       </c>
       <c r="N10" t="n">
-        <v>68.20999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O10" t="n">
-        <v>70.73</v>
+        <v>68.13</v>
       </c>
       <c r="P10" t="n">
-        <v>67.75</v>
+        <v>66.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>69.2</v>
+        <v>67.62</v>
       </c>
       <c r="R10" t="n">
-        <v>19.3634</v>
+        <v>6.1267</v>
       </c>
       <c r="S10" t="n">
-        <v>27.9621</v>
+        <v>35.084</v>
       </c>
       <c r="T10" t="n">
-        <v>40.8892</v>
+        <v>44.8152</v>
       </c>
       <c r="U10" t="n">
-        <v>8.7203</v>
+        <v>0.4289</v>
       </c>
       <c r="V10" t="n">
-        <v>10.7778</v>
+        <v>11.3703</v>
       </c>
       <c r="W10" t="n">
-        <v>15.1631</v>
+        <v>13.478</v>
       </c>
       <c r="X10" t="n">
-        <v>-19.3539</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y10" t="n">
-        <v>-24.9652</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z10" t="n">
-        <v>-32.3633</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA10" t="n">
-        <v>-8.839399999999999</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB10" t="n">
-        <v>-10.4671</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC10" t="n">
-        <v>-14.0266</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68.12</v>
+        <v>75.59</v>
       </c>
       <c r="C11" t="n">
-        <v>72.28</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>68.12</v>
+        <v>75.25</v>
       </c>
       <c r="E11" t="n">
-        <v>71.98</v>
+        <v>80.56</v>
       </c>
       <c r="F11" t="n">
-        <v>48.02</v>
+        <v>48.78</v>
       </c>
       <c r="G11" t="n">
-        <v>49.09</v>
+        <v>50.74</v>
       </c>
       <c r="H11" t="n">
-        <v>47.31</v>
+        <v>48.46</v>
       </c>
       <c r="I11" t="n">
-        <v>48.96</v>
+        <v>50.66</v>
       </c>
       <c r="J11" t="n">
-        <v>26.76</v>
+        <v>23.92</v>
       </c>
       <c r="K11" t="n">
-        <v>26.76</v>
+        <v>24.03</v>
       </c>
       <c r="L11" t="n">
-        <v>25.09</v>
+        <v>22.32</v>
       </c>
       <c r="M11" t="n">
-        <v>25.2</v>
+        <v>22.42</v>
       </c>
       <c r="N11" t="n">
-        <v>69.31999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="O11" t="n">
-        <v>70.3</v>
+        <v>68.63</v>
       </c>
       <c r="P11" t="n">
-        <v>67.72</v>
+        <v>65.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>67.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>6.637</v>
+        <v>5.4588</v>
       </c>
       <c r="S11" t="n">
-        <v>31.3264</v>
+        <v>19.3481</v>
       </c>
       <c r="T11" t="n">
-        <v>37.7344</v>
+        <v>46.9805</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>3.0303</v>
       </c>
       <c r="V11" t="n">
-        <v>11.0204</v>
+        <v>5.5417</v>
       </c>
       <c r="W11" t="n">
-        <v>13.2547</v>
+        <v>14.8753</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.5282</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y11" t="n">
-        <v>-27.0622</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z11" t="n">
-        <v>-30.5019</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.9364</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB11" t="n">
-        <v>-10.6164</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC11" t="n">
-        <v>-12.3822</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74.3</v>
+        <v>83.27</v>
       </c>
       <c r="C12" t="n">
-        <v>78.3</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>74.3</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>76.39</v>
+        <v>85.31</v>
       </c>
       <c r="F12" t="n">
-        <v>49.36</v>
+        <v>51.39</v>
       </c>
       <c r="G12" t="n">
-        <v>49.81</v>
+        <v>53.43</v>
       </c>
       <c r="H12" t="n">
-        <v>48.82</v>
+        <v>51.38</v>
       </c>
       <c r="I12" t="n">
-        <v>49.17</v>
+        <v>53.41</v>
       </c>
       <c r="J12" t="n">
-        <v>24.38</v>
+        <v>21.6</v>
       </c>
       <c r="K12" t="n">
-        <v>24.42</v>
+        <v>22.34</v>
       </c>
       <c r="L12" t="n">
-        <v>23.01</v>
+        <v>21</v>
       </c>
       <c r="M12" t="n">
-        <v>23.69</v>
+        <v>21.05</v>
       </c>
       <c r="N12" t="n">
-        <v>67.38</v>
+        <v>64.67</v>
       </c>
       <c r="O12" t="n">
-        <v>68.13</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>66.75</v>
+        <v>62.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>67.62</v>
+        <v>62.02</v>
       </c>
       <c r="R12" t="n">
-        <v>6.1267</v>
+        <v>5.8962</v>
       </c>
       <c r="S12" t="n">
-        <v>35.084</v>
+        <v>18.519</v>
       </c>
       <c r="T12" t="n">
-        <v>44.8152</v>
+        <v>50.8576</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4289</v>
+        <v>5.4283</v>
       </c>
       <c r="V12" t="n">
-        <v>11.3703</v>
+        <v>9.0891</v>
       </c>
       <c r="W12" t="n">
-        <v>13.478</v>
+        <v>20.974</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.9921</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y12" t="n">
-        <v>-29.1355</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z12" t="n">
-        <v>-34.0662</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.3537</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB12" t="n">
-        <v>-10.9208</v>
+        <v>-8.606</v>
       </c>
       <c r="AC12" t="n">
-        <v>-12.5113</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>75.59</v>
+        <v>84.66</v>
       </c>
       <c r="C13" t="n">
-        <v>80.73999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D13" t="n">
-        <v>75.25</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>80.56</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>48.78</v>
+        <v>53.57</v>
       </c>
       <c r="G13" t="n">
-        <v>50.74</v>
+        <v>55.74</v>
       </c>
       <c r="H13" t="n">
-        <v>48.46</v>
+        <v>53.33</v>
       </c>
       <c r="I13" t="n">
-        <v>50.66</v>
+        <v>55.65</v>
       </c>
       <c r="J13" t="n">
-        <v>23.92</v>
+        <v>21.23</v>
       </c>
       <c r="K13" t="n">
-        <v>24.03</v>
+        <v>22.43</v>
       </c>
       <c r="L13" t="n">
-        <v>22.32</v>
+        <v>20.9</v>
       </c>
       <c r="M13" t="n">
-        <v>22.42</v>
+        <v>20.94</v>
       </c>
       <c r="N13" t="n">
-        <v>68.2</v>
+        <v>61.88</v>
       </c>
       <c r="O13" t="n">
-        <v>68.63</v>
+        <v>62.15</v>
       </c>
       <c r="P13" t="n">
-        <v>65.5</v>
+        <v>59.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.56999999999999</v>
+        <v>59.44</v>
       </c>
       <c r="R13" t="n">
-        <v>5.4588</v>
+        <v>0.7619</v>
       </c>
       <c r="S13" t="n">
-        <v>19.3481</v>
+        <v>12.5278</v>
       </c>
       <c r="T13" t="n">
-        <v>46.9805</v>
+        <v>27.3481</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0303</v>
+        <v>4.194</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5417</v>
+        <v>13.1788</v>
       </c>
       <c r="W13" t="n">
-        <v>14.8753</v>
+        <v>15.9375</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.3609</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y13" t="n">
-        <v>-16.8398</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z13" t="n">
-        <v>-35.1085</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3.0316</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB13" t="n">
-        <v>-5.2457</v>
+        <v>-12.097</v>
       </c>
       <c r="AC13" t="n">
-        <v>-13.6328</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83.27</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>85.56999999999999</v>
+        <v>89.39</v>
       </c>
       <c r="D14" t="n">
-        <v>80.70999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="E14" t="n">
-        <v>85.31</v>
+        <v>88.37</v>
       </c>
       <c r="F14" t="n">
-        <v>51.39</v>
+        <v>56.13</v>
       </c>
       <c r="G14" t="n">
-        <v>53.43</v>
+        <v>56.92</v>
       </c>
       <c r="H14" t="n">
-        <v>51.38</v>
+        <v>55.1</v>
       </c>
       <c r="I14" t="n">
-        <v>53.41</v>
+        <v>56.43</v>
       </c>
       <c r="J14" t="n">
-        <v>21.6</v>
+        <v>21.13</v>
       </c>
       <c r="K14" t="n">
-        <v>22.34</v>
+        <v>21.56</v>
       </c>
       <c r="L14" t="n">
-        <v>21</v>
+        <v>20.07</v>
       </c>
       <c r="M14" t="n">
-        <v>21.05</v>
+        <v>20.28</v>
       </c>
       <c r="N14" t="n">
-        <v>64.67</v>
+        <v>58.95</v>
       </c>
       <c r="O14" t="n">
-        <v>64.68000000000001</v>
+        <v>60.06</v>
       </c>
       <c r="P14" t="n">
-        <v>62.02</v>
+        <v>58.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>62.02</v>
+        <v>58.61</v>
       </c>
       <c r="R14" t="n">
-        <v>5.8962</v>
+        <v>2.8036</v>
       </c>
       <c r="S14" t="n">
-        <v>18.519</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>50.8576</v>
+        <v>22.7702</v>
       </c>
       <c r="U14" t="n">
-        <v>5.4283</v>
+        <v>1.4016</v>
       </c>
       <c r="V14" t="n">
-        <v>9.0891</v>
+        <v>11.3897</v>
       </c>
       <c r="W14" t="n">
-        <v>20.974</v>
+        <v>15.2574</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.1106</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y14" t="n">
-        <v>-16.4683</v>
+        <v>-9.545</v>
       </c>
       <c r="Z14" t="n">
-        <v>-37.0326</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA14" t="n">
-        <v>-5.4141</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB14" t="n">
-        <v>-8.606</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC14" t="n">
-        <v>-18.298</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84.66</v>
+        <v>93.2</v>
       </c>
       <c r="C15" t="n">
-        <v>85.98</v>
+        <v>94.75</v>
       </c>
       <c r="D15" t="n">
-        <v>79.76000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="E15" t="n">
-        <v>85.95999999999999</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>53.57</v>
+        <v>57.78</v>
       </c>
       <c r="G15" t="n">
-        <v>55.74</v>
+        <v>58.94</v>
       </c>
       <c r="H15" t="n">
-        <v>53.33</v>
+        <v>57.37</v>
       </c>
       <c r="I15" t="n">
-        <v>55.65</v>
+        <v>58.59</v>
       </c>
       <c r="J15" t="n">
-        <v>21.23</v>
+        <v>19.23</v>
       </c>
       <c r="K15" t="n">
-        <v>22.43</v>
+        <v>19.8</v>
       </c>
       <c r="L15" t="n">
-        <v>20.9</v>
+        <v>18.86</v>
       </c>
       <c r="M15" t="n">
-        <v>20.94</v>
+        <v>18.87</v>
       </c>
       <c r="N15" t="n">
-        <v>61.88</v>
+        <v>57.25</v>
       </c>
       <c r="O15" t="n">
-        <v>62.15</v>
+        <v>57.67</v>
       </c>
       <c r="P15" t="n">
-        <v>59.35</v>
+        <v>56.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>59.44</v>
+        <v>56.39</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7619</v>
+        <v>7.1404</v>
       </c>
       <c r="S15" t="n">
-        <v>12.5278</v>
+        <v>10.9835</v>
       </c>
       <c r="T15" t="n">
-        <v>27.3481</v>
+        <v>23.9429</v>
       </c>
       <c r="U15" t="n">
-        <v>4.194</v>
+        <v>3.8278</v>
       </c>
       <c r="V15" t="n">
-        <v>13.1788</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>15.9375</v>
+        <v>19.158</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5226</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y15" t="n">
-        <v>-11.6083</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z15" t="n">
-        <v>-22.3294</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA15" t="n">
-        <v>-4.1599</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB15" t="n">
-        <v>-12.097</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC15" t="n">
-        <v>-14.104</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.01000000000001</v>
+        <v>95.97</v>
       </c>
       <c r="C16" t="n">
-        <v>89.39</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>83.31</v>
+        <v>92.03</v>
       </c>
       <c r="E16" t="n">
-        <v>88.37</v>
+        <v>95.94</v>
       </c>
       <c r="F16" t="n">
-        <v>56.13</v>
+        <v>58.4</v>
       </c>
       <c r="G16" t="n">
-        <v>56.92</v>
+        <v>58.58</v>
       </c>
       <c r="H16" t="n">
-        <v>55.1</v>
+        <v>56.91</v>
       </c>
       <c r="I16" t="n">
-        <v>56.43</v>
+        <v>58.08</v>
       </c>
       <c r="J16" t="n">
-        <v>21.13</v>
+        <v>18.64</v>
       </c>
       <c r="K16" t="n">
-        <v>21.56</v>
+        <v>19.41</v>
       </c>
       <c r="L16" t="n">
-        <v>20.07</v>
+        <v>18.44</v>
       </c>
       <c r="M16" t="n">
-        <v>20.28</v>
+        <v>18.63</v>
       </c>
       <c r="N16" t="n">
-        <v>58.95</v>
+        <v>56.59</v>
       </c>
       <c r="O16" t="n">
-        <v>60.06</v>
+        <v>58.04</v>
       </c>
       <c r="P16" t="n">
-        <v>58.11</v>
+        <v>56.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>58.61</v>
+        <v>56.91</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8036</v>
+        <v>1.3308</v>
       </c>
       <c r="S16" t="n">
-        <v>9.694599999999999</v>
+        <v>11.6101</v>
       </c>
       <c r="T16" t="n">
-        <v>22.7702</v>
+        <v>19.0914</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4016</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>11.3897</v>
+        <v>4.3666</v>
       </c>
       <c r="W16" t="n">
-        <v>15.2574</v>
+        <v>14.6467</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.1519</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y16" t="n">
-        <v>-9.545</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z16" t="n">
-        <v>-19.5238</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.3964</v>
+        <v>0.9221</v>
       </c>
       <c r="AB16" t="n">
-        <v>-10.6146</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC16" t="n">
-        <v>-13.631</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93.2</v>
+        <v>97.97</v>
       </c>
       <c r="C17" t="n">
-        <v>94.75</v>
+        <v>99.95</v>
       </c>
       <c r="D17" t="n">
-        <v>90.66</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>94.68000000000001</v>
+        <v>98.09</v>
       </c>
       <c r="F17" t="n">
-        <v>57.78</v>
+        <v>58.48</v>
       </c>
       <c r="G17" t="n">
-        <v>58.94</v>
+        <v>58.97</v>
       </c>
       <c r="H17" t="n">
-        <v>57.37</v>
+        <v>56.82</v>
       </c>
       <c r="I17" t="n">
-        <v>58.59</v>
+        <v>57.4</v>
       </c>
       <c r="J17" t="n">
-        <v>19.23</v>
+        <v>18.25</v>
       </c>
       <c r="K17" t="n">
-        <v>19.8</v>
+        <v>18.76</v>
       </c>
       <c r="L17" t="n">
-        <v>18.86</v>
+        <v>17.85</v>
       </c>
       <c r="M17" t="n">
-        <v>18.87</v>
+        <v>18.2</v>
       </c>
       <c r="N17" t="n">
-        <v>57.25</v>
+        <v>56.52</v>
       </c>
       <c r="O17" t="n">
-        <v>57.67</v>
+        <v>58.15</v>
       </c>
       <c r="P17" t="n">
         <v>56.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>56.39</v>
+        <v>57.59</v>
       </c>
       <c r="R17" t="n">
-        <v>7.1404</v>
+        <v>2.241</v>
       </c>
       <c r="S17" t="n">
-        <v>10.9835</v>
+        <v>10.9992</v>
       </c>
       <c r="T17" t="n">
-        <v>23.9429</v>
+        <v>14.9807</v>
       </c>
       <c r="U17" t="n">
-        <v>3.8278</v>
+        <v>-1.1708</v>
       </c>
       <c r="V17" t="n">
-        <v>9.698600000000001</v>
+        <v>1.7189</v>
       </c>
       <c r="W17" t="n">
-        <v>19.158</v>
+        <v>7.4705</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.9527</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y17" t="n">
-        <v>-10.3563</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z17" t="n">
-        <v>-20.3461</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA17" t="n">
-        <v>-3.7877</v>
+        <v>1.1949</v>
       </c>
       <c r="AB17" t="n">
-        <v>-9.0777</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC17" t="n">
-        <v>-16.6075</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>95.97</v>
+        <v>102.94</v>
       </c>
       <c r="C18" t="n">
-        <v>96.93000000000001</v>
+        <v>106.09</v>
       </c>
       <c r="D18" t="n">
-        <v>92.03</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>95.94</v>
+        <v>105.64</v>
       </c>
       <c r="F18" t="n">
-        <v>58.4</v>
+        <v>58.93</v>
       </c>
       <c r="G18" t="n">
-        <v>58.58</v>
+        <v>60.3</v>
       </c>
       <c r="H18" t="n">
-        <v>56.91</v>
+        <v>58.49</v>
       </c>
       <c r="I18" t="n">
-        <v>58.08</v>
+        <v>60.21</v>
       </c>
       <c r="J18" t="n">
-        <v>18.64</v>
+        <v>17.37</v>
       </c>
       <c r="K18" t="n">
-        <v>19.41</v>
+        <v>17.95</v>
       </c>
       <c r="L18" t="n">
-        <v>18.44</v>
+        <v>16.72</v>
       </c>
       <c r="M18" t="n">
-        <v>18.63</v>
+        <v>16.8</v>
       </c>
       <c r="N18" t="n">
-        <v>56.59</v>
+        <v>56.05</v>
       </c>
       <c r="O18" t="n">
-        <v>58.04</v>
+        <v>56.49</v>
       </c>
       <c r="P18" t="n">
-        <v>56.41</v>
+        <v>54.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>56.91</v>
+        <v>54.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3308</v>
+        <v>7.697</v>
       </c>
       <c r="S18" t="n">
-        <v>11.6101</v>
+        <v>11.5758</v>
       </c>
       <c r="T18" t="n">
-        <v>19.0914</v>
+        <v>22.8944</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8705000000000001</v>
+        <v>4.8955</v>
       </c>
       <c r="V18" t="n">
-        <v>4.3666</v>
+        <v>2.765</v>
       </c>
       <c r="W18" t="n">
-        <v>14.6467</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2719</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y18" t="n">
-        <v>-11.0315</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z18" t="n">
-        <v>-16.9045</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.9221</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB18" t="n">
-        <v>-4.2564</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC18" t="n">
-        <v>-13.2073</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>97.97</v>
+        <v>108.62</v>
       </c>
       <c r="C19" t="n">
-        <v>99.95</v>
+        <v>116.77</v>
       </c>
       <c r="D19" t="n">
-        <v>95.31999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E19" t="n">
-        <v>98.09</v>
+        <v>112.77</v>
       </c>
       <c r="F19" t="n">
-        <v>58.48</v>
+        <v>59.8</v>
       </c>
       <c r="G19" t="n">
-        <v>58.97</v>
+        <v>60.73</v>
       </c>
       <c r="H19" t="n">
-        <v>56.82</v>
+        <v>57.59</v>
       </c>
       <c r="I19" t="n">
-        <v>57.4</v>
+        <v>59.22</v>
       </c>
       <c r="J19" t="n">
-        <v>18.25</v>
+        <v>16.35</v>
       </c>
       <c r="K19" t="n">
-        <v>18.76</v>
+        <v>16.52</v>
       </c>
       <c r="L19" t="n">
-        <v>17.85</v>
+        <v>15.06</v>
       </c>
       <c r="M19" t="n">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="N19" t="n">
-        <v>56.52</v>
+        <v>55.13</v>
       </c>
       <c r="O19" t="n">
-        <v>58.15</v>
+        <v>57.14</v>
       </c>
       <c r="P19" t="n">
-        <v>56.04</v>
+        <v>54.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.59</v>
+        <v>55.66</v>
       </c>
       <c r="R19" t="n">
-        <v>2.241</v>
+        <v>6.7493</v>
       </c>
       <c r="S19" t="n">
-        <v>10.9992</v>
+        <v>17.5422</v>
       </c>
       <c r="T19" t="n">
-        <v>14.9807</v>
+        <v>27.6112</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1708</v>
+        <v>-1.6442</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7189</v>
+        <v>1.9628</v>
       </c>
       <c r="W19" t="n">
-        <v>7.4705</v>
+        <v>4.9442</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3081</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y19" t="n">
-        <v>-10.2564</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z19" t="n">
-        <v>-13.5392</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.1949</v>
+        <v>1.6993</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.7403</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.1429</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>102.94</v>
+        <v>125.21</v>
       </c>
       <c r="C20" t="n">
-        <v>106.09</v>
+        <v>130.12</v>
       </c>
       <c r="D20" t="n">
-        <v>99.59999999999999</v>
+        <v>120.24</v>
       </c>
       <c r="E20" t="n">
-        <v>105.64</v>
+        <v>128.32</v>
       </c>
       <c r="F20" t="n">
-        <v>58.93</v>
+        <v>61.08</v>
       </c>
       <c r="G20" t="n">
-        <v>60.3</v>
+        <v>62.74</v>
       </c>
       <c r="H20" t="n">
-        <v>58.49</v>
+        <v>60.56</v>
       </c>
       <c r="I20" t="n">
-        <v>60.21</v>
+        <v>62.56</v>
       </c>
       <c r="J20" t="n">
-        <v>17.37</v>
+        <v>13.99</v>
       </c>
       <c r="K20" t="n">
-        <v>17.95</v>
+        <v>14.66</v>
       </c>
       <c r="L20" t="n">
-        <v>16.72</v>
+        <v>13.3</v>
       </c>
       <c r="M20" t="n">
-        <v>16.8</v>
+        <v>13.52</v>
       </c>
       <c r="N20" t="n">
-        <v>56.05</v>
+        <v>53.93</v>
       </c>
       <c r="O20" t="n">
-        <v>56.49</v>
+        <v>54.43</v>
       </c>
       <c r="P20" t="n">
-        <v>54.66</v>
+        <v>52.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>54.73</v>
+        <v>52.5</v>
       </c>
       <c r="R20" t="n">
-        <v>7.697</v>
+        <v>13.7891</v>
       </c>
       <c r="S20" t="n">
-        <v>11.5758</v>
+        <v>30.8186</v>
       </c>
       <c r="T20" t="n">
-        <v>22.8944</v>
+        <v>35.5302</v>
       </c>
       <c r="U20" t="n">
-        <v>4.8955</v>
+        <v>5.64</v>
       </c>
       <c r="V20" t="n">
-        <v>2.765</v>
+        <v>8.9895</v>
       </c>
       <c r="W20" t="n">
-        <v>8.194100000000001</v>
+        <v>6.7759</v>
       </c>
       <c r="X20" t="n">
-        <v>-7.6923</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y20" t="n">
-        <v>-10.9698</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z20" t="n">
-        <v>-19.7708</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA20" t="n">
-        <v>-4.9661</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.9438</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC20" t="n">
-        <v>-7.924</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>108.62</v>
+        <v>128.325</v>
       </c>
       <c r="C21" t="n">
-        <v>116.77</v>
+        <v>129.59</v>
       </c>
       <c r="D21" t="n">
-        <v>107.46</v>
+        <v>117.7902</v>
       </c>
       <c r="E21" t="n">
-        <v>112.77</v>
+        <v>123.39</v>
       </c>
       <c r="F21" t="n">
-        <v>59.8</v>
+        <v>62.41</v>
       </c>
       <c r="G21" t="n">
-        <v>60.73</v>
+        <v>62.6995</v>
       </c>
       <c r="H21" t="n">
-        <v>57.59</v>
+        <v>61.64</v>
       </c>
       <c r="I21" t="n">
-        <v>59.22</v>
+        <v>62.64</v>
       </c>
       <c r="J21" t="n">
-        <v>16.35</v>
+        <v>13.51</v>
       </c>
       <c r="K21" t="n">
-        <v>16.52</v>
+        <v>14.625</v>
       </c>
       <c r="L21" t="n">
-        <v>15.06</v>
+        <v>13.41</v>
       </c>
       <c r="M21" t="n">
-        <v>15.7</v>
+        <v>14.03</v>
       </c>
       <c r="N21" t="n">
-        <v>55.13</v>
+        <v>52.67</v>
       </c>
       <c r="O21" t="n">
-        <v>57.14</v>
+        <v>53.31</v>
       </c>
       <c r="P21" t="n">
-        <v>54.28</v>
+        <v>52.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>55.66</v>
+        <v>52.45</v>
       </c>
       <c r="R21" t="n">
-        <v>6.7493</v>
+        <v>-3.842</v>
       </c>
       <c r="S21" t="n">
-        <v>17.5422</v>
+        <v>16.8023</v>
       </c>
       <c r="T21" t="n">
-        <v>27.6112</v>
+        <v>28.6116</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.6442</v>
+        <v>0.1279</v>
       </c>
       <c r="V21" t="n">
-        <v>1.9628</v>
+        <v>4.0359</v>
       </c>
       <c r="W21" t="n">
-        <v>4.9442</v>
+        <v>7.8512</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.5476</v>
+        <v>3.7722</v>
       </c>
       <c r="Y21" t="n">
-        <v>-15.7273</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z21" t="n">
-        <v>-22.5838</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6993</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>-2.1965</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.0333</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>125.21</v>
-      </c>
-      <c r="C22" t="n">
-        <v>130.1175</v>
-      </c>
-      <c r="D22" t="n">
-        <v>120.25</v>
-      </c>
-      <c r="E22" t="n">
-        <v>128.32</v>
-      </c>
-      <c r="F22" t="n">
-        <v>61.08</v>
-      </c>
-      <c r="G22" t="n">
-        <v>62.73</v>
-      </c>
-      <c r="H22" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="I22" t="n">
-        <v>62.56</v>
-      </c>
-      <c r="J22" t="n">
-        <v>13.985</v>
-      </c>
-      <c r="K22" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="L22" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>13.52</v>
-      </c>
-      <c r="N22" t="n">
-        <v>53.925</v>
-      </c>
-      <c r="O22" t="n">
-        <v>54.425</v>
-      </c>
-      <c r="P22" t="n">
-        <v>52.37</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>13.7891</v>
-      </c>
-      <c r="S22" t="n">
-        <v>30.8186</v>
-      </c>
-      <c r="T22" t="n">
-        <v>35.5302</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="V22" t="n">
-        <v>8.9895</v>
-      </c>
-      <c r="W22" t="n">
-        <v>6.7759</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-13.8854</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>-25.7143</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-28.3519</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>-5.6773</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-8.8383</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26384,13 +26384,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>128.325</v>
+        <v>128.33</v>
       </c>
       <c r="C21" t="n">
         <v>129.59</v>
       </c>
       <c r="D21" t="n">
-        <v>117.7902</v>
+        <v>117.79</v>
       </c>
       <c r="E21" t="n">
         <v>123.39</v>
@@ -26399,7 +26399,7 @@
         <v>62.41</v>
       </c>
       <c r="G21" t="n">
-        <v>62.6995</v>
+        <v>62.7</v>
       </c>
       <c r="H21" t="n">
         <v>61.64</v>
@@ -26411,7 +26411,7 @@
         <v>13.51</v>
       </c>
       <c r="K21" t="n">
-        <v>14.625</v>
+        <v>14.63</v>
       </c>
       <c r="L21" t="n">
         <v>13.41</v>
@@ -26466,6 +26466,97 @@
       </c>
       <c r="AC21" t="n">
         <v>-7.8369</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="C22" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="D22" t="n">
+        <v>103.99</v>
+      </c>
+      <c r="E22" t="n">
+        <v>109.56</v>
+      </c>
+      <c r="F22" t="n">
+        <v>60.715</v>
+      </c>
+      <c r="G22" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="H22" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="I22" t="n">
+        <v>60.74</v>
+      </c>
+      <c r="J22" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="K22" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="M22" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="N22" t="n">
+        <v>54.085</v>
+      </c>
+      <c r="O22" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="P22" t="n">
+        <v>53.5799</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-11.2084</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-2.8465</v>
+      </c>
+      <c r="T22" t="n">
+        <v>11.6933</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-3.0332</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.5667</v>
+      </c>
+      <c r="W22" t="n">
+        <v>5.8188</v>
+      </c>
+      <c r="X22" t="n">
+        <v>11.119</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.7006</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-14.3407</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.0505</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-2.8926</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-6.1469</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.86</v>
+        <v>42.88</v>
       </c>
       <c r="C2" t="n">
-        <v>48.29</v>
+        <v>48.18</v>
       </c>
       <c r="D2" t="n">
-        <v>39.52</v>
+        <v>42.61</v>
       </c>
       <c r="E2" t="n">
-        <v>40.62</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="n">
-        <v>39.75</v>
+        <v>39.09</v>
       </c>
       <c r="G2" t="n">
-        <v>39.91</v>
+        <v>42</v>
       </c>
       <c r="H2" t="n">
-        <v>37.32</v>
+        <v>39.07</v>
       </c>
       <c r="I2" t="n">
-        <v>37.89</v>
+        <v>41.68</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>45.87</v>
       </c>
       <c r="K2" t="n">
-        <v>49.76</v>
+        <v>46.38</v>
       </c>
       <c r="L2" t="n">
-        <v>41.57</v>
+        <v>39.61</v>
       </c>
       <c r="M2" t="n">
-        <v>48.74</v>
+        <v>39.86</v>
       </c>
       <c r="N2" t="n">
-        <v>85.27</v>
+        <v>86.62</v>
       </c>
       <c r="O2" t="n">
-        <v>90.72</v>
+        <v>86.66</v>
       </c>
       <c r="P2" t="n">
-        <v>84.89</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.42</v>
+        <v>80.48999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.88</v>
+        <v>50.04</v>
       </c>
       <c r="C3" t="n">
-        <v>48.18</v>
+        <v>54.09</v>
       </c>
       <c r="D3" t="n">
-        <v>42.61</v>
+        <v>49.62</v>
       </c>
       <c r="E3" t="n">
-        <v>47.91</v>
+        <v>52.26</v>
       </c>
       <c r="F3" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>43.98</v>
       </c>
       <c r="H3" t="n">
-        <v>39.07</v>
+        <v>42.41</v>
       </c>
       <c r="I3" t="n">
-        <v>41.68</v>
+        <v>43.23</v>
       </c>
       <c r="J3" t="n">
-        <v>45.87</v>
+        <v>38.07</v>
       </c>
       <c r="K3" t="n">
-        <v>46.38</v>
+        <v>38.49</v>
       </c>
       <c r="L3" t="n">
-        <v>39.61</v>
+        <v>34.78</v>
       </c>
       <c r="M3" t="n">
-        <v>39.86</v>
+        <v>36.26</v>
       </c>
       <c r="N3" t="n">
-        <v>86.62</v>
+        <v>78.62</v>
       </c>
       <c r="O3" t="n">
-        <v>86.66</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>79.73999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="Q3" t="n">
-        <v>80.48999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="R3" t="n">
-        <v>17.9468</v>
+        <v>9.079499999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>10.0026</v>
+        <v>3.7188</v>
       </c>
       <c r="X3" t="n">
-        <v>-18.2191</v>
+        <v>-9.031599999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>-9.986599999999999</v>
+        <v>-3.7769</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C4" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D4" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E4" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F4" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G4" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H4" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I4" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J4" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K4" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L4" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M4" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N4" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O4" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P4" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>9.079499999999999</v>
+        <v>0.9376</v>
       </c>
       <c r="U4" t="n">
-        <v>3.7188</v>
+        <v>0.2313</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.031599999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3.7769</v>
+        <v>-0.2066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C5" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D5" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E5" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F5" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G5" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H5" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I5" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J5" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K5" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L5" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M5" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N5" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P5" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="S5" t="n">
-        <v>29.8621</v>
+        <v>14.402</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="V5" t="n">
-        <v>14.3574</v>
+        <v>5.8061</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="Y5" t="n">
-        <v>-26.2823</v>
+        <v>-13.3216</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
       <c r="AB5" t="n">
-        <v>-13.5652</v>
+        <v>-5.6777</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C6" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D6" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E6" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F6" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G6" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H6" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I6" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J6" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K6" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L6" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M6" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N6" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O6" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P6" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="S6" t="n">
-        <v>14.402</v>
+        <v>8.209</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8061</v>
+        <v>2.1282</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y6" t="n">
-        <v>-13.3216</v>
+        <v>-7.8047</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB6" t="n">
-        <v>-5.6777</v>
+        <v>-1.9884</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C7" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D7" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E7" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F7" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G7" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H7" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I7" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J7" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K7" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L7" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M7" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N7" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P7" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S7" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="T7" t="n">
-        <v>39.2171</v>
+        <v>40.8892</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="W7" t="n">
-        <v>16.5215</v>
+        <v>15.1631</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y7" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="Z7" t="n">
-        <v>-31.4116</v>
+        <v>-32.3633</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
       <c r="AC7" t="n">
-        <v>-15.1085</v>
+        <v>-14.0266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C8" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D8" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E8" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F8" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G8" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H8" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J8" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K8" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L8" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M8" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N8" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P8" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R8" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S8" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="T8" t="n">
-        <v>40.8892</v>
+        <v>37.7344</v>
       </c>
       <c r="U8" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="W8" t="n">
-        <v>15.1631</v>
+        <v>13.2547</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y8" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z8" t="n">
-        <v>-32.3633</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA8" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB8" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC8" t="n">
-        <v>-14.0266</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C9" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D9" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E9" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F9" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G9" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H9" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I9" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J9" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K9" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L9" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M9" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N9" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O9" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P9" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R9" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S9" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T9" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V9" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W9" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y9" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z9" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB9" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC9" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C10" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E10" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F10" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G10" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H10" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I10" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J10" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K10" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L10" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M10" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N10" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O10" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P10" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S10" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T10" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V10" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W10" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y10" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z10" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB10" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC10" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C11" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F11" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G11" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H11" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I11" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J11" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K11" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L11" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M11" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N11" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O11" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R11" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S11" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T11" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U11" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W11" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y11" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z11" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB11" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC11" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C12" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D12" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G12" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H12" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I12" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J12" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K12" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L12" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M12" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N12" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O12" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P12" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R12" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S12" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T12" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U12" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V12" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W12" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y12" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z12" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA12" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB12" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC12" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D13" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E13" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F13" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G13" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H13" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I13" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J13" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K13" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L13" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M13" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N13" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O13" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P13" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S13" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U13" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V13" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W13" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y13" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z13" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA13" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB13" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC13" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C14" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D14" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E14" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G14" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H14" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I14" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J14" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K14" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L14" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M14" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N14" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O14" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P14" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S14" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T14" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V14" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y14" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z14" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB14" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC14" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C15" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E15" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F15" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G15" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H15" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I15" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J15" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K15" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L15" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M15" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N15" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O15" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P15" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R15" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S15" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T15" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U15" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W15" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y15" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z15" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA15" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB15" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC15" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C16" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D16" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F16" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G16" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H16" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I16" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J16" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K16" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L16" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M16" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N16" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O16" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P16" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S16" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T16" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V16" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W16" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y16" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z16" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB16" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC16" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C17" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D17" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F17" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G17" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H17" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I17" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J17" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K17" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L17" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M17" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O17" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P17" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R17" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S17" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T17" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y17" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z17" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC17" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C18" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D18" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E18" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F18" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G18" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H18" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I18" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J18" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K18" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L18" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M18" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N18" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O18" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P18" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R18" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S18" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T18" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U18" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V18" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W18" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X18" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y18" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z18" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA18" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C19" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D19" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E19" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F19" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G19" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H19" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I19" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J19" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K19" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L19" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M19" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N19" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O19" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P19" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R19" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S19" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T19" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V19" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W19" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X19" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y19" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z19" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB19" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C20" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D20" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E20" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F20" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G20" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H20" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I20" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J20" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K20" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L20" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M20" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N20" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O20" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P20" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R20" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S20" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T20" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U20" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V20" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W20" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y20" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z20" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA20" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB20" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC20" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C21" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D21" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E21" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F21" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G21" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H21" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I21" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J21" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K21" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L21" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M21" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N21" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O21" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P21" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R21" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S21" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T21" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V21" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W21" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y21" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z21" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C22" t="n">
-        <v>115.62</v>
+        <v>118.315</v>
       </c>
       <c r="D22" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E22" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F22" t="n">
-        <v>60.715</v>
+        <v>61.01</v>
       </c>
       <c r="G22" t="n">
-        <v>61.33</v>
+        <v>61.8675</v>
       </c>
       <c r="H22" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I22" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J22" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K22" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L22" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M22" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N22" t="n">
-        <v>54.085</v>
+        <v>53.83</v>
       </c>
       <c r="O22" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P22" t="n">
-        <v>53.5799</v>
+        <v>53.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R22" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V22" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W22" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X22" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z22" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB22" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.88</v>
+        <v>50.04</v>
       </c>
       <c r="C2" t="n">
-        <v>48.18</v>
+        <v>54.09</v>
       </c>
       <c r="D2" t="n">
-        <v>42.61</v>
+        <v>49.62</v>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>52.26</v>
       </c>
       <c r="F2" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="G2" t="n">
-        <v>42</v>
+        <v>43.98</v>
       </c>
       <c r="H2" t="n">
-        <v>39.07</v>
+        <v>42.41</v>
       </c>
       <c r="I2" t="n">
-        <v>41.68</v>
+        <v>43.23</v>
       </c>
       <c r="J2" t="n">
-        <v>45.87</v>
+        <v>38.07</v>
       </c>
       <c r="K2" t="n">
-        <v>46.38</v>
+        <v>38.49</v>
       </c>
       <c r="L2" t="n">
-        <v>39.61</v>
+        <v>34.78</v>
       </c>
       <c r="M2" t="n">
-        <v>39.86</v>
+        <v>36.26</v>
       </c>
       <c r="N2" t="n">
-        <v>86.62</v>
+        <v>78.62</v>
       </c>
       <c r="O2" t="n">
-        <v>86.66</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>79.73999999999999</v>
+        <v>76.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>80.48999999999999</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C3" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D3" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E3" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F3" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G3" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H3" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I3" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J3" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K3" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L3" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M3" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N3" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O3" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P3" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.079499999999999</v>
+        <v>0.9376</v>
       </c>
       <c r="U3" t="n">
-        <v>3.7188</v>
+        <v>0.2313</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.031599999999999</v>
+        <v>-0.9101</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3.7769</v>
+        <v>-0.2066</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C4" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D4" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E4" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F4" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G4" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H4" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I4" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J4" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K4" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L4" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M4" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N4" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P4" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C5" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D5" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E5" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F5" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G5" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H5" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I5" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J5" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K5" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L5" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M5" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N5" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O5" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P5" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R5" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="S5" t="n">
-        <v>14.402</v>
+        <v>8.209</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8061</v>
+        <v>2.1282</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="Y5" t="n">
-        <v>-13.3216</v>
+        <v>-7.8047</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
       <c r="AB5" t="n">
-        <v>-5.6777</v>
+        <v>-1.9884</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C6" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D6" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E6" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F6" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G6" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H6" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I6" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J6" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K6" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L6" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M6" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N6" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P6" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S6" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y6" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C7" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D7" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E7" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F7" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G7" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H7" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I7" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J7" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K7" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L7" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M7" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N7" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P7" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R7" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S7" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="T7" t="n">
-        <v>40.8892</v>
+        <v>37.7344</v>
       </c>
       <c r="U7" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="W7" t="n">
-        <v>15.1631</v>
+        <v>13.2547</v>
       </c>
       <c r="X7" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y7" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="Z7" t="n">
-        <v>-32.3633</v>
+        <v>-30.5019</v>
       </c>
       <c r="AA7" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB7" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
       <c r="AC7" t="n">
-        <v>-14.0266</v>
+        <v>-12.3822</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C8" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D8" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E8" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F8" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G8" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H8" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I8" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J8" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K8" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L8" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M8" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N8" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O8" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P8" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R8" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S8" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T8" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V8" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W8" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y8" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z8" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB8" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC8" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C9" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E9" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F9" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G9" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H9" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I9" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J9" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K9" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L9" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M9" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N9" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O9" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P9" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S9" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T9" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V9" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W9" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y9" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z9" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB9" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC9" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C10" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F10" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G10" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H10" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I10" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J10" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K10" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L10" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M10" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N10" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O10" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R10" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S10" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T10" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U10" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W10" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y10" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z10" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB10" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC10" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C11" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D11" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G11" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H11" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I11" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J11" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K11" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L11" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M11" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N11" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O11" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P11" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R11" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S11" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T11" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U11" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V11" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W11" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y11" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z11" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA11" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB11" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC11" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D12" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E12" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F12" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G12" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H12" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I12" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J12" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K12" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L12" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M12" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N12" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O12" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P12" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S12" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U12" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V12" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W12" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y12" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z12" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA12" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB12" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC12" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C13" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D13" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E13" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G13" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H13" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I13" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J13" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K13" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L13" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M13" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N13" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O13" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P13" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S13" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T13" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V13" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y13" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z13" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB13" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC13" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C14" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E14" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F14" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G14" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H14" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I14" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J14" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K14" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L14" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M14" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N14" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O14" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P14" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R14" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S14" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T14" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U14" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W14" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y14" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z14" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB14" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC14" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C15" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D15" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F15" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G15" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H15" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I15" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J15" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K15" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L15" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M15" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N15" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O15" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P15" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S15" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T15" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V15" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W15" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y15" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z15" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB15" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC15" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C16" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D16" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F16" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G16" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H16" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I16" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J16" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K16" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L16" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M16" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N16" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O16" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P16" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R16" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S16" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T16" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W16" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y16" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z16" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C17" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D17" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E17" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F17" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G17" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H17" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I17" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J17" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K17" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L17" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M17" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N17" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O17" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P17" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R17" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S17" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T17" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U17" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V17" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W17" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y17" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z17" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA17" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC17" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C18" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D18" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E18" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F18" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G18" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H18" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I18" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J18" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K18" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L18" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N18" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O18" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P18" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R18" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S18" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T18" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W18" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X18" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y18" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z18" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC18" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C19" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D19" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E19" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F19" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G19" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H19" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I19" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J19" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K19" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L19" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M19" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N19" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O19" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P19" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R19" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S19" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T19" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U19" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V19" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W19" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X19" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y19" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z19" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA19" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C20" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D20" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E20" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F20" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G20" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H20" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I20" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J20" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K20" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L20" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M20" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N20" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O20" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P20" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R20" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S20" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T20" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V20" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W20" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y20" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z20" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC20" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C21" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D21" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E21" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F21" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G21" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H21" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I21" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J21" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K21" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L21" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M21" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N21" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O21" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P21" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R21" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V21" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W21" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X21" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z21" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB21" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C22" t="n">
-        <v>118.315</v>
+        <v>127.45</v>
       </c>
       <c r="D22" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E22" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F22" t="n">
-        <v>61.01</v>
+        <v>62.885</v>
       </c>
       <c r="G22" t="n">
-        <v>61.8675</v>
+        <v>63.8</v>
       </c>
       <c r="H22" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I22" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J22" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K22" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L22" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M22" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N22" t="n">
-        <v>53.83</v>
+        <v>52.215</v>
       </c>
       <c r="O22" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P22" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R22" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S22" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T22" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W22" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z22" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA22" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC22" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.04</v>
+        <v>46.06</v>
       </c>
       <c r="C2" t="n">
-        <v>54.09</v>
+        <v>53.07</v>
       </c>
       <c r="D2" t="n">
-        <v>49.62</v>
+        <v>46.05</v>
       </c>
       <c r="E2" t="n">
-        <v>52.26</v>
+        <v>52.75</v>
       </c>
       <c r="F2" t="n">
-        <v>42.63</v>
+        <v>40.88</v>
       </c>
       <c r="G2" t="n">
-        <v>43.98</v>
+        <v>43.55</v>
       </c>
       <c r="H2" t="n">
-        <v>42.41</v>
+        <v>40.44</v>
       </c>
       <c r="I2" t="n">
-        <v>43.23</v>
+        <v>43.33</v>
       </c>
       <c r="J2" t="n">
-        <v>38.07</v>
+        <v>40.57</v>
       </c>
       <c r="K2" t="n">
-        <v>38.49</v>
+        <v>40.59</v>
       </c>
       <c r="L2" t="n">
-        <v>34.78</v>
+        <v>35.73</v>
       </c>
       <c r="M2" t="n">
-        <v>36.26</v>
+        <v>35.93</v>
       </c>
       <c r="N2" t="n">
-        <v>78.62</v>
+        <v>81.7</v>
       </c>
       <c r="O2" t="n">
-        <v>79.06999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="P2" t="n">
-        <v>76.03</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>77.45</v>
+        <v>77.29000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C3" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D3" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E3" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F3" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G3" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H3" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I3" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J3" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K3" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L3" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M3" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N3" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P3" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9376</v>
+        <v>3.9052</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2313</v>
+        <v>1.7771</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9101</v>
+        <v>-3.8408</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2066</v>
+        <v>-1.7725</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C4" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D4" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E4" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F4" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G4" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H4" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I4" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J4" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K4" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L4" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M4" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N4" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O4" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P4" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C5" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D5" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E5" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F5" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G5" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H5" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I5" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J5" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K5" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L5" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M5" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N5" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P5" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="S5" t="n">
-        <v>8.209</v>
+        <v>27.9621</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1282</v>
+        <v>10.7778</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="Y5" t="n">
-        <v>-7.8047</v>
+        <v>-24.9652</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.9884</v>
+        <v>-10.4671</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C6" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D6" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E6" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F6" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G6" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H6" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I6" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J6" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K6" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L6" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M6" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N6" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P6" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R6" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S6" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="U6" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y6" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="AA6" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB6" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C7" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D7" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E7" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F7" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G7" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H7" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I7" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J7" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K7" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L7" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M7" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N7" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O7" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P7" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R7" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S7" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="T7" t="n">
-        <v>37.7344</v>
+        <v>44.8152</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V7" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="W7" t="n">
-        <v>13.2547</v>
+        <v>13.478</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y7" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="Z7" t="n">
-        <v>-30.5019</v>
+        <v>-34.0662</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB7" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
       <c r="AC7" t="n">
-        <v>-12.3822</v>
+        <v>-12.5113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C8" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E8" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F8" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G8" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H8" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I8" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J8" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K8" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L8" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M8" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N8" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O8" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P8" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S8" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T8" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V8" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W8" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y8" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z8" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB8" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC8" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C9" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F9" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G9" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H9" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I9" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J9" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K9" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L9" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M9" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N9" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O9" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R9" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S9" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T9" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U9" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W9" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y9" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z9" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA9" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB9" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC9" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C10" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D10" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G10" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H10" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I10" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J10" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K10" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M10" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N10" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O10" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P10" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R10" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S10" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T10" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U10" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V10" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W10" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y10" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z10" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA10" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB10" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC10" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D11" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E11" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F11" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G11" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H11" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I11" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J11" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K11" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L11" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M11" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N11" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O11" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P11" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S11" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U11" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V11" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W11" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y11" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z11" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA11" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB11" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC11" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C12" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D12" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E12" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G12" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H12" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I12" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J12" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K12" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L12" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M12" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N12" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O12" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P12" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S12" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T12" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V12" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y12" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z12" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB12" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC12" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C13" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E13" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F13" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G13" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H13" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I13" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J13" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K13" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L13" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M13" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N13" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O13" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P13" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R13" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S13" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T13" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U13" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W13" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y13" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z13" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB13" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC13" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C14" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D14" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F14" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G14" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H14" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I14" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J14" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K14" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L14" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M14" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N14" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O14" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P14" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S14" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T14" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V14" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W14" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y14" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z14" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB14" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC14" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C15" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D15" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F15" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G15" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H15" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I15" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J15" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K15" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L15" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M15" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N15" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O15" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P15" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R15" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S15" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T15" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y15" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z15" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC15" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C16" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D16" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E16" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F16" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G16" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H16" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I16" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J16" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K16" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L16" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M16" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N16" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O16" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P16" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R16" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S16" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T16" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U16" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V16" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W16" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y16" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z16" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA16" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C17" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D17" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E17" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F17" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G17" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H17" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I17" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J17" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K17" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L17" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M17" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N17" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O17" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P17" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q17" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R17" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S17" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T17" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W17" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y17" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z17" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC17" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C18" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D18" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E18" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F18" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G18" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H18" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I18" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J18" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K18" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L18" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M18" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N18" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O18" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P18" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R18" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S18" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T18" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U18" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V18" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W18" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X18" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y18" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z18" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA18" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C19" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D19" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E19" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F19" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G19" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H19" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I19" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J19" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K19" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L19" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M19" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N19" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O19" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P19" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R19" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S19" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T19" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V19" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W19" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X19" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y19" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z19" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB19" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C20" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D20" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E20" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F20" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H20" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I20" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J20" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K20" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L20" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M20" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N20" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O20" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P20" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R20" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V20" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W20" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X20" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z20" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC20" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C21" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D21" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E21" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F21" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G21" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H21" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I21" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J21" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K21" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L21" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M21" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N21" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O21" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P21" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R21" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S21" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T21" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X21" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z21" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C22" t="n">
-        <v>127.45</v>
+        <v>131.3799</v>
       </c>
       <c r="D22" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E22" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F22" t="n">
-        <v>62.885</v>
+        <v>63.89</v>
       </c>
       <c r="G22" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H22" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I22" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J22" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K22" t="n">
-        <v>14.49</v>
+        <v>13.8899</v>
       </c>
       <c r="L22" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M22" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N22" t="n">
-        <v>52.215</v>
+        <v>51.36</v>
       </c>
       <c r="O22" t="n">
-        <v>54.09</v>
+        <v>51.445</v>
       </c>
       <c r="P22" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R22" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T22" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W22" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y22" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z22" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA22" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB22" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC22" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.06</v>
+        <v>53.75</v>
       </c>
       <c r="C2" t="n">
-        <v>53.07</v>
+        <v>55.6</v>
       </c>
       <c r="D2" t="n">
-        <v>46.05</v>
+        <v>52.88</v>
       </c>
       <c r="E2" t="n">
-        <v>52.75</v>
+        <v>54.81</v>
       </c>
       <c r="F2" t="n">
-        <v>40.88</v>
+        <v>43.6</v>
       </c>
       <c r="G2" t="n">
-        <v>43.55</v>
+        <v>44.59</v>
       </c>
       <c r="H2" t="n">
-        <v>40.44</v>
+        <v>43.27</v>
       </c>
       <c r="I2" t="n">
-        <v>43.33</v>
+        <v>44.1</v>
       </c>
       <c r="J2" t="n">
-        <v>40.57</v>
+        <v>35.18</v>
       </c>
       <c r="K2" t="n">
-        <v>40.59</v>
+        <v>35.87</v>
       </c>
       <c r="L2" t="n">
-        <v>35.73</v>
+        <v>34.01</v>
       </c>
       <c r="M2" t="n">
-        <v>35.93</v>
+        <v>34.55</v>
       </c>
       <c r="N2" t="n">
-        <v>81.7</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>82.5</v>
+        <v>77.45</v>
       </c>
       <c r="P2" t="n">
-        <v>76.93000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>77.29000000000001</v>
+        <v>75.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C3" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D3" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E3" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F3" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G3" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H3" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I3" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J3" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K3" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L3" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M3" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N3" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O3" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P3" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9052</v>
+        <v>3.1746</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7771</v>
+        <v>0.1134</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.8408</v>
+        <v>-3.2417</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.7725</v>
+        <v>-0.0132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C4" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D4" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E4" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F4" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G4" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H4" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I4" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J4" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K4" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L4" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M4" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N4" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P4" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C5" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D5" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E5" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F5" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G5" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H5" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I5" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J5" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K5" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L5" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M5" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N5" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P5" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R5" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="S5" t="n">
-        <v>27.9621</v>
+        <v>31.3264</v>
       </c>
       <c r="U5" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>10.7778</v>
+        <v>11.0204</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="Y5" t="n">
-        <v>-24.9652</v>
+        <v>-27.0622</v>
       </c>
       <c r="AA5" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
       <c r="AB5" t="n">
-        <v>-10.4671</v>
+        <v>-10.6164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C6" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D6" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E6" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F6" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G6" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H6" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I6" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J6" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K6" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L6" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M6" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N6" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O6" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P6" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R6" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V6" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y6" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB6" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C7" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E7" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F7" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G7" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H7" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I7" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J7" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K7" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L7" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M7" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N7" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O7" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P7" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S7" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="T7" t="n">
-        <v>44.8152</v>
+        <v>46.9805</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V7" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="W7" t="n">
-        <v>13.478</v>
+        <v>14.8753</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y7" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="Z7" t="n">
-        <v>-34.0662</v>
+        <v>-35.1085</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB7" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
       <c r="AC7" t="n">
-        <v>-12.5113</v>
+        <v>-13.6328</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C8" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F8" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G8" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H8" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I8" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J8" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K8" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L8" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M8" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N8" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O8" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R8" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S8" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T8" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U8" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V8" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W8" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y8" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z8" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC8" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C9" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D9" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G9" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H9" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I9" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J9" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K9" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L9" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M9" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N9" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O9" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P9" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R9" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S9" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T9" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U9" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V9" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W9" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y9" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z9" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA9" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB9" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC9" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D10" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E10" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F10" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G10" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H10" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I10" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J10" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K10" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L10" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M10" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N10" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O10" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P10" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S10" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U10" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V10" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W10" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y10" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z10" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA10" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB10" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC10" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C11" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D11" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E11" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G11" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H11" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I11" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J11" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K11" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L11" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M11" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N11" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O11" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P11" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S11" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T11" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V11" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y11" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z11" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB11" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC11" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C12" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E12" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F12" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G12" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H12" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I12" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J12" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K12" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L12" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M12" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N12" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O12" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P12" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R12" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S12" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T12" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U12" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W12" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y12" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z12" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB12" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC12" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C13" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D13" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F13" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G13" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H13" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I13" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J13" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K13" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L13" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M13" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N13" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O13" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P13" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S13" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T13" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V13" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W13" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y13" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z13" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB13" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC13" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C14" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D14" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F14" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G14" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H14" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I14" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J14" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K14" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L14" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M14" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N14" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O14" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P14" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R14" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S14" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T14" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W14" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y14" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z14" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC14" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C15" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D15" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E15" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F15" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G15" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H15" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I15" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J15" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K15" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L15" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M15" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N15" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O15" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P15" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R15" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S15" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T15" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U15" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V15" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W15" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y15" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z15" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA15" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC15" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C16" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D16" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E16" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F16" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G16" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H16" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I16" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J16" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K16" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L16" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M16" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N16" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O16" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P16" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R16" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S16" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T16" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V16" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W16" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y16" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z16" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC16" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C17" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D17" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E17" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F17" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G17" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H17" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I17" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J17" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K17" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L17" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M17" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N17" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O17" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P17" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R17" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S17" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T17" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U17" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V17" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W17" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y17" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z17" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA17" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C18" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D18" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E18" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F18" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G18" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H18" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I18" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J18" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K18" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L18" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M18" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N18" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O18" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P18" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R18" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S18" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T18" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V18" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W18" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X18" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y18" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z18" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB18" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C19" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D19" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E19" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F19" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G19" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H19" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I19" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J19" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K19" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L19" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M19" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N19" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O19" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P19" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R19" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W19" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X19" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z19" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB19" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C20" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D20" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E20" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G20" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H20" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I20" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J20" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K20" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L20" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M20" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N20" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O20" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P20" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R20" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S20" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T20" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U20" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X20" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z20" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C21" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D21" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E21" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F21" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G21" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H21" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I21" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J21" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K21" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L21" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M21" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N21" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O21" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P21" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R21" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T21" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U21" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W21" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X21" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y21" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z21" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA21" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB21" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>124.39</v>
+        <v>132.195</v>
       </c>
       <c r="C22" t="n">
-        <v>131.3799</v>
+        <v>133.67</v>
       </c>
       <c r="D22" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E22" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F22" t="n">
-        <v>63.89</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H22" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I22" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J22" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K22" t="n">
-        <v>13.8899</v>
+        <v>13.6386</v>
       </c>
       <c r="L22" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M22" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N22" t="n">
-        <v>51.36</v>
+        <v>50.11</v>
       </c>
       <c r="O22" t="n">
-        <v>51.445</v>
+        <v>51.43</v>
       </c>
       <c r="P22" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S22" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W22" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y22" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z22" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA22" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB22" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26475,7 +26475,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>132.195</v>
+        <v>132.2</v>
       </c>
       <c r="C22" t="n">
         <v>133.67</v>
@@ -26487,7 +26487,7 @@
         <v>127.55</v>
       </c>
       <c r="F22" t="n">
-        <v>65.45999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="G22" t="n">
         <v>66.05</v>
@@ -26502,7 +26502,7 @@
         <v>12.8</v>
       </c>
       <c r="K22" t="n">
-        <v>13.6386</v>
+        <v>13.64</v>
       </c>
       <c r="L22" t="n">
         <v>12.65</v>
@@ -26511,7 +26511,7 @@
         <v>13.26</v>
       </c>
       <c r="N22" t="n">
-        <v>50.11</v>
+        <v>50.12</v>
       </c>
       <c r="O22" t="n">
         <v>51.43</v>
@@ -26557,6 +26557,97 @@
       </c>
       <c r="AC22" t="n">
         <v>-3.6988</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>135</v>
+      </c>
+      <c r="C23" t="n">
+        <v>147.26</v>
+      </c>
+      <c r="D23" t="n">
+        <v>134.02</v>
+      </c>
+      <c r="E23" t="n">
+        <v>144.16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="G23" t="n">
+        <v>67.76860000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>67.39</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>12.585</v>
+      </c>
+      <c r="L23" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="N23" t="n">
+        <v>49.365</v>
+      </c>
+      <c r="O23" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="P23" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="R23" t="n">
+        <v>13.0223</v>
+      </c>
+      <c r="S23" t="n">
+        <v>13.5297</v>
+      </c>
+      <c r="T23" t="n">
+        <v>31.5809</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.8207</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.0592</v>
+      </c>
+      <c r="W23" t="n">
+        <v>10.9483</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-13.1976</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-13.4586</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-26.1706</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-3.8012</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-5.9245</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-10.1018</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.75</v>
+        <v>54.32</v>
       </c>
       <c r="C2" t="n">
-        <v>55.6</v>
+        <v>56.6</v>
       </c>
       <c r="D2" t="n">
-        <v>52.88</v>
+        <v>52.13</v>
       </c>
       <c r="E2" t="n">
-        <v>54.81</v>
+        <v>56.55</v>
       </c>
       <c r="F2" t="n">
-        <v>43.6</v>
+        <v>43.45</v>
       </c>
       <c r="G2" t="n">
-        <v>44.59</v>
+        <v>44.21</v>
       </c>
       <c r="H2" t="n">
-        <v>43.27</v>
+        <v>41.84</v>
       </c>
       <c r="I2" t="n">
-        <v>44.1</v>
+        <v>44.15</v>
       </c>
       <c r="J2" t="n">
-        <v>35.18</v>
+        <v>34.82</v>
       </c>
       <c r="K2" t="n">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="L2" t="n">
-        <v>34.01</v>
+        <v>33.43</v>
       </c>
       <c r="M2" t="n">
-        <v>34.55</v>
+        <v>33.43</v>
       </c>
       <c r="N2" t="n">
-        <v>76.84999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="O2" t="n">
-        <v>77.45</v>
+        <v>79.88</v>
       </c>
       <c r="P2" t="n">
-        <v>75.09999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C3" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D3" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E3" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F3" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G3" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H3" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I3" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J3" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K3" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L3" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M3" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N3" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P3" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1746</v>
+        <v>19.3634</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1134</v>
+        <v>8.7203</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.2417</v>
+        <v>-19.3539</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0132</v>
+        <v>-8.839399999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C4" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D4" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E4" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F4" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G4" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H4" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I4" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J4" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K4" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L4" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M4" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N4" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P4" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R4" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="U4" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="AA4" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C5" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D5" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E5" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F5" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G5" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H5" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I5" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J5" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K5" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L5" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M5" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N5" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O5" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P5" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R5" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="S5" t="n">
-        <v>31.3264</v>
+        <v>35.084</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="V5" t="n">
-        <v>11.0204</v>
+        <v>11.3703</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="Y5" t="n">
-        <v>-27.0622</v>
+        <v>-29.1355</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
       <c r="AB5" t="n">
-        <v>-10.6164</v>
+        <v>-10.9208</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C6" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E6" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F6" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G6" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H6" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I6" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J6" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K6" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L6" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M6" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N6" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O6" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P6" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S6" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V6" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y6" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB6" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C7" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F7" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G7" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H7" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I7" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J7" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K7" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L7" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M7" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N7" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O7" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R7" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S7" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="T7" t="n">
-        <v>46.9805</v>
+        <v>50.8576</v>
       </c>
       <c r="U7" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="W7" t="n">
-        <v>14.8753</v>
+        <v>20.974</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y7" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="Z7" t="n">
-        <v>-35.1085</v>
+        <v>-37.0326</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB7" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
       <c r="AC7" t="n">
-        <v>-13.6328</v>
+        <v>-18.298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C8" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D8" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G8" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H8" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I8" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J8" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K8" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L8" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M8" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N8" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O8" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P8" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R8" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S8" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T8" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U8" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V8" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W8" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y8" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z8" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA8" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB8" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC8" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D9" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E9" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F9" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G9" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H9" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I9" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J9" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K9" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L9" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M9" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N9" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O9" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P9" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S9" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U9" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V9" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W9" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y9" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z9" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA9" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB9" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC9" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C10" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D10" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E10" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G10" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H10" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I10" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J10" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K10" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L10" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M10" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N10" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O10" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P10" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S10" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T10" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V10" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y10" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z10" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB10" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC10" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C11" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E11" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F11" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G11" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H11" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I11" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J11" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K11" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L11" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M11" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N11" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O11" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P11" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R11" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S11" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T11" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U11" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W11" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y11" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z11" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB11" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC11" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C12" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D12" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F12" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G12" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H12" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I12" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J12" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K12" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L12" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M12" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N12" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O12" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P12" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S12" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T12" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V12" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W12" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y12" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z12" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB12" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC12" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C13" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D13" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F13" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G13" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H13" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I13" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J13" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K13" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L13" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M13" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N13" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O13" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P13" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R13" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S13" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T13" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W13" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y13" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z13" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC13" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C14" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D14" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E14" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F14" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G14" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H14" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I14" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J14" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K14" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L14" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M14" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N14" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O14" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P14" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R14" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S14" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T14" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U14" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V14" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W14" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y14" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z14" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA14" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC14" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C15" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D15" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E15" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F15" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G15" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H15" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I15" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J15" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K15" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L15" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M15" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N15" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O15" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P15" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R15" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S15" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T15" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W15" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y15" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z15" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C16" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D16" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E16" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F16" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G16" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H16" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I16" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J16" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K16" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L16" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M16" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N16" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O16" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P16" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R16" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S16" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T16" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U16" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V16" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W16" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X16" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y16" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z16" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA16" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC16" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C17" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D17" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E17" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F17" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G17" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H17" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I17" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J17" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K17" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L17" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M17" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N17" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O17" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P17" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R17" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S17" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T17" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V17" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W17" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X17" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y17" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z17" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB17" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC17" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C18" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D18" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E18" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F18" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H18" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I18" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J18" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K18" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L18" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M18" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N18" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O18" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P18" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R18" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W18" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X18" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z18" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C19" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D19" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E19" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F19" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G19" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H19" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I19" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J19" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K19" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L19" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M19" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N19" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O19" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P19" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R19" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S19" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T19" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W19" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z19" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C20" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D20" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E20" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F20" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G20" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H20" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I20" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J20" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K20" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L20" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M20" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N20" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O20" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P20" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R20" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T20" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U20" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W20" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X20" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y20" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z20" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB20" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC20" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C21" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D21" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E21" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F21" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G21" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H21" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I21" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J21" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K21" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L21" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M21" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N21" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O21" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P21" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R21" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S21" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U21" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W21" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y21" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z21" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA21" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB21" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC21" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C22" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D22" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E22" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F22" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G22" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H22" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I22" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J22" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K22" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L22" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M22" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N22" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O22" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P22" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R22" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S22" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T22" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V22" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W22" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X22" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y22" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z22" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB22" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC22" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C23" t="n">
-        <v>147.26</v>
+        <v>165.9936</v>
       </c>
       <c r="D23" t="n">
-        <v>134.02</v>
+        <v>149.0617</v>
       </c>
       <c r="E23" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F23" t="n">
-        <v>66.38</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>67.76860000000001</v>
+        <v>71.6587</v>
       </c>
       <c r="H23" t="n">
-        <v>66.26000000000001</v>
+        <v>68.88</v>
       </c>
       <c r="I23" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K23" t="n">
-        <v>12.585</v>
+        <v>11.14</v>
       </c>
       <c r="L23" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N23" t="n">
-        <v>49.365</v>
+        <v>47.26</v>
       </c>
       <c r="O23" t="n">
-        <v>49.49</v>
+        <v>47.535</v>
       </c>
       <c r="P23" t="n">
-        <v>48.3</v>
+        <v>45.5201</v>
       </c>
       <c r="Q23" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R23" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S23" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T23" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U23" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V23" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X23" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y23" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z23" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA23" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB23" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC23" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.32</v>
+        <v>66.33</v>
       </c>
       <c r="C2" t="n">
-        <v>56.6</v>
+        <v>67.98</v>
       </c>
       <c r="D2" t="n">
-        <v>52.13</v>
+        <v>63.56</v>
       </c>
       <c r="E2" t="n">
-        <v>56.55</v>
+        <v>67.5</v>
       </c>
       <c r="F2" t="n">
-        <v>43.45</v>
+        <v>48.64</v>
       </c>
       <c r="G2" t="n">
-        <v>44.21</v>
+        <v>48.92</v>
       </c>
       <c r="H2" t="n">
-        <v>41.84</v>
+        <v>47.15</v>
       </c>
       <c r="I2" t="n">
-        <v>44.15</v>
+        <v>48</v>
       </c>
       <c r="J2" t="n">
-        <v>34.82</v>
+        <v>27.7</v>
       </c>
       <c r="K2" t="n">
-        <v>36.26</v>
+        <v>29.31</v>
       </c>
       <c r="L2" t="n">
-        <v>33.43</v>
+        <v>26.75</v>
       </c>
       <c r="M2" t="n">
-        <v>33.43</v>
+        <v>26.96</v>
       </c>
       <c r="N2" t="n">
-        <v>77.08</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>79.88</v>
+        <v>70.73</v>
       </c>
       <c r="P2" t="n">
-        <v>75.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>75.91</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C3" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D3" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E3" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F3" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G3" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H3" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I3" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J3" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K3" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L3" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M3" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N3" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P3" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
       <c r="R3" t="n">
-        <v>19.3634</v>
+        <v>6.637</v>
       </c>
       <c r="U3" t="n">
-        <v>8.7203</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.3539</v>
+        <v>-6.5282</v>
       </c>
       <c r="AA3" t="n">
-        <v>-8.839399999999999</v>
+        <v>-1.9364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C4" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D4" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E4" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F4" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G4" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H4" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I4" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J4" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K4" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L4" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M4" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N4" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O4" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P4" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R4" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C5" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E5" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F5" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G5" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H5" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I5" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J5" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K5" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L5" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M5" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N5" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O5" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P5" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="S5" t="n">
-        <v>35.084</v>
+        <v>19.3481</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="V5" t="n">
-        <v>11.3703</v>
+        <v>5.5417</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="Y5" t="n">
-        <v>-29.1355</v>
+        <v>-16.8398</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
       <c r="AB5" t="n">
-        <v>-10.9208</v>
+        <v>-5.2457</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C6" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F6" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G6" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H6" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I6" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J6" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K6" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L6" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M6" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N6" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O6" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R6" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S6" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="U6" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y6" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB6" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C7" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D7" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G7" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H7" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I7" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J7" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K7" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L7" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M7" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N7" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O7" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P7" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R7" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S7" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="T7" t="n">
-        <v>50.8576</v>
+        <v>27.3481</v>
       </c>
       <c r="U7" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V7" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="W7" t="n">
-        <v>20.974</v>
+        <v>15.9375</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y7" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="Z7" t="n">
-        <v>-37.0326</v>
+        <v>-22.3294</v>
       </c>
       <c r="AA7" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB7" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
       <c r="AC7" t="n">
-        <v>-18.298</v>
+        <v>-14.104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D8" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E8" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F8" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G8" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H8" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I8" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J8" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K8" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L8" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M8" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N8" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O8" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P8" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S8" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U8" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V8" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W8" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y8" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z8" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA8" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB8" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC8" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C9" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D9" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E9" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G9" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H9" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I9" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J9" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K9" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L9" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M9" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N9" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O9" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P9" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S9" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T9" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V9" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y9" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z9" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB9" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC9" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C10" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E10" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F10" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G10" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H10" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I10" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J10" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K10" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L10" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M10" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N10" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O10" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P10" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R10" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S10" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T10" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U10" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W10" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y10" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z10" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB10" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC10" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C11" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D11" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F11" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G11" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H11" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I11" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J11" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K11" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L11" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M11" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N11" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O11" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P11" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S11" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T11" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V11" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W11" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y11" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z11" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC11" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C12" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D12" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F12" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G12" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H12" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I12" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J12" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K12" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L12" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M12" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N12" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O12" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P12" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R12" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S12" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T12" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V12" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y12" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z12" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC12" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C13" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D13" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E13" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F13" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G13" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H13" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I13" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J13" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K13" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L13" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M13" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N13" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O13" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P13" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R13" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S13" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T13" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U13" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V13" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W13" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y13" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z13" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA13" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB13" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC13" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C14" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D14" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E14" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F14" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G14" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H14" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I14" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J14" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K14" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L14" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M14" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N14" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O14" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P14" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q14" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R14" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S14" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T14" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W14" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y14" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z14" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC14" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C15" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D15" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E15" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F15" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G15" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H15" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I15" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J15" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K15" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L15" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M15" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N15" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O15" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P15" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R15" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S15" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T15" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U15" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V15" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W15" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y15" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z15" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA15" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C16" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D16" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E16" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F16" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G16" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H16" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I16" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J16" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K16" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L16" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M16" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N16" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O16" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P16" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R16" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S16" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T16" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V16" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W16" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X16" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y16" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z16" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB16" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C17" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D17" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E17" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F17" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H17" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I17" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J17" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K17" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L17" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M17" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N17" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O17" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P17" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R17" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W17" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X17" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z17" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C18" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D18" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E18" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G18" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H18" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I18" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J18" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K18" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L18" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M18" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N18" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O18" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P18" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R18" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S18" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T18" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X18" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z18" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C19" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D19" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E19" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F19" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G19" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H19" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I19" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J19" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K19" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L19" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M19" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N19" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O19" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P19" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R19" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T19" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U19" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W19" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y19" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z19" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C20" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D20" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E20" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F20" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G20" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H20" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I20" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J20" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K20" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L20" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M20" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N20" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O20" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P20" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S20" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U20" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V20" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W20" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y20" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z20" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB20" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C21" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D21" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E21" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F21" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G21" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H21" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I21" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J21" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K21" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L21" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M21" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N21" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O21" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P21" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S21" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W21" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X21" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y21" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z21" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C22" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D22" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E22" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F22" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H22" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I22" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K22" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L22" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N22" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O22" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P22" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R22" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S22" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T22" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U22" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V22" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y22" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z22" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA22" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB22" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC22" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>157.84</v>
+        <v>162.115</v>
       </c>
       <c r="C23" t="n">
-        <v>165.9936</v>
+        <v>162.9</v>
       </c>
       <c r="D23" t="n">
-        <v>149.0617</v>
+        <v>147.61</v>
       </c>
       <c r="E23" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F23" t="n">
-        <v>69.23999999999999</v>
+        <v>71.86499999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>71.6587</v>
+        <v>73.295</v>
       </c>
       <c r="H23" t="n">
-        <v>68.88</v>
+        <v>70.38500000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J23" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K23" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N23" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O23" t="n">
-        <v>47.535</v>
+        <v>46.357</v>
       </c>
       <c r="P23" t="n">
-        <v>45.5201</v>
+        <v>44.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R23" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S23" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T23" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U23" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V23" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X23" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z23" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB23" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC23" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.33</v>
+        <v>68.12</v>
       </c>
       <c r="C2" t="n">
-        <v>67.98</v>
+        <v>72.28</v>
       </c>
       <c r="D2" t="n">
-        <v>63.56</v>
+        <v>68.12</v>
       </c>
       <c r="E2" t="n">
-        <v>67.5</v>
+        <v>71.98</v>
       </c>
       <c r="F2" t="n">
-        <v>48.64</v>
+        <v>48.02</v>
       </c>
       <c r="G2" t="n">
-        <v>48.92</v>
+        <v>49.09</v>
       </c>
       <c r="H2" t="n">
-        <v>47.15</v>
+        <v>47.31</v>
       </c>
       <c r="I2" t="n">
-        <v>48</v>
+        <v>48.96</v>
       </c>
       <c r="J2" t="n">
-        <v>27.7</v>
+        <v>26.76</v>
       </c>
       <c r="K2" t="n">
-        <v>29.31</v>
+        <v>26.76</v>
       </c>
       <c r="L2" t="n">
-        <v>26.75</v>
+        <v>25.09</v>
       </c>
       <c r="M2" t="n">
-        <v>26.96</v>
+        <v>25.2</v>
       </c>
       <c r="N2" t="n">
-        <v>68.20999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>70.73</v>
+        <v>70.3</v>
       </c>
       <c r="P2" t="n">
-        <v>67.75</v>
+        <v>67.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>69.2</v>
+        <v>67.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="C3" t="n">
-        <v>72.28</v>
+        <v>78.3</v>
       </c>
       <c r="D3" t="n">
-        <v>68.12</v>
+        <v>74.3</v>
       </c>
       <c r="E3" t="n">
-        <v>71.98</v>
+        <v>76.39</v>
       </c>
       <c r="F3" t="n">
-        <v>48.02</v>
+        <v>49.36</v>
       </c>
       <c r="G3" t="n">
-        <v>49.09</v>
+        <v>49.81</v>
       </c>
       <c r="H3" t="n">
-        <v>47.31</v>
+        <v>48.82</v>
       </c>
       <c r="I3" t="n">
-        <v>48.96</v>
+        <v>49.17</v>
       </c>
       <c r="J3" t="n">
-        <v>26.76</v>
+        <v>24.38</v>
       </c>
       <c r="K3" t="n">
-        <v>26.76</v>
+        <v>24.42</v>
       </c>
       <c r="L3" t="n">
-        <v>25.09</v>
+        <v>23.01</v>
       </c>
       <c r="M3" t="n">
-        <v>25.2</v>
+        <v>23.69</v>
       </c>
       <c r="N3" t="n">
-        <v>69.31999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="O3" t="n">
-        <v>70.3</v>
+        <v>68.13</v>
       </c>
       <c r="P3" t="n">
-        <v>67.72</v>
+        <v>66.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>67.86</v>
+        <v>67.62</v>
       </c>
       <c r="R3" t="n">
-        <v>6.637</v>
+        <v>6.1267</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0.4289</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.5282</v>
+        <v>-5.9921</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.9364</v>
+        <v>-0.3537</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.3</v>
+        <v>75.59</v>
       </c>
       <c r="C4" t="n">
-        <v>78.3</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>74.3</v>
+        <v>75.25</v>
       </c>
       <c r="E4" t="n">
-        <v>76.39</v>
+        <v>80.56</v>
       </c>
       <c r="F4" t="n">
-        <v>49.36</v>
+        <v>48.78</v>
       </c>
       <c r="G4" t="n">
-        <v>49.81</v>
+        <v>50.74</v>
       </c>
       <c r="H4" t="n">
-        <v>48.82</v>
+        <v>48.46</v>
       </c>
       <c r="I4" t="n">
-        <v>49.17</v>
+        <v>50.66</v>
       </c>
       <c r="J4" t="n">
-        <v>24.38</v>
+        <v>23.92</v>
       </c>
       <c r="K4" t="n">
-        <v>24.42</v>
+        <v>24.03</v>
       </c>
       <c r="L4" t="n">
-        <v>23.01</v>
+        <v>22.32</v>
       </c>
       <c r="M4" t="n">
-        <v>23.69</v>
+        <v>22.42</v>
       </c>
       <c r="N4" t="n">
-        <v>67.38</v>
+        <v>68.2</v>
       </c>
       <c r="O4" t="n">
-        <v>68.13</v>
+        <v>68.63</v>
       </c>
       <c r="P4" t="n">
-        <v>66.75</v>
+        <v>65.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>67.62</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>6.1267</v>
+        <v>5.4588</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4289</v>
+        <v>3.0303</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.9921</v>
+        <v>-5.3609</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.3537</v>
+        <v>-3.0316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C5" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F5" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G5" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H5" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I5" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J5" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K5" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L5" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M5" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N5" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O5" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
       <c r="R5" t="n">
-        <v>5.4588</v>
+        <v>5.8962</v>
       </c>
       <c r="S5" t="n">
-        <v>19.3481</v>
+        <v>18.519</v>
       </c>
       <c r="U5" t="n">
-        <v>3.0303</v>
+        <v>5.4283</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5417</v>
+        <v>9.0891</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.3609</v>
+        <v>-6.1106</v>
       </c>
       <c r="Y5" t="n">
-        <v>-16.8398</v>
+        <v>-16.4683</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.0316</v>
+        <v>-5.4141</v>
       </c>
       <c r="AB5" t="n">
-        <v>-5.2457</v>
+        <v>-8.606</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C6" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D6" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G6" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H6" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I6" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J6" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K6" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L6" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M6" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N6" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O6" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P6" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R6" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="S6" t="n">
-        <v>18.519</v>
+        <v>12.5278</v>
       </c>
       <c r="U6" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="V6" t="n">
-        <v>9.0891</v>
+        <v>13.1788</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="Y6" t="n">
-        <v>-16.4683</v>
+        <v>-11.6083</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
       <c r="AB6" t="n">
-        <v>-8.606</v>
+        <v>-12.097</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D7" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E7" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F7" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G7" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H7" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I7" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J7" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K7" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L7" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M7" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N7" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O7" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P7" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="S7" t="n">
-        <v>12.5278</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>27.3481</v>
+        <v>22.7702</v>
       </c>
       <c r="U7" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="V7" t="n">
-        <v>13.1788</v>
+        <v>11.3897</v>
       </c>
       <c r="W7" t="n">
-        <v>15.9375</v>
+        <v>15.2574</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y7" t="n">
-        <v>-11.6083</v>
+        <v>-9.545</v>
       </c>
       <c r="Z7" t="n">
-        <v>-22.3294</v>
+        <v>-19.5238</v>
       </c>
       <c r="AA7" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB7" t="n">
-        <v>-12.097</v>
+        <v>-10.6146</v>
       </c>
       <c r="AC7" t="n">
-        <v>-14.104</v>
+        <v>-13.631</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C8" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D8" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E8" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G8" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H8" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I8" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J8" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K8" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L8" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M8" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N8" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O8" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P8" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S8" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="T8" t="n">
-        <v>22.7702</v>
+        <v>23.9429</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V8" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>15.2574</v>
+        <v>19.158</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="Z8" t="n">
-        <v>-19.5238</v>
+        <v>-20.3461</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB8" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
       <c r="AC8" t="n">
-        <v>-13.631</v>
+        <v>-16.6075</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C9" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E9" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F9" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G9" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H9" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I9" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J9" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K9" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L9" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M9" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N9" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O9" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P9" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R9" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S9" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="T9" t="n">
-        <v>23.9429</v>
+        <v>19.0914</v>
       </c>
       <c r="U9" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="W9" t="n">
-        <v>19.158</v>
+        <v>14.6467</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y9" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z9" t="n">
-        <v>-20.3461</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA9" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB9" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC9" t="n">
-        <v>-16.6075</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C10" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D10" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F10" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G10" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H10" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I10" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J10" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K10" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L10" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M10" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N10" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O10" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P10" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S10" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T10" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V10" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W10" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y10" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z10" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB10" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC10" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C11" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D11" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F11" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G11" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H11" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I11" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J11" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K11" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L11" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M11" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N11" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O11" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P11" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R11" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S11" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T11" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y11" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z11" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC11" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C12" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D12" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E12" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F12" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G12" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H12" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I12" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J12" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K12" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L12" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M12" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N12" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O12" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P12" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R12" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S12" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T12" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U12" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V12" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W12" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y12" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z12" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA12" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC12" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C13" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D13" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E13" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F13" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G13" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H13" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I13" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J13" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K13" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L13" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M13" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N13" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O13" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P13" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R13" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S13" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T13" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V13" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W13" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y13" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z13" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB13" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C14" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D14" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E14" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F14" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G14" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H14" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I14" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J14" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K14" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L14" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M14" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N14" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O14" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P14" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R14" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S14" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T14" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U14" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V14" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W14" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y14" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z14" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA14" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC14" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C15" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D15" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E15" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F15" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G15" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H15" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I15" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J15" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K15" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L15" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M15" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N15" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O15" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P15" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S15" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T15" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V15" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W15" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X15" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y15" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z15" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB15" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC15" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C16" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D16" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E16" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F16" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H16" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I16" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J16" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K16" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L16" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M16" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N16" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O16" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P16" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R16" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W16" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X16" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z16" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC16" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C17" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D17" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E17" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G17" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H17" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I17" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J17" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K17" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L17" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M17" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N17" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O17" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P17" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R17" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S17" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T17" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z17" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C18" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D18" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E18" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F18" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G18" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H18" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I18" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J18" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K18" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L18" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M18" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N18" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O18" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P18" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R18" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T18" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U18" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W18" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X18" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y18" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z18" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA18" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB18" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C19" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D19" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E19" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F19" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G19" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H19" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I19" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J19" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K19" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L19" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M19" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N19" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O19" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P19" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S19" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U19" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W19" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y19" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z19" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB19" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C20" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D20" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E20" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F20" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G20" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H20" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I20" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J20" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K20" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L20" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M20" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N20" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O20" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P20" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S20" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W20" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X20" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y20" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z20" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C21" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D21" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E21" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F21" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H21" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I21" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K21" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L21" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N21" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O21" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P21" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R21" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S21" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T21" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U21" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V21" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X21" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y21" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z21" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA21" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB21" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC21" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C22" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D22" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E22" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F22" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G22" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H22" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I22" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J22" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K22" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N22" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O22" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P22" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R22" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S22" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T22" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U22" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V22" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X22" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z22" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB22" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC22" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>162.115</v>
+        <v>163</v>
       </c>
       <c r="C23" t="n">
-        <v>162.9</v>
+        <v>177.495</v>
       </c>
       <c r="D23" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E23" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F23" t="n">
-        <v>71.86499999999999</v>
+        <v>72.825</v>
       </c>
       <c r="G23" t="n">
-        <v>73.295</v>
+        <v>76.31</v>
       </c>
       <c r="H23" t="n">
-        <v>70.38500000000001</v>
+        <v>72.69499999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J23" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M23" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N23" t="n">
-        <v>45.41</v>
+        <v>44.8</v>
       </c>
       <c r="O23" t="n">
-        <v>46.357</v>
+        <v>44.89</v>
       </c>
       <c r="P23" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R23" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S23" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="T23" t="n">
-        <v>19.7826</v>
+        <v>35.6902</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V23" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W23" t="n">
-        <v>12.2757</v>
+        <v>16.8147</v>
       </c>
       <c r="X23" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y23" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z23" t="n">
-        <v>-20.3008</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB23" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC23" t="n">
-        <v>-11.4618</v>
+        <v>-15.233</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24759,1895 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.12</v>
+        <v>75.59</v>
       </c>
       <c r="C2" t="n">
-        <v>72.28</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>68.12</v>
+        <v>75.25</v>
       </c>
       <c r="E2" t="n">
-        <v>71.98</v>
+        <v>80.56</v>
       </c>
       <c r="F2" t="n">
-        <v>48.02</v>
+        <v>48.78</v>
       </c>
       <c r="G2" t="n">
-        <v>49.09</v>
+        <v>50.74</v>
       </c>
       <c r="H2" t="n">
-        <v>47.31</v>
+        <v>48.46</v>
       </c>
       <c r="I2" t="n">
-        <v>48.96</v>
+        <v>50.66</v>
       </c>
       <c r="J2" t="n">
-        <v>26.76</v>
+        <v>23.92</v>
       </c>
       <c r="K2" t="n">
-        <v>26.76</v>
+        <v>24.03</v>
       </c>
       <c r="L2" t="n">
-        <v>25.09</v>
+        <v>22.32</v>
       </c>
       <c r="M2" t="n">
-        <v>25.2</v>
+        <v>22.42</v>
       </c>
       <c r="N2" t="n">
-        <v>69.31999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="O2" t="n">
-        <v>70.3</v>
+        <v>68.63</v>
       </c>
       <c r="P2" t="n">
-        <v>67.72</v>
+        <v>65.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>67.86</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.3</v>
+        <v>83.27</v>
       </c>
       <c r="C3" t="n">
-        <v>78.3</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>74.3</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>76.39</v>
+        <v>85.31</v>
       </c>
       <c r="F3" t="n">
-        <v>49.36</v>
+        <v>51.39</v>
       </c>
       <c r="G3" t="n">
-        <v>49.81</v>
+        <v>53.43</v>
       </c>
       <c r="H3" t="n">
-        <v>48.82</v>
+        <v>51.38</v>
       </c>
       <c r="I3" t="n">
-        <v>49.17</v>
+        <v>53.41</v>
       </c>
       <c r="J3" t="n">
-        <v>24.38</v>
+        <v>21.6</v>
       </c>
       <c r="K3" t="n">
-        <v>24.42</v>
+        <v>22.34</v>
       </c>
       <c r="L3" t="n">
-        <v>23.01</v>
+        <v>21</v>
       </c>
       <c r="M3" t="n">
-        <v>23.69</v>
+        <v>21.05</v>
       </c>
       <c r="N3" t="n">
-        <v>67.38</v>
+        <v>64.67</v>
       </c>
       <c r="O3" t="n">
-        <v>68.13</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>66.75</v>
+        <v>62.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>67.62</v>
+        <v>62.02</v>
       </c>
       <c r="R3" t="n">
-        <v>6.1267</v>
+        <v>5.8962</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4289</v>
+        <v>5.4283</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.9921</v>
+        <v>-6.1106</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.3537</v>
+        <v>-5.4141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.59</v>
+        <v>84.66</v>
       </c>
       <c r="C4" t="n">
-        <v>80.73999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D4" t="n">
-        <v>75.25</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>80.56</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>48.78</v>
+        <v>53.57</v>
       </c>
       <c r="G4" t="n">
-        <v>50.74</v>
+        <v>55.74</v>
       </c>
       <c r="H4" t="n">
-        <v>48.46</v>
+        <v>53.33</v>
       </c>
       <c r="I4" t="n">
-        <v>50.66</v>
+        <v>55.65</v>
       </c>
       <c r="J4" t="n">
-        <v>23.92</v>
+        <v>21.23</v>
       </c>
       <c r="K4" t="n">
-        <v>24.03</v>
+        <v>22.43</v>
       </c>
       <c r="L4" t="n">
-        <v>22.32</v>
+        <v>20.9</v>
       </c>
       <c r="M4" t="n">
-        <v>22.42</v>
+        <v>20.94</v>
       </c>
       <c r="N4" t="n">
-        <v>68.2</v>
+        <v>61.88</v>
       </c>
       <c r="O4" t="n">
-        <v>68.63</v>
+        <v>62.15</v>
       </c>
       <c r="P4" t="n">
-        <v>65.5</v>
+        <v>59.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>65.56999999999999</v>
+        <v>59.44</v>
       </c>
       <c r="R4" t="n">
-        <v>5.4588</v>
+        <v>0.7619</v>
       </c>
       <c r="U4" t="n">
-        <v>3.0303</v>
+        <v>4.194</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.3609</v>
+        <v>-0.5226</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3.0316</v>
+        <v>-4.1599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83.27</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>85.56999999999999</v>
+        <v>89.39</v>
       </c>
       <c r="D5" t="n">
-        <v>80.70999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="E5" t="n">
-        <v>85.31</v>
+        <v>88.37</v>
       </c>
       <c r="F5" t="n">
-        <v>51.39</v>
+        <v>56.13</v>
       </c>
       <c r="G5" t="n">
-        <v>53.43</v>
+        <v>56.92</v>
       </c>
       <c r="H5" t="n">
-        <v>51.38</v>
+        <v>55.1</v>
       </c>
       <c r="I5" t="n">
-        <v>53.41</v>
+        <v>56.43</v>
       </c>
       <c r="J5" t="n">
-        <v>21.6</v>
+        <v>21.13</v>
       </c>
       <c r="K5" t="n">
-        <v>22.34</v>
+        <v>21.56</v>
       </c>
       <c r="L5" t="n">
-        <v>21</v>
+        <v>20.07</v>
       </c>
       <c r="M5" t="n">
-        <v>21.05</v>
+        <v>20.28</v>
       </c>
       <c r="N5" t="n">
-        <v>64.67</v>
+        <v>58.95</v>
       </c>
       <c r="O5" t="n">
-        <v>64.68000000000001</v>
+        <v>60.06</v>
       </c>
       <c r="P5" t="n">
-        <v>62.02</v>
+        <v>58.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.02</v>
+        <v>58.61</v>
       </c>
       <c r="R5" t="n">
-        <v>5.8962</v>
+        <v>2.8036</v>
       </c>
       <c r="S5" t="n">
-        <v>18.519</v>
+        <v>9.694599999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>5.4283</v>
+        <v>1.4016</v>
       </c>
       <c r="V5" t="n">
-        <v>9.0891</v>
+        <v>11.3897</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.1106</v>
+        <v>-3.1519</v>
       </c>
       <c r="Y5" t="n">
-        <v>-16.4683</v>
+        <v>-9.545</v>
       </c>
       <c r="AA5" t="n">
-        <v>-5.4141</v>
+        <v>-1.3964</v>
       </c>
       <c r="AB5" t="n">
-        <v>-8.606</v>
+        <v>-10.6146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84.66</v>
+        <v>93.2</v>
       </c>
       <c r="C6" t="n">
-        <v>85.98</v>
+        <v>94.75</v>
       </c>
       <c r="D6" t="n">
-        <v>79.76000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="E6" t="n">
-        <v>85.95999999999999</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>53.57</v>
+        <v>57.78</v>
       </c>
       <c r="G6" t="n">
-        <v>55.74</v>
+        <v>58.94</v>
       </c>
       <c r="H6" t="n">
-        <v>53.33</v>
+        <v>57.37</v>
       </c>
       <c r="I6" t="n">
-        <v>55.65</v>
+        <v>58.59</v>
       </c>
       <c r="J6" t="n">
-        <v>21.23</v>
+        <v>19.23</v>
       </c>
       <c r="K6" t="n">
-        <v>22.43</v>
+        <v>19.8</v>
       </c>
       <c r="L6" t="n">
-        <v>20.9</v>
+        <v>18.86</v>
       </c>
       <c r="M6" t="n">
-        <v>20.94</v>
+        <v>18.87</v>
       </c>
       <c r="N6" t="n">
-        <v>61.88</v>
+        <v>57.25</v>
       </c>
       <c r="O6" t="n">
-        <v>62.15</v>
+        <v>57.67</v>
       </c>
       <c r="P6" t="n">
-        <v>59.35</v>
+        <v>56.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>59.44</v>
+        <v>56.39</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7619</v>
+        <v>7.1404</v>
       </c>
       <c r="S6" t="n">
-        <v>12.5278</v>
+        <v>10.9835</v>
       </c>
       <c r="U6" t="n">
-        <v>4.194</v>
+        <v>3.8278</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1788</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5226</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y6" t="n">
-        <v>-11.6083</v>
+        <v>-10.3563</v>
       </c>
       <c r="AA6" t="n">
-        <v>-4.1599</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB6" t="n">
-        <v>-12.097</v>
+        <v>-9.0777</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85.01000000000001</v>
+        <v>95.97</v>
       </c>
       <c r="C7" t="n">
-        <v>89.39</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>83.31</v>
+        <v>92.03</v>
       </c>
       <c r="E7" t="n">
-        <v>88.37</v>
+        <v>95.94</v>
       </c>
       <c r="F7" t="n">
-        <v>56.13</v>
+        <v>58.4</v>
       </c>
       <c r="G7" t="n">
-        <v>56.92</v>
+        <v>58.58</v>
       </c>
       <c r="H7" t="n">
-        <v>55.1</v>
+        <v>56.91</v>
       </c>
       <c r="I7" t="n">
-        <v>56.43</v>
+        <v>58.08</v>
       </c>
       <c r="J7" t="n">
-        <v>21.13</v>
+        <v>18.64</v>
       </c>
       <c r="K7" t="n">
-        <v>21.56</v>
+        <v>19.41</v>
       </c>
       <c r="L7" t="n">
-        <v>20.07</v>
+        <v>18.44</v>
       </c>
       <c r="M7" t="n">
-        <v>20.28</v>
+        <v>18.63</v>
       </c>
       <c r="N7" t="n">
-        <v>58.95</v>
+        <v>56.59</v>
       </c>
       <c r="O7" t="n">
-        <v>60.06</v>
+        <v>58.04</v>
       </c>
       <c r="P7" t="n">
-        <v>58.11</v>
+        <v>56.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>58.61</v>
+        <v>56.91</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8036</v>
+        <v>1.3308</v>
       </c>
       <c r="S7" t="n">
-        <v>9.694599999999999</v>
+        <v>11.6101</v>
       </c>
       <c r="T7" t="n">
-        <v>22.7702</v>
+        <v>19.0914</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4016</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>11.3897</v>
+        <v>4.3666</v>
       </c>
       <c r="W7" t="n">
-        <v>15.2574</v>
+        <v>14.6467</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.1519</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y7" t="n">
-        <v>-9.545</v>
+        <v>-11.0315</v>
       </c>
       <c r="Z7" t="n">
-        <v>-19.5238</v>
+        <v>-16.9045</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.3964</v>
+        <v>0.9221</v>
       </c>
       <c r="AB7" t="n">
-        <v>-10.6146</v>
+        <v>-4.2564</v>
       </c>
       <c r="AC7" t="n">
-        <v>-13.631</v>
+        <v>-13.2073</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93.2</v>
+        <v>97.97</v>
       </c>
       <c r="C8" t="n">
-        <v>94.75</v>
+        <v>99.95</v>
       </c>
       <c r="D8" t="n">
-        <v>90.66</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>94.68000000000001</v>
+        <v>98.09</v>
       </c>
       <c r="F8" t="n">
-        <v>57.78</v>
+        <v>58.48</v>
       </c>
       <c r="G8" t="n">
-        <v>58.94</v>
+        <v>58.97</v>
       </c>
       <c r="H8" t="n">
-        <v>57.37</v>
+        <v>56.82</v>
       </c>
       <c r="I8" t="n">
-        <v>58.59</v>
+        <v>57.4</v>
       </c>
       <c r="J8" t="n">
-        <v>19.23</v>
+        <v>18.25</v>
       </c>
       <c r="K8" t="n">
-        <v>19.8</v>
+        <v>18.76</v>
       </c>
       <c r="L8" t="n">
-        <v>18.86</v>
+        <v>17.85</v>
       </c>
       <c r="M8" t="n">
-        <v>18.87</v>
+        <v>18.2</v>
       </c>
       <c r="N8" t="n">
-        <v>57.25</v>
+        <v>56.52</v>
       </c>
       <c r="O8" t="n">
-        <v>57.67</v>
+        <v>58.15</v>
       </c>
       <c r="P8" t="n">
         <v>56.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>56.39</v>
+        <v>57.59</v>
       </c>
       <c r="R8" t="n">
-        <v>7.1404</v>
+        <v>2.241</v>
       </c>
       <c r="S8" t="n">
-        <v>10.9835</v>
+        <v>10.9992</v>
       </c>
       <c r="T8" t="n">
-        <v>23.9429</v>
+        <v>14.9807</v>
       </c>
       <c r="U8" t="n">
-        <v>3.8278</v>
+        <v>-1.1708</v>
       </c>
       <c r="V8" t="n">
-        <v>9.698600000000001</v>
+        <v>1.7189</v>
       </c>
       <c r="W8" t="n">
-        <v>19.158</v>
+        <v>7.4705</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.9527</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y8" t="n">
-        <v>-10.3563</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z8" t="n">
-        <v>-20.3461</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3.7877</v>
+        <v>1.1949</v>
       </c>
       <c r="AB8" t="n">
-        <v>-9.0777</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC8" t="n">
-        <v>-16.6075</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95.97</v>
+        <v>102.94</v>
       </c>
       <c r="C9" t="n">
-        <v>96.93000000000001</v>
+        <v>106.09</v>
       </c>
       <c r="D9" t="n">
-        <v>92.03</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>95.94</v>
+        <v>105.64</v>
       </c>
       <c r="F9" t="n">
-        <v>58.4</v>
+        <v>58.93</v>
       </c>
       <c r="G9" t="n">
-        <v>58.58</v>
+        <v>60.3</v>
       </c>
       <c r="H9" t="n">
-        <v>56.91</v>
+        <v>58.49</v>
       </c>
       <c r="I9" t="n">
-        <v>58.08</v>
+        <v>60.21</v>
       </c>
       <c r="J9" t="n">
-        <v>18.64</v>
+        <v>17.37</v>
       </c>
       <c r="K9" t="n">
-        <v>19.41</v>
+        <v>17.95</v>
       </c>
       <c r="L9" t="n">
-        <v>18.44</v>
+        <v>16.72</v>
       </c>
       <c r="M9" t="n">
-        <v>18.63</v>
+        <v>16.8</v>
       </c>
       <c r="N9" t="n">
-        <v>56.59</v>
+        <v>56.05</v>
       </c>
       <c r="O9" t="n">
-        <v>58.04</v>
+        <v>56.49</v>
       </c>
       <c r="P9" t="n">
-        <v>56.41</v>
+        <v>54.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>56.91</v>
+        <v>54.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3308</v>
+        <v>7.697</v>
       </c>
       <c r="S9" t="n">
-        <v>11.6101</v>
+        <v>11.5758</v>
       </c>
       <c r="T9" t="n">
-        <v>19.0914</v>
+        <v>22.8944</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8705000000000001</v>
+        <v>4.8955</v>
       </c>
       <c r="V9" t="n">
-        <v>4.3666</v>
+        <v>2.765</v>
       </c>
       <c r="W9" t="n">
-        <v>14.6467</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2719</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y9" t="n">
-        <v>-11.0315</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z9" t="n">
-        <v>-16.9045</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.9221</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4.2564</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC9" t="n">
-        <v>-13.2073</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97.97</v>
+        <v>108.62</v>
       </c>
       <c r="C10" t="n">
-        <v>99.95</v>
+        <v>116.77</v>
       </c>
       <c r="D10" t="n">
-        <v>95.31999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E10" t="n">
-        <v>98.09</v>
+        <v>112.77</v>
       </c>
       <c r="F10" t="n">
-        <v>58.48</v>
+        <v>59.8</v>
       </c>
       <c r="G10" t="n">
-        <v>58.97</v>
+        <v>60.73</v>
       </c>
       <c r="H10" t="n">
-        <v>56.82</v>
+        <v>57.59</v>
       </c>
       <c r="I10" t="n">
-        <v>57.4</v>
+        <v>59.22</v>
       </c>
       <c r="J10" t="n">
-        <v>18.25</v>
+        <v>16.35</v>
       </c>
       <c r="K10" t="n">
-        <v>18.76</v>
+        <v>16.52</v>
       </c>
       <c r="L10" t="n">
-        <v>17.85</v>
+        <v>15.06</v>
       </c>
       <c r="M10" t="n">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="N10" t="n">
-        <v>56.52</v>
+        <v>55.13</v>
       </c>
       <c r="O10" t="n">
-        <v>58.15</v>
+        <v>57.14</v>
       </c>
       <c r="P10" t="n">
-        <v>56.04</v>
+        <v>54.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>57.59</v>
+        <v>55.66</v>
       </c>
       <c r="R10" t="n">
-        <v>2.241</v>
+        <v>6.7493</v>
       </c>
       <c r="S10" t="n">
-        <v>10.9992</v>
+        <v>17.5422</v>
       </c>
       <c r="T10" t="n">
-        <v>14.9807</v>
+        <v>27.6112</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1708</v>
+        <v>-1.6442</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7189</v>
+        <v>1.9628</v>
       </c>
       <c r="W10" t="n">
-        <v>7.4705</v>
+        <v>4.9442</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3081</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y10" t="n">
-        <v>-10.2564</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z10" t="n">
-        <v>-13.5392</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.1949</v>
+        <v>1.6993</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.7403</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC10" t="n">
-        <v>-7.1429</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>102.94</v>
+        <v>125.21</v>
       </c>
       <c r="C11" t="n">
-        <v>106.09</v>
+        <v>130.12</v>
       </c>
       <c r="D11" t="n">
-        <v>99.59999999999999</v>
+        <v>120.24</v>
       </c>
       <c r="E11" t="n">
-        <v>105.64</v>
+        <v>128.32</v>
       </c>
       <c r="F11" t="n">
-        <v>58.93</v>
+        <v>61.08</v>
       </c>
       <c r="G11" t="n">
-        <v>60.3</v>
+        <v>62.74</v>
       </c>
       <c r="H11" t="n">
-        <v>58.49</v>
+        <v>60.56</v>
       </c>
       <c r="I11" t="n">
-        <v>60.21</v>
+        <v>62.56</v>
       </c>
       <c r="J11" t="n">
-        <v>17.37</v>
+        <v>13.99</v>
       </c>
       <c r="K11" t="n">
-        <v>17.95</v>
+        <v>14.66</v>
       </c>
       <c r="L11" t="n">
-        <v>16.72</v>
+        <v>13.3</v>
       </c>
       <c r="M11" t="n">
-        <v>16.8</v>
+        <v>13.52</v>
       </c>
       <c r="N11" t="n">
-        <v>56.05</v>
+        <v>53.93</v>
       </c>
       <c r="O11" t="n">
-        <v>56.49</v>
+        <v>54.43</v>
       </c>
       <c r="P11" t="n">
-        <v>54.66</v>
+        <v>52.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>54.73</v>
+        <v>52.5</v>
       </c>
       <c r="R11" t="n">
-        <v>7.697</v>
+        <v>13.7891</v>
       </c>
       <c r="S11" t="n">
-        <v>11.5758</v>
+        <v>30.8186</v>
       </c>
       <c r="T11" t="n">
-        <v>22.8944</v>
+        <v>35.5302</v>
       </c>
       <c r="U11" t="n">
-        <v>4.8955</v>
+        <v>5.64</v>
       </c>
       <c r="V11" t="n">
-        <v>2.765</v>
+        <v>8.9895</v>
       </c>
       <c r="W11" t="n">
-        <v>8.194100000000001</v>
+        <v>6.7759</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.6923</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y11" t="n">
-        <v>-10.9698</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z11" t="n">
-        <v>-19.7708</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA11" t="n">
-        <v>-4.9661</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB11" t="n">
-        <v>-2.9438</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC11" t="n">
-        <v>-7.924</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108.62</v>
+        <v>128.33</v>
       </c>
       <c r="C12" t="n">
-        <v>116.77</v>
+        <v>129.59</v>
       </c>
       <c r="D12" t="n">
-        <v>107.46</v>
+        <v>117.79</v>
       </c>
       <c r="E12" t="n">
-        <v>112.77</v>
+        <v>123.39</v>
       </c>
       <c r="F12" t="n">
-        <v>59.8</v>
+        <v>62.41</v>
       </c>
       <c r="G12" t="n">
-        <v>60.73</v>
+        <v>62.7</v>
       </c>
       <c r="H12" t="n">
-        <v>57.59</v>
+        <v>61.64</v>
       </c>
       <c r="I12" t="n">
-        <v>59.22</v>
+        <v>62.64</v>
       </c>
       <c r="J12" t="n">
-        <v>16.35</v>
+        <v>13.51</v>
       </c>
       <c r="K12" t="n">
-        <v>16.52</v>
+        <v>14.63</v>
       </c>
       <c r="L12" t="n">
-        <v>15.06</v>
+        <v>13.41</v>
       </c>
       <c r="M12" t="n">
-        <v>15.7</v>
+        <v>14.03</v>
       </c>
       <c r="N12" t="n">
-        <v>55.13</v>
+        <v>52.67</v>
       </c>
       <c r="O12" t="n">
-        <v>57.14</v>
+        <v>53.31</v>
       </c>
       <c r="P12" t="n">
-        <v>54.28</v>
+        <v>52.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>55.66</v>
+        <v>52.45</v>
       </c>
       <c r="R12" t="n">
-        <v>6.7493</v>
+        <v>-3.842</v>
       </c>
       <c r="S12" t="n">
-        <v>17.5422</v>
+        <v>16.8023</v>
       </c>
       <c r="T12" t="n">
-        <v>27.6112</v>
+        <v>28.6116</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6442</v>
+        <v>0.1279</v>
       </c>
       <c r="V12" t="n">
-        <v>1.9628</v>
+        <v>4.0359</v>
       </c>
       <c r="W12" t="n">
-        <v>4.9442</v>
+        <v>7.8512</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.5476</v>
+        <v>3.7722</v>
       </c>
       <c r="Y12" t="n">
-        <v>-15.7273</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z12" t="n">
-        <v>-22.5838</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6993</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.1965</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC12" t="n">
-        <v>-5.0333</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>125.21</v>
+        <v>108.75</v>
       </c>
       <c r="C13" t="n">
-        <v>130.12</v>
+        <v>115.62</v>
       </c>
       <c r="D13" t="n">
-        <v>120.24</v>
+        <v>103.99</v>
       </c>
       <c r="E13" t="n">
-        <v>128.32</v>
+        <v>109.56</v>
       </c>
       <c r="F13" t="n">
-        <v>61.08</v>
+        <v>60.72</v>
       </c>
       <c r="G13" t="n">
-        <v>62.74</v>
+        <v>61.33</v>
       </c>
       <c r="H13" t="n">
-        <v>60.56</v>
+        <v>59.68</v>
       </c>
       <c r="I13" t="n">
-        <v>62.56</v>
+        <v>60.74</v>
       </c>
       <c r="J13" t="n">
-        <v>13.99</v>
+        <v>15.71</v>
       </c>
       <c r="K13" t="n">
-        <v>14.66</v>
+        <v>16.27</v>
       </c>
       <c r="L13" t="n">
-        <v>13.3</v>
+        <v>14.93</v>
       </c>
       <c r="M13" t="n">
-        <v>13.52</v>
+        <v>15.59</v>
       </c>
       <c r="N13" t="n">
-        <v>53.93</v>
+        <v>54.09</v>
       </c>
       <c r="O13" t="n">
-        <v>54.43</v>
+        <v>54.96</v>
       </c>
       <c r="P13" t="n">
-        <v>52.37</v>
+        <v>53.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>52.5</v>
+        <v>54.05</v>
       </c>
       <c r="R13" t="n">
-        <v>13.7891</v>
+        <v>-11.2084</v>
       </c>
       <c r="S13" t="n">
-        <v>30.8186</v>
+        <v>-2.8465</v>
       </c>
       <c r="T13" t="n">
-        <v>35.5302</v>
+        <v>11.6933</v>
       </c>
       <c r="U13" t="n">
-        <v>5.64</v>
+        <v>-3.0332</v>
       </c>
       <c r="V13" t="n">
-        <v>8.9895</v>
+        <v>2.5667</v>
       </c>
       <c r="W13" t="n">
-        <v>6.7759</v>
+        <v>5.8188</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.8854</v>
+        <v>11.119</v>
       </c>
       <c r="Y13" t="n">
-        <v>-25.7143</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z13" t="n">
-        <v>-28.3519</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA13" t="n">
-        <v>-5.6773</v>
+        <v>3.0505</v>
       </c>
       <c r="AB13" t="n">
-        <v>-8.8383</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.8984</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>128.33</v>
+        <v>114.76</v>
       </c>
       <c r="C14" t="n">
-        <v>129.59</v>
+        <v>118.32</v>
       </c>
       <c r="D14" t="n">
-        <v>117.79</v>
+        <v>112.3</v>
       </c>
       <c r="E14" t="n">
-        <v>123.39</v>
+        <v>117.97</v>
       </c>
       <c r="F14" t="n">
-        <v>62.41</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>62.7</v>
+        <v>61.87</v>
       </c>
       <c r="H14" t="n">
-        <v>61.64</v>
+        <v>60.45</v>
       </c>
       <c r="I14" t="n">
-        <v>62.64</v>
+        <v>61.86</v>
       </c>
       <c r="J14" t="n">
-        <v>13.51</v>
+        <v>14.91</v>
       </c>
       <c r="K14" t="n">
-        <v>14.63</v>
+        <v>15.24</v>
       </c>
       <c r="L14" t="n">
-        <v>13.41</v>
+        <v>14.38</v>
       </c>
       <c r="M14" t="n">
-        <v>14.03</v>
+        <v>14.4</v>
       </c>
       <c r="N14" t="n">
-        <v>52.67</v>
+        <v>53.84</v>
       </c>
       <c r="O14" t="n">
-        <v>53.31</v>
+        <v>54.33</v>
       </c>
       <c r="P14" t="n">
-        <v>52.42</v>
+        <v>53.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>52.45</v>
+        <v>53.08</v>
       </c>
       <c r="R14" t="n">
-        <v>-3.842</v>
+        <v>7.6762</v>
       </c>
       <c r="S14" t="n">
-        <v>16.8023</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>28.6116</v>
+        <v>11.6717</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1279</v>
+        <v>1.8439</v>
       </c>
       <c r="V14" t="n">
-        <v>4.0359</v>
+        <v>-1.1189</v>
       </c>
       <c r="W14" t="n">
-        <v>7.8512</v>
+        <v>2.7404</v>
       </c>
       <c r="X14" t="n">
-        <v>3.7722</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y14" t="n">
-        <v>-16.4881</v>
+        <v>6.5089</v>
       </c>
       <c r="Z14" t="n">
-        <v>-24.6914</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB14" t="n">
-        <v>-4.1659</v>
+        <v>1.1048</v>
       </c>
       <c r="AC14" t="n">
-        <v>-7.8369</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108.75</v>
+        <v>122.81</v>
       </c>
       <c r="C15" t="n">
-        <v>115.62</v>
+        <v>127.45</v>
       </c>
       <c r="D15" t="n">
-        <v>103.99</v>
+        <v>117.5</v>
       </c>
       <c r="E15" t="n">
-        <v>109.56</v>
+        <v>126.98</v>
       </c>
       <c r="F15" t="n">
-        <v>60.72</v>
+        <v>62.89</v>
       </c>
       <c r="G15" t="n">
-        <v>61.33</v>
+        <v>63.8</v>
       </c>
       <c r="H15" t="n">
-        <v>59.68</v>
+        <v>60.7</v>
       </c>
       <c r="I15" t="n">
-        <v>60.74</v>
+        <v>63.54</v>
       </c>
       <c r="J15" t="n">
-        <v>15.71</v>
+        <v>13.84</v>
       </c>
       <c r="K15" t="n">
-        <v>16.27</v>
+        <v>14.49</v>
       </c>
       <c r="L15" t="n">
-        <v>14.93</v>
+        <v>13.25</v>
       </c>
       <c r="M15" t="n">
-        <v>15.59</v>
+        <v>13.3</v>
       </c>
       <c r="N15" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="O15" t="n">
         <v>54.09</v>
       </c>
-      <c r="O15" t="n">
-        <v>54.96</v>
-      </c>
       <c r="P15" t="n">
-        <v>53.58</v>
+        <v>51.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>54.05</v>
+        <v>51.65</v>
       </c>
       <c r="R15" t="n">
-        <v>-11.2084</v>
+        <v>7.6375</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.8465</v>
+        <v>2.9095</v>
       </c>
       <c r="T15" t="n">
-        <v>11.6933</v>
+        <v>12.6009</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.0332</v>
+        <v>2.7158</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5667</v>
+        <v>1.4368</v>
       </c>
       <c r="W15" t="n">
-        <v>5.8188</v>
+        <v>7.2948</v>
       </c>
       <c r="X15" t="n">
-        <v>11.119</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.7006</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z15" t="n">
-        <v>-14.3407</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.0505</v>
+        <v>-2.694</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.8926</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.1469</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>114.76</v>
+        <v>124.39</v>
       </c>
       <c r="C16" t="n">
-        <v>118.32</v>
+        <v>131.38</v>
       </c>
       <c r="D16" t="n">
-        <v>112.3</v>
+        <v>121.66</v>
       </c>
       <c r="E16" t="n">
-        <v>117.97</v>
+        <v>130.4</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>63.89</v>
       </c>
       <c r="G16" t="n">
-        <v>61.87</v>
+        <v>65.84</v>
       </c>
       <c r="H16" t="n">
-        <v>60.45</v>
+        <v>63.81</v>
       </c>
       <c r="I16" t="n">
-        <v>61.86</v>
+        <v>65.3</v>
       </c>
       <c r="J16" t="n">
-        <v>14.91</v>
+        <v>13.61</v>
       </c>
       <c r="K16" t="n">
-        <v>15.24</v>
+        <v>13.89</v>
       </c>
       <c r="L16" t="n">
-        <v>14.38</v>
+        <v>12.87</v>
       </c>
       <c r="M16" t="n">
-        <v>14.4</v>
+        <v>12.98</v>
       </c>
       <c r="N16" t="n">
-        <v>53.84</v>
+        <v>51.36</v>
       </c>
       <c r="O16" t="n">
-        <v>54.33</v>
+        <v>51.45</v>
       </c>
       <c r="P16" t="n">
-        <v>53.06</v>
+        <v>49.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>53.08</v>
+        <v>50.22</v>
       </c>
       <c r="R16" t="n">
-        <v>7.6762</v>
+        <v>2.6933</v>
       </c>
       <c r="S16" t="n">
-        <v>-8.065799999999999</v>
+        <v>19.0215</v>
       </c>
       <c r="T16" t="n">
-        <v>11.6717</v>
+        <v>1.6209</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8439</v>
+        <v>2.7699</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1189</v>
+        <v>7.5074</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7404</v>
+        <v>4.3798</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.6331</v>
+        <v>-2.406</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.5089</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z16" t="n">
-        <v>-14.2857</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.7946</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.1048</v>
+        <v>-7.086</v>
       </c>
       <c r="AC16" t="n">
-        <v>-3.0148</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>122.81</v>
+        <v>132.2</v>
       </c>
       <c r="C17" t="n">
-        <v>127.45</v>
+        <v>133.67</v>
       </c>
       <c r="D17" t="n">
-        <v>117.5</v>
+        <v>123.8</v>
       </c>
       <c r="E17" t="n">
-        <v>126.98</v>
+        <v>127.55</v>
       </c>
       <c r="F17" t="n">
-        <v>62.89</v>
+        <v>65.44</v>
       </c>
       <c r="G17" t="n">
-        <v>63.8</v>
+        <v>66.05</v>
       </c>
       <c r="H17" t="n">
-        <v>60.7</v>
+        <v>63.78</v>
       </c>
       <c r="I17" t="n">
-        <v>63.54</v>
+        <v>64.91</v>
       </c>
       <c r="J17" t="n">
-        <v>13.84</v>
+        <v>12.8</v>
       </c>
       <c r="K17" t="n">
-        <v>14.49</v>
+        <v>13.64</v>
       </c>
       <c r="L17" t="n">
-        <v>13.25</v>
+        <v>12.65</v>
       </c>
       <c r="M17" t="n">
-        <v>13.3</v>
+        <v>13.26</v>
       </c>
       <c r="N17" t="n">
-        <v>52.21</v>
+        <v>50.12</v>
       </c>
       <c r="O17" t="n">
-        <v>54.09</v>
+        <v>51.43</v>
       </c>
       <c r="P17" t="n">
-        <v>51.4</v>
+        <v>49.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>51.65</v>
+        <v>50.51</v>
       </c>
       <c r="R17" t="n">
-        <v>7.6375</v>
+        <v>-2.1856</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9095</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>12.6009</v>
+        <v>3.3714</v>
       </c>
       <c r="U17" t="n">
-        <v>2.7158</v>
+        <v>-0.5972</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4368</v>
+        <v>4.9305</v>
       </c>
       <c r="W17" t="n">
-        <v>7.2948</v>
+        <v>3.6239</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.6389</v>
+        <v>2.1572</v>
       </c>
       <c r="Y17" t="n">
-        <v>-5.2031</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z17" t="n">
-        <v>-15.2866</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.694</v>
+        <v>0.5775</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.5253</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC17" t="n">
-        <v>-7.2045</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>124.39</v>
+        <v>135</v>
       </c>
       <c r="C18" t="n">
-        <v>131.38</v>
+        <v>147.26</v>
       </c>
       <c r="D18" t="n">
-        <v>121.66</v>
+        <v>134.02</v>
       </c>
       <c r="E18" t="n">
-        <v>130.4</v>
+        <v>144.16</v>
       </c>
       <c r="F18" t="n">
-        <v>63.89</v>
+        <v>66.37</v>
       </c>
       <c r="G18" t="n">
-        <v>65.84</v>
+        <v>67.77</v>
       </c>
       <c r="H18" t="n">
-        <v>63.81</v>
+        <v>66.25</v>
       </c>
       <c r="I18" t="n">
-        <v>65.3</v>
+        <v>67.39</v>
       </c>
       <c r="J18" t="n">
-        <v>13.61</v>
+        <v>12.5</v>
       </c>
       <c r="K18" t="n">
-        <v>13.89</v>
+        <v>12.59</v>
       </c>
       <c r="L18" t="n">
-        <v>12.87</v>
+        <v>11.21</v>
       </c>
       <c r="M18" t="n">
-        <v>12.98</v>
+        <v>11.51</v>
       </c>
       <c r="N18" t="n">
-        <v>51.36</v>
+        <v>49.4</v>
       </c>
       <c r="O18" t="n">
-        <v>51.45</v>
+        <v>49.49</v>
       </c>
       <c r="P18" t="n">
-        <v>49.79</v>
+        <v>48.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>50.22</v>
+        <v>48.59</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6933</v>
+        <v>13.0223</v>
       </c>
       <c r="S18" t="n">
-        <v>19.0215</v>
+        <v>13.5297</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6209</v>
+        <v>31.5809</v>
       </c>
       <c r="U18" t="n">
-        <v>2.7699</v>
+        <v>3.8207</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5074</v>
+        <v>6.0592</v>
       </c>
       <c r="W18" t="n">
-        <v>4.3798</v>
+        <v>10.9483</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.406</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y18" t="n">
-        <v>-16.7415</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z18" t="n">
-        <v>-3.9941</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA18" t="n">
-        <v>-2.7686</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB18" t="n">
-        <v>-7.086</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.3429</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>132.2</v>
+        <v>157.84</v>
       </c>
       <c r="C19" t="n">
-        <v>133.67</v>
+        <v>166</v>
       </c>
       <c r="D19" t="n">
-        <v>123.8</v>
+        <v>149.06</v>
       </c>
       <c r="E19" t="n">
-        <v>127.55</v>
+        <v>165.85</v>
       </c>
       <c r="F19" t="n">
-        <v>65.44</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>66.05</v>
+        <v>71.66</v>
       </c>
       <c r="H19" t="n">
-        <v>63.78</v>
+        <v>68.88</v>
       </c>
       <c r="I19" t="n">
-        <v>64.91</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>12.8</v>
+        <v>10.43</v>
       </c>
       <c r="K19" t="n">
-        <v>13.64</v>
+        <v>11.14</v>
       </c>
       <c r="L19" t="n">
-        <v>12.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>13.26</v>
+        <v>9.81</v>
       </c>
       <c r="N19" t="n">
-        <v>50.12</v>
+        <v>47.26</v>
       </c>
       <c r="O19" t="n">
-        <v>51.43</v>
+        <v>47.54</v>
       </c>
       <c r="P19" t="n">
-        <v>49.65</v>
+        <v>45.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>50.51</v>
+        <v>45.59</v>
       </c>
       <c r="R19" t="n">
-        <v>-2.1856</v>
+        <v>15.0458</v>
       </c>
       <c r="S19" t="n">
-        <v>8.120699999999999</v>
+        <v>27.1856</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3714</v>
+        <v>40.5866</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5972</v>
+        <v>6.2027</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9305</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>3.6239</v>
+        <v>15.6967</v>
       </c>
       <c r="X19" t="n">
-        <v>2.1572</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y19" t="n">
-        <v>-7.9167</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z19" t="n">
-        <v>-5.4882</v>
+        <v>-31.875</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.5775</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB19" t="n">
-        <v>-4.8417</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.6988</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>135</v>
+        <v>162.12</v>
       </c>
       <c r="C20" t="n">
-        <v>147.26</v>
+        <v>162.9</v>
       </c>
       <c r="D20" t="n">
-        <v>134.02</v>
+        <v>147.61</v>
       </c>
       <c r="E20" t="n">
-        <v>144.16</v>
+        <v>152.1</v>
       </c>
       <c r="F20" t="n">
-        <v>66.37</v>
+        <v>71.87</v>
       </c>
       <c r="G20" t="n">
-        <v>67.77</v>
+        <v>73.3</v>
       </c>
       <c r="H20" t="n">
-        <v>66.25</v>
+        <v>70.38</v>
       </c>
       <c r="I20" t="n">
-        <v>67.39</v>
+        <v>71.34</v>
       </c>
       <c r="J20" t="n">
-        <v>12.5</v>
+        <v>10.02</v>
       </c>
       <c r="K20" t="n">
-        <v>12.59</v>
+        <v>10.88</v>
       </c>
       <c r="L20" t="n">
-        <v>11.21</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>11.51</v>
+        <v>10.6</v>
       </c>
       <c r="N20" t="n">
-        <v>49.4</v>
+        <v>45.41</v>
       </c>
       <c r="O20" t="n">
-        <v>49.49</v>
+        <v>46.36</v>
       </c>
       <c r="P20" t="n">
-        <v>48.3</v>
+        <v>44.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>48.59</v>
+        <v>45.73</v>
       </c>
       <c r="R20" t="n">
-        <v>13.0223</v>
+        <v>-8.2906</v>
       </c>
       <c r="S20" t="n">
-        <v>13.5297</v>
+        <v>19.2474</v>
       </c>
       <c r="T20" t="n">
-        <v>31.5809</v>
+        <v>19.7826</v>
       </c>
       <c r="U20" t="n">
-        <v>3.8207</v>
+        <v>-0.3214</v>
       </c>
       <c r="V20" t="n">
-        <v>6.0592</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>10.9483</v>
+        <v>12.2757</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.1976</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>-13.4586</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z20" t="n">
-        <v>-26.1706</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.8012</v>
+        <v>0.3071</v>
       </c>
       <c r="AB20" t="n">
-        <v>-5.9245</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC20" t="n">
-        <v>-10.1018</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>157.84</v>
+        <v>163</v>
       </c>
       <c r="C21" t="n">
-        <v>166</v>
+        <v>177.5</v>
       </c>
       <c r="D21" t="n">
-        <v>149.06</v>
+        <v>161.51</v>
       </c>
       <c r="E21" t="n">
-        <v>165.85</v>
+        <v>176.94</v>
       </c>
       <c r="F21" t="n">
-        <v>69.26000000000001</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>71.66</v>
+        <v>76.31</v>
       </c>
       <c r="H21" t="n">
-        <v>68.88</v>
+        <v>72.7</v>
       </c>
       <c r="I21" t="n">
-        <v>71.56999999999999</v>
+        <v>76.28</v>
       </c>
       <c r="J21" t="n">
-        <v>10.43</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>11.14</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>9.800000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M21" t="n">
-        <v>9.81</v>
+        <v>8.85</v>
       </c>
       <c r="N21" t="n">
-        <v>47.26</v>
+        <v>44.82</v>
       </c>
       <c r="O21" t="n">
-        <v>47.54</v>
+        <v>44.89</v>
       </c>
       <c r="P21" t="n">
-        <v>45.52</v>
+        <v>42.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>45.59</v>
+        <v>42.57</v>
       </c>
       <c r="R21" t="n">
-        <v>15.0458</v>
+        <v>16.3314</v>
       </c>
       <c r="S21" t="n">
-        <v>27.1856</v>
+        <v>22.7386</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5866</v>
+        <v>35.6902</v>
       </c>
       <c r="U21" t="n">
-        <v>6.2027</v>
+        <v>6.9246</v>
       </c>
       <c r="V21" t="n">
-        <v>9.601800000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W21" t="n">
-        <v>15.6967</v>
+        <v>16.8147</v>
       </c>
       <c r="X21" t="n">
-        <v>-14.7698</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y21" t="n">
-        <v>-24.4222</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z21" t="n">
-        <v>-31.875</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA21" t="n">
-        <v>-6.1741</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB21" t="n">
-        <v>-9.2194</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC21" t="n">
-        <v>-14.1108</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>162.12</v>
+        <v>181</v>
       </c>
       <c r="C22" t="n">
-        <v>162.9</v>
+        <v>191.2899</v>
       </c>
       <c r="D22" t="n">
-        <v>147.61</v>
+        <v>178.94</v>
       </c>
       <c r="E22" t="n">
-        <v>152.1</v>
+        <v>190.42</v>
       </c>
       <c r="F22" t="n">
-        <v>71.87</v>
+        <v>76.02</v>
       </c>
       <c r="G22" t="n">
-        <v>73.3</v>
+        <v>77.36</v>
       </c>
       <c r="H22" t="n">
-        <v>70.38</v>
+        <v>75.55</v>
       </c>
       <c r="I22" t="n">
-        <v>71.34</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>10.02</v>
+        <v>8.65</v>
       </c>
       <c r="K22" t="n">
-        <v>10.88</v>
+        <v>8.77</v>
       </c>
       <c r="L22" t="n">
-        <v>9.970000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="M22" t="n">
-        <v>10.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>45.41</v>
+        <v>42.74</v>
       </c>
       <c r="O22" t="n">
-        <v>46.36</v>
+        <v>43</v>
       </c>
       <c r="P22" t="n">
-        <v>44.5</v>
+        <v>41.985</v>
       </c>
       <c r="Q22" t="n">
-        <v>45.73</v>
+        <v>42.22</v>
       </c>
       <c r="R22" t="n">
-        <v>-8.2906</v>
+        <v>7.6184</v>
       </c>
       <c r="S22" t="n">
-        <v>19.2474</v>
+        <v>14.8146</v>
       </c>
       <c r="T22" t="n">
-        <v>19.7826</v>
+        <v>49.2905</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3214</v>
+        <v>0.8915</v>
       </c>
       <c r="V22" t="n">
-        <v>9.906000000000001</v>
+        <v>7.5311</v>
       </c>
       <c r="W22" t="n">
-        <v>12.2757</v>
+        <v>18.5642</v>
       </c>
       <c r="X22" t="n">
-        <v>8.053000000000001</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y22" t="n">
-        <v>-20.0603</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z22" t="n">
-        <v>-20.3008</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.3071</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB22" t="n">
-        <v>-9.4635</v>
+        <v>-7.392</v>
       </c>
       <c r="AC22" t="n">
-        <v>-11.4618</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>163</v>
-      </c>
-      <c r="C23" t="n">
-        <v>177.495</v>
-      </c>
-      <c r="D23" t="n">
-        <v>161.51</v>
-      </c>
-      <c r="E23" t="n">
-        <v>176.94</v>
-      </c>
-      <c r="F23" t="n">
-        <v>72.825</v>
-      </c>
-      <c r="G23" t="n">
-        <v>76.31</v>
-      </c>
-      <c r="H23" t="n">
-        <v>72.69499999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>76.28</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="K23" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="L23" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="N23" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="O23" t="n">
-        <v>44.89</v>
-      </c>
-      <c r="P23" t="n">
-        <v>42.57</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>42.57</v>
-      </c>
-      <c r="R23" t="n">
-        <v>16.3314</v>
-      </c>
-      <c r="S23" t="n">
-        <v>22.7386</v>
-      </c>
-      <c r="T23" t="n">
-        <v>35.6902</v>
-      </c>
-      <c r="U23" t="n">
-        <v>6.9246</v>
-      </c>
-      <c r="V23" t="n">
-        <v>13.1919</v>
-      </c>
-      <c r="W23" t="n">
-        <v>16.8147</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-16.5094</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>-23.1103</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-31.8182</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-6.9101</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-12.3894</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-15.233</v>
+        <v>-16.4126</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26478,7 +26478,7 @@
         <v>181</v>
       </c>
       <c r="C22" t="n">
-        <v>191.2899</v>
+        <v>191.29</v>
       </c>
       <c r="D22" t="n">
         <v>178.94</v>
@@ -26487,7 +26487,7 @@
         <v>190.42</v>
       </c>
       <c r="F22" t="n">
-        <v>76.02</v>
+        <v>76</v>
       </c>
       <c r="G22" t="n">
         <v>77.36</v>
@@ -26517,7 +26517,7 @@
         <v>43</v>
       </c>
       <c r="P22" t="n">
-        <v>41.985</v>
+        <v>41.99</v>
       </c>
       <c r="Q22" t="n">
         <v>42.22</v>
@@ -26557,6 +26557,97 @@
       </c>
       <c r="AC22" t="n">
         <v>-16.4126</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>177.62</v>
+      </c>
+      <c r="C23" t="n">
+        <v>182.2399</v>
+      </c>
+      <c r="D23" t="n">
+        <v>150.58</v>
+      </c>
+      <c r="E23" t="n">
+        <v>172.52</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>75.92919999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="I23" t="n">
+        <v>74.95999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8.744999999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="N23" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="P23" t="n">
+        <v>42.785</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-9.4003</v>
+      </c>
+      <c r="S23" t="n">
+        <v>13.4254</v>
+      </c>
+      <c r="T23" t="n">
+        <v>19.6726</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-2.5988</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.0743</v>
+      </c>
+      <c r="W23" t="n">
+        <v>11.2331</v>
+      </c>
+      <c r="X23" t="n">
+        <v>9.1463</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-15.566</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-22.2415</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.5817</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-5.2919</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-10.8664</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75.59</v>
+        <v>83.27</v>
       </c>
       <c r="C2" t="n">
-        <v>80.73999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>75.25</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>80.56</v>
+        <v>85.31</v>
       </c>
       <c r="F2" t="n">
-        <v>48.78</v>
+        <v>51.39</v>
       </c>
       <c r="G2" t="n">
-        <v>50.74</v>
+        <v>53.43</v>
       </c>
       <c r="H2" t="n">
-        <v>48.46</v>
+        <v>51.38</v>
       </c>
       <c r="I2" t="n">
-        <v>50.66</v>
+        <v>53.41</v>
       </c>
       <c r="J2" t="n">
-        <v>23.92</v>
+        <v>21.6</v>
       </c>
       <c r="K2" t="n">
-        <v>24.03</v>
+        <v>22.34</v>
       </c>
       <c r="L2" t="n">
-        <v>22.32</v>
+        <v>21</v>
       </c>
       <c r="M2" t="n">
-        <v>22.42</v>
+        <v>21.05</v>
       </c>
       <c r="N2" t="n">
-        <v>68.2</v>
+        <v>64.67</v>
       </c>
       <c r="O2" t="n">
-        <v>68.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>65.5</v>
+        <v>62.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>65.56999999999999</v>
+        <v>62.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C3" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D3" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G3" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H3" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I3" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J3" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K3" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L3" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M3" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N3" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O3" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P3" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
       <c r="R3" t="n">
-        <v>5.8962</v>
+        <v>0.7619</v>
       </c>
       <c r="U3" t="n">
-        <v>5.4283</v>
+        <v>4.194</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.1106</v>
+        <v>-0.5226</v>
       </c>
       <c r="AA3" t="n">
-        <v>-5.4141</v>
+        <v>-4.1599</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D4" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E4" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F4" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G4" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H4" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I4" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J4" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K4" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L4" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M4" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N4" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O4" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P4" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="U4" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C5" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D5" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E5" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G5" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H5" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I5" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J5" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K5" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L5" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M5" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N5" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O5" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P5" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="S5" t="n">
-        <v>9.694599999999999</v>
+        <v>10.9835</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="V5" t="n">
-        <v>11.3897</v>
+        <v>9.698600000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="Y5" t="n">
-        <v>-9.545</v>
+        <v>-10.3563</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
       <c r="AB5" t="n">
-        <v>-10.6146</v>
+        <v>-9.0777</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C6" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E6" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F6" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G6" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H6" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I6" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J6" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K6" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L6" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M6" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N6" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O6" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P6" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R6" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S6" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="U6" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y6" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB6" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C7" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D7" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F7" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G7" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H7" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I7" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J7" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K7" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L7" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M7" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N7" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O7" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P7" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S7" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="T7" t="n">
-        <v>19.0914</v>
+        <v>14.9807</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V7" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="W7" t="n">
-        <v>14.6467</v>
+        <v>7.4705</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y7" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="Z7" t="n">
-        <v>-16.9045</v>
+        <v>-13.5392</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB7" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
       <c r="AC7" t="n">
-        <v>-13.2073</v>
+        <v>-7.1429</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C8" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D8" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F8" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G8" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H8" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I8" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J8" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K8" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L8" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M8" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N8" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O8" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P8" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R8" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S8" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T8" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W8" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y8" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC8" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C9" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D9" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E9" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F9" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G9" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H9" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I9" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J9" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K9" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L9" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M9" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N9" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O9" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P9" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R9" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S9" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T9" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U9" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V9" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W9" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y9" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z9" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA9" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C10" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D10" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E10" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F10" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G10" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H10" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I10" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J10" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K10" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L10" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M10" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N10" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O10" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P10" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q10" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R10" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S10" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T10" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W10" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y10" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z10" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC10" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C11" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D11" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E11" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F11" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G11" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H11" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I11" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J11" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K11" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L11" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M11" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N11" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O11" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P11" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R11" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S11" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T11" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U11" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W11" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X11" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y11" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z11" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA11" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC11" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C12" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D12" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E12" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F12" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G12" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H12" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I12" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J12" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K12" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L12" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M12" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N12" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O12" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P12" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R12" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S12" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T12" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V12" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W12" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X12" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y12" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z12" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB12" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC12" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C13" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D13" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E13" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F13" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G13" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H13" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I13" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J13" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K13" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L13" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M13" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N13" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O13" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P13" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R13" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W13" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X13" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z13" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB13" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C14" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D14" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E14" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G14" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H14" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I14" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J14" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K14" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L14" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N14" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O14" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P14" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R14" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T14" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z14" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC14" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C15" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D15" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E15" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F15" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G15" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H15" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I15" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J15" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K15" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L15" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M15" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N15" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O15" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P15" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R15" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T15" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U15" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W15" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y15" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z15" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC15" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C16" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D16" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E16" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F16" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G16" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H16" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I16" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J16" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K16" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L16" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M16" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N16" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O16" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P16" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S16" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U16" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W16" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y16" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z16" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA16" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB16" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC16" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C17" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D17" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E17" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F17" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G17" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H17" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I17" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J17" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K17" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L17" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M17" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N17" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O17" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P17" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R17" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S17" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W17" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X17" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y17" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z17" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB17" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C18" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D18" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E18" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F18" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H18" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I18" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K18" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L18" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N18" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O18" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P18" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R18" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S18" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T18" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U18" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V18" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X18" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y18" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z18" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA18" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB18" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC18" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C19" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D19" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E19" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F19" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G19" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H19" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I19" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J19" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K19" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N19" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O19" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P19" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R19" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S19" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T19" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U19" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V19" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X19" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z19" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA19" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB19" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC19" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C20" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D20" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E20" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F20" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H20" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I20" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J20" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M20" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N20" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O20" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P20" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R20" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S20" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="T20" t="n">
-        <v>19.7826</v>
+        <v>35.6902</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V20" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W20" t="n">
-        <v>12.2757</v>
+        <v>16.8147</v>
       </c>
       <c r="X20" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y20" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z20" t="n">
-        <v>-20.3008</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB20" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC20" t="n">
-        <v>-11.4618</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C21" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D21" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E21" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F21" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G21" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H21" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I21" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K21" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L21" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M21" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O21" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P21" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R21" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S21" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="T21" t="n">
-        <v>35.6902</v>
+        <v>49.2905</v>
       </c>
       <c r="U21" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V21" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="W21" t="n">
-        <v>16.8147</v>
+        <v>18.5642</v>
       </c>
       <c r="X21" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y21" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z21" t="n">
-        <v>-31.8182</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA21" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB21" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
       <c r="AC21" t="n">
-        <v>-15.233</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C22" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D22" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E22" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F22" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G22" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I22" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K22" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L22" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O22" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P22" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R22" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S22" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="T22" t="n">
-        <v>49.2905</v>
+        <v>19.6726</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="W22" t="n">
-        <v>18.5642</v>
+        <v>11.2331</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y22" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="Z22" t="n">
-        <v>-38.1599</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB22" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC22" t="n">
-        <v>-16.4126</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>177.62</v>
+        <v>183.835</v>
       </c>
       <c r="C23" t="n">
-        <v>182.2399</v>
+        <v>188.488</v>
       </c>
       <c r="D23" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E23" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F23" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G23" t="n">
-        <v>75.92919999999999</v>
+        <v>77.94</v>
       </c>
       <c r="H23" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I23" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>8.744999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L23" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N23" t="n">
-        <v>43.14</v>
+        <v>42.87</v>
       </c>
       <c r="O23" t="n">
-        <v>45.19</v>
+        <v>43.765</v>
       </c>
       <c r="P23" t="n">
-        <v>42.785</v>
+        <v>41.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R23" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S23" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T23" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V23" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W23" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X23" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y23" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z23" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB23" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC23" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83.27</v>
+        <v>84.66</v>
       </c>
       <c r="C2" t="n">
-        <v>85.56999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="D2" t="n">
-        <v>80.70999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>85.31</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>51.39</v>
+        <v>53.57</v>
       </c>
       <c r="G2" t="n">
-        <v>53.43</v>
+        <v>55.74</v>
       </c>
       <c r="H2" t="n">
-        <v>51.38</v>
+        <v>53.33</v>
       </c>
       <c r="I2" t="n">
-        <v>53.41</v>
+        <v>55.65</v>
       </c>
       <c r="J2" t="n">
-        <v>21.6</v>
+        <v>21.23</v>
       </c>
       <c r="K2" t="n">
-        <v>22.34</v>
+        <v>22.43</v>
       </c>
       <c r="L2" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M2" t="n">
-        <v>21.05</v>
+        <v>20.94</v>
       </c>
       <c r="N2" t="n">
-        <v>64.67</v>
+        <v>61.88</v>
       </c>
       <c r="O2" t="n">
-        <v>64.68000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="P2" t="n">
-        <v>62.02</v>
+        <v>59.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>62.02</v>
+        <v>59.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D3" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E3" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F3" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G3" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H3" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I3" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J3" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K3" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L3" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M3" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N3" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O3" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P3" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7619</v>
+        <v>2.8036</v>
       </c>
       <c r="U3" t="n">
-        <v>4.194</v>
+        <v>1.4016</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5226</v>
+        <v>-3.1519</v>
       </c>
       <c r="AA3" t="n">
-        <v>-4.1599</v>
+        <v>-1.3964</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C4" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D4" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E4" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G4" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H4" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I4" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J4" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K4" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L4" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M4" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N4" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O4" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P4" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C5" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E5" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F5" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G5" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H5" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I5" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J5" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K5" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L5" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M5" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N5" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O5" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P5" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R5" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="S5" t="n">
-        <v>10.9835</v>
+        <v>11.6101</v>
       </c>
       <c r="U5" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>9.698600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="Y5" t="n">
-        <v>-10.3563</v>
+        <v>-11.0315</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
       <c r="AB5" t="n">
-        <v>-9.0777</v>
+        <v>-4.2564</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C6" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D6" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F6" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G6" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H6" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I6" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J6" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K6" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L6" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M6" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N6" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O6" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P6" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S6" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V6" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y6" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB6" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C7" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D7" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F7" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G7" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H7" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I7" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J7" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K7" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L7" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M7" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N7" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O7" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P7" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R7" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S7" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="T7" t="n">
-        <v>14.9807</v>
+        <v>22.8944</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="W7" t="n">
-        <v>7.4705</v>
+        <v>8.194100000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y7" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="Z7" t="n">
-        <v>-13.5392</v>
+        <v>-19.7708</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
       <c r="AC7" t="n">
-        <v>-7.1429</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C8" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D8" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E8" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F8" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G8" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H8" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I8" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J8" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K8" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L8" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M8" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N8" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O8" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P8" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R8" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S8" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T8" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U8" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V8" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W8" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y8" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z8" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA8" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC8" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C9" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D9" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E9" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F9" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G9" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H9" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I9" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J9" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K9" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L9" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M9" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N9" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O9" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P9" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R9" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S9" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T9" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W9" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y9" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z9" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C10" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D10" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E10" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F10" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G10" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H10" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I10" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J10" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K10" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L10" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M10" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N10" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O10" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P10" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R10" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T10" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U10" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V10" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W10" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X10" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y10" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z10" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA10" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC10" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C11" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D11" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E11" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F11" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G11" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H11" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I11" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J11" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K11" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L11" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M11" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N11" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O11" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P11" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R11" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S11" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T11" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V11" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W11" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X11" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y11" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z11" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC11" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C12" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D12" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E12" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F12" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H12" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I12" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J12" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K12" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L12" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M12" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N12" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O12" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P12" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R12" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W12" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X12" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z12" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC12" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C13" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D13" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E13" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G13" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H13" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I13" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J13" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K13" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L13" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N13" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O13" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P13" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R13" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T13" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z13" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC13" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C14" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D14" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E14" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F14" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G14" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H14" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I14" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J14" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K14" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L14" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M14" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N14" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O14" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P14" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R14" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T14" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W14" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y14" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z14" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA14" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC14" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C15" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D15" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E15" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F15" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G15" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H15" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I15" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J15" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K15" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L15" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M15" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N15" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O15" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P15" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S15" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U15" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W15" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y15" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z15" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB15" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C16" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D16" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E16" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F16" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G16" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H16" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I16" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J16" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K16" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L16" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M16" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N16" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O16" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P16" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R16" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S16" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V16" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y16" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z16" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB16" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC16" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C17" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D17" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E17" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F17" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H17" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I17" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K17" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L17" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N17" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O17" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P17" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R17" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S17" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T17" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U17" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V17" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y17" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z17" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA17" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB17" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC17" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C18" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D18" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E18" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F18" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G18" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H18" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I18" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J18" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K18" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N18" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O18" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P18" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R18" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S18" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T18" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U18" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V18" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X18" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z18" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA18" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB18" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC18" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C19" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D19" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E19" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F19" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H19" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I19" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J19" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M19" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N19" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O19" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P19" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R19" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S19" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="T19" t="n">
-        <v>19.7826</v>
+        <v>35.6902</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V19" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W19" t="n">
-        <v>12.2757</v>
+        <v>16.8147</v>
       </c>
       <c r="X19" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y19" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z19" t="n">
-        <v>-20.3008</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB19" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC19" t="n">
-        <v>-11.4618</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C20" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D20" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E20" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F20" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G20" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H20" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I20" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K20" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L20" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M20" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O20" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P20" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R20" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S20" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="T20" t="n">
-        <v>35.6902</v>
+        <v>49.2905</v>
       </c>
       <c r="U20" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="W20" t="n">
-        <v>16.8147</v>
+        <v>18.5642</v>
       </c>
       <c r="X20" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y20" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z20" t="n">
-        <v>-31.8182</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA20" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB20" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
       <c r="AC20" t="n">
-        <v>-15.233</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C21" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D21" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E21" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G21" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I21" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K21" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L21" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O21" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P21" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R21" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S21" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="T21" t="n">
-        <v>49.2905</v>
+        <v>19.6726</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="W21" t="n">
-        <v>18.5642</v>
+        <v>11.2331</v>
       </c>
       <c r="X21" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y21" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="Z21" t="n">
-        <v>-38.1599</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB21" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC21" t="n">
-        <v>-16.4126</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C22" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D22" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E22" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F22" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G22" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H22" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I22" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L22" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N22" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O22" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P22" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R22" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S22" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T22" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V22" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W22" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X22" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y22" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z22" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB22" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC22" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>183.835</v>
+        <v>182.67</v>
       </c>
       <c r="C23" t="n">
-        <v>188.488</v>
+        <v>189.56</v>
       </c>
       <c r="D23" t="n">
-        <v>172.26</v>
+        <v>178.2775</v>
       </c>
       <c r="E23" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F23" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>74.19</v>
+        <v>77.155</v>
       </c>
       <c r="I23" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J23" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K23" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N23" t="n">
-        <v>42.87</v>
+        <v>41.99</v>
       </c>
       <c r="O23" t="n">
-        <v>43.765</v>
+        <v>42.06</v>
       </c>
       <c r="P23" t="n">
-        <v>41.6</v>
+        <v>40.6801</v>
       </c>
       <c r="Q23" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R23" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T23" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U23" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W23" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y23" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z23" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA23" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB23" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC23" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.66</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>85.98</v>
+        <v>89.39</v>
       </c>
       <c r="D2" t="n">
-        <v>79.76000000000001</v>
+        <v>83.31</v>
       </c>
       <c r="E2" t="n">
-        <v>85.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F2" t="n">
-        <v>53.57</v>
+        <v>56.13</v>
       </c>
       <c r="G2" t="n">
-        <v>55.74</v>
+        <v>56.92</v>
       </c>
       <c r="H2" t="n">
-        <v>53.33</v>
+        <v>55.1</v>
       </c>
       <c r="I2" t="n">
-        <v>55.65</v>
+        <v>56.43</v>
       </c>
       <c r="J2" t="n">
-        <v>21.23</v>
+        <v>21.13</v>
       </c>
       <c r="K2" t="n">
-        <v>22.43</v>
+        <v>21.56</v>
       </c>
       <c r="L2" t="n">
-        <v>20.9</v>
+        <v>20.07</v>
       </c>
       <c r="M2" t="n">
-        <v>20.94</v>
+        <v>20.28</v>
       </c>
       <c r="N2" t="n">
-        <v>61.88</v>
+        <v>58.95</v>
       </c>
       <c r="O2" t="n">
-        <v>62.15</v>
+        <v>60.06</v>
       </c>
       <c r="P2" t="n">
-        <v>59.35</v>
+        <v>58.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>59.44</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85.01000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="C3" t="n">
-        <v>89.39</v>
+        <v>94.75</v>
       </c>
       <c r="D3" t="n">
-        <v>83.31</v>
+        <v>90.66</v>
       </c>
       <c r="E3" t="n">
-        <v>88.37</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>56.13</v>
+        <v>57.78</v>
       </c>
       <c r="G3" t="n">
-        <v>56.92</v>
+        <v>58.94</v>
       </c>
       <c r="H3" t="n">
-        <v>55.1</v>
+        <v>57.37</v>
       </c>
       <c r="I3" t="n">
-        <v>56.43</v>
+        <v>58.59</v>
       </c>
       <c r="J3" t="n">
-        <v>21.13</v>
+        <v>19.23</v>
       </c>
       <c r="K3" t="n">
-        <v>21.56</v>
+        <v>19.8</v>
       </c>
       <c r="L3" t="n">
-        <v>20.07</v>
+        <v>18.86</v>
       </c>
       <c r="M3" t="n">
-        <v>20.28</v>
+        <v>18.87</v>
       </c>
       <c r="N3" t="n">
-        <v>58.95</v>
+        <v>57.25</v>
       </c>
       <c r="O3" t="n">
-        <v>60.06</v>
+        <v>57.67</v>
       </c>
       <c r="P3" t="n">
-        <v>58.11</v>
+        <v>56.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>58.61</v>
+        <v>56.39</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8036</v>
+        <v>7.1404</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4016</v>
+        <v>3.8278</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.1519</v>
+        <v>-6.9527</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.3964</v>
+        <v>-3.7877</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93.2</v>
+        <v>95.97</v>
       </c>
       <c r="C4" t="n">
-        <v>94.75</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>90.66</v>
+        <v>92.03</v>
       </c>
       <c r="E4" t="n">
-        <v>94.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="F4" t="n">
-        <v>57.78</v>
+        <v>58.4</v>
       </c>
       <c r="G4" t="n">
-        <v>58.94</v>
+        <v>58.58</v>
       </c>
       <c r="H4" t="n">
-        <v>57.37</v>
+        <v>56.91</v>
       </c>
       <c r="I4" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="J4" t="n">
-        <v>19.23</v>
+        <v>18.64</v>
       </c>
       <c r="K4" t="n">
-        <v>19.8</v>
+        <v>19.41</v>
       </c>
       <c r="L4" t="n">
-        <v>18.86</v>
+        <v>18.44</v>
       </c>
       <c r="M4" t="n">
-        <v>18.87</v>
+        <v>18.63</v>
       </c>
       <c r="N4" t="n">
-        <v>57.25</v>
+        <v>56.59</v>
       </c>
       <c r="O4" t="n">
-        <v>57.67</v>
+        <v>58.04</v>
       </c>
       <c r="P4" t="n">
-        <v>56.04</v>
+        <v>56.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R4" t="n">
-        <v>7.1404</v>
+        <v>1.3308</v>
       </c>
       <c r="U4" t="n">
-        <v>3.8278</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.9527</v>
+        <v>-1.2719</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3.7877</v>
+        <v>0.9221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C5" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D5" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F5" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G5" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H5" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I5" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J5" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K5" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L5" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M5" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N5" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O5" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P5" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3308</v>
+        <v>2.241</v>
       </c>
       <c r="S5" t="n">
-        <v>11.6101</v>
+        <v>10.9992</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.1708</v>
       </c>
       <c r="V5" t="n">
-        <v>4.3666</v>
+        <v>1.7189</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2719</v>
+        <v>-2.3081</v>
       </c>
       <c r="Y5" t="n">
-        <v>-11.0315</v>
+        <v>-10.2564</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.9221</v>
+        <v>1.1949</v>
       </c>
       <c r="AB5" t="n">
-        <v>-4.2564</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C6" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D6" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F6" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G6" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H6" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I6" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J6" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K6" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L6" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M6" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N6" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O6" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P6" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R6" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="S6" t="n">
-        <v>10.9992</v>
+        <v>11.5758</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7189</v>
+        <v>2.765</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="Y6" t="n">
-        <v>-10.2564</v>
+        <v>-10.9698</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.7403</v>
+        <v>-2.9438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C7" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D7" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E7" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F7" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G7" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H7" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I7" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J7" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K7" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L7" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M7" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N7" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O7" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P7" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R7" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="S7" t="n">
-        <v>11.5758</v>
+        <v>17.5422</v>
       </c>
       <c r="T7" t="n">
-        <v>22.8944</v>
+        <v>27.6112</v>
       </c>
       <c r="U7" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="V7" t="n">
-        <v>2.765</v>
+        <v>1.9628</v>
       </c>
       <c r="W7" t="n">
-        <v>8.194100000000001</v>
+        <v>4.9442</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y7" t="n">
-        <v>-10.9698</v>
+        <v>-15.7273</v>
       </c>
       <c r="Z7" t="n">
-        <v>-19.7708</v>
+        <v>-22.5838</v>
       </c>
       <c r="AA7" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.9438</v>
+        <v>-2.1965</v>
       </c>
       <c r="AC7" t="n">
-        <v>-7.924</v>
+        <v>-5.0333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C8" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D8" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E8" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F8" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G8" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H8" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I8" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J8" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K8" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L8" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M8" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N8" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O8" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P8" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R8" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S8" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="T8" t="n">
-        <v>27.6112</v>
+        <v>35.5302</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V8" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="W8" t="n">
-        <v>4.9442</v>
+        <v>6.7759</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y8" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="Z8" t="n">
-        <v>-22.5838</v>
+        <v>-28.3519</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
       <c r="AC8" t="n">
-        <v>-5.0333</v>
+        <v>-6.8984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C9" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D9" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E9" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F9" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G9" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H9" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I9" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J9" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K9" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L9" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M9" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N9" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O9" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P9" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R9" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S9" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="T9" t="n">
-        <v>35.5302</v>
+        <v>28.6116</v>
       </c>
       <c r="U9" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V9" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="W9" t="n">
-        <v>6.7759</v>
+        <v>7.8512</v>
       </c>
       <c r="X9" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y9" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z9" t="n">
-        <v>-28.3519</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA9" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.8984</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C10" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D10" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E10" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F10" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G10" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H10" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I10" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J10" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K10" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L10" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M10" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N10" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O10" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P10" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R10" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S10" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T10" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V10" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W10" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X10" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y10" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z10" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB10" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC10" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C11" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D11" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E11" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F11" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H11" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I11" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J11" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K11" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L11" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M11" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N11" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O11" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P11" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R11" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W11" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X11" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z11" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB11" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC11" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C12" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D12" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E12" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G12" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H12" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I12" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J12" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K12" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L12" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M12" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N12" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O12" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P12" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R12" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T12" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W12" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z12" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC12" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C13" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D13" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E13" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F13" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G13" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H13" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I13" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J13" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K13" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L13" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M13" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N13" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O13" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P13" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R13" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T13" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y13" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z13" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA13" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC13" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C14" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D14" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E14" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F14" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G14" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H14" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I14" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J14" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K14" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L14" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M14" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N14" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O14" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P14" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S14" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W14" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y14" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z14" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA14" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB14" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC14" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C15" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D15" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E15" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F15" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G15" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H15" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I15" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J15" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K15" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L15" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M15" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N15" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O15" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P15" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R15" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S15" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V15" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y15" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z15" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB15" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC15" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C16" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D16" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E16" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F16" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H16" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I16" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K16" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L16" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N16" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O16" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P16" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R16" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S16" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T16" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U16" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V16" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X16" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y16" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z16" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB16" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC16" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C17" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D17" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E17" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F17" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G17" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H17" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I17" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J17" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K17" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N17" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O17" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P17" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R17" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S17" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T17" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U17" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V17" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X17" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z17" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA17" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB17" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC17" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C18" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D18" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E18" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F18" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H18" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I18" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J18" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M18" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N18" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O18" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P18" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R18" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S18" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="T18" t="n">
-        <v>19.7826</v>
+        <v>35.6902</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V18" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W18" t="n">
-        <v>12.2757</v>
+        <v>16.8147</v>
       </c>
       <c r="X18" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y18" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z18" t="n">
-        <v>-20.3008</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB18" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC18" t="n">
-        <v>-11.4618</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C19" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D19" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E19" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F19" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H19" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I19" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K19" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L19" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M19" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O19" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P19" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R19" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S19" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="T19" t="n">
-        <v>35.6902</v>
+        <v>49.2905</v>
       </c>
       <c r="U19" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V19" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="W19" t="n">
-        <v>16.8147</v>
+        <v>18.5642</v>
       </c>
       <c r="X19" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y19" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z19" t="n">
-        <v>-31.8182</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA19" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB19" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
       <c r="AC19" t="n">
-        <v>-15.233</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C20" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D20" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E20" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G20" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I20" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K20" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L20" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O20" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P20" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R20" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S20" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="T20" t="n">
-        <v>49.2905</v>
+        <v>19.6726</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V20" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="W20" t="n">
-        <v>18.5642</v>
+        <v>11.2331</v>
       </c>
       <c r="X20" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y20" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="Z20" t="n">
-        <v>-38.1599</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB20" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC20" t="n">
-        <v>-16.4126</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C21" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D21" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E21" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F21" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G21" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H21" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I21" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L21" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N21" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O21" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P21" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R21" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S21" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T21" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V21" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W21" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X21" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y21" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z21" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB21" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC21" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>183.84</v>
+        <v>182.67</v>
       </c>
       <c r="C22" t="n">
-        <v>188.49</v>
+        <v>189.56</v>
       </c>
       <c r="D22" t="n">
-        <v>172.26</v>
+        <v>178.28</v>
       </c>
       <c r="E22" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F22" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>74.19</v>
+        <v>77.16</v>
       </c>
       <c r="I22" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J22" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K22" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N22" t="n">
-        <v>42.83</v>
+        <v>41.98</v>
       </c>
       <c r="O22" t="n">
-        <v>43.77</v>
+        <v>42.06</v>
       </c>
       <c r="P22" t="n">
-        <v>41.6</v>
+        <v>40.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R22" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T22" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U22" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W22" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y22" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z22" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA22" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB22" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC22" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>182.67</v>
+        <v>167</v>
       </c>
       <c r="C23" t="n">
-        <v>189.56</v>
+        <v>174.4</v>
       </c>
       <c r="D23" t="n">
-        <v>178.2775</v>
+        <v>161.1402</v>
       </c>
       <c r="E23" t="n">
-        <v>186.19</v>
+        <v>164.18</v>
       </c>
       <c r="F23" t="n">
-        <v>77.29000000000001</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>79.68000000000001</v>
+        <v>77.36499999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>77.155</v>
+        <v>74.22799999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>78.95</v>
+        <v>75.34</v>
       </c>
       <c r="J23" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>8.630000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>8.27</v>
+        <v>9.23</v>
       </c>
       <c r="N23" t="n">
-        <v>41.99</v>
+        <v>42.77</v>
       </c>
       <c r="O23" t="n">
-        <v>42.06</v>
+        <v>43.565</v>
       </c>
       <c r="P23" t="n">
-        <v>40.6801</v>
+        <v>41.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>41.07</v>
+        <v>42.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0584</v>
+        <v>-11.8213</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2214</v>
+        <v>-4.8342</v>
       </c>
       <c r="T23" t="n">
-        <v>22.4129</v>
+        <v>-7.2115</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2139</v>
+        <v>-4.5725</v>
       </c>
       <c r="V23" t="n">
-        <v>2.5858</v>
+        <v>0.5069</v>
       </c>
       <c r="W23" t="n">
-        <v>10.6672</v>
+        <v>-1.2323</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9581</v>
+        <v>11.6082</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.8537</v>
+        <v>3.1285</v>
       </c>
       <c r="Z23" t="n">
-        <v>-21.9811</v>
+        <v>4.2938</v>
       </c>
       <c r="AA23" t="n">
-        <v>-2.191</v>
+        <v>4.6506</v>
       </c>
       <c r="AB23" t="n">
-        <v>-2.7238</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC23" t="n">
-        <v>-10.1902</v>
+        <v>0.9631</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24759,1895 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85.01000000000001</v>
+        <v>95.97</v>
       </c>
       <c r="C2" t="n">
-        <v>89.39</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>83.31</v>
+        <v>92.03</v>
       </c>
       <c r="E2" t="n">
-        <v>88.37</v>
+        <v>95.94</v>
       </c>
       <c r="F2" t="n">
-        <v>56.13</v>
+        <v>58.4</v>
       </c>
       <c r="G2" t="n">
-        <v>56.92</v>
+        <v>58.58</v>
       </c>
       <c r="H2" t="n">
-        <v>55.1</v>
+        <v>56.91</v>
       </c>
       <c r="I2" t="n">
-        <v>56.43</v>
+        <v>58.08</v>
       </c>
       <c r="J2" t="n">
-        <v>21.13</v>
+        <v>18.64</v>
       </c>
       <c r="K2" t="n">
-        <v>21.56</v>
+        <v>19.41</v>
       </c>
       <c r="L2" t="n">
-        <v>20.07</v>
+        <v>18.44</v>
       </c>
       <c r="M2" t="n">
-        <v>20.28</v>
+        <v>18.63</v>
       </c>
       <c r="N2" t="n">
-        <v>58.95</v>
+        <v>56.59</v>
       </c>
       <c r="O2" t="n">
-        <v>60.06</v>
+        <v>58.04</v>
       </c>
       <c r="P2" t="n">
-        <v>58.11</v>
+        <v>56.41</v>
       </c>
       <c r="Q2" t="n">
-        <v>58.61</v>
+        <v>56.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93.2</v>
+        <v>97.97</v>
       </c>
       <c r="C3" t="n">
-        <v>94.75</v>
+        <v>99.95</v>
       </c>
       <c r="D3" t="n">
-        <v>90.66</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>94.68000000000001</v>
+        <v>98.09</v>
       </c>
       <c r="F3" t="n">
-        <v>57.78</v>
+        <v>58.48</v>
       </c>
       <c r="G3" t="n">
-        <v>58.94</v>
+        <v>58.97</v>
       </c>
       <c r="H3" t="n">
-        <v>57.37</v>
+        <v>56.82</v>
       </c>
       <c r="I3" t="n">
-        <v>58.59</v>
+        <v>57.4</v>
       </c>
       <c r="J3" t="n">
-        <v>19.23</v>
+        <v>18.25</v>
       </c>
       <c r="K3" t="n">
-        <v>19.8</v>
+        <v>18.76</v>
       </c>
       <c r="L3" t="n">
-        <v>18.86</v>
+        <v>17.85</v>
       </c>
       <c r="M3" t="n">
-        <v>18.87</v>
+        <v>18.2</v>
       </c>
       <c r="N3" t="n">
-        <v>57.25</v>
+        <v>56.52</v>
       </c>
       <c r="O3" t="n">
-        <v>57.67</v>
+        <v>58.15</v>
       </c>
       <c r="P3" t="n">
         <v>56.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>56.39</v>
+        <v>57.59</v>
       </c>
       <c r="R3" t="n">
-        <v>7.1404</v>
+        <v>2.241</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8278</v>
+        <v>-1.1708</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.9527</v>
+        <v>-2.3081</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3.7877</v>
+        <v>1.1949</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.97</v>
+        <v>102.94</v>
       </c>
       <c r="C4" t="n">
-        <v>96.93000000000001</v>
+        <v>106.09</v>
       </c>
       <c r="D4" t="n">
-        <v>92.03</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>95.94</v>
+        <v>105.64</v>
       </c>
       <c r="F4" t="n">
-        <v>58.4</v>
+        <v>58.93</v>
       </c>
       <c r="G4" t="n">
-        <v>58.58</v>
+        <v>60.3</v>
       </c>
       <c r="H4" t="n">
-        <v>56.91</v>
+        <v>58.49</v>
       </c>
       <c r="I4" t="n">
-        <v>58.08</v>
+        <v>60.21</v>
       </c>
       <c r="J4" t="n">
-        <v>18.64</v>
+        <v>17.37</v>
       </c>
       <c r="K4" t="n">
-        <v>19.41</v>
+        <v>17.95</v>
       </c>
       <c r="L4" t="n">
-        <v>18.44</v>
+        <v>16.72</v>
       </c>
       <c r="M4" t="n">
-        <v>18.63</v>
+        <v>16.8</v>
       </c>
       <c r="N4" t="n">
-        <v>56.59</v>
+        <v>56.05</v>
       </c>
       <c r="O4" t="n">
-        <v>58.04</v>
+        <v>56.49</v>
       </c>
       <c r="P4" t="n">
-        <v>56.41</v>
+        <v>54.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>56.91</v>
+        <v>54.73</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3308</v>
+        <v>7.697</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8705000000000001</v>
+        <v>4.8955</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2719</v>
+        <v>-7.6923</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9221</v>
+        <v>-4.9661</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97.97</v>
+        <v>108.62</v>
       </c>
       <c r="C5" t="n">
-        <v>99.95</v>
+        <v>116.77</v>
       </c>
       <c r="D5" t="n">
-        <v>95.31999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E5" t="n">
-        <v>98.09</v>
+        <v>112.77</v>
       </c>
       <c r="F5" t="n">
-        <v>58.48</v>
+        <v>59.8</v>
       </c>
       <c r="G5" t="n">
-        <v>58.97</v>
+        <v>60.73</v>
       </c>
       <c r="H5" t="n">
-        <v>56.82</v>
+        <v>57.59</v>
       </c>
       <c r="I5" t="n">
-        <v>57.4</v>
+        <v>59.22</v>
       </c>
       <c r="J5" t="n">
-        <v>18.25</v>
+        <v>16.35</v>
       </c>
       <c r="K5" t="n">
-        <v>18.76</v>
+        <v>16.52</v>
       </c>
       <c r="L5" t="n">
-        <v>17.85</v>
+        <v>15.06</v>
       </c>
       <c r="M5" t="n">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>56.52</v>
+        <v>55.13</v>
       </c>
       <c r="O5" t="n">
-        <v>58.15</v>
+        <v>57.14</v>
       </c>
       <c r="P5" t="n">
-        <v>56.04</v>
+        <v>54.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.59</v>
+        <v>55.66</v>
       </c>
       <c r="R5" t="n">
-        <v>2.241</v>
+        <v>6.7493</v>
       </c>
       <c r="S5" t="n">
-        <v>10.9992</v>
+        <v>17.5422</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1708</v>
+        <v>-1.6442</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7189</v>
+        <v>1.9628</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3081</v>
+        <v>-6.5476</v>
       </c>
       <c r="Y5" t="n">
-        <v>-10.2564</v>
+        <v>-15.7273</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.1949</v>
+        <v>1.6993</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.7403</v>
+        <v>-2.1965</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102.94</v>
+        <v>125.21</v>
       </c>
       <c r="C6" t="n">
-        <v>106.09</v>
+        <v>130.12</v>
       </c>
       <c r="D6" t="n">
-        <v>99.59999999999999</v>
+        <v>120.24</v>
       </c>
       <c r="E6" t="n">
-        <v>105.64</v>
+        <v>128.32</v>
       </c>
       <c r="F6" t="n">
-        <v>58.93</v>
+        <v>61.08</v>
       </c>
       <c r="G6" t="n">
-        <v>60.3</v>
+        <v>62.74</v>
       </c>
       <c r="H6" t="n">
-        <v>58.49</v>
+        <v>60.56</v>
       </c>
       <c r="I6" t="n">
-        <v>60.21</v>
+        <v>62.56</v>
       </c>
       <c r="J6" t="n">
-        <v>17.37</v>
+        <v>13.99</v>
       </c>
       <c r="K6" t="n">
-        <v>17.95</v>
+        <v>14.66</v>
       </c>
       <c r="L6" t="n">
-        <v>16.72</v>
+        <v>13.3</v>
       </c>
       <c r="M6" t="n">
-        <v>16.8</v>
+        <v>13.52</v>
       </c>
       <c r="N6" t="n">
-        <v>56.05</v>
+        <v>53.93</v>
       </c>
       <c r="O6" t="n">
-        <v>56.49</v>
+        <v>54.43</v>
       </c>
       <c r="P6" t="n">
-        <v>54.66</v>
+        <v>52.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>54.73</v>
+        <v>52.5</v>
       </c>
       <c r="R6" t="n">
-        <v>7.697</v>
+        <v>13.7891</v>
       </c>
       <c r="S6" t="n">
-        <v>11.5758</v>
+        <v>30.8186</v>
       </c>
       <c r="U6" t="n">
-        <v>4.8955</v>
+        <v>5.64</v>
       </c>
       <c r="V6" t="n">
-        <v>2.765</v>
+        <v>8.9895</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.6923</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y6" t="n">
-        <v>-10.9698</v>
+        <v>-25.7143</v>
       </c>
       <c r="AA6" t="n">
-        <v>-4.9661</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.9438</v>
+        <v>-8.8383</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108.62</v>
+        <v>128.33</v>
       </c>
       <c r="C7" t="n">
-        <v>116.77</v>
+        <v>129.59</v>
       </c>
       <c r="D7" t="n">
-        <v>107.46</v>
+        <v>117.79</v>
       </c>
       <c r="E7" t="n">
-        <v>112.77</v>
+        <v>123.39</v>
       </c>
       <c r="F7" t="n">
-        <v>59.8</v>
+        <v>62.41</v>
       </c>
       <c r="G7" t="n">
-        <v>60.73</v>
+        <v>62.7</v>
       </c>
       <c r="H7" t="n">
-        <v>57.59</v>
+        <v>61.64</v>
       </c>
       <c r="I7" t="n">
-        <v>59.22</v>
+        <v>62.64</v>
       </c>
       <c r="J7" t="n">
-        <v>16.35</v>
+        <v>13.51</v>
       </c>
       <c r="K7" t="n">
-        <v>16.52</v>
+        <v>14.63</v>
       </c>
       <c r="L7" t="n">
-        <v>15.06</v>
+        <v>13.41</v>
       </c>
       <c r="M7" t="n">
-        <v>15.7</v>
+        <v>14.03</v>
       </c>
       <c r="N7" t="n">
-        <v>55.13</v>
+        <v>52.67</v>
       </c>
       <c r="O7" t="n">
-        <v>57.14</v>
+        <v>53.31</v>
       </c>
       <c r="P7" t="n">
-        <v>54.28</v>
+        <v>52.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>55.66</v>
+        <v>52.45</v>
       </c>
       <c r="R7" t="n">
-        <v>6.7493</v>
+        <v>-3.842</v>
       </c>
       <c r="S7" t="n">
-        <v>17.5422</v>
+        <v>16.8023</v>
       </c>
       <c r="T7" t="n">
-        <v>27.6112</v>
+        <v>28.6116</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6442</v>
+        <v>0.1279</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9628</v>
+        <v>4.0359</v>
       </c>
       <c r="W7" t="n">
-        <v>4.9442</v>
+        <v>7.8512</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.5476</v>
+        <v>3.7722</v>
       </c>
       <c r="Y7" t="n">
-        <v>-15.7273</v>
+        <v>-16.4881</v>
       </c>
       <c r="Z7" t="n">
-        <v>-22.5838</v>
+        <v>-24.6914</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6993</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.1965</v>
+        <v>-4.1659</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.0333</v>
+        <v>-7.8369</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>125.21</v>
+        <v>108.75</v>
       </c>
       <c r="C8" t="n">
-        <v>130.12</v>
+        <v>115.62</v>
       </c>
       <c r="D8" t="n">
-        <v>120.24</v>
+        <v>103.99</v>
       </c>
       <c r="E8" t="n">
-        <v>128.32</v>
+        <v>109.56</v>
       </c>
       <c r="F8" t="n">
-        <v>61.08</v>
+        <v>60.72</v>
       </c>
       <c r="G8" t="n">
-        <v>62.74</v>
+        <v>61.33</v>
       </c>
       <c r="H8" t="n">
-        <v>60.56</v>
+        <v>59.68</v>
       </c>
       <c r="I8" t="n">
-        <v>62.56</v>
+        <v>60.74</v>
       </c>
       <c r="J8" t="n">
-        <v>13.99</v>
+        <v>15.71</v>
       </c>
       <c r="K8" t="n">
-        <v>14.66</v>
+        <v>16.27</v>
       </c>
       <c r="L8" t="n">
-        <v>13.3</v>
+        <v>14.93</v>
       </c>
       <c r="M8" t="n">
-        <v>13.52</v>
+        <v>15.59</v>
       </c>
       <c r="N8" t="n">
-        <v>53.93</v>
+        <v>54.09</v>
       </c>
       <c r="O8" t="n">
-        <v>54.43</v>
+        <v>54.96</v>
       </c>
       <c r="P8" t="n">
-        <v>52.37</v>
+        <v>53.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>52.5</v>
+        <v>54.05</v>
       </c>
       <c r="R8" t="n">
-        <v>13.7891</v>
+        <v>-11.2084</v>
       </c>
       <c r="S8" t="n">
-        <v>30.8186</v>
+        <v>-2.8465</v>
       </c>
       <c r="T8" t="n">
-        <v>35.5302</v>
+        <v>11.6933</v>
       </c>
       <c r="U8" t="n">
-        <v>5.64</v>
+        <v>-3.0332</v>
       </c>
       <c r="V8" t="n">
-        <v>8.9895</v>
+        <v>2.5667</v>
       </c>
       <c r="W8" t="n">
-        <v>6.7759</v>
+        <v>5.8188</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.8854</v>
+        <v>11.119</v>
       </c>
       <c r="Y8" t="n">
-        <v>-25.7143</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z8" t="n">
-        <v>-28.3519</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA8" t="n">
-        <v>-5.6773</v>
+        <v>3.0505</v>
       </c>
       <c r="AB8" t="n">
-        <v>-8.8383</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.8984</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128.33</v>
+        <v>114.76</v>
       </c>
       <c r="C9" t="n">
-        <v>129.59</v>
+        <v>118.32</v>
       </c>
       <c r="D9" t="n">
-        <v>117.79</v>
+        <v>112.3</v>
       </c>
       <c r="E9" t="n">
-        <v>123.39</v>
+        <v>117.97</v>
       </c>
       <c r="F9" t="n">
-        <v>62.41</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>62.7</v>
+        <v>61.87</v>
       </c>
       <c r="H9" t="n">
-        <v>61.64</v>
+        <v>60.45</v>
       </c>
       <c r="I9" t="n">
-        <v>62.64</v>
+        <v>61.86</v>
       </c>
       <c r="J9" t="n">
-        <v>13.51</v>
+        <v>14.91</v>
       </c>
       <c r="K9" t="n">
-        <v>14.63</v>
+        <v>15.24</v>
       </c>
       <c r="L9" t="n">
-        <v>13.41</v>
+        <v>14.38</v>
       </c>
       <c r="M9" t="n">
-        <v>14.03</v>
+        <v>14.4</v>
       </c>
       <c r="N9" t="n">
-        <v>52.67</v>
+        <v>53.84</v>
       </c>
       <c r="O9" t="n">
-        <v>53.31</v>
+        <v>54.33</v>
       </c>
       <c r="P9" t="n">
-        <v>52.42</v>
+        <v>53.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>52.45</v>
+        <v>53.08</v>
       </c>
       <c r="R9" t="n">
-        <v>-3.842</v>
+        <v>7.6762</v>
       </c>
       <c r="S9" t="n">
-        <v>16.8023</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>28.6116</v>
+        <v>11.6717</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1279</v>
+        <v>1.8439</v>
       </c>
       <c r="V9" t="n">
-        <v>4.0359</v>
+        <v>-1.1189</v>
       </c>
       <c r="W9" t="n">
-        <v>7.8512</v>
+        <v>2.7404</v>
       </c>
       <c r="X9" t="n">
-        <v>3.7722</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y9" t="n">
-        <v>-16.4881</v>
+        <v>6.5089</v>
       </c>
       <c r="Z9" t="n">
-        <v>-24.6914</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4.1659</v>
+        <v>1.1048</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.8369</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108.75</v>
+        <v>122.81</v>
       </c>
       <c r="C10" t="n">
-        <v>115.62</v>
+        <v>127.45</v>
       </c>
       <c r="D10" t="n">
-        <v>103.99</v>
+        <v>117.5</v>
       </c>
       <c r="E10" t="n">
-        <v>109.56</v>
+        <v>126.98</v>
       </c>
       <c r="F10" t="n">
-        <v>60.72</v>
+        <v>62.89</v>
       </c>
       <c r="G10" t="n">
-        <v>61.33</v>
+        <v>63.8</v>
       </c>
       <c r="H10" t="n">
-        <v>59.68</v>
+        <v>60.7</v>
       </c>
       <c r="I10" t="n">
-        <v>60.74</v>
+        <v>63.54</v>
       </c>
       <c r="J10" t="n">
-        <v>15.71</v>
+        <v>13.84</v>
       </c>
       <c r="K10" t="n">
-        <v>16.27</v>
+        <v>14.49</v>
       </c>
       <c r="L10" t="n">
-        <v>14.93</v>
+        <v>13.25</v>
       </c>
       <c r="M10" t="n">
-        <v>15.59</v>
+        <v>13.3</v>
       </c>
       <c r="N10" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="O10" t="n">
         <v>54.09</v>
       </c>
-      <c r="O10" t="n">
-        <v>54.96</v>
-      </c>
       <c r="P10" t="n">
-        <v>53.58</v>
+        <v>51.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>54.05</v>
+        <v>51.65</v>
       </c>
       <c r="R10" t="n">
-        <v>-11.2084</v>
+        <v>7.6375</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.8465</v>
+        <v>2.9095</v>
       </c>
       <c r="T10" t="n">
-        <v>11.6933</v>
+        <v>12.6009</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.0332</v>
+        <v>2.7158</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5667</v>
+        <v>1.4368</v>
       </c>
       <c r="W10" t="n">
-        <v>5.8188</v>
+        <v>7.2948</v>
       </c>
       <c r="X10" t="n">
-        <v>11.119</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.7006</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z10" t="n">
-        <v>-14.3407</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.0505</v>
+        <v>-2.694</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.8926</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC10" t="n">
-        <v>-6.1469</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>114.76</v>
+        <v>124.39</v>
       </c>
       <c r="C11" t="n">
-        <v>118.32</v>
+        <v>131.38</v>
       </c>
       <c r="D11" t="n">
-        <v>112.3</v>
+        <v>121.66</v>
       </c>
       <c r="E11" t="n">
-        <v>117.97</v>
+        <v>130.4</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>63.89</v>
       </c>
       <c r="G11" t="n">
-        <v>61.87</v>
+        <v>65.84</v>
       </c>
       <c r="H11" t="n">
-        <v>60.45</v>
+        <v>63.81</v>
       </c>
       <c r="I11" t="n">
-        <v>61.86</v>
+        <v>65.3</v>
       </c>
       <c r="J11" t="n">
-        <v>14.91</v>
+        <v>13.61</v>
       </c>
       <c r="K11" t="n">
-        <v>15.24</v>
+        <v>13.89</v>
       </c>
       <c r="L11" t="n">
-        <v>14.38</v>
+        <v>12.87</v>
       </c>
       <c r="M11" t="n">
-        <v>14.4</v>
+        <v>12.98</v>
       </c>
       <c r="N11" t="n">
-        <v>53.84</v>
+        <v>51.36</v>
       </c>
       <c r="O11" t="n">
-        <v>54.33</v>
+        <v>51.45</v>
       </c>
       <c r="P11" t="n">
-        <v>53.06</v>
+        <v>49.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>53.08</v>
+        <v>50.22</v>
       </c>
       <c r="R11" t="n">
-        <v>7.6762</v>
+        <v>2.6933</v>
       </c>
       <c r="S11" t="n">
-        <v>-8.065799999999999</v>
+        <v>19.0215</v>
       </c>
       <c r="T11" t="n">
-        <v>11.6717</v>
+        <v>1.6209</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8439</v>
+        <v>2.7699</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1189</v>
+        <v>7.5074</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7404</v>
+        <v>4.3798</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.6331</v>
+        <v>-2.406</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.5089</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z11" t="n">
-        <v>-14.2857</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.7946</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1048</v>
+        <v>-7.086</v>
       </c>
       <c r="AC11" t="n">
-        <v>-3.0148</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122.81</v>
+        <v>132.2</v>
       </c>
       <c r="C12" t="n">
-        <v>127.45</v>
+        <v>133.67</v>
       </c>
       <c r="D12" t="n">
-        <v>117.5</v>
+        <v>123.8</v>
       </c>
       <c r="E12" t="n">
-        <v>126.98</v>
+        <v>127.55</v>
       </c>
       <c r="F12" t="n">
-        <v>62.89</v>
+        <v>65.44</v>
       </c>
       <c r="G12" t="n">
-        <v>63.8</v>
+        <v>66.05</v>
       </c>
       <c r="H12" t="n">
-        <v>60.7</v>
+        <v>63.78</v>
       </c>
       <c r="I12" t="n">
-        <v>63.54</v>
+        <v>64.91</v>
       </c>
       <c r="J12" t="n">
-        <v>13.84</v>
+        <v>12.8</v>
       </c>
       <c r="K12" t="n">
-        <v>14.49</v>
+        <v>13.64</v>
       </c>
       <c r="L12" t="n">
-        <v>13.25</v>
+        <v>12.65</v>
       </c>
       <c r="M12" t="n">
-        <v>13.3</v>
+        <v>13.26</v>
       </c>
       <c r="N12" t="n">
-        <v>52.21</v>
+        <v>50.12</v>
       </c>
       <c r="O12" t="n">
-        <v>54.09</v>
+        <v>51.43</v>
       </c>
       <c r="P12" t="n">
-        <v>51.4</v>
+        <v>49.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>51.65</v>
+        <v>50.51</v>
       </c>
       <c r="R12" t="n">
-        <v>7.6375</v>
+        <v>-2.1856</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9095</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>12.6009</v>
+        <v>3.3714</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7158</v>
+        <v>-0.5972</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4368</v>
+        <v>4.9305</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2948</v>
+        <v>3.6239</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.6389</v>
+        <v>2.1572</v>
       </c>
       <c r="Y12" t="n">
-        <v>-5.2031</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z12" t="n">
-        <v>-15.2866</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA12" t="n">
-        <v>-2.694</v>
+        <v>0.5775</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.5253</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC12" t="n">
-        <v>-7.2045</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>124.39</v>
+        <v>135</v>
       </c>
       <c r="C13" t="n">
-        <v>131.38</v>
+        <v>147.26</v>
       </c>
       <c r="D13" t="n">
-        <v>121.66</v>
+        <v>134.02</v>
       </c>
       <c r="E13" t="n">
-        <v>130.4</v>
+        <v>144.16</v>
       </c>
       <c r="F13" t="n">
-        <v>63.89</v>
+        <v>66.37</v>
       </c>
       <c r="G13" t="n">
-        <v>65.84</v>
+        <v>67.77</v>
       </c>
       <c r="H13" t="n">
-        <v>63.81</v>
+        <v>66.25</v>
       </c>
       <c r="I13" t="n">
-        <v>65.3</v>
+        <v>67.39</v>
       </c>
       <c r="J13" t="n">
-        <v>13.61</v>
+        <v>12.5</v>
       </c>
       <c r="K13" t="n">
-        <v>13.89</v>
+        <v>12.59</v>
       </c>
       <c r="L13" t="n">
-        <v>12.87</v>
+        <v>11.21</v>
       </c>
       <c r="M13" t="n">
-        <v>12.98</v>
+        <v>11.51</v>
       </c>
       <c r="N13" t="n">
-        <v>51.36</v>
+        <v>49.4</v>
       </c>
       <c r="O13" t="n">
-        <v>51.45</v>
+        <v>49.49</v>
       </c>
       <c r="P13" t="n">
-        <v>49.79</v>
+        <v>48.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>50.22</v>
+        <v>48.59</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6933</v>
+        <v>13.0223</v>
       </c>
       <c r="S13" t="n">
-        <v>19.0215</v>
+        <v>13.5297</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6209</v>
+        <v>31.5809</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7699</v>
+        <v>3.8207</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5074</v>
+        <v>6.0592</v>
       </c>
       <c r="W13" t="n">
-        <v>4.3798</v>
+        <v>10.9483</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.406</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y13" t="n">
-        <v>-16.7415</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z13" t="n">
-        <v>-3.9941</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA13" t="n">
-        <v>-2.7686</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB13" t="n">
-        <v>-7.086</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.3429</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>132.2</v>
+        <v>157.84</v>
       </c>
       <c r="C14" t="n">
-        <v>133.67</v>
+        <v>166</v>
       </c>
       <c r="D14" t="n">
-        <v>123.8</v>
+        <v>149.06</v>
       </c>
       <c r="E14" t="n">
-        <v>127.55</v>
+        <v>165.85</v>
       </c>
       <c r="F14" t="n">
-        <v>65.44</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>66.05</v>
+        <v>71.66</v>
       </c>
       <c r="H14" t="n">
-        <v>63.78</v>
+        <v>68.88</v>
       </c>
       <c r="I14" t="n">
-        <v>64.91</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>12.8</v>
+        <v>10.43</v>
       </c>
       <c r="K14" t="n">
-        <v>13.64</v>
+        <v>11.14</v>
       </c>
       <c r="L14" t="n">
-        <v>12.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>13.26</v>
+        <v>9.81</v>
       </c>
       <c r="N14" t="n">
-        <v>50.12</v>
+        <v>47.26</v>
       </c>
       <c r="O14" t="n">
-        <v>51.43</v>
+        <v>47.54</v>
       </c>
       <c r="P14" t="n">
-        <v>49.65</v>
+        <v>45.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>50.51</v>
+        <v>45.59</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.1856</v>
+        <v>15.0458</v>
       </c>
       <c r="S14" t="n">
-        <v>8.120699999999999</v>
+        <v>27.1856</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3714</v>
+        <v>40.5866</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5972</v>
+        <v>6.2027</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9305</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6239</v>
+        <v>15.6967</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1572</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y14" t="n">
-        <v>-7.9167</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z14" t="n">
-        <v>-5.4882</v>
+        <v>-31.875</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5775</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB14" t="n">
-        <v>-4.8417</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC14" t="n">
-        <v>-3.6988</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>135</v>
+        <v>162.12</v>
       </c>
       <c r="C15" t="n">
-        <v>147.26</v>
+        <v>162.9</v>
       </c>
       <c r="D15" t="n">
-        <v>134.02</v>
+        <v>147.61</v>
       </c>
       <c r="E15" t="n">
-        <v>144.16</v>
+        <v>152.1</v>
       </c>
       <c r="F15" t="n">
-        <v>66.37</v>
+        <v>71.87</v>
       </c>
       <c r="G15" t="n">
-        <v>67.77</v>
+        <v>73.3</v>
       </c>
       <c r="H15" t="n">
-        <v>66.25</v>
+        <v>70.38</v>
       </c>
       <c r="I15" t="n">
-        <v>67.39</v>
+        <v>71.34</v>
       </c>
       <c r="J15" t="n">
-        <v>12.5</v>
+        <v>10.02</v>
       </c>
       <c r="K15" t="n">
-        <v>12.59</v>
+        <v>10.88</v>
       </c>
       <c r="L15" t="n">
-        <v>11.21</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>11.51</v>
+        <v>10.6</v>
       </c>
       <c r="N15" t="n">
-        <v>49.4</v>
+        <v>45.41</v>
       </c>
       <c r="O15" t="n">
-        <v>49.49</v>
+        <v>46.36</v>
       </c>
       <c r="P15" t="n">
-        <v>48.3</v>
+        <v>44.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>48.59</v>
+        <v>45.73</v>
       </c>
       <c r="R15" t="n">
-        <v>13.0223</v>
+        <v>-8.2906</v>
       </c>
       <c r="S15" t="n">
-        <v>13.5297</v>
+        <v>19.2474</v>
       </c>
       <c r="T15" t="n">
-        <v>31.5809</v>
+        <v>19.7826</v>
       </c>
       <c r="U15" t="n">
-        <v>3.8207</v>
+        <v>-0.3214</v>
       </c>
       <c r="V15" t="n">
-        <v>6.0592</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>10.9483</v>
+        <v>12.2757</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.1976</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>-13.4586</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z15" t="n">
-        <v>-26.1706</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA15" t="n">
-        <v>-3.8012</v>
+        <v>0.3071</v>
       </c>
       <c r="AB15" t="n">
-        <v>-5.9245</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC15" t="n">
-        <v>-10.1018</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>157.84</v>
+        <v>163</v>
       </c>
       <c r="C16" t="n">
-        <v>166</v>
+        <v>177.5</v>
       </c>
       <c r="D16" t="n">
-        <v>149.06</v>
+        <v>161.51</v>
       </c>
       <c r="E16" t="n">
-        <v>165.85</v>
+        <v>176.94</v>
       </c>
       <c r="F16" t="n">
-        <v>69.26000000000001</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>71.66</v>
+        <v>76.31</v>
       </c>
       <c r="H16" t="n">
-        <v>68.88</v>
+        <v>72.7</v>
       </c>
       <c r="I16" t="n">
-        <v>71.56999999999999</v>
+        <v>76.28</v>
       </c>
       <c r="J16" t="n">
-        <v>10.43</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>11.14</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>9.800000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M16" t="n">
-        <v>9.81</v>
+        <v>8.85</v>
       </c>
       <c r="N16" t="n">
-        <v>47.26</v>
+        <v>44.82</v>
       </c>
       <c r="O16" t="n">
-        <v>47.54</v>
+        <v>44.89</v>
       </c>
       <c r="P16" t="n">
-        <v>45.52</v>
+        <v>42.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>45.59</v>
+        <v>42.57</v>
       </c>
       <c r="R16" t="n">
-        <v>15.0458</v>
+        <v>16.3314</v>
       </c>
       <c r="S16" t="n">
-        <v>27.1856</v>
+        <v>22.7386</v>
       </c>
       <c r="T16" t="n">
-        <v>40.5866</v>
+        <v>35.6902</v>
       </c>
       <c r="U16" t="n">
-        <v>6.2027</v>
+        <v>6.9246</v>
       </c>
       <c r="V16" t="n">
-        <v>9.601800000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W16" t="n">
-        <v>15.6967</v>
+        <v>16.8147</v>
       </c>
       <c r="X16" t="n">
-        <v>-14.7698</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y16" t="n">
-        <v>-24.4222</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z16" t="n">
-        <v>-31.875</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA16" t="n">
-        <v>-6.1741</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB16" t="n">
-        <v>-9.2194</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC16" t="n">
-        <v>-14.1108</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>162.12</v>
+        <v>181</v>
       </c>
       <c r="C17" t="n">
-        <v>162.9</v>
+        <v>191.29</v>
       </c>
       <c r="D17" t="n">
-        <v>147.61</v>
+        <v>178.94</v>
       </c>
       <c r="E17" t="n">
-        <v>152.1</v>
+        <v>190.42</v>
       </c>
       <c r="F17" t="n">
-        <v>71.87</v>
+        <v>76</v>
       </c>
       <c r="G17" t="n">
-        <v>73.3</v>
+        <v>77.36</v>
       </c>
       <c r="H17" t="n">
-        <v>70.38</v>
+        <v>75.55</v>
       </c>
       <c r="I17" t="n">
-        <v>71.34</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>10.02</v>
+        <v>8.65</v>
       </c>
       <c r="K17" t="n">
-        <v>10.88</v>
+        <v>8.77</v>
       </c>
       <c r="L17" t="n">
-        <v>9.970000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="M17" t="n">
-        <v>10.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>45.41</v>
+        <v>42.74</v>
       </c>
       <c r="O17" t="n">
-        <v>46.36</v>
+        <v>43</v>
       </c>
       <c r="P17" t="n">
-        <v>44.5</v>
+        <v>41.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>45.73</v>
+        <v>42.22</v>
       </c>
       <c r="R17" t="n">
-        <v>-8.2906</v>
+        <v>7.6184</v>
       </c>
       <c r="S17" t="n">
-        <v>19.2474</v>
+        <v>14.8146</v>
       </c>
       <c r="T17" t="n">
-        <v>19.7826</v>
+        <v>49.2905</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3214</v>
+        <v>0.8915</v>
       </c>
       <c r="V17" t="n">
-        <v>9.906000000000001</v>
+        <v>7.5311</v>
       </c>
       <c r="W17" t="n">
-        <v>12.2757</v>
+        <v>18.5642</v>
       </c>
       <c r="X17" t="n">
-        <v>8.053000000000001</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y17" t="n">
-        <v>-20.0603</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z17" t="n">
-        <v>-20.3008</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.3071</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB17" t="n">
-        <v>-9.4635</v>
+        <v>-7.392</v>
       </c>
       <c r="AC17" t="n">
-        <v>-11.4618</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>163</v>
+        <v>177.62</v>
       </c>
       <c r="C18" t="n">
-        <v>177.5</v>
+        <v>182.24</v>
       </c>
       <c r="D18" t="n">
-        <v>161.51</v>
+        <v>150.58</v>
       </c>
       <c r="E18" t="n">
-        <v>176.94</v>
+        <v>172.52</v>
       </c>
       <c r="F18" t="n">
-        <v>72.81999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="G18" t="n">
-        <v>76.31</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>72.7</v>
+        <v>71.55</v>
       </c>
       <c r="I18" t="n">
-        <v>76.28</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>9.859999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="K18" t="n">
-        <v>9.970000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="L18" t="n">
-        <v>8.84</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>8.85</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>44.82</v>
+        <v>43.14</v>
       </c>
       <c r="O18" t="n">
-        <v>44.89</v>
+        <v>45.19</v>
       </c>
       <c r="P18" t="n">
-        <v>42.57</v>
+        <v>42.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>42.57</v>
+        <v>43.31</v>
       </c>
       <c r="R18" t="n">
-        <v>16.3314</v>
+        <v>-9.4003</v>
       </c>
       <c r="S18" t="n">
-        <v>22.7386</v>
+        <v>13.4254</v>
       </c>
       <c r="T18" t="n">
-        <v>35.6902</v>
+        <v>19.6726</v>
       </c>
       <c r="U18" t="n">
-        <v>6.9246</v>
+        <v>-2.5988</v>
       </c>
       <c r="V18" t="n">
-        <v>13.1919</v>
+        <v>5.0743</v>
       </c>
       <c r="W18" t="n">
-        <v>16.8147</v>
+        <v>11.2331</v>
       </c>
       <c r="X18" t="n">
-        <v>-16.5094</v>
+        <v>9.1463</v>
       </c>
       <c r="Y18" t="n">
-        <v>-23.1103</v>
+        <v>-15.566</v>
       </c>
       <c r="Z18" t="n">
-        <v>-31.8182</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA18" t="n">
-        <v>-6.9101</v>
+        <v>2.5817</v>
       </c>
       <c r="AB18" t="n">
-        <v>-12.3894</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC18" t="n">
-        <v>-15.233</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>181</v>
+        <v>183.84</v>
       </c>
       <c r="C19" t="n">
-        <v>191.29</v>
+        <v>188.49</v>
       </c>
       <c r="D19" t="n">
-        <v>178.94</v>
+        <v>172.26</v>
       </c>
       <c r="E19" t="n">
-        <v>190.42</v>
+        <v>184.24</v>
       </c>
       <c r="F19" t="n">
-        <v>76</v>
+        <v>75.81</v>
       </c>
       <c r="G19" t="n">
-        <v>77.36</v>
+        <v>77.94</v>
       </c>
       <c r="H19" t="n">
-        <v>75.55</v>
+        <v>74.19</v>
       </c>
       <c r="I19" t="n">
-        <v>76.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>8.65</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>8.77</v>
+        <v>8.98</v>
       </c>
       <c r="L19" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N19" t="n">
-        <v>42.74</v>
+        <v>42.83</v>
       </c>
       <c r="O19" t="n">
-        <v>43</v>
+        <v>43.77</v>
       </c>
       <c r="P19" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="Q19" t="n">
         <v>41.99</v>
       </c>
-      <c r="Q19" t="n">
-        <v>42.22</v>
-      </c>
       <c r="R19" t="n">
-        <v>7.6184</v>
+        <v>6.7934</v>
       </c>
       <c r="S19" t="n">
-        <v>14.8146</v>
+        <v>4.1257</v>
       </c>
       <c r="T19" t="n">
-        <v>49.2905</v>
+        <v>11.0883</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8915</v>
+        <v>3.0416</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5311</v>
+        <v>1.2585</v>
       </c>
       <c r="W19" t="n">
-        <v>18.5642</v>
+        <v>7.9223</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.3446</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y19" t="n">
-        <v>-16.4118</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z19" t="n">
-        <v>-38.1599</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.8222</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB19" t="n">
-        <v>-7.392</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC19" t="n">
-        <v>-16.4126</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>177.62</v>
+        <v>182.67</v>
       </c>
       <c r="C20" t="n">
-        <v>182.24</v>
+        <v>189.56</v>
       </c>
       <c r="D20" t="n">
-        <v>150.58</v>
+        <v>178.28</v>
       </c>
       <c r="E20" t="n">
-        <v>172.52</v>
+        <v>186.19</v>
       </c>
       <c r="F20" t="n">
-        <v>75.3</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>75.93000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>71.55</v>
+        <v>77.16</v>
       </c>
       <c r="I20" t="n">
-        <v>74.95999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J20" t="n">
-        <v>8.75</v>
+        <v>8.43</v>
       </c>
       <c r="K20" t="n">
-        <v>9.91</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>8.550000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>8.949999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="N20" t="n">
-        <v>43.14</v>
+        <v>41.98</v>
       </c>
       <c r="O20" t="n">
-        <v>45.19</v>
+        <v>42.06</v>
       </c>
       <c r="P20" t="n">
-        <v>42.79</v>
+        <v>40.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>43.31</v>
+        <v>41.07</v>
       </c>
       <c r="R20" t="n">
-        <v>-9.4003</v>
+        <v>1.0584</v>
       </c>
       <c r="S20" t="n">
-        <v>13.4254</v>
+        <v>-2.2214</v>
       </c>
       <c r="T20" t="n">
-        <v>19.6726</v>
+        <v>22.4129</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.5988</v>
+        <v>2.2139</v>
       </c>
       <c r="V20" t="n">
-        <v>5.0743</v>
+        <v>2.5858</v>
       </c>
       <c r="W20" t="n">
-        <v>11.2331</v>
+        <v>10.6672</v>
       </c>
       <c r="X20" t="n">
-        <v>9.1463</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y20" t="n">
-        <v>-15.566</v>
+        <v>0.8537</v>
       </c>
       <c r="Z20" t="n">
-        <v>-22.2415</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.5817</v>
+        <v>-2.191</v>
       </c>
       <c r="AB20" t="n">
-        <v>-5.2919</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC20" t="n">
-        <v>-10.8664</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>183.84</v>
+        <v>167</v>
       </c>
       <c r="C21" t="n">
-        <v>188.49</v>
+        <v>174.4</v>
       </c>
       <c r="D21" t="n">
-        <v>172.26</v>
+        <v>161.14</v>
       </c>
       <c r="E21" t="n">
-        <v>184.24</v>
+        <v>164.18</v>
       </c>
       <c r="F21" t="n">
-        <v>75.81</v>
+        <v>75.73</v>
       </c>
       <c r="G21" t="n">
-        <v>77.94</v>
+        <v>77.37</v>
       </c>
       <c r="H21" t="n">
-        <v>74.19</v>
+        <v>74.23</v>
       </c>
       <c r="I21" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="J21" t="n">
-        <v>8.380000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>8.98</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>8.140000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>8.35</v>
+        <v>9.23</v>
       </c>
       <c r="N21" t="n">
-        <v>42.83</v>
+        <v>42.77</v>
       </c>
       <c r="O21" t="n">
-        <v>43.77</v>
+        <v>43.57</v>
       </c>
       <c r="P21" t="n">
-        <v>41.6</v>
+        <v>41.93</v>
       </c>
       <c r="Q21" t="n">
-        <v>41.99</v>
+        <v>42.98</v>
       </c>
       <c r="R21" t="n">
-        <v>6.7934</v>
+        <v>-11.8213</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1257</v>
+        <v>-4.8342</v>
       </c>
       <c r="T21" t="n">
-        <v>11.0883</v>
+        <v>-7.2115</v>
       </c>
       <c r="U21" t="n">
-        <v>3.0416</v>
+        <v>-4.5725</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2585</v>
+        <v>0.5069</v>
       </c>
       <c r="W21" t="n">
-        <v>7.9223</v>
+        <v>-1.2323</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.7039</v>
+        <v>11.6082</v>
       </c>
       <c r="Y21" t="n">
-        <v>-5.6497</v>
+        <v>3.1285</v>
       </c>
       <c r="Z21" t="n">
-        <v>-14.8828</v>
+        <v>4.2938</v>
       </c>
       <c r="AA21" t="n">
-        <v>-3.0478</v>
+        <v>4.6506</v>
       </c>
       <c r="AB21" t="n">
-        <v>-1.3625</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.8965</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>182.67</v>
+        <v>172.95</v>
       </c>
       <c r="C22" t="n">
-        <v>189.56</v>
+        <v>174.61</v>
       </c>
       <c r="D22" t="n">
-        <v>178.28</v>
+        <v>142.69</v>
       </c>
       <c r="E22" t="n">
-        <v>186.19</v>
+        <v>151.75</v>
       </c>
       <c r="F22" t="n">
-        <v>77.29000000000001</v>
+        <v>76.13500000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>79.68000000000001</v>
+        <v>76.2713</v>
       </c>
       <c r="H22" t="n">
-        <v>77.16</v>
+        <v>72.101</v>
       </c>
       <c r="I22" t="n">
-        <v>78.95</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>8.43</v>
+        <v>8.77</v>
       </c>
       <c r="K22" t="n">
-        <v>8.630000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L22" t="n">
-        <v>8.119999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="M22" t="n">
-        <v>8.27</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>41.98</v>
+        <v>42.515</v>
       </c>
       <c r="O22" t="n">
-        <v>42.06</v>
+        <v>44.8201</v>
       </c>
       <c r="P22" t="n">
-        <v>40.68</v>
+        <v>42.44</v>
       </c>
       <c r="Q22" t="n">
-        <v>41.07</v>
+        <v>43.54</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0584</v>
+        <v>-7.571</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2214</v>
+        <v>-17.6346</v>
       </c>
       <c r="T22" t="n">
-        <v>22.4129</v>
+        <v>-20.3077</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2139</v>
+        <v>-1.3539</v>
       </c>
       <c r="V22" t="n">
-        <v>2.5858</v>
+        <v>-3.7804</v>
       </c>
       <c r="W22" t="n">
-        <v>10.6672</v>
+        <v>-3.4304</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9581</v>
+        <v>7.8007</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.8537</v>
+        <v>19.1617</v>
       </c>
       <c r="Z22" t="n">
-        <v>-21.9811</v>
+        <v>21.3415</v>
       </c>
       <c r="AA22" t="n">
-        <v>-2.191</v>
+        <v>1.3029</v>
       </c>
       <c r="AB22" t="n">
-        <v>-2.7238</v>
+        <v>3.6914</v>
       </c>
       <c r="AC22" t="n">
-        <v>-10.1902</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>167</v>
-      </c>
-      <c r="C23" t="n">
-        <v>174.4</v>
-      </c>
-      <c r="D23" t="n">
-        <v>161.1402</v>
-      </c>
-      <c r="E23" t="n">
-        <v>164.18</v>
-      </c>
-      <c r="F23" t="n">
-        <v>75.70999999999999</v>
-      </c>
-      <c r="G23" t="n">
-        <v>77.36499999999999</v>
-      </c>
-      <c r="H23" t="n">
-        <v>74.22799999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>75.34</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="K23" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="L23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M23" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="N23" t="n">
-        <v>42.77</v>
-      </c>
-      <c r="O23" t="n">
-        <v>43.565</v>
-      </c>
-      <c r="P23" t="n">
-        <v>41.93</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>42.98</v>
-      </c>
-      <c r="R23" t="n">
-        <v>-11.8213</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-4.8342</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-7.2115</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-4.5725</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.5069</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-1.2323</v>
-      </c>
-      <c r="X23" t="n">
-        <v>11.6082</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>3.1285</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.2938</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.6506</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-0.7619</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.9631</v>
+        <v>3.1265</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26487,13 +26487,13 @@
         <v>151.75</v>
       </c>
       <c r="F22" t="n">
-        <v>76.13500000000001</v>
+        <v>76.13</v>
       </c>
       <c r="G22" t="n">
-        <v>76.2713</v>
+        <v>76.27</v>
       </c>
       <c r="H22" t="n">
-        <v>72.101</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>74.31999999999999</v>
@@ -26511,10 +26511,10 @@
         <v>9.949999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>42.515</v>
+        <v>42.51</v>
       </c>
       <c r="O22" t="n">
-        <v>44.8201</v>
+        <v>44.82</v>
       </c>
       <c r="P22" t="n">
         <v>42.44</v>
@@ -26557,6 +26557,97 @@
       </c>
       <c r="AC22" t="n">
         <v>3.1265</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>141.24</v>
+      </c>
+      <c r="C23" t="n">
+        <v>160.58</v>
+      </c>
+      <c r="D23" t="n">
+        <v>135.02</v>
+      </c>
+      <c r="E23" t="n">
+        <v>151.89</v>
+      </c>
+      <c r="F23" t="n">
+        <v>72.41</v>
+      </c>
+      <c r="G23" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>70.9616</v>
+      </c>
+      <c r="I23" t="n">
+        <v>72.93000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10.6403</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="N23" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="O23" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="P23" t="n">
+        <v>43.455</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.09229999999999999</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-18.422</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-11.958</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-1.8703</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-7.6251</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-2.7081</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.201</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20.0726</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>10.9497</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.9063</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>8.0351</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.4475</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95.97</v>
+        <v>97.97</v>
       </c>
       <c r="C2" t="n">
-        <v>96.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D2" t="n">
-        <v>92.03</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>95.94</v>
+        <v>98.09</v>
       </c>
       <c r="F2" t="n">
-        <v>58.4</v>
+        <v>58.48</v>
       </c>
       <c r="G2" t="n">
-        <v>58.58</v>
+        <v>58.97</v>
       </c>
       <c r="H2" t="n">
-        <v>56.91</v>
+        <v>56.82</v>
       </c>
       <c r="I2" t="n">
-        <v>58.08</v>
+        <v>57.4</v>
       </c>
       <c r="J2" t="n">
-        <v>18.64</v>
+        <v>18.25</v>
       </c>
       <c r="K2" t="n">
-        <v>19.41</v>
+        <v>18.76</v>
       </c>
       <c r="L2" t="n">
-        <v>18.44</v>
+        <v>17.85</v>
       </c>
       <c r="M2" t="n">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="N2" t="n">
-        <v>56.59</v>
+        <v>56.52</v>
       </c>
       <c r="O2" t="n">
-        <v>58.04</v>
+        <v>58.15</v>
       </c>
       <c r="P2" t="n">
-        <v>56.41</v>
+        <v>56.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>56.91</v>
+        <v>57.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C3" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D3" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F3" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G3" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H3" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I3" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J3" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K3" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L3" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M3" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N3" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O3" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P3" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
       <c r="R3" t="n">
-        <v>2.241</v>
+        <v>7.697</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1708</v>
+        <v>4.8955</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3081</v>
+        <v>-7.6923</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1949</v>
+        <v>-4.9661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C4" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D4" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E4" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F4" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G4" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H4" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I4" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J4" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K4" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L4" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M4" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N4" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O4" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P4" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R4" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="U4" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C5" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D5" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E5" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F5" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G5" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H5" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I5" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J5" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K5" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L5" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N5" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O5" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P5" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R5" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="S5" t="n">
-        <v>17.5422</v>
+        <v>30.8186</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.9628</v>
+        <v>8.9895</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="Y5" t="n">
-        <v>-15.7273</v>
+        <v>-25.7143</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.1965</v>
+        <v>-8.8383</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C6" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D6" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E6" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F6" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G6" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H6" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I6" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J6" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K6" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L6" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M6" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N6" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O6" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P6" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R6" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="U6" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y6" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C7" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D7" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E7" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F7" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G7" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H7" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I7" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J7" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K7" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L7" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M7" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N7" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O7" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P7" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R7" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S7" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="T7" t="n">
-        <v>28.6116</v>
+        <v>11.6933</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V7" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="W7" t="n">
-        <v>7.8512</v>
+        <v>5.8188</v>
       </c>
       <c r="X7" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y7" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="Z7" t="n">
-        <v>-24.6914</v>
+        <v>-14.3407</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB7" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
       <c r="AC7" t="n">
-        <v>-7.8369</v>
+        <v>-6.1469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C8" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D8" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E8" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F8" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H8" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I8" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J8" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K8" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L8" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M8" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N8" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O8" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P8" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R8" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W8" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X8" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z8" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C9" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D9" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E9" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G9" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H9" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I9" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J9" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K9" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L9" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N9" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O9" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P9" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R9" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S9" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T9" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W9" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z9" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C10" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D10" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E10" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F10" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G10" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H10" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I10" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J10" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K10" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L10" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M10" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N10" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O10" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P10" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q10" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R10" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T10" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W10" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y10" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z10" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC10" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C11" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D11" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E11" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F11" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G11" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H11" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I11" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J11" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K11" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L11" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M11" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N11" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O11" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P11" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S11" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U11" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W11" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y11" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z11" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB11" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC11" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C12" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D12" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E12" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F12" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G12" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H12" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I12" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J12" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K12" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L12" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M12" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N12" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O12" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P12" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S12" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W12" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X12" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y12" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z12" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB12" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC12" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C13" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D13" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E13" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F13" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H13" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I13" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K13" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L13" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N13" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O13" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P13" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R13" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S13" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T13" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U13" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V13" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y13" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z13" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB13" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC13" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C14" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D14" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E14" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F14" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G14" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H14" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I14" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J14" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K14" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N14" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O14" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P14" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R14" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S14" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T14" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U14" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V14" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z14" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA14" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB14" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC14" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C15" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D15" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E15" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F15" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H15" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I15" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J15" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M15" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N15" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O15" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P15" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R15" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S15" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="T15" t="n">
-        <v>19.7826</v>
+        <v>35.6902</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V15" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W15" t="n">
-        <v>12.2757</v>
+        <v>16.8147</v>
       </c>
       <c r="X15" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y15" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z15" t="n">
-        <v>-20.3008</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB15" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC15" t="n">
-        <v>-11.4618</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C16" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D16" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E16" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F16" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G16" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H16" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I16" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K16" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L16" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M16" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O16" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P16" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R16" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S16" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="T16" t="n">
-        <v>35.6902</v>
+        <v>49.2905</v>
       </c>
       <c r="U16" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V16" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="W16" t="n">
-        <v>16.8147</v>
+        <v>18.5642</v>
       </c>
       <c r="X16" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y16" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z16" t="n">
-        <v>-31.8182</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA16" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB16" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
       <c r="AC16" t="n">
-        <v>-15.233</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C17" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D17" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E17" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F17" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G17" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I17" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K17" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L17" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O17" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P17" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R17" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S17" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="T17" t="n">
-        <v>49.2905</v>
+        <v>19.6726</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="W17" t="n">
-        <v>18.5642</v>
+        <v>11.2331</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y17" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="Z17" t="n">
-        <v>-38.1599</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB17" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC17" t="n">
-        <v>-16.4126</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C18" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D18" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E18" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F18" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G18" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H18" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I18" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L18" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N18" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O18" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P18" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R18" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S18" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T18" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V18" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W18" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X18" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y18" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z18" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB18" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC18" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>183.84</v>
+        <v>182.67</v>
       </c>
       <c r="C19" t="n">
-        <v>188.49</v>
+        <v>189.56</v>
       </c>
       <c r="D19" t="n">
-        <v>172.26</v>
+        <v>178.28</v>
       </c>
       <c r="E19" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F19" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>74.19</v>
+        <v>77.16</v>
       </c>
       <c r="I19" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J19" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K19" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N19" t="n">
-        <v>42.83</v>
+        <v>41.98</v>
       </c>
       <c r="O19" t="n">
-        <v>43.77</v>
+        <v>42.06</v>
       </c>
       <c r="P19" t="n">
-        <v>41.6</v>
+        <v>40.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R19" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T19" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U19" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W19" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X19" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y19" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z19" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA19" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>182.67</v>
+        <v>167</v>
       </c>
       <c r="C20" t="n">
-        <v>189.56</v>
+        <v>174.4</v>
       </c>
       <c r="D20" t="n">
-        <v>178.28</v>
+        <v>161.14</v>
       </c>
       <c r="E20" t="n">
-        <v>186.19</v>
+        <v>164.18</v>
       </c>
       <c r="F20" t="n">
-        <v>77.29000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G20" t="n">
-        <v>79.68000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="H20" t="n">
-        <v>77.16</v>
+        <v>74.23</v>
       </c>
       <c r="I20" t="n">
-        <v>78.95</v>
+        <v>75.34</v>
       </c>
       <c r="J20" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>8.630000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>8.27</v>
+        <v>9.23</v>
       </c>
       <c r="N20" t="n">
-        <v>41.98</v>
+        <v>42.77</v>
       </c>
       <c r="O20" t="n">
-        <v>42.06</v>
+        <v>43.57</v>
       </c>
       <c r="P20" t="n">
-        <v>40.68</v>
+        <v>41.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>41.07</v>
+        <v>42.98</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0584</v>
+        <v>-11.8213</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2214</v>
+        <v>-4.8342</v>
       </c>
       <c r="T20" t="n">
-        <v>22.4129</v>
+        <v>-7.2115</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2139</v>
+        <v>-4.5725</v>
       </c>
       <c r="V20" t="n">
-        <v>2.5858</v>
+        <v>0.5069</v>
       </c>
       <c r="W20" t="n">
-        <v>10.6672</v>
+        <v>-1.2323</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9581</v>
+        <v>11.6082</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.8537</v>
+        <v>3.1285</v>
       </c>
       <c r="Z20" t="n">
-        <v>-21.9811</v>
+        <v>4.2938</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.191</v>
+        <v>4.6506</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.7238</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC20" t="n">
-        <v>-10.1902</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>167</v>
+        <v>172.95</v>
       </c>
       <c r="C21" t="n">
-        <v>174.4</v>
+        <v>174.61</v>
       </c>
       <c r="D21" t="n">
-        <v>161.14</v>
+        <v>142.69</v>
       </c>
       <c r="E21" t="n">
-        <v>164.18</v>
+        <v>151.75</v>
       </c>
       <c r="F21" t="n">
-        <v>75.73</v>
+        <v>76.13</v>
       </c>
       <c r="G21" t="n">
-        <v>77.37</v>
+        <v>76.27</v>
       </c>
       <c r="H21" t="n">
-        <v>74.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>75.34</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K21" t="n">
-        <v>9.390000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M21" t="n">
-        <v>9.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>42.77</v>
+        <v>42.51</v>
       </c>
       <c r="O21" t="n">
-        <v>43.57</v>
+        <v>44.82</v>
       </c>
       <c r="P21" t="n">
-        <v>41.93</v>
+        <v>42.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.98</v>
+        <v>43.54</v>
       </c>
       <c r="R21" t="n">
-        <v>-11.8213</v>
+        <v>-7.571</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.8342</v>
+        <v>-17.6346</v>
       </c>
       <c r="T21" t="n">
-        <v>-7.2115</v>
+        <v>-20.3077</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.5725</v>
+        <v>-1.3539</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5069</v>
+        <v>-3.7804</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.2323</v>
+        <v>-3.4304</v>
       </c>
       <c r="X21" t="n">
-        <v>11.6082</v>
+        <v>7.8007</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.1285</v>
+        <v>19.1617</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2938</v>
+        <v>21.3415</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.6506</v>
+        <v>1.3029</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.7619</v>
+        <v>3.6914</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.9631</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>172.95</v>
+        <v>141.24</v>
       </c>
       <c r="C22" t="n">
-        <v>174.61</v>
+        <v>160.6</v>
       </c>
       <c r="D22" t="n">
-        <v>142.69</v>
+        <v>135.02</v>
       </c>
       <c r="E22" t="n">
-        <v>151.75</v>
+        <v>151.89</v>
       </c>
       <c r="F22" t="n">
-        <v>76.13</v>
+        <v>72.41</v>
       </c>
       <c r="G22" t="n">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="H22" t="n">
-        <v>72.09999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>74.31999999999999</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>8.77</v>
+        <v>10.64</v>
       </c>
       <c r="K22" t="n">
-        <v>10.47</v>
+        <v>11.07</v>
       </c>
       <c r="L22" t="n">
-        <v>8.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="N22" t="n">
-        <v>42.51</v>
+        <v>44.68</v>
       </c>
       <c r="O22" t="n">
-        <v>44.82</v>
+        <v>45.53</v>
       </c>
       <c r="P22" t="n">
-        <v>42.44</v>
+        <v>43.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>43.54</v>
+        <v>44.37</v>
       </c>
       <c r="R22" t="n">
-        <v>-7.571</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-17.6346</v>
+        <v>-18.422</v>
       </c>
       <c r="T22" t="n">
-        <v>-20.3077</v>
+        <v>-11.958</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3539</v>
+        <v>-1.8703</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.7804</v>
+        <v>-7.6251</v>
       </c>
       <c r="W22" t="n">
-        <v>-3.4304</v>
+        <v>-2.7081</v>
       </c>
       <c r="X22" t="n">
-        <v>7.8007</v>
+        <v>-0.201</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.1617</v>
+        <v>20.0726</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.3415</v>
+        <v>10.9497</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.3029</v>
+        <v>1.9063</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.6914</v>
+        <v>8.0351</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.1265</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141.24</v>
+        <v>161</v>
       </c>
       <c r="C23" t="n">
-        <v>160.58</v>
+        <v>173.69</v>
       </c>
       <c r="D23" t="n">
-        <v>135.02</v>
+        <v>161.04</v>
       </c>
       <c r="E23" t="n">
-        <v>151.89</v>
+        <v>173.2</v>
       </c>
       <c r="F23" t="n">
-        <v>72.41</v>
+        <v>74.084</v>
       </c>
       <c r="G23" t="n">
-        <v>74.5</v>
+        <v>76.53</v>
       </c>
       <c r="H23" t="n">
-        <v>70.9616</v>
+        <v>73.61499999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>72.93000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>10.6403</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>11.07</v>
+        <v>9.35</v>
       </c>
       <c r="L23" t="n">
-        <v>9.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M23" t="n">
-        <v>9.93</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>44.69</v>
+        <v>43.675</v>
       </c>
       <c r="O23" t="n">
-        <v>45.53</v>
+        <v>43.965</v>
       </c>
       <c r="P23" t="n">
-        <v>43.455</v>
+        <v>42.19</v>
       </c>
       <c r="Q23" t="n">
-        <v>44.37</v>
+        <v>42.19</v>
       </c>
       <c r="R23" t="n">
-        <v>0.09229999999999999</v>
+        <v>14.0299</v>
       </c>
       <c r="S23" t="n">
-        <v>-18.422</v>
+        <v>5.494</v>
       </c>
       <c r="T23" t="n">
-        <v>-11.958</v>
+        <v>-5.9922</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8703</v>
+        <v>4.9088</v>
       </c>
       <c r="V23" t="n">
-        <v>-7.6251</v>
+        <v>1.553</v>
       </c>
       <c r="W23" t="n">
-        <v>-2.7081</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.201</v>
+        <v>-13.998</v>
       </c>
       <c r="Y23" t="n">
-        <v>20.0726</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z23" t="n">
-        <v>10.9497</v>
+        <v>2.2754</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9063</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.0351</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.4475</v>
+        <v>0.4763</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>97.97</v>
+        <v>102.94</v>
       </c>
       <c r="C2" t="n">
-        <v>99.95</v>
+        <v>106.09</v>
       </c>
       <c r="D2" t="n">
-        <v>95.31999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>98.09</v>
+        <v>105.64</v>
       </c>
       <c r="F2" t="n">
-        <v>58.48</v>
+        <v>58.93</v>
       </c>
       <c r="G2" t="n">
-        <v>58.97</v>
+        <v>60.3</v>
       </c>
       <c r="H2" t="n">
-        <v>56.82</v>
+        <v>58.49</v>
       </c>
       <c r="I2" t="n">
-        <v>57.4</v>
+        <v>60.21</v>
       </c>
       <c r="J2" t="n">
-        <v>18.25</v>
+        <v>17.37</v>
       </c>
       <c r="K2" t="n">
-        <v>18.76</v>
+        <v>17.95</v>
       </c>
       <c r="L2" t="n">
-        <v>17.85</v>
+        <v>16.72</v>
       </c>
       <c r="M2" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="N2" t="n">
-        <v>56.52</v>
+        <v>56.05</v>
       </c>
       <c r="O2" t="n">
-        <v>58.15</v>
+        <v>56.49</v>
       </c>
       <c r="P2" t="n">
-        <v>56.04</v>
+        <v>54.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>57.59</v>
+        <v>54.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C3" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D3" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E3" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F3" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G3" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H3" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I3" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J3" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K3" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L3" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M3" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N3" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O3" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P3" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
       <c r="R3" t="n">
-        <v>7.697</v>
+        <v>6.7493</v>
       </c>
       <c r="U3" t="n">
-        <v>4.8955</v>
+        <v>-1.6442</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.6923</v>
+        <v>-6.5476</v>
       </c>
       <c r="AA3" t="n">
-        <v>-4.9661</v>
+        <v>1.6993</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C4" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D4" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E4" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F4" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G4" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H4" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I4" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J4" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K4" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L4" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M4" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N4" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O4" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P4" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R4" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C5" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D5" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E5" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F5" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G5" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H5" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I5" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J5" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K5" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L5" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M5" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N5" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O5" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P5" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R5" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="S5" t="n">
-        <v>30.8186</v>
+        <v>16.8023</v>
       </c>
       <c r="U5" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="V5" t="n">
-        <v>8.9895</v>
+        <v>4.0359</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="Y5" t="n">
-        <v>-25.7143</v>
+        <v>-16.4881</v>
       </c>
       <c r="AA5" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>-8.8383</v>
+        <v>-4.1659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C6" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D6" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E6" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F6" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G6" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H6" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I6" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J6" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K6" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L6" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M6" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N6" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O6" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P6" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R6" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S6" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V6" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="X6" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y6" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB6" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C7" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D7" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E7" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F7" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H7" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I7" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J7" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K7" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L7" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M7" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N7" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O7" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P7" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R7" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>11.6933</v>
+        <v>11.6717</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V7" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="W7" t="n">
-        <v>5.8188</v>
+        <v>2.7404</v>
       </c>
       <c r="X7" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="Z7" t="n">
-        <v>-14.3407</v>
+        <v>-14.2857</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
       <c r="AC7" t="n">
-        <v>-6.1469</v>
+        <v>-3.0148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C8" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D8" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E8" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G8" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H8" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I8" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J8" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K8" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L8" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N8" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O8" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P8" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R8" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S8" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T8" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z8" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C9" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D9" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E9" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F9" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G9" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H9" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I9" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J9" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K9" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L9" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M9" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N9" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O9" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P9" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R9" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T9" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y9" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z9" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C10" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D10" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E10" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F10" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G10" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H10" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I10" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J10" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K10" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L10" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M10" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N10" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O10" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P10" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S10" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W10" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y10" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z10" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB10" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C11" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D11" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E11" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F11" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G11" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H11" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I11" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J11" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K11" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L11" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M11" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N11" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O11" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P11" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S11" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X11" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y11" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z11" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC11" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C12" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D12" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E12" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F12" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H12" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I12" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K12" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L12" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N12" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O12" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P12" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R12" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S12" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T12" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U12" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V12" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y12" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z12" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB12" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC12" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C13" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D13" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E13" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F13" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G13" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H13" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I13" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J13" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K13" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N13" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O13" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P13" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R13" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S13" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T13" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U13" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V13" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z13" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA13" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB13" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC13" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C14" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D14" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E14" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F14" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H14" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I14" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J14" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M14" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N14" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O14" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P14" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R14" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S14" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="T14" t="n">
-        <v>19.7826</v>
+        <v>35.6902</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V14" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W14" t="n">
-        <v>12.2757</v>
+        <v>16.8147</v>
       </c>
       <c r="X14" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y14" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z14" t="n">
-        <v>-20.3008</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB14" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC14" t="n">
-        <v>-11.4618</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C15" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D15" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E15" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F15" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H15" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I15" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K15" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L15" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M15" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O15" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P15" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R15" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S15" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="T15" t="n">
-        <v>35.6902</v>
+        <v>49.2905</v>
       </c>
       <c r="U15" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V15" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="W15" t="n">
-        <v>16.8147</v>
+        <v>18.5642</v>
       </c>
       <c r="X15" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y15" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z15" t="n">
-        <v>-31.8182</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA15" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB15" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
       <c r="AC15" t="n">
-        <v>-15.233</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C16" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D16" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E16" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G16" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I16" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K16" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L16" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O16" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P16" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R16" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S16" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="T16" t="n">
-        <v>49.2905</v>
+        <v>19.6726</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="W16" t="n">
-        <v>18.5642</v>
+        <v>11.2331</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y16" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="Z16" t="n">
-        <v>-38.1599</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB16" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC16" t="n">
-        <v>-16.4126</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C17" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D17" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E17" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F17" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G17" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H17" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I17" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L17" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N17" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O17" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P17" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R17" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S17" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T17" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V17" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W17" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X17" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y17" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z17" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB17" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC17" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>183.84</v>
+        <v>182.67</v>
       </c>
       <c r="C18" t="n">
-        <v>188.49</v>
+        <v>189.56</v>
       </c>
       <c r="D18" t="n">
-        <v>172.26</v>
+        <v>178.28</v>
       </c>
       <c r="E18" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F18" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>74.19</v>
+        <v>77.16</v>
       </c>
       <c r="I18" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J18" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K18" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N18" t="n">
-        <v>42.83</v>
+        <v>41.98</v>
       </c>
       <c r="O18" t="n">
-        <v>43.77</v>
+        <v>42.06</v>
       </c>
       <c r="P18" t="n">
-        <v>41.6</v>
+        <v>40.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R18" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T18" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U18" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W18" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X18" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y18" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z18" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA18" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB18" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>182.67</v>
+        <v>167</v>
       </c>
       <c r="C19" t="n">
-        <v>189.56</v>
+        <v>174.4</v>
       </c>
       <c r="D19" t="n">
-        <v>178.28</v>
+        <v>161.14</v>
       </c>
       <c r="E19" t="n">
-        <v>186.19</v>
+        <v>164.18</v>
       </c>
       <c r="F19" t="n">
-        <v>77.29000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G19" t="n">
-        <v>79.68000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="H19" t="n">
-        <v>77.16</v>
+        <v>74.23</v>
       </c>
       <c r="I19" t="n">
-        <v>78.95</v>
+        <v>75.34</v>
       </c>
       <c r="J19" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>8.630000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>8.27</v>
+        <v>9.23</v>
       </c>
       <c r="N19" t="n">
-        <v>41.98</v>
+        <v>42.77</v>
       </c>
       <c r="O19" t="n">
-        <v>42.06</v>
+        <v>43.57</v>
       </c>
       <c r="P19" t="n">
-        <v>40.68</v>
+        <v>41.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.07</v>
+        <v>42.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0584</v>
+        <v>-11.8213</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2214</v>
+        <v>-4.8342</v>
       </c>
       <c r="T19" t="n">
-        <v>22.4129</v>
+        <v>-7.2115</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2139</v>
+        <v>-4.5725</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5858</v>
+        <v>0.5069</v>
       </c>
       <c r="W19" t="n">
-        <v>10.6672</v>
+        <v>-1.2323</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9581</v>
+        <v>11.6082</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.8537</v>
+        <v>3.1285</v>
       </c>
       <c r="Z19" t="n">
-        <v>-21.9811</v>
+        <v>4.2938</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.191</v>
+        <v>4.6506</v>
       </c>
       <c r="AB19" t="n">
-        <v>-2.7238</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC19" t="n">
-        <v>-10.1902</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>167</v>
+        <v>172.95</v>
       </c>
       <c r="C20" t="n">
-        <v>174.4</v>
+        <v>174.61</v>
       </c>
       <c r="D20" t="n">
-        <v>161.14</v>
+        <v>142.69</v>
       </c>
       <c r="E20" t="n">
-        <v>164.18</v>
+        <v>151.75</v>
       </c>
       <c r="F20" t="n">
-        <v>75.73</v>
+        <v>76.13</v>
       </c>
       <c r="G20" t="n">
-        <v>77.37</v>
+        <v>76.27</v>
       </c>
       <c r="H20" t="n">
-        <v>74.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>75.34</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K20" t="n">
-        <v>9.390000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M20" t="n">
-        <v>9.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>42.77</v>
+        <v>42.51</v>
       </c>
       <c r="O20" t="n">
-        <v>43.57</v>
+        <v>44.82</v>
       </c>
       <c r="P20" t="n">
-        <v>41.93</v>
+        <v>42.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>42.98</v>
+        <v>43.54</v>
       </c>
       <c r="R20" t="n">
-        <v>-11.8213</v>
+        <v>-7.571</v>
       </c>
       <c r="S20" t="n">
-        <v>-4.8342</v>
+        <v>-17.6346</v>
       </c>
       <c r="T20" t="n">
-        <v>-7.2115</v>
+        <v>-20.3077</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.5725</v>
+        <v>-1.3539</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5069</v>
+        <v>-3.7804</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.2323</v>
+        <v>-3.4304</v>
       </c>
       <c r="X20" t="n">
-        <v>11.6082</v>
+        <v>7.8007</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.1285</v>
+        <v>19.1617</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2938</v>
+        <v>21.3415</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.6506</v>
+        <v>1.3029</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.7619</v>
+        <v>3.6914</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.9631</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>172.95</v>
+        <v>141.24</v>
       </c>
       <c r="C21" t="n">
-        <v>174.61</v>
+        <v>160.6</v>
       </c>
       <c r="D21" t="n">
-        <v>142.69</v>
+        <v>135.02</v>
       </c>
       <c r="E21" t="n">
-        <v>151.75</v>
+        <v>151.89</v>
       </c>
       <c r="F21" t="n">
-        <v>76.13</v>
+        <v>72.41</v>
       </c>
       <c r="G21" t="n">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="H21" t="n">
-        <v>72.09999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>74.31999999999999</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>8.77</v>
+        <v>10.64</v>
       </c>
       <c r="K21" t="n">
-        <v>10.47</v>
+        <v>11.07</v>
       </c>
       <c r="L21" t="n">
-        <v>8.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="N21" t="n">
-        <v>42.51</v>
+        <v>44.68</v>
       </c>
       <c r="O21" t="n">
-        <v>44.82</v>
+        <v>45.53</v>
       </c>
       <c r="P21" t="n">
-        <v>42.44</v>
+        <v>43.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>43.54</v>
+        <v>44.37</v>
       </c>
       <c r="R21" t="n">
-        <v>-7.571</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-17.6346</v>
+        <v>-18.422</v>
       </c>
       <c r="T21" t="n">
-        <v>-20.3077</v>
+        <v>-11.958</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3539</v>
+        <v>-1.8703</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.7804</v>
+        <v>-7.6251</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.4304</v>
+        <v>-2.7081</v>
       </c>
       <c r="X21" t="n">
-        <v>7.8007</v>
+        <v>-0.201</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.1617</v>
+        <v>20.0726</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.3415</v>
+        <v>10.9497</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3029</v>
+        <v>1.9063</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.6914</v>
+        <v>8.0351</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1265</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>141.24</v>
+        <v>161</v>
       </c>
       <c r="C22" t="n">
-        <v>160.6</v>
+        <v>173.7</v>
       </c>
       <c r="D22" t="n">
-        <v>135.02</v>
+        <v>161</v>
       </c>
       <c r="E22" t="n">
-        <v>151.89</v>
+        <v>173.2</v>
       </c>
       <c r="F22" t="n">
-        <v>72.41</v>
+        <v>74.09</v>
       </c>
       <c r="G22" t="n">
-        <v>74.5</v>
+        <v>76.53</v>
       </c>
       <c r="H22" t="n">
-        <v>70.95999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="I22" t="n">
-        <v>72.93000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>10.64</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>11.07</v>
+        <v>9.35</v>
       </c>
       <c r="L22" t="n">
-        <v>9.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M22" t="n">
-        <v>9.93</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>44.68</v>
+        <v>43.67</v>
       </c>
       <c r="O22" t="n">
-        <v>45.53</v>
+        <v>43.97</v>
       </c>
       <c r="P22" t="n">
-        <v>43.46</v>
+        <v>42.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>44.37</v>
+        <v>42.19</v>
       </c>
       <c r="R22" t="n">
-        <v>0.09229999999999999</v>
+        <v>14.0299</v>
       </c>
       <c r="S22" t="n">
-        <v>-18.422</v>
+        <v>5.494</v>
       </c>
       <c r="T22" t="n">
-        <v>-11.958</v>
+        <v>-5.9922</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.8703</v>
+        <v>4.9088</v>
       </c>
       <c r="V22" t="n">
-        <v>-7.6251</v>
+        <v>1.553</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.7081</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.201</v>
+        <v>-13.998</v>
       </c>
       <c r="Y22" t="n">
-        <v>20.0726</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z22" t="n">
-        <v>10.9497</v>
+        <v>2.2754</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.9063</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.0351</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4475</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>161</v>
+        <v>171.26</v>
       </c>
       <c r="C23" t="n">
-        <v>173.69</v>
+        <v>179.97</v>
       </c>
       <c r="D23" t="n">
-        <v>161.04</v>
+        <v>168.2501</v>
       </c>
       <c r="E23" t="n">
-        <v>173.2</v>
+        <v>178.39</v>
       </c>
       <c r="F23" t="n">
-        <v>74.084</v>
+        <v>75.19</v>
       </c>
       <c r="G23" t="n">
-        <v>76.53</v>
+        <v>77.7895</v>
       </c>
       <c r="H23" t="n">
-        <v>73.61499999999999</v>
+        <v>74.471</v>
       </c>
       <c r="I23" t="n">
-        <v>76.51000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="J23" t="n">
-        <v>9.300000000000001</v>
+        <v>8.645</v>
       </c>
       <c r="K23" t="n">
-        <v>9.35</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>8.51</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>8.539999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>43.675</v>
+        <v>42.97</v>
       </c>
       <c r="O23" t="n">
-        <v>43.965</v>
+        <v>43.3305</v>
       </c>
       <c r="P23" t="n">
-        <v>42.19</v>
+        <v>41.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>42.19</v>
+        <v>41.96</v>
       </c>
       <c r="R23" t="n">
-        <v>14.0299</v>
+        <v>2.9965</v>
       </c>
       <c r="S23" t="n">
-        <v>5.494</v>
+        <v>17.5552</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.9922</v>
+        <v>-4.1893</v>
       </c>
       <c r="U23" t="n">
-        <v>4.9088</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>1.553</v>
+        <v>3.5388</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-2.5332</v>
       </c>
       <c r="X23" t="n">
-        <v>-13.998</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y23" t="n">
-        <v>-7.4756</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2754</v>
+        <v>0.2418</v>
       </c>
       <c r="AA23" t="n">
-        <v>-4.9132</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB23" t="n">
-        <v>-1.8381</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.4763</v>
+        <v>2.167</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -24759,1895 +24759,1895 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102.94</v>
+        <v>108.62</v>
       </c>
       <c r="C2" t="n">
-        <v>106.09</v>
+        <v>116.77</v>
       </c>
       <c r="D2" t="n">
-        <v>99.59999999999999</v>
+        <v>107.46</v>
       </c>
       <c r="E2" t="n">
-        <v>105.64</v>
+        <v>112.77</v>
       </c>
       <c r="F2" t="n">
-        <v>58.93</v>
+        <v>59.8</v>
       </c>
       <c r="G2" t="n">
-        <v>60.3</v>
+        <v>60.73</v>
       </c>
       <c r="H2" t="n">
-        <v>58.49</v>
+        <v>57.59</v>
       </c>
       <c r="I2" t="n">
-        <v>60.21</v>
+        <v>59.22</v>
       </c>
       <c r="J2" t="n">
-        <v>17.37</v>
+        <v>16.35</v>
       </c>
       <c r="K2" t="n">
-        <v>17.95</v>
+        <v>16.52</v>
       </c>
       <c r="L2" t="n">
-        <v>16.72</v>
+        <v>15.06</v>
       </c>
       <c r="M2" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="N2" t="n">
-        <v>56.05</v>
+        <v>55.13</v>
       </c>
       <c r="O2" t="n">
-        <v>56.49</v>
+        <v>57.14</v>
       </c>
       <c r="P2" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>54.73</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>108.62</v>
+        <v>125.21</v>
       </c>
       <c r="C3" t="n">
-        <v>116.77</v>
+        <v>130.12</v>
       </c>
       <c r="D3" t="n">
-        <v>107.46</v>
+        <v>120.24</v>
       </c>
       <c r="E3" t="n">
-        <v>112.77</v>
+        <v>128.32</v>
       </c>
       <c r="F3" t="n">
-        <v>59.8</v>
+        <v>61.08</v>
       </c>
       <c r="G3" t="n">
-        <v>60.73</v>
+        <v>62.74</v>
       </c>
       <c r="H3" t="n">
-        <v>57.59</v>
+        <v>60.56</v>
       </c>
       <c r="I3" t="n">
-        <v>59.22</v>
+        <v>62.56</v>
       </c>
       <c r="J3" t="n">
-        <v>16.35</v>
+        <v>13.99</v>
       </c>
       <c r="K3" t="n">
-        <v>16.52</v>
+        <v>14.66</v>
       </c>
       <c r="L3" t="n">
-        <v>15.06</v>
+        <v>13.3</v>
       </c>
       <c r="M3" t="n">
-        <v>15.7</v>
+        <v>13.52</v>
       </c>
       <c r="N3" t="n">
-        <v>55.13</v>
+        <v>53.93</v>
       </c>
       <c r="O3" t="n">
-        <v>57.14</v>
+        <v>54.43</v>
       </c>
       <c r="P3" t="n">
-        <v>54.28</v>
+        <v>52.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>55.66</v>
+        <v>52.5</v>
       </c>
       <c r="R3" t="n">
-        <v>6.7493</v>
+        <v>13.7891</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.6442</v>
+        <v>5.64</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.5476</v>
+        <v>-13.8854</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6993</v>
+        <v>-5.6773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>125.21</v>
+        <v>128.33</v>
       </c>
       <c r="C4" t="n">
-        <v>130.12</v>
+        <v>129.59</v>
       </c>
       <c r="D4" t="n">
-        <v>120.24</v>
+        <v>117.79</v>
       </c>
       <c r="E4" t="n">
-        <v>128.32</v>
+        <v>123.39</v>
       </c>
       <c r="F4" t="n">
-        <v>61.08</v>
+        <v>62.41</v>
       </c>
       <c r="G4" t="n">
-        <v>62.74</v>
+        <v>62.7</v>
       </c>
       <c r="H4" t="n">
-        <v>60.56</v>
+        <v>61.64</v>
       </c>
       <c r="I4" t="n">
-        <v>62.56</v>
+        <v>62.64</v>
       </c>
       <c r="J4" t="n">
-        <v>13.99</v>
+        <v>13.51</v>
       </c>
       <c r="K4" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="L4" t="n">
-        <v>13.3</v>
+        <v>13.41</v>
       </c>
       <c r="M4" t="n">
-        <v>13.52</v>
+        <v>14.03</v>
       </c>
       <c r="N4" t="n">
-        <v>53.93</v>
+        <v>52.67</v>
       </c>
       <c r="O4" t="n">
-        <v>54.43</v>
+        <v>53.31</v>
       </c>
       <c r="P4" t="n">
-        <v>52.37</v>
+        <v>52.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.5</v>
+        <v>52.45</v>
       </c>
       <c r="R4" t="n">
-        <v>13.7891</v>
+        <v>-3.842</v>
       </c>
       <c r="U4" t="n">
-        <v>5.64</v>
+        <v>0.1279</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.8854</v>
+        <v>3.7722</v>
       </c>
       <c r="AA4" t="n">
-        <v>-5.6773</v>
+        <v>-0.09520000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>128.33</v>
+        <v>108.75</v>
       </c>
       <c r="C5" t="n">
-        <v>129.59</v>
+        <v>115.62</v>
       </c>
       <c r="D5" t="n">
-        <v>117.79</v>
+        <v>103.99</v>
       </c>
       <c r="E5" t="n">
-        <v>123.39</v>
+        <v>109.56</v>
       </c>
       <c r="F5" t="n">
-        <v>62.41</v>
+        <v>60.72</v>
       </c>
       <c r="G5" t="n">
-        <v>62.7</v>
+        <v>61.33</v>
       </c>
       <c r="H5" t="n">
-        <v>61.64</v>
+        <v>59.68</v>
       </c>
       <c r="I5" t="n">
-        <v>62.64</v>
+        <v>60.74</v>
       </c>
       <c r="J5" t="n">
-        <v>13.51</v>
+        <v>15.71</v>
       </c>
       <c r="K5" t="n">
-        <v>14.63</v>
+        <v>16.27</v>
       </c>
       <c r="L5" t="n">
-        <v>13.41</v>
+        <v>14.93</v>
       </c>
       <c r="M5" t="n">
-        <v>14.03</v>
+        <v>15.59</v>
       </c>
       <c r="N5" t="n">
-        <v>52.67</v>
+        <v>54.09</v>
       </c>
       <c r="O5" t="n">
-        <v>53.31</v>
+        <v>54.96</v>
       </c>
       <c r="P5" t="n">
-        <v>52.42</v>
+        <v>53.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.45</v>
+        <v>54.05</v>
       </c>
       <c r="R5" t="n">
-        <v>-3.842</v>
+        <v>-11.2084</v>
       </c>
       <c r="S5" t="n">
-        <v>16.8023</v>
+        <v>-2.8465</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1279</v>
+        <v>-3.0332</v>
       </c>
       <c r="V5" t="n">
-        <v>4.0359</v>
+        <v>2.5667</v>
       </c>
       <c r="X5" t="n">
-        <v>3.7722</v>
+        <v>11.119</v>
       </c>
       <c r="Y5" t="n">
-        <v>-16.4881</v>
+        <v>-0.7006</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.09520000000000001</v>
+        <v>3.0505</v>
       </c>
       <c r="AB5" t="n">
-        <v>-4.1659</v>
+        <v>-2.8926</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108.75</v>
+        <v>114.76</v>
       </c>
       <c r="C6" t="n">
-        <v>115.62</v>
+        <v>118.32</v>
       </c>
       <c r="D6" t="n">
-        <v>103.99</v>
+        <v>112.3</v>
       </c>
       <c r="E6" t="n">
-        <v>109.56</v>
+        <v>117.97</v>
       </c>
       <c r="F6" t="n">
-        <v>60.72</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>61.33</v>
+        <v>61.87</v>
       </c>
       <c r="H6" t="n">
-        <v>59.68</v>
+        <v>60.45</v>
       </c>
       <c r="I6" t="n">
-        <v>60.74</v>
+        <v>61.86</v>
       </c>
       <c r="J6" t="n">
-        <v>15.71</v>
+        <v>14.91</v>
       </c>
       <c r="K6" t="n">
-        <v>16.27</v>
+        <v>15.24</v>
       </c>
       <c r="L6" t="n">
-        <v>14.93</v>
+        <v>14.38</v>
       </c>
       <c r="M6" t="n">
-        <v>15.59</v>
+        <v>14.4</v>
       </c>
       <c r="N6" t="n">
-        <v>54.09</v>
+        <v>53.84</v>
       </c>
       <c r="O6" t="n">
-        <v>54.96</v>
+        <v>54.33</v>
       </c>
       <c r="P6" t="n">
-        <v>53.58</v>
+        <v>53.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>54.05</v>
+        <v>53.08</v>
       </c>
       <c r="R6" t="n">
-        <v>-11.2084</v>
+        <v>7.6762</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.8465</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.0332</v>
+        <v>1.8439</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5667</v>
+        <v>-1.1189</v>
       </c>
       <c r="X6" t="n">
-        <v>11.119</v>
+        <v>-7.6331</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.7006</v>
+        <v>6.5089</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.0505</v>
+        <v>-1.7946</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.8926</v>
+        <v>1.1048</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C7" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D7" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E7" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G7" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H7" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I7" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J7" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K7" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L7" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N7" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O7" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P7" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6762</v>
+        <v>7.6375</v>
       </c>
       <c r="S7" t="n">
-        <v>-8.065799999999999</v>
+        <v>2.9095</v>
       </c>
       <c r="T7" t="n">
-        <v>11.6717</v>
+        <v>12.6009</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8439</v>
+        <v>2.7158</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1189</v>
+        <v>1.4368</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7404</v>
+        <v>7.2948</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.6331</v>
+        <v>-7.6389</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.5089</v>
+        <v>-5.2031</v>
       </c>
       <c r="Z7" t="n">
-        <v>-14.2857</v>
+        <v>-15.2866</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.7946</v>
+        <v>-2.694</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.1048</v>
+        <v>-1.5253</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.0148</v>
+        <v>-7.2045</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C8" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D8" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E8" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F8" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G8" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H8" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I8" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J8" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K8" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L8" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M8" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N8" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O8" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P8" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R8" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9095</v>
+        <v>19.0215</v>
       </c>
       <c r="T8" t="n">
-        <v>12.6009</v>
+        <v>1.6209</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4368</v>
+        <v>7.5074</v>
       </c>
       <c r="W8" t="n">
-        <v>7.2948</v>
+        <v>4.3798</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="Y8" t="n">
-        <v>-5.2031</v>
+        <v>-16.7415</v>
       </c>
       <c r="Z8" t="n">
-        <v>-15.2866</v>
+        <v>-3.9941</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.5253</v>
+        <v>-7.086</v>
       </c>
       <c r="AC8" t="n">
-        <v>-7.2045</v>
+        <v>-4.3429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C9" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D9" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E9" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F9" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G9" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H9" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I9" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J9" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K9" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L9" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M9" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N9" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O9" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P9" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="S9" t="n">
-        <v>19.0215</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6209</v>
+        <v>3.3714</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5074</v>
+        <v>4.9305</v>
       </c>
       <c r="W9" t="n">
-        <v>4.3798</v>
+        <v>3.6239</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="Y9" t="n">
-        <v>-16.7415</v>
+        <v>-7.9167</v>
       </c>
       <c r="Z9" t="n">
-        <v>-3.9941</v>
+        <v>-5.4882</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
       <c r="AB9" t="n">
-        <v>-7.086</v>
+        <v>-4.8417</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.3429</v>
+        <v>-3.6988</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C10" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D10" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E10" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F10" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G10" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H10" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I10" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J10" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K10" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L10" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M10" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N10" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O10" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P10" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R10" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S10" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3714</v>
+        <v>31.5809</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V10" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6239</v>
+        <v>10.9483</v>
       </c>
       <c r="X10" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y10" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="Z10" t="n">
-        <v>-5.4882</v>
+        <v>-26.1706</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB10" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6988</v>
+        <v>-10.1018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C11" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E11" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F11" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H11" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I11" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K11" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L11" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N11" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O11" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P11" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R11" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S11" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="T11" t="n">
-        <v>31.5809</v>
+        <v>40.5866</v>
       </c>
       <c r="U11" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V11" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>10.9483</v>
+        <v>15.6967</v>
       </c>
       <c r="X11" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y11" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z11" t="n">
-        <v>-26.1706</v>
+        <v>-31.875</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB11" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC11" t="n">
-        <v>-10.1018</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C12" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D12" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E12" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F12" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G12" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H12" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I12" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J12" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K12" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N12" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O12" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P12" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R12" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S12" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T12" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U12" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V12" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X12" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z12" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA12" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB12" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC12" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C13" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D13" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E13" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F13" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H13" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I13" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J13" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M13" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N13" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O13" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P13" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R13" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S13" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="T13" t="n">
-        <v>19.7826</v>
+        <v>35.6902</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V13" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W13" t="n">
-        <v>12.2757</v>
+        <v>16.8147</v>
       </c>
       <c r="X13" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y13" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z13" t="n">
-        <v>-20.3008</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB13" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC13" t="n">
-        <v>-11.4618</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C14" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D14" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E14" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F14" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H14" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I14" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K14" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L14" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M14" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O14" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P14" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R14" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S14" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="T14" t="n">
-        <v>35.6902</v>
+        <v>49.2905</v>
       </c>
       <c r="U14" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V14" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="W14" t="n">
-        <v>16.8147</v>
+        <v>18.5642</v>
       </c>
       <c r="X14" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y14" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z14" t="n">
-        <v>-31.8182</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA14" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB14" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
       <c r="AC14" t="n">
-        <v>-15.233</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C15" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D15" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E15" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F15" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G15" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I15" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K15" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L15" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O15" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P15" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R15" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S15" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="T15" t="n">
-        <v>49.2905</v>
+        <v>19.6726</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="W15" t="n">
-        <v>18.5642</v>
+        <v>11.2331</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y15" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="Z15" t="n">
-        <v>-38.1599</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB15" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC15" t="n">
-        <v>-16.4126</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C16" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D16" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E16" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F16" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G16" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H16" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I16" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L16" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N16" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O16" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P16" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R16" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S16" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T16" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V16" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W16" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X16" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y16" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z16" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB16" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC16" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>183.84</v>
+        <v>182.67</v>
       </c>
       <c r="C17" t="n">
-        <v>188.49</v>
+        <v>189.56</v>
       </c>
       <c r="D17" t="n">
-        <v>172.26</v>
+        <v>178.28</v>
       </c>
       <c r="E17" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F17" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>74.19</v>
+        <v>77.16</v>
       </c>
       <c r="I17" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J17" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K17" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N17" t="n">
-        <v>42.83</v>
+        <v>41.98</v>
       </c>
       <c r="O17" t="n">
-        <v>43.77</v>
+        <v>42.06</v>
       </c>
       <c r="P17" t="n">
-        <v>41.6</v>
+        <v>40.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R17" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T17" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U17" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W17" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y17" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z17" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA17" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC17" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>182.67</v>
+        <v>167</v>
       </c>
       <c r="C18" t="n">
-        <v>189.56</v>
+        <v>174.4</v>
       </c>
       <c r="D18" t="n">
-        <v>178.28</v>
+        <v>161.14</v>
       </c>
       <c r="E18" t="n">
-        <v>186.19</v>
+        <v>164.18</v>
       </c>
       <c r="F18" t="n">
-        <v>77.29000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G18" t="n">
-        <v>79.68000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="H18" t="n">
-        <v>77.16</v>
+        <v>74.23</v>
       </c>
       <c r="I18" t="n">
-        <v>78.95</v>
+        <v>75.34</v>
       </c>
       <c r="J18" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>8.630000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>8.27</v>
+        <v>9.23</v>
       </c>
       <c r="N18" t="n">
-        <v>41.98</v>
+        <v>42.77</v>
       </c>
       <c r="O18" t="n">
-        <v>42.06</v>
+        <v>43.57</v>
       </c>
       <c r="P18" t="n">
-        <v>40.68</v>
+        <v>41.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.07</v>
+        <v>42.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0584</v>
+        <v>-11.8213</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.2214</v>
+        <v>-4.8342</v>
       </c>
       <c r="T18" t="n">
-        <v>22.4129</v>
+        <v>-7.2115</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2139</v>
+        <v>-4.5725</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5858</v>
+        <v>0.5069</v>
       </c>
       <c r="W18" t="n">
-        <v>10.6672</v>
+        <v>-1.2323</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9581</v>
+        <v>11.6082</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.8537</v>
+        <v>3.1285</v>
       </c>
       <c r="Z18" t="n">
-        <v>-21.9811</v>
+        <v>4.2938</v>
       </c>
       <c r="AA18" t="n">
-        <v>-2.191</v>
+        <v>4.6506</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.7238</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC18" t="n">
-        <v>-10.1902</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>167</v>
+        <v>172.95</v>
       </c>
       <c r="C19" t="n">
-        <v>174.4</v>
+        <v>174.61</v>
       </c>
       <c r="D19" t="n">
-        <v>161.14</v>
+        <v>142.69</v>
       </c>
       <c r="E19" t="n">
-        <v>164.18</v>
+        <v>151.75</v>
       </c>
       <c r="F19" t="n">
-        <v>75.73</v>
+        <v>76.13</v>
       </c>
       <c r="G19" t="n">
-        <v>77.37</v>
+        <v>76.27</v>
       </c>
       <c r="H19" t="n">
-        <v>74.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>75.34</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K19" t="n">
-        <v>9.390000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M19" t="n">
-        <v>9.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>42.77</v>
+        <v>42.51</v>
       </c>
       <c r="O19" t="n">
-        <v>43.57</v>
+        <v>44.82</v>
       </c>
       <c r="P19" t="n">
-        <v>41.93</v>
+        <v>42.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>42.98</v>
+        <v>43.54</v>
       </c>
       <c r="R19" t="n">
-        <v>-11.8213</v>
+        <v>-7.571</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.8342</v>
+        <v>-17.6346</v>
       </c>
       <c r="T19" t="n">
-        <v>-7.2115</v>
+        <v>-20.3077</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.5725</v>
+        <v>-1.3539</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5069</v>
+        <v>-3.7804</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.2323</v>
+        <v>-3.4304</v>
       </c>
       <c r="X19" t="n">
-        <v>11.6082</v>
+        <v>7.8007</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.1285</v>
+        <v>19.1617</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2938</v>
+        <v>21.3415</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.6506</v>
+        <v>1.3029</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.7619</v>
+        <v>3.6914</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.9631</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>172.95</v>
+        <v>141.24</v>
       </c>
       <c r="C20" t="n">
-        <v>174.61</v>
+        <v>160.6</v>
       </c>
       <c r="D20" t="n">
-        <v>142.69</v>
+        <v>135.02</v>
       </c>
       <c r="E20" t="n">
-        <v>151.75</v>
+        <v>151.89</v>
       </c>
       <c r="F20" t="n">
-        <v>76.13</v>
+        <v>72.41</v>
       </c>
       <c r="G20" t="n">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="H20" t="n">
-        <v>72.09999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>74.31999999999999</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>8.77</v>
+        <v>10.64</v>
       </c>
       <c r="K20" t="n">
-        <v>10.47</v>
+        <v>11.07</v>
       </c>
       <c r="L20" t="n">
-        <v>8.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="N20" t="n">
-        <v>42.51</v>
+        <v>44.68</v>
       </c>
       <c r="O20" t="n">
-        <v>44.82</v>
+        <v>45.53</v>
       </c>
       <c r="P20" t="n">
-        <v>42.44</v>
+        <v>43.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>43.54</v>
+        <v>44.37</v>
       </c>
       <c r="R20" t="n">
-        <v>-7.571</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-17.6346</v>
+        <v>-18.422</v>
       </c>
       <c r="T20" t="n">
-        <v>-20.3077</v>
+        <v>-11.958</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3539</v>
+        <v>-1.8703</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.7804</v>
+        <v>-7.6251</v>
       </c>
       <c r="W20" t="n">
-        <v>-3.4304</v>
+        <v>-2.7081</v>
       </c>
       <c r="X20" t="n">
-        <v>7.8007</v>
+        <v>-0.201</v>
       </c>
       <c r="Y20" t="n">
-        <v>19.1617</v>
+        <v>20.0726</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.3415</v>
+        <v>10.9497</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3029</v>
+        <v>1.9063</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.6914</v>
+        <v>8.0351</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.1265</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>141.24</v>
+        <v>161</v>
       </c>
       <c r="C21" t="n">
-        <v>160.6</v>
+        <v>173.7</v>
       </c>
       <c r="D21" t="n">
-        <v>135.02</v>
+        <v>161</v>
       </c>
       <c r="E21" t="n">
-        <v>151.89</v>
+        <v>173.2</v>
       </c>
       <c r="F21" t="n">
-        <v>72.41</v>
+        <v>74.09</v>
       </c>
       <c r="G21" t="n">
-        <v>74.5</v>
+        <v>76.53</v>
       </c>
       <c r="H21" t="n">
-        <v>70.95999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="I21" t="n">
-        <v>72.93000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>10.64</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>11.07</v>
+        <v>9.35</v>
       </c>
       <c r="L21" t="n">
-        <v>9.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M21" t="n">
-        <v>9.93</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>44.68</v>
+        <v>43.67</v>
       </c>
       <c r="O21" t="n">
-        <v>45.53</v>
+        <v>43.97</v>
       </c>
       <c r="P21" t="n">
-        <v>43.46</v>
+        <v>42.19</v>
       </c>
       <c r="Q21" t="n">
-        <v>44.37</v>
+        <v>42.19</v>
       </c>
       <c r="R21" t="n">
-        <v>0.09229999999999999</v>
+        <v>14.0299</v>
       </c>
       <c r="S21" t="n">
-        <v>-18.422</v>
+        <v>5.494</v>
       </c>
       <c r="T21" t="n">
-        <v>-11.958</v>
+        <v>-5.9922</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8703</v>
+        <v>4.9088</v>
       </c>
       <c r="V21" t="n">
-        <v>-7.6251</v>
+        <v>1.553</v>
       </c>
       <c r="W21" t="n">
-        <v>-2.7081</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.201</v>
+        <v>-13.998</v>
       </c>
       <c r="Y21" t="n">
-        <v>20.0726</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z21" t="n">
-        <v>10.9497</v>
+        <v>2.2754</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.9063</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.0351</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.4475</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>161</v>
+        <v>171.26</v>
       </c>
       <c r="C22" t="n">
-        <v>173.7</v>
+        <v>179.97</v>
       </c>
       <c r="D22" t="n">
-        <v>161</v>
+        <v>168.23</v>
       </c>
       <c r="E22" t="n">
-        <v>173.2</v>
+        <v>178.39</v>
       </c>
       <c r="F22" t="n">
-        <v>74.09</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>73.62</v>
+        <v>74.47</v>
       </c>
       <c r="I22" t="n">
-        <v>76.51000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="J22" t="n">
-        <v>9.300000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="K22" t="n">
-        <v>9.35</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>8.51</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>8.539999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>43.67</v>
+        <v>42.94</v>
       </c>
       <c r="O22" t="n">
-        <v>43.97</v>
+        <v>43.33</v>
       </c>
       <c r="P22" t="n">
-        <v>42.19</v>
+        <v>41.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>42.19</v>
+        <v>41.96</v>
       </c>
       <c r="R22" t="n">
-        <v>14.0299</v>
+        <v>2.9965</v>
       </c>
       <c r="S22" t="n">
-        <v>5.494</v>
+        <v>17.5552</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.9922</v>
+        <v>-4.1893</v>
       </c>
       <c r="U22" t="n">
-        <v>4.9088</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>1.553</v>
+        <v>3.5388</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-2.5332</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.998</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y22" t="n">
-        <v>-7.4756</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2754</v>
+        <v>0.2418</v>
       </c>
       <c r="AA22" t="n">
-        <v>-4.9132</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB22" t="n">
-        <v>-1.8381</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.4763</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>171.26</v>
+        <v>184.8</v>
       </c>
       <c r="C23" t="n">
-        <v>179.97</v>
+        <v>195.255</v>
       </c>
       <c r="D23" t="n">
-        <v>168.2501</v>
+        <v>183.34</v>
       </c>
       <c r="E23" t="n">
-        <v>178.39</v>
+        <v>190.56</v>
       </c>
       <c r="F23" t="n">
-        <v>75.19</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>77.7895</v>
+        <v>79.33</v>
       </c>
       <c r="H23" t="n">
-        <v>74.471</v>
+        <v>77.33199999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>76.95</v>
+        <v>77.84</v>
       </c>
       <c r="J23" t="n">
-        <v>8.645</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>8.779999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="L23" t="n">
-        <v>8.210000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
-        <v>8.289999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="N23" t="n">
-        <v>42.97</v>
+        <v>41.39</v>
       </c>
       <c r="O23" t="n">
-        <v>43.3305</v>
+        <v>41.78</v>
       </c>
       <c r="P23" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="Q23" t="n">
         <v>41.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>41.96</v>
-      </c>
       <c r="R23" t="n">
-        <v>2.9965</v>
+        <v>6.8221</v>
       </c>
       <c r="S23" t="n">
-        <v>17.5552</v>
+        <v>25.4592</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.1893</v>
+        <v>16.0677</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5750999999999999</v>
+        <v>1.1566</v>
       </c>
       <c r="V23" t="n">
-        <v>3.5388</v>
+        <v>6.7325</v>
       </c>
       <c r="W23" t="n">
-        <v>-2.5332</v>
+        <v>3.3183</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.9274</v>
+        <v>-6.7551</v>
       </c>
       <c r="Y23" t="n">
-        <v>-16.6834</v>
+        <v>-22.1551</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.2418</v>
+        <v>-16.2514</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.5452</v>
+        <v>-1.0963</v>
       </c>
       <c r="AB23" t="n">
-        <v>-3.6288</v>
+        <v>-6.4683</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.167</v>
+        <v>-3.4435</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24759,1895 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.62</v>
+        <v>114.76</v>
       </c>
       <c r="C2" t="n">
-        <v>116.77</v>
+        <v>118.32</v>
       </c>
       <c r="D2" t="n">
-        <v>107.46</v>
+        <v>112.3</v>
       </c>
       <c r="E2" t="n">
-        <v>112.77</v>
+        <v>117.97</v>
       </c>
       <c r="F2" t="n">
-        <v>59.8</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>60.73</v>
+        <v>61.87</v>
       </c>
       <c r="H2" t="n">
-        <v>57.59</v>
+        <v>60.45</v>
       </c>
       <c r="I2" t="n">
-        <v>59.22</v>
+        <v>61.86</v>
       </c>
       <c r="J2" t="n">
-        <v>16.35</v>
+        <v>14.91</v>
       </c>
       <c r="K2" t="n">
-        <v>16.52</v>
+        <v>15.24</v>
       </c>
       <c r="L2" t="n">
-        <v>15.06</v>
+        <v>14.38</v>
       </c>
       <c r="M2" t="n">
-        <v>15.7</v>
+        <v>14.4</v>
       </c>
       <c r="N2" t="n">
-        <v>55.13</v>
+        <v>53.84</v>
       </c>
       <c r="O2" t="n">
-        <v>57.14</v>
+        <v>54.33</v>
       </c>
       <c r="P2" t="n">
-        <v>54.28</v>
+        <v>53.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>55.66</v>
+        <v>53.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125.21</v>
+        <v>122.81</v>
       </c>
       <c r="C3" t="n">
-        <v>130.12</v>
+        <v>127.45</v>
       </c>
       <c r="D3" t="n">
-        <v>120.24</v>
+        <v>117.5</v>
       </c>
       <c r="E3" t="n">
-        <v>128.32</v>
+        <v>126.98</v>
       </c>
       <c r="F3" t="n">
-        <v>61.08</v>
+        <v>62.89</v>
       </c>
       <c r="G3" t="n">
-        <v>62.74</v>
+        <v>63.8</v>
       </c>
       <c r="H3" t="n">
-        <v>60.56</v>
+        <v>60.7</v>
       </c>
       <c r="I3" t="n">
-        <v>62.56</v>
+        <v>63.54</v>
       </c>
       <c r="J3" t="n">
-        <v>13.99</v>
+        <v>13.84</v>
       </c>
       <c r="K3" t="n">
-        <v>14.66</v>
+        <v>14.49</v>
       </c>
       <c r="L3" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="M3" t="n">
         <v>13.3</v>
       </c>
-      <c r="M3" t="n">
-        <v>13.52</v>
-      </c>
       <c r="N3" t="n">
-        <v>53.93</v>
+        <v>52.21</v>
       </c>
       <c r="O3" t="n">
-        <v>54.43</v>
+        <v>54.09</v>
       </c>
       <c r="P3" t="n">
-        <v>52.37</v>
+        <v>51.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>52.5</v>
+        <v>51.65</v>
       </c>
       <c r="R3" t="n">
-        <v>13.7891</v>
+        <v>7.6375</v>
       </c>
       <c r="U3" t="n">
-        <v>5.64</v>
+        <v>2.7158</v>
       </c>
       <c r="X3" t="n">
-        <v>-13.8854</v>
+        <v>-7.6389</v>
       </c>
       <c r="AA3" t="n">
-        <v>-5.6773</v>
+        <v>-2.694</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>128.33</v>
+        <v>124.39</v>
       </c>
       <c r="C4" t="n">
-        <v>129.59</v>
+        <v>131.38</v>
       </c>
       <c r="D4" t="n">
-        <v>117.79</v>
+        <v>121.66</v>
       </c>
       <c r="E4" t="n">
-        <v>123.39</v>
+        <v>130.4</v>
       </c>
       <c r="F4" t="n">
-        <v>62.41</v>
+        <v>63.89</v>
       </c>
       <c r="G4" t="n">
-        <v>62.7</v>
+        <v>65.84</v>
       </c>
       <c r="H4" t="n">
-        <v>61.64</v>
+        <v>63.81</v>
       </c>
       <c r="I4" t="n">
-        <v>62.64</v>
+        <v>65.3</v>
       </c>
       <c r="J4" t="n">
-        <v>13.51</v>
+        <v>13.61</v>
       </c>
       <c r="K4" t="n">
-        <v>14.63</v>
+        <v>13.89</v>
       </c>
       <c r="L4" t="n">
-        <v>13.41</v>
+        <v>12.87</v>
       </c>
       <c r="M4" t="n">
-        <v>14.03</v>
+        <v>12.98</v>
       </c>
       <c r="N4" t="n">
-        <v>52.67</v>
+        <v>51.36</v>
       </c>
       <c r="O4" t="n">
-        <v>53.31</v>
+        <v>51.45</v>
       </c>
       <c r="P4" t="n">
-        <v>52.42</v>
+        <v>49.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.45</v>
+        <v>50.22</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.842</v>
+        <v>2.6933</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1279</v>
+        <v>2.7699</v>
       </c>
       <c r="X4" t="n">
-        <v>3.7722</v>
+        <v>-2.406</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-2.7686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.75</v>
+        <v>132.2</v>
       </c>
       <c r="C5" t="n">
-        <v>115.62</v>
+        <v>133.67</v>
       </c>
       <c r="D5" t="n">
-        <v>103.99</v>
+        <v>123.8</v>
       </c>
       <c r="E5" t="n">
-        <v>109.56</v>
+        <v>127.55</v>
       </c>
       <c r="F5" t="n">
-        <v>60.72</v>
+        <v>65.44</v>
       </c>
       <c r="G5" t="n">
-        <v>61.33</v>
+        <v>66.05</v>
       </c>
       <c r="H5" t="n">
-        <v>59.68</v>
+        <v>63.78</v>
       </c>
       <c r="I5" t="n">
-        <v>60.74</v>
+        <v>64.91</v>
       </c>
       <c r="J5" t="n">
-        <v>15.71</v>
+        <v>12.8</v>
       </c>
       <c r="K5" t="n">
-        <v>16.27</v>
+        <v>13.64</v>
       </c>
       <c r="L5" t="n">
-        <v>14.93</v>
+        <v>12.65</v>
       </c>
       <c r="M5" t="n">
-        <v>15.59</v>
+        <v>13.26</v>
       </c>
       <c r="N5" t="n">
-        <v>54.09</v>
+        <v>50.12</v>
       </c>
       <c r="O5" t="n">
-        <v>54.96</v>
+        <v>51.43</v>
       </c>
       <c r="P5" t="n">
-        <v>53.58</v>
+        <v>49.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.05</v>
+        <v>50.51</v>
       </c>
       <c r="R5" t="n">
-        <v>-11.2084</v>
+        <v>-2.1856</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.8465</v>
+        <v>8.120699999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.0332</v>
+        <v>-0.5972</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5667</v>
+        <v>4.9305</v>
       </c>
       <c r="X5" t="n">
-        <v>11.119</v>
+        <v>2.1572</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.7006</v>
+        <v>-7.9167</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.0505</v>
+        <v>0.5775</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.8926</v>
+        <v>-4.8417</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>114.76</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>118.32</v>
+        <v>147.26</v>
       </c>
       <c r="D6" t="n">
-        <v>112.3</v>
+        <v>134.02</v>
       </c>
       <c r="E6" t="n">
-        <v>117.97</v>
+        <v>144.16</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>66.37</v>
       </c>
       <c r="G6" t="n">
-        <v>61.87</v>
+        <v>67.77</v>
       </c>
       <c r="H6" t="n">
-        <v>60.45</v>
+        <v>66.25</v>
       </c>
       <c r="I6" t="n">
-        <v>61.86</v>
+        <v>67.39</v>
       </c>
       <c r="J6" t="n">
-        <v>14.91</v>
+        <v>12.5</v>
       </c>
       <c r="K6" t="n">
-        <v>15.24</v>
+        <v>12.59</v>
       </c>
       <c r="L6" t="n">
-        <v>14.38</v>
+        <v>11.21</v>
       </c>
       <c r="M6" t="n">
-        <v>14.4</v>
+        <v>11.51</v>
       </c>
       <c r="N6" t="n">
-        <v>53.84</v>
+        <v>49.4</v>
       </c>
       <c r="O6" t="n">
-        <v>54.33</v>
+        <v>49.49</v>
       </c>
       <c r="P6" t="n">
-        <v>53.06</v>
+        <v>48.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>53.08</v>
+        <v>48.59</v>
       </c>
       <c r="R6" t="n">
-        <v>7.6762</v>
+        <v>13.0223</v>
       </c>
       <c r="S6" t="n">
-        <v>-8.065799999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8439</v>
+        <v>3.8207</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1189</v>
+        <v>6.0592</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.6331</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.5089</v>
+        <v>-13.4586</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.7946</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1048</v>
+        <v>-5.9245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122.81</v>
+        <v>157.84</v>
       </c>
       <c r="C7" t="n">
-        <v>127.45</v>
+        <v>166</v>
       </c>
       <c r="D7" t="n">
-        <v>117.5</v>
+        <v>149.06</v>
       </c>
       <c r="E7" t="n">
-        <v>126.98</v>
+        <v>165.85</v>
       </c>
       <c r="F7" t="n">
-        <v>62.89</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>63.8</v>
+        <v>71.66</v>
       </c>
       <c r="H7" t="n">
-        <v>60.7</v>
+        <v>68.88</v>
       </c>
       <c r="I7" t="n">
-        <v>63.54</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>13.84</v>
+        <v>10.43</v>
       </c>
       <c r="K7" t="n">
-        <v>14.49</v>
+        <v>11.14</v>
       </c>
       <c r="L7" t="n">
-        <v>13.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>13.3</v>
+        <v>9.81</v>
       </c>
       <c r="N7" t="n">
-        <v>52.21</v>
+        <v>47.26</v>
       </c>
       <c r="O7" t="n">
-        <v>54.09</v>
+        <v>47.54</v>
       </c>
       <c r="P7" t="n">
-        <v>51.4</v>
+        <v>45.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>51.65</v>
+        <v>45.59</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6375</v>
+        <v>15.0458</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9095</v>
+        <v>27.1856</v>
       </c>
       <c r="T7" t="n">
-        <v>12.6009</v>
+        <v>40.5866</v>
       </c>
       <c r="U7" t="n">
-        <v>2.7158</v>
+        <v>6.2027</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4368</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2948</v>
+        <v>15.6967</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.6389</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y7" t="n">
-        <v>-5.2031</v>
+        <v>-24.4222</v>
       </c>
       <c r="Z7" t="n">
-        <v>-15.2866</v>
+        <v>-31.875</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.694</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.5253</v>
+        <v>-9.2194</v>
       </c>
       <c r="AC7" t="n">
-        <v>-7.2045</v>
+        <v>-14.1108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>124.39</v>
+        <v>162.12</v>
       </c>
       <c r="C8" t="n">
-        <v>131.38</v>
+        <v>162.9</v>
       </c>
       <c r="D8" t="n">
-        <v>121.66</v>
+        <v>147.61</v>
       </c>
       <c r="E8" t="n">
-        <v>130.4</v>
+        <v>152.1</v>
       </c>
       <c r="F8" t="n">
-        <v>63.89</v>
+        <v>71.87</v>
       </c>
       <c r="G8" t="n">
-        <v>65.84</v>
+        <v>73.3</v>
       </c>
       <c r="H8" t="n">
-        <v>63.81</v>
+        <v>70.38</v>
       </c>
       <c r="I8" t="n">
-        <v>65.3</v>
+        <v>71.34</v>
       </c>
       <c r="J8" t="n">
-        <v>13.61</v>
+        <v>10.02</v>
       </c>
       <c r="K8" t="n">
-        <v>13.89</v>
+        <v>10.88</v>
       </c>
       <c r="L8" t="n">
-        <v>12.87</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>12.98</v>
+        <v>10.6</v>
       </c>
       <c r="N8" t="n">
-        <v>51.36</v>
+        <v>45.41</v>
       </c>
       <c r="O8" t="n">
-        <v>51.45</v>
+        <v>46.36</v>
       </c>
       <c r="P8" t="n">
-        <v>49.79</v>
+        <v>44.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>50.22</v>
+        <v>45.73</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6933</v>
+        <v>-8.2906</v>
       </c>
       <c r="S8" t="n">
-        <v>19.0215</v>
+        <v>19.2474</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6209</v>
+        <v>19.7826</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7699</v>
+        <v>-0.3214</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5074</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>4.3798</v>
+        <v>12.2757</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.406</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>-16.7415</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z8" t="n">
-        <v>-3.9941</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2.7686</v>
+        <v>0.3071</v>
       </c>
       <c r="AB8" t="n">
-        <v>-7.086</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.3429</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132.2</v>
+        <v>163</v>
       </c>
       <c r="C9" t="n">
-        <v>133.67</v>
+        <v>177.5</v>
       </c>
       <c r="D9" t="n">
-        <v>123.8</v>
+        <v>161.51</v>
       </c>
       <c r="E9" t="n">
-        <v>127.55</v>
+        <v>176.94</v>
       </c>
       <c r="F9" t="n">
-        <v>65.44</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>66.05</v>
+        <v>76.31</v>
       </c>
       <c r="H9" t="n">
-        <v>63.78</v>
+        <v>72.7</v>
       </c>
       <c r="I9" t="n">
-        <v>64.91</v>
+        <v>76.28</v>
       </c>
       <c r="J9" t="n">
-        <v>12.8</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>13.64</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>12.65</v>
+        <v>8.84</v>
       </c>
       <c r="M9" t="n">
-        <v>13.26</v>
+        <v>8.85</v>
       </c>
       <c r="N9" t="n">
-        <v>50.12</v>
+        <v>44.82</v>
       </c>
       <c r="O9" t="n">
-        <v>51.43</v>
+        <v>44.89</v>
       </c>
       <c r="P9" t="n">
-        <v>49.65</v>
+        <v>42.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.51</v>
+        <v>42.57</v>
       </c>
       <c r="R9" t="n">
-        <v>-2.1856</v>
+        <v>16.3314</v>
       </c>
       <c r="S9" t="n">
-        <v>8.120699999999999</v>
+        <v>22.7386</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3714</v>
+        <v>35.6902</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5972</v>
+        <v>6.9246</v>
       </c>
       <c r="V9" t="n">
-        <v>4.9305</v>
+        <v>13.1919</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6239</v>
+        <v>16.8147</v>
       </c>
       <c r="X9" t="n">
-        <v>2.1572</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y9" t="n">
-        <v>-7.9167</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z9" t="n">
-        <v>-5.4882</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5775</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4.8417</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.6988</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="C10" t="n">
-        <v>147.26</v>
+        <v>191.29</v>
       </c>
       <c r="D10" t="n">
-        <v>134.02</v>
+        <v>178.94</v>
       </c>
       <c r="E10" t="n">
-        <v>144.16</v>
+        <v>190.42</v>
       </c>
       <c r="F10" t="n">
-        <v>66.37</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>67.77</v>
+        <v>77.36</v>
       </c>
       <c r="H10" t="n">
-        <v>66.25</v>
+        <v>75.55</v>
       </c>
       <c r="I10" t="n">
-        <v>67.39</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>12.5</v>
+        <v>8.65</v>
       </c>
       <c r="K10" t="n">
-        <v>12.59</v>
+        <v>8.77</v>
       </c>
       <c r="L10" t="n">
-        <v>11.21</v>
+        <v>8.15</v>
       </c>
       <c r="M10" t="n">
-        <v>11.51</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>49.4</v>
+        <v>42.74</v>
       </c>
       <c r="O10" t="n">
-        <v>49.49</v>
+        <v>43</v>
       </c>
       <c r="P10" t="n">
-        <v>48.3</v>
+        <v>41.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>48.59</v>
+        <v>42.22</v>
       </c>
       <c r="R10" t="n">
-        <v>13.0223</v>
+        <v>7.6184</v>
       </c>
       <c r="S10" t="n">
-        <v>13.5297</v>
+        <v>14.8146</v>
       </c>
       <c r="T10" t="n">
-        <v>31.5809</v>
+        <v>49.2905</v>
       </c>
       <c r="U10" t="n">
-        <v>3.8207</v>
+        <v>0.8915</v>
       </c>
       <c r="V10" t="n">
-        <v>6.0592</v>
+        <v>7.5311</v>
       </c>
       <c r="W10" t="n">
-        <v>10.9483</v>
+        <v>18.5642</v>
       </c>
       <c r="X10" t="n">
-        <v>-13.1976</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y10" t="n">
-        <v>-13.4586</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z10" t="n">
-        <v>-26.1706</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.8012</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB10" t="n">
-        <v>-5.9245</v>
+        <v>-7.392</v>
       </c>
       <c r="AC10" t="n">
-        <v>-10.1018</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>157.84</v>
+        <v>177.62</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>182.24</v>
       </c>
       <c r="D11" t="n">
-        <v>149.06</v>
+        <v>150.58</v>
       </c>
       <c r="E11" t="n">
-        <v>165.85</v>
+        <v>172.52</v>
       </c>
       <c r="F11" t="n">
-        <v>69.26000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="G11" t="n">
-        <v>71.66</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>68.88</v>
+        <v>71.55</v>
       </c>
       <c r="I11" t="n">
-        <v>71.56999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>10.43</v>
+        <v>8.75</v>
       </c>
       <c r="K11" t="n">
-        <v>11.14</v>
+        <v>9.91</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>9.81</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>47.26</v>
+        <v>43.14</v>
       </c>
       <c r="O11" t="n">
-        <v>47.54</v>
+        <v>45.19</v>
       </c>
       <c r="P11" t="n">
-        <v>45.52</v>
+        <v>42.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>45.59</v>
+        <v>43.31</v>
       </c>
       <c r="R11" t="n">
-        <v>15.0458</v>
+        <v>-9.4003</v>
       </c>
       <c r="S11" t="n">
-        <v>27.1856</v>
+        <v>13.4254</v>
       </c>
       <c r="T11" t="n">
-        <v>40.5866</v>
+        <v>19.6726</v>
       </c>
       <c r="U11" t="n">
-        <v>6.2027</v>
+        <v>-2.5988</v>
       </c>
       <c r="V11" t="n">
-        <v>9.601800000000001</v>
+        <v>5.0743</v>
       </c>
       <c r="W11" t="n">
-        <v>15.6967</v>
+        <v>11.2331</v>
       </c>
       <c r="X11" t="n">
-        <v>-14.7698</v>
+        <v>9.1463</v>
       </c>
       <c r="Y11" t="n">
-        <v>-24.4222</v>
+        <v>-15.566</v>
       </c>
       <c r="Z11" t="n">
-        <v>-31.875</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA11" t="n">
-        <v>-6.1741</v>
+        <v>2.5817</v>
       </c>
       <c r="AB11" t="n">
-        <v>-9.2194</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC11" t="n">
-        <v>-14.1108</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>162.12</v>
+        <v>183.84</v>
       </c>
       <c r="C12" t="n">
-        <v>162.9</v>
+        <v>188.49</v>
       </c>
       <c r="D12" t="n">
-        <v>147.61</v>
+        <v>172.26</v>
       </c>
       <c r="E12" t="n">
-        <v>152.1</v>
+        <v>184.24</v>
       </c>
       <c r="F12" t="n">
-        <v>71.87</v>
+        <v>75.81</v>
       </c>
       <c r="G12" t="n">
-        <v>73.3</v>
+        <v>77.94</v>
       </c>
       <c r="H12" t="n">
-        <v>70.38</v>
+        <v>74.19</v>
       </c>
       <c r="I12" t="n">
-        <v>71.34</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>10.02</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>10.88</v>
+        <v>8.98</v>
       </c>
       <c r="L12" t="n">
-        <v>9.970000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>10.6</v>
+        <v>8.35</v>
       </c>
       <c r="N12" t="n">
-        <v>45.41</v>
+        <v>42.83</v>
       </c>
       <c r="O12" t="n">
-        <v>46.36</v>
+        <v>43.77</v>
       </c>
       <c r="P12" t="n">
-        <v>44.5</v>
+        <v>41.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>45.73</v>
+        <v>41.99</v>
       </c>
       <c r="R12" t="n">
-        <v>-8.2906</v>
+        <v>6.7934</v>
       </c>
       <c r="S12" t="n">
-        <v>19.2474</v>
+        <v>4.1257</v>
       </c>
       <c r="T12" t="n">
-        <v>19.7826</v>
+        <v>11.0883</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3214</v>
+        <v>3.0416</v>
       </c>
       <c r="V12" t="n">
-        <v>9.906000000000001</v>
+        <v>1.2585</v>
       </c>
       <c r="W12" t="n">
-        <v>12.2757</v>
+        <v>7.9223</v>
       </c>
       <c r="X12" t="n">
-        <v>8.053000000000001</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y12" t="n">
-        <v>-20.0603</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z12" t="n">
-        <v>-20.3008</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.3071</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB12" t="n">
-        <v>-9.4635</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC12" t="n">
-        <v>-11.4618</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>163</v>
+        <v>182.67</v>
       </c>
       <c r="C13" t="n">
-        <v>177.5</v>
+        <v>189.56</v>
       </c>
       <c r="D13" t="n">
-        <v>161.51</v>
+        <v>178.28</v>
       </c>
       <c r="E13" t="n">
-        <v>176.94</v>
+        <v>186.19</v>
       </c>
       <c r="F13" t="n">
-        <v>72.81999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>76.31</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>72.7</v>
+        <v>77.16</v>
       </c>
       <c r="I13" t="n">
-        <v>76.28</v>
+        <v>78.95</v>
       </c>
       <c r="J13" t="n">
-        <v>9.859999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="K13" t="n">
-        <v>9.970000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>8.84</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>8.85</v>
+        <v>8.27</v>
       </c>
       <c r="N13" t="n">
-        <v>44.82</v>
+        <v>41.98</v>
       </c>
       <c r="O13" t="n">
-        <v>44.89</v>
+        <v>42.06</v>
       </c>
       <c r="P13" t="n">
-        <v>42.57</v>
+        <v>40.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.57</v>
+        <v>41.07</v>
       </c>
       <c r="R13" t="n">
-        <v>16.3314</v>
+        <v>1.0584</v>
       </c>
       <c r="S13" t="n">
-        <v>22.7386</v>
+        <v>-2.2214</v>
       </c>
       <c r="T13" t="n">
-        <v>35.6902</v>
+        <v>22.4129</v>
       </c>
       <c r="U13" t="n">
-        <v>6.9246</v>
+        <v>2.2139</v>
       </c>
       <c r="V13" t="n">
-        <v>13.1919</v>
+        <v>2.5858</v>
       </c>
       <c r="W13" t="n">
-        <v>16.8147</v>
+        <v>10.6672</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.5094</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y13" t="n">
-        <v>-23.1103</v>
+        <v>0.8537</v>
       </c>
       <c r="Z13" t="n">
-        <v>-31.8182</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA13" t="n">
-        <v>-6.9101</v>
+        <v>-2.191</v>
       </c>
       <c r="AB13" t="n">
-        <v>-12.3894</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC13" t="n">
-        <v>-15.233</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C14" t="n">
-        <v>191.29</v>
+        <v>174.4</v>
       </c>
       <c r="D14" t="n">
-        <v>178.94</v>
+        <v>161.14</v>
       </c>
       <c r="E14" t="n">
-        <v>190.42</v>
+        <v>164.18</v>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>75.73</v>
       </c>
       <c r="G14" t="n">
-        <v>77.36</v>
+        <v>77.37</v>
       </c>
       <c r="H14" t="n">
-        <v>75.55</v>
+        <v>74.23</v>
       </c>
       <c r="I14" t="n">
-        <v>76.95999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="J14" t="n">
-        <v>8.65</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>8.77</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>8.15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="N14" t="n">
-        <v>42.74</v>
+        <v>42.77</v>
       </c>
       <c r="O14" t="n">
-        <v>43</v>
+        <v>43.57</v>
       </c>
       <c r="P14" t="n">
-        <v>41.99</v>
+        <v>41.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>42.22</v>
+        <v>42.98</v>
       </c>
       <c r="R14" t="n">
-        <v>7.6184</v>
+        <v>-11.8213</v>
       </c>
       <c r="S14" t="n">
-        <v>14.8146</v>
+        <v>-4.8342</v>
       </c>
       <c r="T14" t="n">
-        <v>49.2905</v>
+        <v>-7.2115</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8915</v>
+        <v>-4.5725</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5311</v>
+        <v>0.5069</v>
       </c>
       <c r="W14" t="n">
-        <v>18.5642</v>
+        <v>-1.2323</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.3446</v>
+        <v>11.6082</v>
       </c>
       <c r="Y14" t="n">
-        <v>-16.4118</v>
+        <v>3.1285</v>
       </c>
       <c r="Z14" t="n">
-        <v>-38.1599</v>
+        <v>4.2938</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.8222</v>
+        <v>4.6506</v>
       </c>
       <c r="AB14" t="n">
-        <v>-7.392</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC14" t="n">
-        <v>-16.4126</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>177.62</v>
+        <v>172.95</v>
       </c>
       <c r="C15" t="n">
-        <v>182.24</v>
+        <v>174.61</v>
       </c>
       <c r="D15" t="n">
-        <v>150.58</v>
+        <v>142.69</v>
       </c>
       <c r="E15" t="n">
-        <v>172.52</v>
+        <v>151.75</v>
       </c>
       <c r="F15" t="n">
-        <v>75.3</v>
+        <v>76.13</v>
       </c>
       <c r="G15" t="n">
-        <v>75.93000000000001</v>
+        <v>76.27</v>
       </c>
       <c r="H15" t="n">
-        <v>71.55</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>74.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>8.75</v>
+        <v>8.77</v>
       </c>
       <c r="K15" t="n">
-        <v>9.91</v>
+        <v>10.47</v>
       </c>
       <c r="L15" t="n">
-        <v>8.550000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M15" t="n">
-        <v>8.949999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>43.14</v>
+        <v>42.51</v>
       </c>
       <c r="O15" t="n">
-        <v>45.19</v>
+        <v>44.82</v>
       </c>
       <c r="P15" t="n">
-        <v>42.79</v>
+        <v>42.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>43.31</v>
+        <v>43.54</v>
       </c>
       <c r="R15" t="n">
-        <v>-9.4003</v>
+        <v>-7.571</v>
       </c>
       <c r="S15" t="n">
-        <v>13.4254</v>
+        <v>-17.6346</v>
       </c>
       <c r="T15" t="n">
-        <v>19.6726</v>
+        <v>-20.3077</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.5988</v>
+        <v>-1.3539</v>
       </c>
       <c r="V15" t="n">
-        <v>5.0743</v>
+        <v>-3.7804</v>
       </c>
       <c r="W15" t="n">
-        <v>11.2331</v>
+        <v>-3.4304</v>
       </c>
       <c r="X15" t="n">
-        <v>9.1463</v>
+        <v>7.8007</v>
       </c>
       <c r="Y15" t="n">
-        <v>-15.566</v>
+        <v>19.1617</v>
       </c>
       <c r="Z15" t="n">
-        <v>-22.2415</v>
+        <v>21.3415</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.5817</v>
+        <v>1.3029</v>
       </c>
       <c r="AB15" t="n">
-        <v>-5.2919</v>
+        <v>3.6914</v>
       </c>
       <c r="AC15" t="n">
-        <v>-10.8664</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>183.84</v>
+        <v>141.24</v>
       </c>
       <c r="C16" t="n">
-        <v>188.49</v>
+        <v>160.6</v>
       </c>
       <c r="D16" t="n">
-        <v>172.26</v>
+        <v>135.02</v>
       </c>
       <c r="E16" t="n">
-        <v>184.24</v>
+        <v>151.89</v>
       </c>
       <c r="F16" t="n">
-        <v>75.81</v>
+        <v>72.41</v>
       </c>
       <c r="G16" t="n">
-        <v>77.94</v>
+        <v>74.5</v>
       </c>
       <c r="H16" t="n">
-        <v>74.19</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>77.23999999999999</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>8.380000000000001</v>
+        <v>10.64</v>
       </c>
       <c r="K16" t="n">
-        <v>8.98</v>
+        <v>11.07</v>
       </c>
       <c r="L16" t="n">
-        <v>8.140000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>8.35</v>
+        <v>9.93</v>
       </c>
       <c r="N16" t="n">
-        <v>42.83</v>
+        <v>44.68</v>
       </c>
       <c r="O16" t="n">
-        <v>43.77</v>
+        <v>45.53</v>
       </c>
       <c r="P16" t="n">
-        <v>41.6</v>
+        <v>43.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.99</v>
+        <v>44.37</v>
       </c>
       <c r="R16" t="n">
-        <v>6.7934</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1257</v>
+        <v>-18.422</v>
       </c>
       <c r="T16" t="n">
-        <v>11.0883</v>
+        <v>-11.958</v>
       </c>
       <c r="U16" t="n">
-        <v>3.0416</v>
+        <v>-1.8703</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2585</v>
+        <v>-7.6251</v>
       </c>
       <c r="W16" t="n">
-        <v>7.9223</v>
+        <v>-2.7081</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.7039</v>
+        <v>-0.201</v>
       </c>
       <c r="Y16" t="n">
-        <v>-5.6497</v>
+        <v>20.0726</v>
       </c>
       <c r="Z16" t="n">
-        <v>-14.8828</v>
+        <v>10.9497</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.0478</v>
+        <v>1.9063</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.3625</v>
+        <v>8.0351</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.8965</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>182.67</v>
+        <v>161</v>
       </c>
       <c r="C17" t="n">
-        <v>189.56</v>
+        <v>173.7</v>
       </c>
       <c r="D17" t="n">
-        <v>178.28</v>
+        <v>161</v>
       </c>
       <c r="E17" t="n">
-        <v>186.19</v>
+        <v>173.2</v>
       </c>
       <c r="F17" t="n">
-        <v>77.29000000000001</v>
+        <v>74.09</v>
       </c>
       <c r="G17" t="n">
-        <v>79.68000000000001</v>
+        <v>76.53</v>
       </c>
       <c r="H17" t="n">
-        <v>77.16</v>
+        <v>73.62</v>
       </c>
       <c r="I17" t="n">
-        <v>78.95</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>8.43</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>8.630000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="L17" t="n">
-        <v>8.119999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M17" t="n">
-        <v>8.27</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>41.98</v>
+        <v>43.67</v>
       </c>
       <c r="O17" t="n">
-        <v>42.06</v>
+        <v>43.97</v>
       </c>
       <c r="P17" t="n">
-        <v>40.68</v>
+        <v>42.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.07</v>
+        <v>42.19</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0584</v>
+        <v>14.0299</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2214</v>
+        <v>5.494</v>
       </c>
       <c r="T17" t="n">
-        <v>22.4129</v>
+        <v>-5.9922</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2139</v>
+        <v>4.9088</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5858</v>
+        <v>1.553</v>
       </c>
       <c r="W17" t="n">
-        <v>10.6672</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9581</v>
+        <v>-13.998</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.8537</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z17" t="n">
-        <v>-21.9811</v>
+        <v>2.2754</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.191</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.7238</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC17" t="n">
-        <v>-10.1902</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>167</v>
+        <v>171.26</v>
       </c>
       <c r="C18" t="n">
-        <v>174.4</v>
+        <v>179.97</v>
       </c>
       <c r="D18" t="n">
-        <v>161.14</v>
+        <v>168.23</v>
       </c>
       <c r="E18" t="n">
-        <v>164.18</v>
+        <v>178.39</v>
       </c>
       <c r="F18" t="n">
-        <v>75.73</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>77.37</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>74.23</v>
+        <v>74.47</v>
       </c>
       <c r="I18" t="n">
-        <v>75.34</v>
+        <v>76.95</v>
       </c>
       <c r="J18" t="n">
-        <v>9.130000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="K18" t="n">
-        <v>9.390000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>9.23</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>42.77</v>
+        <v>42.94</v>
       </c>
       <c r="O18" t="n">
-        <v>43.57</v>
+        <v>43.33</v>
       </c>
       <c r="P18" t="n">
-        <v>41.93</v>
+        <v>41.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>42.98</v>
+        <v>41.96</v>
       </c>
       <c r="R18" t="n">
-        <v>-11.8213</v>
+        <v>2.9965</v>
       </c>
       <c r="S18" t="n">
-        <v>-4.8342</v>
+        <v>17.5552</v>
       </c>
       <c r="T18" t="n">
-        <v>-7.2115</v>
+        <v>-4.1893</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.5725</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5069</v>
+        <v>3.5388</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.2323</v>
+        <v>-2.5332</v>
       </c>
       <c r="X18" t="n">
-        <v>11.6082</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.1285</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2938</v>
+        <v>0.2418</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.6506</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.7619</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.9631</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>172.95</v>
+        <v>184.8</v>
       </c>
       <c r="C19" t="n">
-        <v>174.61</v>
+        <v>195.27</v>
       </c>
       <c r="D19" t="n">
-        <v>142.69</v>
+        <v>183.34</v>
       </c>
       <c r="E19" t="n">
-        <v>151.75</v>
+        <v>190.56</v>
       </c>
       <c r="F19" t="n">
-        <v>76.13</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>76.27</v>
+        <v>79.33</v>
       </c>
       <c r="H19" t="n">
-        <v>72.09999999999999</v>
+        <v>77.33</v>
       </c>
       <c r="I19" t="n">
-        <v>74.31999999999999</v>
+        <v>77.84</v>
       </c>
       <c r="J19" t="n">
-        <v>8.77</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>10.47</v>
+        <v>8.06</v>
       </c>
       <c r="L19" t="n">
-        <v>8.68</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>9.949999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="N19" t="n">
-        <v>42.51</v>
+        <v>41.4</v>
       </c>
       <c r="O19" t="n">
-        <v>44.82</v>
+        <v>41.78</v>
       </c>
       <c r="P19" t="n">
-        <v>42.44</v>
+        <v>40.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>43.54</v>
+        <v>41.5</v>
       </c>
       <c r="R19" t="n">
-        <v>-7.571</v>
+        <v>6.8221</v>
       </c>
       <c r="S19" t="n">
-        <v>-17.6346</v>
+        <v>25.4592</v>
       </c>
       <c r="T19" t="n">
-        <v>-20.3077</v>
+        <v>16.0677</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3539</v>
+        <v>1.1566</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.7804</v>
+        <v>6.7325</v>
       </c>
       <c r="W19" t="n">
-        <v>-3.4304</v>
+        <v>3.3183</v>
       </c>
       <c r="X19" t="n">
-        <v>7.8007</v>
+        <v>-6.7551</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.1617</v>
+        <v>-22.1551</v>
       </c>
       <c r="Z19" t="n">
-        <v>21.3415</v>
+        <v>-16.2514</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.3029</v>
+        <v>-1.0963</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.6914</v>
+        <v>-6.4683</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1265</v>
+        <v>-3.4435</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>141.24</v>
+        <v>211.38</v>
       </c>
       <c r="C20" t="n">
-        <v>160.6</v>
+        <v>228.5</v>
       </c>
       <c r="D20" t="n">
-        <v>135.02</v>
+        <v>209.89</v>
       </c>
       <c r="E20" t="n">
-        <v>151.89</v>
+        <v>225.79</v>
       </c>
       <c r="F20" t="n">
-        <v>72.41</v>
+        <v>80.59</v>
       </c>
       <c r="G20" t="n">
-        <v>74.5</v>
+        <v>82.27</v>
       </c>
       <c r="H20" t="n">
-        <v>70.95999999999999</v>
+        <v>79.98</v>
       </c>
       <c r="I20" t="n">
-        <v>72.93000000000001</v>
+        <v>81.95</v>
       </c>
       <c r="J20" t="n">
-        <v>10.64</v>
+        <v>6.9</v>
       </c>
       <c r="K20" t="n">
-        <v>11.07</v>
+        <v>6.95</v>
       </c>
       <c r="L20" t="n">
-        <v>9.369999999999999</v>
+        <v>6.19</v>
       </c>
       <c r="M20" t="n">
-        <v>9.93</v>
+        <v>6.29</v>
       </c>
       <c r="N20" t="n">
-        <v>44.68</v>
+        <v>40.05</v>
       </c>
       <c r="O20" t="n">
-        <v>45.53</v>
+        <v>40.35</v>
       </c>
       <c r="P20" t="n">
-        <v>43.46</v>
+        <v>39.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>44.37</v>
+        <v>39.28</v>
       </c>
       <c r="R20" t="n">
-        <v>0.09229999999999999</v>
+        <v>18.4876</v>
       </c>
       <c r="S20" t="n">
-        <v>-18.422</v>
+        <v>30.3637</v>
       </c>
       <c r="T20" t="n">
-        <v>-11.958</v>
+        <v>48.7908</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8703</v>
+        <v>5.2801</v>
       </c>
       <c r="V20" t="n">
-        <v>-7.6251</v>
+        <v>7.1102</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.7081</v>
+        <v>10.2664</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.201</v>
+        <v>-18.6287</v>
       </c>
       <c r="Y20" t="n">
-        <v>20.0726</v>
+        <v>-26.3466</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.9497</v>
+        <v>-36.7839</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9063</v>
+        <v>-5.3494</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.0351</v>
+        <v>-6.8974</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4475</v>
+        <v>-9.7841</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>161</v>
+        <v>242.66</v>
       </c>
       <c r="C21" t="n">
-        <v>173.7</v>
+        <v>242.66</v>
       </c>
       <c r="D21" t="n">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="E21" t="n">
-        <v>173.2</v>
+        <v>217.98</v>
       </c>
       <c r="F21" t="n">
-        <v>74.09</v>
+        <v>82.87</v>
       </c>
       <c r="G21" t="n">
-        <v>76.53</v>
+        <v>82.91</v>
       </c>
       <c r="H21" t="n">
-        <v>73.62</v>
+        <v>80.33</v>
       </c>
       <c r="I21" t="n">
-        <v>76.51000000000001</v>
+        <v>81.67</v>
       </c>
       <c r="J21" t="n">
-        <v>9.300000000000001</v>
+        <v>5.83</v>
       </c>
       <c r="K21" t="n">
-        <v>9.35</v>
+        <v>6.91</v>
       </c>
       <c r="L21" t="n">
-        <v>8.51</v>
+        <v>5.83</v>
       </c>
       <c r="M21" t="n">
-        <v>8.539999999999999</v>
+        <v>6.53</v>
       </c>
       <c r="N21" t="n">
-        <v>43.67</v>
+        <v>38.87</v>
       </c>
       <c r="O21" t="n">
-        <v>43.97</v>
+        <v>40.09</v>
       </c>
       <c r="P21" t="n">
-        <v>42.19</v>
+        <v>38.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.19</v>
+        <v>39.44</v>
       </c>
       <c r="R21" t="n">
-        <v>14.0299</v>
+        <v>-3.459</v>
       </c>
       <c r="S21" t="n">
-        <v>5.494</v>
+        <v>22.1929</v>
       </c>
       <c r="T21" t="n">
-        <v>-5.9922</v>
+        <v>43.5118</v>
       </c>
       <c r="U21" t="n">
-        <v>4.9088</v>
+        <v>-0.3417</v>
       </c>
       <c r="V21" t="n">
-        <v>1.553</v>
+        <v>6.1339</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.9451000000000001</v>
+        <v>11.9841</v>
       </c>
       <c r="X21" t="n">
-        <v>-13.998</v>
+        <v>3.8156</v>
       </c>
       <c r="Y21" t="n">
-        <v>-7.4756</v>
+        <v>-21.2304</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2754</v>
+        <v>-34.2397</v>
       </c>
       <c r="AA21" t="n">
-        <v>-4.9132</v>
+        <v>0.4073</v>
       </c>
       <c r="AB21" t="n">
-        <v>-1.8381</v>
+        <v>-6.0057</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.4763</v>
+        <v>-11.1111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>171.26</v>
+        <v>219</v>
       </c>
       <c r="C22" t="n">
-        <v>179.97</v>
+        <v>231.89</v>
       </c>
       <c r="D22" t="n">
-        <v>168.23</v>
+        <v>207.61</v>
       </c>
       <c r="E22" t="n">
-        <v>178.39</v>
+        <v>224.63</v>
       </c>
       <c r="F22" t="n">
-        <v>75.18000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="G22" t="n">
-        <v>77.79000000000001</v>
+        <v>84.05</v>
       </c>
       <c r="H22" t="n">
-        <v>74.47</v>
+        <v>80.66</v>
       </c>
       <c r="I22" t="n">
-        <v>76.95</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>8.65</v>
+        <v>6.49</v>
       </c>
       <c r="K22" t="n">
-        <v>8.779999999999999</v>
+        <v>6.83</v>
       </c>
       <c r="L22" t="n">
-        <v>8.210000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="M22" t="n">
-        <v>8.289999999999999</v>
+        <v>6.31</v>
       </c>
       <c r="N22" t="n">
-        <v>42.94</v>
+        <v>39.41</v>
       </c>
       <c r="O22" t="n">
-        <v>43.33</v>
+        <v>39.94</v>
       </c>
       <c r="P22" t="n">
-        <v>41.5</v>
+        <v>38.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>41.96</v>
+        <v>38.47</v>
       </c>
       <c r="R22" t="n">
-        <v>2.9965</v>
+        <v>3.0507</v>
       </c>
       <c r="S22" t="n">
-        <v>17.5552</v>
+        <v>17.8789</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.1893</v>
+        <v>29.694</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5750999999999999</v>
+        <v>2.4611</v>
       </c>
       <c r="V22" t="n">
-        <v>3.5388</v>
+        <v>7.5026</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.5332</v>
+        <v>9.3713</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.9274</v>
+        <v>-3.3691</v>
       </c>
       <c r="Y22" t="n">
-        <v>-16.6834</v>
+        <v>-18.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.2418</v>
+        <v>-26.1124</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.5452</v>
+        <v>-2.4594</v>
       </c>
       <c r="AB22" t="n">
-        <v>-3.6288</v>
+        <v>-7.3012</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.167</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>184.8</v>
-      </c>
-      <c r="C23" t="n">
-        <v>195.255</v>
-      </c>
-      <c r="D23" t="n">
-        <v>183.34</v>
-      </c>
-      <c r="E23" t="n">
-        <v>190.56</v>
-      </c>
-      <c r="F23" t="n">
-        <v>78.01000000000001</v>
-      </c>
-      <c r="G23" t="n">
-        <v>79.33</v>
-      </c>
-      <c r="H23" t="n">
-        <v>77.33199999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>77.84</v>
-      </c>
-      <c r="J23" t="n">
-        <v>8</v>
-      </c>
-      <c r="K23" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="N23" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="O23" t="n">
-        <v>41.78</v>
-      </c>
-      <c r="P23" t="n">
-        <v>40.68</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6.8221</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25.4592</v>
-      </c>
-      <c r="T23" t="n">
-        <v>16.0677</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.1566</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.7325</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.3183</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-6.7551</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>-22.1551</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-16.2514</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-1.0963</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-6.4683</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-3.4435</v>
+        <v>-8.817299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>114.76</v>
+        <v>122.81</v>
       </c>
       <c r="C2" t="n">
-        <v>118.32</v>
+        <v>127.45</v>
       </c>
       <c r="D2" t="n">
-        <v>112.3</v>
+        <v>117.5</v>
       </c>
       <c r="E2" t="n">
-        <v>117.97</v>
+        <v>126.98</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>62.89</v>
       </c>
       <c r="G2" t="n">
-        <v>61.87</v>
+        <v>63.8</v>
       </c>
       <c r="H2" t="n">
-        <v>60.45</v>
+        <v>60.7</v>
       </c>
       <c r="I2" t="n">
-        <v>61.86</v>
+        <v>63.54</v>
       </c>
       <c r="J2" t="n">
-        <v>14.91</v>
+        <v>13.84</v>
       </c>
       <c r="K2" t="n">
-        <v>15.24</v>
+        <v>14.49</v>
       </c>
       <c r="L2" t="n">
-        <v>14.38</v>
+        <v>13.25</v>
       </c>
       <c r="M2" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="N2" t="n">
-        <v>53.84</v>
+        <v>52.21</v>
       </c>
       <c r="O2" t="n">
-        <v>54.33</v>
+        <v>54.09</v>
       </c>
       <c r="P2" t="n">
-        <v>53.06</v>
+        <v>51.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>53.08</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>122.81</v>
+        <v>124.39</v>
       </c>
       <c r="C3" t="n">
-        <v>127.45</v>
+        <v>131.38</v>
       </c>
       <c r="D3" t="n">
-        <v>117.5</v>
+        <v>121.66</v>
       </c>
       <c r="E3" t="n">
-        <v>126.98</v>
+        <v>130.4</v>
       </c>
       <c r="F3" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="G3" t="n">
-        <v>63.8</v>
+        <v>65.84</v>
       </c>
       <c r="H3" t="n">
-        <v>60.7</v>
+        <v>63.81</v>
       </c>
       <c r="I3" t="n">
-        <v>63.54</v>
+        <v>65.3</v>
       </c>
       <c r="J3" t="n">
-        <v>13.84</v>
+        <v>13.61</v>
       </c>
       <c r="K3" t="n">
-        <v>14.49</v>
+        <v>13.89</v>
       </c>
       <c r="L3" t="n">
-        <v>13.25</v>
+        <v>12.87</v>
       </c>
       <c r="M3" t="n">
-        <v>13.3</v>
+        <v>12.98</v>
       </c>
       <c r="N3" t="n">
-        <v>52.21</v>
+        <v>51.36</v>
       </c>
       <c r="O3" t="n">
-        <v>54.09</v>
+        <v>51.45</v>
       </c>
       <c r="P3" t="n">
-        <v>51.4</v>
+        <v>49.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>51.65</v>
+        <v>50.22</v>
       </c>
       <c r="R3" t="n">
-        <v>7.6375</v>
+        <v>2.6933</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7158</v>
+        <v>2.7699</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.6389</v>
+        <v>-2.406</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2.694</v>
+        <v>-2.7686</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>124.39</v>
+        <v>132.2</v>
       </c>
       <c r="C4" t="n">
-        <v>131.38</v>
+        <v>133.67</v>
       </c>
       <c r="D4" t="n">
-        <v>121.66</v>
+        <v>123.8</v>
       </c>
       <c r="E4" t="n">
-        <v>130.4</v>
+        <v>127.55</v>
       </c>
       <c r="F4" t="n">
-        <v>63.89</v>
+        <v>65.44</v>
       </c>
       <c r="G4" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="H4" t="n">
-        <v>63.81</v>
+        <v>63.78</v>
       </c>
       <c r="I4" t="n">
-        <v>65.3</v>
+        <v>64.91</v>
       </c>
       <c r="J4" t="n">
-        <v>13.61</v>
+        <v>12.8</v>
       </c>
       <c r="K4" t="n">
-        <v>13.89</v>
+        <v>13.64</v>
       </c>
       <c r="L4" t="n">
-        <v>12.87</v>
+        <v>12.65</v>
       </c>
       <c r="M4" t="n">
-        <v>12.98</v>
+        <v>13.26</v>
       </c>
       <c r="N4" t="n">
-        <v>51.36</v>
+        <v>50.12</v>
       </c>
       <c r="O4" t="n">
-        <v>51.45</v>
+        <v>51.43</v>
       </c>
       <c r="P4" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>50.22</v>
+        <v>50.51</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6933</v>
+        <v>-2.1856</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7699</v>
+        <v>-0.5972</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.406</v>
+        <v>2.1572</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2.7686</v>
+        <v>0.5775</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C5" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D5" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E5" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F5" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G5" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H5" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I5" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J5" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K5" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L5" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M5" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N5" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O5" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P5" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.1856</v>
+        <v>13.0223</v>
       </c>
       <c r="S5" t="n">
-        <v>8.120699999999999</v>
+        <v>13.5297</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5972</v>
+        <v>3.8207</v>
       </c>
       <c r="V5" t="n">
-        <v>4.9305</v>
+        <v>6.0592</v>
       </c>
       <c r="X5" t="n">
-        <v>2.1572</v>
+        <v>-13.1976</v>
       </c>
       <c r="Y5" t="n">
-        <v>-7.9167</v>
+        <v>-13.4586</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5775</v>
+        <v>-3.8012</v>
       </c>
       <c r="AB5" t="n">
-        <v>-4.8417</v>
+        <v>-5.9245</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C6" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D6" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E6" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F6" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H6" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I6" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K6" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L6" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N6" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O6" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P6" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R6" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="S6" t="n">
-        <v>13.5297</v>
+        <v>27.1856</v>
       </c>
       <c r="U6" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="V6" t="n">
-        <v>6.0592</v>
+        <v>9.601800000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="Y6" t="n">
-        <v>-13.4586</v>
+        <v>-24.4222</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
       <c r="AB6" t="n">
-        <v>-5.9245</v>
+        <v>-9.2194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C7" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D7" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E7" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F7" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G7" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H7" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I7" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J7" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K7" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N7" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O7" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P7" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R7" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="S7" t="n">
-        <v>27.1856</v>
+        <v>19.2474</v>
       </c>
       <c r="T7" t="n">
-        <v>40.5866</v>
+        <v>19.7826</v>
       </c>
       <c r="U7" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="V7" t="n">
-        <v>9.601800000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>15.6967</v>
+        <v>12.2757</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>-24.4222</v>
+        <v>-20.0603</v>
       </c>
       <c r="Z7" t="n">
-        <v>-31.875</v>
+        <v>-20.3008</v>
       </c>
       <c r="AA7" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
       <c r="AB7" t="n">
-        <v>-9.2194</v>
+        <v>-9.4635</v>
       </c>
       <c r="AC7" t="n">
-        <v>-14.1108</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C8" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D8" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E8" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F8" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H8" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I8" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J8" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M8" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N8" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O8" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P8" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R8" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S8" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="T8" t="n">
-        <v>19.7826</v>
+        <v>35.6902</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V8" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="W8" t="n">
-        <v>12.2757</v>
+        <v>16.8147</v>
       </c>
       <c r="X8" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y8" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="Z8" t="n">
-        <v>-20.3008</v>
+        <v>-31.8182</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB8" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
       <c r="AC8" t="n">
-        <v>-11.4618</v>
+        <v>-15.233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C9" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D9" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E9" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F9" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H9" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I9" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K9" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L9" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M9" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O9" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P9" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R9" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S9" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="T9" t="n">
-        <v>35.6902</v>
+        <v>49.2905</v>
       </c>
       <c r="U9" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V9" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="W9" t="n">
-        <v>16.8147</v>
+        <v>18.5642</v>
       </c>
       <c r="X9" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y9" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z9" t="n">
-        <v>-31.8182</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA9" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB9" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
       <c r="AC9" t="n">
-        <v>-15.233</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C10" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D10" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E10" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G10" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I10" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K10" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L10" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O10" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P10" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q10" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R10" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S10" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="T10" t="n">
-        <v>49.2905</v>
+        <v>19.6726</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="W10" t="n">
-        <v>18.5642</v>
+        <v>11.2331</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y10" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="Z10" t="n">
-        <v>-38.1599</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB10" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC10" t="n">
-        <v>-16.4126</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C11" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D11" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E11" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F11" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G11" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H11" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I11" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L11" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N11" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O11" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P11" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R11" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S11" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T11" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V11" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W11" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X11" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y11" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z11" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB11" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC11" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>183.84</v>
+        <v>182.67</v>
       </c>
       <c r="C12" t="n">
-        <v>188.49</v>
+        <v>189.56</v>
       </c>
       <c r="D12" t="n">
-        <v>172.26</v>
+        <v>178.28</v>
       </c>
       <c r="E12" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F12" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>74.19</v>
+        <v>77.16</v>
       </c>
       <c r="I12" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J12" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K12" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N12" t="n">
-        <v>42.83</v>
+        <v>41.98</v>
       </c>
       <c r="O12" t="n">
-        <v>43.77</v>
+        <v>42.06</v>
       </c>
       <c r="P12" t="n">
-        <v>41.6</v>
+        <v>40.68</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R12" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T12" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W12" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y12" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z12" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC12" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>182.67</v>
+        <v>167</v>
       </c>
       <c r="C13" t="n">
-        <v>189.56</v>
+        <v>174.4</v>
       </c>
       <c r="D13" t="n">
-        <v>178.28</v>
+        <v>161.14</v>
       </c>
       <c r="E13" t="n">
-        <v>186.19</v>
+        <v>164.18</v>
       </c>
       <c r="F13" t="n">
-        <v>77.29000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G13" t="n">
-        <v>79.68000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="H13" t="n">
-        <v>77.16</v>
+        <v>74.23</v>
       </c>
       <c r="I13" t="n">
-        <v>78.95</v>
+        <v>75.34</v>
       </c>
       <c r="J13" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>8.630000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.27</v>
+        <v>9.23</v>
       </c>
       <c r="N13" t="n">
-        <v>41.98</v>
+        <v>42.77</v>
       </c>
       <c r="O13" t="n">
-        <v>42.06</v>
+        <v>43.57</v>
       </c>
       <c r="P13" t="n">
-        <v>40.68</v>
+        <v>41.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.07</v>
+        <v>42.98</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0584</v>
+        <v>-11.8213</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2214</v>
+        <v>-4.8342</v>
       </c>
       <c r="T13" t="n">
-        <v>22.4129</v>
+        <v>-7.2115</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2139</v>
+        <v>-4.5725</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5858</v>
+        <v>0.5069</v>
       </c>
       <c r="W13" t="n">
-        <v>10.6672</v>
+        <v>-1.2323</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9581</v>
+        <v>11.6082</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.8537</v>
+        <v>3.1285</v>
       </c>
       <c r="Z13" t="n">
-        <v>-21.9811</v>
+        <v>4.2938</v>
       </c>
       <c r="AA13" t="n">
-        <v>-2.191</v>
+        <v>4.6506</v>
       </c>
       <c r="AB13" t="n">
-        <v>-2.7238</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC13" t="n">
-        <v>-10.1902</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>167</v>
+        <v>172.95</v>
       </c>
       <c r="C14" t="n">
-        <v>174.4</v>
+        <v>174.61</v>
       </c>
       <c r="D14" t="n">
-        <v>161.14</v>
+        <v>142.69</v>
       </c>
       <c r="E14" t="n">
-        <v>164.18</v>
+        <v>151.75</v>
       </c>
       <c r="F14" t="n">
-        <v>75.73</v>
+        <v>76.13</v>
       </c>
       <c r="G14" t="n">
-        <v>77.37</v>
+        <v>76.27</v>
       </c>
       <c r="H14" t="n">
-        <v>74.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>75.34</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K14" t="n">
-        <v>9.390000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M14" t="n">
-        <v>9.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>42.77</v>
+        <v>42.51</v>
       </c>
       <c r="O14" t="n">
-        <v>43.57</v>
+        <v>44.82</v>
       </c>
       <c r="P14" t="n">
-        <v>41.93</v>
+        <v>42.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>42.98</v>
+        <v>43.54</v>
       </c>
       <c r="R14" t="n">
-        <v>-11.8213</v>
+        <v>-7.571</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.8342</v>
+        <v>-17.6346</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.2115</v>
+        <v>-20.3077</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.5725</v>
+        <v>-1.3539</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5069</v>
+        <v>-3.7804</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.2323</v>
+        <v>-3.4304</v>
       </c>
       <c r="X14" t="n">
-        <v>11.6082</v>
+        <v>7.8007</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.1285</v>
+        <v>19.1617</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2938</v>
+        <v>21.3415</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.6506</v>
+        <v>1.3029</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.7619</v>
+        <v>3.6914</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.9631</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>172.95</v>
+        <v>141.24</v>
       </c>
       <c r="C15" t="n">
-        <v>174.61</v>
+        <v>160.6</v>
       </c>
       <c r="D15" t="n">
-        <v>142.69</v>
+        <v>135.02</v>
       </c>
       <c r="E15" t="n">
-        <v>151.75</v>
+        <v>151.89</v>
       </c>
       <c r="F15" t="n">
-        <v>76.13</v>
+        <v>72.41</v>
       </c>
       <c r="G15" t="n">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="H15" t="n">
-        <v>72.09999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>74.31999999999999</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>8.77</v>
+        <v>10.64</v>
       </c>
       <c r="K15" t="n">
-        <v>10.47</v>
+        <v>11.07</v>
       </c>
       <c r="L15" t="n">
-        <v>8.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="N15" t="n">
-        <v>42.51</v>
+        <v>44.68</v>
       </c>
       <c r="O15" t="n">
-        <v>44.82</v>
+        <v>45.53</v>
       </c>
       <c r="P15" t="n">
-        <v>42.44</v>
+        <v>43.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>43.54</v>
+        <v>44.37</v>
       </c>
       <c r="R15" t="n">
-        <v>-7.571</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-17.6346</v>
+        <v>-18.422</v>
       </c>
       <c r="T15" t="n">
-        <v>-20.3077</v>
+        <v>-11.958</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3539</v>
+        <v>-1.8703</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.7804</v>
+        <v>-7.6251</v>
       </c>
       <c r="W15" t="n">
-        <v>-3.4304</v>
+        <v>-2.7081</v>
       </c>
       <c r="X15" t="n">
-        <v>7.8007</v>
+        <v>-0.201</v>
       </c>
       <c r="Y15" t="n">
-        <v>19.1617</v>
+        <v>20.0726</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3415</v>
+        <v>10.9497</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3029</v>
+        <v>1.9063</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.6914</v>
+        <v>8.0351</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1265</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>141.24</v>
+        <v>161</v>
       </c>
       <c r="C16" t="n">
-        <v>160.6</v>
+        <v>173.7</v>
       </c>
       <c r="D16" t="n">
-        <v>135.02</v>
+        <v>161</v>
       </c>
       <c r="E16" t="n">
-        <v>151.89</v>
+        <v>173.2</v>
       </c>
       <c r="F16" t="n">
-        <v>72.41</v>
+        <v>74.09</v>
       </c>
       <c r="G16" t="n">
-        <v>74.5</v>
+        <v>76.53</v>
       </c>
       <c r="H16" t="n">
-        <v>70.95999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="I16" t="n">
-        <v>72.93000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>10.64</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>11.07</v>
+        <v>9.35</v>
       </c>
       <c r="L16" t="n">
-        <v>9.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M16" t="n">
-        <v>9.93</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>44.68</v>
+        <v>43.67</v>
       </c>
       <c r="O16" t="n">
-        <v>45.53</v>
+        <v>43.97</v>
       </c>
       <c r="P16" t="n">
-        <v>43.46</v>
+        <v>42.19</v>
       </c>
       <c r="Q16" t="n">
-        <v>44.37</v>
+        <v>42.19</v>
       </c>
       <c r="R16" t="n">
-        <v>0.09229999999999999</v>
+        <v>14.0299</v>
       </c>
       <c r="S16" t="n">
-        <v>-18.422</v>
+        <v>5.494</v>
       </c>
       <c r="T16" t="n">
-        <v>-11.958</v>
+        <v>-5.9922</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.8703</v>
+        <v>4.9088</v>
       </c>
       <c r="V16" t="n">
-        <v>-7.6251</v>
+        <v>1.553</v>
       </c>
       <c r="W16" t="n">
-        <v>-2.7081</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.201</v>
+        <v>-13.998</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.0726</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z16" t="n">
-        <v>10.9497</v>
+        <v>2.2754</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9063</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.0351</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4475</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>161</v>
+        <v>171.26</v>
       </c>
       <c r="C17" t="n">
-        <v>173.7</v>
+        <v>179.97</v>
       </c>
       <c r="D17" t="n">
-        <v>161</v>
+        <v>168.23</v>
       </c>
       <c r="E17" t="n">
-        <v>173.2</v>
+        <v>178.39</v>
       </c>
       <c r="F17" t="n">
-        <v>74.09</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>73.62</v>
+        <v>74.47</v>
       </c>
       <c r="I17" t="n">
-        <v>76.51000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="J17" t="n">
-        <v>9.300000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="K17" t="n">
-        <v>9.35</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>8.51</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>8.539999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>43.67</v>
+        <v>42.94</v>
       </c>
       <c r="O17" t="n">
-        <v>43.97</v>
+        <v>43.33</v>
       </c>
       <c r="P17" t="n">
-        <v>42.19</v>
+        <v>41.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>42.19</v>
+        <v>41.96</v>
       </c>
       <c r="R17" t="n">
-        <v>14.0299</v>
+        <v>2.9965</v>
       </c>
       <c r="S17" t="n">
-        <v>5.494</v>
+        <v>17.5552</v>
       </c>
       <c r="T17" t="n">
-        <v>-5.9922</v>
+        <v>-4.1893</v>
       </c>
       <c r="U17" t="n">
-        <v>4.9088</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>1.553</v>
+        <v>3.5388</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-2.5332</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.998</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y17" t="n">
-        <v>-7.4756</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.2754</v>
+        <v>0.2418</v>
       </c>
       <c r="AA17" t="n">
-        <v>-4.9132</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.8381</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4763</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>171.26</v>
+        <v>184.8</v>
       </c>
       <c r="C18" t="n">
-        <v>179.97</v>
+        <v>195.27</v>
       </c>
       <c r="D18" t="n">
-        <v>168.23</v>
+        <v>183.34</v>
       </c>
       <c r="E18" t="n">
-        <v>178.39</v>
+        <v>190.56</v>
       </c>
       <c r="F18" t="n">
-        <v>75.18000000000001</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>77.79000000000001</v>
+        <v>79.33</v>
       </c>
       <c r="H18" t="n">
-        <v>74.47</v>
+        <v>77.33</v>
       </c>
       <c r="I18" t="n">
-        <v>76.95</v>
+        <v>77.84</v>
       </c>
       <c r="J18" t="n">
-        <v>8.65</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>8.779999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="L18" t="n">
-        <v>8.210000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>8.289999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="N18" t="n">
-        <v>42.94</v>
+        <v>41.4</v>
       </c>
       <c r="O18" t="n">
-        <v>43.33</v>
+        <v>41.78</v>
       </c>
       <c r="P18" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="Q18" t="n">
         <v>41.5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>41.96</v>
-      </c>
       <c r="R18" t="n">
-        <v>2.9965</v>
+        <v>6.8221</v>
       </c>
       <c r="S18" t="n">
-        <v>17.5552</v>
+        <v>25.4592</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.1893</v>
+        <v>16.0677</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5750999999999999</v>
+        <v>1.1566</v>
       </c>
       <c r="V18" t="n">
-        <v>3.5388</v>
+        <v>6.7325</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.5332</v>
+        <v>3.3183</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.9274</v>
+        <v>-6.7551</v>
       </c>
       <c r="Y18" t="n">
-        <v>-16.6834</v>
+        <v>-22.1551</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.2418</v>
+        <v>-16.2514</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.5452</v>
+        <v>-1.0963</v>
       </c>
       <c r="AB18" t="n">
-        <v>-3.6288</v>
+        <v>-6.4683</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.167</v>
+        <v>-3.4435</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>184.8</v>
+        <v>211.38</v>
       </c>
       <c r="C19" t="n">
-        <v>195.27</v>
+        <v>228.5</v>
       </c>
       <c r="D19" t="n">
-        <v>183.34</v>
+        <v>209.89</v>
       </c>
       <c r="E19" t="n">
-        <v>190.56</v>
+        <v>225.79</v>
       </c>
       <c r="F19" t="n">
-        <v>78.04000000000001</v>
+        <v>80.59</v>
       </c>
       <c r="G19" t="n">
-        <v>79.33</v>
+        <v>82.27</v>
       </c>
       <c r="H19" t="n">
-        <v>77.33</v>
+        <v>79.98</v>
       </c>
       <c r="I19" t="n">
-        <v>77.84</v>
+        <v>81.95</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="K19" t="n">
-        <v>8.06</v>
+        <v>6.95</v>
       </c>
       <c r="L19" t="n">
-        <v>7.5</v>
+        <v>6.19</v>
       </c>
       <c r="M19" t="n">
-        <v>7.73</v>
+        <v>6.29</v>
       </c>
       <c r="N19" t="n">
-        <v>41.4</v>
+        <v>40.05</v>
       </c>
       <c r="O19" t="n">
-        <v>41.78</v>
+        <v>40.35</v>
       </c>
       <c r="P19" t="n">
-        <v>40.68</v>
+        <v>39.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.5</v>
+        <v>39.28</v>
       </c>
       <c r="R19" t="n">
-        <v>6.8221</v>
+        <v>18.4876</v>
       </c>
       <c r="S19" t="n">
-        <v>25.4592</v>
+        <v>30.3637</v>
       </c>
       <c r="T19" t="n">
-        <v>16.0677</v>
+        <v>48.7908</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1566</v>
+        <v>5.2801</v>
       </c>
       <c r="V19" t="n">
-        <v>6.7325</v>
+        <v>7.1102</v>
       </c>
       <c r="W19" t="n">
-        <v>3.3183</v>
+        <v>10.2664</v>
       </c>
       <c r="X19" t="n">
-        <v>-6.7551</v>
+        <v>-18.6287</v>
       </c>
       <c r="Y19" t="n">
-        <v>-22.1551</v>
+        <v>-26.3466</v>
       </c>
       <c r="Z19" t="n">
-        <v>-16.2514</v>
+        <v>-36.7839</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.0963</v>
+        <v>-5.3494</v>
       </c>
       <c r="AB19" t="n">
-        <v>-6.4683</v>
+        <v>-6.8974</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.4435</v>
+        <v>-9.7841</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>211.38</v>
+        <v>242.66</v>
       </c>
       <c r="C20" t="n">
-        <v>228.5</v>
+        <v>242.66</v>
       </c>
       <c r="D20" t="n">
-        <v>209.89</v>
+        <v>204</v>
       </c>
       <c r="E20" t="n">
-        <v>225.79</v>
+        <v>217.98</v>
       </c>
       <c r="F20" t="n">
-        <v>80.59</v>
+        <v>82.87</v>
       </c>
       <c r="G20" t="n">
-        <v>82.27</v>
+        <v>82.91</v>
       </c>
       <c r="H20" t="n">
-        <v>79.98</v>
+        <v>80.33</v>
       </c>
       <c r="I20" t="n">
-        <v>81.95</v>
+        <v>81.67</v>
       </c>
       <c r="J20" t="n">
-        <v>6.9</v>
+        <v>5.83</v>
       </c>
       <c r="K20" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="L20" t="n">
-        <v>6.19</v>
+        <v>5.83</v>
       </c>
       <c r="M20" t="n">
-        <v>6.29</v>
+        <v>6.53</v>
       </c>
       <c r="N20" t="n">
-        <v>40.05</v>
+        <v>38.87</v>
       </c>
       <c r="O20" t="n">
-        <v>40.35</v>
+        <v>40.09</v>
       </c>
       <c r="P20" t="n">
-        <v>39.14</v>
+        <v>38.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>39.28</v>
+        <v>39.44</v>
       </c>
       <c r="R20" t="n">
-        <v>18.4876</v>
+        <v>-3.459</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3637</v>
+        <v>22.1929</v>
       </c>
       <c r="T20" t="n">
-        <v>48.7908</v>
+        <v>43.5118</v>
       </c>
       <c r="U20" t="n">
-        <v>5.2801</v>
+        <v>-0.3417</v>
       </c>
       <c r="V20" t="n">
-        <v>7.1102</v>
+        <v>6.1339</v>
       </c>
       <c r="W20" t="n">
-        <v>10.2664</v>
+        <v>11.9841</v>
       </c>
       <c r="X20" t="n">
-        <v>-18.6287</v>
+        <v>3.8156</v>
       </c>
       <c r="Y20" t="n">
-        <v>-26.3466</v>
+        <v>-21.2304</v>
       </c>
       <c r="Z20" t="n">
-        <v>-36.7839</v>
+        <v>-34.2397</v>
       </c>
       <c r="AA20" t="n">
-        <v>-5.3494</v>
+        <v>0.4073</v>
       </c>
       <c r="AB20" t="n">
-        <v>-6.8974</v>
+        <v>-6.0057</v>
       </c>
       <c r="AC20" t="n">
-        <v>-9.7841</v>
+        <v>-11.1111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>242.66</v>
+        <v>219</v>
       </c>
       <c r="C21" t="n">
-        <v>242.66</v>
+        <v>231.89</v>
       </c>
       <c r="D21" t="n">
-        <v>204</v>
+        <v>207.56</v>
       </c>
       <c r="E21" t="n">
-        <v>217.98</v>
+        <v>224.63</v>
       </c>
       <c r="F21" t="n">
-        <v>82.87</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>82.91</v>
+        <v>84.05</v>
       </c>
       <c r="H21" t="n">
-        <v>80.33</v>
+        <v>80.66</v>
       </c>
       <c r="I21" t="n">
-        <v>81.67</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>5.83</v>
+        <v>6.49</v>
       </c>
       <c r="K21" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="L21" t="n">
-        <v>5.83</v>
+        <v>6.1</v>
       </c>
       <c r="M21" t="n">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
       <c r="N21" t="n">
-        <v>38.87</v>
+        <v>39.41</v>
       </c>
       <c r="O21" t="n">
-        <v>40.09</v>
+        <v>39.94</v>
       </c>
       <c r="P21" t="n">
-        <v>38.86</v>
+        <v>38.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>39.44</v>
+        <v>38.47</v>
       </c>
       <c r="R21" t="n">
-        <v>-3.459</v>
+        <v>3.0507</v>
       </c>
       <c r="S21" t="n">
-        <v>22.1929</v>
+        <v>17.8789</v>
       </c>
       <c r="T21" t="n">
-        <v>43.5118</v>
+        <v>29.694</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3417</v>
+        <v>2.4611</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1339</v>
+        <v>7.5026</v>
       </c>
       <c r="W21" t="n">
-        <v>11.9841</v>
+        <v>9.3713</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8156</v>
+        <v>-3.3691</v>
       </c>
       <c r="Y21" t="n">
-        <v>-21.2304</v>
+        <v>-18.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>-34.2397</v>
+        <v>-26.1124</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.4073</v>
+        <v>-2.4594</v>
       </c>
       <c r="AB21" t="n">
-        <v>-6.0057</v>
+        <v>-7.3012</v>
       </c>
       <c r="AC21" t="n">
-        <v>-11.1111</v>
+        <v>-8.817299999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>219</v>
+        <v>231.82</v>
       </c>
       <c r="C22" t="n">
-        <v>231.89</v>
+        <v>239.05</v>
       </c>
       <c r="D22" t="n">
-        <v>207.61</v>
+        <v>218.56</v>
       </c>
       <c r="E22" t="n">
-        <v>224.63</v>
+        <v>224.34</v>
       </c>
       <c r="F22" t="n">
-        <v>81.73</v>
+        <v>84.42</v>
       </c>
       <c r="G22" t="n">
-        <v>84.05</v>
+        <v>85.7</v>
       </c>
       <c r="H22" t="n">
-        <v>80.66</v>
+        <v>83.53</v>
       </c>
       <c r="I22" t="n">
-        <v>83.68000000000001</v>
+        <v>84.56</v>
       </c>
       <c r="J22" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="K22" t="n">
         <v>6.49</v>
       </c>
-      <c r="K22" t="n">
-        <v>6.83</v>
-      </c>
       <c r="L22" t="n">
-        <v>6.1</v>
+        <v>5.9107</v>
       </c>
       <c r="M22" t="n">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
       <c r="N22" t="n">
-        <v>39.41</v>
+        <v>38.16</v>
       </c>
       <c r="O22" t="n">
-        <v>39.94</v>
+        <v>38.5599</v>
       </c>
       <c r="P22" t="n">
-        <v>38.3</v>
+        <v>37.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>38.47</v>
+        <v>38.08</v>
       </c>
       <c r="R22" t="n">
-        <v>3.0507</v>
+        <v>-0.1291</v>
       </c>
       <c r="S22" t="n">
-        <v>17.8789</v>
+        <v>-0.6422</v>
       </c>
       <c r="T22" t="n">
-        <v>29.694</v>
+        <v>25.7582</v>
       </c>
       <c r="U22" t="n">
-        <v>2.4611</v>
+        <v>1.0516</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5026</v>
+        <v>3.1849</v>
       </c>
       <c r="W22" t="n">
-        <v>9.3713</v>
+        <v>9.8895</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.3691</v>
+        <v>0.317</v>
       </c>
       <c r="Y22" t="n">
-        <v>-18.37</v>
+        <v>0.6359</v>
       </c>
       <c r="Z22" t="n">
-        <v>-26.1124</v>
+        <v>-23.6429</v>
       </c>
       <c r="AA22" t="n">
-        <v>-2.4594</v>
+        <v>-1.0138</v>
       </c>
       <c r="AB22" t="n">
-        <v>-7.3012</v>
+        <v>-3.055</v>
       </c>
       <c r="AC22" t="n">
-        <v>-8.817299999999999</v>
+        <v>-9.2469</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24759,1804 +24759,1713 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>122.81</v>
+        <v>132.2</v>
       </c>
       <c r="C2" t="n">
-        <v>127.45</v>
+        <v>133.67</v>
       </c>
       <c r="D2" t="n">
-        <v>117.5</v>
+        <v>123.8</v>
       </c>
       <c r="E2" t="n">
-        <v>126.98</v>
+        <v>127.55</v>
       </c>
       <c r="F2" t="n">
-        <v>62.89</v>
+        <v>65.44</v>
       </c>
       <c r="G2" t="n">
-        <v>63.8</v>
+        <v>66.05</v>
       </c>
       <c r="H2" t="n">
-        <v>60.7</v>
+        <v>63.78</v>
       </c>
       <c r="I2" t="n">
-        <v>63.54</v>
+        <v>64.91</v>
       </c>
       <c r="J2" t="n">
-        <v>13.84</v>
+        <v>12.8</v>
       </c>
       <c r="K2" t="n">
-        <v>14.49</v>
+        <v>13.64</v>
       </c>
       <c r="L2" t="n">
-        <v>13.25</v>
+        <v>12.65</v>
       </c>
       <c r="M2" t="n">
-        <v>13.3</v>
+        <v>13.26</v>
       </c>
       <c r="N2" t="n">
-        <v>52.21</v>
+        <v>50.12</v>
       </c>
       <c r="O2" t="n">
-        <v>54.09</v>
+        <v>51.43</v>
       </c>
       <c r="P2" t="n">
-        <v>51.4</v>
+        <v>49.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>51.65</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>124.39</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>131.38</v>
+        <v>147.26</v>
       </c>
       <c r="D3" t="n">
-        <v>121.66</v>
+        <v>134.02</v>
       </c>
       <c r="E3" t="n">
-        <v>130.4</v>
+        <v>144.16</v>
       </c>
       <c r="F3" t="n">
-        <v>63.89</v>
+        <v>66.37</v>
       </c>
       <c r="G3" t="n">
-        <v>65.84</v>
+        <v>67.77</v>
       </c>
       <c r="H3" t="n">
-        <v>63.81</v>
+        <v>66.25</v>
       </c>
       <c r="I3" t="n">
-        <v>65.3</v>
+        <v>67.39</v>
       </c>
       <c r="J3" t="n">
-        <v>13.61</v>
+        <v>12.5</v>
       </c>
       <c r="K3" t="n">
-        <v>13.89</v>
+        <v>12.59</v>
       </c>
       <c r="L3" t="n">
-        <v>12.87</v>
+        <v>11.21</v>
       </c>
       <c r="M3" t="n">
-        <v>12.98</v>
+        <v>11.51</v>
       </c>
       <c r="N3" t="n">
-        <v>51.36</v>
+        <v>49.4</v>
       </c>
       <c r="O3" t="n">
-        <v>51.45</v>
+        <v>49.49</v>
       </c>
       <c r="P3" t="n">
-        <v>49.79</v>
+        <v>48.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>50.22</v>
+        <v>48.59</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6933</v>
+        <v>13.0223</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7699</v>
+        <v>3.8207</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.406</v>
+        <v>-13.1976</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2.7686</v>
+        <v>-3.8012</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>132.2</v>
+        <v>157.84</v>
       </c>
       <c r="C4" t="n">
-        <v>133.67</v>
+        <v>166</v>
       </c>
       <c r="D4" t="n">
-        <v>123.8</v>
+        <v>149.06</v>
       </c>
       <c r="E4" t="n">
-        <v>127.55</v>
+        <v>165.85</v>
       </c>
       <c r="F4" t="n">
-        <v>65.44</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>66.05</v>
+        <v>71.66</v>
       </c>
       <c r="H4" t="n">
-        <v>63.78</v>
+        <v>68.88</v>
       </c>
       <c r="I4" t="n">
-        <v>64.91</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>12.8</v>
+        <v>10.43</v>
       </c>
       <c r="K4" t="n">
-        <v>13.64</v>
+        <v>11.14</v>
       </c>
       <c r="L4" t="n">
-        <v>12.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>13.26</v>
+        <v>9.81</v>
       </c>
       <c r="N4" t="n">
-        <v>50.12</v>
+        <v>47.26</v>
       </c>
       <c r="O4" t="n">
-        <v>51.43</v>
+        <v>47.54</v>
       </c>
       <c r="P4" t="n">
-        <v>49.65</v>
+        <v>45.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>50.51</v>
+        <v>45.59</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.1856</v>
+        <v>15.0458</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5972</v>
+        <v>6.2027</v>
       </c>
       <c r="X4" t="n">
-        <v>2.1572</v>
+        <v>-14.7698</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5775</v>
+        <v>-6.1741</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>135</v>
+        <v>162.12</v>
       </c>
       <c r="C5" t="n">
-        <v>147.26</v>
+        <v>162.9</v>
       </c>
       <c r="D5" t="n">
-        <v>134.02</v>
+        <v>147.61</v>
       </c>
       <c r="E5" t="n">
-        <v>144.16</v>
+        <v>152.1</v>
       </c>
       <c r="F5" t="n">
-        <v>66.37</v>
+        <v>71.87</v>
       </c>
       <c r="G5" t="n">
-        <v>67.77</v>
+        <v>73.3</v>
       </c>
       <c r="H5" t="n">
-        <v>66.25</v>
+        <v>70.38</v>
       </c>
       <c r="I5" t="n">
-        <v>67.39</v>
+        <v>71.34</v>
       </c>
       <c r="J5" t="n">
-        <v>12.5</v>
+        <v>10.02</v>
       </c>
       <c r="K5" t="n">
-        <v>12.59</v>
+        <v>10.88</v>
       </c>
       <c r="L5" t="n">
-        <v>11.21</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>11.51</v>
+        <v>10.6</v>
       </c>
       <c r="N5" t="n">
-        <v>49.4</v>
+        <v>45.41</v>
       </c>
       <c r="O5" t="n">
-        <v>49.49</v>
+        <v>46.36</v>
       </c>
       <c r="P5" t="n">
-        <v>48.3</v>
+        <v>44.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>48.59</v>
+        <v>45.73</v>
       </c>
       <c r="R5" t="n">
-        <v>13.0223</v>
+        <v>-8.2906</v>
       </c>
       <c r="S5" t="n">
-        <v>13.5297</v>
+        <v>19.2474</v>
       </c>
       <c r="U5" t="n">
-        <v>3.8207</v>
+        <v>-0.3214</v>
       </c>
       <c r="V5" t="n">
-        <v>6.0592</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.1976</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>-13.4586</v>
+        <v>-20.0603</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.8012</v>
+        <v>0.3071</v>
       </c>
       <c r="AB5" t="n">
-        <v>-5.9245</v>
+        <v>-9.4635</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>157.84</v>
+        <v>163</v>
       </c>
       <c r="C6" t="n">
-        <v>166</v>
+        <v>177.5</v>
       </c>
       <c r="D6" t="n">
-        <v>149.06</v>
+        <v>161.51</v>
       </c>
       <c r="E6" t="n">
-        <v>165.85</v>
+        <v>176.94</v>
       </c>
       <c r="F6" t="n">
-        <v>69.26000000000001</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>71.66</v>
+        <v>76.31</v>
       </c>
       <c r="H6" t="n">
-        <v>68.88</v>
+        <v>72.7</v>
       </c>
       <c r="I6" t="n">
-        <v>71.56999999999999</v>
+        <v>76.28</v>
       </c>
       <c r="J6" t="n">
-        <v>10.43</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>11.14</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M6" t="n">
-        <v>9.81</v>
+        <v>8.85</v>
       </c>
       <c r="N6" t="n">
-        <v>47.26</v>
+        <v>44.82</v>
       </c>
       <c r="O6" t="n">
-        <v>47.54</v>
+        <v>44.89</v>
       </c>
       <c r="P6" t="n">
-        <v>45.52</v>
+        <v>42.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>45.59</v>
+        <v>42.57</v>
       </c>
       <c r="R6" t="n">
-        <v>15.0458</v>
+        <v>16.3314</v>
       </c>
       <c r="S6" t="n">
-        <v>27.1856</v>
+        <v>22.7386</v>
       </c>
       <c r="U6" t="n">
-        <v>6.2027</v>
+        <v>6.9246</v>
       </c>
       <c r="V6" t="n">
-        <v>9.601800000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="X6" t="n">
-        <v>-14.7698</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y6" t="n">
-        <v>-24.4222</v>
+        <v>-23.1103</v>
       </c>
       <c r="AA6" t="n">
-        <v>-6.1741</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB6" t="n">
-        <v>-9.2194</v>
+        <v>-12.3894</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>162.12</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>162.9</v>
+        <v>191.29</v>
       </c>
       <c r="D7" t="n">
-        <v>147.61</v>
+        <v>178.94</v>
       </c>
       <c r="E7" t="n">
-        <v>152.1</v>
+        <v>190.42</v>
       </c>
       <c r="F7" t="n">
-        <v>71.87</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>73.3</v>
+        <v>77.36</v>
       </c>
       <c r="H7" t="n">
-        <v>70.38</v>
+        <v>75.55</v>
       </c>
       <c r="I7" t="n">
-        <v>71.34</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>10.02</v>
+        <v>8.65</v>
       </c>
       <c r="K7" t="n">
-        <v>10.88</v>
+        <v>8.77</v>
       </c>
       <c r="L7" t="n">
-        <v>9.970000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="M7" t="n">
-        <v>10.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>45.41</v>
+        <v>42.74</v>
       </c>
       <c r="O7" t="n">
-        <v>46.36</v>
+        <v>43</v>
       </c>
       <c r="P7" t="n">
-        <v>44.5</v>
+        <v>41.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>45.73</v>
+        <v>42.22</v>
       </c>
       <c r="R7" t="n">
-        <v>-8.2906</v>
+        <v>7.6184</v>
       </c>
       <c r="S7" t="n">
-        <v>19.2474</v>
+        <v>14.8146</v>
       </c>
       <c r="T7" t="n">
-        <v>19.7826</v>
+        <v>49.2905</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3214</v>
+        <v>0.8915</v>
       </c>
       <c r="V7" t="n">
-        <v>9.906000000000001</v>
+        <v>7.5311</v>
       </c>
       <c r="W7" t="n">
-        <v>12.2757</v>
+        <v>18.5642</v>
       </c>
       <c r="X7" t="n">
-        <v>8.053000000000001</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y7" t="n">
-        <v>-20.0603</v>
+        <v>-16.4118</v>
       </c>
       <c r="Z7" t="n">
-        <v>-20.3008</v>
+        <v>-38.1599</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3071</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB7" t="n">
-        <v>-9.4635</v>
+        <v>-7.392</v>
       </c>
       <c r="AC7" t="n">
-        <v>-11.4618</v>
+        <v>-16.4126</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>177.62</v>
       </c>
       <c r="C8" t="n">
-        <v>177.5</v>
+        <v>182.24</v>
       </c>
       <c r="D8" t="n">
-        <v>161.51</v>
+        <v>150.58</v>
       </c>
       <c r="E8" t="n">
-        <v>176.94</v>
+        <v>172.52</v>
       </c>
       <c r="F8" t="n">
-        <v>72.81999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="G8" t="n">
-        <v>76.31</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>72.7</v>
+        <v>71.55</v>
       </c>
       <c r="I8" t="n">
-        <v>76.28</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>9.859999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="K8" t="n">
-        <v>9.970000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="L8" t="n">
-        <v>8.84</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>8.85</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>44.82</v>
+        <v>43.14</v>
       </c>
       <c r="O8" t="n">
-        <v>44.89</v>
+        <v>45.19</v>
       </c>
       <c r="P8" t="n">
-        <v>42.57</v>
+        <v>42.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>42.57</v>
+        <v>43.31</v>
       </c>
       <c r="R8" t="n">
-        <v>16.3314</v>
+        <v>-9.4003</v>
       </c>
       <c r="S8" t="n">
-        <v>22.7386</v>
+        <v>13.4254</v>
       </c>
       <c r="T8" t="n">
-        <v>35.6902</v>
+        <v>19.6726</v>
       </c>
       <c r="U8" t="n">
-        <v>6.9246</v>
+        <v>-2.5988</v>
       </c>
       <c r="V8" t="n">
-        <v>13.1919</v>
+        <v>5.0743</v>
       </c>
       <c r="W8" t="n">
-        <v>16.8147</v>
+        <v>11.2331</v>
       </c>
       <c r="X8" t="n">
-        <v>-16.5094</v>
+        <v>9.1463</v>
       </c>
       <c r="Y8" t="n">
-        <v>-23.1103</v>
+        <v>-15.566</v>
       </c>
       <c r="Z8" t="n">
-        <v>-31.8182</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA8" t="n">
-        <v>-6.9101</v>
+        <v>2.5817</v>
       </c>
       <c r="AB8" t="n">
-        <v>-12.3894</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC8" t="n">
-        <v>-15.233</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>183.84</v>
       </c>
       <c r="C9" t="n">
-        <v>191.29</v>
+        <v>188.49</v>
       </c>
       <c r="D9" t="n">
-        <v>178.94</v>
+        <v>172.26</v>
       </c>
       <c r="E9" t="n">
-        <v>190.42</v>
+        <v>184.24</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>75.81</v>
       </c>
       <c r="G9" t="n">
-        <v>77.36</v>
+        <v>77.94</v>
       </c>
       <c r="H9" t="n">
-        <v>75.55</v>
+        <v>74.19</v>
       </c>
       <c r="I9" t="n">
-        <v>76.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>8.65</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>8.77</v>
+        <v>8.98</v>
       </c>
       <c r="L9" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N9" t="n">
-        <v>42.74</v>
+        <v>42.83</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
+        <v>43.77</v>
       </c>
       <c r="P9" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="Q9" t="n">
         <v>41.99</v>
       </c>
-      <c r="Q9" t="n">
-        <v>42.22</v>
-      </c>
       <c r="R9" t="n">
-        <v>7.6184</v>
+        <v>6.7934</v>
       </c>
       <c r="S9" t="n">
-        <v>14.8146</v>
+        <v>4.1257</v>
       </c>
       <c r="T9" t="n">
-        <v>49.2905</v>
+        <v>11.0883</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8915</v>
+        <v>3.0416</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5311</v>
+        <v>1.2585</v>
       </c>
       <c r="W9" t="n">
-        <v>18.5642</v>
+        <v>7.9223</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.3446</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y9" t="n">
-        <v>-16.4118</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z9" t="n">
-        <v>-38.1599</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.8222</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB9" t="n">
-        <v>-7.392</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC9" t="n">
-        <v>-16.4126</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177.62</v>
+        <v>182.67</v>
       </c>
       <c r="C10" t="n">
-        <v>182.24</v>
+        <v>189.56</v>
       </c>
       <c r="D10" t="n">
-        <v>150.58</v>
+        <v>178.28</v>
       </c>
       <c r="E10" t="n">
-        <v>172.52</v>
+        <v>186.19</v>
       </c>
       <c r="F10" t="n">
-        <v>75.3</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>75.93000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>71.55</v>
+        <v>77.16</v>
       </c>
       <c r="I10" t="n">
-        <v>74.95999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J10" t="n">
-        <v>8.75</v>
+        <v>8.43</v>
       </c>
       <c r="K10" t="n">
-        <v>9.91</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>8.949999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="N10" t="n">
-        <v>43.14</v>
+        <v>41.98</v>
       </c>
       <c r="O10" t="n">
-        <v>45.19</v>
+        <v>42.06</v>
       </c>
       <c r="P10" t="n">
-        <v>42.79</v>
+        <v>40.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>43.31</v>
+        <v>41.07</v>
       </c>
       <c r="R10" t="n">
-        <v>-9.4003</v>
+        <v>1.0584</v>
       </c>
       <c r="S10" t="n">
-        <v>13.4254</v>
+        <v>-2.2214</v>
       </c>
       <c r="T10" t="n">
-        <v>19.6726</v>
+        <v>22.4129</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.5988</v>
+        <v>2.2139</v>
       </c>
       <c r="V10" t="n">
-        <v>5.0743</v>
+        <v>2.5858</v>
       </c>
       <c r="W10" t="n">
-        <v>11.2331</v>
+        <v>10.6672</v>
       </c>
       <c r="X10" t="n">
-        <v>9.1463</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y10" t="n">
-        <v>-15.566</v>
+        <v>0.8537</v>
       </c>
       <c r="Z10" t="n">
-        <v>-22.2415</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.5817</v>
+        <v>-2.191</v>
       </c>
       <c r="AB10" t="n">
-        <v>-5.2919</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC10" t="n">
-        <v>-10.8664</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>183.84</v>
+        <v>167</v>
       </c>
       <c r="C11" t="n">
-        <v>188.49</v>
+        <v>174.4</v>
       </c>
       <c r="D11" t="n">
-        <v>172.26</v>
+        <v>161.14</v>
       </c>
       <c r="E11" t="n">
-        <v>184.24</v>
+        <v>164.18</v>
       </c>
       <c r="F11" t="n">
-        <v>75.81</v>
+        <v>75.73</v>
       </c>
       <c r="G11" t="n">
-        <v>77.94</v>
+        <v>77.37</v>
       </c>
       <c r="H11" t="n">
-        <v>74.19</v>
+        <v>74.23</v>
       </c>
       <c r="I11" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="J11" t="n">
-        <v>8.380000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>8.98</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>8.140000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>8.35</v>
+        <v>9.23</v>
       </c>
       <c r="N11" t="n">
-        <v>42.83</v>
+        <v>42.77</v>
       </c>
       <c r="O11" t="n">
-        <v>43.77</v>
+        <v>43.57</v>
       </c>
       <c r="P11" t="n">
-        <v>41.6</v>
+        <v>41.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.99</v>
+        <v>42.98</v>
       </c>
       <c r="R11" t="n">
-        <v>6.7934</v>
+        <v>-11.8213</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1257</v>
+        <v>-4.8342</v>
       </c>
       <c r="T11" t="n">
-        <v>11.0883</v>
+        <v>-7.2115</v>
       </c>
       <c r="U11" t="n">
-        <v>3.0416</v>
+        <v>-4.5725</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2585</v>
+        <v>0.5069</v>
       </c>
       <c r="W11" t="n">
-        <v>7.9223</v>
+        <v>-1.2323</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.7039</v>
+        <v>11.6082</v>
       </c>
       <c r="Y11" t="n">
-        <v>-5.6497</v>
+        <v>3.1285</v>
       </c>
       <c r="Z11" t="n">
-        <v>-14.8828</v>
+        <v>4.2938</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.0478</v>
+        <v>4.6506</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.3625</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC11" t="n">
-        <v>-7.8965</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>182.67</v>
+        <v>172.95</v>
       </c>
       <c r="C12" t="n">
-        <v>189.56</v>
+        <v>174.61</v>
       </c>
       <c r="D12" t="n">
-        <v>178.28</v>
+        <v>142.69</v>
       </c>
       <c r="E12" t="n">
-        <v>186.19</v>
+        <v>151.75</v>
       </c>
       <c r="F12" t="n">
-        <v>77.29000000000001</v>
+        <v>76.13</v>
       </c>
       <c r="G12" t="n">
-        <v>79.68000000000001</v>
+        <v>76.27</v>
       </c>
       <c r="H12" t="n">
-        <v>77.16</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>78.95</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>8.43</v>
+        <v>8.77</v>
       </c>
       <c r="K12" t="n">
-        <v>8.630000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L12" t="n">
-        <v>8.119999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="M12" t="n">
-        <v>8.27</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>41.98</v>
+        <v>42.51</v>
       </c>
       <c r="O12" t="n">
-        <v>42.06</v>
+        <v>44.82</v>
       </c>
       <c r="P12" t="n">
-        <v>40.68</v>
+        <v>42.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.07</v>
+        <v>43.54</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0584</v>
+        <v>-7.571</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2214</v>
+        <v>-17.6346</v>
       </c>
       <c r="T12" t="n">
-        <v>22.4129</v>
+        <v>-20.3077</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2139</v>
+        <v>-1.3539</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5858</v>
+        <v>-3.7804</v>
       </c>
       <c r="W12" t="n">
-        <v>10.6672</v>
+        <v>-3.4304</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9581</v>
+        <v>7.8007</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.8537</v>
+        <v>19.1617</v>
       </c>
       <c r="Z12" t="n">
-        <v>-21.9811</v>
+        <v>21.3415</v>
       </c>
       <c r="AA12" t="n">
-        <v>-2.191</v>
+        <v>1.3029</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.7238</v>
+        <v>3.6914</v>
       </c>
       <c r="AC12" t="n">
-        <v>-10.1902</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>167</v>
+        <v>141.24</v>
       </c>
       <c r="C13" t="n">
-        <v>174.4</v>
+        <v>160.6</v>
       </c>
       <c r="D13" t="n">
-        <v>161.14</v>
+        <v>135.02</v>
       </c>
       <c r="E13" t="n">
-        <v>164.18</v>
+        <v>151.89</v>
       </c>
       <c r="F13" t="n">
-        <v>75.73</v>
+        <v>72.41</v>
       </c>
       <c r="G13" t="n">
-        <v>77.37</v>
+        <v>74.5</v>
       </c>
       <c r="H13" t="n">
-        <v>74.23</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>75.34</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>9.130000000000001</v>
+        <v>10.64</v>
       </c>
       <c r="K13" t="n">
-        <v>9.390000000000001</v>
+        <v>11.07</v>
       </c>
       <c r="L13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>9.23</v>
+        <v>9.93</v>
       </c>
       <c r="N13" t="n">
-        <v>42.77</v>
+        <v>44.68</v>
       </c>
       <c r="O13" t="n">
-        <v>43.57</v>
+        <v>45.53</v>
       </c>
       <c r="P13" t="n">
-        <v>41.93</v>
+        <v>43.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.98</v>
+        <v>44.37</v>
       </c>
       <c r="R13" t="n">
-        <v>-11.8213</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8342</v>
+        <v>-18.422</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.2115</v>
+        <v>-11.958</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.5725</v>
+        <v>-1.8703</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5069</v>
+        <v>-7.6251</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.2323</v>
+        <v>-2.7081</v>
       </c>
       <c r="X13" t="n">
-        <v>11.6082</v>
+        <v>-0.201</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.1285</v>
+        <v>20.0726</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2938</v>
+        <v>10.9497</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.6506</v>
+        <v>1.9063</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.7619</v>
+        <v>8.0351</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.9631</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>172.95</v>
+        <v>161</v>
       </c>
       <c r="C14" t="n">
-        <v>174.61</v>
+        <v>173.7</v>
       </c>
       <c r="D14" t="n">
-        <v>142.69</v>
+        <v>161</v>
       </c>
       <c r="E14" t="n">
-        <v>151.75</v>
+        <v>173.2</v>
       </c>
       <c r="F14" t="n">
-        <v>76.13</v>
+        <v>74.09</v>
       </c>
       <c r="G14" t="n">
-        <v>76.27</v>
+        <v>76.53</v>
       </c>
       <c r="H14" t="n">
-        <v>72.09999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="I14" t="n">
-        <v>74.31999999999999</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>8.77</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>10.47</v>
+        <v>9.35</v>
       </c>
       <c r="L14" t="n">
-        <v>8.68</v>
+        <v>8.51</v>
       </c>
       <c r="M14" t="n">
-        <v>9.949999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>42.51</v>
+        <v>43.67</v>
       </c>
       <c r="O14" t="n">
-        <v>44.82</v>
+        <v>43.97</v>
       </c>
       <c r="P14" t="n">
-        <v>42.44</v>
+        <v>42.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>43.54</v>
+        <v>42.19</v>
       </c>
       <c r="R14" t="n">
-        <v>-7.571</v>
+        <v>14.0299</v>
       </c>
       <c r="S14" t="n">
-        <v>-17.6346</v>
+        <v>5.494</v>
       </c>
       <c r="T14" t="n">
-        <v>-20.3077</v>
+        <v>-5.9922</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3539</v>
+        <v>4.9088</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.7804</v>
+        <v>1.553</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.4304</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>7.8007</v>
+        <v>-13.998</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.1617</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.3415</v>
+        <v>2.2754</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3029</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.6914</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1265</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>141.24</v>
+        <v>171.26</v>
       </c>
       <c r="C15" t="n">
-        <v>160.6</v>
+        <v>179.97</v>
       </c>
       <c r="D15" t="n">
-        <v>135.02</v>
+        <v>168.23</v>
       </c>
       <c r="E15" t="n">
-        <v>151.89</v>
+        <v>178.39</v>
       </c>
       <c r="F15" t="n">
-        <v>72.41</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>74.5</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>70.95999999999999</v>
+        <v>74.47</v>
       </c>
       <c r="I15" t="n">
-        <v>72.93000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="J15" t="n">
-        <v>10.64</v>
+        <v>8.65</v>
       </c>
       <c r="K15" t="n">
-        <v>11.07</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>9.369999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>9.93</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>44.68</v>
+        <v>42.94</v>
       </c>
       <c r="O15" t="n">
-        <v>45.53</v>
+        <v>43.33</v>
       </c>
       <c r="P15" t="n">
-        <v>43.46</v>
+        <v>41.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>44.37</v>
+        <v>41.96</v>
       </c>
       <c r="R15" t="n">
-        <v>0.09229999999999999</v>
+        <v>2.9965</v>
       </c>
       <c r="S15" t="n">
-        <v>-18.422</v>
+        <v>17.5552</v>
       </c>
       <c r="T15" t="n">
-        <v>-11.958</v>
+        <v>-4.1893</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.8703</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.6251</v>
+        <v>3.5388</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.7081</v>
+        <v>-2.5332</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.201</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y15" t="n">
-        <v>20.0726</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.9497</v>
+        <v>0.2418</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9063</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.0351</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4475</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>161</v>
+        <v>184.8</v>
       </c>
       <c r="C16" t="n">
-        <v>173.7</v>
+        <v>195.27</v>
       </c>
       <c r="D16" t="n">
-        <v>161</v>
+        <v>183.34</v>
       </c>
       <c r="E16" t="n">
-        <v>173.2</v>
+        <v>190.56</v>
       </c>
       <c r="F16" t="n">
-        <v>74.09</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>76.53</v>
+        <v>79.33</v>
       </c>
       <c r="H16" t="n">
-        <v>73.62</v>
+        <v>77.33</v>
       </c>
       <c r="I16" t="n">
-        <v>76.51000000000001</v>
+        <v>77.84</v>
       </c>
       <c r="J16" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>9.35</v>
+        <v>8.06</v>
       </c>
       <c r="L16" t="n">
-        <v>8.51</v>
+        <v>7.5</v>
       </c>
       <c r="M16" t="n">
-        <v>8.539999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="N16" t="n">
-        <v>43.67</v>
+        <v>41.4</v>
       </c>
       <c r="O16" t="n">
-        <v>43.97</v>
+        <v>41.78</v>
       </c>
       <c r="P16" t="n">
-        <v>42.19</v>
+        <v>40.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.19</v>
+        <v>41.5</v>
       </c>
       <c r="R16" t="n">
-        <v>14.0299</v>
+        <v>6.8221</v>
       </c>
       <c r="S16" t="n">
-        <v>5.494</v>
+        <v>25.4592</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.9922</v>
+        <v>16.0677</v>
       </c>
       <c r="U16" t="n">
-        <v>4.9088</v>
+        <v>1.1566</v>
       </c>
       <c r="V16" t="n">
-        <v>1.553</v>
+        <v>6.7325</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9451000000000001</v>
+        <v>3.3183</v>
       </c>
       <c r="X16" t="n">
-        <v>-13.998</v>
+        <v>-6.7551</v>
       </c>
       <c r="Y16" t="n">
-        <v>-7.4756</v>
+        <v>-22.1551</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2754</v>
+        <v>-16.2514</v>
       </c>
       <c r="AA16" t="n">
-        <v>-4.9132</v>
+        <v>-1.0963</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.8381</v>
+        <v>-6.4683</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4763</v>
+        <v>-3.4435</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>171.26</v>
+        <v>211.38</v>
       </c>
       <c r="C17" t="n">
-        <v>179.97</v>
+        <v>228.5</v>
       </c>
       <c r="D17" t="n">
-        <v>168.23</v>
+        <v>209.89</v>
       </c>
       <c r="E17" t="n">
-        <v>178.39</v>
+        <v>225.79</v>
       </c>
       <c r="F17" t="n">
-        <v>75.18000000000001</v>
+        <v>80.59</v>
       </c>
       <c r="G17" t="n">
-        <v>77.79000000000001</v>
+        <v>82.27</v>
       </c>
       <c r="H17" t="n">
-        <v>74.47</v>
+        <v>79.98</v>
       </c>
       <c r="I17" t="n">
-        <v>76.95</v>
+        <v>81.95</v>
       </c>
       <c r="J17" t="n">
-        <v>8.65</v>
+        <v>6.9</v>
       </c>
       <c r="K17" t="n">
-        <v>8.779999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="L17" t="n">
-        <v>8.210000000000001</v>
+        <v>6.19</v>
       </c>
       <c r="M17" t="n">
-        <v>8.289999999999999</v>
+        <v>6.29</v>
       </c>
       <c r="N17" t="n">
-        <v>42.94</v>
+        <v>40.05</v>
       </c>
       <c r="O17" t="n">
-        <v>43.33</v>
+        <v>40.35</v>
       </c>
       <c r="P17" t="n">
-        <v>41.5</v>
+        <v>39.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.96</v>
+        <v>39.28</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9965</v>
+        <v>18.4876</v>
       </c>
       <c r="S17" t="n">
-        <v>17.5552</v>
+        <v>30.3637</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.1893</v>
+        <v>48.7908</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5750999999999999</v>
+        <v>5.2801</v>
       </c>
       <c r="V17" t="n">
-        <v>3.5388</v>
+        <v>7.1102</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.5332</v>
+        <v>10.2664</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.9274</v>
+        <v>-18.6287</v>
       </c>
       <c r="Y17" t="n">
-        <v>-16.6834</v>
+        <v>-26.3466</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.2418</v>
+        <v>-36.7839</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.5452</v>
+        <v>-5.3494</v>
       </c>
       <c r="AB17" t="n">
-        <v>-3.6288</v>
+        <v>-6.8974</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.167</v>
+        <v>-9.7841</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>184.8</v>
+        <v>242.66</v>
       </c>
       <c r="C18" t="n">
-        <v>195.27</v>
+        <v>242.66</v>
       </c>
       <c r="D18" t="n">
-        <v>183.34</v>
+        <v>204</v>
       </c>
       <c r="E18" t="n">
-        <v>190.56</v>
+        <v>217.98</v>
       </c>
       <c r="F18" t="n">
-        <v>78.04000000000001</v>
+        <v>82.87</v>
       </c>
       <c r="G18" t="n">
-        <v>79.33</v>
+        <v>82.91</v>
       </c>
       <c r="H18" t="n">
-        <v>77.33</v>
+        <v>80.33</v>
       </c>
       <c r="I18" t="n">
-        <v>77.84</v>
+        <v>81.67</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>5.83</v>
       </c>
       <c r="K18" t="n">
-        <v>8.06</v>
+        <v>6.91</v>
       </c>
       <c r="L18" t="n">
-        <v>7.5</v>
+        <v>5.83</v>
       </c>
       <c r="M18" t="n">
-        <v>7.73</v>
+        <v>6.53</v>
       </c>
       <c r="N18" t="n">
-        <v>41.4</v>
+        <v>38.87</v>
       </c>
       <c r="O18" t="n">
-        <v>41.78</v>
+        <v>40.09</v>
       </c>
       <c r="P18" t="n">
-        <v>40.68</v>
+        <v>38.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.5</v>
+        <v>39.44</v>
       </c>
       <c r="R18" t="n">
-        <v>6.8221</v>
+        <v>-3.459</v>
       </c>
       <c r="S18" t="n">
-        <v>25.4592</v>
+        <v>22.1929</v>
       </c>
       <c r="T18" t="n">
-        <v>16.0677</v>
+        <v>43.5118</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1566</v>
+        <v>-0.3417</v>
       </c>
       <c r="V18" t="n">
-        <v>6.7325</v>
+        <v>6.1339</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3183</v>
+        <v>11.9841</v>
       </c>
       <c r="X18" t="n">
-        <v>-6.7551</v>
+        <v>3.8156</v>
       </c>
       <c r="Y18" t="n">
-        <v>-22.1551</v>
+        <v>-21.2304</v>
       </c>
       <c r="Z18" t="n">
-        <v>-16.2514</v>
+        <v>-34.2397</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1.0963</v>
+        <v>0.4073</v>
       </c>
       <c r="AB18" t="n">
-        <v>-6.4683</v>
+        <v>-6.0057</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.4435</v>
+        <v>-11.1111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>211.38</v>
+        <v>219</v>
       </c>
       <c r="C19" t="n">
-        <v>228.5</v>
+        <v>231.89</v>
       </c>
       <c r="D19" t="n">
-        <v>209.89</v>
+        <v>207.56</v>
       </c>
       <c r="E19" t="n">
-        <v>225.79</v>
+        <v>224.63</v>
       </c>
       <c r="F19" t="n">
-        <v>80.59</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>82.27</v>
+        <v>84.05</v>
       </c>
       <c r="H19" t="n">
-        <v>79.98</v>
+        <v>80.66</v>
       </c>
       <c r="I19" t="n">
-        <v>81.95</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>6.9</v>
+        <v>6.49</v>
       </c>
       <c r="K19" t="n">
-        <v>6.95</v>
+        <v>6.83</v>
       </c>
       <c r="L19" t="n">
-        <v>6.19</v>
+        <v>6.1</v>
       </c>
       <c r="M19" t="n">
-        <v>6.29</v>
+        <v>6.31</v>
       </c>
       <c r="N19" t="n">
-        <v>40.05</v>
+        <v>39.41</v>
       </c>
       <c r="O19" t="n">
-        <v>40.35</v>
+        <v>39.94</v>
       </c>
       <c r="P19" t="n">
-        <v>39.14</v>
+        <v>38.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>39.28</v>
+        <v>38.47</v>
       </c>
       <c r="R19" t="n">
-        <v>18.4876</v>
+        <v>3.0507</v>
       </c>
       <c r="S19" t="n">
-        <v>30.3637</v>
+        <v>17.8789</v>
       </c>
       <c r="T19" t="n">
-        <v>48.7908</v>
+        <v>29.694</v>
       </c>
       <c r="U19" t="n">
-        <v>5.2801</v>
+        <v>2.4611</v>
       </c>
       <c r="V19" t="n">
-        <v>7.1102</v>
+        <v>7.5026</v>
       </c>
       <c r="W19" t="n">
-        <v>10.2664</v>
+        <v>9.3713</v>
       </c>
       <c r="X19" t="n">
-        <v>-18.6287</v>
+        <v>-3.3691</v>
       </c>
       <c r="Y19" t="n">
-        <v>-26.3466</v>
+        <v>-18.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>-36.7839</v>
+        <v>-26.1124</v>
       </c>
       <c r="AA19" t="n">
-        <v>-5.3494</v>
+        <v>-2.4594</v>
       </c>
       <c r="AB19" t="n">
-        <v>-6.8974</v>
+        <v>-7.3012</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.7841</v>
+        <v>-8.817299999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>242.66</v>
+        <v>231.82</v>
       </c>
       <c r="C20" t="n">
-        <v>242.66</v>
+        <v>239.07</v>
       </c>
       <c r="D20" t="n">
-        <v>204</v>
+        <v>218.56</v>
       </c>
       <c r="E20" t="n">
-        <v>217.98</v>
+        <v>224.34</v>
       </c>
       <c r="F20" t="n">
-        <v>82.87</v>
+        <v>84.41</v>
       </c>
       <c r="G20" t="n">
-        <v>82.91</v>
+        <v>85.7</v>
       </c>
       <c r="H20" t="n">
-        <v>80.33</v>
+        <v>83.53</v>
       </c>
       <c r="I20" t="n">
-        <v>81.67</v>
+        <v>84.56</v>
       </c>
       <c r="J20" t="n">
-        <v>5.83</v>
+        <v>6.11</v>
       </c>
       <c r="K20" t="n">
-        <v>6.91</v>
+        <v>6.49</v>
       </c>
       <c r="L20" t="n">
-        <v>5.83</v>
+        <v>5.91</v>
       </c>
       <c r="M20" t="n">
-        <v>6.53</v>
+        <v>6.33</v>
       </c>
       <c r="N20" t="n">
-        <v>38.87</v>
+        <v>38.15</v>
       </c>
       <c r="O20" t="n">
-        <v>40.09</v>
+        <v>38.56</v>
       </c>
       <c r="P20" t="n">
-        <v>38.86</v>
+        <v>37.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>39.44</v>
+        <v>38.08</v>
       </c>
       <c r="R20" t="n">
-        <v>-3.459</v>
+        <v>-0.1291</v>
       </c>
       <c r="S20" t="n">
-        <v>22.1929</v>
+        <v>-0.6422</v>
       </c>
       <c r="T20" t="n">
-        <v>43.5118</v>
+        <v>25.7582</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3417</v>
+        <v>1.0516</v>
       </c>
       <c r="V20" t="n">
-        <v>6.1339</v>
+        <v>3.1849</v>
       </c>
       <c r="W20" t="n">
-        <v>11.9841</v>
+        <v>9.8895</v>
       </c>
       <c r="X20" t="n">
-        <v>3.8156</v>
+        <v>0.317</v>
       </c>
       <c r="Y20" t="n">
-        <v>-21.2304</v>
+        <v>0.6359</v>
       </c>
       <c r="Z20" t="n">
-        <v>-34.2397</v>
+        <v>-23.6429</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.4073</v>
+        <v>-1.0138</v>
       </c>
       <c r="AB20" t="n">
-        <v>-6.0057</v>
+        <v>-3.055</v>
       </c>
       <c r="AC20" t="n">
-        <v>-11.1111</v>
+        <v>-9.2469</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>219</v>
+        <v>217.265</v>
       </c>
       <c r="C21" t="n">
-        <v>231.89</v>
+        <v>234.06</v>
       </c>
       <c r="D21" t="n">
-        <v>207.56</v>
+        <v>210.14</v>
       </c>
       <c r="E21" t="n">
-        <v>224.63</v>
+        <v>227.03</v>
       </c>
       <c r="F21" t="n">
-        <v>81.73999999999999</v>
+        <v>84.14749999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>84.05</v>
+        <v>87.06</v>
       </c>
       <c r="H21" t="n">
-        <v>80.66</v>
+        <v>83.75</v>
       </c>
       <c r="I21" t="n">
-        <v>83.68000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="K21" t="n">
-        <v>6.83</v>
+        <v>6.74</v>
       </c>
       <c r="L21" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="M21" t="n">
-        <v>6.31</v>
+        <v>6.26</v>
       </c>
       <c r="N21" t="n">
-        <v>39.41</v>
+        <v>38.27</v>
       </c>
       <c r="O21" t="n">
-        <v>39.94</v>
+        <v>38.4599</v>
       </c>
       <c r="P21" t="n">
-        <v>38.3</v>
+        <v>36.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>38.47</v>
+        <v>37.42</v>
       </c>
       <c r="R21" t="n">
-        <v>3.0507</v>
+        <v>1.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>17.8789</v>
+        <v>4.1518</v>
       </c>
       <c r="T21" t="n">
-        <v>29.694</v>
+        <v>19.1383</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4611</v>
+        <v>1.7502</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5026</v>
+        <v>5.3508</v>
       </c>
       <c r="W21" t="n">
-        <v>9.3713</v>
+        <v>10.5344</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.3691</v>
+        <v>-1.1058</v>
       </c>
       <c r="Y21" t="n">
-        <v>-18.37</v>
+        <v>-4.1348</v>
       </c>
       <c r="Z21" t="n">
-        <v>-26.1124</v>
+        <v>-19.0168</v>
       </c>
       <c r="AA21" t="n">
-        <v>-2.4594</v>
+        <v>-1.7332</v>
       </c>
       <c r="AB21" t="n">
-        <v>-7.3012</v>
+        <v>-5.1217</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8.817299999999999</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>231.82</v>
-      </c>
-      <c r="C22" t="n">
-        <v>239.05</v>
-      </c>
-      <c r="D22" t="n">
-        <v>218.56</v>
-      </c>
-      <c r="E22" t="n">
-        <v>224.34</v>
-      </c>
-      <c r="F22" t="n">
-        <v>84.42</v>
-      </c>
-      <c r="G22" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>83.53</v>
-      </c>
-      <c r="I22" t="n">
-        <v>84.56</v>
-      </c>
-      <c r="J22" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5.9107</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="N22" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="O22" t="n">
-        <v>38.5599</v>
-      </c>
-      <c r="P22" t="n">
-        <v>37.57</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>38.08</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-0.1291</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-0.6422</v>
-      </c>
-      <c r="T22" t="n">
-        <v>25.7582</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.0516</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3.1849</v>
-      </c>
-      <c r="W22" t="n">
-        <v>9.8895</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.6359</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-23.6429</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>-1.0138</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-3.055</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-9.2469</v>
+        <v>-9.831300000000001</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26384,7 +26384,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>217.265</v>
+        <v>217.27</v>
       </c>
       <c r="C21" t="n">
         <v>234.06</v>
@@ -26396,7 +26396,7 @@
         <v>227.03</v>
       </c>
       <c r="F21" t="n">
-        <v>84.14749999999999</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>87.06</v>
@@ -26423,7 +26423,7 @@
         <v>38.27</v>
       </c>
       <c r="O21" t="n">
-        <v>38.4599</v>
+        <v>38.46</v>
       </c>
       <c r="P21" t="n">
         <v>36.96</v>
@@ -26466,6 +26466,97 @@
       </c>
       <c r="AC21" t="n">
         <v>-9.831300000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>243.18</v>
+      </c>
+      <c r="C22" t="n">
+        <v>267.08</v>
+      </c>
+      <c r="D22" t="n">
+        <v>238.8233</v>
+      </c>
+      <c r="E22" t="n">
+        <v>266.32</v>
+      </c>
+      <c r="F22" t="n">
+        <v>85.95</v>
+      </c>
+      <c r="G22" t="n">
+        <v>87.31999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>84.8313</v>
+      </c>
+      <c r="I22" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="N22" t="n">
+        <v>37.46</v>
+      </c>
+      <c r="O22" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="P22" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="R22" t="n">
+        <v>17.3061</v>
+      </c>
+      <c r="S22" t="n">
+        <v>18.5594</v>
+      </c>
+      <c r="T22" t="n">
+        <v>17.9503</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.3715</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.2304</v>
+      </c>
+      <c r="W22" t="n">
+        <v>6.4308</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-17.4121</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-18.0666</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-17.806</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.3629</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-4.0551</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-6.0336</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>132.2</v>
+        <v>135</v>
       </c>
       <c r="C2" t="n">
-        <v>133.67</v>
+        <v>147.26</v>
       </c>
       <c r="D2" t="n">
-        <v>123.8</v>
+        <v>134.02</v>
       </c>
       <c r="E2" t="n">
-        <v>127.55</v>
+        <v>144.16</v>
       </c>
       <c r="F2" t="n">
-        <v>65.44</v>
+        <v>66.37</v>
       </c>
       <c r="G2" t="n">
-        <v>66.05</v>
+        <v>67.77</v>
       </c>
       <c r="H2" t="n">
-        <v>63.78</v>
+        <v>66.25</v>
       </c>
       <c r="I2" t="n">
-        <v>64.91</v>
+        <v>67.39</v>
       </c>
       <c r="J2" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="K2" t="n">
-        <v>13.64</v>
+        <v>12.59</v>
       </c>
       <c r="L2" t="n">
-        <v>12.65</v>
+        <v>11.21</v>
       </c>
       <c r="M2" t="n">
-        <v>13.26</v>
+        <v>11.51</v>
       </c>
       <c r="N2" t="n">
-        <v>50.12</v>
+        <v>49.4</v>
       </c>
       <c r="O2" t="n">
-        <v>51.43</v>
+        <v>49.49</v>
       </c>
       <c r="P2" t="n">
-        <v>49.65</v>
+        <v>48.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>50.51</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C3" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D3" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E3" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F3" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H3" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I3" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K3" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L3" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N3" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O3" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
       <c r="R3" t="n">
-        <v>13.0223</v>
+        <v>15.0458</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8207</v>
+        <v>6.2027</v>
       </c>
       <c r="X3" t="n">
-        <v>-13.1976</v>
+        <v>-14.7698</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3.8012</v>
+        <v>-6.1741</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C4" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D4" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E4" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F4" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G4" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H4" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I4" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J4" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K4" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N4" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O4" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P4" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R4" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="U4" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="X4" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C5" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D5" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E5" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F5" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H5" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I5" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J5" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M5" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N5" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O5" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P5" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R5" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="S5" t="n">
-        <v>19.2474</v>
+        <v>22.7386</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="V5" t="n">
-        <v>9.906000000000001</v>
+        <v>13.1919</v>
       </c>
       <c r="X5" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="Y5" t="n">
-        <v>-20.0603</v>
+        <v>-23.1103</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
       <c r="AB5" t="n">
-        <v>-9.4635</v>
+        <v>-12.3894</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C6" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D6" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E6" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F6" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H6" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I6" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K6" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L6" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M6" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O6" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P6" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R6" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S6" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="U6" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y6" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="AA6" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB6" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C7" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D7" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E7" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G7" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I7" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K7" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L7" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O7" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P7" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S7" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="T7" t="n">
-        <v>49.2905</v>
+        <v>19.6726</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="W7" t="n">
-        <v>18.5642</v>
+        <v>11.2331</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y7" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="Z7" t="n">
-        <v>-38.1599</v>
+        <v>-22.2415</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB7" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
       <c r="AC7" t="n">
-        <v>-16.4126</v>
+        <v>-10.8664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C8" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D8" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E8" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F8" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G8" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H8" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I8" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N8" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O8" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P8" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R8" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S8" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T8" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V8" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W8" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X8" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y8" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z8" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC8" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>183.84</v>
+        <v>182.67</v>
       </c>
       <c r="C9" t="n">
-        <v>188.49</v>
+        <v>189.56</v>
       </c>
       <c r="D9" t="n">
-        <v>172.26</v>
+        <v>178.28</v>
       </c>
       <c r="E9" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F9" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>74.19</v>
+        <v>77.16</v>
       </c>
       <c r="I9" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K9" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N9" t="n">
-        <v>42.83</v>
+        <v>41.98</v>
       </c>
       <c r="O9" t="n">
-        <v>43.77</v>
+        <v>42.06</v>
       </c>
       <c r="P9" t="n">
-        <v>41.6</v>
+        <v>40.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R9" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T9" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U9" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W9" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y9" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z9" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA9" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>182.67</v>
+        <v>167</v>
       </c>
       <c r="C10" t="n">
-        <v>189.56</v>
+        <v>174.4</v>
       </c>
       <c r="D10" t="n">
-        <v>178.28</v>
+        <v>161.14</v>
       </c>
       <c r="E10" t="n">
-        <v>186.19</v>
+        <v>164.18</v>
       </c>
       <c r="F10" t="n">
-        <v>77.29000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G10" t="n">
-        <v>79.68000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="H10" t="n">
-        <v>77.16</v>
+        <v>74.23</v>
       </c>
       <c r="I10" t="n">
-        <v>78.95</v>
+        <v>75.34</v>
       </c>
       <c r="J10" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>8.630000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>8.27</v>
+        <v>9.23</v>
       </c>
       <c r="N10" t="n">
-        <v>41.98</v>
+        <v>42.77</v>
       </c>
       <c r="O10" t="n">
-        <v>42.06</v>
+        <v>43.57</v>
       </c>
       <c r="P10" t="n">
-        <v>40.68</v>
+        <v>41.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.07</v>
+        <v>42.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0584</v>
+        <v>-11.8213</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2214</v>
+        <v>-4.8342</v>
       </c>
       <c r="T10" t="n">
-        <v>22.4129</v>
+        <v>-7.2115</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2139</v>
+        <v>-4.5725</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5858</v>
+        <v>0.5069</v>
       </c>
       <c r="W10" t="n">
-        <v>10.6672</v>
+        <v>-1.2323</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9581</v>
+        <v>11.6082</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8537</v>
+        <v>3.1285</v>
       </c>
       <c r="Z10" t="n">
-        <v>-21.9811</v>
+        <v>4.2938</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.191</v>
+        <v>4.6506</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.7238</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC10" t="n">
-        <v>-10.1902</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>167</v>
+        <v>172.95</v>
       </c>
       <c r="C11" t="n">
-        <v>174.4</v>
+        <v>174.61</v>
       </c>
       <c r="D11" t="n">
-        <v>161.14</v>
+        <v>142.69</v>
       </c>
       <c r="E11" t="n">
-        <v>164.18</v>
+        <v>151.75</v>
       </c>
       <c r="F11" t="n">
-        <v>75.73</v>
+        <v>76.13</v>
       </c>
       <c r="G11" t="n">
-        <v>77.37</v>
+        <v>76.27</v>
       </c>
       <c r="H11" t="n">
-        <v>74.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>75.34</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K11" t="n">
-        <v>9.390000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M11" t="n">
-        <v>9.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>42.77</v>
+        <v>42.51</v>
       </c>
       <c r="O11" t="n">
-        <v>43.57</v>
+        <v>44.82</v>
       </c>
       <c r="P11" t="n">
-        <v>41.93</v>
+        <v>42.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>42.98</v>
+        <v>43.54</v>
       </c>
       <c r="R11" t="n">
-        <v>-11.8213</v>
+        <v>-7.571</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.8342</v>
+        <v>-17.6346</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.2115</v>
+        <v>-20.3077</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.5725</v>
+        <v>-1.3539</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5069</v>
+        <v>-3.7804</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.2323</v>
+        <v>-3.4304</v>
       </c>
       <c r="X11" t="n">
-        <v>11.6082</v>
+        <v>7.8007</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.1285</v>
+        <v>19.1617</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2938</v>
+        <v>21.3415</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.6506</v>
+        <v>1.3029</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.7619</v>
+        <v>3.6914</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.9631</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>172.95</v>
+        <v>141.24</v>
       </c>
       <c r="C12" t="n">
-        <v>174.61</v>
+        <v>160.6</v>
       </c>
       <c r="D12" t="n">
-        <v>142.69</v>
+        <v>135.02</v>
       </c>
       <c r="E12" t="n">
-        <v>151.75</v>
+        <v>151.89</v>
       </c>
       <c r="F12" t="n">
-        <v>76.13</v>
+        <v>72.41</v>
       </c>
       <c r="G12" t="n">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="H12" t="n">
-        <v>72.09999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>74.31999999999999</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>8.77</v>
+        <v>10.64</v>
       </c>
       <c r="K12" t="n">
-        <v>10.47</v>
+        <v>11.07</v>
       </c>
       <c r="L12" t="n">
-        <v>8.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="N12" t="n">
-        <v>42.51</v>
+        <v>44.68</v>
       </c>
       <c r="O12" t="n">
-        <v>44.82</v>
+        <v>45.53</v>
       </c>
       <c r="P12" t="n">
-        <v>42.44</v>
+        <v>43.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>43.54</v>
+        <v>44.37</v>
       </c>
       <c r="R12" t="n">
-        <v>-7.571</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-17.6346</v>
+        <v>-18.422</v>
       </c>
       <c r="T12" t="n">
-        <v>-20.3077</v>
+        <v>-11.958</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3539</v>
+        <v>-1.8703</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7804</v>
+        <v>-7.6251</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.4304</v>
+        <v>-2.7081</v>
       </c>
       <c r="X12" t="n">
-        <v>7.8007</v>
+        <v>-0.201</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.1617</v>
+        <v>20.0726</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.3415</v>
+        <v>10.9497</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3029</v>
+        <v>1.9063</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.6914</v>
+        <v>8.0351</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1265</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>141.24</v>
+        <v>161</v>
       </c>
       <c r="C13" t="n">
-        <v>160.6</v>
+        <v>173.7</v>
       </c>
       <c r="D13" t="n">
-        <v>135.02</v>
+        <v>161</v>
       </c>
       <c r="E13" t="n">
-        <v>151.89</v>
+        <v>173.2</v>
       </c>
       <c r="F13" t="n">
-        <v>72.41</v>
+        <v>74.09</v>
       </c>
       <c r="G13" t="n">
-        <v>74.5</v>
+        <v>76.53</v>
       </c>
       <c r="H13" t="n">
-        <v>70.95999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="I13" t="n">
-        <v>72.93000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>10.64</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>11.07</v>
+        <v>9.35</v>
       </c>
       <c r="L13" t="n">
-        <v>9.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M13" t="n">
-        <v>9.93</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>44.68</v>
+        <v>43.67</v>
       </c>
       <c r="O13" t="n">
-        <v>45.53</v>
+        <v>43.97</v>
       </c>
       <c r="P13" t="n">
-        <v>43.46</v>
+        <v>42.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.37</v>
+        <v>42.19</v>
       </c>
       <c r="R13" t="n">
-        <v>0.09229999999999999</v>
+        <v>14.0299</v>
       </c>
       <c r="S13" t="n">
-        <v>-18.422</v>
+        <v>5.494</v>
       </c>
       <c r="T13" t="n">
-        <v>-11.958</v>
+        <v>-5.9922</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8703</v>
+        <v>4.9088</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.6251</v>
+        <v>1.553</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.7081</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.201</v>
+        <v>-13.998</v>
       </c>
       <c r="Y13" t="n">
-        <v>20.0726</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.9497</v>
+        <v>2.2754</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9063</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.0351</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4475</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>161</v>
+        <v>171.26</v>
       </c>
       <c r="C14" t="n">
-        <v>173.7</v>
+        <v>179.97</v>
       </c>
       <c r="D14" t="n">
-        <v>161</v>
+        <v>168.23</v>
       </c>
       <c r="E14" t="n">
-        <v>173.2</v>
+        <v>178.39</v>
       </c>
       <c r="F14" t="n">
-        <v>74.09</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>73.62</v>
+        <v>74.47</v>
       </c>
       <c r="I14" t="n">
-        <v>76.51000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="J14" t="n">
-        <v>9.300000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="K14" t="n">
-        <v>9.35</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>8.51</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>8.539999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>43.67</v>
+        <v>42.94</v>
       </c>
       <c r="O14" t="n">
-        <v>43.97</v>
+        <v>43.33</v>
       </c>
       <c r="P14" t="n">
-        <v>42.19</v>
+        <v>41.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>42.19</v>
+        <v>41.96</v>
       </c>
       <c r="R14" t="n">
-        <v>14.0299</v>
+        <v>2.9965</v>
       </c>
       <c r="S14" t="n">
-        <v>5.494</v>
+        <v>17.5552</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.9922</v>
+        <v>-4.1893</v>
       </c>
       <c r="U14" t="n">
-        <v>4.9088</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>1.553</v>
+        <v>3.5388</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-2.5332</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.998</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y14" t="n">
-        <v>-7.4756</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2754</v>
+        <v>0.2418</v>
       </c>
       <c r="AA14" t="n">
-        <v>-4.9132</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.8381</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.4763</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>171.26</v>
+        <v>184.8</v>
       </c>
       <c r="C15" t="n">
-        <v>179.97</v>
+        <v>195.27</v>
       </c>
       <c r="D15" t="n">
-        <v>168.23</v>
+        <v>183.34</v>
       </c>
       <c r="E15" t="n">
-        <v>178.39</v>
+        <v>190.56</v>
       </c>
       <c r="F15" t="n">
-        <v>75.18000000000001</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>77.79000000000001</v>
+        <v>79.33</v>
       </c>
       <c r="H15" t="n">
-        <v>74.47</v>
+        <v>77.33</v>
       </c>
       <c r="I15" t="n">
-        <v>76.95</v>
+        <v>77.84</v>
       </c>
       <c r="J15" t="n">
-        <v>8.65</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>8.779999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="L15" t="n">
-        <v>8.210000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="M15" t="n">
-        <v>8.289999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="N15" t="n">
-        <v>42.94</v>
+        <v>41.4</v>
       </c>
       <c r="O15" t="n">
-        <v>43.33</v>
+        <v>41.78</v>
       </c>
       <c r="P15" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="Q15" t="n">
         <v>41.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>41.96</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.9965</v>
+        <v>6.8221</v>
       </c>
       <c r="S15" t="n">
-        <v>17.5552</v>
+        <v>25.4592</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.1893</v>
+        <v>16.0677</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5750999999999999</v>
+        <v>1.1566</v>
       </c>
       <c r="V15" t="n">
-        <v>3.5388</v>
+        <v>6.7325</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.5332</v>
+        <v>3.3183</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.9274</v>
+        <v>-6.7551</v>
       </c>
       <c r="Y15" t="n">
-        <v>-16.6834</v>
+        <v>-22.1551</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2418</v>
+        <v>-16.2514</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.5452</v>
+        <v>-1.0963</v>
       </c>
       <c r="AB15" t="n">
-        <v>-3.6288</v>
+        <v>-6.4683</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.167</v>
+        <v>-3.4435</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>184.8</v>
+        <v>211.38</v>
       </c>
       <c r="C16" t="n">
-        <v>195.27</v>
+        <v>228.5</v>
       </c>
       <c r="D16" t="n">
-        <v>183.34</v>
+        <v>209.89</v>
       </c>
       <c r="E16" t="n">
-        <v>190.56</v>
+        <v>225.79</v>
       </c>
       <c r="F16" t="n">
-        <v>78.04000000000001</v>
+        <v>80.59</v>
       </c>
       <c r="G16" t="n">
-        <v>79.33</v>
+        <v>82.27</v>
       </c>
       <c r="H16" t="n">
-        <v>77.33</v>
+        <v>79.98</v>
       </c>
       <c r="I16" t="n">
-        <v>77.84</v>
+        <v>81.95</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="K16" t="n">
-        <v>8.06</v>
+        <v>6.95</v>
       </c>
       <c r="L16" t="n">
-        <v>7.5</v>
+        <v>6.19</v>
       </c>
       <c r="M16" t="n">
-        <v>7.73</v>
+        <v>6.29</v>
       </c>
       <c r="N16" t="n">
-        <v>41.4</v>
+        <v>40.05</v>
       </c>
       <c r="O16" t="n">
-        <v>41.78</v>
+        <v>40.35</v>
       </c>
       <c r="P16" t="n">
-        <v>40.68</v>
+        <v>39.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.5</v>
+        <v>39.28</v>
       </c>
       <c r="R16" t="n">
-        <v>6.8221</v>
+        <v>18.4876</v>
       </c>
       <c r="S16" t="n">
-        <v>25.4592</v>
+        <v>30.3637</v>
       </c>
       <c r="T16" t="n">
-        <v>16.0677</v>
+        <v>48.7908</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1566</v>
+        <v>5.2801</v>
       </c>
       <c r="V16" t="n">
-        <v>6.7325</v>
+        <v>7.1102</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3183</v>
+        <v>10.2664</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.7551</v>
+        <v>-18.6287</v>
       </c>
       <c r="Y16" t="n">
-        <v>-22.1551</v>
+        <v>-26.3466</v>
       </c>
       <c r="Z16" t="n">
-        <v>-16.2514</v>
+        <v>-36.7839</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.0963</v>
+        <v>-5.3494</v>
       </c>
       <c r="AB16" t="n">
-        <v>-6.4683</v>
+        <v>-6.8974</v>
       </c>
       <c r="AC16" t="n">
-        <v>-3.4435</v>
+        <v>-9.7841</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>211.38</v>
+        <v>242.66</v>
       </c>
       <c r="C17" t="n">
-        <v>228.5</v>
+        <v>242.66</v>
       </c>
       <c r="D17" t="n">
-        <v>209.89</v>
+        <v>204</v>
       </c>
       <c r="E17" t="n">
-        <v>225.79</v>
+        <v>217.98</v>
       </c>
       <c r="F17" t="n">
-        <v>80.59</v>
+        <v>82.87</v>
       </c>
       <c r="G17" t="n">
-        <v>82.27</v>
+        <v>82.91</v>
       </c>
       <c r="H17" t="n">
-        <v>79.98</v>
+        <v>80.33</v>
       </c>
       <c r="I17" t="n">
-        <v>81.95</v>
+        <v>81.67</v>
       </c>
       <c r="J17" t="n">
-        <v>6.9</v>
+        <v>5.83</v>
       </c>
       <c r="K17" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="L17" t="n">
-        <v>6.19</v>
+        <v>5.83</v>
       </c>
       <c r="M17" t="n">
-        <v>6.29</v>
+        <v>6.53</v>
       </c>
       <c r="N17" t="n">
-        <v>40.05</v>
+        <v>38.87</v>
       </c>
       <c r="O17" t="n">
-        <v>40.35</v>
+        <v>40.09</v>
       </c>
       <c r="P17" t="n">
-        <v>39.14</v>
+        <v>38.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>39.28</v>
+        <v>39.44</v>
       </c>
       <c r="R17" t="n">
-        <v>18.4876</v>
+        <v>-3.459</v>
       </c>
       <c r="S17" t="n">
-        <v>30.3637</v>
+        <v>22.1929</v>
       </c>
       <c r="T17" t="n">
-        <v>48.7908</v>
+        <v>43.5118</v>
       </c>
       <c r="U17" t="n">
-        <v>5.2801</v>
+        <v>-0.3417</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1102</v>
+        <v>6.1339</v>
       </c>
       <c r="W17" t="n">
-        <v>10.2664</v>
+        <v>11.9841</v>
       </c>
       <c r="X17" t="n">
-        <v>-18.6287</v>
+        <v>3.8156</v>
       </c>
       <c r="Y17" t="n">
-        <v>-26.3466</v>
+        <v>-21.2304</v>
       </c>
       <c r="Z17" t="n">
-        <v>-36.7839</v>
+        <v>-34.2397</v>
       </c>
       <c r="AA17" t="n">
-        <v>-5.3494</v>
+        <v>0.4073</v>
       </c>
       <c r="AB17" t="n">
-        <v>-6.8974</v>
+        <v>-6.0057</v>
       </c>
       <c r="AC17" t="n">
-        <v>-9.7841</v>
+        <v>-11.1111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>242.66</v>
+        <v>219</v>
       </c>
       <c r="C18" t="n">
-        <v>242.66</v>
+        <v>231.89</v>
       </c>
       <c r="D18" t="n">
-        <v>204</v>
+        <v>207.56</v>
       </c>
       <c r="E18" t="n">
-        <v>217.98</v>
+        <v>224.63</v>
       </c>
       <c r="F18" t="n">
-        <v>82.87</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>82.91</v>
+        <v>84.05</v>
       </c>
       <c r="H18" t="n">
-        <v>80.33</v>
+        <v>80.66</v>
       </c>
       <c r="I18" t="n">
-        <v>81.67</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>5.83</v>
+        <v>6.49</v>
       </c>
       <c r="K18" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="L18" t="n">
-        <v>5.83</v>
+        <v>6.1</v>
       </c>
       <c r="M18" t="n">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
       <c r="N18" t="n">
-        <v>38.87</v>
+        <v>39.41</v>
       </c>
       <c r="O18" t="n">
-        <v>40.09</v>
+        <v>39.94</v>
       </c>
       <c r="P18" t="n">
-        <v>38.86</v>
+        <v>38.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>39.44</v>
+        <v>38.47</v>
       </c>
       <c r="R18" t="n">
-        <v>-3.459</v>
+        <v>3.0507</v>
       </c>
       <c r="S18" t="n">
-        <v>22.1929</v>
+        <v>17.8789</v>
       </c>
       <c r="T18" t="n">
-        <v>43.5118</v>
+        <v>29.694</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3417</v>
+        <v>2.4611</v>
       </c>
       <c r="V18" t="n">
-        <v>6.1339</v>
+        <v>7.5026</v>
       </c>
       <c r="W18" t="n">
-        <v>11.9841</v>
+        <v>9.3713</v>
       </c>
       <c r="X18" t="n">
-        <v>3.8156</v>
+        <v>-3.3691</v>
       </c>
       <c r="Y18" t="n">
-        <v>-21.2304</v>
+        <v>-18.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>-34.2397</v>
+        <v>-26.1124</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.4073</v>
+        <v>-2.4594</v>
       </c>
       <c r="AB18" t="n">
-        <v>-6.0057</v>
+        <v>-7.3012</v>
       </c>
       <c r="AC18" t="n">
-        <v>-11.1111</v>
+        <v>-8.817299999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>219</v>
+        <v>231.82</v>
       </c>
       <c r="C19" t="n">
-        <v>231.89</v>
+        <v>239.07</v>
       </c>
       <c r="D19" t="n">
-        <v>207.56</v>
+        <v>218.56</v>
       </c>
       <c r="E19" t="n">
-        <v>224.63</v>
+        <v>224.34</v>
       </c>
       <c r="F19" t="n">
-        <v>81.73999999999999</v>
+        <v>84.41</v>
       </c>
       <c r="G19" t="n">
-        <v>84.05</v>
+        <v>85.7</v>
       </c>
       <c r="H19" t="n">
-        <v>80.66</v>
+        <v>83.53</v>
       </c>
       <c r="I19" t="n">
-        <v>83.68000000000001</v>
+        <v>84.56</v>
       </c>
       <c r="J19" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="K19" t="n">
         <v>6.49</v>
       </c>
-      <c r="K19" t="n">
-        <v>6.83</v>
-      </c>
       <c r="L19" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="M19" t="n">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
       <c r="N19" t="n">
-        <v>39.41</v>
+        <v>38.15</v>
       </c>
       <c r="O19" t="n">
-        <v>39.94</v>
+        <v>38.56</v>
       </c>
       <c r="P19" t="n">
-        <v>38.3</v>
+        <v>37.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>38.47</v>
+        <v>38.08</v>
       </c>
       <c r="R19" t="n">
-        <v>3.0507</v>
+        <v>-0.1291</v>
       </c>
       <c r="S19" t="n">
-        <v>17.8789</v>
+        <v>-0.6422</v>
       </c>
       <c r="T19" t="n">
-        <v>29.694</v>
+        <v>25.7582</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4611</v>
+        <v>1.0516</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5026</v>
+        <v>3.1849</v>
       </c>
       <c r="W19" t="n">
-        <v>9.3713</v>
+        <v>9.8895</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.3691</v>
+        <v>0.317</v>
       </c>
       <c r="Y19" t="n">
-        <v>-18.37</v>
+        <v>0.6359</v>
       </c>
       <c r="Z19" t="n">
-        <v>-26.1124</v>
+        <v>-23.6429</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.4594</v>
+        <v>-1.0138</v>
       </c>
       <c r="AB19" t="n">
-        <v>-7.3012</v>
+        <v>-3.055</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.817299999999999</v>
+        <v>-9.2469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>231.82</v>
+        <v>217.27</v>
       </c>
       <c r="C20" t="n">
-        <v>239.07</v>
+        <v>234.06</v>
       </c>
       <c r="D20" t="n">
-        <v>218.56</v>
+        <v>210.14</v>
       </c>
       <c r="E20" t="n">
-        <v>224.34</v>
+        <v>227.03</v>
       </c>
       <c r="F20" t="n">
-        <v>84.41</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>85.7</v>
+        <v>87.06</v>
       </c>
       <c r="H20" t="n">
-        <v>83.53</v>
+        <v>83.75</v>
       </c>
       <c r="I20" t="n">
-        <v>84.56</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>6.11</v>
+        <v>6.55</v>
       </c>
       <c r="K20" t="n">
-        <v>6.49</v>
+        <v>6.74</v>
       </c>
       <c r="L20" t="n">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M20" t="n">
-        <v>6.33</v>
+        <v>6.26</v>
       </c>
       <c r="N20" t="n">
-        <v>38.15</v>
+        <v>38.27</v>
       </c>
       <c r="O20" t="n">
-        <v>38.56</v>
+        <v>38.46</v>
       </c>
       <c r="P20" t="n">
-        <v>37.56</v>
+        <v>36.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>38.08</v>
+        <v>37.42</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.1291</v>
+        <v>1.1991</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6422</v>
+        <v>4.1518</v>
       </c>
       <c r="T20" t="n">
-        <v>25.7582</v>
+        <v>19.1383</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0516</v>
+        <v>1.7502</v>
       </c>
       <c r="V20" t="n">
-        <v>3.1849</v>
+        <v>5.3508</v>
       </c>
       <c r="W20" t="n">
-        <v>9.8895</v>
+        <v>10.5344</v>
       </c>
       <c r="X20" t="n">
-        <v>0.317</v>
+        <v>-1.1058</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.6359</v>
+        <v>-4.1348</v>
       </c>
       <c r="Z20" t="n">
-        <v>-23.6429</v>
+        <v>-19.0168</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.0138</v>
+        <v>-1.7332</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.055</v>
+        <v>-5.1217</v>
       </c>
       <c r="AC20" t="n">
-        <v>-9.2469</v>
+        <v>-9.831300000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>217.27</v>
+        <v>243.18</v>
       </c>
       <c r="C21" t="n">
-        <v>234.06</v>
+        <v>267.08</v>
       </c>
       <c r="D21" t="n">
-        <v>210.14</v>
+        <v>238.82</v>
       </c>
       <c r="E21" t="n">
-        <v>227.03</v>
+        <v>266.32</v>
       </c>
       <c r="F21" t="n">
-        <v>84.15000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="G21" t="n">
-        <v>87.06</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>83.75</v>
+        <v>84.83</v>
       </c>
       <c r="I21" t="n">
-        <v>86.04000000000001</v>
+        <v>87.22</v>
       </c>
       <c r="J21" t="n">
-        <v>6.55</v>
+        <v>5.8</v>
       </c>
       <c r="K21" t="n">
-        <v>6.74</v>
+        <v>5.93</v>
       </c>
       <c r="L21" t="n">
-        <v>6.05</v>
+        <v>5.15</v>
       </c>
       <c r="M21" t="n">
-        <v>6.26</v>
+        <v>5.17</v>
       </c>
       <c r="N21" t="n">
-        <v>38.27</v>
+        <v>37.47</v>
       </c>
       <c r="O21" t="n">
-        <v>38.46</v>
+        <v>37.95</v>
       </c>
       <c r="P21" t="n">
-        <v>36.96</v>
+        <v>36.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.42</v>
+        <v>36.91</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1991</v>
+        <v>17.3061</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1518</v>
+        <v>18.5594</v>
       </c>
       <c r="T21" t="n">
-        <v>19.1383</v>
+        <v>17.9503</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7502</v>
+        <v>1.3715</v>
       </c>
       <c r="V21" t="n">
-        <v>5.3508</v>
+        <v>4.2304</v>
       </c>
       <c r="W21" t="n">
-        <v>10.5344</v>
+        <v>6.4308</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1058</v>
+        <v>-17.4121</v>
       </c>
       <c r="Y21" t="n">
-        <v>-4.1348</v>
+        <v>-18.0666</v>
       </c>
       <c r="Z21" t="n">
-        <v>-19.0168</v>
+        <v>-17.806</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.7332</v>
+        <v>-1.3629</v>
       </c>
       <c r="AB21" t="n">
-        <v>-5.1217</v>
+        <v>-4.0551</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9.831300000000001</v>
+        <v>-6.0336</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>243.18</v>
+        <v>281.47</v>
       </c>
       <c r="C22" t="n">
-        <v>267.08</v>
+        <v>284.58</v>
       </c>
       <c r="D22" t="n">
-        <v>238.8233</v>
+        <v>257.2601</v>
       </c>
       <c r="E22" t="n">
-        <v>266.32</v>
+        <v>280.54</v>
       </c>
       <c r="F22" t="n">
-        <v>85.95</v>
+        <v>87.675</v>
       </c>
       <c r="G22" t="n">
-        <v>87.31999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="H22" t="n">
-        <v>84.8313</v>
+        <v>85.41</v>
       </c>
       <c r="I22" t="n">
-        <v>87.22</v>
+        <v>86.56</v>
       </c>
       <c r="J22" t="n">
-        <v>5.8</v>
+        <v>4.88</v>
       </c>
       <c r="K22" t="n">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="L22" t="n">
-        <v>5.15</v>
+        <v>4.82</v>
       </c>
       <c r="M22" t="n">
-        <v>5.17</v>
+        <v>4.91</v>
       </c>
       <c r="N22" t="n">
-        <v>37.46</v>
+        <v>36.73</v>
       </c>
       <c r="O22" t="n">
-        <v>37.95</v>
+        <v>37.6869</v>
       </c>
       <c r="P22" t="n">
-        <v>36.86</v>
+        <v>36.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>36.91</v>
+        <v>37.19</v>
       </c>
       <c r="R22" t="n">
-        <v>17.3061</v>
+        <v>5.3394</v>
       </c>
       <c r="S22" t="n">
-        <v>18.5594</v>
+        <v>25.0513</v>
       </c>
       <c r="T22" t="n">
-        <v>17.9503</v>
+        <v>28.6999</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3715</v>
+        <v>-0.7567</v>
       </c>
       <c r="V22" t="n">
-        <v>4.2304</v>
+        <v>2.3652</v>
       </c>
       <c r="W22" t="n">
-        <v>6.4308</v>
+        <v>5.9875</v>
       </c>
       <c r="X22" t="n">
-        <v>-17.4121</v>
+        <v>-5.029</v>
       </c>
       <c r="Y22" t="n">
-        <v>-18.0666</v>
+        <v>-22.4329</v>
       </c>
       <c r="Z22" t="n">
-        <v>-17.806</v>
+        <v>-24.8086</v>
       </c>
       <c r="AA22" t="n">
-        <v>-1.3629</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="AB22" t="n">
-        <v>-4.0551</v>
+        <v>-2.3372</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.0336</v>
+        <v>-5.7049</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>135</v>
+        <v>157.84</v>
       </c>
       <c r="C2" t="n">
-        <v>147.26</v>
+        <v>166</v>
       </c>
       <c r="D2" t="n">
-        <v>134.02</v>
+        <v>149.06</v>
       </c>
       <c r="E2" t="n">
-        <v>144.16</v>
+        <v>165.85</v>
       </c>
       <c r="F2" t="n">
-        <v>66.37</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>67.77</v>
+        <v>71.66</v>
       </c>
       <c r="H2" t="n">
-        <v>66.25</v>
+        <v>68.88</v>
       </c>
       <c r="I2" t="n">
-        <v>67.39</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>12.5</v>
+        <v>10.43</v>
       </c>
       <c r="K2" t="n">
-        <v>12.59</v>
+        <v>11.14</v>
       </c>
       <c r="L2" t="n">
-        <v>11.21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>11.51</v>
+        <v>9.81</v>
       </c>
       <c r="N2" t="n">
-        <v>49.4</v>
+        <v>47.26</v>
       </c>
       <c r="O2" t="n">
-        <v>49.49</v>
+        <v>47.54</v>
       </c>
       <c r="P2" t="n">
-        <v>48.3</v>
+        <v>45.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>48.59</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C3" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D3" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E3" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F3" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G3" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H3" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I3" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J3" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K3" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N3" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O3" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P3" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
       <c r="R3" t="n">
-        <v>15.0458</v>
+        <v>-8.2906</v>
       </c>
       <c r="U3" t="n">
-        <v>6.2027</v>
+        <v>-0.3214</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.7698</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>-6.1741</v>
+        <v>0.3071</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C4" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D4" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E4" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F4" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H4" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I4" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J4" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M4" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N4" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O4" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P4" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R4" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="X4" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C5" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D5" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E5" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F5" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H5" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I5" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K5" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L5" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M5" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O5" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P5" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R5" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="S5" t="n">
-        <v>22.7386</v>
+        <v>14.8146</v>
       </c>
       <c r="U5" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="V5" t="n">
-        <v>13.1919</v>
+        <v>7.5311</v>
       </c>
       <c r="X5" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="Y5" t="n">
-        <v>-23.1103</v>
+        <v>-16.4118</v>
       </c>
       <c r="AA5" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
       <c r="AB5" t="n">
-        <v>-12.3894</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C6" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D6" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E6" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G6" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I6" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K6" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L6" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O6" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P6" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R6" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S6" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y6" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB6" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C7" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D7" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E7" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F7" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G7" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H7" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I7" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L7" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N7" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O7" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P7" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S7" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="T7" t="n">
-        <v>19.6726</v>
+        <v>11.0883</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V7" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="W7" t="n">
-        <v>11.2331</v>
+        <v>7.9223</v>
       </c>
       <c r="X7" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y7" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="Z7" t="n">
-        <v>-22.2415</v>
+        <v>-14.8828</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB7" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
       <c r="AC7" t="n">
-        <v>-10.8664</v>
+        <v>-7.8965</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>183.84</v>
+        <v>182.67</v>
       </c>
       <c r="C8" t="n">
-        <v>188.49</v>
+        <v>189.56</v>
       </c>
       <c r="D8" t="n">
-        <v>172.26</v>
+        <v>178.28</v>
       </c>
       <c r="E8" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F8" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>74.19</v>
+        <v>77.16</v>
       </c>
       <c r="I8" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J8" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K8" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N8" t="n">
-        <v>42.83</v>
+        <v>41.98</v>
       </c>
       <c r="O8" t="n">
-        <v>43.77</v>
+        <v>42.06</v>
       </c>
       <c r="P8" t="n">
-        <v>41.6</v>
+        <v>40.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R8" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T8" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U8" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y8" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z8" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC8" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>182.67</v>
+        <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>189.56</v>
+        <v>174.4</v>
       </c>
       <c r="D9" t="n">
-        <v>178.28</v>
+        <v>161.14</v>
       </c>
       <c r="E9" t="n">
-        <v>186.19</v>
+        <v>164.18</v>
       </c>
       <c r="F9" t="n">
-        <v>77.29000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G9" t="n">
-        <v>79.68000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="H9" t="n">
-        <v>77.16</v>
+        <v>74.23</v>
       </c>
       <c r="I9" t="n">
-        <v>78.95</v>
+        <v>75.34</v>
       </c>
       <c r="J9" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>8.630000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>8.27</v>
+        <v>9.23</v>
       </c>
       <c r="N9" t="n">
-        <v>41.98</v>
+        <v>42.77</v>
       </c>
       <c r="O9" t="n">
-        <v>42.06</v>
+        <v>43.57</v>
       </c>
       <c r="P9" t="n">
-        <v>40.68</v>
+        <v>41.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.07</v>
+        <v>42.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0584</v>
+        <v>-11.8213</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.2214</v>
+        <v>-4.8342</v>
       </c>
       <c r="T9" t="n">
-        <v>22.4129</v>
+        <v>-7.2115</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2139</v>
+        <v>-4.5725</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5858</v>
+        <v>0.5069</v>
       </c>
       <c r="W9" t="n">
-        <v>10.6672</v>
+        <v>-1.2323</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9581</v>
+        <v>11.6082</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8537</v>
+        <v>3.1285</v>
       </c>
       <c r="Z9" t="n">
-        <v>-21.9811</v>
+        <v>4.2938</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2.191</v>
+        <v>4.6506</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.7238</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.1902</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167</v>
+        <v>172.95</v>
       </c>
       <c r="C10" t="n">
-        <v>174.4</v>
+        <v>174.61</v>
       </c>
       <c r="D10" t="n">
-        <v>161.14</v>
+        <v>142.69</v>
       </c>
       <c r="E10" t="n">
-        <v>164.18</v>
+        <v>151.75</v>
       </c>
       <c r="F10" t="n">
-        <v>75.73</v>
+        <v>76.13</v>
       </c>
       <c r="G10" t="n">
-        <v>77.37</v>
+        <v>76.27</v>
       </c>
       <c r="H10" t="n">
-        <v>74.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>75.34</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K10" t="n">
-        <v>9.390000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M10" t="n">
-        <v>9.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>42.77</v>
+        <v>42.51</v>
       </c>
       <c r="O10" t="n">
-        <v>43.57</v>
+        <v>44.82</v>
       </c>
       <c r="P10" t="n">
-        <v>41.93</v>
+        <v>42.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>42.98</v>
+        <v>43.54</v>
       </c>
       <c r="R10" t="n">
-        <v>-11.8213</v>
+        <v>-7.571</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.8342</v>
+        <v>-17.6346</v>
       </c>
       <c r="T10" t="n">
-        <v>-7.2115</v>
+        <v>-20.3077</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.5725</v>
+        <v>-1.3539</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5069</v>
+        <v>-3.7804</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.2323</v>
+        <v>-3.4304</v>
       </c>
       <c r="X10" t="n">
-        <v>11.6082</v>
+        <v>7.8007</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.1285</v>
+        <v>19.1617</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2938</v>
+        <v>21.3415</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.6506</v>
+        <v>1.3029</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.7619</v>
+        <v>3.6914</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.9631</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>172.95</v>
+        <v>141.24</v>
       </c>
       <c r="C11" t="n">
-        <v>174.61</v>
+        <v>160.6</v>
       </c>
       <c r="D11" t="n">
-        <v>142.69</v>
+        <v>135.02</v>
       </c>
       <c r="E11" t="n">
-        <v>151.75</v>
+        <v>151.89</v>
       </c>
       <c r="F11" t="n">
-        <v>76.13</v>
+        <v>72.41</v>
       </c>
       <c r="G11" t="n">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="H11" t="n">
-        <v>72.09999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>74.31999999999999</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>8.77</v>
+        <v>10.64</v>
       </c>
       <c r="K11" t="n">
-        <v>10.47</v>
+        <v>11.07</v>
       </c>
       <c r="L11" t="n">
-        <v>8.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="N11" t="n">
-        <v>42.51</v>
+        <v>44.68</v>
       </c>
       <c r="O11" t="n">
-        <v>44.82</v>
+        <v>45.53</v>
       </c>
       <c r="P11" t="n">
-        <v>42.44</v>
+        <v>43.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>43.54</v>
+        <v>44.37</v>
       </c>
       <c r="R11" t="n">
-        <v>-7.571</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-17.6346</v>
+        <v>-18.422</v>
       </c>
       <c r="T11" t="n">
-        <v>-20.3077</v>
+        <v>-11.958</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3539</v>
+        <v>-1.8703</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.7804</v>
+        <v>-7.6251</v>
       </c>
       <c r="W11" t="n">
-        <v>-3.4304</v>
+        <v>-2.7081</v>
       </c>
       <c r="X11" t="n">
-        <v>7.8007</v>
+        <v>-0.201</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.1617</v>
+        <v>20.0726</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.3415</v>
+        <v>10.9497</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3029</v>
+        <v>1.9063</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6914</v>
+        <v>8.0351</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1265</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>141.24</v>
+        <v>161</v>
       </c>
       <c r="C12" t="n">
-        <v>160.6</v>
+        <v>173.7</v>
       </c>
       <c r="D12" t="n">
-        <v>135.02</v>
+        <v>161</v>
       </c>
       <c r="E12" t="n">
-        <v>151.89</v>
+        <v>173.2</v>
       </c>
       <c r="F12" t="n">
-        <v>72.41</v>
+        <v>74.09</v>
       </c>
       <c r="G12" t="n">
-        <v>74.5</v>
+        <v>76.53</v>
       </c>
       <c r="H12" t="n">
-        <v>70.95999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="I12" t="n">
-        <v>72.93000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>10.64</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>11.07</v>
+        <v>9.35</v>
       </c>
       <c r="L12" t="n">
-        <v>9.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M12" t="n">
-        <v>9.93</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>44.68</v>
+        <v>43.67</v>
       </c>
       <c r="O12" t="n">
-        <v>45.53</v>
+        <v>43.97</v>
       </c>
       <c r="P12" t="n">
-        <v>43.46</v>
+        <v>42.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>44.37</v>
+        <v>42.19</v>
       </c>
       <c r="R12" t="n">
-        <v>0.09229999999999999</v>
+        <v>14.0299</v>
       </c>
       <c r="S12" t="n">
-        <v>-18.422</v>
+        <v>5.494</v>
       </c>
       <c r="T12" t="n">
-        <v>-11.958</v>
+        <v>-5.9922</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8703</v>
+        <v>4.9088</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.6251</v>
+        <v>1.553</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.7081</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.201</v>
+        <v>-13.998</v>
       </c>
       <c r="Y12" t="n">
-        <v>20.0726</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.9497</v>
+        <v>2.2754</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9063</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.0351</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4475</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>161</v>
+        <v>171.26</v>
       </c>
       <c r="C13" t="n">
-        <v>173.7</v>
+        <v>179.97</v>
       </c>
       <c r="D13" t="n">
-        <v>161</v>
+        <v>168.23</v>
       </c>
       <c r="E13" t="n">
-        <v>173.2</v>
+        <v>178.39</v>
       </c>
       <c r="F13" t="n">
-        <v>74.09</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>73.62</v>
+        <v>74.47</v>
       </c>
       <c r="I13" t="n">
-        <v>76.51000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="J13" t="n">
-        <v>9.300000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="K13" t="n">
-        <v>9.35</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>8.51</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.539999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>43.67</v>
+        <v>42.94</v>
       </c>
       <c r="O13" t="n">
-        <v>43.97</v>
+        <v>43.33</v>
       </c>
       <c r="P13" t="n">
-        <v>42.19</v>
+        <v>41.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.19</v>
+        <v>41.96</v>
       </c>
       <c r="R13" t="n">
-        <v>14.0299</v>
+        <v>2.9965</v>
       </c>
       <c r="S13" t="n">
-        <v>5.494</v>
+        <v>17.5552</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.9922</v>
+        <v>-4.1893</v>
       </c>
       <c r="U13" t="n">
-        <v>4.9088</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.553</v>
+        <v>3.5388</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-2.5332</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.998</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y13" t="n">
-        <v>-7.4756</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2754</v>
+        <v>0.2418</v>
       </c>
       <c r="AA13" t="n">
-        <v>-4.9132</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.8381</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.4763</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>171.26</v>
+        <v>184.8</v>
       </c>
       <c r="C14" t="n">
-        <v>179.97</v>
+        <v>195.27</v>
       </c>
       <c r="D14" t="n">
-        <v>168.23</v>
+        <v>183.34</v>
       </c>
       <c r="E14" t="n">
-        <v>178.39</v>
+        <v>190.56</v>
       </c>
       <c r="F14" t="n">
-        <v>75.18000000000001</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>77.79000000000001</v>
+        <v>79.33</v>
       </c>
       <c r="H14" t="n">
-        <v>74.47</v>
+        <v>77.33</v>
       </c>
       <c r="I14" t="n">
-        <v>76.95</v>
+        <v>77.84</v>
       </c>
       <c r="J14" t="n">
-        <v>8.65</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>8.779999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="L14" t="n">
-        <v>8.210000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="M14" t="n">
-        <v>8.289999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="N14" t="n">
-        <v>42.94</v>
+        <v>41.4</v>
       </c>
       <c r="O14" t="n">
-        <v>43.33</v>
+        <v>41.78</v>
       </c>
       <c r="P14" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="Q14" t="n">
         <v>41.5</v>
       </c>
-      <c r="Q14" t="n">
-        <v>41.96</v>
-      </c>
       <c r="R14" t="n">
-        <v>2.9965</v>
+        <v>6.8221</v>
       </c>
       <c r="S14" t="n">
-        <v>17.5552</v>
+        <v>25.4592</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.1893</v>
+        <v>16.0677</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5750999999999999</v>
+        <v>1.1566</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5388</v>
+        <v>6.7325</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.5332</v>
+        <v>3.3183</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.9274</v>
+        <v>-6.7551</v>
       </c>
       <c r="Y14" t="n">
-        <v>-16.6834</v>
+        <v>-22.1551</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.2418</v>
+        <v>-16.2514</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.5452</v>
+        <v>-1.0963</v>
       </c>
       <c r="AB14" t="n">
-        <v>-3.6288</v>
+        <v>-6.4683</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.167</v>
+        <v>-3.4435</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>184.8</v>
+        <v>211.38</v>
       </c>
       <c r="C15" t="n">
-        <v>195.27</v>
+        <v>228.5</v>
       </c>
       <c r="D15" t="n">
-        <v>183.34</v>
+        <v>209.89</v>
       </c>
       <c r="E15" t="n">
-        <v>190.56</v>
+        <v>225.79</v>
       </c>
       <c r="F15" t="n">
-        <v>78.04000000000001</v>
+        <v>80.59</v>
       </c>
       <c r="G15" t="n">
-        <v>79.33</v>
+        <v>82.27</v>
       </c>
       <c r="H15" t="n">
-        <v>77.33</v>
+        <v>79.98</v>
       </c>
       <c r="I15" t="n">
-        <v>77.84</v>
+        <v>81.95</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="K15" t="n">
-        <v>8.06</v>
+        <v>6.95</v>
       </c>
       <c r="L15" t="n">
-        <v>7.5</v>
+        <v>6.19</v>
       </c>
       <c r="M15" t="n">
-        <v>7.73</v>
+        <v>6.29</v>
       </c>
       <c r="N15" t="n">
-        <v>41.4</v>
+        <v>40.05</v>
       </c>
       <c r="O15" t="n">
-        <v>41.78</v>
+        <v>40.35</v>
       </c>
       <c r="P15" t="n">
-        <v>40.68</v>
+        <v>39.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.5</v>
+        <v>39.28</v>
       </c>
       <c r="R15" t="n">
-        <v>6.8221</v>
+        <v>18.4876</v>
       </c>
       <c r="S15" t="n">
-        <v>25.4592</v>
+        <v>30.3637</v>
       </c>
       <c r="T15" t="n">
-        <v>16.0677</v>
+        <v>48.7908</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1566</v>
+        <v>5.2801</v>
       </c>
       <c r="V15" t="n">
-        <v>6.7325</v>
+        <v>7.1102</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3183</v>
+        <v>10.2664</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.7551</v>
+        <v>-18.6287</v>
       </c>
       <c r="Y15" t="n">
-        <v>-22.1551</v>
+        <v>-26.3466</v>
       </c>
       <c r="Z15" t="n">
-        <v>-16.2514</v>
+        <v>-36.7839</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.0963</v>
+        <v>-5.3494</v>
       </c>
       <c r="AB15" t="n">
-        <v>-6.4683</v>
+        <v>-6.8974</v>
       </c>
       <c r="AC15" t="n">
-        <v>-3.4435</v>
+        <v>-9.7841</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>211.38</v>
+        <v>242.66</v>
       </c>
       <c r="C16" t="n">
-        <v>228.5</v>
+        <v>242.66</v>
       </c>
       <c r="D16" t="n">
-        <v>209.89</v>
+        <v>204</v>
       </c>
       <c r="E16" t="n">
-        <v>225.79</v>
+        <v>217.98</v>
       </c>
       <c r="F16" t="n">
-        <v>80.59</v>
+        <v>82.87</v>
       </c>
       <c r="G16" t="n">
-        <v>82.27</v>
+        <v>82.91</v>
       </c>
       <c r="H16" t="n">
-        <v>79.98</v>
+        <v>80.33</v>
       </c>
       <c r="I16" t="n">
-        <v>81.95</v>
+        <v>81.67</v>
       </c>
       <c r="J16" t="n">
-        <v>6.9</v>
+        <v>5.83</v>
       </c>
       <c r="K16" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="L16" t="n">
-        <v>6.19</v>
+        <v>5.83</v>
       </c>
       <c r="M16" t="n">
-        <v>6.29</v>
+        <v>6.53</v>
       </c>
       <c r="N16" t="n">
-        <v>40.05</v>
+        <v>38.87</v>
       </c>
       <c r="O16" t="n">
-        <v>40.35</v>
+        <v>40.09</v>
       </c>
       <c r="P16" t="n">
-        <v>39.14</v>
+        <v>38.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>39.28</v>
+        <v>39.44</v>
       </c>
       <c r="R16" t="n">
-        <v>18.4876</v>
+        <v>-3.459</v>
       </c>
       <c r="S16" t="n">
-        <v>30.3637</v>
+        <v>22.1929</v>
       </c>
       <c r="T16" t="n">
-        <v>48.7908</v>
+        <v>43.5118</v>
       </c>
       <c r="U16" t="n">
-        <v>5.2801</v>
+        <v>-0.3417</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1102</v>
+        <v>6.1339</v>
       </c>
       <c r="W16" t="n">
-        <v>10.2664</v>
+        <v>11.9841</v>
       </c>
       <c r="X16" t="n">
-        <v>-18.6287</v>
+        <v>3.8156</v>
       </c>
       <c r="Y16" t="n">
-        <v>-26.3466</v>
+        <v>-21.2304</v>
       </c>
       <c r="Z16" t="n">
-        <v>-36.7839</v>
+        <v>-34.2397</v>
       </c>
       <c r="AA16" t="n">
-        <v>-5.3494</v>
+        <v>0.4073</v>
       </c>
       <c r="AB16" t="n">
-        <v>-6.8974</v>
+        <v>-6.0057</v>
       </c>
       <c r="AC16" t="n">
-        <v>-9.7841</v>
+        <v>-11.1111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>242.66</v>
+        <v>219</v>
       </c>
       <c r="C17" t="n">
-        <v>242.66</v>
+        <v>231.89</v>
       </c>
       <c r="D17" t="n">
-        <v>204</v>
+        <v>207.56</v>
       </c>
       <c r="E17" t="n">
-        <v>217.98</v>
+        <v>224.63</v>
       </c>
       <c r="F17" t="n">
-        <v>82.87</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>82.91</v>
+        <v>84.05</v>
       </c>
       <c r="H17" t="n">
-        <v>80.33</v>
+        <v>80.66</v>
       </c>
       <c r="I17" t="n">
-        <v>81.67</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>5.83</v>
+        <v>6.49</v>
       </c>
       <c r="K17" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="L17" t="n">
-        <v>5.83</v>
+        <v>6.1</v>
       </c>
       <c r="M17" t="n">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
       <c r="N17" t="n">
-        <v>38.87</v>
+        <v>39.41</v>
       </c>
       <c r="O17" t="n">
-        <v>40.09</v>
+        <v>39.94</v>
       </c>
       <c r="P17" t="n">
-        <v>38.86</v>
+        <v>38.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>39.44</v>
+        <v>38.47</v>
       </c>
       <c r="R17" t="n">
-        <v>-3.459</v>
+        <v>3.0507</v>
       </c>
       <c r="S17" t="n">
-        <v>22.1929</v>
+        <v>17.8789</v>
       </c>
       <c r="T17" t="n">
-        <v>43.5118</v>
+        <v>29.694</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3417</v>
+        <v>2.4611</v>
       </c>
       <c r="V17" t="n">
-        <v>6.1339</v>
+        <v>7.5026</v>
       </c>
       <c r="W17" t="n">
-        <v>11.9841</v>
+        <v>9.3713</v>
       </c>
       <c r="X17" t="n">
-        <v>3.8156</v>
+        <v>-3.3691</v>
       </c>
       <c r="Y17" t="n">
-        <v>-21.2304</v>
+        <v>-18.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>-34.2397</v>
+        <v>-26.1124</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.4073</v>
+        <v>-2.4594</v>
       </c>
       <c r="AB17" t="n">
-        <v>-6.0057</v>
+        <v>-7.3012</v>
       </c>
       <c r="AC17" t="n">
-        <v>-11.1111</v>
+        <v>-8.817299999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>219</v>
+        <v>231.82</v>
       </c>
       <c r="C18" t="n">
-        <v>231.89</v>
+        <v>239.07</v>
       </c>
       <c r="D18" t="n">
-        <v>207.56</v>
+        <v>218.56</v>
       </c>
       <c r="E18" t="n">
-        <v>224.63</v>
+        <v>224.34</v>
       </c>
       <c r="F18" t="n">
-        <v>81.73999999999999</v>
+        <v>84.41</v>
       </c>
       <c r="G18" t="n">
-        <v>84.05</v>
+        <v>85.7</v>
       </c>
       <c r="H18" t="n">
-        <v>80.66</v>
+        <v>83.53</v>
       </c>
       <c r="I18" t="n">
-        <v>83.68000000000001</v>
+        <v>84.56</v>
       </c>
       <c r="J18" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="K18" t="n">
         <v>6.49</v>
       </c>
-      <c r="K18" t="n">
-        <v>6.83</v>
-      </c>
       <c r="L18" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="M18" t="n">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
       <c r="N18" t="n">
-        <v>39.41</v>
+        <v>38.15</v>
       </c>
       <c r="O18" t="n">
-        <v>39.94</v>
+        <v>38.56</v>
       </c>
       <c r="P18" t="n">
-        <v>38.3</v>
+        <v>37.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.47</v>
+        <v>38.08</v>
       </c>
       <c r="R18" t="n">
-        <v>3.0507</v>
+        <v>-0.1291</v>
       </c>
       <c r="S18" t="n">
-        <v>17.8789</v>
+        <v>-0.6422</v>
       </c>
       <c r="T18" t="n">
-        <v>29.694</v>
+        <v>25.7582</v>
       </c>
       <c r="U18" t="n">
-        <v>2.4611</v>
+        <v>1.0516</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5026</v>
+        <v>3.1849</v>
       </c>
       <c r="W18" t="n">
-        <v>9.3713</v>
+        <v>9.8895</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.3691</v>
+        <v>0.317</v>
       </c>
       <c r="Y18" t="n">
-        <v>-18.37</v>
+        <v>0.6359</v>
       </c>
       <c r="Z18" t="n">
-        <v>-26.1124</v>
+        <v>-23.6429</v>
       </c>
       <c r="AA18" t="n">
-        <v>-2.4594</v>
+        <v>-1.0138</v>
       </c>
       <c r="AB18" t="n">
-        <v>-7.3012</v>
+        <v>-3.055</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.817299999999999</v>
+        <v>-9.2469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>231.82</v>
+        <v>217.27</v>
       </c>
       <c r="C19" t="n">
-        <v>239.07</v>
+        <v>234.06</v>
       </c>
       <c r="D19" t="n">
-        <v>218.56</v>
+        <v>210.14</v>
       </c>
       <c r="E19" t="n">
-        <v>224.34</v>
+        <v>227.03</v>
       </c>
       <c r="F19" t="n">
-        <v>84.41</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>85.7</v>
+        <v>87.06</v>
       </c>
       <c r="H19" t="n">
-        <v>83.53</v>
+        <v>83.75</v>
       </c>
       <c r="I19" t="n">
-        <v>84.56</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>6.11</v>
+        <v>6.55</v>
       </c>
       <c r="K19" t="n">
-        <v>6.49</v>
+        <v>6.74</v>
       </c>
       <c r="L19" t="n">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M19" t="n">
-        <v>6.33</v>
+        <v>6.26</v>
       </c>
       <c r="N19" t="n">
-        <v>38.15</v>
+        <v>38.27</v>
       </c>
       <c r="O19" t="n">
-        <v>38.56</v>
+        <v>38.46</v>
       </c>
       <c r="P19" t="n">
-        <v>37.56</v>
+        <v>36.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>38.08</v>
+        <v>37.42</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1291</v>
+        <v>1.1991</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6422</v>
+        <v>4.1518</v>
       </c>
       <c r="T19" t="n">
-        <v>25.7582</v>
+        <v>19.1383</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0516</v>
+        <v>1.7502</v>
       </c>
       <c r="V19" t="n">
-        <v>3.1849</v>
+        <v>5.3508</v>
       </c>
       <c r="W19" t="n">
-        <v>9.8895</v>
+        <v>10.5344</v>
       </c>
       <c r="X19" t="n">
-        <v>0.317</v>
+        <v>-1.1058</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.6359</v>
+        <v>-4.1348</v>
       </c>
       <c r="Z19" t="n">
-        <v>-23.6429</v>
+        <v>-19.0168</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.0138</v>
+        <v>-1.7332</v>
       </c>
       <c r="AB19" t="n">
-        <v>-3.055</v>
+        <v>-5.1217</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.2469</v>
+        <v>-9.831300000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>217.27</v>
+        <v>243.18</v>
       </c>
       <c r="C20" t="n">
-        <v>234.06</v>
+        <v>267.08</v>
       </c>
       <c r="D20" t="n">
-        <v>210.14</v>
+        <v>238.82</v>
       </c>
       <c r="E20" t="n">
-        <v>227.03</v>
+        <v>266.32</v>
       </c>
       <c r="F20" t="n">
-        <v>84.15000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="G20" t="n">
-        <v>87.06</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>83.75</v>
+        <v>84.83</v>
       </c>
       <c r="I20" t="n">
-        <v>86.04000000000001</v>
+        <v>87.22</v>
       </c>
       <c r="J20" t="n">
-        <v>6.55</v>
+        <v>5.8</v>
       </c>
       <c r="K20" t="n">
-        <v>6.74</v>
+        <v>5.93</v>
       </c>
       <c r="L20" t="n">
-        <v>6.05</v>
+        <v>5.15</v>
       </c>
       <c r="M20" t="n">
-        <v>6.26</v>
+        <v>5.17</v>
       </c>
       <c r="N20" t="n">
-        <v>38.27</v>
+        <v>37.47</v>
       </c>
       <c r="O20" t="n">
-        <v>38.46</v>
+        <v>37.95</v>
       </c>
       <c r="P20" t="n">
-        <v>36.96</v>
+        <v>36.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.42</v>
+        <v>36.91</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1991</v>
+        <v>17.3061</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1518</v>
+        <v>18.5594</v>
       </c>
       <c r="T20" t="n">
-        <v>19.1383</v>
+        <v>17.9503</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7502</v>
+        <v>1.3715</v>
       </c>
       <c r="V20" t="n">
-        <v>5.3508</v>
+        <v>4.2304</v>
       </c>
       <c r="W20" t="n">
-        <v>10.5344</v>
+        <v>6.4308</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1058</v>
+        <v>-17.4121</v>
       </c>
       <c r="Y20" t="n">
-        <v>-4.1348</v>
+        <v>-18.0666</v>
       </c>
       <c r="Z20" t="n">
-        <v>-19.0168</v>
+        <v>-17.806</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.7332</v>
+        <v>-1.3629</v>
       </c>
       <c r="AB20" t="n">
-        <v>-5.1217</v>
+        <v>-4.0551</v>
       </c>
       <c r="AC20" t="n">
-        <v>-9.831300000000001</v>
+        <v>-6.0336</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>243.18</v>
+        <v>281.47</v>
       </c>
       <c r="C21" t="n">
-        <v>267.08</v>
+        <v>284.58</v>
       </c>
       <c r="D21" t="n">
-        <v>238.82</v>
+        <v>257.26</v>
       </c>
       <c r="E21" t="n">
-        <v>266.32</v>
+        <v>280.54</v>
       </c>
       <c r="F21" t="n">
-        <v>85.94</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>87.31999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="H21" t="n">
-        <v>84.83</v>
+        <v>85.41</v>
       </c>
       <c r="I21" t="n">
-        <v>87.22</v>
+        <v>86.56</v>
       </c>
       <c r="J21" t="n">
-        <v>5.8</v>
+        <v>4.88</v>
       </c>
       <c r="K21" t="n">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="L21" t="n">
-        <v>5.15</v>
+        <v>4.82</v>
       </c>
       <c r="M21" t="n">
-        <v>5.17</v>
+        <v>4.91</v>
       </c>
       <c r="N21" t="n">
-        <v>37.47</v>
+        <v>36.73</v>
       </c>
       <c r="O21" t="n">
-        <v>37.95</v>
+        <v>37.69</v>
       </c>
       <c r="P21" t="n">
-        <v>36.86</v>
+        <v>36.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>36.91</v>
+        <v>37.19</v>
       </c>
       <c r="R21" t="n">
-        <v>17.3061</v>
+        <v>5.3394</v>
       </c>
       <c r="S21" t="n">
-        <v>18.5594</v>
+        <v>25.0513</v>
       </c>
       <c r="T21" t="n">
-        <v>17.9503</v>
+        <v>28.6999</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3715</v>
+        <v>-0.7567</v>
       </c>
       <c r="V21" t="n">
-        <v>4.2304</v>
+        <v>2.3652</v>
       </c>
       <c r="W21" t="n">
-        <v>6.4308</v>
+        <v>5.9875</v>
       </c>
       <c r="X21" t="n">
-        <v>-17.4121</v>
+        <v>-5.029</v>
       </c>
       <c r="Y21" t="n">
-        <v>-18.0666</v>
+        <v>-22.4329</v>
       </c>
       <c r="Z21" t="n">
-        <v>-17.806</v>
+        <v>-24.8086</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.3629</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.0551</v>
+        <v>-2.3372</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.0336</v>
+        <v>-5.7049</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>281.47</v>
+        <v>242.04</v>
       </c>
       <c r="C22" t="n">
-        <v>284.58</v>
+        <v>274.5</v>
       </c>
       <c r="D22" t="n">
-        <v>257.2601</v>
+        <v>228.55</v>
       </c>
       <c r="E22" t="n">
-        <v>280.54</v>
+        <v>262.7</v>
       </c>
       <c r="F22" t="n">
-        <v>87.675</v>
+        <v>83.47</v>
       </c>
       <c r="G22" t="n">
-        <v>88.09</v>
+        <v>86.245</v>
       </c>
       <c r="H22" t="n">
-        <v>85.41</v>
+        <v>82.47499999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>86.56</v>
+        <v>85.22</v>
       </c>
       <c r="J22" t="n">
-        <v>4.88</v>
+        <v>5.57</v>
       </c>
       <c r="K22" t="n">
-        <v>5.35</v>
+        <v>5.81</v>
       </c>
       <c r="L22" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>4.91</v>
+        <v>5.2</v>
       </c>
       <c r="N22" t="n">
-        <v>36.73</v>
+        <v>38.53</v>
       </c>
       <c r="O22" t="n">
-        <v>37.6869</v>
+        <v>38.96</v>
       </c>
       <c r="P22" t="n">
-        <v>36.55</v>
+        <v>37.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.19</v>
+        <v>37.76</v>
       </c>
       <c r="R22" t="n">
-        <v>5.3394</v>
+        <v>-6.3592</v>
       </c>
       <c r="S22" t="n">
-        <v>25.0513</v>
+        <v>15.7116</v>
       </c>
       <c r="T22" t="n">
-        <v>28.6999</v>
+        <v>16.9479</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7567</v>
+        <v>-1.5481</v>
       </c>
       <c r="V22" t="n">
-        <v>2.3652</v>
+        <v>-0.953</v>
       </c>
       <c r="W22" t="n">
-        <v>5.9875</v>
+        <v>1.8403</v>
       </c>
       <c r="X22" t="n">
-        <v>-5.029</v>
+        <v>5.9063</v>
       </c>
       <c r="Y22" t="n">
-        <v>-22.4329</v>
+        <v>-16.9329</v>
       </c>
       <c r="Z22" t="n">
-        <v>-24.8086</v>
+        <v>-17.5911</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.5327</v>
       </c>
       <c r="AB22" t="n">
-        <v>-2.3372</v>
+        <v>0.9086</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.7049</v>
+        <v>-1.8456</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -24759,1804 +24759,1804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>157.84</v>
+        <v>162.12</v>
       </c>
       <c r="C2" t="n">
-        <v>166</v>
+        <v>162.9</v>
       </c>
       <c r="D2" t="n">
-        <v>149.06</v>
+        <v>147.61</v>
       </c>
       <c r="E2" t="n">
-        <v>165.85</v>
+        <v>152.1</v>
       </c>
       <c r="F2" t="n">
-        <v>69.26000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="G2" t="n">
-        <v>71.66</v>
+        <v>73.3</v>
       </c>
       <c r="H2" t="n">
-        <v>68.88</v>
+        <v>70.38</v>
       </c>
       <c r="I2" t="n">
-        <v>71.56999999999999</v>
+        <v>71.34</v>
       </c>
       <c r="J2" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
       <c r="K2" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="L2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>9.81</v>
+        <v>10.6</v>
       </c>
       <c r="N2" t="n">
-        <v>47.26</v>
+        <v>45.41</v>
       </c>
       <c r="O2" t="n">
-        <v>47.54</v>
+        <v>46.36</v>
       </c>
       <c r="P2" t="n">
-        <v>45.52</v>
+        <v>44.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>45.59</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>162.12</v>
+        <v>163</v>
       </c>
       <c r="C3" t="n">
-        <v>162.9</v>
+        <v>177.5</v>
       </c>
       <c r="D3" t="n">
-        <v>147.61</v>
+        <v>161.51</v>
       </c>
       <c r="E3" t="n">
-        <v>152.1</v>
+        <v>176.94</v>
       </c>
       <c r="F3" t="n">
-        <v>71.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>73.3</v>
+        <v>76.31</v>
       </c>
       <c r="H3" t="n">
-        <v>70.38</v>
+        <v>72.7</v>
       </c>
       <c r="I3" t="n">
-        <v>71.34</v>
+        <v>76.28</v>
       </c>
       <c r="J3" t="n">
-        <v>10.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>10.88</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>9.970000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M3" t="n">
-        <v>10.6</v>
+        <v>8.85</v>
       </c>
       <c r="N3" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="O3" t="n">
-        <v>46.36</v>
+        <v>44.89</v>
       </c>
       <c r="P3" t="n">
-        <v>44.5</v>
+        <v>42.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>45.73</v>
+        <v>42.57</v>
       </c>
       <c r="R3" t="n">
-        <v>-8.2906</v>
+        <v>16.3314</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3214</v>
+        <v>6.9246</v>
       </c>
       <c r="X3" t="n">
-        <v>8.053000000000001</v>
+        <v>-16.5094</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.3071</v>
+        <v>-6.9101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C4" t="n">
-        <v>177.5</v>
+        <v>191.29</v>
       </c>
       <c r="D4" t="n">
-        <v>161.51</v>
+        <v>178.94</v>
       </c>
       <c r="E4" t="n">
-        <v>176.94</v>
+        <v>190.42</v>
       </c>
       <c r="F4" t="n">
-        <v>72.81999999999999</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="H4" t="n">
-        <v>72.7</v>
+        <v>75.55</v>
       </c>
       <c r="I4" t="n">
-        <v>76.28</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>9.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K4" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="L4" t="n">
-        <v>8.84</v>
+        <v>8.15</v>
       </c>
       <c r="M4" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>44.82</v>
+        <v>42.74</v>
       </c>
       <c r="O4" t="n">
-        <v>44.89</v>
+        <v>43</v>
       </c>
       <c r="P4" t="n">
-        <v>42.57</v>
+        <v>41.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>42.57</v>
+        <v>42.22</v>
       </c>
       <c r="R4" t="n">
-        <v>16.3314</v>
+        <v>7.6184</v>
       </c>
       <c r="U4" t="n">
-        <v>6.9246</v>
+        <v>0.8915</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.5094</v>
+        <v>-7.3446</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6.9101</v>
+        <v>-0.8222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>181</v>
+        <v>177.62</v>
       </c>
       <c r="C5" t="n">
-        <v>191.29</v>
+        <v>182.24</v>
       </c>
       <c r="D5" t="n">
-        <v>178.94</v>
+        <v>150.58</v>
       </c>
       <c r="E5" t="n">
-        <v>190.42</v>
+        <v>172.52</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G5" t="n">
-        <v>77.36</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>75.55</v>
+        <v>71.55</v>
       </c>
       <c r="I5" t="n">
-        <v>76.95999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="K5" t="n">
-        <v>8.77</v>
+        <v>9.91</v>
       </c>
       <c r="L5" t="n">
-        <v>8.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>42.74</v>
+        <v>43.14</v>
       </c>
       <c r="O5" t="n">
-        <v>43</v>
+        <v>45.19</v>
       </c>
       <c r="P5" t="n">
-        <v>41.99</v>
+        <v>42.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>42.22</v>
+        <v>43.31</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6184</v>
+        <v>-9.4003</v>
       </c>
       <c r="S5" t="n">
-        <v>14.8146</v>
+        <v>13.4254</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8915</v>
+        <v>-2.5988</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5311</v>
+        <v>5.0743</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.3446</v>
+        <v>9.1463</v>
       </c>
       <c r="Y5" t="n">
-        <v>-16.4118</v>
+        <v>-15.566</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.8222</v>
+        <v>2.5817</v>
       </c>
       <c r="AB5" t="n">
-        <v>-7.392</v>
+        <v>-5.2919</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>177.62</v>
+        <v>183.84</v>
       </c>
       <c r="C6" t="n">
-        <v>182.24</v>
+        <v>188.49</v>
       </c>
       <c r="D6" t="n">
-        <v>150.58</v>
+        <v>172.26</v>
       </c>
       <c r="E6" t="n">
-        <v>172.52</v>
+        <v>184.24</v>
       </c>
       <c r="F6" t="n">
-        <v>75.3</v>
+        <v>75.81</v>
       </c>
       <c r="G6" t="n">
-        <v>75.93000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="H6" t="n">
-        <v>71.55</v>
+        <v>74.19</v>
       </c>
       <c r="I6" t="n">
-        <v>74.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>9.91</v>
+        <v>8.98</v>
       </c>
       <c r="L6" t="n">
-        <v>8.550000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>8.949999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N6" t="n">
-        <v>43.14</v>
+        <v>42.83</v>
       </c>
       <c r="O6" t="n">
-        <v>45.19</v>
+        <v>43.77</v>
       </c>
       <c r="P6" t="n">
-        <v>42.79</v>
+        <v>41.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.31</v>
+        <v>41.99</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.4003</v>
+        <v>6.7934</v>
       </c>
       <c r="S6" t="n">
-        <v>13.4254</v>
+        <v>4.1257</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.5988</v>
+        <v>3.0416</v>
       </c>
       <c r="V6" t="n">
-        <v>5.0743</v>
+        <v>1.2585</v>
       </c>
       <c r="X6" t="n">
-        <v>9.1463</v>
+        <v>-6.7039</v>
       </c>
       <c r="Y6" t="n">
-        <v>-15.566</v>
+        <v>-5.6497</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.5817</v>
+        <v>-3.0478</v>
       </c>
       <c r="AB6" t="n">
-        <v>-5.2919</v>
+        <v>-1.3625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>183.84</v>
+        <v>182.67</v>
       </c>
       <c r="C7" t="n">
-        <v>188.49</v>
+        <v>189.56</v>
       </c>
       <c r="D7" t="n">
-        <v>172.26</v>
+        <v>178.28</v>
       </c>
       <c r="E7" t="n">
-        <v>184.24</v>
+        <v>186.19</v>
       </c>
       <c r="F7" t="n">
-        <v>75.81</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>77.94</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>74.19</v>
+        <v>77.16</v>
       </c>
       <c r="I7" t="n">
-        <v>77.23999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="K7" t="n">
-        <v>8.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>8.35</v>
+        <v>8.27</v>
       </c>
       <c r="N7" t="n">
-        <v>42.83</v>
+        <v>41.98</v>
       </c>
       <c r="O7" t="n">
-        <v>43.77</v>
+        <v>42.06</v>
       </c>
       <c r="P7" t="n">
-        <v>41.6</v>
+        <v>40.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.99</v>
+        <v>41.07</v>
       </c>
       <c r="R7" t="n">
-        <v>6.7934</v>
+        <v>1.0584</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1257</v>
+        <v>-2.2214</v>
       </c>
       <c r="T7" t="n">
-        <v>11.0883</v>
+        <v>22.4129</v>
       </c>
       <c r="U7" t="n">
-        <v>3.0416</v>
+        <v>2.2139</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2585</v>
+        <v>2.5858</v>
       </c>
       <c r="W7" t="n">
-        <v>7.9223</v>
+        <v>10.6672</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.7039</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y7" t="n">
-        <v>-5.6497</v>
+        <v>0.8537</v>
       </c>
       <c r="Z7" t="n">
-        <v>-14.8828</v>
+        <v>-21.9811</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.0478</v>
+        <v>-2.191</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.3625</v>
+        <v>-2.7238</v>
       </c>
       <c r="AC7" t="n">
-        <v>-7.8965</v>
+        <v>-10.1902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>182.67</v>
+        <v>167</v>
       </c>
       <c r="C8" t="n">
-        <v>189.56</v>
+        <v>174.4</v>
       </c>
       <c r="D8" t="n">
-        <v>178.28</v>
+        <v>161.14</v>
       </c>
       <c r="E8" t="n">
-        <v>186.19</v>
+        <v>164.18</v>
       </c>
       <c r="F8" t="n">
-        <v>77.29000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G8" t="n">
-        <v>79.68000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="H8" t="n">
-        <v>77.16</v>
+        <v>74.23</v>
       </c>
       <c r="I8" t="n">
-        <v>78.95</v>
+        <v>75.34</v>
       </c>
       <c r="J8" t="n">
-        <v>8.43</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>8.630000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>8.119999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>8.27</v>
+        <v>9.23</v>
       </c>
       <c r="N8" t="n">
-        <v>41.98</v>
+        <v>42.77</v>
       </c>
       <c r="O8" t="n">
-        <v>42.06</v>
+        <v>43.57</v>
       </c>
       <c r="P8" t="n">
-        <v>40.68</v>
+        <v>41.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.07</v>
+        <v>42.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0584</v>
+        <v>-11.8213</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.2214</v>
+        <v>-4.8342</v>
       </c>
       <c r="T8" t="n">
-        <v>22.4129</v>
+        <v>-7.2115</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2139</v>
+        <v>-4.5725</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5858</v>
+        <v>0.5069</v>
       </c>
       <c r="W8" t="n">
-        <v>10.6672</v>
+        <v>-1.2323</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9581</v>
+        <v>11.6082</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8537</v>
+        <v>3.1285</v>
       </c>
       <c r="Z8" t="n">
-        <v>-21.9811</v>
+        <v>4.2938</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2.191</v>
+        <v>4.6506</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.7238</v>
+        <v>-0.7619</v>
       </c>
       <c r="AC8" t="n">
-        <v>-10.1902</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>172.95</v>
       </c>
       <c r="C9" t="n">
-        <v>174.4</v>
+        <v>174.61</v>
       </c>
       <c r="D9" t="n">
-        <v>161.14</v>
+        <v>142.69</v>
       </c>
       <c r="E9" t="n">
-        <v>164.18</v>
+        <v>151.75</v>
       </c>
       <c r="F9" t="n">
-        <v>75.73</v>
+        <v>76.13</v>
       </c>
       <c r="G9" t="n">
-        <v>77.37</v>
+        <v>76.27</v>
       </c>
       <c r="H9" t="n">
-        <v>74.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>75.34</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K9" t="n">
-        <v>9.390000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M9" t="n">
-        <v>9.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>42.77</v>
+        <v>42.51</v>
       </c>
       <c r="O9" t="n">
-        <v>43.57</v>
+        <v>44.82</v>
       </c>
       <c r="P9" t="n">
-        <v>41.93</v>
+        <v>42.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>42.98</v>
+        <v>43.54</v>
       </c>
       <c r="R9" t="n">
-        <v>-11.8213</v>
+        <v>-7.571</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.8342</v>
+        <v>-17.6346</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.2115</v>
+        <v>-20.3077</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.5725</v>
+        <v>-1.3539</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5069</v>
+        <v>-3.7804</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.2323</v>
+        <v>-3.4304</v>
       </c>
       <c r="X9" t="n">
-        <v>11.6082</v>
+        <v>7.8007</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.1285</v>
+        <v>19.1617</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2938</v>
+        <v>21.3415</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.6506</v>
+        <v>1.3029</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.7619</v>
+        <v>3.6914</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.9631</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172.95</v>
+        <v>141.24</v>
       </c>
       <c r="C10" t="n">
-        <v>174.61</v>
+        <v>160.6</v>
       </c>
       <c r="D10" t="n">
-        <v>142.69</v>
+        <v>135.02</v>
       </c>
       <c r="E10" t="n">
-        <v>151.75</v>
+        <v>151.89</v>
       </c>
       <c r="F10" t="n">
-        <v>76.13</v>
+        <v>72.41</v>
       </c>
       <c r="G10" t="n">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="H10" t="n">
-        <v>72.09999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>74.31999999999999</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>8.77</v>
+        <v>10.64</v>
       </c>
       <c r="K10" t="n">
-        <v>10.47</v>
+        <v>11.07</v>
       </c>
       <c r="L10" t="n">
-        <v>8.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="N10" t="n">
-        <v>42.51</v>
+        <v>44.68</v>
       </c>
       <c r="O10" t="n">
-        <v>44.82</v>
+        <v>45.53</v>
       </c>
       <c r="P10" t="n">
-        <v>42.44</v>
+        <v>43.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>43.54</v>
+        <v>44.37</v>
       </c>
       <c r="R10" t="n">
-        <v>-7.571</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-17.6346</v>
+        <v>-18.422</v>
       </c>
       <c r="T10" t="n">
-        <v>-20.3077</v>
+        <v>-11.958</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3539</v>
+        <v>-1.8703</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.7804</v>
+        <v>-7.6251</v>
       </c>
       <c r="W10" t="n">
-        <v>-3.4304</v>
+        <v>-2.7081</v>
       </c>
       <c r="X10" t="n">
-        <v>7.8007</v>
+        <v>-0.201</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.1617</v>
+        <v>20.0726</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.3415</v>
+        <v>10.9497</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3029</v>
+        <v>1.9063</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6914</v>
+        <v>8.0351</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1265</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141.24</v>
+        <v>161</v>
       </c>
       <c r="C11" t="n">
-        <v>160.6</v>
+        <v>173.7</v>
       </c>
       <c r="D11" t="n">
-        <v>135.02</v>
+        <v>161</v>
       </c>
       <c r="E11" t="n">
-        <v>151.89</v>
+        <v>173.2</v>
       </c>
       <c r="F11" t="n">
-        <v>72.41</v>
+        <v>74.09</v>
       </c>
       <c r="G11" t="n">
-        <v>74.5</v>
+        <v>76.53</v>
       </c>
       <c r="H11" t="n">
-        <v>70.95999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="I11" t="n">
-        <v>72.93000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>10.64</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>11.07</v>
+        <v>9.35</v>
       </c>
       <c r="L11" t="n">
-        <v>9.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M11" t="n">
-        <v>9.93</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>44.68</v>
+        <v>43.67</v>
       </c>
       <c r="O11" t="n">
-        <v>45.53</v>
+        <v>43.97</v>
       </c>
       <c r="P11" t="n">
-        <v>43.46</v>
+        <v>42.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>44.37</v>
+        <v>42.19</v>
       </c>
       <c r="R11" t="n">
-        <v>0.09229999999999999</v>
+        <v>14.0299</v>
       </c>
       <c r="S11" t="n">
-        <v>-18.422</v>
+        <v>5.494</v>
       </c>
       <c r="T11" t="n">
-        <v>-11.958</v>
+        <v>-5.9922</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8703</v>
+        <v>4.9088</v>
       </c>
       <c r="V11" t="n">
-        <v>-7.6251</v>
+        <v>1.553</v>
       </c>
       <c r="W11" t="n">
-        <v>-2.7081</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.201</v>
+        <v>-13.998</v>
       </c>
       <c r="Y11" t="n">
-        <v>20.0726</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.9497</v>
+        <v>2.2754</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9063</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.0351</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4475</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>161</v>
+        <v>171.26</v>
       </c>
       <c r="C12" t="n">
-        <v>173.7</v>
+        <v>179.97</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>168.23</v>
       </c>
       <c r="E12" t="n">
-        <v>173.2</v>
+        <v>178.39</v>
       </c>
       <c r="F12" t="n">
-        <v>74.09</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>73.62</v>
+        <v>74.47</v>
       </c>
       <c r="I12" t="n">
-        <v>76.51000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="J12" t="n">
-        <v>9.300000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="K12" t="n">
-        <v>9.35</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>8.51</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>8.539999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>43.67</v>
+        <v>42.94</v>
       </c>
       <c r="O12" t="n">
-        <v>43.97</v>
+        <v>43.33</v>
       </c>
       <c r="P12" t="n">
-        <v>42.19</v>
+        <v>41.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>42.19</v>
+        <v>41.96</v>
       </c>
       <c r="R12" t="n">
-        <v>14.0299</v>
+        <v>2.9965</v>
       </c>
       <c r="S12" t="n">
-        <v>5.494</v>
+        <v>17.5552</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.9922</v>
+        <v>-4.1893</v>
       </c>
       <c r="U12" t="n">
-        <v>4.9088</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>1.553</v>
+        <v>3.5388</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-2.5332</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.998</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y12" t="n">
-        <v>-7.4756</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2754</v>
+        <v>0.2418</v>
       </c>
       <c r="AA12" t="n">
-        <v>-4.9132</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.8381</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.4763</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>171.26</v>
+        <v>184.8</v>
       </c>
       <c r="C13" t="n">
-        <v>179.97</v>
+        <v>195.27</v>
       </c>
       <c r="D13" t="n">
-        <v>168.23</v>
+        <v>183.34</v>
       </c>
       <c r="E13" t="n">
-        <v>178.39</v>
+        <v>190.56</v>
       </c>
       <c r="F13" t="n">
-        <v>75.18000000000001</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>77.79000000000001</v>
+        <v>79.33</v>
       </c>
       <c r="H13" t="n">
-        <v>74.47</v>
+        <v>77.33</v>
       </c>
       <c r="I13" t="n">
-        <v>76.95</v>
+        <v>77.84</v>
       </c>
       <c r="J13" t="n">
-        <v>8.65</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>8.779999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="L13" t="n">
-        <v>8.210000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="M13" t="n">
-        <v>8.289999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="N13" t="n">
-        <v>42.94</v>
+        <v>41.4</v>
       </c>
       <c r="O13" t="n">
-        <v>43.33</v>
+        <v>41.78</v>
       </c>
       <c r="P13" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="Q13" t="n">
         <v>41.5</v>
       </c>
-      <c r="Q13" t="n">
-        <v>41.96</v>
-      </c>
       <c r="R13" t="n">
-        <v>2.9965</v>
+        <v>6.8221</v>
       </c>
       <c r="S13" t="n">
-        <v>17.5552</v>
+        <v>25.4592</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.1893</v>
+        <v>16.0677</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5750999999999999</v>
+        <v>1.1566</v>
       </c>
       <c r="V13" t="n">
-        <v>3.5388</v>
+        <v>6.7325</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.5332</v>
+        <v>3.3183</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.9274</v>
+        <v>-6.7551</v>
       </c>
       <c r="Y13" t="n">
-        <v>-16.6834</v>
+        <v>-22.1551</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2418</v>
+        <v>-16.2514</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.5452</v>
+        <v>-1.0963</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.6288</v>
+        <v>-6.4683</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.167</v>
+        <v>-3.4435</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>184.8</v>
+        <v>211.38</v>
       </c>
       <c r="C14" t="n">
-        <v>195.27</v>
+        <v>228.5</v>
       </c>
       <c r="D14" t="n">
-        <v>183.34</v>
+        <v>209.89</v>
       </c>
       <c r="E14" t="n">
-        <v>190.56</v>
+        <v>225.79</v>
       </c>
       <c r="F14" t="n">
-        <v>78.04000000000001</v>
+        <v>80.59</v>
       </c>
       <c r="G14" t="n">
-        <v>79.33</v>
+        <v>82.27</v>
       </c>
       <c r="H14" t="n">
-        <v>77.33</v>
+        <v>79.98</v>
       </c>
       <c r="I14" t="n">
-        <v>77.84</v>
+        <v>81.95</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="K14" t="n">
-        <v>8.06</v>
+        <v>6.95</v>
       </c>
       <c r="L14" t="n">
-        <v>7.5</v>
+        <v>6.19</v>
       </c>
       <c r="M14" t="n">
-        <v>7.73</v>
+        <v>6.29</v>
       </c>
       <c r="N14" t="n">
-        <v>41.4</v>
+        <v>40.05</v>
       </c>
       <c r="O14" t="n">
-        <v>41.78</v>
+        <v>40.35</v>
       </c>
       <c r="P14" t="n">
-        <v>40.68</v>
+        <v>39.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.5</v>
+        <v>39.28</v>
       </c>
       <c r="R14" t="n">
-        <v>6.8221</v>
+        <v>18.4876</v>
       </c>
       <c r="S14" t="n">
-        <v>25.4592</v>
+        <v>30.3637</v>
       </c>
       <c r="T14" t="n">
-        <v>16.0677</v>
+        <v>48.7908</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1566</v>
+        <v>5.2801</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7325</v>
+        <v>7.1102</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3183</v>
+        <v>10.2664</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.7551</v>
+        <v>-18.6287</v>
       </c>
       <c r="Y14" t="n">
-        <v>-22.1551</v>
+        <v>-26.3466</v>
       </c>
       <c r="Z14" t="n">
-        <v>-16.2514</v>
+        <v>-36.7839</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.0963</v>
+        <v>-5.3494</v>
       </c>
       <c r="AB14" t="n">
-        <v>-6.4683</v>
+        <v>-6.8974</v>
       </c>
       <c r="AC14" t="n">
-        <v>-3.4435</v>
+        <v>-9.7841</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>211.38</v>
+        <v>242.66</v>
       </c>
       <c r="C15" t="n">
-        <v>228.5</v>
+        <v>242.66</v>
       </c>
       <c r="D15" t="n">
-        <v>209.89</v>
+        <v>204</v>
       </c>
       <c r="E15" t="n">
-        <v>225.79</v>
+        <v>217.98</v>
       </c>
       <c r="F15" t="n">
-        <v>80.59</v>
+        <v>82.87</v>
       </c>
       <c r="G15" t="n">
-        <v>82.27</v>
+        <v>82.91</v>
       </c>
       <c r="H15" t="n">
-        <v>79.98</v>
+        <v>80.33</v>
       </c>
       <c r="I15" t="n">
-        <v>81.95</v>
+        <v>81.67</v>
       </c>
       <c r="J15" t="n">
-        <v>6.9</v>
+        <v>5.83</v>
       </c>
       <c r="K15" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="L15" t="n">
-        <v>6.19</v>
+        <v>5.83</v>
       </c>
       <c r="M15" t="n">
-        <v>6.29</v>
+        <v>6.53</v>
       </c>
       <c r="N15" t="n">
-        <v>40.05</v>
+        <v>38.87</v>
       </c>
       <c r="O15" t="n">
-        <v>40.35</v>
+        <v>40.09</v>
       </c>
       <c r="P15" t="n">
-        <v>39.14</v>
+        <v>38.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>39.28</v>
+        <v>39.44</v>
       </c>
       <c r="R15" t="n">
-        <v>18.4876</v>
+        <v>-3.459</v>
       </c>
       <c r="S15" t="n">
-        <v>30.3637</v>
+        <v>22.1929</v>
       </c>
       <c r="T15" t="n">
-        <v>48.7908</v>
+        <v>43.5118</v>
       </c>
       <c r="U15" t="n">
-        <v>5.2801</v>
+        <v>-0.3417</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1102</v>
+        <v>6.1339</v>
       </c>
       <c r="W15" t="n">
-        <v>10.2664</v>
+        <v>11.9841</v>
       </c>
       <c r="X15" t="n">
-        <v>-18.6287</v>
+        <v>3.8156</v>
       </c>
       <c r="Y15" t="n">
-        <v>-26.3466</v>
+        <v>-21.2304</v>
       </c>
       <c r="Z15" t="n">
-        <v>-36.7839</v>
+        <v>-34.2397</v>
       </c>
       <c r="AA15" t="n">
-        <v>-5.3494</v>
+        <v>0.4073</v>
       </c>
       <c r="AB15" t="n">
-        <v>-6.8974</v>
+        <v>-6.0057</v>
       </c>
       <c r="AC15" t="n">
-        <v>-9.7841</v>
+        <v>-11.1111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>242.66</v>
+        <v>219</v>
       </c>
       <c r="C16" t="n">
-        <v>242.66</v>
+        <v>231.89</v>
       </c>
       <c r="D16" t="n">
-        <v>204</v>
+        <v>207.56</v>
       </c>
       <c r="E16" t="n">
-        <v>217.98</v>
+        <v>224.63</v>
       </c>
       <c r="F16" t="n">
-        <v>82.87</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>82.91</v>
+        <v>84.05</v>
       </c>
       <c r="H16" t="n">
-        <v>80.33</v>
+        <v>80.66</v>
       </c>
       <c r="I16" t="n">
-        <v>81.67</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>5.83</v>
+        <v>6.49</v>
       </c>
       <c r="K16" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="L16" t="n">
-        <v>5.83</v>
+        <v>6.1</v>
       </c>
       <c r="M16" t="n">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
       <c r="N16" t="n">
-        <v>38.87</v>
+        <v>39.41</v>
       </c>
       <c r="O16" t="n">
-        <v>40.09</v>
+        <v>39.94</v>
       </c>
       <c r="P16" t="n">
-        <v>38.86</v>
+        <v>38.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>39.44</v>
+        <v>38.47</v>
       </c>
       <c r="R16" t="n">
-        <v>-3.459</v>
+        <v>3.0507</v>
       </c>
       <c r="S16" t="n">
-        <v>22.1929</v>
+        <v>17.8789</v>
       </c>
       <c r="T16" t="n">
-        <v>43.5118</v>
+        <v>29.694</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3417</v>
+        <v>2.4611</v>
       </c>
       <c r="V16" t="n">
-        <v>6.1339</v>
+        <v>7.5026</v>
       </c>
       <c r="W16" t="n">
-        <v>11.9841</v>
+        <v>9.3713</v>
       </c>
       <c r="X16" t="n">
-        <v>3.8156</v>
+        <v>-3.3691</v>
       </c>
       <c r="Y16" t="n">
-        <v>-21.2304</v>
+        <v>-18.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>-34.2397</v>
+        <v>-26.1124</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.4073</v>
+        <v>-2.4594</v>
       </c>
       <c r="AB16" t="n">
-        <v>-6.0057</v>
+        <v>-7.3012</v>
       </c>
       <c r="AC16" t="n">
-        <v>-11.1111</v>
+        <v>-8.817299999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>219</v>
+        <v>231.82</v>
       </c>
       <c r="C17" t="n">
-        <v>231.89</v>
+        <v>239.07</v>
       </c>
       <c r="D17" t="n">
-        <v>207.56</v>
+        <v>218.56</v>
       </c>
       <c r="E17" t="n">
-        <v>224.63</v>
+        <v>224.34</v>
       </c>
       <c r="F17" t="n">
-        <v>81.73999999999999</v>
+        <v>84.41</v>
       </c>
       <c r="G17" t="n">
-        <v>84.05</v>
+        <v>85.7</v>
       </c>
       <c r="H17" t="n">
-        <v>80.66</v>
+        <v>83.53</v>
       </c>
       <c r="I17" t="n">
-        <v>83.68000000000001</v>
+        <v>84.56</v>
       </c>
       <c r="J17" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="K17" t="n">
         <v>6.49</v>
       </c>
-      <c r="K17" t="n">
-        <v>6.83</v>
-      </c>
       <c r="L17" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="M17" t="n">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
       <c r="N17" t="n">
-        <v>39.41</v>
+        <v>38.15</v>
       </c>
       <c r="O17" t="n">
-        <v>39.94</v>
+        <v>38.56</v>
       </c>
       <c r="P17" t="n">
-        <v>38.3</v>
+        <v>37.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>38.47</v>
+        <v>38.08</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0507</v>
+        <v>-0.1291</v>
       </c>
       <c r="S17" t="n">
-        <v>17.8789</v>
+        <v>-0.6422</v>
       </c>
       <c r="T17" t="n">
-        <v>29.694</v>
+        <v>25.7582</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4611</v>
+        <v>1.0516</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5026</v>
+        <v>3.1849</v>
       </c>
       <c r="W17" t="n">
-        <v>9.3713</v>
+        <v>9.8895</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.3691</v>
+        <v>0.317</v>
       </c>
       <c r="Y17" t="n">
-        <v>-18.37</v>
+        <v>0.6359</v>
       </c>
       <c r="Z17" t="n">
-        <v>-26.1124</v>
+        <v>-23.6429</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.4594</v>
+        <v>-1.0138</v>
       </c>
       <c r="AB17" t="n">
-        <v>-7.3012</v>
+        <v>-3.055</v>
       </c>
       <c r="AC17" t="n">
-        <v>-8.817299999999999</v>
+        <v>-9.2469</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>231.82</v>
+        <v>217.27</v>
       </c>
       <c r="C18" t="n">
-        <v>239.07</v>
+        <v>234.06</v>
       </c>
       <c r="D18" t="n">
-        <v>218.56</v>
+        <v>210.14</v>
       </c>
       <c r="E18" t="n">
-        <v>224.34</v>
+        <v>227.03</v>
       </c>
       <c r="F18" t="n">
-        <v>84.41</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>85.7</v>
+        <v>87.06</v>
       </c>
       <c r="H18" t="n">
-        <v>83.53</v>
+        <v>83.75</v>
       </c>
       <c r="I18" t="n">
-        <v>84.56</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>6.11</v>
+        <v>6.55</v>
       </c>
       <c r="K18" t="n">
-        <v>6.49</v>
+        <v>6.74</v>
       </c>
       <c r="L18" t="n">
-        <v>5.91</v>
+        <v>6.05</v>
       </c>
       <c r="M18" t="n">
-        <v>6.33</v>
+        <v>6.26</v>
       </c>
       <c r="N18" t="n">
-        <v>38.15</v>
+        <v>38.27</v>
       </c>
       <c r="O18" t="n">
-        <v>38.56</v>
+        <v>38.46</v>
       </c>
       <c r="P18" t="n">
-        <v>37.56</v>
+        <v>36.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.08</v>
+        <v>37.42</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.1291</v>
+        <v>1.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6422</v>
+        <v>4.1518</v>
       </c>
       <c r="T18" t="n">
-        <v>25.7582</v>
+        <v>19.1383</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0516</v>
+        <v>1.7502</v>
       </c>
       <c r="V18" t="n">
-        <v>3.1849</v>
+        <v>5.3508</v>
       </c>
       <c r="W18" t="n">
-        <v>9.8895</v>
+        <v>10.5344</v>
       </c>
       <c r="X18" t="n">
-        <v>0.317</v>
+        <v>-1.1058</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.6359</v>
+        <v>-4.1348</v>
       </c>
       <c r="Z18" t="n">
-        <v>-23.6429</v>
+        <v>-19.0168</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1.0138</v>
+        <v>-1.7332</v>
       </c>
       <c r="AB18" t="n">
-        <v>-3.055</v>
+        <v>-5.1217</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.2469</v>
+        <v>-9.831300000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>217.27</v>
+        <v>243.18</v>
       </c>
       <c r="C19" t="n">
-        <v>234.06</v>
+        <v>267.08</v>
       </c>
       <c r="D19" t="n">
-        <v>210.14</v>
+        <v>238.82</v>
       </c>
       <c r="E19" t="n">
-        <v>227.03</v>
+        <v>266.32</v>
       </c>
       <c r="F19" t="n">
-        <v>84.15000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="G19" t="n">
-        <v>87.06</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>83.75</v>
+        <v>84.83</v>
       </c>
       <c r="I19" t="n">
-        <v>86.04000000000001</v>
+        <v>87.22</v>
       </c>
       <c r="J19" t="n">
-        <v>6.55</v>
+        <v>5.8</v>
       </c>
       <c r="K19" t="n">
-        <v>6.74</v>
+        <v>5.93</v>
       </c>
       <c r="L19" t="n">
-        <v>6.05</v>
+        <v>5.15</v>
       </c>
       <c r="M19" t="n">
-        <v>6.26</v>
+        <v>5.17</v>
       </c>
       <c r="N19" t="n">
-        <v>38.27</v>
+        <v>37.47</v>
       </c>
       <c r="O19" t="n">
-        <v>38.46</v>
+        <v>37.95</v>
       </c>
       <c r="P19" t="n">
-        <v>36.96</v>
+        <v>36.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.42</v>
+        <v>36.91</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1991</v>
+        <v>17.3061</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1518</v>
+        <v>18.5594</v>
       </c>
       <c r="T19" t="n">
-        <v>19.1383</v>
+        <v>17.9503</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7502</v>
+        <v>1.3715</v>
       </c>
       <c r="V19" t="n">
-        <v>5.3508</v>
+        <v>4.2304</v>
       </c>
       <c r="W19" t="n">
-        <v>10.5344</v>
+        <v>6.4308</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1058</v>
+        <v>-17.4121</v>
       </c>
       <c r="Y19" t="n">
-        <v>-4.1348</v>
+        <v>-18.0666</v>
       </c>
       <c r="Z19" t="n">
-        <v>-19.0168</v>
+        <v>-17.806</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.7332</v>
+        <v>-1.3629</v>
       </c>
       <c r="AB19" t="n">
-        <v>-5.1217</v>
+        <v>-4.0551</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.831300000000001</v>
+        <v>-6.0336</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>243.18</v>
+        <v>281.47</v>
       </c>
       <c r="C20" t="n">
-        <v>267.08</v>
+        <v>284.58</v>
       </c>
       <c r="D20" t="n">
-        <v>238.82</v>
+        <v>257.26</v>
       </c>
       <c r="E20" t="n">
-        <v>266.32</v>
+        <v>280.54</v>
       </c>
       <c r="F20" t="n">
-        <v>85.94</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>87.31999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="H20" t="n">
-        <v>84.83</v>
+        <v>85.41</v>
       </c>
       <c r="I20" t="n">
-        <v>87.22</v>
+        <v>86.56</v>
       </c>
       <c r="J20" t="n">
-        <v>5.8</v>
+        <v>4.88</v>
       </c>
       <c r="K20" t="n">
-        <v>5.93</v>
+        <v>5.35</v>
       </c>
       <c r="L20" t="n">
-        <v>5.15</v>
+        <v>4.82</v>
       </c>
       <c r="M20" t="n">
-        <v>5.17</v>
+        <v>4.91</v>
       </c>
       <c r="N20" t="n">
-        <v>37.47</v>
+        <v>36.73</v>
       </c>
       <c r="O20" t="n">
-        <v>37.95</v>
+        <v>37.69</v>
       </c>
       <c r="P20" t="n">
-        <v>36.86</v>
+        <v>36.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>36.91</v>
+        <v>37.19</v>
       </c>
       <c r="R20" t="n">
-        <v>17.3061</v>
+        <v>5.3394</v>
       </c>
       <c r="S20" t="n">
-        <v>18.5594</v>
+        <v>25.0513</v>
       </c>
       <c r="T20" t="n">
-        <v>17.9503</v>
+        <v>28.6999</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3715</v>
+        <v>-0.7567</v>
       </c>
       <c r="V20" t="n">
-        <v>4.2304</v>
+        <v>2.3652</v>
       </c>
       <c r="W20" t="n">
-        <v>6.4308</v>
+        <v>5.9875</v>
       </c>
       <c r="X20" t="n">
-        <v>-17.4121</v>
+        <v>-5.029</v>
       </c>
       <c r="Y20" t="n">
-        <v>-18.0666</v>
+        <v>-22.4329</v>
       </c>
       <c r="Z20" t="n">
-        <v>-17.806</v>
+        <v>-24.8086</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.3629</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.0551</v>
+        <v>-2.3372</v>
       </c>
       <c r="AC20" t="n">
-        <v>-6.0336</v>
+        <v>-5.7049</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>281.47</v>
+        <v>242.04</v>
       </c>
       <c r="C21" t="n">
-        <v>284.58</v>
+        <v>274.5</v>
       </c>
       <c r="D21" t="n">
-        <v>257.26</v>
+        <v>228.55</v>
       </c>
       <c r="E21" t="n">
-        <v>280.54</v>
+        <v>262.7</v>
       </c>
       <c r="F21" t="n">
-        <v>87.68000000000001</v>
+        <v>83.47</v>
       </c>
       <c r="G21" t="n">
-        <v>88.09</v>
+        <v>86.25</v>
       </c>
       <c r="H21" t="n">
-        <v>85.41</v>
+        <v>82.48</v>
       </c>
       <c r="I21" t="n">
-        <v>86.56</v>
+        <v>85.22</v>
       </c>
       <c r="J21" t="n">
-        <v>4.88</v>
+        <v>5.57</v>
       </c>
       <c r="K21" t="n">
-        <v>5.35</v>
+        <v>5.81</v>
       </c>
       <c r="L21" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.91</v>
+        <v>5.2</v>
       </c>
       <c r="N21" t="n">
-        <v>36.73</v>
+        <v>38.53</v>
       </c>
       <c r="O21" t="n">
-        <v>37.69</v>
+        <v>38.96</v>
       </c>
       <c r="P21" t="n">
-        <v>36.55</v>
+        <v>37.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.19</v>
+        <v>37.76</v>
       </c>
       <c r="R21" t="n">
-        <v>5.3394</v>
+        <v>-6.3592</v>
       </c>
       <c r="S21" t="n">
-        <v>25.0513</v>
+        <v>15.7116</v>
       </c>
       <c r="T21" t="n">
-        <v>28.6999</v>
+        <v>16.9479</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7567</v>
+        <v>-1.5481</v>
       </c>
       <c r="V21" t="n">
-        <v>2.3652</v>
+        <v>-0.953</v>
       </c>
       <c r="W21" t="n">
-        <v>5.9875</v>
+        <v>1.8403</v>
       </c>
       <c r="X21" t="n">
-        <v>-5.029</v>
+        <v>5.9063</v>
       </c>
       <c r="Y21" t="n">
-        <v>-22.4329</v>
+        <v>-16.9329</v>
       </c>
       <c r="Z21" t="n">
-        <v>-24.8086</v>
+        <v>-17.5911</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.5327</v>
       </c>
       <c r="AB21" t="n">
-        <v>-2.3372</v>
+        <v>0.9086</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.7049</v>
+        <v>-1.8456</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>242.04</v>
+        <v>230.8482</v>
       </c>
       <c r="C22" t="n">
-        <v>274.5</v>
+        <v>233.69</v>
       </c>
       <c r="D22" t="n">
-        <v>228.55</v>
+        <v>182.0033</v>
       </c>
       <c r="E22" t="n">
-        <v>262.7</v>
+        <v>182.54</v>
       </c>
       <c r="F22" t="n">
-        <v>83.47</v>
+        <v>81.55</v>
       </c>
       <c r="G22" t="n">
-        <v>86.245</v>
+        <v>82.08</v>
       </c>
       <c r="H22" t="n">
-        <v>82.47499999999999</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>85.22</v>
+        <v>73.05</v>
       </c>
       <c r="J22" t="n">
-        <v>5.57</v>
+        <v>5.855</v>
       </c>
       <c r="K22" t="n">
-        <v>5.81</v>
+        <v>6.85</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>5.79</v>
       </c>
       <c r="M22" t="n">
-        <v>5.2</v>
+        <v>6.84</v>
       </c>
       <c r="N22" t="n">
-        <v>38.53</v>
+        <v>39.45</v>
       </c>
       <c r="O22" t="n">
-        <v>38.96</v>
+        <v>43.35</v>
       </c>
       <c r="P22" t="n">
-        <v>37.33</v>
+        <v>39.185</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.76</v>
+        <v>43.19</v>
       </c>
       <c r="R22" t="n">
-        <v>-6.3592</v>
+        <v>-30.5139</v>
       </c>
       <c r="S22" t="n">
-        <v>15.7116</v>
+        <v>-31.4584</v>
       </c>
       <c r="T22" t="n">
-        <v>16.9479</v>
+        <v>-18.6324</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5481</v>
+        <v>-14.2807</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.953</v>
+        <v>-16.2463</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8403</v>
+        <v>-13.6116</v>
       </c>
       <c r="X22" t="n">
-        <v>5.9063</v>
+        <v>31.5385</v>
       </c>
       <c r="Y22" t="n">
-        <v>-16.9329</v>
+        <v>32.3017</v>
       </c>
       <c r="Z22" t="n">
-        <v>-17.5911</v>
+        <v>8.056900000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5327</v>
+        <v>14.3803</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9086</v>
+        <v>17.0144</v>
       </c>
       <c r="AC22" t="n">
-        <v>-1.8456</v>
+        <v>13.4191</v>
       </c>
     </row>
   </sheetData>

--- a/4_ETF_Trading_Workbook_Template.xlsx
+++ b/4_ETF_Trading_Workbook_Template.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24759,1804 +24759,1713 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>162.12</v>
+        <v>181</v>
       </c>
       <c r="C2" t="n">
-        <v>162.9</v>
+        <v>191.29</v>
       </c>
       <c r="D2" t="n">
-        <v>147.61</v>
+        <v>178.94</v>
       </c>
       <c r="E2" t="n">
-        <v>152.1</v>
+        <v>190.42</v>
       </c>
       <c r="F2" t="n">
-        <v>71.87</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>73.3</v>
+        <v>77.36</v>
       </c>
       <c r="H2" t="n">
-        <v>70.38</v>
+        <v>75.55</v>
       </c>
       <c r="I2" t="n">
-        <v>71.34</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>10.02</v>
+        <v>8.65</v>
       </c>
       <c r="K2" t="n">
-        <v>10.88</v>
+        <v>8.77</v>
       </c>
       <c r="L2" t="n">
-        <v>9.970000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="M2" t="n">
-        <v>10.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>45.41</v>
+        <v>42.74</v>
       </c>
       <c r="O2" t="n">
-        <v>46.36</v>
+        <v>43</v>
       </c>
       <c r="P2" t="n">
-        <v>44.5</v>
+        <v>41.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>45.73</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>163</v>
+        <v>177.62</v>
       </c>
       <c r="C3" t="n">
-        <v>177.5</v>
+        <v>182.24</v>
       </c>
       <c r="D3" t="n">
-        <v>161.51</v>
+        <v>150.58</v>
       </c>
       <c r="E3" t="n">
-        <v>176.94</v>
+        <v>172.52</v>
       </c>
       <c r="F3" t="n">
-        <v>72.81999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="G3" t="n">
-        <v>76.31</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>72.7</v>
+        <v>71.55</v>
       </c>
       <c r="I3" t="n">
-        <v>76.28</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>9.859999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="K3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="L3" t="n">
-        <v>8.84</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>8.85</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>44.82</v>
+        <v>43.14</v>
       </c>
       <c r="O3" t="n">
-        <v>44.89</v>
+        <v>45.19</v>
       </c>
       <c r="P3" t="n">
-        <v>42.57</v>
+        <v>42.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>42.57</v>
+        <v>43.31</v>
       </c>
       <c r="R3" t="n">
-        <v>16.3314</v>
+        <v>-9.4003</v>
       </c>
       <c r="U3" t="n">
-        <v>6.9246</v>
+        <v>-2.5988</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.5094</v>
+        <v>9.1463</v>
       </c>
       <c r="AA3" t="n">
-        <v>-6.9101</v>
+        <v>2.5817</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>181</v>
+        <v>183.84</v>
       </c>
       <c r="C4" t="n">
-        <v>191.29</v>
+        <v>188.49</v>
       </c>
       <c r="D4" t="n">
-        <v>178.94</v>
+        <v>172.26</v>
       </c>
       <c r="E4" t="n">
-        <v>190.42</v>
+        <v>184.24</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>75.81</v>
       </c>
       <c r="G4" t="n">
-        <v>77.36</v>
+        <v>77.94</v>
       </c>
       <c r="H4" t="n">
-        <v>75.55</v>
+        <v>74.19</v>
       </c>
       <c r="I4" t="n">
-        <v>76.95999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>8.65</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>8.77</v>
+        <v>8.98</v>
       </c>
       <c r="L4" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N4" t="n">
-        <v>42.74</v>
+        <v>42.83</v>
       </c>
       <c r="O4" t="n">
-        <v>43</v>
+        <v>43.77</v>
       </c>
       <c r="P4" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="Q4" t="n">
         <v>41.99</v>
       </c>
-      <c r="Q4" t="n">
-        <v>42.22</v>
-      </c>
       <c r="R4" t="n">
-        <v>7.6184</v>
+        <v>6.7934</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8915</v>
+        <v>3.0416</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.3446</v>
+        <v>-6.7039</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.8222</v>
+        <v>-3.0478</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>177.62</v>
+        <v>182.67</v>
       </c>
       <c r="C5" t="n">
-        <v>182.24</v>
+        <v>189.56</v>
       </c>
       <c r="D5" t="n">
-        <v>150.58</v>
+        <v>178.28</v>
       </c>
       <c r="E5" t="n">
-        <v>172.52</v>
+        <v>186.19</v>
       </c>
       <c r="F5" t="n">
-        <v>75.3</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>75.93000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>71.55</v>
+        <v>77.16</v>
       </c>
       <c r="I5" t="n">
-        <v>74.95999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="J5" t="n">
-        <v>8.75</v>
+        <v>8.43</v>
       </c>
       <c r="K5" t="n">
-        <v>9.91</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>8.550000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>8.949999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="N5" t="n">
-        <v>43.14</v>
+        <v>41.98</v>
       </c>
       <c r="O5" t="n">
-        <v>45.19</v>
+        <v>42.06</v>
       </c>
       <c r="P5" t="n">
-        <v>42.79</v>
+        <v>40.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>43.31</v>
+        <v>41.07</v>
       </c>
       <c r="R5" t="n">
-        <v>-9.4003</v>
+        <v>1.0584</v>
       </c>
       <c r="S5" t="n">
-        <v>13.4254</v>
+        <v>-2.2214</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.5988</v>
+        <v>2.2139</v>
       </c>
       <c r="V5" t="n">
-        <v>5.0743</v>
+        <v>2.5858</v>
       </c>
       <c r="X5" t="n">
-        <v>9.1463</v>
+        <v>-0.9581</v>
       </c>
       <c r="Y5" t="n">
-        <v>-15.566</v>
+        <v>0.8537</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.5817</v>
+        <v>-2.191</v>
       </c>
       <c r="AB5" t="n">
-        <v>-5.2919</v>
+        <v>-2.7238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>183.84</v>
+        <v>167</v>
       </c>
       <c r="C6" t="n">
-        <v>188.49</v>
+        <v>174.4</v>
       </c>
       <c r="D6" t="n">
-        <v>172.26</v>
+        <v>161.14</v>
       </c>
       <c r="E6" t="n">
-        <v>184.24</v>
+        <v>164.18</v>
       </c>
       <c r="F6" t="n">
-        <v>75.81</v>
+        <v>75.73</v>
       </c>
       <c r="G6" t="n">
-        <v>77.94</v>
+        <v>77.37</v>
       </c>
       <c r="H6" t="n">
-        <v>74.19</v>
+        <v>74.23</v>
       </c>
       <c r="I6" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="J6" t="n">
-        <v>8.380000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>8.98</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>8.140000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>8.35</v>
+        <v>9.23</v>
       </c>
       <c r="N6" t="n">
-        <v>42.83</v>
+        <v>42.77</v>
       </c>
       <c r="O6" t="n">
-        <v>43.77</v>
+        <v>43.57</v>
       </c>
       <c r="P6" t="n">
-        <v>41.6</v>
+        <v>41.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.99</v>
+        <v>42.98</v>
       </c>
       <c r="R6" t="n">
-        <v>6.7934</v>
+        <v>-11.8213</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1257</v>
+        <v>-4.8342</v>
       </c>
       <c r="U6" t="n">
-        <v>3.0416</v>
+        <v>-4.5725</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2585</v>
+        <v>0.5069</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.7039</v>
+        <v>11.6082</v>
       </c>
       <c r="Y6" t="n">
-        <v>-5.6497</v>
+        <v>3.1285</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.0478</v>
+        <v>4.6506</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.3625</v>
+        <v>-0.7619</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>182.67</v>
+        <v>172.95</v>
       </c>
       <c r="C7" t="n">
-        <v>189.56</v>
+        <v>174.61</v>
       </c>
       <c r="D7" t="n">
-        <v>178.28</v>
+        <v>142.69</v>
       </c>
       <c r="E7" t="n">
-        <v>186.19</v>
+        <v>151.75</v>
       </c>
       <c r="F7" t="n">
-        <v>77.29000000000001</v>
+        <v>76.13</v>
       </c>
       <c r="G7" t="n">
-        <v>79.68000000000001</v>
+        <v>76.27</v>
       </c>
       <c r="H7" t="n">
-        <v>77.16</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>78.95</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>8.43</v>
+        <v>8.77</v>
       </c>
       <c r="K7" t="n">
-        <v>8.630000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="L7" t="n">
-        <v>8.119999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="M7" t="n">
-        <v>8.27</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>41.98</v>
+        <v>42.51</v>
       </c>
       <c r="O7" t="n">
-        <v>42.06</v>
+        <v>44.82</v>
       </c>
       <c r="P7" t="n">
-        <v>40.68</v>
+        <v>42.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.07</v>
+        <v>43.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0584</v>
+        <v>-7.571</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2214</v>
+        <v>-17.6346</v>
       </c>
       <c r="T7" t="n">
-        <v>22.4129</v>
+        <v>-20.3077</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2139</v>
+        <v>-1.3539</v>
       </c>
       <c r="V7" t="n">
-        <v>2.5858</v>
+        <v>-3.7804</v>
       </c>
       <c r="W7" t="n">
-        <v>10.6672</v>
+        <v>-3.4304</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9581</v>
+        <v>7.8007</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8537</v>
+        <v>19.1617</v>
       </c>
       <c r="Z7" t="n">
-        <v>-21.9811</v>
+        <v>21.3415</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.191</v>
+        <v>1.3029</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.7238</v>
+        <v>3.6914</v>
       </c>
       <c r="AC7" t="n">
-        <v>-10.1902</v>
+        <v>3.1265</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>141.24</v>
       </c>
       <c r="C8" t="n">
-        <v>174.4</v>
+        <v>160.6</v>
       </c>
       <c r="D8" t="n">
-        <v>161.14</v>
+        <v>135.02</v>
       </c>
       <c r="E8" t="n">
-        <v>164.18</v>
+        <v>151.89</v>
       </c>
       <c r="F8" t="n">
-        <v>75.73</v>
+        <v>72.41</v>
       </c>
       <c r="G8" t="n">
-        <v>77.37</v>
+        <v>74.5</v>
       </c>
       <c r="H8" t="n">
-        <v>74.23</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>75.34</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>9.130000000000001</v>
+        <v>10.64</v>
       </c>
       <c r="K8" t="n">
-        <v>9.390000000000001</v>
+        <v>11.07</v>
       </c>
       <c r="L8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>9.23</v>
+        <v>9.93</v>
       </c>
       <c r="N8" t="n">
-        <v>42.77</v>
+        <v>44.68</v>
       </c>
       <c r="O8" t="n">
-        <v>43.57</v>
+        <v>45.53</v>
       </c>
       <c r="P8" t="n">
-        <v>41.93</v>
+        <v>43.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>42.98</v>
+        <v>44.37</v>
       </c>
       <c r="R8" t="n">
-        <v>-11.8213</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.8342</v>
+        <v>-18.422</v>
       </c>
       <c r="T8" t="n">
-        <v>-7.2115</v>
+        <v>-11.958</v>
       </c>
       <c r="U8" t="n">
-        <v>-4.5725</v>
+        <v>-1.8703</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5069</v>
+        <v>-7.6251</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.2323</v>
+        <v>-2.7081</v>
       </c>
       <c r="X8" t="n">
-        <v>11.6082</v>
+        <v>-0.201</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.1285</v>
+        <v>20.0726</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2938</v>
+        <v>10.9497</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.6506</v>
+        <v>1.9063</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.7619</v>
+        <v>8.0351</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.9631</v>
+        <v>2.4475</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>172.95</v>
+        <v>161</v>
       </c>
       <c r="C9" t="n">
-        <v>174.61</v>
+        <v>173.7</v>
       </c>
       <c r="D9" t="n">
-        <v>142.69</v>
+        <v>161</v>
       </c>
       <c r="E9" t="n">
-        <v>151.75</v>
+        <v>173.2</v>
       </c>
       <c r="F9" t="n">
-        <v>76.13</v>
+        <v>74.09</v>
       </c>
       <c r="G9" t="n">
-        <v>76.27</v>
+        <v>76.53</v>
       </c>
       <c r="H9" t="n">
-        <v>72.09999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="I9" t="n">
-        <v>74.31999999999999</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>8.77</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>10.47</v>
+        <v>9.35</v>
       </c>
       <c r="L9" t="n">
-        <v>8.68</v>
+        <v>8.51</v>
       </c>
       <c r="M9" t="n">
-        <v>9.949999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>42.51</v>
+        <v>43.67</v>
       </c>
       <c r="O9" t="n">
-        <v>44.82</v>
+        <v>43.97</v>
       </c>
       <c r="P9" t="n">
-        <v>42.44</v>
+        <v>42.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>43.54</v>
+        <v>42.19</v>
       </c>
       <c r="R9" t="n">
-        <v>-7.571</v>
+        <v>14.0299</v>
       </c>
       <c r="S9" t="n">
-        <v>-17.6346</v>
+        <v>5.494</v>
       </c>
       <c r="T9" t="n">
-        <v>-20.3077</v>
+        <v>-5.9922</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3539</v>
+        <v>4.9088</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.7804</v>
+        <v>1.553</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.4304</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>7.8007</v>
+        <v>-13.998</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.1617</v>
+        <v>-7.4756</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.3415</v>
+        <v>2.2754</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3029</v>
+        <v>-4.9132</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.6914</v>
+        <v>-1.8381</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1265</v>
+        <v>0.4763</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141.24</v>
+        <v>171.26</v>
       </c>
       <c r="C10" t="n">
-        <v>160.6</v>
+        <v>179.97</v>
       </c>
       <c r="D10" t="n">
-        <v>135.02</v>
+        <v>168.23</v>
       </c>
       <c r="E10" t="n">
-        <v>151.89</v>
+        <v>178.39</v>
       </c>
       <c r="F10" t="n">
-        <v>72.41</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>74.5</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>70.95999999999999</v>
+        <v>74.47</v>
       </c>
       <c r="I10" t="n">
-        <v>72.93000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="J10" t="n">
-        <v>10.64</v>
+        <v>8.65</v>
       </c>
       <c r="K10" t="n">
-        <v>11.07</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>9.369999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>9.93</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>44.68</v>
+        <v>42.94</v>
       </c>
       <c r="O10" t="n">
-        <v>45.53</v>
+        <v>43.33</v>
       </c>
       <c r="P10" t="n">
-        <v>43.46</v>
+        <v>41.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>44.37</v>
+        <v>41.96</v>
       </c>
       <c r="R10" t="n">
-        <v>0.09229999999999999</v>
+        <v>2.9965</v>
       </c>
       <c r="S10" t="n">
-        <v>-18.422</v>
+        <v>17.5552</v>
       </c>
       <c r="T10" t="n">
-        <v>-11.958</v>
+        <v>-4.1893</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.8703</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.6251</v>
+        <v>3.5388</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.7081</v>
+        <v>-2.5332</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.201</v>
+        <v>-2.9274</v>
       </c>
       <c r="Y10" t="n">
-        <v>20.0726</v>
+        <v>-16.6834</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.9497</v>
+        <v>0.2418</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9063</v>
+        <v>-0.5452</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.0351</v>
+        <v>-3.6288</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4475</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>161</v>
+        <v>184.8</v>
       </c>
       <c r="C11" t="n">
-        <v>173.7</v>
+        <v>195.27</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>183.34</v>
       </c>
       <c r="E11" t="n">
-        <v>173.2</v>
+        <v>190.56</v>
       </c>
       <c r="F11" t="n">
-        <v>74.09</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>76.53</v>
+        <v>79.33</v>
       </c>
       <c r="H11" t="n">
-        <v>73.62</v>
+        <v>77.33</v>
       </c>
       <c r="I11" t="n">
-        <v>76.51000000000001</v>
+        <v>77.84</v>
       </c>
       <c r="J11" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>9.35</v>
+        <v>8.06</v>
       </c>
       <c r="L11" t="n">
-        <v>8.51</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
-        <v>8.539999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="N11" t="n">
-        <v>43.67</v>
+        <v>41.4</v>
       </c>
       <c r="O11" t="n">
-        <v>43.97</v>
+        <v>41.78</v>
       </c>
     